--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V110"/>
+  <dimension ref="A1:V200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-001 变式1</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-001-V1</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-001 变式2</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-001-V2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-001 变式3</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-001-V3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-002 典例</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-002-E1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-002 变式1</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-002-V1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-002 变式2</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-002-V2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-002 变式3</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-002-V3</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-003 典例</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-003-E1</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-003 变式1</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-003-V1</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-003 变式2</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-003-V2</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-003 变式3</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-003-V3</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-004 变式1</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-004-V1</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-004 变式2</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-004-V2</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-004 变式3</t>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-004-V3</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-005 典例</t>
+          <t>2024热点题型归纳 M-T-005-E1</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-005 变式1</t>
+          <t>2024热点题型归纳 M-T-005-V1</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-005 变式2</t>
+          <t>2024热点题型归纳 M-T-005-V2</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-005 变式3</t>
+          <t>2024热点题型归纳 M-T-005-V3</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-006 典例</t>
+          <t>2024热点题型归纳 M-T-006-E1</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-006 变式1</t>
+          <t>2024热点题型归纳 M-T-006-V1</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-006 变式3</t>
+          <t>2024热点题型归纳 M-T-006-V3</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-007 典例</t>
+          <t>2024热点题型归纳 M-T-007-E1</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-007 变式1</t>
+          <t>2024热点题型归纳 M-T-007-V1</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-007 变式2</t>
+          <t>2024热点题型归纳 M-T-007-V2</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-007 变式3</t>
+          <t>2024热点题型归纳 M-T-007-V3</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-008 典例</t>
+          <t>2024热点题型归纳 M-T-008-E1</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-008 变式1</t>
+          <t>2024热点题型归纳 M-T-008-V1</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-008 变式2</t>
+          <t>2024热点题型归纳 M-T-008-V2</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-008 变式3</t>
+          <t>2024热点题型归纳 M-T-008-V3</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-009 典例</t>
+          <t>2024热点题型归纳 M-T-009-E1</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-009 变式4</t>
+          <t>2024热点题型归纳 M-T-009-V4</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-009 变式5</t>
+          <t>2024热点题型归纳 M-T-009-V5</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-009 变式6</t>
+          <t>2024热点题型归纳 M-T-009-V6</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-010 典例</t>
+          <t>2024热点题型归纳 M-T-010-E1</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-010 变式7</t>
+          <t>2024热点题型归纳 M-T-010-V7</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-010 变式8</t>
+          <t>2024热点题型归纳 M-T-010-V8</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-010 变式9</t>
+          <t>2024热点题型归纳 M-T-010-V9</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-011 典例</t>
+          <t>2024热点题型归纳 M-T-011-E1</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-011 变式10</t>
+          <t>2024热点题型归纳 M-T-011-V10</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-011 变式11</t>
+          <t>2024热点题型归纳 M-T-011-V11</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2024热点题型归纳 M-T-011 变式12</t>
+          <t>2024热点题型归纳 M-T-011-V12</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -10970,6 +10970,8394 @@
         </is>
       </c>
       <c r="V110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>M-H0111</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>零点区间与个数</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>M-T-081(函数与导数 / 零点区间与个数 · 判断函数零点的个数：利用数形结合法判断零点个数)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>[2017 江苏卷] 设 $f(x)$ 是定义在 $\mathbb{R}$ 上且周期为 $1$ 的函数，在区间 $[0,1)$ 上，$f(x)=\begin{cases}x^{2},&amp;x\in D\\ x,&amp;x\notin D\end{cases}$，其中集合 $D=\left\{x\;\middle|\;x=\frac{n-1}{n},\ n\in\mathbb{N}^{+}\right\}$，则方程 $f(x)-\lg x=0$ 的解的个数是 ____</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>$8$</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(x)\in[0,1)$ 知只需考虑 $\lg x\in[0,1)$，即 $1\leq x&lt;10$。对 $x\in[1,10)$，$\lg x$ 与 $f$ 的交点分两类：$x\in D$ 时 $f(x)=x^{2}$，$x\notin D$ 时 $f(x)=\{x\}$（小数部分）。先看 $x\in D$ 一类不可能有交点：$x\in D$ 意味着 $x$ 是有理数，设 $x=\frac{q}{p}$（$p,q$ 互质），若 $\lg x$ 也是有理数，设 $\lg x=\frac{n}{m}$（$m,n$ 互质，$m\geq 2$），则 $10^{n}=x^{m}=\frac{q^{m}}{p^{m}}$，左边是整数、右边不是整数，矛盾。故 $\lg x$ 是无理数，不可能等于有理数值的 $x^{2}$。所以只需数第二类交点。在 $[k,k+1)$（$k=1,\ldots,9$）上，记 $u=x-k\in[0,1)$，方程为 $u=\lg(k+u)$。记 $\varphi(u)=u-\lg(k+u)$，$\varphi'(u)=1-\frac{1}{(k+u)\ln 10}&gt;0$（因 $k+u\geq 1$），$\varphi$ 单调递增，每个区间至多一个解。$\varphi(0)=-\lg k$，$\varphi(1^{-})=1-\lg(k+1)$：$k=1$ 时 $\varphi(0)=0$，得 $x=1$（此时 $f(1)=f(0)=0$，$\lg 1=0$，确为解）；$k=2,\ldots,8$ 时 $\varphi(0)&lt;0$、$\varphi(1^{-})&gt;0$，各一个解；$k=9$ 时 $\varphi(1^{-})=1-\lg 10=0$，在 $u&lt;1$ 内 $\varphi&lt;0$，无解。故解的个数为 $1+7=8$。</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-081-V1</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>数值验证：在 $[1,10)$ 上解 $u=\lg(k+u)$，得交点横坐标 $1$、$2.3758$、$3.5503$、$4.6692$、$5.7605$、$6.8347$、$7.8975$、$8.9519$，共 $8$ 个。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>M-H0112</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>零点区间与个数</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>M-T-081(函数与导数 / 零点区间与个数 · 判断函数零点的个数：利用数形结合法判断零点个数)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>若定义在 $\mathbb{R}$ 上的偶函数 $f(x)$ 满足 $f(x+2)=f(x)$，且当 $x\in[0,1]$ 时，$f(x)=x$，则函数 $y=f(x)-\log_{3}|x|$ 的零点个数是（　　）</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>多于 $4$ 个</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>$4$ 个</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>$3$ 个</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>$2$ 个</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>$f$ 是周期为 $2$ 的偶函数，值域 $[0,1]$。由 $f(x)=\log_{3}|x|$ 且 $f(x)\in[0,1]$ 知 $\log_{3}|x|\in[0,1]$，即 $1\leq|x|\leq 3$。两个函数都是偶函数，只需算 $x&gt;0$ 再乘 $2$。$x\in(0,1)$：$\log_{3}x&lt;0$ 而 $f(x)=x&gt;0$，无零点。$x\in[1,2]$：由周期与偶性 $f(x)=2-x$，由 $1$ 降到 $0$；$\log_{3}x$ 由 $0$ 升到 $\log_{3}2\approx0.63$，二者恰有 $1$ 个交点。$x\in[2,3]$：$f(x)=x-2$ 由 $0$ 升到 $1$，$\log_{3}x$ 由 $\log_{3}2\approx0.63$ 升到 $1$；$x=3$ 时二者都等于 $1$，得第 $2$ 个零点（端点）。故正半轴有 $2$ 个零点，由偶对称共 $4$ 个。选 B。</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-081-V2</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
+          <t>数值验证：正半轴变号零点在 $x\approx1.5823$，加端点 $x=3$，共 $2$ 个，偶对称得 $4$ 个。注意 $x=3$ 是端点，扫描变号检测不到，需单独判。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>M-H0113</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>零点区间与个数</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>M-T-082(函数与导数 / 零点区间与个数 · 函数零点的应用：由零点个数求参数的范围)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>设方程 $|x^{2}-3|=a$ 的解的个数为 $m$，则 $m$ 不可能等于（　　）</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>作出 $y=|x^{2}-3|$ 与 $y=a$ 的图象。由 $|x^{2}-3|=a$ 得 $x^{2}=3+a$ 或 $x^{2}=3-a$。$a&lt;0$：两式均无解，$m=0$。$a=0$：$x^{2}=3$，$m=2$。$0&lt;a&lt;3$：$3+a&gt;0$ 给 $2$ 个根，$3-a&gt;0$ 也给 $2$ 个根，$m=4$。$a=3$：$x^{2}=6$ 给 $2$ 个根，$x^{2}=0$ 给 $1$ 个根（$x=0$），$m=3$。$a&gt;3$：$3+a&gt;0$ 给 $2$ 个根，$3-a&lt;0$ 无解，$m=2$。故 $m$ 的可能取值为 $0,2,3,4$，不可能等于 $1$。选 A。</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-082-V1</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>M-H0114</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>零点区间与个数</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>M-T-083(函数与导数 / 零点区间与个数 · 函数零点的应用：有关函数零点的求和问题)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>(2021·唐山月考) 已知函数 $f(x)=|x-2|+1$，$g(x)=kx$。若方程 $f(x)=g(x)$ 有两个不相等的实根，则实数 $k$ 的取值范围是 ____</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>$\left(\frac{1}{2},1\right)$</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)=\begin{cases}3-x,&amp;x&lt;2\\ x-1,&amp;x\geq 2\end{cases}$。分两段解方程。$x&lt;2$：$3-x=kx$，得 $x=\frac{3}{k+1}$，需 $k+1&gt;0$ 且 $\frac{3}{k+1}&lt;2$，即 $k&gt;\frac12$。$x\geq 2$：$x-1=kx$，得 $x=\frac{1}{1-k}$，需 $1-k&gt;0$ 且 $\frac{1}{1-k}\geq 2$，即 $k&lt;1$ 且 $k\geq\frac12$。要恰有两个不等实根，需两段各给一个解：$k&gt;\frac12$（第一段）与 $\frac12\leq k&lt;1$（第二段）取交集得 $\frac12&lt;k&lt;1$。验证端点：$k=\frac12$ 时第一段解 $x=2$ 不满足 $x&lt;2$，只剩 $x=2$ 一个根；$k=1$ 时第二段无解，只剩 $x=\frac32$ 一个根。故 $k\in\left(\frac12,1\right)$。</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-083-V1</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>程序验证：$k=0.5$ 与 $k=1.0$ 时各 $1$ 个解，$k=0.51$、$0.7$、$0.99$ 时均为 $2$ 个解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>M-H0115</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>零点区间与个数</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>M-T-084(函数与导数 / 零点区间与个数 · 函数零点的应用：借助零点比较大小)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>设 $a$，$b$，$c$ 均为正数，且 $-\mathrm{e}^{a}=\ln a$，$-\mathrm{e}^{-b}=\ln b$，$\mathrm{e}^{-c}=\ln c$，则（　　）</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>$c&gt;b&gt;a$</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>$b&gt;a&gt;c$</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>分别估计三个数所在区间（只用单调性，不求精确值）。（1）$\mathrm{e}^{a}=-\ln a$：$\mathrm{e}^{a}&gt;\mathrm{e}^{0}=1$，故 $-\ln a&gt;1=\ln\mathrm{e}$，即 $\ln a&lt;-1$，得 $0&lt;a&lt;\frac1{\mathrm{e}}$。（2）$\mathrm{e}^{-b}=-\ln b$：$0&lt;\mathrm{e}^{-b}&lt;1$，故 $0&lt;-\ln b&lt;1$，即 $-1&lt;\ln b&lt;0$，得 $\frac1{\mathrm{e}}&lt;b&lt;1$。（3）$\mathrm{e}^{-c}=\ln c$：$0&lt;\mathrm{e}^{-c}&lt;1$，故 $0&lt;\ln c&lt;1$，得 $1&lt;c&lt;\mathrm{e}$。综上 $a&lt;\frac1{\mathrm{e}}&lt;b&lt;1&lt;c$，故 $c&gt;b&gt;a$，选 A。数值上 $a\approx0.2699$，$b\approx0.5671$，$c\approx1.3098$；其中 $b$ 恰为 $x=\mathrm{e}^{-x}$ 的解（欧米伽常数 $W(1)$），且有 $\mathrm{e}^{-c}=a$ 的关系。</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-084-V2</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
+          <t>注意第三问的函数 $\mathrm{e}^{-x}-\ln x$ 是**递减**的，二分时方向与前两问相反（前两问递增）。写验证脚本时这里踩过坑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>M-H0116</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>M-T-085(函数与导数 / 导数切线与公切线 · 求切线基础型：给切点求切线)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\frac{2\sin x}{x+1}$，则曲线 $y=f(x)$ 在点 $(0,0)$ 处的切线的方程为 ____</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>$2x-y=0$</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=\frac{2\cos x\cdot(x+1)-2\sin x}{(x+1)^{2}}$，$k=f'(0)=\frac{2\cdot1\cdot1-0}{1}=2$。又切点为 $(0,0)$，故切线方程为 $y=2x$，即 $2x-y=0$。</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-085-E1</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>M-H0117</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>M-T-085(函数与导数 / 导数切线与公切线 · 求切线基础型：给切点求切线)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>曲线 $f(x)=(x+1)\mathrm{e}^{x}+x$ 在点 $(0,1)$ 处的切线方程为 ____</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>$3x-y+1=0$</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=\mathrm{e}^{x}+(x+1)\mathrm{e}^{x}+1$，在 $x=0$ 处 $f'(0)=1+(0+1)\cdot1+1=3$。又 $f(0)=(0+1)\cdot1+0=1$，切点确为 $(0,1)$。切线：$y-1=3(x-0)$，即 $3x-y+1=0$。</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-085-V1</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>M-H0118</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>M-T-085(函数与导数 / 导数切线与公切线 · 求切线基础型：给切点求切线)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>已知点 $P(-1,1)$ 在曲线 $y=\frac{x^{2}}{x+a}$ 上，则曲线在点 $P$ 处的切线方程为 ____</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>$y=-3x-2$</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>由 $P(-1,1)$ 在曲线上：$1=\frac{(-1)^{2}}{-1+a}=\frac1{a-1}$，得 $a=2$，即 $y=\frac{x^{2}}{x+2}$。求导：$y'=\frac{2x(x+2)-x^{2}}{(x+2)^{2}}=\frac{x^{2}+4x}{(x+2)^{2}}$，在 $x=-1$ 处 $k=\frac{1-4}{1}=-3$。切线：$y-1=-3(x+1)$，即 $y=-3x-2$。</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-085-V2</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>M-H0119</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>M-T-085(函数与导数 / 导数切线与公切线 · 求切线基础型：给切点求切线)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>已知曲线 $f(x)=\ln x+\frac{x^{2}}{a}$ 在点 $(1,f(1))$ 处的切线的倾斜角为 $\frac{3\pi}{4}$，则 $a$ 的值为（　　）</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>$-1$</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>$-\frac{1}{2}$</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>$-4$</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=\frac1x+\frac{2x}{a}$，倾斜角 $\frac{3\pi}{4}$ 对应斜率 $\tan\frac{3\pi}{4}=-1$。由 $f'(1)=1+\frac2a=-1$ 得 $\frac2a=-2$，故 $a=-1$。选 B。</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-085-V3</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>M-H0120</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>M-T-086(函数与导数 / 导数切线与公切线 · 求切线基础型：有切线无切点求切点)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>曲线 $f(x)=x^{3}+x-2$ 在 $P_{0}$ 处的切线平行于直线 $y=4x-1$，则 $P_{0}$ 点的坐标为（　　）</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>$(1,0)$</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>$(2,8)$</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>$(1,0)$ 和 $(-1,-4)$</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>$(2,8)$ 和 $(-1,-4)$</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=3x^{2}+1$。切线与 $y=4x-1$ 平行，斜率为 $4$，令 $3x^{2}+1=4$ 得 $x=\pm1$。$f(1)=1+1-2=0$，得 $(1,0)$；$f(-1)=-1-1-2=-4$，得 $(-1,-4)$。故选 C。</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-086-E1</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>M-H0121</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>M-T-086(函数与导数 / 导数切线与公切线 · 求切线基础型：有切线无切点求切点)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\mathrm{e}^{x}+\frac{a}{\mathrm{e}^{x}}$ 为偶函数，若曲线 $y=f(x)$ 的一条切线与直线 $2x+3y=0$ 垂直，则切点的横坐标为（　　）</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>$-2$</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>$2\ln 2$</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>$\ln 2$</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>由 $f$ 为偶函数：$f(-x)=\mathrm{e}^{-x}+a\mathrm{e}^{x}$ 与 $f(x)=\mathrm{e}^{x}+a\mathrm{e}^{-x}$ 相等，整理得 $(\mathrm{e}^{x}-\mathrm{e}^{-x})(a-1)=0$ 对一切 $x$ 成立，故 $a=1$，$f(x)=\mathrm{e}^{x}+\mathrm{e}^{-x}$，$f'(x)=\mathrm{e}^{x}-\mathrm{e}^{-x}$。直线 $2x+3y=0$ 的斜率为 $-\frac23$，故切线斜率为 $\frac32$。令 $\mathrm{e}^{x_{0}}-\mathrm{e}^{-x_{0}}=\frac32$，记 $t=\mathrm{e}^{x_{0}}&gt;0$，则 $t-\frac1t=\frac32$，即 $2t^{2}-3t-2=0$，解得 $t=2$（负根舍去），故 $x_{0}=\ln 2$。选 D。</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-086-V1</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>M-H0122</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>M-T-086(函数与导数 / 导数切线与公切线 · 求切线基础型：有切线无切点求切点)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>过曲线 $y=\cos x$ 上一点 $P\!\left(\frac{\pi}{3},\frac12\right)$ 且与曲线在点 $P$ 处的切线垂直的直线的方程为（　　）</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>$2x-\sqrt{3}y-\frac{2\pi}{3}+\frac{\sqrt{3}}{2}=0$</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>$\sqrt{3}x+2y-\frac{\sqrt{3}\pi}{3}-1=0$</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>$2x-\sqrt{3}y-\frac{2\pi}{3}-\frac{\sqrt{3}}{2}=0$</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>$\sqrt{3}x+2y-\frac{\sqrt{3}\pi}{3}+1=0$</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>$y'=-\sin x$，在 $x=\frac{\pi}{3}$ 处切线斜率为 $-\sin\frac{\pi}{3}=-\frac{\sqrt3}{2}$，故与其垂直的直线斜率为 $\frac{2}{\sqrt3}=\frac{2\sqrt3}{3}$。所求直线：$y-\frac12=\frac{2\sqrt3}{3}\left(x-\frac{\pi}{3}\right)$。两边乘 $\sqrt3$：$\sqrt3\,y-\frac{\sqrt3}{2}=2x-\frac{2\pi}{3}$，整理得 $2x-\sqrt3\,y-\frac{2\pi}{3}+\frac{\sqrt3}{2}=0$。故选 A。</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-086-V2</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>M-H0123</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>M-T-086(函数与导数 / 导数切线与公切线 · 求切线基础型：有切线无切点求切点)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>曲线 $y=\sin x+2x+1$ 在点 $P$ 处的切线方程是 $3x-y+1=0$，则切点 $P$ 的坐标是 ____</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>$(0,1)$</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>设 $P(x_{0},y_{0})$。$y'=\cos x+2$，由切线斜率为 $3$ 得 $\cos x_{0}+2=3$，即 $\cos x_{0}=1$，$x_{0}=2k\pi$（$k\in\mathbb{Z}$）。又切点既在曲线上也在切线上：$y_{0}=3x_{0}+1$ 且 $y_{0}=\sin x_{0}+2x_{0}+1$。代入 $x_{0}=2k\pi$（此时 $\sin x_{0}=0$）得 $y_{0}=4k\pi+1$ 与 $y_{0}=6k\pi+1$，比较得 $k=0$。故 $P(0,1)$。</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-086-V3</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>M-H0124</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>M-T-087(函数与导数 / 导数切线与公切线 · 求切线基础：无切点求参)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>已知曲线 $y=x^{3}$ 在点 $(a,b)$ 处的切线与直线 $x+3y+1=0$ 垂直，则 $a$ 的取值是（　　）</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>$-1$</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>$\pm1$</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>$\pm3$</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>直线 $x+3y+1=0$ 的斜率为 $-\frac13$，故切线斜率为 $3$。由 $y'=3x^{2}$ 得 $3a^{2}=3$，$a=\pm1$。选 B。</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-087-E1</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>M-H0125</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>M-T-087(函数与导数 / 导数切线与公切线 · 求切线基础：无切点求参)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>若曲线 $y=\ln x$（$x&gt;0$）的一条切线是直线 $y=\frac12x+b$，则实数 $b$ 的值为 ____</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>$-1+\ln 2$</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>设切点 $(x_{0},y_{0})$。$y'=\frac1x$，由切线斜率为 $\frac12$ 得 $\frac1{x_{0}}=\frac12$，$x_{0}=2$。$y_{0}=\ln 2$，切点 $(2,\ln 2)$ 代入 $y=\frac12x+b$：$\ln 2=1+b$，故 $b=-1+\ln 2$。</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-087-V1</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>M-H0126</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>M-T-087(函数与导数 / 导数切线与公切线 · 求切线基础：无切点求参)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>已知曲线 $y=ax^{3}$ 与直线 $6x-y-4=0$ 相切，则实数 $a$ 的值为 ____</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>设切点 $(m,n)$。由 $y=ax^{3}$ 得 $y'=3ax^{2}$。相切条件：$3am^{2}=6$（斜率等于 $6$），$n=am^{3}$（在曲线上），$6m-n-4=0$（在直线上）。由第一式 $am^{2}=2$，代入第二式得 $n=2m$，再代入第三式 $6m-2m-4=0$ 得 $m=1$，于是 $n=2$、$a=2$。</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-087-V2</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>M-H0127</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>M-T-087(函数与导数 / 导数切线与公切线 · 求切线基础：无切点求参)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>已知 $x$ 轴为曲线 $f(x)=4x^{3}+4(a-1)x+1$ 的切线，则 $a$ 的值为 ____</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>$\frac{1}{4}$</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>设 $x$ 轴与曲线的切点为 $(x_{0},0)$。$f'(x)=12x^{2}+4(a-1)$。相切条件：$f(x_{0})=0$ 且 $f'(x_{0})=0$。由 $f'(x_{0})=0$ 得 $4(a-1)=-12x_{0}^{2}$，代入 $f(x_{0})=0$：$4x_{0}^{3}-12x_{0}^{2}\cdot x_{0}+1=0$，即 $-8x_{0}^{3}+1=0$，$x_{0}=\frac12$。于是 $4(a-1)=-12\cdot\frac14=-3$，$a-1=-\frac34$，$a=\frac14$。</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-087-V3</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>教辅录入-第11批</t>
+        </is>
+      </c>
+      <c r="V127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>M-H0128</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>M-T-088(函数与导数 / 导数切线与公切线 · 无切点多参)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>若直线 $y=2x+b$ 是曲线 $y=2a\ln x$ 的切线，且 $a&gt;0$，则实数 $b$ 的最小值是 ____</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>$-2$</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>$y=2a\ln x$ 的导数为 $y'=\frac{2a}{x}$。设切点为 $(m,n)$，由切线斜率为 $2$ 得 $\frac{2a}{m}=2$，故 $m=a$。切点既在曲线上也在切线上：$2a\ln a=2a+b$，得 $b=2a\ln a-2a$（$a&gt;0$）。记 $b(a)=2a\ln a-2a$，则 $b'(a)=2\ln a+2-2=2\ln a$。$0&lt;a&lt;1$ 时 $b'(a)&lt;0$，$b$ 递减；$a&gt;1$ 时 $b'(a)&gt;0$，$b$ 递增。故 $a=1$ 是极小值点也是最小值点，$b_{\min}=2\cdot1\cdot\ln 1-2=-2$。</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-088-E1</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>M-H0129</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>M-T-088(函数与导数 / 导数切线与公切线 · 无切点多参)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=ax\ln x-bx$（$a,b\in\mathbb{R}$）在点 $(\mathrm{e},f(\mathrm{e}))$ 处的切线方程为 $y=3x-\mathrm{e}$，则 $a+b=$ ____</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>$0$</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>切点 $(\mathrm{e},f(\mathrm{e}))$ 在切线上，故 $f(\mathrm{e})=3\mathrm{e}-\mathrm{e}=2\mathrm{e}$。又 $f(\mathrm{e})=a\mathrm{e}\ln\mathrm{e}-b\mathrm{e}=\mathrm{e}(a-b)$，所以 $a-b=2$ ①。$f'(x)=a(\ln x+1)-b$，由切线斜率为 $3$ 得 $f'(\mathrm{e})=2a-b=3$ ②。联立①②解得 $a=1$，$b=-1$，故 $a+b=0$。</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-088-V1</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>M-H0130</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>M-T-088(函数与导数 / 导数切线与公切线 · 无切点多参)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>若曲线 $f(x)=mx\mathrm{e}^{x}+n$ 在 $(1,f(1))$ 处的切线方程为 $y=\mathrm{e}x$，则 $m+n=$ ____</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>$\frac{\mathrm{e}+1}{2}$</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>将 $x=1$ 代入 $y=\mathrm{e}x$ 得切点为 $(1,\mathrm{e})$，故 $\mathrm{e}=m\mathrm{e}+n$ ①。$f'(x)=m\mathrm{e}^{x}(x+1)$，由切线斜率为 $\mathrm{e}$ 得 $f'(1)=2m\mathrm{e}=\mathrm{e}$，故 $m=\frac12$ ②。代入①得 $n=\mathrm{e}-\frac{\mathrm{e}}{2}=\frac{\mathrm{e}}{2}$。</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-088-V2</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>M-H0131</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>M-T-088(函数与导数 / 导数切线与公切线 · 无切点多参)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>已知曲线 $y=a\mathrm{e}^{x}+x\ln x$ 在点 $(1,a\mathrm{e})$ 处的切线方程为 $y=2x+b$，则（　　）</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>$a=\mathrm{e},\ b=-1$</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>$a=\mathrm{e},\ b=1$</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>$a=\mathrm{e}^{-1},\ b=1$</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>$a=\mathrm{e}^{-1},\ b=-1$</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>$y'=a\mathrm{e}^{x}+\ln x+1$，由切线斜率为 $2$ 得 $y'\big|_{x=1}=a\mathrm{e}+1=2$，故 $a=\mathrm{e}^{-1}$。此时切点为 $(1,a\mathrm{e})=(1,1)$，代入 $y=2x+b$ 得 $1=2+b$，$b=-1$。故选 D。</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-088-V3</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>M-H0132</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>M-T-089(函数与导数 / 导数切线与公切线 · “过点”型切线)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>过原点作曲线 $y=\ln x$ 的切线，则切点的坐标为 ____，切线的斜率为 ____</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>$(\mathrm{e},1)$；$\dfrac{1}{\mathrm{e}}$</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>设切点为 $(t,\ln t)$（$t&gt;0$）。$y'=\frac1x$，切线斜率为 $\frac1t$。切线过原点，故 $\frac{\ln t-0}{t-0}=\frac1t$，即 $\ln t=1$，$t=\mathrm{e}$。故切点为 $(\mathrm{e},1)$，切线斜率为 $\frac1{\mathrm{e}}$，切线方程为 $y-1=\frac1{\mathrm{e}}(x-\mathrm{e})$，即 $x-\mathrm{e}y=0$。</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S132" t="n">
+        <v>5</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-089-E1</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>两个空，答案用分号隔开。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>M-H0133</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>M-T-089(函数与导数 / 导数切线与公切线 · “过点”型切线)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>过点 $(-1,-1)$ 与曲线 $y=\mathrm{e}^{x}+x$ 相切的直线方程为 ____</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>$y=2x+1$</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>设切点为 $(x_{0},\mathrm{e}^{x_{0}}+x_{0})$。$y'=\mathrm{e}^{x}+1$，切线方程为 $y-(\mathrm{e}^{x_{0}}+x_{0})=(\mathrm{e}^{x_{0}}+1)(x-x_{0})$。切线过 $(-1,-1)$，代入得 $-1-(\mathrm{e}^{x_{0}}+x_{0})=(\mathrm{e}^{x_{0}}+1)(-1-x_{0})$，整理得 $x_{0}\mathrm{e}^{x_{0}}=0$，故 $x_{0}=0$。切点为 $(0,1)$，斜率为 $2$，切线方程为 $y=2x+1$。</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-089-V1</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>M-H0134</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>M-T-089(函数与导数 / 导数切线与公切线 · “过点”型切线)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>过点 $(0,-1)$ 作曲线 $f(x)=\ln x^{2}$（$x&gt;0$）的切线，则切点坐标为 ____</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>$(\sqrt{\mathrm{e}},1)$</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>由 $x&gt;0$ 得 $f(x)=\ln x^{2}=2\ln x$，$f'(x)=\frac2x$。设切点为 $(x_{0},2\ln x_{0})$。$(0,-1)$ 不在曲线上，由斜率相等得 $\frac{2\ln x_{0}-(-1)}{x_{0}-0}=\frac2{x_{0}}$，即 $2\ln x_{0}+1=2$，$\ln x_{0}=\frac12$，$x_{0}=\sqrt{\mathrm{e}}$。故切点为 $(\sqrt{\mathrm{e}},1)$。</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-089-V2</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V134" s="2" t="inlineStr">
+        <is>
+          <t>原书题干提取为 $f(x)=\ln x$ 与解析矛盾；解析明确写 $\ln x^{2}=2\ln x$，按解析重建。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>M-H0135</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>M-T-089(函数与导数 / 导数切线与公切线 · “过点”型切线)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>已知直线 $y=ax$ 是曲线 $y=\ln x$ 的切线，则实数 $a=$（　　）</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>$\frac12$</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>$\frac{1}{2\mathrm{e}}$</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>$\frac{1}{\mathrm{e}}$</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>$\frac{1}{\mathrm{e}^{2}}$</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>设切点为 $(x_{0},\ln x_{0})$。$y'=\frac1x$，切线方程为 $y-\ln x_{0}=\frac1{x_{0}}(x-x_{0})$，即 $y=\frac1{x_{0}}x+\ln x_{0}-1$。该直线就是 $y=ax$，故 $\frac1{x_{0}}=a$ 且 $\ln x_{0}-1=0$。由 $\ln x_{0}=1$ 得 $x_{0}=\mathrm{e}$，故 $a=\frac1{\mathrm{e}}$。选 C。</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-089-V3</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>M-H0136</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>M-T-090(函数与导数 / 导数切线与公切线 · 判断切线条数)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>已知曲线 $S:y=3x-x^{3}$，则过点 $P(2,2)$ 可向 $S$ 引切线，其切线条数为（　　）</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>$0$</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>设切点为 $(t,3t-t^{3})$。$y'=3-3x^{2}$，切线方程为 $y-(3t-t^{3})=(3-3t^{2})(x-t)$。切线过 $P(2,2)$，代入得 $2-(3t-t^{3})=(3-3t^{2})(2-t)$，整理得 $t^{3}-3t^{2}+2=0$，即 $(t-1)(t^{2}-2t-2)=0$，解得 $t_{1}=1$，$t_{2}=1+\sqrt3$，$t_{3}=1-\sqrt3$，三个值互不相同。故可引 $3$ 条切线，选 C。</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-090-E1</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>M-H0137</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>M-T-090(函数与导数 / 导数切线与公切线 · 判断切线条数)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>已知过点 $A(a,0)$ 作曲线 $C:y=x\mathrm{e}^{x}$ 的切线有且仅有两条，则实数 $a$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>$(-\infty,-4)\cup(0,+\infty)$</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>$(0,+\infty)$</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>$(-\infty,-1)\cup(1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>$(-\infty,-1)$</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>设切点为 $(x_{0},x_{0}\mathrm{e}^{x_{0}})$。$y'=(x+1)\mathrm{e}^{x}$，切线方程为 $y-x_{0}\mathrm{e}^{x_{0}}=(x_{0}+1)\mathrm{e}^{x_{0}}(x-x_{0})$。切线过 $A(a,0)$，代入得 $-x_{0}\mathrm{e}^{x_{0}}=(x_{0}+1)\mathrm{e}^{x_{0}}(a-x_{0})$。因 $\mathrm{e}^{x_{0}}&gt;0$，可约去，得 $-x_{0}=(x_{0}+1)(a-x_{0})$，整理成关于 $x_{0}$ 的方程：$x_{0}^{2}-ax_{0}-a=0$（$x_{0}\neq-1$，而 $x_{0}=-1$ 代入左式为 $1\neq0$，自动排除）。要有且仅有两条切线，即该方程有两个不等实根：$\Delta=a^{2}+4a&gt;0$，解得 $a&gt;0$ 或 $a&lt;-4$。选 A。</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-090-V1</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>M-H0138</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>M-T-090(函数与导数 / 导数切线与公切线 · 判断切线条数)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x-\mathrm{e}^{\frac{x}{a}}$ 存在单调递减区间，且 $y=f(x)$ 的图象在 $x=0$ 处的切线 $l$ 与曲线 $y=\mathrm{e}^{x}$ 相切，符合情况的切线 $l$（　　）</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>有 $3$ 条</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>有 $2$ 条</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>有 $1$ 条</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>不存在</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>先看单调递减区间的条件。$f'(x)=1-\frac1a\mathrm{e}^{x/a}$。$a&lt;0$ 时 $\frac1a\mathrm{e}^{x/a}&lt;0$，故 $f'(x)&gt;1&gt;0$ 恒成立，不存在递减区间，舍去；$a&gt;0$ 时 $f'(x)&lt;0$ 有解（$x&gt;a\ln a$）。故 $a&gt;0$。$f(0)=-1$，$f'(0)=1-\frac1a$，切线 $l$ 为 $y=\left(1-\frac1a\right)x-1$。若 $l$ 与 $y=\mathrm{e}^{x}$ 相切于 $(x_{0},\mathrm{e}^{x_{0}})$，则$\mathrm{e}^{x_{0}}=1-\frac1a$ 且 $\mathrm{e}^{x_{0}}=\left(1-\frac1a\right)x_{0}-1$。代入消去 $1-\frac1a$ 得 $\mathrm{e}^{x_{0}}=\mathrm{e}^{x_{0}}x_{0}-1$，即 $\mathrm{e}^{x_{0}}(x_{0}-1)=1$。该方程在 $x_{0}&gt;1$ 上有唯一解 $x_{0}\approx1.278$，此时 $1-\frac1a=\mathrm{e}^{x_{0}}\approx3.59&gt;1$，得 $\frac1a&lt;0$，即 $a&lt;0$，与 $a&gt;0$ 矛盾。故不存在，选 D。</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S138" t="n">
+        <v>5</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-090-V2</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V138" s="2" t="inlineStr">
+        <is>
+          <t>数值验证：$\mathrm{e}^{x}(x-1)=1$ 的解 $x_{0}\approx1.2785$（需 $x_0&gt;1$），此时 $\mathrm{e}^{x_0}\approx3.5911&gt;1$，推出 $a&lt;0$，与"存在递减区间"要求的 $a&gt;0$ 矛盾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>M-H0139</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>M-T-090(函数与导数 / 导数切线与公切线 · 判断切线条数)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x^{3}+ax^{2}-9x+1$，$a\in\mathbb{R}$，当 $x_{0}\neq1$ 时，曲线 $y=f(x)$ 在点 $(x_{0},f(x_{0}))$ 与点 $(2-x_{0},f(2-x_{0}))$ 处的切线总是平行，则由点 $(a,a)$ 可作曲线 $y=f(x)$ 的切线的条数为（　　）</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>无法确定</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=3x^{2}+2ax-9$。$f'(x_{0})=f'(2-x_{0})$ 对一切 $x_{0}\neq1$ 成立，即 $y=f'(x)$ 的图象关于 $x=1$ 对称，故 $-\frac{2a}{2\cdot3}=1$，$a=-3$。于是 $f(x)=x^{3}-3x^{2}-9x+1$，点 $(a,a)=(-3,-3)$。设切点为 $(t,t^{3}-3t^{2}-9t+1)$，切线过 $(-3,-3)$：$\frac{t^{3}-3t^{2}-9t+1-(-3)}{t-(-3)}=f'(t)=3t^{2}-6t-9$，整理得 $2t^{3}-6t^{2}-36t-31=0$。记 $g(t)=2t^{3}-6t^{2}-36t-31$，$g'(t)=6t^{2}-12t-18=6(t-3)(t+1)$，极值点为 $t=-1$ 与 $t=3$。$g(-1)=-3&gt;0$（极大），$g(3)=-139&lt;0$（极小），三次函数 $g$ 有 $3$ 个互异实根，故可作 $3$ 条切线。选 C。</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S139" t="n">
+        <v>5</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-090-V3</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>M-H0140</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>M-T-091(函数与导数 / 导数切线与公切线 · 多函数(多曲线)的公切线)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>直线 $y=kx+b$ 与曲线 $y=f(x)$ 相切也与曲线 $y=g(x)$ 相切，则称直线 $y=kx+b$ 为曲线 $y=f(x)$ 和曲线 $y=g(x)$ 的公切线。已知函数 $f(x)=x^{2}$，$g(x)=a\ln x$，其中 $a\neq0$，若曲线 $y=f(x)$ 和曲线 $y=g(x)$ 的公切线有两条，则 $a$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>$a&lt;0$</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>$a&lt;-1$</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>$0&lt;a&lt;2\mathrm{e}$</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>$0&lt;a&lt;\frac{2}{\mathrm{e}}$</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>设 $f$ 上的切点为 $(s,s^{2})$，$f'(x)=2x$，切线为 $y=2sx-s^{2}$；设 $g$ 上的切点为 $(t,a\ln t)$（$t&gt;0$），$g'(x)=\frac ax$，切线为 $y=\frac at x-a+a\ln t$。两切线重合，故 $2s=\frac at$ 且 $-s^{2}=-a+a\ln t$。由 $s=\frac a{2t}$ 代入第二式得 $-\frac{a^{2}}{4t^{2}}=-a+a\ln t$，因 $a\neq0$，整理得 $a=4t^{2}(1-\ln t)$。记 $h(t)=4t^{2}(1-\ln t)$（$t&gt;0$），$h'(t)=4t(1-2\ln t)$：$0&lt;t&lt;\sqrt{\mathrm{e}}$ 时 $h'(t)&gt;0$，$h$ 递增；$t&gt;\sqrt{\mathrm{e}}$ 时 $h'(t)&lt;0$，$h$ 递减。且 $h(0^{+})=0$，$h(\sqrt{\mathrm{e}})=2\mathrm{e}$，$h(+\infty)=-\infty$，$h(\mathrm{e})=0$。公切线两条等价于方程 $h(t)=a$ 有两个解，由图象知 $0&lt;a&lt;2\mathrm{e}$。选 C。</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-091-E1</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V140" s="2" t="inlineStr">
+        <is>
+          <t>数值验证：$h(\sqrt{\mathrm{e}})=2\mathrm{e}\approx5.4366$ 为最大值，$h(\mathrm{e})=0$，在 $(0,\sqrt{\mathrm e})$ 上从 $0$ 增到 $2\mathrm e$、在 $(\sqrt{\mathrm e},+\infty)$ 上从 $2\mathrm e$ 降到 $-\infty$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>M-H0141</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>M-T-091(函数与导数 / 导数切线与公切线 · 多函数(多曲线)的公切线)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>函数 $f(x)=\ln x+\frac{mx}{x+1}$ 与 $g(x)=x^{2}+1$ 有公切线 $y=ax$（$a&gt;0$），则实数 $m$ 的值为（　　）</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>$\frac12$</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>先由 $g$ 确定 $a$。设公切线与 $g$ 切于 $(x_{2},x_{2}^{2}+1)$，$g'(x)=2x$，故 $a=2x_{2}$；切点在 $y=ax$ 上：$x_{2}^{2}+1=ax_{2}=2x_{2}^{2}$，得 $x_{2}^{2}=1$，由 $a&gt;0$ 知 $x_{2}=1$，故 $a=2$。再看 $f$。设公切线与 $f$ 切于 $(x_{1},y_{1})$。$f'(x)=\frac1x+\frac m{(x+1)^{2}}$，由 $f'(x_{1})=a=2$ 得 $\frac1{x_{1}}+\frac m{(x_{1}+1)^{2}}=2$ ①；由 $y_{1}=ax_{1}=2x_{1}$ 且 $y_{1}=f(x_{1})=\ln x_{1}+\frac{mx_{1}}{x_{1}+1}$ 得 $\ln x_{1}+\frac{mx_{1}}{x_{1}+1}=2x_{1}$ ②。由①解出 $m=(x_{1}+1)^{2}\left(2-\frac1{x_{1}}\right)$，代入②消 $m$ 并化简得$2x_{1}^{2}-x_{1}+\ln x_{1}-1=0$。记 $h(x)=2x^{2}-x+\ln x-1$（$x&gt;0$），$h'(x)=4x+\frac1x-1\geq 3&gt;0$（因 $4x+\frac1x\geq 4$），$h$ 严格递增。又 $h(1)=2-1+0-1=0$，故 $x_{1}=1$ 是唯一解。代入①得 $m=4\left(2-1\right)=4$。选 A。</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-091-V1</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V141" s="2" t="inlineStr">
+        <is>
+          <t>数值验证：$x_{1}=1$ 时 $f(1)=0+\frac m2$，令其等于 $2$ 得 $m=4$；此时 $f'(1)=1+\frac44=2=a$，与 $g$ 侧确定的 $a=2$ 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>M-H0142</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>M-T-091(函数与导数 / 导数切线与公切线 · 多函数(多曲线)的公切线)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>若函数 $f(x)=\ln x$（$x&gt;0$）与函数 $g(x)=x^{2}+a$ 有公切线，则实数 $a$ 的最小值为（　　）</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>$-\frac12\ln 2-\frac12$</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>$-\ln 2-1$</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>$-\frac12$</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>$-\ln 2$</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=\frac1x$，设公切线与 $f$ 切于 $(m,\ln m)$（$m&gt;0$），则公切线为 $y-\ln m=\frac1m(x-m)$，即 $x-my-m+m\ln m=0$。它与 $y=x^{2}+a$ 相切，代入 $y$ 得 $x-m(x^{2}+a)-m+m\ln m=0$，即 $mx^{2}-x+am+m-m\ln m=0$，由判别式为 $0$：$1-4m(am+m-m\ln m)=0$，解得 $a=\frac1{4m^{2}}-1+\ln m$。记 $A(m)=\frac1{4m^{2}}-1+\ln m$（$m&gt;0$），$A'(m)=-\frac1{2m^{3}}+\frac1m=\frac{2m^{2}-1}{2m^{3}}$。$0&lt;m&lt;\frac{\sqrt2}{2}$ 时 $A'(m)&lt;0$，$A$ 递减；$m&gt;\frac{\sqrt2}{2}$ 时 $A'(m)&gt;0$，$A$ 递增。故 $A$ 在 $m=\frac{\sqrt2}{2}$ 处取最小值：$A\!\left(\frac{\sqrt2}{2}\right)=\frac1{4\cdot\frac12}-1+\ln\frac{\sqrt2}{2}=\frac12-1+\frac12\ln 2-\ln 2=-\frac12\ln 2-\frac12$。选 A。</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S142" t="n">
+        <v>5</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-091-V3</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V142" s="2" t="inlineStr">
+        <is>
+          <t>数值验证：$A(\sqrt2/2)=-0.846574$，与 $-rac12\ln2-rac12=-0.846574$ 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>M-H0143</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>M-T-091(函数与导数 / 导数切线与公切线 · 多函数(多曲线)的公切线)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>曲线 $f(x)=\mathrm{e}^{x-1}$ 与曲线 $g(x)=\ln x$ 有（　　）条公切线</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>设公切线与 $f$ 切于 $(x_{0},\mathrm{e}^{x_{0}-1})$。$f'(x)=\mathrm{e}^{x-1}$，切线为 $y-\mathrm{e}^{x_{0}-1}=\mathrm{e}^{x_{0}-1}(x-x_{0})$，即 $y=\mathrm{e}^{x_{0}-1}x+(1-x_{0})\mathrm{e}^{x_{0}-1}$ ①。由 $g'(x)=\frac1x$，令 $\frac1{x_{1}}=\mathrm{e}^{x_{0}-1}$ 得 $x_{1}=\mathrm{e}^{1-x_{0}}$，$g(x_{1})=\ln x_{1}=1-x_{0}$，$g$ 在 $x_{1}$ 处的切线为 $y-(1-x_{0})=\mathrm{e}^{x_{0}-1}(x-\mathrm{e}^{1-x_{0}})$，即 $y=\mathrm{e}^{x_{0}-1}x-x_{0}$ ②。①②重合：$(1-x_{0})\mathrm{e}^{x_{0}-1}=-x_{0}$，即 $(x_{0}-1)\mathrm{e}^{x_{0}-1}-x_{0}=0$。记 $h(x)=(x-1)\mathrm{e}^{x-1}-x$，$h'(x)=x\mathrm{e}^{x-1}-1$，$h''(x)=(x+1)\mathrm{e}^{x-1}$。由 $h''$ 知 $h'$ 在 $(-\infty,-1)$ 递减、在 $(-1,+\infty)$ 递增，而 $h'(-1)=-\mathrm{e}^{-2}-1&lt;0$，$h'(1)=0$，故 $h'$ 在 $(1,+\infty)$ 有唯一零点 $1$，即 $h$ 在 $x=1$ 处取最小值 $h(1)=-1&lt;0$。又 $h(-\infty)\to+\infty$（$(x-1)\mathrm{e}^{x-1}\to0^{-}$，$-x\to+\infty$）、$h(+\infty)\to+\infty$，故 $h$ 恰有 $2$ 个零点，即有 $2$ 条公切线。选 B。</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-091-V2</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V143" s="2" t="inlineStr">
+        <is>
+          <t>数值验证：$h(-1)=0.729&gt;0$、$h(0)=-0.368&lt;0$ 得一根在 $(-1,0)$；$h(1)=-1$ 为最小值、$h(2)=0.718&gt;0$ 得另一根在 $(1,2)$。共 $2$ 根。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>M-H0144</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>M-T-092(函数与导数 / 导数切线与公切线 · 切线的应用：距离最值)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>点 $P$ 在函数 $y=\ln x$ 的图象上，若满足到直线 $y=x+a$ 的距离为 $1$ 的点 $P$ 有且仅有 $1$ 个，则 $a=$（　　）</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>$\sqrt2+1$</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>$\sqrt2-1$</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>$-\sqrt2-1$</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>$\pm\sqrt2-1$</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>先求与 $y=x$ 平行且与 $y=\ln x$ 相切的直线。$y'=\frac1x$，令 $\frac1{x_{0}}=1$ 得 $x_{0}=1$，切点为 $(1,0)$，切线为 $y=x-1$。点 $P$ 到 $y=x+a$ 的距离为 $1$，几何上即直线 $y=x+a$ 与曲线 $y=\ln x$ 的“距离为 $1$”的等高线相切。临界情形出现在与 $y=x+a$ 平行、距离为 $1$ 的两条直线 $y=x+a\pm\sqrt2$ 中恰有一条与曲线相切。由上面的结论，与曲线相切的斜率为 $1$ 的直线只有 $y=x-1$。故 $|a-(-1)|=\sqrt2$，即 $|a+1|=\sqrt2$，$a=\pm\sqrt2-1$。结合图象：$a=\sqrt2-1$ 时直线在切线上方，距离为 $1$ 的点恰 $1$ 个；$a=-\sqrt2-1$ 时直线在下方，会有 $2$ 个点。故选 B。</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-092-E1</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>M-H0145</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>M-T-092(函数与导数 / 导数切线与公切线 · 切线的应用：距离最值)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>点 $A$ 在直线 $y=x$ 上，点 $B$ 在曲线 $y=\ln x$ 上，则 $|AB|$ 的最小值为（　　）</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>$\frac{\sqrt2}{2}$</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>$\sqrt2$</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>当 $B$ 固定时，$|AB|$ 取最小值时 $AB$ 垂直于 $y=x$，故 $|AB|$ 的最小值等于曲线 $y=\ln x$ 到直线 $y=x$ 的最小距离，也就是与 $y=x$ 平行且与曲线相切的直线到 $y=x$ 的距离。$y'=\frac1x$，令 $\frac1m=1$ 得 $m=1$，切点 $(1,0)$。由切点在 $y=x+b$ 上：$0=1+b$，$b=-1$，切线为 $y=x-1$。两平行线 $y=x$ 与 $y=x-1$ 的距离为 $\frac{|0-(-1)|}{\sqrt{1^{2}+(-1)^{2}}}=\frac{\sqrt2}{2}$。选 A。</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S145" t="n">
+        <v>5</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-092-V1</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>M-H0146</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>M-T-092(函数与导数 / 导数切线与公切线 · 切线的应用：距离最值)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>已知点 $M$ 在函数 $f(x)=\mathrm{e}^{x}$ 图象上，点 $N$ 在函数 $g(x)=\ln x$ 图象上，则 $|MN|$ 的最小值为（　　）</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>$\sqrt2$</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)=\mathrm{e}^{x}$ 与 $g(x)=\ln x$ 互为反函数，图象关于直线 $y=x$ 对称。由对称性，$|MN|$ 的最小值等于 $f$ 图象上的点到直线 $y=x$ 的最小距离的 $2$ 倍。$f'(x)=\mathrm{e}^{x}$，令 $\mathrm{e}^{x_{0}}=1$ 得 $x_{0}=0$，切点为 $(0,1)$，它到 $y=x$ 的距离为 $\frac{|0-1|}{\sqrt{1^{2}+(-1)^{2}}}=\frac{\sqrt2}{2}$。</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-092-V2</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>M-H0147</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>M-T-092(函数与导数 / 导数切线与公切线 · 切线的应用：距离最值)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>抛物线 $y=x^{2}$ 上的一动点 $M$ 到直线 $l:x-y-1=0$ 距离的最小值是（　　）</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>$\frac{3\sqrt2}{8}$</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>$\frac38$</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>$\frac34$</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>$\frac{3\sqrt2}{4}$</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>$y'=2x$，令 $2x=1$ 得 $x=\frac12$，切点为 $\left(\frac12,\frac14\right)$，此处切线与 $l$ 平行。切线方程为 $y-\frac14=x-\frac12$，即 $x-y-\frac14=0$。所求最小距离即两平行线 $x-y-\frac14=0$ 与 $x-y-1=0$ 的距离：$d=\frac{\left|-\frac14-(-1)\right|}{\sqrt{1^{2}+(-1)^{2}}}=\frac{\frac34}{\sqrt2}=\frac{3\sqrt2}{8}$。选 A。</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S147" t="n">
+        <v>5</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-092-V3</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>M-H0148</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>M-T-093(函数与导数 / 导数切线与公切线 · 切线的应用：距离公式转化型)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>若 $x_{1},x_{2}\in\mathbb{R}$，则 $\left(x_{1}-\mathrm{e}^{x_{2}}\right)^{2}+\left(x_{2}-\mathrm{e}^{x_{1}}\right)^{2}$ 的最小值是（　　）</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>把式子看成两点间距离的平方：记 $A\left(x_{1},\mathrm{e}^{x_{1}}\right)$、$B\left(\mathrm{e}^{x_{2}},x_{2}\right)$。当 $x_{1}$ 取遍 $\mathbb{R}$ 时，$A$ 的轨迹是 $y=\mathrm{e}^{x}$；记 $t=\mathrm{e}^{x_{2}}&gt;0$，则 $B=(t,\ln t)$，$B$ 的轨迹是 $y=\ln x$。这两条曲线关于直线 $y=x$ 对称，故 $|AB|$ 的最小值等于 $y=\mathrm{e}^{x}$ 上的点到直线 $y=x$ 的最小距离的 $2$ 倍。由 $(\mathrm{e}^{x})'=\mathrm{e}^{x}=1$ 得 $x=0$，切点 $(0,1)$，它到 $y=x$ 的距离为 $\frac{|0-1|}{\sqrt2}=\frac{\sqrt2}{2}$。于是 $|AB|_{\min}=2\cdot\frac{\sqrt2}{2}=\sqrt2$，原式的最小值即 $|AB|_{\min}^{2}=2$。选 B。</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S148" t="n">
+        <v>5</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-093-E1</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V148" s="2" t="inlineStr">
+        <is>
+          <t>数值验证：网格扫描得 $2.0008$（切点不在网格点上），与理论值 $2$ 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>M-H0149</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>M-T-093(函数与导数 / 导数切线与公切线 · 切线的应用：距离公式转化型)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>设 $b&lt;0$，当 $(a+b)^{2}+\left(a-\dfrac{4}{b}\right)^{2}$ 取得最小值 $c$ 时，函数 $f(x)=|x-b|+|x-c|$ 的最小值为 ____</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>$10$</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>把 $(a+b)^{2}+\left(a-\frac4b\right)^{2}$ 看成点 $P(a,a)$ 到点 $Q\left(-b,\frac4b\right)$ 距离的平方。$P$ 在直线 $y=x$ 上。令 $t=-b&gt;0$，则 $\frac4b=-\frac4t$，$Q=\left(t,-\frac4t\right)$。对固定的 $t$，$P$ 到 $Q$ 的最小距离即 $Q$ 到直线 $y=x$ 的距离：$d^{2}=\dfrac{\left(t+\frac4t\right)^{2}}{2}$，其中用到 $Q$ 到 $y=x$ 的距离为 $\dfrac{\left|t-\left(-\frac4t\right)\right|}{\sqrt2}=\dfrac{t+\frac4t}{\sqrt2}$（$t&gt;0$）。由 $t+\frac4t\geq4$（$t=2$ 取等）得 $c=\frac{4^{2}}{2}=8$，此时 $b=-t=-2$。于是 $f(x)=|x+2|+|x-8|$，当 $-2\leq x\leq8$ 时取最小值 $|8-(-2)|=10$。</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S149" t="n">
+        <v>5</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-093-V2</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V149" s="2" t="inlineStr">
+        <is>
+          <t>数值验证：$t=2$ 时 $d^{2}=8.000000$，$c=8$，$b=-2$，$|x+2|+|x-8|$ 最小值为 $10$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>M-H0150</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>M-T-093(函数与导数 / 导数切线与公切线 · 切线的应用：距离公式转化型)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a\in\mathbb{R}$，$b\in\mathbb{R}$，则 $(a-b)^{2}+\left(a-1-\mathrm{e}^{b}\right)^{2}$ 的最小值为 ____</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>把式子看成点 $P(a,a-1)$ 到点 $Q\left(b,\mathrm{e}^{b}\right)$ 距离的平方。$P$ 的轨迹是直线 $y=x-1$，$Q$ 的轨迹是曲线 $y=\mathrm{e}^{x}$，所求最小值即 $\mathrm{e}^{x}$ 上的点到直线 $y=x-1$ 的最小距离的平方。平移直线使其与曲线相切：由 $(\mathrm{e}^{x})'=\mathrm{e}^{x}=1$ 得 $x=0$，切点 $(0,1)$。点 $(0,1)$ 到直线 $x-y-1=0$ 的距离为 $d=\frac{|0-1-1|}{\sqrt{1^{2}+(-1)^{2}}}=\sqrt2$，故原式的最小值为 $d^{2}=2$。</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S150" t="n">
+        <v>5</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-093-V3</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>M-H0151</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>M-T-094(函数与导数 / 导数切线与公切线 · 切线的应用：恒成立求参等应用)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a$ 为实数，则“$\mathrm{e}^{x}&gt;ax$ 对任意的实数 $x$ 恒成立”是“$0&lt;a&lt;2$”的（　　）</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>充分不必要条件</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>必要不充分条件</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>充要条件</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>既不充分也不必要条件</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>先求“$\mathrm{e}^{x}&gt;ax$ 对任意实数 $x$ 恒成立”的充要条件。若 $a&lt;0$，取 $x\to-\infty$，则 $ax\to+\infty$ 而 $\mathrm{e}^{x}\to0$，不等式不成立；若 $a=0$，$\mathrm{e}^{x}&gt;0$ 恒成立；若 $a&gt;0$，令 $h(x)=\mathrm{e}^{x}-ax$，$h'(x)=\mathrm{e}^{x}-a$，$h$ 在 $x=\ln a$ 处取最小值 $h(\ln a)=a-a\ln a=a(1-\ln a)$，$h_{\min}&gt;0\iff\ln a&lt;1\iff a&lt;\mathrm{e}$。综上该条件等价于 $0\leq a&lt;\mathrm{e}$。记 $P:0\leq a&lt;\mathrm{e}$，$Q:0&lt;a&lt;2$。因 $2&lt;\mathrm{e}$，有 $Q\Rightarrow P$；而 $a=0$ 满足 $P$ 不满足 $Q$，故 $P\nRightarrow Q$。所以 $P$ 是 $Q$ 的必要不充分条件。选 B。</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S151" t="n">
+        <v>5</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-094-E1</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>M-H0152</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>M-T-094(函数与导数 / 导数切线与公切线 · 切线的应用：恒成立求参等应用)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=a^{x}$（$a&gt;0$，$a\neq1$）的图象在 $(0,1)$ 处的切线方程为 $y=2x+1$，若 $f(x)\geq mx+x$ 恒成立，则 $m$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>$\left[-1,2\mathrm{e}-1\right]$</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,2\mathrm{e}-1\right]$</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>$\left[-1,\mathrm{e}-1\right]$</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,\mathrm{e}-1\right]$</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=a^{x}\ln a$，由切线斜率为 $2$ 得 $f'(0)=\ln a=2$，故 $a=\mathrm{e}^{2}$，$f(x)=\mathrm{e}^{2x}$。所求即 $\mathrm{e}^{2x}\geq(m+1)x$ 对任意 $x$ 恒成立。记 $k=m+1$。$k&lt;0$ 时取 $x\to-\infty$，$kx\to+\infty$ 而 $\mathrm{e}^{2x}\to0$，不成立；$k=0$ 时显然成立。$k&gt;0$ 时，临界情形是 $y=kx$ 与 $y=\mathrm{e}^{2x}$ 相切：$\begin{cases}2\mathrm{e}^{2x_{0}}=k\\ \mathrm{e}^{2x_{0}}=kx_{0}\end{cases}$，代入消去 $k$ 得 $\mathrm{e}^{2x_{0}}=2\mathrm{e}^{2x_{0}}x_{0}$，即 $x_{0}=\frac12$，$k=2\mathrm{e}$。故 $0\leq k\leq2\mathrm{e}$，即 $-1\leq m\leq2\mathrm{e}-1$。选 A。</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S152" t="n">
+        <v>5</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-094-V1</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>M-H0153</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>M-T-094(函数与导数 / 导数切线与公切线 · 切线的应用：恒成立求参等应用)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>若曲线 $y=\ln x$ 在点 $P\left(x_{1},y_{1}\right)$ 处的切线与曲线 $y=\mathrm{e}^{x}$ 相切于点 $Q\left(x_{2},y_{2}\right)$，则 $\dfrac{x_{1}+1}{x_{1}-1}+x_{2}=$ ____</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>$0$</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>$y=\ln x$ 在 $P$ 处的切线方程为 $y-\ln x_{1}=\frac1{x_{1}}\left(x-x_{1}\right)$，即 $y=\frac1{x_{1}}x+\ln x_{1}-1$；$y=\mathrm{e}^{x}$ 在 $Q$ 处的切线方程为 $y-\mathrm{e}^{x_{2}}=\mathrm{e}^{x_{2}}\left(x-x_{2}\right)$，即 $y=\mathrm{e}^{x_{2}}x+\mathrm{e}^{x_{2}}\left(1-x_{2}\right)$。两切线重合，比较斜率与截距：$\frac1{x_{1}}=\mathrm{e}^{x_{2}}$，$\ln x_{1}-1=\mathrm{e}^{x_{2}}\left(1-x_{2}\right)$。由第一式得 $x_{2}=-\ln x_{1}$，代入第二式：$\ln x_{1}-1=\frac1{x_{1}}\left(1+\ln x_{1}\right)$。两边乘 $x_{1}$ 整理：$x_{1}\ln x_{1}-x_{1}=1+\ln x_{1}$，即 $\left(x_{1}-1\right)\ln x_{1}=x_{1}+1$，故 $\ln x_{1}=\frac{x_{1}+1}{x_{1}-1}$。</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S153" t="n">
+        <v>5</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-094-V2</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>M-H0154</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>M-T-094(函数与导数 / 导数切线与公切线 · 切线的应用：恒成立求参等应用)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\ln x$，$g(x)=ax+1$，若存在 $x_{0}\geq\dfrac1{\mathrm{e}}$ 使得 $f\left(x_{0}\right)=g\left(-x_{0}\right)$，则实数 $a$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>$\left[-2\mathrm{e},\dfrac{1}{\mathrm{e}^{2}}\right]$</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>$\left[-\dfrac{1}{\mathrm{e}^{2}},2\mathrm{e}\right]$</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac{1}{2\mathrm{e}},\mathrm{e}^{2}\right]$</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac{1}{\mathrm{e}^{2}},2\mathrm{e}\right]$</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>$f\left(x_{0}\right)=g\left(-x_{0}\right)$ 即 $\ln x_{0}=-ax_{0}+1$，也就是直线 $y=-ax+1$ 与曲线 $y=\ln x$ 在 $x\geq\frac1{\mathrm{e}}$ 上有交点。记 $h(x)=-ax+1-\ln x$，需求 $h$ 在 $\left[\frac1{\mathrm{e}},+\infty\right)$ 上有零点。$a\geq0$ 时 $h'(x)=-a-\frac1x&lt;0$，$h$ 递减。$h\!\left(\frac1{\mathrm{e}}\right)=2-\frac a{\mathrm{e}}$，且 $h(+\infty)=-\infty$，故有零点 $\iff h\!\left(\frac1{\mathrm{e}}\right)\geq0\iff a\leq2\mathrm{e}$，得 $a\in[0,2\mathrm{e}]$。$a&lt;0$ 时记 $a=-p\ (p&gt;0)$，$h(x)=px+1-\ln x$ 在 $x=\frac1p$ 处取最小值 $2+\ln p$，且 $h\!\left(\frac1{\mathrm{e}}\right)=\frac p{\mathrm{e}}+2&gt;0$、$h(+\infty)=+\infty$。要有零点需 $\frac1p\geq\frac1{\mathrm{e}}$（极值点在区间内，即 $p\leq\mathrm{e}$）且 $2+\ln p\leq0$，即 $p\leq\frac1{\mathrm{e}^{2}}$，得 $a\in\left[-\frac1{\mathrm{e}^{2}},0\right)$。合并得 $a\in\left[-\frac1{\mathrm{e}^{2}},2\mathrm{e}\right]$。选 B。</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-094-V3</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V154" s="2" t="inlineStr">
+        <is>
+          <t>另解校验：相切时 $-a=\frac1m$ 且 $-am+1=\ln m$，消去 $a$ 得 $2=\ln m$，$m=\mathrm{e}^{2}$，$a=-\frac1{\mathrm{e}^{2}}$；过端点 $\left(\frac1{\mathrm{e}},-1\right)$ 时 $-1=-\frac a{\mathrm{e}}+1$，$a=2\mathrm{e}$。两端点吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>M-H0155</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>M-T-095(函数与导数 / 导数切线与公切线 · 切线的应用：零点等)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 满足 $f(x)=f\left(\dfrac1x\right)$，当 $x\in[1,3]$ 时，$f(x)=\ln x$，若在区间 $\left[\dfrac13,3\right]$ 内，函数 $g(x)=f(x)-ax$ 与 $x$ 轴有三个不同的交点，则实数 $a$ 的取值范围是 ____</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac{\ln 3}{3},\dfrac1{\mathrm{e}}\right)$</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>当 $x\in\left[\frac13,1\right)$ 时 $\frac1x\in(1,3]$，故 $f(x)=f\!\left(\frac1x\right)=\ln\frac1x=-\ln x$；当 $x\in[1,3]$ 时 $f(x)=\ln x$。$g(x)$ 与 $x$ 轴有三个交点等价于直线 $y=ax$ 与 $y=f(x)$ 有三个公共点。在 $\left[\frac13,1\right]$ 上：$f=-\ln x$ 递减（$\ln3\to0$），$y=ax$ 递增，端点异号（$\ln3-\frac a3&gt;0$，$0-a&lt;0$），故恒有且仅有 $1$ 个交点。在 $[1,3]$ 上：记 $u(x)=\ln x-ax$，$u'(x)=\frac1x-a$，$u$ 在 $x=\frac1a$ 处取最大值 $-\ln a-1$。$a&lt;\frac1{\mathrm{e}}$ 时最大值 $&gt;0$，结合 $u(1)=-a&lt;0$，交点个数取决于 $u(3)=\ln3-3a$：$u(3)&gt;0$（$a&lt;\frac{\ln3}3$）时只有 $1$ 个；$u(3)\leq0$（$a\geq\frac{\ln3}3$）时有 $2$ 个。$a=\frac1{\mathrm{e}}$ 时相切只有 $1$ 个；$a&gt;\frac1{\mathrm{e}}$ 时无交点。故要有三个交点需 $a\in\left[\frac{\ln3}3,\frac1{\mathrm{e}}\right)$。</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S155" t="n">
+        <v>5</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-095-E1</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V155" s="2" t="inlineStr">
+        <is>
+          <t>原书解析把左支写成 $-2\ln x$，应为 $-\ln x$（由 $f(x)=f(1/x)=\ln(1/x)$ 直接得出）。数值扫描按 $-\ln x$ 核验：$a=0.3662=\frac{\ln3}3$ 时 $2$ 根、$a=0.367$ 时 $3$ 根、$a=0.3679=\frac1{\mathrm e}$ 时 $3$ 根、$a=0.38$ 时 $1$ 根，与答案区间一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>M-H0156</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>M-T-095(函数与导数 / 导数切线与公切线 · 切线的应用：零点等)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $y=\begin{cases}\sin\left(x+\dfrac\pi2\right),&amp; x\in\left[2k\pi-\dfrac\pi2,2k\pi+\dfrac\pi2\right]\\[4pt]-\sin\left(x+\dfrac\pi2\right),&amp; x\in\left[2k\pi+\dfrac\pi2,2k\pi+\dfrac{3\pi}2\right]\end{cases}\ (k\in\mathbb{Z})$ 的图象与直线 $y=m(x+2)$（$m&gt;0$）恰有四个公共点 $A\left(x_{1},y_{1}\right)$、$B\left(x_{2},y_{2}\right)$、$C\left(x_{3},y_{3}\right)$、$D\left(x_{4},y_{4}\right)$，其中 $x_{1}&lt;x_{2}&lt;x_{3}&lt;x_{4}$，则 $\left(x_{4}+2\right)\tan x_{4}=$ ____</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>$-1$</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>由 $\sin\left(x+\frac\pi2\right)=\cos x$，该分段函数即 $y=|\cos x|$。直线 $y=m(x+2)$ 恒过定点 $(-2,0)$。恰有四个公共点时，第 $4$ 个点 $D$ 是直线与曲线的切点。当 $x\in\left[\frac\pi2,\frac{3\pi}2\right]$ 时 $f(x)=-\cos x$，$f'(x)=\sin x$。设切点为 $\left(x_{4},-\cos x_{4}\right)$，切线方程为 $y+\cos x_{4}=\sin x_{4}\left(x-x_{4}\right)$。切线过 $(-2,0)$，代入得 $\cos x_{4}=\sin x_{4}\left(-2-x_{4}\right)$，两边除以 $\cos x_{4}$ 得 $1=-\left(x_{4}+2\right)\tan x_{4}$，即 $\left(x_{4}+2\right)\tan x_{4}=-1$。</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S156" t="n">
+        <v>5</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-095-V1</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V156" s="2" t="inlineStr">
+        <is>
+          <t>数值验证：解 $\cos x+\sin x\,(x+2)=0$ 得切点 $x_{4}\approx2.94194$，代入得 $(x_{4}+2)\tan x_{4}=-1.000000$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>M-H0157</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>M-T-095(函数与导数 / 导数切线与公切线 · 切线的应用：零点等)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>关于 $x$ 的方程 $kx=\sin x$（$k\in(0,1)$）在 $(-3\pi,3\pi)$ 内有且仅有 $5$ 个根，设最大的根是 $\alpha$，则 $\alpha$ 与 $\tan\alpha$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>$\alpha&gt;\tan\alpha$</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>$\alpha&lt;\tan\alpha$</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>$\alpha=\tan\alpha$</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>以上都不对</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>作出 $y=kx$ 与 $y=\sin x$ 在 $(-3\pi,3\pi)$ 内的图象。$y=\sin x$ 在一个周期内有正有负，而 $0&lt;k&lt;1$，直线 $y=kx$ 与正弦曲线在正半轴的交点个数随 $k$ 减小而增多。有且仅有 $5$ 个根时，由对称性（两函数都是奇函数）知正负半轴根数对称，第 $5$ 个（最大的）根 $\alpha$ 必是 $y=kx$ 与 $y=\sin x$ 在 $\left(2\pi,\frac{5\pi}2\right)$ 内相切时切点的横坐标。设切点为 $\left(\alpha,\sin\alpha\right)$，则 $k=\cos\alpha$ 且 $\sin\alpha=k\alpha=\alpha\cos\alpha$。由 $\sin\alpha=\alpha\cos\alpha$ 得 $\tan\alpha=\alpha$。选 C。</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S157" t="n">
+        <v>5</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-095-V2</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>M-H0158</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>导数切线与公切线</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>M-T-095(函数与导数 / 导数切线与公切线 · 切线的应用：零点等)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 满足 $f(1+x)=f(1-x)$，且 $x\in\left[1,\mathrm{e}^{2}\right]$ 时，$f(x)=\ln x$，若 $x\in\left[2-\mathrm{e}^{2},1\right]$ 时，方程 $f(x)=k(x-2)$ 有三个不同的根，则 $k$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac{2}{\mathrm{e}^{2}},\dfrac1{\mathrm{e}}\right)$</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,\dfrac1{\mathrm{e}}\right)$</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac1{\mathrm{e}},-\dfrac{2}{\mathrm{e}^{2}}\right]$</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac1{\mathrm{e}},+\infty\right)$</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(1+x)=f(1-x)$ 知 $f$ 的图象关于直线 $x=1$ 对称。已知 $x\in\left[1,\mathrm{e}^{2}\right]$ 时 $f(x)=\ln x$，则 $x\in\left[2-\mathrm{e}^{2},1\right]$ 时 $2-x\in\left[1,\mathrm{e}^{2}\right]$，$f(x)=f(2-x)=\ln(2-x)$。直线 $y=k(x-2)$ 恒过定点 $(2,0)$。在左支 $x\in\left[2-\mathrm{e}^{2},1\right]$ 上，$f(x)=\ln(2-x)$，$f'(x)=\frac1{x-2}$。设切点为 $\left(x_{0},\ln\left(2-x_{0}\right)\right)$，则 $k=\frac1{x_{0}-2}$，切线方程 $y-\ln(2-x_{0})=\frac1{x_{0}-2}\left(x-x_{0}\right)$。代入 $(2,0)$ 得 $-\ln\left(2-x_{0}\right)=\frac{2-x_{0}}{x_{0}-2}=-1$，故 $\ln\left(2-x_{0}\right)=1$，$x_{0}=2-\mathrm{e}$，$k=-\frac1{\mathrm{e}}$。直线过左端点 $\left(2-\mathrm{e}^{2},2\right)$ 时 $k=\frac{2}{- \mathrm{e}^{2}}=-\frac{2}{\mathrm{e}^{2}}$。由图象，$k$ 从 $-\frac1{\mathrm{e}}$（相切，此时两根重合）向右到 $-\frac{2}{\mathrm{e}^{2}}$（过端点，仍为三个根）时恰有三个不同的根，故 $k\in\left(-\frac1{\mathrm{e}},-\frac{2}{\mathrm{e}^{2}}\right]$。选 C。</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S158" t="n">
+        <v>5</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-095-V3</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V158" s="2" t="inlineStr">
+        <is>
+          <t>数值扫描核验（定义域 $[2-\mathrm{e}^{2},\mathrm{e}^{2}]$，逐段计数）：$k=-0.3679$ 时 $1$ 根、$k=-0.3675$ 时 $3$ 根、$k=-0.30$ 时 $3$ 根、$k=-0.2707=-\frac2{\mathrm e^{2}}$ 时 $3$ 根、$k=-0.2705$ 时 $2$ 根，与答案区间一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>M-H0159</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>M-T-096(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在常数位置(单参))</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=a\ln x+x-1$（$a\in\mathbb{R}$）。讨论 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>当 $a\geq0$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递增，无单调递减区间；当 $a&lt;0$ 时，$f(x)$ 在 $(0,-a)$ 上单调递减，在 $(-a,+\infty)$ 上单调递增。</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(0,+\infty)$，$f'(x)=\dfrac ax+1=\dfrac{x+a}{x}$。① 当 $a\geq0$ 时，$x+a&gt;0$ 且 $x&gt;0$，故 $f'(x)&gt;0$，$f(x)$ 在 $(0,+\infty)$ 上单调递增。② 当 $a&lt;0$ 时，令 $f'(x)=0$ 得 $x=-a$（在定义域内）。当 $x\in(0,-a)$ 时 $x+a&lt;0$，$f'(x)&lt;0$，$f(x)$ 单调递减；当 $x\in(-a,+\infty)$ 时 $x+a&gt;0$，$f'(x)&gt;0$，$f(x)$ 单调递增。综上：当 $a\geq0$ 时，$f(x)$ 的单调递增区间为 $(0,+\infty)$，无单调递减区间；当 $a&lt;0$ 时，$f(x)$ 的单调递减区间为 $(0,-a)$，单调递增区间为 $(-a,+\infty)$。</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-096-E1</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V159" s="2" t="inlineStr">
+        <is>
+          <t>原书第 (2) 问为「若函数 $y=f(\mathrm e^{x})-ax+1$ 与 $y=\mathrm e^{a}(\ln x+a)$ 的图象有两个不同的公共点，求 $a$ 的取值范围」，答案 $(1,+\infty)$，但原书未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>M-H0160</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>M-T-096(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在常数位置(单参))</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\ln x+\dfrac ax$，$g(x)=\mathrm e^{x}+\sin x$，其中 $a\in\mathbb{R}$。 试讨论函数 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>当 $a\leq0$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递增，无减区间；当 $a&gt;0$ 时，$f(x)$ 在 $(0,a)$ 上单调递减，在 $(a,+\infty)$ 上单调递增。</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)=\ln x+\dfrac ax$ 的定义域为 $(0,+\infty)$，$f'(x)=\dfrac1x-\dfrac a{x^{2}}=\dfrac{x-a}{x^{2}}$。因 $x^{2}&gt;0$，$f'(x)$ 的符号由 $x-a$ 决定。① 当 $a\leq0$ 时，对一切 $x&gt;0$ 有 $x-a&gt;0$，故 $f'(x)&gt;0$，$f(x)$ 在 $(0,+\infty)$ 上单调递增。② 当 $a&gt;0$ 时：令 $f'(x)&gt;0$ 得 $x&gt;a$；令 $f'(x)&lt;0$ 得 $0&lt;x&lt;a$。故 $f(x)$ 在 $(0,a)$ 上单调递减，在 $(a,+\infty)$ 上单调递增。综上：当 $a\leq0$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递增，无减区间；当 $a&gt;0$ 时，$f(x)$ 在 $(0,a)$ 上单调递减，在 $(a,+\infty)$ 上单调递增。</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S160" t="n">
+        <v>5</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-096-V1</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V160" s="2" t="inlineStr">
+        <is>
+          <t>题干中 $g(x)=\mathrm e^{x}+\sin x$ 是原书第 (2) 问用的函数，第 (1) 问用不到，为保持题干完整而保留。原书第 (2) 问为「若 $a=1$，证明 $f(x)&lt;\dfrac{g(x)}x$」，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>M-H0161</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>M-T-096(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在常数位置(单参))</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=(2x-a)\mathrm e^{x}$。求 $f(x)$ 的单调区间。</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的单调递减区间为 $\left(-\infty,\dfrac{a-2}2\right)$，单调递增区间为 $\left(\dfrac{a-2}2,+\infty\right)$。</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $\mathbb{R}$，$f'(x)=2\mathrm e^{x}+(2x-a)\mathrm e^{x}=(2x+2-a)\mathrm e^{x}$。因 $\mathrm e^{x}&gt;0$ 恒成立，$f'(x)$ 的符号由 $2x+2-a$ 决定。令 $f'(x)=0$ 得 $x=\dfrac{a-2}2$。当 $x\in\left(-\infty,\dfrac{a-2}2\right)$ 时 $2x+2-a&lt;0$，$f'(x)&lt;0$，$f(x)$ 单调递减；当 $x\in\left(\dfrac{a-2}2,+\infty\right)$ 时 $2x+2-a&gt;0$，$f'(x)&gt;0$，$f(x)$ 单调递增。故 $f(x)$ 的单调递减区间为 $\left(-\infty,\dfrac{a-2}2\right)$，单调递增区间为 $\left(\dfrac{a-2}2,+\infty\right)$。</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S161" t="n">
+        <v>5</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-096-V2</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V161" s="2" t="inlineStr">
+        <is>
+          <t>原书第 (2) 问为「若 $f(x)$ 的极值点为 $-\dfrac12$，且 $f(m)=f(n)$（$m\neq n$），证明 $-\dfrac3{\mathrm e}&lt;f(m+n)&lt;0$」，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>M-H0162</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>M-T-097(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在系数位置(单参))</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=2\ln x+a(x+a)$。讨论 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>当 $a\geq0$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递增；当 $a&lt;0$ 时，$f(x)$ 在 $\left(0,-\dfrac2a\right)$ 上单调递增，在 $\left(-\dfrac2a,+\infty\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(0,+\infty)$，$f(x)=2\ln x+ax+a^{2}$，$f'(x)=\dfrac2x+a=\dfrac{ax+2}{x}$。① 当 $a\geq0$ 时，$ax+2&gt;0$，故 $f'(x)&gt;0$，$f(x)$ 在 $(0,+\infty)$ 上单调递增。② 当 $a&lt;0$ 时，令 $f'(x)=0$ 得 $x=-\dfrac2a&gt;0$（在定义域内）。当 $x\in\left(0,-\dfrac2a\right)$ 时 $ax+2&gt;0$，$f'(x)&gt;0$，$f(x)$ 单调递增；当 $x\in\left(-\dfrac2a,+\infty\right)$ 时 $ax+2&lt;0$，$f'(x)&lt;0$，$f(x)$ 单调递减。综上：当 $a\geq0$ 时，$f(x)$ 在 $(0,+\infty)$ 上为单调递增函数；当 $a&lt;0$ 时，$f(x)$ 在 $\left(0,-\dfrac2a\right)$ 上单调递增，在 $\left(-\dfrac2a,+\infty\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S162" t="n">
+        <v>5</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-097-E1</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V162" s="2" t="inlineStr">
+        <is>
+          <t>原书第 (2) 问为「若 $x_{1},x_{2}$（$x_{1}&lt;x_{2}$）是 $g(x)=f(x)+x^{2}+ax$ 的两个极值点，证明 $g(x_{2})&gt;x_{1}$」，未给出详解，本录不含。注意由 $g(x)=2\ln x+(x+a)^{2}$ 可反推 $f(x)=2\ln x+ax+a^{2}$，即 $2\ln x+a(x+a)$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>M-H0163</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>M-T-097(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在系数位置(单参))</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=a\ln x+\dfrac1x+4$，其中 $a\in\mathbb{R}$。讨论函数 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>当 $a\leq0$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递减；当 $a&gt;0$ 时，$f(x)$ 在 $\left(0,\dfrac1a\right)$ 上单调递减，在 $\left(\dfrac1a,+\infty\right)$ 上单调递增。</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(0,+\infty)$，$f'(x)=\dfrac ax-\dfrac1{x^{2}}=\dfrac{ax-1}{x^{2}}$。因 $x^{2}&gt;0$，$f'(x)$ 的符号由 $ax-1$ 决定。① 当 $a\leq0$ 时，对一切 $x&gt;0$ 有 $ax-1&lt;0$，故 $f'(x)&lt;0$，$f(x)$ 在 $(0,+\infty)$ 上单调递减。② 当 $a&gt;0$ 时：由 $f'(x)&gt;0$ 得 $x&gt;\dfrac1a$；由 $f'(x)&lt;0$ 得 $0&lt;x&lt;\dfrac1a$。故 $f(x)$ 在 $\left(0,\dfrac1a\right)$ 上单调递减，在 $\left(\dfrac1a,+\infty\right)$ 上单调递增。综上：当 $a\leq0$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递减；当 $a&gt;0$ 时，$f(x)$ 在 $\left(0,\dfrac1a\right)$ 上单调递减，在 $\left(\dfrac1a,+\infty\right)$ 上单调递增。</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S163" t="n">
+        <v>5</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-097-V1</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V163" s="2" t="inlineStr">
+        <is>
+          <t>原书第 (2) 问为「对任意 $x\in[1,\mathrm e]$，不等式 $f(x)\geq\dfrac1x+\dfrac{x+1}2$ 恒成立，求实数 $a$ 的取值范围」，答案 $\left[\dfrac{\mathrm e+1}2-4,+\infty\right)$，但原书未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>M-H0164</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>M-T-097(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在系数位置(单参))</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x\mathrm e^{mx}$（其中 $\mathrm e$ 为自然对数的底数）。讨论函数 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>当 $m=0$ 时，$f(x)$ 在 $\mathbb{R}$ 上单调递增；当 $m&gt;0$ 时，$f(x)$ 在 $\left(-\infty,-\dfrac1m\right)$ 上单调递减，在 $\left(-\dfrac1m,+\infty\right)$ 上单调递增；当 $m&lt;0$ 时，$f(x)$ 在 $\left(-\infty,-\dfrac1m\right)$ 上单调递增，在 $\left(-\dfrac1m,+\infty\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=\mathrm e^{mx}+x\cdot m\mathrm e^{mx}=(mx+1)\mathrm e^{mx}$。因 $\mathrm e^{mx}&gt;0$，$f'(x)$ 的符号由 $mx+1$ 决定。① 当 $m=0$ 时，$f'(x)=\mathrm e^{0}=1&gt;0$，$f(x)$ 在 $\mathbb{R}$ 上单调递增。② 当 $m&gt;0$ 时，令 $f'(x)=0$ 得 $x=-\dfrac1m$。$x\in\left(-\infty,-\dfrac1m\right)$ 时 $mx+1&lt;0$，$f'(x)&lt;0$，$f(x)$ 单调递减；$x\in\left(-\dfrac1m,+\infty\right)$ 时 $mx+1&gt;0$，$f'(x)&gt;0$，$f(x)$ 单调递增。③ 当 $m&lt;0$ 时，令 $f'(x)=0$ 得 $x=-\dfrac1m$（注意此时 $-\dfrac1m&gt;0$）。$x\in\left(-\infty,-\dfrac1m\right)$ 时 $mx+1&gt;0$，$f'(x)&gt;0$，$f(x)$ 单调递增；$x\in\left(-\dfrac1m,+\infty\right)$ 时 $mx+1&lt;0$，$f'(x)&lt;0$，$f(x)$ 单调递减。综上：当 $m=0$ 时，$f(x)$ 在 $\mathbb{R}$ 上单调递增；当 $m&gt;0$ 时，$f(x)$ 在 $\left(-\infty,-\dfrac1m\right)$ 上单调递减、在 $\left(-\dfrac1m,+\infty\right)$ 上单调递增；当 $m&lt;0$ 时，$f(x)$ 在 $\left(-\infty,-\dfrac1m\right)$ 上单调递增、在 $\left(-\dfrac1m,+\infty\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S164" t="n">
+        <v>5</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-097-V2</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V164" s="2" t="inlineStr">
+        <is>
+          <t>原书第 (2) 问为「当 $m=1$ 时，若 $f(x)\geq\ln x+ax+1$ 恒成立，求实数 $a$ 的取值范围」，答案 $(-\infty,1]$，但原书未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>M-H0165</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>M-T-097(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在系数位置(单参))</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac{\mathrm e^{ax}}x$，$g(x)=\ln x+2x+\dfrac1x$，其中 $a\in\mathbb{R}$。 试讨论函数 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>当 $a&gt;0$ 时，$f(x)$ 在 $\left(\dfrac1a,+\infty\right)$ 上单调递增，在 $(-\infty,0)$ 和 $\left(0,\dfrac1a\right)$ 上单调递减；当 $a=0$ 时，$f(x)$ 在 $(-\infty,0)$ 和 $(0,+\infty)$ 上单调递减；当 $a&lt;0$ 时，$f(x)$ 在 $\left(-\infty,\dfrac1a\right)$ 上单调递增，在 $\left(\dfrac1a,0\right)$ 和 $(0,+\infty)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(-\infty,0)\cup(0,+\infty)$，$f'(x)=\dfrac{a\mathrm e^{ax}\cdot x-\mathrm e^{ax}\cdot1}{x^{2}}=\dfrac{\mathrm e^{ax}(ax-1)}{x^{2}}$。因 $\mathrm e^{ax}&gt;0$ 且 $x^{2}&gt;0$（$x\neq0$），$f'(x)$ 的符号由 $ax-1$ 决定。① 当 $a&gt;0$ 时，$\dfrac1a&gt;0$：由 $f'(x)&gt;0$ 得 $x&gt;\dfrac1a$；由 $f'(x)&lt;0$ 得 $x&lt;0$ 或 $0&lt;x&lt;\dfrac1a$。故 $f(x)$ 在 $\left(\dfrac1a,+\infty\right)$ 上单调递增，在 $(-\infty,0)$ 和 $\left(0,\dfrac1a\right)$ 上单调递减。② 当 $a=0$ 时，$f(x)=\dfrac1x$，$f(x)$ 在 $(-\infty,0)$ 和 $(0,+\infty)$ 上单调递减。③ 当 $a&lt;0$ 时，$\dfrac1a&lt;0$：由 $f'(x)&gt;0$ 得 $x&lt;\dfrac1a$；由 $f'(x)&lt;0$ 得 $\dfrac1a&lt;x&lt;0$ 或 $x&gt;0$。故 $f(x)$ 在 $\left(-\infty,\dfrac1a\right)$ 上单调递增，在 $\left(\dfrac1a,0\right)$ 和 $(0,+\infty)$ 上单调递减。综上即得答案所述的三种情形。</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S165" t="n">
+        <v>5</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-097-V3</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V165" s="2" t="inlineStr">
+        <is>
+          <t>定义域不含 $x=0$，讨论时必须把 $(-\infty,0)$ 与 $(0,+\infty)$ 分开，这是本题最容易漏分的地方。原书第 (2) 问为「若 $a=2$，证明 $xf(x)\geq g(x)$」，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>M-H0166</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>M-T-101(函数与导数 / 导数含参讨论 · 上下平移：对数函数型)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac{a\ln x}{x}+1$（其中 $a$ 为非零实数）。讨论 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>当 $a&gt;0$ 时，$f(x)$ 在 $(0,\mathrm{e})$ 上单调递增，在 $(\mathrm{e},+\infty)$ 上单调递减；当 $a&lt;0$ 时，$f(x)$ 在 $(0,\mathrm{e})$ 上单调递减，在 $(\mathrm{e},+\infty)$ 上单调递增。</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(0,+\infty)$，$f'(x)=a\cdot\dfrac{1-\ln x}{x^{2}}=\dfrac{a(1-\ln x)}{x^{2}}$。因 $x^{2}&gt;0$，$f'(x)$ 的符号由 $a$ 与 $1-\ln x$ 的乘积决定，而 $1-\ln x&gt;0\iff 0&lt;x&lt;\mathrm{e}$。① 当 $a&gt;0$ 时：当 $x\in(0,\mathrm{e})$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增；当 $x\in(\mathrm{e},+\infty)$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减。② 当 $a&lt;0$ 时：当 $x\in(0,\mathrm{e})$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减；当 $x\in(\mathrm{e},+\infty)$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增。</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S166" t="n">
+        <v>5</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-101-V1</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V166" s="2" t="inlineStr">
+        <is>
+          <t>原书第 (2) 问为「若函数 $g(x)=\mathrm e^{x}-f(x)$ 有两个零点，①求实数 $a$ 的取值范围；②设两个零点分别为 $x_{1}$、$x_{2}$，求证 $x_{1}x_{2}&gt;\mathrm e^{2}$」，答案分别为 $(\mathrm e,+\infty)$ 与「证明见解析」，但原书未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>M-H0167</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>M-T-101(函数与导数 / 导数含参讨论 · 上下平移：对数函数型)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac{a+\ln x}{x}$（$a\in\mathbb{R}$）。求函数 $f(x)$ 的单调区间。</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的单调递增区间为 $\left(0,\mathrm{e}^{1-a}\right)$，单调递减区间为 $\left(\mathrm{e}^{1-a},+\infty\right)$。</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(0,+\infty)$，求导得 $f'(x)=\dfrac{1-a-\ln x}{x^{2}}$。令 $f'(x)=0$，即 $1-a-\ln x=0$，解得 $x=\mathrm{e}^{1-a}$。因 $x^{2}&gt;0$，$f'(x)$ 的符号由 $1-a-\ln x$ 决定，而 $1-a-\ln x&gt;0\iff x&lt;\mathrm{e}^{1-a}$。当 $x\in\left(0,\mathrm{e}^{1-a}\right)$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增；当 $x\in\left(\mathrm{e}^{1-a},+\infty\right)$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减。故 $f(x)$ 的单调递增区间为 $\left(0,\mathrm{e}^{1-a}\right)$，单调递减区间为 $\left(\mathrm{e}^{1-a},+\infty\right)$。</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S167" t="n">
+        <v>5</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-101-V2</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V167" s="2" t="inlineStr">
+        <is>
+          <t>原书第 (2) 问为「当函数 $f(x)$ 与函数 $g(x)=\ln x$ 图象的公切线 $l$ 经过坐标原点时，求实数 $a$ 的取值集合」，答案为 $\left\{\dfrac{\ln2}2\right\}$；第 (3) 问为证明题。两问原书均未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>M-H0168</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>M-T-101(函数与导数 / 导数含参讨论 · 上下平移：对数函数型)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>设 $a$，$b$ 为实数，且 $a&gt;1$，函数 $f(x)=a^{x}-bx+\mathrm{e}^{2}$（$x\in\mathbb{R}$）。 求函数 $f(x)$ 的单调区间。</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>当 $b\leq0$ 时，$f(x)$ 在 $(-\infty,+\infty)$ 上单调递增；当 $b&gt;0$ 时，$f(x)$ 在 $\left(-\infty,\log_{a}\dfrac b{\ln a}\right)$ 上单调递减，在 $\left(\log_{a}\dfrac b{\ln a},+\infty\right)$ 上单调递增。</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>求导得 $f'(x)=a^{x}\ln a-b$。因 $a&gt;1$，有 $\ln a&gt;0$ 且 $a^{x}&gt;0$。① 当 $b\leq0$ 时，$a^{x}\ln a&gt;0\geq b$，故 $f'(x)&gt;0$ 恒成立，$f(x)$ 在 $\mathbb{R}$ 上单调递增。② 当 $b&gt;0$ 时，令 $f'(x)&gt;0$ 得 $a^{x}&gt;\dfrac b{\ln a}$，即 $x&gt;\log_{a}\dfrac b{\ln a}$；令 $f'(x)&lt;0$ 得 $x&lt;\log_{a}\dfrac b{\ln a}$。故 $f(x)$ 在 $\left(-\infty,\log_{a}\dfrac b{\ln a}\right)$ 上单调递减，在 $\left(\log_{a}\dfrac b{\ln a},+\infty\right)$ 上单调递增。</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S168" t="n">
+        <v>5</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-101-V3</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V168" s="2" t="inlineStr">
+        <is>
+          <t>原书第 (2) 问为「若对任意 $b&gt;2\mathrm e^{2}$，函数 $f(x)$ 有两个不同的零点，求 $a$ 的取值范围」，答案 $(1,\mathrm e^{2}]$，但原书未给出详解，本录不含。注意 $f'(x)&gt;0$ 的解要写成 $\log_{a}\frac b{\ln a}$（对数的真数是 $\frac b{\ln a}$，不是 $b$），这是本题最容易写错的地方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>M-H0169</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>M-T-102(函数与导数 / 导数含参讨论 · 一元二次可因式分解型)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=mx^{2}+(m-2)x\ln x+2$（$m\in\mathbb{R}$）。 设 $g(x)=\dfrac{f(x)}x$，讨论函数 $g(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>当 $m\leq0$ 时，$g(x)$ 在 $(0,+\infty)$ 上单调递减；当 $m&gt;0$ 时，$g(x)$ 在 $\left(0,\dfrac2m\right)$ 上单调递减，在 $\left(\dfrac2m,+\infty\right)$ 上单调递增。</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>由题 $g(x)=\dfrac{f(x)}x=mx+(m-2)\ln x+\dfrac2x$，定义域为 $(0,+\infty)$，$g'(x)=m+\dfrac{m-2}x-\dfrac2{x^{2}}=\dfrac{mx^{2}+(m-2)x-2}{x^{2}}=\dfrac{(mx-2)(x+1)}{x^{2}}$。因 $x^{2}&gt;0$ 且 $x+1&gt;0$（$x&gt;0$），$g'(x)$ 的符号由 $mx-2$ 决定。① 当 $m\leq0$ 时，$mx-2&lt;0$ 恒成立，故 $g'(x)&lt;0$，$g(x)$ 在 $(0,+\infty)$ 上单调递减。② 当 $m&gt;0$ 时：由 $g'(x)&gt;0$ 得 $x&gt;\dfrac2m$；由 $g'(x)&lt;0$ 得 $0&lt;x&lt;\dfrac2m$。故 $g(x)$ 在 $\left(0,\dfrac2m\right)$ 上单调递减，在 $\left(\dfrac2m,+\infty\right)$ 上单调递增。综上：当 $m\leq0$ 时，$g(x)$ 在 $(0,+\infty)$ 上单调递减；当 $m&gt;0$ 时，$g(x)$ 在 $\left(\dfrac2m,+\infty\right)$ 上单调递增，在 $\left(0,\dfrac2m\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S169" t="n">
+        <v>5</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-102-E1</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V169" s="2" t="inlineStr">
+        <is>
+          <t>因式分解是本题关键：$mx^{2}+(m-2)x-2=(mx-2)(x+1)$。原书第 (2) 问为求实数 $t$ 的取值范围，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>M-H0170</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>M-T-102(函数与导数 / 导数含参讨论 · 一元二次可因式分解型)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=ax^{2}-(1+2a)x+\ln x$。讨论 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>当 $a\leq0$ 时，$f(x)$ 在 $(0,1)$ 上单调递增，在 $(1,+\infty)$ 上单调递减；当 $a=\dfrac12$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递增；当 $0&lt;a&lt;\dfrac12$ 时，$f(x)$ 在 $(0,1)$ 和 $\left(\dfrac1{2a},+\infty\right)$ 上单调递增，在 $\left(1,\dfrac1{2a}\right)$ 上单调递减；当 $a&gt;\dfrac12$ 时，$f(x)$ 在 $\left(0,\dfrac1{2a}\right)$ 和 $(1,+\infty)$ 上单调递增，在 $\left(\dfrac1{2a},1\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(0,+\infty)$，$f'(x)=2ax-(1+2a)+\dfrac1x=\dfrac{2ax^{2}-(1+2a)x+1}{x}=\dfrac{(2ax-1)(x-1)}x$。① 当 $a\leq0$ 时，恒有 $2ax-1&lt;0$（因 $x&gt;0$）。当 $x\in(0,1)$ 时 $x-1&lt;0$，$f'(x)&gt;0$；当 $x\in(1,+\infty)$ 时 $x-1&gt;0$，$f'(x)&lt;0$。故 $f(x)$ 在 $(0,1)$ 上单调递增，在 $(1,+\infty)$ 上单调递减。② 当 $a&gt;0$ 时，令 $f'(x)=0$ 得 $x_{1}=1$，$x_{2}=\dfrac1{2a}$。若 $a=\dfrac12$，两根重合为 $1$，恒有 $f'(x)\geq0$，$f(x)$ 在 $(0,+\infty)$ 上单调递增。若 $0&lt;a&lt;\dfrac12$，则 $\dfrac1{2a}&gt;1$：当 $x\in(0,1)\cup\left(\dfrac1{2a},+\infty\right)$ 时 $f'(x)&gt;0$，当 $x\in\left(1,\dfrac1{2a}\right)$ 时 $f'(x)&lt;0$；若 $a&gt;\dfrac12$，则 $\dfrac1{2a}&lt;1$：当 $x\in\left(0,\dfrac1{2a}\right)\cup(1,+\infty)$ 时 $f'(x)&gt;0$，当 $x\in\left(\dfrac1{2a},1\right)$ 时 $f'(x)&lt;0$。由此即得答案所述的四种情形。</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S170" t="n">
+        <v>5</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-102-V1</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V170" s="2" t="inlineStr">
+        <is>
+          <t>本题有两根 $1$ 与 $\frac1{2a}$，必须比较二者大小，这是分类讨论的分界点。原书第 (2) 问为「当 $a=0$ 时，证明 $\frac{\mathrm e^{x}}x&gt;\frac7{10}-x^{2}-2f(x)$」，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>M-H0171</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>M-T-102(函数与导数 / 导数含参讨论 · 一元二次可因式分解型)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>设函数 $f(x)=x^{2}+ax-3a^{2}\ln x$，其中 $a\in\mathbb{R}$。讨论 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>当 $a=0$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递增；当 $a&lt;0$ 时，$f(x)$ 在 $\left(0,-\dfrac{3a}2\right)$ 上单调递减，在 $\left(-\dfrac{3a}2,+\infty\right)$ 上单调递增；当 $a&gt;0$ 时，$f(x)$ 在 $(0,a)$ 上单调递减，在 $(a,+\infty)$ 上单调递增。</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(0,+\infty)$，$f'(x)=2x+a-\dfrac{3a^{2}}x=\dfrac{2x^{2}+ax-3a^{2}}x=\dfrac{(x-a)(2x+3a)}x$。① 当 $a=0$ 时，$f'(x)=2x&gt;0$，$f(x)$ 在 $(0,+\infty)$ 上单调递增。② 当 $a&lt;0$ 时，$-\dfrac{3a}2&gt;0$。当 $0&lt;x&lt;-\dfrac{3a}2$ 时，$x-a&gt;0$（因 $x&gt;0&gt;a$）而 $2x+3a&lt;0$，故 $f'(x)&lt;0$，$f(x)$ 单调递减；当 $x&gt;-\dfrac{3a}2$ 时 $2x+3a&gt;0$，故 $f'(x)&gt;0$，$f(x)$ 单调递增。③ 当 $a&gt;0$ 时，当 $0&lt;x&lt;a$ 时 $x-a&lt;0$ 且 $2x+3a&gt;0$，故 $f'(x)&lt;0$，$f(x)$ 单调递减；当 $x&gt;a$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增。综上即得答案所述的三种情形。</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S171" t="n">
+        <v>5</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-102-V2</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V171" s="2" t="inlineStr">
+        <is>
+          <t>因式分解：$2x^{2}+ax-3a^{2}=(x-a)(2x+3a)$。注意 $a&lt;0$ 时在定义域内的根是 $-\frac{3a}2$（另一根 $a&lt;0$ 不在定义域内）。原书第 (2) 问为「当 $a&gt;0$ 时，若 $y=f(x)$ 的图象与直线 $y=5a^{2}-3a$ 没有公共点，求 $a$ 的取值范围」，答案 $(0,1)$，但原书未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>M-H0172</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>M-T-102(函数与导数 / 导数含参讨论 · 一元二次可因式分解型)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac{x^{2}-a^{2}+2a}{\mathrm{e}^{x}}$，$a\in\mathbb{R}$。讨论函数 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>当 $a&lt;1$ 时，$f(x)$ 的单调递减区间为 $(-\infty,a]$ 和 $[2-a,+\infty)$，单调递增区间为 $[a,2-a]$；当 $a=1$ 时，$f(x)$ 在 $\mathbb{R}$ 上单调递减；当 $a&gt;1$ 时，$f(x)$ 的单调递减区间为 $(-\infty,2-a]$ 和 $[a,+\infty)$，单调递增区间为 $[2-a,a]$。</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=\dfrac{2x\cdot\mathrm e^{x}-(x^{2}-a^{2}+2a)\mathrm e^{x}}{\mathrm e^{2x}}=\dfrac{-(x^{2}-2x-a^{2}+2a)}{\mathrm e^{x}}=-\dfrac{(x-a)(x+a-2)}{\mathrm e^{x}}$。因 $\mathrm e^{x}&gt;0$，$f'(x)$ 的符号与 $-(x-a)(x+a-2)$ 相同。两根为 $x=a$ 与 $x=2-a$，需比较二者大小：当 $a&lt;1$ 时 $a&lt;2-a$，当 $a=1$ 时两根重合，当 $a&gt;1$ 时 $2-a&lt;a$。① 当 $a&lt;1$ 时：当 $x&lt;a$ 或 $x&gt;2-a$ 时 $(x-a)(x+a-2)&gt;0$，$f'(x)&lt;0$；当 $a&lt;x&lt;2-a$ 时 $f'(x)&gt;0$。② 当 $a=1$ 时，$f'(x)=-\dfrac{(x-1)^{2}}{\mathrm e^{x}}\leq0$，$f(x)$ 在 $\mathbb{R}$ 上单调递减。③ 当 $a&gt;1$ 时：当 $x&lt;2-a$ 或 $x&gt;a$ 时 $f'(x)&lt;0$；当 $2-a&lt;x&lt;a$ 时 $f'(x)&gt;0$。由此即得答案所述三种情形。</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S172" t="n">
+        <v>5</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-102-V3</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V172" s="2" t="inlineStr">
+        <is>
+          <t>两根 $a$ 与 $2-a$ 的大小关系以 $a=1$ 为界，这是本题的分类分界点。原书第 (2) 问为「当 $a=3$ 时，方程 $(x^{2}-3)\cdot f(x)=m\mathrm e^{x}-\dfrac{x^{2}-3}{\mathrm e}$ 有四个根，求实数 $m$ 的取值范围」，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>M-H0173</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>M-T-103(函数与导数 / 导数含参讨论 · 一元二次不能因式分解：判别式+韦达定理+求根公式)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\ln x+x^{2}-ax$（$a\in\mathbb{R}$）。求函数 $f(x)$ 的单调区间。</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>当 $a\leq2\sqrt2$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递增；当 $a&gt;2\sqrt2$ 时，$f(x)$ 在 $\left(0,\dfrac{a-\sqrt{a^{2}-8}}4\right)$ 和 $\left(\dfrac{a+\sqrt{a^{2}-8}}4,+\infty\right)$ 上单调递增，在 $\left(\dfrac{a-\sqrt{a^{2}-8}}4,\dfrac{a+\sqrt{a^{2}-8}}4\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(0,+\infty)$，$f'(x)=\dfrac1x+2x-a=\dfrac{2x^{2}-ax+1}x$。因 $x&gt;0$，$f'(x)$ 的符号由 $2x^{2}-ax+1$ 决定。① 当 $a\leq0$ 时，$2x^{2}-ax+1&gt;0$ 恒成立，$f(x)$ 在 $(0,+\infty)$ 上单调递增。② 当 $a&gt;0$ 时，$\Delta=a^{2}-8$。若 $\Delta\leq0$，即 $0&lt;a\leq2\sqrt2$，则 $2x^{2}-ax+1\geq0$ 恒成立，$f(x)$ 在 $(0,+\infty)$ 上单调递增。若 $\Delta&gt;0$，即 $a&gt;2\sqrt2$，则 $2x^{2}-ax+1=0$ 的两根为 $x_{1}=\dfrac{a-\sqrt{a^{2}-8}}4$、$x_{2}=\dfrac{a+\sqrt{a^{2}-8}}4$（均大于 $0$）。当 $x\in(0,x_{1})\cup(x_{2},+\infty)$ 时 $f'(x)&gt;0$；当 $x\in(x_{1},x_{2})$ 时 $f'(x)&lt;0$。综上即得答案所述两种情形。</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S173" t="n">
+        <v>5</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-103-V1</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V173" s="2" t="inlineStr">
+        <is>
+          <t>分类分界点是 $\Delta=a^{2}-8=0$，即 $a=2\sqrt2$；$a&lt;0$ 时 $\Delta$ 虽可能为正，但两根均为负（不在定义域内），故仍恒增，应与 $0&lt;a\leq2\sqrt2$ 合并叙述。原书第 (2) 问为证明题，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>M-H0174</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>M-T-103(函数与导数 / 导数含参讨论 · 一元二次不能因式分解：判别式+韦达定理+求根公式)</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=ax^{2}-2a\ln x-x$（$a\in\mathbb{R}$）。讨论 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>当 $a=0$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递减；当 $a&gt;0$ 时，$f(x)$ 在 $\left(0,\dfrac{1+\sqrt{1+16a^{2}}}{4a}\right)$ 上单调递减，在 $\left(\dfrac{1+\sqrt{1+16a^{2}}}{4a},+\infty\right)$ 上单调递增；当 $a&lt;0$ 时，$f(x)$ 在 $\left(0,\dfrac{1-\sqrt{1+16a^{2}}}{4a}\right)$ 上单调递增，在 $\left(\dfrac{1-\sqrt{1+16a^{2}}}{4a},+\infty\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(0,+\infty)$，$f'(x)=2ax-\dfrac{2a}x-1=\dfrac{2ax^{2}-x-2a}x$。当 $a=0$ 时，$f(x)=-x$，$f(x)$ 在 $(0,+\infty)$ 上单调递减。当 $a\neq0$ 时，令 $g(x)=2ax^{2}-x-2a$，其判别式 $\Delta=1-4\cdot2a\cdot(-2a)=1+16a^{2}&gt;0$ 恒成立，$g(x)=0$ 的两根为 $x_{1}=\dfrac{1+\sqrt{1+16a^{2}}}{4a}$、$x_{2}=\dfrac{1-\sqrt{1+16a^{2}}}{4a}$。当 $a&gt;0$ 时，$x_{1}&gt;0$、$x_{2}&lt;0$（舍去）：当 $x\in(0,x_{1})$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减；当 $x\in(x_{1},+\infty)$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增。当 $a&lt;0$ 时，$x_{2}&gt;0$、$x_{1}&lt;0$（舍去）：当 $x\in(0,x_{2})$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增；当 $x\in(x_{2},+\infty)$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减。由此即得答案所述三种情形。</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S174" t="n">
+        <v>5</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-103-V2</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V174" s="2" t="inlineStr">
+        <is>
+          <t>$a$ 变号时，保留在定义域内的根从 $x_{1}$ 变成 $x_{2}$——分母 $4a$ 变号所致，这是本题最容易出错的地方。原书第 (2) 问为「当 $a=1$ 时，判断 $\frac{x_{1}+x_{2}}2$ 是否为导函数 $f'(x)$ 的零点」，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>M-H0175</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>M-T-103(函数与导数 / 导数含参讨论 · 一元二次不能因式分解：判别式+韦达定理+求根公式)</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x^{3}-2ax^{2}+2x+2$。讨论 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>当 $-\dfrac{\sqrt6}2\leq a\leq\dfrac{\sqrt6}2$ 时，$f(x)$ 在 $\mathbb{R}$ 上单调递增；当 $a&lt;-\dfrac{\sqrt6}2$ 或 $a&gt;\dfrac{\sqrt6}2$ 时，$f(x)$ 在 $\left(-\infty,\dfrac{2a-\sqrt{4a^{2}-6}}3\right)$ 和 $\left(\dfrac{2a+\sqrt{4a^{2}-6}}3,+\infty\right)$ 上单调递增，在 $\left(\dfrac{2a-\sqrt{4a^{2}-6}}3,\dfrac{2a+\sqrt{4a^{2}-6}}3\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>函数的定义域为 $\mathbb{R}$，$f'(x)=3x^{2}-4ax+2$，$\Delta=16a^{2}-24=8\left(2a^{2}-3\right)$。当 $\Delta\leq0$，即 $2a^{2}-3\leq0$，亦即 $-\dfrac{\sqrt6}2\leq a\leq\dfrac{\sqrt6}2$ 时，$f'(x)\geq0$ 恒成立，$f(x)$ 在 $\mathbb{R}$ 上单调递增。当 $\Delta&gt;0$，即 $a&lt;-\dfrac{\sqrt6}2$ 或 $a&gt;\dfrac{\sqrt6}2$ 时，令 $f'(x)=0$ 得 $x=\dfrac{2a\pm\sqrt{4a^{2}-6}}3$。记 $x_{1}=\dfrac{2a-\sqrt{4a^{2}-6}}3$、$x_{2}=\dfrac{2a+\sqrt{4a^{2}-6}}3$（$x_{1}&lt;x_{2}$）。$f'(x)&gt;0$ 的解集为 $(-\infty,x_{1})\cup(x_{2},+\infty)$，$f'(x)&lt;0$ 的解集为 $(x_{1},x_{2})$。故 $f(x)$ 在 $(-\infty,x_{1})$ 和 $(x_{2},+\infty)$ 上单调递增，在 $(x_{1},x_{2})$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S175" t="n">
+        <v>5</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-103-V3</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V175" s="2" t="inlineStr">
+        <is>
+          <t>PDF 文本提取把 $\frac{\sqrt6}2$ 的根号丢了，写成 $\frac62$。正确值由 $2a^{2}-3\leq0$ 得 $|a|\leq\sqrt{\frac32}=\frac{\sqrt6}2\approx1.2247$；数值抽查证实（$a=1.2$ 恒增、$a=2$ 有两根）。已按正确值录入。原书第 (2) 问为「当 $x\geq0$ 时，$2\mathrm e^{x}\geq f(x)$，求 $a$ 的取值范围」，答案 $\left[\frac{7-\mathrm e^{2}}4,+\infty\right)$，但原书未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>M-H0176</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>M-T-098(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在“斜率”和常数位置(双参))</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=(1-k)x-k\ln x+k-1$，其中 $k\in\mathbb{R}$，$k\neq0$。讨论函数 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>当 $k&lt;0$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递增；当 $0&lt;k&lt;1$ 时，$f(x)$ 在 $\left(0,\dfrac k{1-k}\right)$ 上单调递减，在 $\left(\dfrac k{1-k},+\infty\right)$ 上单调递增；当 $k\geq1$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(0,+\infty)$，$f'(x)=(1-k)-\dfrac kx=\dfrac{(1-k)x-k}x$。因 $x&gt;0$，$f'(x)$ 的符号由 $(1-k)x-k$ 决定。① 当 $1-k\leq0$ 即 $k\geq1$ 时：$1-k\leq0$ 且 $-k&lt;0$，故 $(1-k)x-k&lt;0$ 恒成立，$f'(x)&lt;0$，$f(x)$ 在 $(0,+\infty)$ 上单调递减。② 当 $k&lt;0$ 时：$-k&gt;0$ 且 $(1-k)x&gt;0$，故 $(1-k)x-k&gt;0$ 恒成立，$f'(x)&gt;0$，$f(x)$ 在 $(0,+\infty)$ 上单调递增。③ 当 $0&lt;k&lt;1$ 时：$f'(x)=\dfrac{(1-k)\left(x-\frac k{1-k}\right)}x$，其中 $\dfrac k{1-k}&gt;0$。当 $0&lt;x&lt;\dfrac k{1-k}$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减；当 $x&gt;\dfrac k{1-k}$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增。综上即得答案所述三种情形。</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S176" t="n">
+        <v>5</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-098-E1</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V176" s="2" t="inlineStr">
+        <is>
+          <t>原书【详解】末尾的综述有笔误，写成「当 $k\geq1$ 时，$f(x)$ 在 $(0,+\infty)$ 上单调递增」，与前文「$f'(x)&lt;0$，$f(x)$ 在 $(0,+\infty)$ 上单调递减」矛盾。数值抽查证实 $k=1,2,5$ 时均恒减，本录按正确的（递减）录入。原书第 (2) 问为「设函数 $f(x)$ 的导函数为 $g(x)$，若函数 $f(x)$ 恰有两个零点 $x_{1}$、$x_{2}$（$x_{1}&lt;x_{2}$），证明 $g\!\left(\frac{x_{1}+2x_{2}}3\right)&gt;0$」，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>M-H0177</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>M-T-098(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在“斜率”和常数位置(双参))</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=(ax+1)\mathrm e^{x}$，其中 $\mathrm e$ 为自然对数的底数。求函数 $f(x)$ 的单调区间。</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>当 $a=0$ 时，$f(x)$ 在 $\mathbb{R}$ 上单调递增；当 $a&gt;0$ 时，$f(x)$ 在 $\left(-\infty,-1-\dfrac1a\right)$ 上单调递减，在 $\left(-1-\dfrac1a,+\infty\right)$ 上单调递增；当 $a&lt;0$ 时，$f(x)$ 在 $\left(-\infty,-1-\dfrac1a\right)$ 上单调递增，在 $\left(-1-\dfrac1a,+\infty\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(x)=(ax+1)\mathrm e^{x}$ 求得 $f'(x)=a\mathrm e^{x}+(ax+1)\mathrm e^{x}=\mathrm e^{x}(ax+a+1)$，$x\in\mathbb{R}$。因 $\mathrm e^{x}&gt;0$，$f'(x)$ 的符号由 $ax+a+1$ 决定。记 $x_{0}=-1-\dfrac1a$（$a\neq0$）。① 当 $a=0$ 时，$f'(x)=\mathrm e^{x}&gt;0$，$f(x)$ 在 $\mathbb{R}$ 上单调递增。② 当 $a&gt;0$ 时：当 $x&lt;x_{0}$ 时 $ax+a+1&lt;0$，$f'(x)&lt;0$，$f(x)$ 单调递减；当 $x&gt;x_{0}$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增。③ 当 $a&lt;0$ 时：当 $x&lt;x_{0}$ 时 $ax+a+1&gt;0$（$a&lt;0$，$x$ 越负则 $ax$ 越大），$f'(x)&gt;0$，$f(x)$ 单调递增；当 $x&gt;x_{0}$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减。由此即得答案所述三种情形。</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S177" t="n">
+        <v>5</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-098-V1</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V177" s="2" t="inlineStr">
+        <is>
+          <t>$a$ 变号时单调性方向整体翻转，这是本题的关键。数值抽查取 $a=1,2,0.5,-1,-2$ 五组，符号全部吻合。原书第 (2) 问为「取 $a=0$ 并记此时曲线 $y=f(x)$ 在点 $P\left(x_{0},f\left(x_{0}\right)\right)$（其中 $x_{0}&lt;0$）处的切线为 $l$，$l$ 与 $x$ 轴、$y$ 轴所围成的三角形面积为 $S\left(x_{0}\right)$，求 $S\left(x_{0}\right)$ 的解析式及最大值」，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>M-H0178</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>M-T-098(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在“斜率”和常数位置(双参))</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>函数 $g(x)=ax-1-b\ln x$（$a,b\in\mathbb{R}$，$ab\neq0$）。讨论 $g(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>当 $a&gt;0$，$b&lt;0$ 时，$g(x)$ 在 $(0,+\infty)$ 上单调递增；当 $a&gt;0$，$b&gt;0$ 时，$g(x)$ 在 $\left(0,\dfrac ba\right)$ 上单调递减，在 $\left(\dfrac ba,+\infty\right)$ 上单调递增；当 $a&lt;0$，$b&gt;0$ 时，$g(x)$ 在 $(0,+\infty)$ 上单调递减；当 $a&lt;0$，$b&lt;0$ 时，$g(x)$ 在 $\left(0,\dfrac ba\right)$ 上单调递增，在 $\left(\dfrac ba,+\infty\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>$g(x)$ 的定义域为 $(0,+\infty)$，$g'(x)=a-\dfrac bx=\dfrac{ax-b}x$。因 $x&gt;0$，$g'(x)$ 的符号由 $ax-b$ 决定。① 当 $a&gt;0$，$b&lt;0$ 时，$ax&gt;0$ 且 $-b&gt;0$，故 $ax-b&gt;0$ 恒成立，$g(x)$ 在 $(0,+\infty)$ 上单调递增。② 当 $a&gt;0$，$b&gt;0$ 时：令 $g'(x)&gt;0$ 得 $x&gt;\dfrac ba$；令 $g'(x)&lt;0$ 得 $0&lt;x&lt;\dfrac ba$。故 $g(x)$ 在 $\left(0,\dfrac ba\right)$ 上单调递减，在 $\left(\dfrac ba,+\infty\right)$ 上单调递增。③ 当 $a&lt;0$，$b&gt;0$ 时，$ax&lt;0$ 且 $-b&lt;0$，故 $ax-b&lt;0$ 恒成立，$g(x)$ 在 $(0,+\infty)$ 上单调递减。④ 当 $a&lt;0$，$b&lt;0$ 时：$\dfrac ba&gt;0$。令 $g'(x)&gt;0$ 得 $0&lt;x&lt;\dfrac ba$；令 $g'(x)&lt;0$ 得 $x&gt;\dfrac ba$。故 $g(x)$ 在 $\left(0,\dfrac ba\right)$ 上单调递增，在 $\left(\dfrac ba,+\infty\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S178" t="n">
+        <v>5</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-098-V2</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V178" s="2" t="inlineStr">
+        <is>
+          <t>双参题要按 $a$、$b$ 的符号分四种情形，逐一判断。注意 $a$、$b$ 同号时 $\frac ba&gt;0$（在定义域内），异号时 $\frac ba&lt;0$（不在定义域内，故恒单调）。数值抽查四种情形各取两组参数，符号全部吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>M-H0179</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>M-T-098(函数与导数 / 导数含参讨论 · 讨论思维基础：求导后一元一次型参数在“斜率”和常数位置(双参))</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>已知 $f(x)=\ln(x+m)-mx$。求 $f(x)$ 的单调区间。</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>当 $m\leq0$ 时，$f(x)$ 的单调递增区间为 $(-m,+\infty)$，无减区间；当 $m&gt;0$ 时，$f(x)$ 的单调递增区间为 $\left(-m,-m+\dfrac1m\right)$，单调递减区间为 $\left(-m+\dfrac1m,+\infty\right)$。</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)=\ln(x+m)-mx$ 的定义域为 $x&gt;-m$，$f'(x)=\dfrac1{x+m}-m$。① 当 $m\leq0$ 时：$\dfrac1{x+m}&gt;0$ 且 $-m\geq0$，故 $f'(x)&gt;0$，$f(x)$ 的单调递增区间为 $(-m,+\infty)$，无减区间。② 当 $m&gt;0$ 时：$f'(x)=\dfrac{1-m(x+m)}{x+m}=\dfrac{-m\left(x+m-\frac1m\right)}{x+m}$，令 $f'(x)=0$ 得 $x=-m+\dfrac1m$，它大于 $-m$，在定义域内。当 $x\in\left(-m,-m+\dfrac1m\right)$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增；当 $x\in\left(-m+\dfrac1m,+\infty\right)$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减。</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S179" t="n">
+        <v>5</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-098-V3</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V179" s="2" t="inlineStr">
+        <is>
+          <t>注意定义域是 $(-m,+\infty)$ 而非 $(0,+\infty)$——参数 $m$ 同时影响定义域，这是本题与前面各题的不同之处。原书第 (2) 问为「设 $m&gt;1$，$x_{1}$、$x_{2}$ 为函数 $f(x)$ 的两个零点，求证 $x_{1}+x_{2}&lt;0$」，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>M-H0180</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>M-T-099(函数与导数 / 导数含参讨论 · 上下平移思维基础：反比例函数型)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=2ax+\ln(2-x)$（$a\in\mathbb{R}$）。求 $f(x)$ 的极值。</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>当 $a\leq0$ 时，$f(x)$ 无极值；当 $a&gt;0$ 时，$f(x)$ 有极大值 $4a-1-\ln(2a)$，无极小值。</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(-\infty,2)$，$f'(x)=2a-\dfrac1{2-x}$（因 $\dfrac{\mathrm d}{\mathrm dx}\ln(2-x)=-\dfrac1{2-x}$）。① 当 $a\leq0$ 时：$2a\leq0$ 且 $-\dfrac1{2-x}&lt;0$，故 $f'(x)&lt;0$，$f(x)$ 在 $(-\infty,2)$ 上单调递减，$f(x)$ 无极值。② 当 $a&gt;0$ 时：令 $f'(x)=0$ 得 $2-x=\dfrac1{2a}$，即 $x=2-\dfrac1{2a}$（小于 $2$，在定义域内）。当 $x&lt;2-\dfrac1{2a}$ 时 $2-x&gt;\dfrac1{2a}$，故 $\dfrac1{2-x}&lt;2a$，$f'(x)&gt;0$，$f(x)$ 单调递增；当 $2-\dfrac1{2a}&lt;x&lt;2$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减。故 $f(x)$ 在 $x=2-\dfrac1{2a}$ 处取得极大值，无极小值，极大值为 $f\!\left(2-\dfrac1{2a}\right)=2a\left(2-\dfrac1{2a}\right)+\ln\dfrac1{2a}=4a-1-\ln(2a)$。</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S180" t="n">
+        <v>5</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-099-E1</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V180" s="2" t="inlineStr">
+        <is>
+          <t>注意 $\ln(2-x)$ 的导数是 $-\frac1{2-x}$（不是 $+\frac1{2-x}$），这是本题最容易出错的一步。数值抽查 $a=0.5,1,2$ 三组，极大值实测与公式 $4a-1-\ln(2a)$ 完全相等。原书第 (2) 问为「若 $x\leq2-\frac1{\mathrm e}$ 时 $f(x)\leq4a-\frac1{2(2-x)}$ 恒成立，求 $a$ 的取值范围」，答案 $\left[\frac{\mathrm e^{2}-2\mathrm e}4,+\infty\right)$，但原书未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>M-H0181</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>M-T-099(函数与导数 / 导数含参讨论 · 上下平移思维基础：反比例函数型)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>设函数 $f(x)=ax-2-\ln x$（$a\in\mathbb{R}$）。若 $f(x)$ 在点 $\left(\mathrm e,f(\mathrm e)\right)$ 处的切线为 $x-\mathrm ey+b=0$，求 $a$，$b$ 的值。</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>$a=\dfrac2{\mathrm e}$，$b=-2\mathrm e$。</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)=ax-2-\ln x$ 的定义域为 $(0,+\infty)$，$f'(x)=a-\dfrac1x$。直线 $x-\mathrm ey+b=0$ 即 $y=\dfrac1{\mathrm e}x+\dfrac b{\mathrm e}$，斜率为 $\dfrac1{\mathrm e}$。因为它是 $f(x)$ 在 $x=\mathrm e$ 处的切线，所以 $f'(\mathrm e)=a-\dfrac1{\mathrm e}=\dfrac1{\mathrm e}$，解得 $a=\dfrac2{\mathrm e}$。于是 $f(\mathrm e)=a\mathrm e-2-\ln\mathrm e=\dfrac2{\mathrm e}\cdot\mathrm e-2-1=-1$，切点为 $(\mathrm e,-1)$。把该点代入切线方程：$\mathrm e-\mathrm e\cdot(-1)+b=0$，解得 $b=-2\mathrm e$。故 $a=\dfrac2{\mathrm e}$，$b=-2\mathrm e$。</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S181" t="n">
+        <v>5</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-099-V1</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V181" s="2" t="inlineStr">
+        <is>
+          <t>这是本批唯一一道“已知切线求参数”的题，第 (1) 问本身完整且有详解，可直接录入。验证：$a=\frac2{\mathrm e}\approx0.7358$ 时 $f(\mathrm e)=-1.000000$，代入切线得 $b=-2\mathrm e\approx-5.4366$。原书第 (2) 问为「求 $f(x)$ 的单调区间」，答案“见解析”但未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>M-H0182</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>M-T-099(函数与导数 / 导数含参讨论 · 上下平移思维基础：反比例函数型)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>已知 $f(x)=\ln(x+2)-bx+a$，$g(x)=\mathrm e^{x}-1$。讨论 $f(x)$ 的单调性。</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>当 $b\leq0$ 时，$f(x)$ 在 $(-2,+\infty)$ 上单调递增；当 $b&gt;0$ 时，$f(x)$ 在 $\left(-2,\dfrac1b-2\right)$ 上单调递增，在 $\left(\dfrac1b-2,+\infty\right)$ 上单调递减。</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $(-2,+\infty)$，且 $f'(x)=\dfrac1{x+2}-b$。（参数 $a$ 是常数项，不影响单调性。）① 当 $b\leq0$ 时：$\dfrac1{x+2}&gt;0$ 且 $-b\geq0$，故 $f'(x)&gt;0$，$f(x)$ 在定义域 $(-2,+\infty)$ 上单调递增。② 当 $b&gt;0$ 时：令 $f'(x)=0$ 得 $x=\dfrac1b-2$，它大于 $-2$，在定义域内。当 $-2&lt;x&lt;\dfrac1b-2$ 时 $x+2&lt;\dfrac1b$，故 $\dfrac1{x+2}&gt;b$，$f'(x)&gt;0$，$f(x)$ 单调递增；当 $x&gt;\dfrac1b-2$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减。综上即得答案所述两种情形。</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S182" t="n">
+        <v>5</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-099-V2</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V182" s="2" t="inlineStr">
+        <is>
+          <t>注意定义域是 $(-2,+\infty)$，且 $a$ 为常数项、对单调性无影响——题干给了 $a$ 和 $g(x)$ 都是为第 (2) 问服务的。原书第 (2) 问为「当 $b=0$ 时，对任意 $x\in(-2,+\infty)$ 都有 $g(x)\geq\frac{f(x)}{x+2}$ 成立，求实数 $a$ 的最大值」，答案 $-1$，但原书未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>M-H0183</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>M-T-100(函数与导数 / 导数含参讨论 · 上下平移：指数型)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x+a\mathrm e^{-x}$。讨论函数 $f(x)$ 的极值。</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>当 $a\leq0$ 时，函数 $f(x)$ 无极值；当 $a&gt;0$ 时，函数 $f(x)$ 的极小值为 $\ln a+1$，无极大值。</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>函数 $f(x)=x+a\mathrm e^{-x}$ 的定义域为 $\mathbb{R}$，$f'(x)=1-a\mathrm e^{-x}=\dfrac{\mathrm e^{x}-a}{\mathrm e^{x}}$。① 当 $a\leq0$ 时：$-a\mathrm e^{-x}\geq0$，故 $f'(x)\geq1&gt;0$，$f(x)$ 在 $\mathbb{R}$ 上单调递增，无极值。② 当 $a&gt;0$ 时：令 $f'(x)=0$ 得 $\mathrm e^{x}=a$，即 $x=\ln a$。当 $x&lt;\ln a$ 时 $\mathrm e^{x}&lt;a$，故 $f'(x)&lt;0$，$f(x)$ 单调递减；当 $x&gt;\ln a$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增。所以 $f(x)$ 在 $x=\ln a$ 处取得极小值，极小值为 $f(\ln a)=\ln a+a\mathrm e^{-\ln a}=\ln a+a\cdot\dfrac1a=\ln a+1$，无极大值。</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S183" t="n">
+        <v>5</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-100-E1</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V183" s="2" t="inlineStr">
+        <is>
+          <t>函数式的判定（重要）：ref_bank 提取为「$f(x)=\frac{x+a}{\mathrm e^{x}}$」，但原书给的导数是 $1-a\mathrm e^{-x}$、极小值是 $\ln a+1$，两者都指向 $f(x)=x+a\mathrm e^{-x}$。若按 $\frac{x+a}{\mathrm e^{x}}$，则 $f'(x)=\frac{1-x-a}{\mathrm e^{x}}$，$a\leq0$ 时符号不定，与原书“当 $a\leq0$ 时 $f'(x)&gt;0$”矛盾。数值抽查 $a=0.5,2,5$ 三组，极小值实测与 $\ln a+1$ 完全相等，确认无误。原书第 (2) 问为「若函数 $f(x)$ 在 $[0,1]$ 上的最小值是 $\frac43$，求实数 $a$ 的值」，答案 $\mathrm e^{\frac13}$，但原书未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>M-H0184</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>M-T-100(函数与导数 / 导数含参讨论 · 上下平移：指数型)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>设函数 $f(x)=x-a\mathrm e^{x}$（$a\in\mathbb{R}$）。求函数 $f(x)$ 的极值。</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>当 $a\leq0$ 时，$f(x)$ 无极值；当 $a&gt;0$ 时，$f(x)$ 有极大值 $\ln\dfrac1a-1$（即 $-\ln a-1$），无极小值。</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $\mathbb{R}$，$f'(x)=1-a\mathrm e^{x}$。① 当 $a\leq0$ 时：$-a\mathrm e^{x}\geq0$，故 $f'(x)\geq1&gt;0$，$f(x)$ 在 $\mathbb{R}$ 上单调递增，没有极值。② 当 $a&gt;0$ 时：令 $f'(x)=0$ 得 $\mathrm e^{x}=\dfrac1a$，即 $x=\ln\dfrac1a=-\ln a$。当 $x&lt;\ln\frac1a$ 时 $a\mathrm e^{x}&lt;1$，故 $f'(x)&gt;0$，$f(x)$ 单调递增；当 $x&gt;\ln\frac1a$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减。所以 $f(x)$ 在 $x=\ln\frac1a$ 处取得极大值，极大值为 $f\!\left(\ln\dfrac1a\right)=\ln\dfrac1a-a\cdot\dfrac1a=\ln\dfrac1a-1$，没有极小值。</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S184" t="n">
+        <v>5</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-100-V1</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V184" s="2" t="inlineStr">
+        <is>
+          <t>与 T100-E1 对照：一个是 $x+a\mathrm e^{-x}$（极小值），一个是 $x-a\mathrm e^{x}$（极大值），指数项的符号与正负决定了极值是极大还是极小。数值抽查 $a=0.5,2$ 两组，极大值实测与 $\ln\frac1a-1$ 完全相等。原书第 (2) 问为「若 $f(x)\leq ax$ 在 $x\in[0,+\infty)$ 时恒成立，求 $a$ 的取值范围」，答案 $\left[\frac1{1+\mathrm e},+\infty\right)$，但原书未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>M-H0185</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>双空题</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>M-T-100(函数与导数 / 导数含参讨论 · 上下平移：指数型)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>设函数 $f(x)=a\mathrm e^{x}+2x+ab+4$（$a,b\in\mathbb{R}$）。求函数 $f(x)$ 的单调区间。</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>当 $a\geq0$ 时，$f(x)$ 的单调递增区间为 $\mathbb{R}$，无单调递减区间；当 $a&lt;0$ 时，$f(x)$ 的单调递增区间为 $\left(-\infty,\ln\left(-\dfrac2a\right)\right)$，单调递减区间为 $\left(\ln\left(-\dfrac2a\right),+\infty\right)$。</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的定义域为 $\mathbb{R}$，$f'(x)=a\mathrm e^{x}+2$。（$ab+4$ 是常数项，不影响单调性。）① 当 $a\geq0$ 时：$a\mathrm e^{x}\geq0$，故 $f'(x)\geq2&gt;0$，$f(x)$ 的单调递增区间为 $\mathbb{R}$，无单调递减区间。② 当 $a&lt;0$ 时：令 $f'(x)=0$ 得 $\mathrm e^{x}=-\dfrac2a$（因 $a&lt;0$，右端为正），即 $x=\ln\left(-\dfrac2a\right)$。令 $f'(x)&gt;0$ 得 $\mathrm e^{x}&lt;-\dfrac2a$，即 $x&lt;\ln\left(-\dfrac2a\right)$；令 $f'(x)&lt;0$ 得 $x&gt;\ln\left(-\dfrac2a\right)$。故 $f(x)$ 的单调递增区间为 $\left(-\infty,\ln\left(-\dfrac2a\right)\right)$，单调递减区间为 $\left(\ln\left(-\dfrac2a\right),+\infty\right)$。</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S185" t="n">
+        <v>5</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-100-V2</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>教辅录入-第12批</t>
+        </is>
+      </c>
+      <c r="V185" s="2" t="inlineStr">
+        <is>
+          <t>注意 $a&lt;0$ 时 $-\frac2a&gt;0$，对数才有意义；这也是 $a\geq0$ 与 $a&lt;0$ 的分界原因。数值抽查 $a=-1,-2,-0.5$ 三组，符号全部吻合。原书第 (2) 问为「若函数 $y=f(x)-ab$ 有两个不同的零点 $x_{1}$、$x_{2}$（$x_{1}&lt;x_{2}$），求证 $f'\left(x_{1}\right)f'\left(x_{2}\right)&gt;-1$」，未给出详解，本录不含。</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>M-H0186</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>M-T-070(函数与导数 / 复合函数与嵌套函数零点 · 一元二次复合型：函数性质综合型)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>已知偶函数 $f(x)$ 满足 $f(3+x)=f(3-x)$，且当 $x\in[0,3]$ 时，$f(x)=-x^{2}+2x+1$，若关于 $x$ 的方程 $f^{2}(x)-tf(x)-3=0$ 在 $[-150,150]$ 上有 $300$ 个解，则实数 $t$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>$\left(-2,\frac{1}{2}\right)$</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>$\left(-\frac{1}{2},\frac{1}{2}\right)$</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>$(-2,+\infty)$</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,\frac{1}{2}\right)$</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(3+x)=f(3-x)$ 知 $f$ 关于直线 $x=3$ 对称，又 $f$ 为偶函数（关于 $x=0$ 对称），两条对称轴相距 $3$，故 $f$ 的周期 $T=2\times 3=6$。
+$x\in[0,3]$ 时 $f(x)=-x^{2}+2x+1=-(x-1)^{2}+2$：$f(0)=1$，$f(1)=2$，$f(3)=-2$。由偶性得 $x\in[-3,0]$ 时 $f(x)=-x^{2}-2x+1$，$f(-1)=2$，$f(-3)=-2$。
+于是一个周期 $[-3,3]$ 上：$[-3,-1]$ 由 $-2$ 增到 $2$，$[-1,0]$ 由 $2$ 降到 $1$，$[0,1]$ 由 $1$ 增到 $2$，$[1,3]$ 由 $2$ 降到 $-2$。数 $f(x)=u$ 的解数：$u\in(1,2)$ 为 $4$ 个，$u=1$ 为 $3$ 个，$u\in(-2,1)$ 为 $2$ 个，$u=2$ 为 $2$ 个，$u=-2$ 为 $1$ 个。
+区间 $[-150,150]$ 长 $300$，含 $50$ 个周期，$300$ 个解即每周期 $6$ 个解。令 $u=f(x)$，方程化为 $u^{2}-tu-3=0$，两根 $u_{1}u_{2}=-3&lt;0$ 一正一负，要有 $4+2=6$ 个解，须 $u_{1}\in(1,2)$ 且 $u_{2}\in(-2,1)$。
+令 $g(u)=u^{2}-tu-3$，由根的分布得 $g(-2)&gt;0$、$g(1)&lt;0$、$g(2)&gt;0$，即$2t+1&gt;0$、$-t-2&lt;0$、$1-2t&gt;0$，解得 $-\frac{1}{2}&lt;t&lt;\frac{1}{2}$。故选 B。</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>较难</t>
+        </is>
+      </c>
+      <c r="S186" t="n">
+        <v>5</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-070-E1</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V186" s="2" t="inlineStr">
+        <is>
+          <t>独立验算：$t=0$ 时 $u=\pm\sqrt{3}$，$u_{1}\approx1.732\in(1,2)$ 给 $4$ 解、$u_{2}\approx-1.732\in(-2,1)$ 给 $2$ 解，共 $6$ 解，符合。端点 $t=\frac{1}{2}$ 时 $u_{1}=2$ 只给 $2$ 解、$t=-\frac{1}{2}$ 时 $u_{2}=-2$ 只给 $1$ 解，均不足 $6$ 解，故两端都是开区间，与答案 B 一致。四个选项的区间括号在 PDF 中为 PMExtra 私用区字符 U+F0EE（圆括号），常规提取会丢失，已按码位还原为圆括号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>M-H0187</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>M-T-070(函数与导数 / 复合函数与嵌套函数零点 · 一元二次复合型：函数性质综合型)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 是定义在 $[-100,100]$ 的偶函数，且 $f(x+2)=f(x-2)$。当 $x\in[0,2]$ 时，$f(x)=(x-2)e^{x}$，若方程 $[f(x)]^{2}-mf(x)+1=0$ 有 $300$ 个不同的实数根，则实数 $m$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>$\left(-e-\frac{1}{e},-\frac{5}{2}\right)$</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>$\left[-e-\frac{1}{e},-\frac{5}{2}\right]$</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>$(-\infty,-2)$</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>$\left(-e-\frac{1}{e},-2\right)$</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(x+2)=f(x-2)$ 知 $f$ 的周期为 $4$。$x\in[0,2]$ 时 $f(x)=(x-2)e^{x}$，则 $f'(x)=(x-1)e^{x}$：$0\leq x&lt;1$ 时 $f'&lt;0$ 递减，$1&lt;x\leq 2$ 时 $f'&gt;0$ 递增，$f$ 在 $x=1$ 处取极小值 $f(1)=-e$；又 $f(0)=-2$、$f(2)=0$。
+由偶性作出 $[-2,2]$ 上的图象：一个周期内，$f$ 在 $[-2,-1]$ 由 $0$ 降到 $-e$、$[-1,0]$ 由 $-e$ 升到 $-2$、$[0,1]$ 由 $-2$ 降到 $-e$、$[1,2]$ 由 $-e$ 升到 $0$。
+数 $f(x)=t$ 在一个周期内的解数：$t\in(-e,-2)$ 为 $4$ 个，$t\in(-2,0)$ 为 $2$ 个，$t=-2$ 为 $3$ 个，$t=-e$ 为 $2$ 个，$t=0$ 为 $2$ 个。
+定义域 $[-100,100]$ 长 $200$，含 $50$ 个周期，$300$ 个根即每周期 $6$ 个根，需 $4+2$，故两根 $t_{1}\in(-e,-2)$、$t_{2}\in(-2,0)$。
+设 $g(t)=t^{2}-mt+1$，由根的分布得 $g(-e)&gt;0$、$g(-2)&lt;0$、$g(0)&gt;0$：$g(-e)=e^{2}+me+1&gt;0\Rightarrow m&gt;-\left(e+\frac{1}{e}\right)$；$g(-2)=2m+5&lt;0\Rightarrow m&lt;-\frac{5}{2}$；$g(0)=1&gt;0$ 恒成立。故 $-e-\frac{1}{e}&lt;m&lt;-\frac{5}{2}$。选 A。</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>较难</t>
+        </is>
+      </c>
+      <c r="S187" t="n">
+        <v>5</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-070-V1</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V187" s="2" t="inlineStr">
+        <is>
+          <t>★ 曾判为「选项 A/B 内容重复」而跳过，拿到 PDF 后核实：A 的括号是 U+F0EE（圆括号）、B 是 U+F0F6（方括号），两者是**开闭区间之别**，并非重复，现已按码位还原。独立验算：取 $m=-2.8$（区间内），$t^{2}+2.8t+1=0$ 得 $t_{1}\approx-2.3798\in(-e,-2)$ 给 $4$ 解、$t_{2}\approx-0.4202\in(-2,0)$ 给 $2$ 解，共 $6$ 解，每周期 $6$ 个、$50$ 个周期共 $300$ 个，符合。端点 $m=-\frac{5}{2}$ 时 $t_{1}=-2$ 只给 $3$ 解，总共 $5$ 解，故排除右端点，与答案 A（开区间）一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>M-H0188</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>M-T-070(函数与导数 / 复合函数与嵌套函数零点 · 一元二次复合型：函数性质综合型)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>设 $\max\{p,q\}$ 表示 $p$，$q$ 两者中较大的一个，已知定义在 $[0,2\pi]$ 的函数 $f(x)=\max\{2\sin x,2\cos x\}$，满足关于 $x$ 的方程 $f^{2}(x)+(1-2m)f(x)+m^{2}-m=0$ 有 $6$ 个不同的解，则 $m$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>$(-1,2)$</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>$(1,1+\sqrt{2})$</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>$(\sqrt{2},2)$</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>$(1+\sqrt{2},2\sqrt{2})$</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>关于 $f(x)$ 的方程 $f^{2}+(1-2m)f+(m^{2}-m)=0$ 的判别式 $\Delta=(1-2m)^{2}-4(m^{2}-m)=1$，故 $f(x)=\frac{2m-1\pm 1}{2}$，即 $f(x)=m$ 或 $f(x)=m-1$。
+$2\sin x=2\cos x$ 得 $x=\frac{\pi}{4}$、$\frac{5\pi}{4}$，故 $f(x)=\begin{cases}2\cos x,&amp;x\in[0,\frac{\pi}{4})\cup[\frac{5\pi}{4},2\pi]\\ 2\sin x,&amp;x\in[\frac{\pi}{4},\frac{5\pi}{4})\end{cases}$。
+图象为：$[0,\frac{\pi}{4}]$ 由 $2$ 降到 $\sqrt{2}$；$[\frac{\pi}{4},\frac{\pi}{2}]$ 由 $\sqrt{2}$ 升到 $2$；$[\frac{\pi}{2},\frac{5\pi}{4}]$ 由 $2$ 降到 $-\sqrt{2}$；$[\frac{5\pi}{4},2\pi]$ 由 $-\sqrt{2}$ 升到 $2$。数 $f(x)=u$ 的解数：$u\in(\sqrt{2},2)$ 为 $4$ 个，$u\in(-\sqrt{2},\sqrt{2})$ 为 $2$ 个，$u=2$ 为 $3$ 个，$u=\sqrt{2}$ 为 $3$ 个，$u=-\sqrt{2}$ 为 $1$ 个。
+要共 $6$ 个解，需 $4+2$，即一个值在 $(\sqrt{2},2)$、另一个在 $(-\sqrt{2},\sqrt{2})$：$\sqrt{2}&lt;m&lt;2$ 且 $-\sqrt{2}&lt;m-1&lt;\sqrt{2}$，后者即 $1-\sqrt{2}&lt;m&lt;1+\sqrt{2}$。
+取交集得 $\sqrt{2}&lt;m&lt;2$。故选 C。</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>较难</t>
+        </is>
+      </c>
+      <c r="S188" t="n">
+        <v>5</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-070-V2</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V188" s="2" t="inlineStr">
+        <is>
+          <t>独立验算：$m=1.5$ 时 $f=1.5\in(\sqrt{2},2)$ 给 $4$ 解、$f=0.5\in(-\sqrt{2},\sqrt{2})$ 给 $2$ 解，共 $6$ 解，符合；$m=1.41&lt;\sqrt{2}$ 时两根都落在 $(-\sqrt{2},\sqrt{2})$，只有 $2+2=4$ 解；$m=2$ 时 $f=2$ 给 $3$ 解、$f=1$ 给 $2$ 解，共 $5$ 解。两端均排除，答案 C 正确。选项的 $\sqrt{2}$、$2\sqrt{2}$ 由根号残留还原。</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>M-H0189</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>M-T-070(函数与导数 / 复合函数与嵌套函数零点 · 一元二次复合型：函数性质综合型)</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>定义在 $\mathbb{R}$ 上的函数 $f(x)$ 满足 $f(-x)=f(x)$，且当 $x\geq 0$ 时，$f(x)=\begin{cases}\frac{5}{4}\sin\frac{\pi}{4}x,&amp;0\leq x\leq 2\\ \left(\frac{1}{2}\right)^{x}+1,&amp;x&gt;2\end{cases}$，若关于 $x$ 的方程 $f^{2}(x)+bf(x)+c=0$（$b,c\in\mathbb{R}$）有且只有 $6$ 个不同的实数根，则实数 $b$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>$\left(-\frac{5}{2},-\frac{9}{4}\right)\cup\left(-\frac{9}{4},-1\right)$</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>$\left(-\frac{5}{2},-1\right)$</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>$\left(-\frac{5}{2},-\frac{9}{4}\right)\cup(-1,0)$</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>$\left(-\frac{9}{4},-1\right)$</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t>先看 $f$ 在 $[0,+\infty)$ 上：$[0,2]$ 上 $f=\frac{5}{4}\sin\frac{\pi}{4}x$ 由 $0$ 增到 $\frac{5}{4}$；$(2,+\infty)$ 上 $f=\left(\frac{1}{2}\right)^{x}+1$ 由 $\frac{5}{4}$ 递减趋近 $1$。
+数 $f(x)=u$ 在 $\mathbb{R}$ 上的解数（偶函数，除 $x=0$ 外解成对出现）：$u=0$ 为 $1$ 个；$u\in(0,1]$ 为 $2$ 个；$u\in(1,\frac{5}{4})$ 为 $4$ 个；$u=\frac{5}{4}$ 为 $2$ 个（即 $x=\pm 2$）；其余为 $0$ 个。
+令 $u=f(x)$，方程化为 $u^{2}+bu+c=0$，两根 $u_{1},u_{2}$，由韦达定理 $-b=u_{1}+u_{2}$。要共 $6$ 个根，只能是 $4+2$，分两种情形：
+情形一：$u_{1}\in(1,\frac{5}{4})$（给 $4$ 个），$u_{2}\in(0,1]$（给 $2$ 个）。此时 $-b=u_{1}+u_{2}\in(1,\frac{9}{4})$（两端均取不到：$\frac{9}{4}$ 需 $u_{1}=\frac{5}{4}$ 或 $u_{2}=\frac{5}{4}$，均不在本情形范围内）。
+情形二：$u_{1}\in(1,\frac{5}{4})$（给 $4$ 个），$u_{2}=\frac{5}{4}$（给 $2$ 个）。此时 $-b=u_{1}+\frac{5}{4}\in(\frac{9}{4},\frac{5}{2})$。
+合并得 $-b\in(1,\frac{9}{4})\cup(\frac{9}{4},\frac{5}{2})$，即 $b\in(-\frac{5}{2},-\frac{9}{4})\cup(-\frac{9}{4},-1)$。故选 A。</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>较难</t>
+        </is>
+      </c>
+      <c r="S189" t="n">
+        <v>5</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-070-V3</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V189" s="2" t="inlineStr">
+        <is>
+          <t>★ 曾误判此答案偏大（以为上界应为 $\frac{9}{4}$ 而非 $\frac{5}{2}$），独立验算后发现是**我漏了情形二**：$u_{2}=\frac{5}{4}$ 时 $f(x)=\frac{5}{4}$ 有 $2$ 个解（$x=\pm 2$），这一支使 $-b$ 可达 $(\frac{9}{4},\frac{5}{2})$，正好撑起答案中 $(-\frac{5}{2},-\frac{9}{4})$ 那一段。补上该分支后与标答 A 完全吻合，原书无误。另注意 $-b=\frac{9}{4}$ 不可取（需 $u_{1}=\frac{5}{4}$ 与 $u_{2}=\frac{5}{4}$ 同时成立，两根相等时判别式为零只给 $2$ 解），故 $\frac{9}{4}$ 处是空档。四个选项的区间括号均为 PDF 私用区 U+F0EE（圆括号），已还原。</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>M-H0190</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>M-T-071(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数基础型)</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>定义域和值域均为 $[-a,a]$（常数 $a&gt;0$）的函数 $y=f(x)$ 和 $y=g(x)$ 的图象如图所示，方程 $g[f(x)]=0$ 解得个数不可能是（　　）</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>因为 $x\in[-a,a]$ 时 $g(x)=0$ 有唯一解，设该解为 $k$。由 $g(x)$ 的图象可知 $k\in(0,a)$。
+由 $g[f(x)]=0$ 得 $f(x)=k$。
+因为 $k\in(0,a)$，观察 $f(x)$ 的图象：水平线 $y=k$ 与 $f$ 的图象相交，随 $k$ 在 $(0,a)$ 内取值，交点个数可能为 $1$ 个、$2$ 个或 $3$ 个，但不可能达到 $4$ 个。
+故选 D。</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S190" t="n">
+        <v>5</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-071-E1</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V190" s="2" t="inlineStr">
+        <is>
+          <t>★ 纯图解题，图由 PDF 原位置切取（页45 右栏两张并排图）。切图边界已程序校验：上下左右外扩 6~14 单位均无相邻题目文本混入，图内无文字（纯曲线与坐标轴），故不存在“切错图”或“混入邻题”的风险。两图并排，按排版顺序左为 $f(x)$、右为 $g(x)$。注意：本题结论完全依赖图象（$f(x)=k$ 至多 $3$ 根），若后续发现图序或图内容与题面不符，以原书为准复核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>M-H0191</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>多选题-3个答案</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>M-T-071(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数基础型)</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>若 $f(x)$ 和 $g(x)$ 都是定义在 $\mathbb{R}$ 上的函数，且方程 $f[g(x)]=x$ 有实数解，则下列式子中可以为 $g[f(x)]$ 的是（　　）</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>$x^{2}+2x$</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>$x+1$</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>$e^{\cos x}$</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>$\ln(|x|+1)$</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>ACD</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>设 $x_{0}$ 满足 $f[g(x_{0})]=x_{0}$，令 $t=g(x_{0})$，则 $f(t)=x_{0}$，于是 $g[f(t)]=g(x_{0})=t$，即 $t$ 是方程 $g[f(x)]=x$ 的解。故条件等价于：$g[f(x)]=x$ 有实数解。
+A：$x^{2}+2x=x$ 即 $x^{2}+x=0$，有解 $x=0$、$-1$，正确；
+B：$x+1=x$ 即 $1=0$，无解，错误；
+C：令 $h(x)=e^{\cos x}-x$，则 $h(0)=e&gt;0$、$h(\frac{\pi}{2})=1-\frac{\pi}{2}&lt;0$，$h$ 连续，由零点存在性定理知在 $(0,\frac{\pi}{2})$ 内有零点，正确；
+D：$\ln(|x|+1)=x$，$x=0$ 时 $\ln 1=0$，有解，正确。
+故选 ACD。</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S191" t="n">
+        <v>5</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-071-V1</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V191" s="2" t="inlineStr">
+        <is>
+          <t>多选题（三个答案）。关键转化已独立验证：由 $f[g(x_{0})]=x_{0}$ 令 $t=g(x_{0})$ 得 $f(t)=x_{0}$，两边作用 $g$ 得 $g[f(t)]=g(x_{0})=t$，推导无误。C 选项另用数值验证：$e^{\cos x}-x$ 在 $x=0$ 处约 $2.718$、$x=1.5$ 处约 $1.073-1.5&lt;0$，确实变号。题干 $f[g(x)]$、$g[f(x)]$ 的外层方括号按原书保留（PDF 中 f[g(x)] 外层为 U+F0F6 方括号）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>M-H0192</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>M-T-071(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数基础型)</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>已知两函数 $f(x)$ 和 $g(x)$ 都是定义在 $\mathbb{R}$ 上的函数，且方程 $x-f[g(x)]=0$ 有实数解，则 $g[f(x)]$ 有可能是（　　）</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>$x^{2}+1$</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>$x^{2}+x+1$</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>$x^{2}-x-1$</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>$2x^{2}-x+1$</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>设 $x_{0}$ 满足 $x_{0}=f[g(x_{0})]$，则 $g(x_{0})=g(f[g(x_{0})])$。令 $t=g(x_{0})$，得 $t=g[f(t)]$，即方程 $x=g[f(x)]$ 有实数解。
+A：$x=x^{2}+1$ 即 $x^{2}-x+1=0$，$\Delta=1-4=-3&lt;0$，无实数解；
+B：$x=x^{2}+x+1$ 即 $x^{2}+1=0$，无实数解；
+C：$x=x^{2}-x-1$ 即 $x^{2}-2x-1=0$，$\Delta=4+4=8&gt;0$，有实数解；
+D：$x=2x^{2}-x+1$ 即 $2x^{2}-2x+1=0$，$\Delta=4-8=-4&lt;0$，无实数解。
+故选 C。</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S192" t="n">
+        <v>5</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-071-V2</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V192" s="2" t="inlineStr">
+        <is>
+          <t>独立验算：C 的解为 $x=1\pm\sqrt{2}$，代入 $x^{2}-x-1$ 得 $(1+\sqrt{2})^{2}-(1+\sqrt{2})-1=1+\sqrt{2}$，与 $x$ 相等，成立。A、B、D 判别式均为负，确认无解。注意本题与 M-T-071-V1 转化相同但选项不同、问法由“可以为”（多选）变为“有可能是”（单选），不是重复题，两道都录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>M-H0193</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>M-T-071(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数基础型)</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>若 $f(x)$ 和 $g(x)$ 是定义在实数集 $\mathbb{R}$ 上的函数，且方程 $x-f[g(x)]=0$ 有实数解，则 $g[f(x)]$ 不可能是（　　）</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>$e^{x}-1$</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>$\cos x$</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>$|x|+1$</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>$\begin{cases}x^{2},&amp;x\leq 0\\ -\ln x,&amp;x&gt;0\end{cases}$</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr">
+        <is>
+          <t>设 $s$ 满足 $s-f[g(s)]=0$，即 $f[g(s)]=s$。令 $t=g(s)$，则 $f(t)=s$，于是 $g[f(t)]=g(s)=t$，即 $t$ 为方程 $g[f(x)]=x$ 的实数解。故只需判断各选项作为 $g[f(x)]$ 时，方程 $g[f(x)]=x$ 是否有解，即图象与直线 $y=x$ 是否有交点。
+A：$e^{x}-1=x$，$x=0$ 时 $1-1=0$，有解；
+B：$\cos x=x$，在 $(0,\frac{\pi}{2})$ 内有交点（约 $0.739$），有解；
+C：$|x|+1=x$。$x\geq 0$ 时化为 $x+1=x$ 即 $1=0$，无解；$x&lt;0$ 时化为 $-x+1=x$ 得 $x=\frac{1}{2}$，与 $x&lt;0$ 矛盾，亦无解。故无解；
+D：$x\leq 0$ 时 $x^{2}=x$ 得 $x=0$（满足 $x\leq 0$），有解。
+故选 C。</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S193" t="n">
+        <v>5</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-071-V3</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V193" s="2" t="inlineStr">
+        <is>
+          <t>独立验算：C 选项 $|x|+1&gt;x$ 对任意实数恒成立，故 $|x|+1=x$ 确无解，图象恒在 $y=x$ 上方，与 $y=x$ 无交点，结论可靠。其余三项均给出具体解验证过。选项 D 的分段函数用 \begin{cases} 重建；题干外层的方括号按原书保留。</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>M-H0194</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>M-T-072(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数常规型：无参双坐标系换元转换法)</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}2x-1,&amp;x\leq 1\\ |\ln(x-1)|,&amp;x&gt;1\end{cases}$，则方程 $f(f(x))=1$ 的根的个数为（　　）</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>$7$</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>$5$</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>令 $u=f(x)$，先解 $f(u)=1$。
+(1) 当 $u\leq 1$ 时，$f(u)=2u-1=1$，得 $u_{1}=1$；
+(2) 当 $u&gt;1$ 时，$f(u)=|\ln(u-1)|=1$，即 $\ln(u-1)=\pm 1$，得 $u-1=e$ 或 $u-1=\frac{1}{e}$，即 $u_{2}=1+\frac{1}{e}$、$u_{3}=1+e$。
+再数 $f(x)=u$ 的解数。$f$ 的图象：$x\leq 1$ 时 $f=2x-1$ 由 $-\infty$ 增到 $1$，值域 $(-\infty,1]$；$x&gt;1$ 时 $f=|\ln(x-1)|$，在 $x\to 1^{+}$ 时趋于 $+\infty$，$x=2$ 处取最小值 $0$，之后递增趋于 $+\infty$，值域 $[0,+\infty)$。
+$u_{1}=1$：$x\leq 1$ 段给 $x=1$；$x&gt;1$ 段 $|\ln(x-1)|=1$ 给 $x=1+e$、$1+\frac{1}{e}$。共 $3$ 个。
+$u_{2}=1+\frac{1}{e}\approx1.368&gt;1$：$x\leq 1$ 段值域上界为 $1$，无解；$x&gt;1$ 段 $|\ln(x-1)|=1.368$ 给 $2$ 个解。共 $2$ 个。
+$u_{3}=1+e\approx3.718$：同理 $x&gt;1$ 段给 $2$ 个解。共 $2$ 个。
+总根数 $3+2+2=7$。故选 A。</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S194" t="n">
+        <v>5</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-072-E1</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V194" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干的绝对值在常规文本提取中会丢失（PDF 中是 PMExtra 私用区 U+F0F4 竖线字符），按提取结果录入会变成 $f=\ln(x-1)$，此时 $f(u)=1$ 只得 $u=1$、$1+e$ 两个值，总数 $3+2=5$，与标答 $7$ 矛盾。已用原书 PDF 字符级核对确认绝对值存在（$x=413.2$ 与 $x=450.2$ 各一个 U+F0F4，正好夹住 $\ln(x-1)$），并按详解“$\ln(u-1)=\pm 1$”反推印证，两者一致。另验算：$u_{2}\approx1.368$、$u_{3}\approx3.718$ 均大于 $1$，故 $x\leq 1$ 段（值域 $(-\infty,1]$）确无解，各只由 $x&gt;1$ 段贡献 $2$ 个解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>M-H0195</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>M-T-072(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数常规型：无参双坐标系换元转换法)</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>已知定义在 $(0,+\infty)$ 上的单调函数 $f(x)$ 满足对 $\forall x\in(0,+\infty)$，$f\left[f(x)-\log_{2}x\right]=3$，则方程 $f(x)-f'(x)=2$ 的解所在区间是（　　）</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>$\left(0,\frac{1}{2}\right)$</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>$\left(\frac{1}{2},1\right)$</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>$(1,2)$</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>$(2,3)$</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>因 $f$ 单调，故为单射。由 $f\left[f(x)-\log_{2}x\right]=3$ 恒成立知 $f(x)-\log_{2}x$ 必为常数，设 $f(x)-\log_{2}x=t$，即 $f(x)=t+\log_{2}x$。
+取 $x=t$ 得 $f(t)=t+\log_{2}t=3$。令 $\varphi(t)=t+\log_{2}t$，$\varphi'(t)=1+\frac{1}{t\ln 2}&gt;0$，故 $\varphi$ 在 $(0,+\infty)$ 上单调递增，而 $\varphi(2)=2+1=3$，故方程有唯一解 $t=2$。于是 $f(x)=2+\log_{2}x$。
+$f'(x)=\frac{1}{x\ln 2}$，方程 $f(x)-f'(x)=2$ 化为 $2+\log_{2}x-\frac{1}{x\ln 2}=2$，即 $\log_{2}x=\frac{1}{x\ln 2}$。
+令 $h(x)=\log_{2}x-\frac{1}{x\ln 2}$，它在 $(0,+\infty)$ 上单调递增。$h(1)=0-\frac{1}{\ln 2}&lt;0$，$h(2)=1-\frac{1}{2\ln 2}&gt;0$（因 $2\ln 2\approx1.386&gt;1$）。故根在 $(1,2)$ 内。选 C。</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S195" t="n">
+        <v>5</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-072-V1</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V195" s="2" t="inlineStr">
+        <is>
+          <t>★ 导数撇号在 PDF 中是 PMExtra 私用区 U+F00A（全书出现 2291 次），常规提取会丢失，题干被抓成“$f(x)-f(x)=2$”（恒假、无解）。已按原书字符级核对确认撇号存在，并据详解中“可化为 $2+\log_{2}x-\frac{1}{x\ln 2}=2$”（其中 $\frac{1}{x\ln 2}$ 正是 $(\log_{2}x)'$）印证，判定第二项为 $f'(x)$。独立验算：$h(1)\approx-1.4427&lt;0$、$h(2)\approx0.2787&gt;0$；再取 $x=1.7$ 处 $h\approx-0.0835&lt;0$、$x=1.8$ 处 $h\approx0.0459&gt;0$，根约 $1.76$，确在 $(1,2)$ 内。书写提醒：含撇号的 LaTeX 一律用 raw 双引号包裹，单引号会被撇号提前截断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>M-H0196</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>M-T-072(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数常规型：无参双坐标系换元转换法)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}x^{3}-3x^{2}+3,&amp;x&lt;2\\ -4(x^{2}-5x+6),&amp;x\geq 2\end{cases}$，则函数 $f(f(x))$ 的零点的个数为（　　）</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>$6$</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>$7$</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>$8$</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>$9$</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>先求 $f$ 的零点。
+$x&lt;2$ 时 $f(x)=x^{3}-3x^{2}+3$，$f'(x)=3x^{2}-6x=3x(x-2)$：$x&lt;0$ 时 $f'&gt;0$ 递增，$0&lt;x&lt;2$ 时 $f'&lt;0$ 递减，故 $x=0$ 处取极大值 $f(0)=3$。又 $f(-1)=-1&lt;0$、$f(0)=3&gt;0$，得零点 $x_{1}\in(-1,0)$；$f(1)=1&gt;0$、$f(2^{-})=-1&lt;0$，得零点 $x_{2}\in(1,2)$。
+$x\geq 2$ 时 $f(x)=-4(x-2)(x-3)$，为开口向下的抛物线，顶点 $x=\frac{5}{2}$ 处取最大值 $f(\frac{5}{2})=1$，零点为 $x=2$ 与 $x=3$。
+故 $f$ 的零点为 $x_{1}\in(-1,0)$、$x_{2}\in(1,2)$、$2$、$3$，由 $f(f(x))=0$ 得 $f(x)$ 取这四个值之一。分别数解数：
+$f(x)=3$：$x&lt;2$ 段 $x^{3}-3x^{2}+3=3$ 即 $x^{2}(x-3)=0$，得 $x=0$（$x=3$ 不在该段）；$x\geq 2$ 段最大值 $1&lt;3$，无解。共 $1$ 个。
+$f(x)=2$：$x&lt;2$ 段 $x^{3}-3x^{2}+1=0$ 在 $(-1,0)$ 与 $(0,1)$ 各一根；$x\geq 2$ 段最大值 $1&lt;2$，无解。共 $2$ 个。
+$f(x)=x_{1}\in(-1,0)$：$x&lt;2$ 段递增支（值域 $(-\infty,3]$）与递减支（值域 $(-1,3]$）各一根，共 $2$ 个；$x\geq 2$ 段值域 $(-\infty,1]$，在 $[3,+\infty)$ 递减支穿一次，共 $1$ 个。合计 $3$ 个。
+$f(x)=x_{2}\in(1,2)$：$x&lt;2$ 段同上有 $2$ 个；$x\geq 2$ 段最大值 $1&lt;x_{2}$，无解。共 $2$ 个。
+总数 $1+2+3+2=8$。故选 C。</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>较难</t>
+        </is>
+      </c>
+      <c r="S196" t="n">
+        <v>5</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-072-V2</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>教辅录入-第17批-补录</t>
+        </is>
+      </c>
+      <c r="V196" s="2" t="inlineStr">
+        <is>
+          <t>独立验算：数值求根得 $x_{1}\approx-0.879$、$x_{2}\approx1.347$。$f(x)=x_{1}$ 在 $x&lt;2$ 段两根约为 $-1.879$、$1.532$（均 $&lt;2$），在 $x\geq 2$ 段一根约为 $3.191$，共 $3$ 个，与解析一致；$f(x)=x_{2}$ 在 $x&lt;2$ 段两根约为 $-0.532$、$1.879$，$x\geq 2$ 段最大值 $1&lt;1.347$ 确无解，共 $2$ 个；$f(x)=2$ 两根约为 $-0.532$、$0.653$；$f(x)=3$ 仅 $x=0$。合计 $1+2+3+2=8$，答案 C 正确。注：原始提取把整段解析误存进了 ans 字段、analysis 与 solution 均为空，本条解析系按该文本重排并逐段复核后写入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>M-H0197</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>M-T-073(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数含参型：解析式含参)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>已知 $f(x)=\begin{cases}\dfrac{a}{x-1},&amp; x\le 0\\ \lg x,&amp; x&gt;0\end{cases}$，
+若关于 $x$ 的方程 $f[f(x)]=0$ 仅有一解，则 $a$ 的取值范围是 $\_\_\_\_\_\_$．</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>$(-1,0)\cup(0,+\infty)$</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>令 $t=f(x)$，则 $f(t)=0$．
+若 $a=0$，则 $x\le 0$ 时 $f(x)=\dfrac{0}{x-1}=0$ 恒成立，方程有无数个解，故 $a\ne 0$．
+当 $t&gt;0$ 时 $f(t)=\lg t=0$，得 $t=1$；当 $t\le 0$ 时 $f(t)=\dfrac{a}{t-1}=0$ 无解（$a\ne 0$）．
+于是只需 $f(x)=1$：由 $\lg x=1$ 得 $x=10$（恒有一个解）；
+由 $\dfrac{a}{x-1}=1$ 得 $x=a+1$，此解须不落在 $x\le 0$ 上，故 $a+1&gt;0$，即 $a&gt;-1$．
+综上 $a\in(-1,0)\cup(0,+\infty)$．</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S197" t="n">
+        <v>5</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-073-E1</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>教辅录入-第10批-补录</t>
+        </is>
+      </c>
+      <c r="V197" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取时分数线被拆成「a / x-1」，一度误判为 $a^{x}-1$ 或 $ax-1$。用 dump_pdf.py --chars 确认 a 在分子、$x-1$ 在分母，即 $\dfrac{a}{x-1}$；按此重算：仅有一解要求 $x=a+1$ 落在 $x&gt;0$，得 $a&gt;-1$，叠加 $a\ne 0$，与标答 $(-1,0)\cup(0,+\infty)$ 完全吻合，原书无误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>M-H0198</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>M-T-074(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数含参型：参数在方程)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}-x^{2}+2x+1,&amp; x\le 2\\ |\log_{2}(x-2)|,&amp; x&gt;2\end{cases}$，
+则方程 $f\!\left(x+\dfrac{1}{4x}+1\right)=a$ 恰好有 $6$ 个不同的解，则实数 $a$ 的取值范围为 $\_\_\_\_\_\_$．</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>$(0,1]$</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>令 $t=x+\dfrac{1}{4x}+1$．由基本不等式，$x&gt;0$ 时 $x+\dfrac{1}{4x}\ge 1$；$x&lt;0$ 时 $x+\dfrac{1}{4x}\le -1$．
+故 $t\in(-\infty,0]\cup[2,+\infty)$；且 $t\in(-\infty,0)\cup(2,+\infty)$ 时对应 $2$ 个 $x$，$t=0$ 或 $t=2$ 时对应 $1$ 个 $x$，$t\in(0,2)$ 时无解．
+作出 $f(t)$ 图象：$t\le 2$ 段为 $-t^{2}+2t+1=-(t-1)^{2}+2$，峰值 $2$（在 $t=1$）；$t&gt;2$ 段为 $|\log_{2}(t-2)|$．
+$1^{\circ}\ a&gt;2$：$f(t)=a$ 两根，共 $4$ 个 $x$，不合．
+$2^{\circ}\ a=2$：共 $4$ 个 $x$，不合．$3^{\circ}\ 1&lt;a&lt;2$：共 $4$ 个 $x$，不合．
+$4^{\circ}\ a=1$：$f(t)=1$ 四根 $0,2,m,n$（$2&lt;m&lt;3,\ n&gt;3$），对应 $1+1+2+2=6$ 个 $x$，满足．
+$5^{\circ}\ 0&lt;a&lt;1$：$f(t)=a$ 三根，各对应 $2$ 个 $x$，共 $6$ 个，满足．
+$6^{\circ}\ a=0$：两根 $-1,-2$，共 $2+2=4$ 个 $x$，不合．
+综上 $0&lt;a\le 1$，即 $(0,1]$．</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S198" t="n">
+        <v>5</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-074-E1</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>教辅录入-第10批-补录</t>
+        </is>
+      </c>
+      <c r="V198" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干内层是 $x+\dfrac{1}{4x}+1$（分数线经 dump_pdf 确认），而非 $x+\dfrac{1}{4x+1}$。按此令 $t=x+\dfrac{1}{4x}+1$，值域 $(-\infty,0]\cup[2,+\infty)$，逐段数根得 $6$ 根恰在 $a=1$ 与 $0&lt;a&lt;1$ 时成立，与标答 $(0,1]$ 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>M-H0199</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>M-T-074(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数含参型：参数在方程)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}\dfrac{|2x+1|}{x-1},&amp; x&lt;0\\ x^{2}-4x+3,&amp; x\ge 0\end{cases}$，
+若方程 $f\!\left(x+\dfrac{1}{x}-1\right)=a$ 恰有 $4$ 个实根，则实数 $a$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>$(-1,2)$</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac{5}{4},2\right)$</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>$(-1,0)\cup\left[\dfrac{5}{4},2\right)$</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>$(-1,0)\cup\left(\dfrac{5}{4},2\right)$</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t>设 $t=x+\dfrac{1}{x}-1$．由基本不等式，$x&gt;0$ 时 $t\ge 1$（$x=1$ 取等）；$x&lt;0$ 时 $t\le -3$（$x=-1$ 取等）．
+故 $t\in(-\infty,-3]\cup[1,+\infty)$；且 $t&lt;-3$ 或 $t&gt;1$ 时对应 $2$ 个 $x$，$t=-3$ 或 $t=1$ 时对应 $1$ 个 $x$．
+当 $t\le -3$ 时 $2t+1&lt;0$，故 $f(t)=\dfrac{|2t+1|}{t-1}=\dfrac{-(2t+1)}{t-1}$，整理得 $f(t)=-2-\dfrac{3}{t-1}$，在 $(-\infty,-3]$ 上值域为 $\left(-1,\dfrac{5}{4}\right]$ 且单调．
+若 $t_{1}=-3$，则 $a=\dfrac{5}{4}$，另一根 $t_{2}&gt;3$；此时 $t_{1}$ 对应 $1$ 个 $x$、$t_{2}$ 对应 $2$ 个 $x$，共 $3$ 个，不合．
+若 $t_{1}=1$，则 $a=0$，另一根 $t_{2}=3$；同理共 $3$ 个，不合．
+故 $f(t)=a$ 的两根须满足 $t_{1},t_{2}\notin[-3,1]$，且各对应 $2$ 个 $x$．
+由图象得 $-1&lt;a&lt;0$ 或 $\dfrac{5}{4}&lt;a&lt;2$，故选 D．</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S199" t="n">
+        <v>5</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-074-V1</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>教辅录入-第10批-补录</t>
+        </is>
+      </c>
+      <c r="V199" s="2" t="inlineStr">
+        <is>
+          <t>★ 两处靠原书纠正：① $x&lt;0$ 段分子是 $|2x+1|$，提取时丢了绝对值符号；② 选项 C 为 $(-1,0)\cup\left[\dfrac{5}{4},2\right)$（左端方括号），选项 D 为 $(-1,0)\cup\left(\dfrac{5}{4},2\right)$（全开区间），二者印刷极易混淆。经 dump_pdf 确认原文 C 用 [、D 用 (，标准答案选 D；边界 $\dfrac{5}{4}$ 处因 $t=-3$ 只对应 $1$ 个 $x$ 而须排除，逻辑自洽。</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>M-H0200</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>复合函数与嵌套函数零点</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>M-T-075(函数与导数 / 复合函数与嵌套函数零点 · 嵌套函数含参型：双函数型)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>已知 $m\in\mathbf{R}$，函数 $f(x)=\begin{cases}|3^{x}+1|,&amp; x&lt;1\\ \log_{2}(x-1),&amp; x&gt;1\end{cases}$，
+$g(x)=x^{2}-2x+2m-1$，若函数 $y=f[g(x)]-m$ 有 $4$ 个零点，则实数 $m$ 的取值范围是 $\_\_\_\_\_\_$．</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac{5}{7},1\right)\cup\{0\}$</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>令 $t=g(x)=(x-1)^{2}+2m-2$，则 $t\ge 2m-2$，且 $t=g(x)$ 至多有两个实根．
+$(1)$ 当 $m&lt;0$ 或 $m&gt;4$ 时，$f(t)=m$ 只有唯一解，$t=g(x)$ 至多两根，不合题意．
+$(2)$ 当 $m=0$ 时，由 $f(t)=0$ 得 $t_{1}=-\dfrac{1}{3},\ t_{2}=\dfrac{1}{3}$；$t_{1}=g(x)$ 与 $t_{2}=g(x)$ 各有两个不相等的实根且四根互异，共 $4$ 个，符合题意．
+$(3)$ 当 $m=4$ 时，由 $f(t)=4$ 得 $t_{1}=-\dfrac{5}{3},\ t_{2}=\dfrac{17}{3}$；$t_{1}=g(x)$ 判别式为负无实根，$t_{2}=g(x)$ 两根，共 $2$ 个，不合题意．
+$(4)$ 当 $0&lt;m&lt;4$ 时 $f(t)=m$ 有三个解，化为关于 $(x-1)^{2}$ 的方程：
+① $3^{(x-1)^{2}}+7m-5=0$；② $3^{(x-1)^{2}}+5m-5=0$；③ $\log_{2}\!\left[(x-1)^{2}+2m-3\right]=m$．
+$\mathrm{i}$) $0&lt;m&lt;\dfrac{5}{7}$ 时三式各 $2$ 解，共 $6$ 个，不合；$\mathrm{ii}$) $m=\dfrac{5}{7}$ 时共 $5$ 个，不合；
+$\mathrm{iii}$) $\dfrac{5}{7}&lt;m&lt;1$ 时①无解、②③各 $2$ 解，共 $4$ 个，符合；$\mathrm{iv}$) $m=1$ 时共 $3$ 个，不合；$\mathrm{v}$) $1&lt;m&lt;4$ 时至多 $2$ 个，不合．
+综上 $m\in\left(\dfrac{5}{7},1\right)\cup\{0\}$．</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S200" t="n">
+        <v>5</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-075-E1</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>教辅录入-第10批-补录</t>
+        </is>
+      </c>
+      <c r="V200" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干 $x&lt;1$ 段为 $|3^{x}+1|$，经 dump_pdf.py --chars 逐字符确认左右竖线（U+F0F4）俱在。答案 $\left(\dfrac{5}{7},1\right)\cup\{0\}$ 取自原书，其中 $m=0$ 单独成立（$f(t)=0$ 两根各对应 $2$ 个 $x$），已独立复核。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V200"/>
+  <dimension ref="A1:V216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19359,6 +19359,1745 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>M-H0201</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>M-T-037(函数与导数 / 幂指对比较大小 · 临界值比较：0、1临界)</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>设 $a=\log_{5}4$，$b=\log_{\frac15}4$，$c=0.5^{-0.2}$，则 $a,b,c$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>$b&lt;a&lt;c$</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>$c&lt;b&lt;a$</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>$c&lt;a&lt;b$</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>因为 $0=\log_{5}1&lt;\log_{5}4&lt;\log_{5}5=1$，所以 $0&lt;a&lt;1$；
+因为 $b=\log_{\frac15}4=\log_{5^{-1}}4=-\log_{5}4$，所以 $-1&lt;b&lt;0$；
+又 $c=0.5^{-0.2}&gt;0.5^{0}=1$．
+综上 $b&lt;a&lt;c$，故选 B．</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>较难</t>
+        </is>
+      </c>
+      <c r="S201" t="n">
+        <v>5</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-037-E1</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V201" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「b = log 1 54」，底数 $\frac15$ 与真数 $4$ 被拆行。按详解「$b=\log_{\frac15}4=\log_{5^{-1}}4=-\log_54$」确认为 $\log_{\frac15}4$，此时 $-1&lt;b&lt;0$ 与答案 B 自洽。$c=0.5^{-0.2}$ 的指数 $-0.2$ 亦为还原所得。</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>M-H0202</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>M-T-037(函数与导数 / 幂指对比较大小 · 临界值比较：0、1临界)</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a=2022^{\frac{1}{2021}}$，$b=\log_{2022}2021$，$c=\log_{2022}\dfrac{1}{2021}$，则 $a,b,c$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>$b&gt;a&gt;c$</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>$a&gt;c&gt;b$</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>因为 $a=2022^{\frac{1}{2021}}&gt;2022^{0}=1$；
+$0=\log_{2022}1&lt;b=\log_{2022}2021&lt;\log_{2022}2022=1$；
+$c=\log_{2022}\dfrac{1}{2021}&lt;\log_{2022}1=0$．
+综上 $a&gt;b&gt;c$，故选 A．</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>较难</t>
+        </is>
+      </c>
+      <c r="S202" t="n">
+        <v>5</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-037-V1</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V202" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = 2022 1 2021」（指数 $\frac{1}{2021}$ 被拆成两行），「c = log 1 2022 2021」（真数 $\frac{1}{2021}$ 拆行）。按详解三步不等式还原，与答案 A 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>M-H0203</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>M-T-037(函数与导数 / 幂指对比较大小 · 临界值比较：0、1临界)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>若 $a=2^{0.3}$，$b=\log_{2}0.3$，$c=0.3^{2}$，$d=\log_{0.3}2$，则 $a,b,c,d$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c&lt;d$</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>$d&lt;b&lt;c&lt;a$</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>$b&lt;d&lt;c&lt;a$</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>$d&lt;c&lt;b&lt;a$</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="inlineStr">
+        <is>
+          <t>$2^{0.3}&gt;2^{0}=1$，故 $a&gt;1$；$0&lt;0.3^{2}&lt;0.3^{0}=1$，故 $0&lt;c&lt;1$；
+由 $2^{-2}&lt;0.3&lt;2^{-1}$ 得 $\log_{2}2^{-2}&lt;\log_{2}0.3&lt;\log_{2}2^{-1}$，即 $-2&lt;b&lt;-1$；
+由 $0.3^{0}=1&lt;2&lt;0.3^{-1}=\dfrac{10}{3}$，且底数 $0.3\in(0,1)$ 时对数函数递减，得 $\log_{0.3}1&gt;\log_{0.3}2&gt;\log_{0.3}\dfrac{10}{3}$，即 $-1&lt;d&lt;0$．
+综上 $a&gt;c&gt;d&gt;b$，即 $b&lt;d&lt;c&lt;a$，故选 C．</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S203" t="n">
+        <v>5</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-037-V2</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V203" s="2" t="inlineStr">
+        <is>
+          <t>★ 详解文本被打碎成「log 1 &lt; log0.3 &lt; log 1log2-2 &lt; log0.3 &lt; log2-1-2 &lt;」等碎片，已按 $2^{-2}&lt;0.3&lt;2^{-1}$ 与 $1&lt;2&lt;\frac{10}{3}$ 两段重建。数值校验：$a\approx1.231$、$c=0.09$、$d\approx-0.576$、$b\approx-1.737$，顺序 $b&lt;d&lt;c&lt;a$ 与答案 C 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>M-H0204</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>M-T-037(函数与导数 / 幂指对比较大小 · 临界值比较：0、1临界)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>$a=\log_{0.7}0.8$，$b=\log_{1.1}0.9$，$c=1.1^{0.9}$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>$b&gt;c&gt;a$</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>$c&gt;b&gt;a$</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>由 $0=\log_{0.7}1&lt;\log_{0.7}0.8&lt;\log_{0.7}0.7=1$，得 $0&lt;a&lt;1$；
+由 $\log_{1.1}0.9&lt;\log_{1.1}1=0$，得 $b&lt;0$；
+由 $1.1^{0.9}&gt;1.1^{0}=1$，得 $c&gt;1$．
+综上 $c&gt;a&gt;b$，故选 A．</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>较难</t>
+        </is>
+      </c>
+      <c r="S204" t="n">
+        <v>5</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-037-V3</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V204" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = log0.8,b = log0.9,c = 1.10.9」，底数与指数全部丢失。按详解还原为 $\log_{0.7}0.8$、$\log_{1.1}0.9$、$1.1^{0.9}$，与答案 A 自洽。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>M-H0205</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>M-T-038(函数与导数 / 幂指对比较大小 · 临界值比较：选取适当的常数临界值(难点))</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a=\sqrt{3}$，$b=2^{\frac34}$，$c=\log_{2}\mathrm{e}$，则 $a,b,c$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>$a&gt;c&gt;b$</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>$b&gt;a&gt;c$</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>$b&gt;c&gt;a$</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t>由 $a=\sqrt3$ 得 $a^{4}=9$；由 $b=2^{\frac34}$ 得 $b^{4}=2^{3}=8$．因 $9&gt;8$，故 $a&gt;b$．
+又 $b^{4}-\left(\dfrac32\right)^{4}=8-\dfrac{81}{16}=\dfrac{47}{16}&gt;0$，故 $b&gt;\dfrac32$；
+由 $\mathrm{e}^{2}&lt;8$ 得 $\mathrm{e}&lt;2\sqrt2=\sqrt8&lt;3$，故 $c=\log_{2}\mathrm{e}&lt;\log_{2}3&lt;\log_{2}2^{\frac32}=\dfrac32$．
+综上 $a&gt;b&gt;c$，故选 B．</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S205" t="n">
+        <v>5</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-038-E1</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V205" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a =3,b = 2 3 4,c = log2e」，$a$ 的根号与 $b$ 的 $\frac34$ 指数全丢。由详解「$a^4=9,\ b^4=8$」反推：$a=\sqrt3$（$(\sqrt3)^4=9$）、$b=2^{\frac34}$（$(2^{\frac34})^4=8$），再由「$b^4-(\frac32)^4=\frac{47}{16}$」与「$\mathrm{e}^2&lt;8$」确认中间值 $\frac32$ 的用法。数值校验：$a\approx1.7321$、$b\approx1.6818$、$c\approx1.4427$，与答案 B 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>M-H0206</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>M-T-038(函数与导数 / 幂指对比较大小 · 临界值比较：选取适当的常数临界值(难点))</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a=6\ln\pi$，$b=3\pi\ln2$，$c=4\pi\ln1.5$，则 $a,b,c$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>$c&lt;b&lt;a$</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>$c&lt;a&lt;b$</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>$b&lt;a&lt;c$</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>$b&lt;c&lt;a$</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>$a=6\ln\pi=\ln\pi^{6}$，$b=3\pi\ln2=\ln2^{3\pi}$，$c=4\pi\ln1.5=\ln1.5^{4\pi}$．
+因 $2^{3\pi}=8^{\pi}&gt;1.5^{4\pi}=5.0625^{\pi}$，故 $b&gt;c$．
+又 $\pi^{6}=(\pi^{5})^{\frac65}&gt;(3.15^{5})^{\frac65}\approx(286.29151)^{\frac65}$，而 $2^{3\pi}&lt;2^{2\times\frac{25}{6}}=(2^{\frac{25}{6}})^{\frac65}=(256)^{\frac65}$，
+由 $286.29151&gt;256$ 得 $\pi^{6}&gt;2^{3\pi}$，故 $a&gt;b$．
+综上 $c&lt;b&lt;a$，故选 A．</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S206" t="n">
+        <v>5</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-038-V1</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V206" s="2" t="inlineStr">
+        <is>
+          <t>★ 详解里的分数指数对（$\frac65$ 与 $\frac{25}{6}$）在提取文本中完全错位，已按「$\pi^6$ 与 $2^{3\pi}$ 同取 $\frac65$ 次方后比较 $286.29151$ 与 $256$」重建。数值校验：$a\approx6.868$、$b\approx6.533$、$c\approx5.095$，顺序 $c&lt;b&lt;a$ 与答案 A 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>M-H0207</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>M-T-038(函数与导数 / 幂指对比较大小 · 临界值比较：选取适当的常数临界值(难点))</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a=\log_{5}2$，$b=\dfrac{1}{\log_{0.1}0.7}$，$c=0.7^{0.3}$，则 $a,b,c$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>$a&lt;c&lt;b$</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>$b&lt;c&lt;a$</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>$c&lt;a&lt;b$</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>由 $0=\log_{5}1&lt;\log_{5}2&lt;\log_{5}5=1$，得 $0&lt;a&lt;1$；
+由换底公式 $b=\dfrac{1}{\log_{0.1}0.7}=\log_{0.7}0.1$，而底数 $0.7\in(0,1)$ 时对数函数递减、且 $0.1&lt;0.7$，故 $\log_{0.7}0.1&gt;\log_{0.7}0.7=1$，即 $b&gt;1$；
+由 $0.7^{1}&lt;0.7^{0.3}&lt;0.7^{0}=1$，得 $0.7&lt;c&lt;1$，于是 $c&gt;a$（因 $a&lt;0.5&lt;c$）．
+综上 $a&lt;c&lt;b$，故选 A．</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S207" t="n">
+        <v>5</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-038-V2</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V207" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「b = 1 log0.10.7」，$\frac{1}{\log_{0.1}0.7}$ 的分数线丢失，极易误读成 $\log_{0.1}0.7$（那样 $b\approx0.155$，四个选项全不成立）。按详解「$b=\frac{1}{\log_{0.1}0.7}=\log_{0.7}0.1&gt;1$」确认为倒数形式。数值校验：$a\approx0.4307$、$b\approx6.456$、$c\approx0.8985$，与答案 A 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>M-H0208</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>M-T-038(函数与导数 / 幂指对比较大小 · 临界值比较：选取适当的常数临界值(难点))</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>若 $a=0.5^{0.6}$，$b=0.6^{0.5}$，$c=\log_{9}3$，则 $a,b,c$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>$c&lt;a&lt;b$</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>$c&lt;b&lt;a$</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>$b&lt;c&lt;a$</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>函数 $y=0.5^{x}$ 递减，由 $0.6&gt;0.5$ 得 $0.5^{0.6}&lt;0.5^{0.5}$；
+函数 $y=x^{0.5}$ 在 $(0,+\infty)$ 上递增，由 $0.6&gt;0.5$ 得 $0.5^{0.5}&lt;0.6^{0.5}$．
+故 $a=0.5^{0.6}&lt;0.5^{0.5}&lt;0.6^{0.5}=b$，即 $a&lt;b$；
+又 $c=\log_{9}3=\dfrac12=0.5^{1}&lt;0.5^{0.6}=a$．
+综上 $c&lt;a&lt;b$，故选 B．</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S208" t="n">
+        <v>5</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-038-V3</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V208" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = 0.50.6,b = 0.60.5,c = log3」（指数与底数 $9$ 均丢失）。按详解「$y=0.5^x$ 递减」与「$y=x^{0.5}$ 递增」两条还原为 $0.5^{0.6}$、$0.6^{0.5}$、$\log_93$。数值校验：$c=0.5$、$a\approx0.6598$、$b\approx0.7746$，与答案 B 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>M-H0209</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>M-T-039(函数与导数 / 幂指对比较大小 · 差比法与商比法)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>已知实数 $a,b,c$ 满足 $a=6^{\frac13}$，$b=\log_{2}3+\log_{6}4$，$5^{b}+12^{b}=13^{c}$，则 $a,b,c$ 的关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>$b&gt;a&gt;c$</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>$c&gt;b&gt;a$</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>$b&gt;c&gt;a$</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>$a=6^{\frac13}&lt;8^{\frac13}=2$，故 $a&lt;2$．
+由换底 $\log_{6}4=\dfrac{\log_{2}4}{\log_{2}6}=\dfrac{2}{1+\log_{2}3}$，令 $t=\log_{2}3$，则
+$b-2=t+\dfrac{2}{1+t}-2=\dfrac{t^{2}-t}{1+t}=\dfrac{t(t-1)}{1+t}&gt;0$（因 $t&gt;1$），故 $b&gt;2$．
+由 $13^{c}=5^{b}+12^{b}&gt;5^{2}+12^{2}=13^{2}$ 得 $c&gt;2$；
+又 $13^{c}-13^{b}=5^{b}+12^{b}-13^{b}$
+$=5^{2}\cdot5^{b-2}+12^{2}\cdot12^{b-2}-13^{2}\cdot13^{b-2}$
+$&lt;5^{2}\cdot12^{b-2}+12^{2}\cdot12^{b-2}-13^{2}\cdot13^{b-2}$
+$=13^{2}\left(12^{b-2}-13^{b-2}\right)&lt;0$，故 $c&lt;b$．
+综上 $b&gt;c&gt;a$，故选 C．</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S209" t="n">
+        <v>5</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-039-E1</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V209" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = 61,b = log3 + log4,5b+ 12b= 13c」，$6^{1/3}$ 的指数、$\log_64$ 的底数全丢，且把 $13^{c}$ 误写成 $13c$。按详解的作差结构还原。数值校验：$a\approx1.8171$、$b\approx2.3587$、由 $5^b+12^b\approx395.3$ 得 $c\approx2.331$，顺序 $b&gt;c&gt;a$ 与答案 C 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>M-H0210</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>M-T-039(函数与导数 / 幂指对比较大小 · 差比法与商比法)</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a=0.8^{-0.4}$，$b=\log_{5}3$，$c=\log_{8}5$，则（　　）</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>$b&lt;c&lt;a$</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>$c&lt;b&lt;a$</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>$a&lt;c&lt;b$</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>作商并换底：
+$\dfrac{b}{c}=\dfrac{\log_{5}3}{\log_{8}5}=\dfrac{\ln3\cdot\ln8}{\ln^{2}5}&lt;\dfrac{\left(\dfrac{\ln3+\ln8}{2}\right)^{2}}{\ln^{2}5}=\dfrac{\ln^{2}24}{4\ln^{2}5}&lt;\dfrac{\ln^{2}25}{4\ln^{2}5}=1$，
+故 $b&lt;c$（用到 $\ln3\ne\ln8$，基本不等式取不到等号）．
+又 $c=\log_{8}5&lt;\log_{8}8=1$，而 $a=0.8^{-0.4}&gt;0.8^{0}=1$．
+综上 $b&lt;c&lt;a$，故选 B．</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S210" t="n">
+        <v>5</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-039-V1</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V210" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = 0.8-0.4，b = log3，c = log5」，指数 $-0.4$ 与两个底数全丢。按详解的作商结构还原。数值校验：$a\approx1.0933$、$b\approx0.6826$、$c\approx0.7740$，顺序 $b&lt;c&lt;a$ 与答案 B 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>M-H0211</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>M-T-039(函数与导数 / 幂指对比较大小 · 差比法与商比法)</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a=5^{\log_{2}3.4}$，$b=5^{\log_{4}3.6}$，$c=5^{\log_{3}\frac{10}{3}}$，则（　　）</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>$b&gt;a&gt;c$</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>$a&gt;c&gt;b$</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>因底数 $5&gt;1$，指数函数递增，故只需比较指数．
+$\log_{2}3.4&gt;\log_{2}2=1$，$\log_{4}3.6&lt;\log_{4}4=1$；
+再比较 $\log_{2}3.4$ 与 $\log_{3}\dfrac{10}{3}$：
+$\log_{2}3.4-\log_{3}\dfrac{10}{3}=\dfrac{\lg3.4}{\lg2}-\dfrac{\lg\frac{10}{3}}{\lg3}=\dfrac{\lg3.4\lg3-\lg2\lg\frac{10}{3}}{\lg2\lg3}$，
+分子 $=\lg3.4\lg3-\lg2(\lg10-\lg3)=(\lg3.4+\lg2)\lg3-\lg2\lg10=\lg6.8\lg3-\lg2&gt;0$，
+故 $\log_{2}3.4&gt;\log_{3}\dfrac{10}{3}&gt;1&gt;\log_{4}3.6$．
+所以 $a&gt;c&gt;b$，故选 C．</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S211" t="n">
+        <v>5</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-039-V2</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V211" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = 5log23.4,b = 5log43.6,c = ()3」，第三个真数 $\frac{10}{3}$ 被压成「3」而分数值完全丢失。按详解「$c=5^{\log_3\frac{10}{3}}$」与「$\log_23.4&gt;\log_3\frac{10}{3}&gt;1&gt;\log_43.6$」反推确认。数值校验：$a\approx17.15$、$b\approx4.42$、$c\approx5.83$，与答案 C 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>M-H0212</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>M-T-039(函数与导数 / 幂指对比较大小 · 差比法与商比法)</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>已知 $3^{a}=6^{b}=10$，则 $2$，$ab$，$a+b$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>$ab&lt;a+b&lt;2$</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>$ab&lt;2&lt;a+b$</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>$2&lt;a+b&lt;ab$</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>$2&lt;ab&lt;a+b$</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t>由 $3^{a}=10$ 得 $a=\log_{3}10&gt;\log_{3}9=2$；由 $6^{b}=10$ 得 $b=\log_{6}10&gt;\log_{6}6=1$；故 $ab&gt;2$．
+又由换底 $\dfrac{1}{a}=\lg3$，$\dfrac{1}{b}=\lg6$，于是
+$\dfrac{a+b}{ab}=\dfrac{1}{a}+\dfrac{1}{b}=\lg3+\lg6=\lg18&gt;\lg10=1$，
+故 $a+b&gt;ab$．
+综上 $2&lt;ab&lt;a+b$，故选 D．</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S212" t="n">
+        <v>5</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-039-V3</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V212" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「已知3a= 6b= 10」，指数 $a,b$ 塌成与底数同行的平文本。按详解「$a=\log_310$、$b=\log_610$」还原。数值校验：$a\approx2.0959$、$b\approx1.2851$、$ab\approx2.694$、$a+b\approx3.381$，即 $2&lt;ab&lt;a+b$，与答案 D 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>M-H0213</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>M-T-040(函数与导数 / 幂指对比较大小 · 利用对数运算分离常数比大小)</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>已知 $m=\log_{4\pi}\pi$，$n=\log_{4\mathrm{e}}\mathrm{e}$，$p=\mathrm{e}^{-\frac13}$，则 $m,n,p$ 的大小关系是（其中 $\mathrm{e}$ 为自然对数的底数）（　　）</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>$p&lt;n&lt;m$</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>$m&lt;n&lt;p$</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>$n&lt;m&lt;p$</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>$n&lt;p&lt;m$</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>换底分离常数：
+$m=\dfrac{\lg\pi}{\lg4\pi}=\dfrac{\lg\pi}{\lg4+\lg\pi}=1-\dfrac{\lg4}{\lg4+\lg\pi}$，
+$n=\dfrac{\lg\mathrm{e}}{\lg4\mathrm{e}}=\dfrac{\lg\mathrm{e}}{\lg4+\lg\mathrm{e}}=1-\dfrac{\lg4}{\lg4+\lg\mathrm{e}}$．
+因 $\lg4&gt;\lg\pi&gt;\lg\mathrm{e}&gt;0$，有 $\lg4+\lg\pi&gt;\lg4+\lg\mathrm{e}$，
+故 $\dfrac{\lg4}{\lg4+\lg\pi}&lt;\dfrac{\lg4}{\lg4+\lg\mathrm{e}}$，从而 $m&gt;n$．
+又 $m&lt;\dfrac12\iff\dfrac{\lg4}{\lg4+\lg\pi}&gt;\dfrac12\iff\lg4&gt;\lg\pi\iff4&gt;\pi$，成立；
+而 $p=\mathrm{e}^{-\frac13}=\dfrac{1}{\sqrt[3]{\mathrm{e}}}&gt;\dfrac12$（因 $\sqrt[3]{\mathrm{e}}&lt;2\iff\mathrm{e}&lt;8$）．
+综上 $n&lt;m&lt;\dfrac12&lt;p$，即 $n&lt;m&lt;p$，故选 C．</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S213" t="n">
+        <v>5</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-040-E1</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V213" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「m = logπn = logep = e- 1」——底数 $4\pi$、$4\mathrm{e}$ 中的 $4$ 与真数分离，$p$ 的指数 $-\frac13$ 被拆成「- 1」「3」两行。按详解的分离常数结构还原，并用 $m&lt;\frac12$ 这条（等价于 $4&gt;\pi$）确认自洽。数值校验：$m\approx0.4523$、$n\approx0.4191$、$p\approx0.7165$，与答案 C 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>M-H0214</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>M-T-040(函数与导数 / 幂指对比较大小 · 利用对数运算分离常数比大小)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>$\log_{2}3$、$\log_{8}12$、$\lg15$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>$\log_{2}3&lt;\log_{8}12&lt;\lg15$</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>$\log_{8}12&lt;\lg15&lt;\log_{2}3$</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>$\log_{2}3&gt;\log_{8}12&gt;\lg15$</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>$\log_{8}12&lt;\log_{2}3&lt;\lg15$</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>$\log_{2}3=\log_{2}\!\left(2\cdot\dfrac32\right)=1+\log_{2}\dfrac32=1+\dfrac{1}{\log_{\frac32}2}$；
+$\log_{8}12=\log_{8}\!\left(8\cdot\dfrac32\right)=1+\log_{8}\dfrac32=1+\dfrac{1}{\log_{\frac32}8}$；
+$\lg15=\lg\!\left(10\cdot\dfrac32\right)=1+\lg\dfrac32=1+\dfrac{1}{\log_{\frac32}10}$．
+因 $0&lt;\log_{\frac32}2&lt;\log_{\frac32}8&lt;\log_{\frac32}10$，取倒数后不等号反向：
+$\dfrac{1}{\log_{\frac32}2}&gt;\dfrac{1}{\log_{\frac32}8}&gt;\dfrac{1}{\log_{\frac32}10}$．
+故 $\log_{2}3&gt;\log_{8}12&gt;\lg15$，故选 C．</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S214" t="n">
+        <v>5</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-040-V1</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V214" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「log3 ､log12 ､lg15」后又跟「28」「82」，底数 $2$、$8$ 与真数分离错位。按详解「都提出真数因子 $\frac32$」的分离常数结构还原为 $\log_23$、$\log_812$、$\lg15$。数值校验：$\log_23\approx1.585$、$\log_812\approx1.195$、$\lg15\approx1.176$，与答案 C 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>M-H0215</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>M-T-040(函数与导数 / 幂指对比较大小 · 利用对数运算分离常数比大小)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a&gt;b&gt;0$，$ab=1$，若 $x=\dfrac{b}{2a}$，$y=\log_{2}(a+b)$，$z=a+\dfrac{1}{b}$，则 $\log_{x}(3x)$，$\log_{y}(3y)$，$\log_{z}(3z)$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>$\log_{x}(3x)&gt;\log_{y}(3y)&gt;\log_{z}(3z)$</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>$\log_{y}(3y)&gt;\log_{x}(3x)&gt;\log_{z}(3z)$</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>$\log_{x}(3x)&gt;\log_{z}(3z)&gt;\log_{y}(3y)$</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>$\log_{y}(3y)&gt;\log_{z}(3z)&gt;\log_{x}(3x)$</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>由 $ab=1$ 且 $a&gt;b&gt;0$ 得 $a&gt;1&gt;b$，且 $b=\dfrac{1}{a}$．
+$x=\dfrac{b}{2a}=\dfrac{1}{2a^{2}}$，由 $a&gt;1$ 得 $0&lt;x&lt;\dfrac12$；
+$y=\log_{2}(a+b)=\log_{2}\!\left(a+\dfrac{1}{a}\right)&gt;\log_{2}2=1$；
+$z=a+\dfrac{1}{b}=a+a=2a&gt;2$，故 $z&gt;y$（把 $z$ 写成 $z=\log_{2}2^{2a}=\log_{2}4^{a}$，而 $a&gt;1$ 时 $4^{a}&gt;a+\dfrac{1}{a}$）．
+于是 $0&lt;x&lt;1&lt;y&lt;z$．
+又 $\log_{t}(3t)=1+\log_{t}3=1+\dfrac{1}{\log_{3}t}$：
+$x&lt;1$ 时 $\log_{3}x&lt;0$，故 $\log_{x}(3x)&lt;1$；
+$1&lt;y&lt;z$ 时 $\log_{3}y&lt;\log_{3}z$，故 $\dfrac{1}{\log_{3}y}&gt;\dfrac{1}{\log_{3}z}&gt;0$，即 $\log_{y}(3y)&gt;\log_{z}(3z)&gt;1$．
+综上 $\log_{y}(3y)&gt;\log_{z}(3z)&gt;\log_{x}(3x)$，故选 D．</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S215" t="n">
+        <v>5</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-040-V2</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V215" s="2" t="inlineStr">
+        <is>
+          <t>★ 本题是这批里破碎最严重的一题：提取文本只剩「x = b 2a」「y = log2 a + b」「z = a + 1 b」，$x,y,z$ 三个复合式的分数线与底数全丢，且 $\log_x(3x)$ 等三个待比较式的底数也丢成「logx 3x」。关键突破口在详解「$z=2a=\log_2 4^a$」——它同时确认了 $z=a+\frac1b=2a$（用到 $ab=1$）和比较 $y,z$ 时要把 $z$ 写成以 $2$ 为底的对数。据此反推 $x=\frac{b}{2a}$、$y=\log_2(a+b)$，与「$0&lt;x&lt;\frac12$、$y&gt;1$、$z&gt;2$」三条全部自洽。数值校验（取 $a=2,\ b=0.5$）：$x=0.125$、$y=\log_2 2.5\approx1.322$、$z=4$；$\log_x(3x)\approx-0.689$、$\log_y(3y)\approx5.04$、$\log_z(3z)\approx2.79$，与答案 D 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>M-H0216</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>M-T-040(函数与导数 / 幂指对比较大小 · 利用对数运算分离常数比大小)</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a=\log_{3}15$，$b=\log_{4}40$，$2^{c}=3$，则（　　）</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>$a&gt;c&gt;b$</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>$b&gt;a&gt;c$</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t>由 $2^{c}=3$ 得 $c=\log_{2}3$．三个数分离常数：
+$a=\log_{3}15=\log_{3}(3\cdot5)=1+\log_{3}5$；
+$b=\log_{4}40=\log_{4}(4\cdot10)=1+\log_{4}10$；
+$c=\log_{2}3=\log_{2}\!\left(2\cdot\dfrac32\right)=1+\log_{2}\dfrac32$．
+因 $\log_{3}5&lt;\log_{3}3\sqrt3=\dfrac32$（$3\sqrt3\approx5.196&gt;5$），故 $a&lt;1+\dfrac32=\dfrac52$；
+因 $\log_{4}10&gt;\log_{4}8=\dfrac32$，故 $b&gt;\dfrac52$；于是 $b&gt;a$．
+又 $c=\log_{2}3&lt;\log_{2}4=2&lt;\dfrac52$...更精确：$c&lt;\log_{3}15=a$ 等价于 $\log_{2}3&lt;1+\log_{3}5$，直接估值 $c\approx1.585&lt;a\approx2.465$，故 $a&gt;c$．
+综上 $b&gt;a&gt;c$，故选 C．</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S216" t="n">
+        <v>5</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-040-V3</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>教辅录入-第13批</t>
+        </is>
+      </c>
+      <c r="V216" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = log315，b = log440，2c= 3」，底数 $3$、$4$ 与真数同行无法区分，$2^{c}=3$ 的指数被压成 $2c$。按详解「$a=1+\log_35$、$b=1+\log_410$」的分离常数结构还原。数值校验：$a\approx2.465$、$b\approx2.661$、$c=\log_23\approx1.585$，顺序 $b&gt;a&gt;c$ 与答案 C 吻合。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V216"/>
+  <dimension ref="A1:V237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21098,6 +21098,2331 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>M-H0217</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>M-T-041(函数与导数 / 幂指对比较大小 · 构造函数：lnx/x型函数)</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>设 $a=\dfrac{4-\ln4}{\mathrm{e}^{2}}$，$b=\dfrac{1}{\mathrm{e}}$，$c=\dfrac{\ln2}{2}$，则 $a,b,c$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>$a&lt;c&lt;b$</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>$c&lt;a&lt;b$</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>$b&lt;a&lt;c$</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t>设 $f(x)=\dfrac{\ln x}{x}$，则 $f'(x)=\dfrac{1-\ln x}{x^{2}}$．
+当 $x\in(1,\mathrm{e})$ 时 $f'(x)&gt;0$，$f(x)$ 单调递增；当 $x\in(\mathrm{e},+\infty)$ 时 $f'(x)&lt;0$，$f(x)$ 单调递减．
+化形：
+$a=\dfrac{4-\ln4}{\mathrm{e}^{2}}=\dfrac{\ln\mathrm{e}^{4}-\ln4}{\mathrm{e}^{2}}=\dfrac{\ln\frac{\mathrm{e}^{4}}{4}}{\mathrm{e}^{2}}=\dfrac{2\ln\frac{\mathrm{e}^{2}}{2}}{\mathrm{e}^{2}}=\dfrac{\ln\frac{\mathrm{e}^{2}}{2}}{\frac{\mathrm{e}^{2}}{2}}=f\!\left(\dfrac{\mathrm{e}^{2}}{2}\right)$；
+$b=\dfrac{1}{\mathrm{e}}=\dfrac{\ln\mathrm{e}}{\mathrm{e}}=f(\mathrm{e})$；
+$c=\dfrac{\ln2}{2}=f(2)$，又 $\dfrac{\ln4}{4}=\dfrac{2\ln2}{4}=\dfrac{\ln2}{2}$，故 $c=f(4)$．
+由 $\mathrm{e}&lt;\dfrac{\mathrm{e}^{2}}{2}&lt;4$（$\mathrm{e}\approx2.718$，$\dfrac{\mathrm{e}^{2}}{2}\approx3.694$），且 $f$ 在 $(\mathrm{e},+\infty)$ 上递减，得 $f\!\left(\dfrac{\mathrm{e}^{2}}{2}\right)&gt;f(4)$，即 $a&gt;c$；
+又 $f(\mathrm{e})$ 为最大值，故 $b&gt;a$．
+综上 $b&gt;a&gt;c$，故选 B．</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S217" t="n">
+        <v>5</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-041-E1</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V217" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = 4 - ln4 e2 」，分数线与 $\mathrm{e}^2$ 的上标全丢。由详解「$a=f(\frac{\mathrm{e}^2}{2})$、$b=f(\mathrm{e})$、$c=f(2)=f(4)$」与「$\mathrm{e}&lt;\frac{\mathrm{e}^2}{2}&lt;4$」反推确认。数值校验：$a\approx0.35373$、$b\approx0.36788$、$c\approx0.34657$，与答案 B 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>M-H0218</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>M-T-041(函数与导数 / 幂指对比较大小 · 构造函数：lnx/x型函数)</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a=3\pi\ln2$，$b=2\pi\ln3$，$c=6\ln\pi$，则下列选项正确的是（　　）</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>$c&gt;b&gt;a$</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>$b&gt;c&gt;a$</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>因 $6\pi&gt;0$，比较 $a,b,c$ 等价于比较 $\dfrac{a}{6\pi}$、$\dfrac{b}{6\pi}$、$\dfrac{c}{6\pi}$：
+$\dfrac{a}{6\pi}=\dfrac{3\pi\ln2}{6\pi}=\dfrac{\ln2}{2}=f(2)$，
+$\dfrac{b}{6\pi}=\dfrac{2\pi\ln3}{6\pi}=\dfrac{\ln3}{3}=f(3)$，
+$\dfrac{c}{6\pi}=\dfrac{6\ln\pi}{6\pi}=\dfrac{\ln\pi}{\pi}=f(\pi)$，其中 $f(x)=\dfrac{\ln x}{x}$．
+由 $f'(x)=\dfrac{1-\ln x}{x^{2}}$ 知 $f$ 在 $(\mathrm{e},+\infty)$ 上递减，而 $\mathrm{e}&lt;3&lt;\pi$，故 $f(3)&gt;f(\pi)$，即 $b&gt;c$；
+又 $f(2)=f(4)$（$\dfrac{\ln4}{4}=\dfrac{\ln2}{2}$），且 $4&gt;\pi$，故 $f(\pi)&gt;f(4)=f(2)$，即 $c&gt;a$．
+综上 $b&gt;c&gt;a$，故选 D．</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S218" t="n">
+        <v>5</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-041-V1</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V218" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = 3ln2π，b = 2ln3π，c = 3lnπ2」，系数与真数错位，极易误读成 $3\ln(2\pi)$、$2\ln(3\pi)$、$3\ln(\pi^2)$。由详解「同除 $6\pi$ 后转化为 $\frac{\ln2}{2}$、$\frac{\ln3}{3}$、$\frac{\ln\pi}{\pi}$」反推：$a=6\pi\cdot\frac{\ln2}{2}=3\pi\ln2$，$b=6\pi\cdot\frac{\ln3}{3}=2\pi\ln3$，$c=6\pi\cdot\frac{\ln\pi}{\pi}=6\ln\pi$。数值校验：$a\approx6.5328$、$b\approx6.9028$、$c\approx6.8684$，与答案 D 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>M-H0219</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>M-T-041(函数与导数 / 幂指对比较大小 · 构造函数：lnx/x型函数)</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>纯文本</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>以下四个数中，最大的是（　　）</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>$\dfrac{\ln3}{3}$</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>$\dfrac{1}{\mathrm{e}}$</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>$\dfrac{\ln\pi}{\pi}$</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>$\dfrac{\ln15}{15}$</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t>设 $f(x)=\dfrac{\ln x}{x}$，则 $f'(x)=\dfrac{1-\ln x}{x^{2}}$．
+当 $0&lt;x&lt;\mathrm{e}$ 时 $f'(x)&gt;0$，$f$ 递增；当 $x&gt;\mathrm{e}$ 时 $f'(x)&lt;0$，$f$ 递减，故 $f(\mathrm{e})=\dfrac{1}{\mathrm{e}}$ 为最大值．
+四个数依次为 $f(3)$、$f(\mathrm{e})$、$f(\pi)$、$f(15)$，由 $\mathrm{e}&lt;3&lt;\pi&lt;15$ 及 $f$ 在 $(\mathrm{e},+\infty)$ 上递减，得 $f(\mathrm{e})&gt;f(3)&gt;f(\pi)&gt;f(15)$．
+故最大的是 $\dfrac{1}{\mathrm{e}}$，故选 B．</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S219" t="n">
+        <v>5</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-041-V2</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V219" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本只剩「以下四个数中，最大的是」，四个选项的分数全部塌成平文本（ref_bank 中该题 stem 无选项内容）。由详解「$\frac{1}{\mathrm{e}}&gt;\frac{\ln3}{3}&gt;\frac{\ln\pi}{\pi}&gt;\frac{\ln15}{15}$，故选 B」还原四个选项。数值校验：$\frac{\ln3}{3}\approx0.36620$、$\frac1{\mathrm{e}}\approx0.36788$、$\frac{\ln\pi}{\pi}\approx0.36438$、$\frac{\ln15}{15}\approx0.18054$，与答案 B 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>M-H0220</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>M-T-041(函数与导数 / 幂指对比较大小 · 构造函数：lnx/x型函数)</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>下列命题为真命题的个数是（　　）
+① $\ln3&lt;\sqrt{3}\ln2$； ② $\ln\pi&lt;\dfrac{\pi}{\mathrm{e}}$； ③ $2^{\sqrt{15}}&lt;15$； ④ $3\mathrm{e}\ln2&lt;4\sqrt{2}$</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>$1$ 个</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>$2$ 个</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>$3$ 个</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>$4$ 个</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t>设 $f(x)=\dfrac{\ln x}{x}$，则 $f'(x)=\dfrac{1-\ln x}{x^{2}}$．
+当 $0&lt;x&lt;\mathrm{e}$ 时 $f'(x)&gt;0$，$f$ 递增；当 $x&gt;\mathrm{e}$ 时 $f'(x)&lt;0$，$f$ 递减，当 $x=\mathrm{e}$ 时 $f$ 取最大值 $\dfrac{1}{\mathrm{e}}$．
+① $\ln3&lt;\sqrt3\ln2\iff\dfrac{\ln3}{\sqrt3}&lt;\ln2\iff\dfrac{\ln\sqrt3}{\sqrt3}&lt;\dfrac{\ln2}{2}\iff f(\sqrt3)&lt;f(2)$；
+由 $\sqrt3&lt;2&lt;\mathrm{e}$ 且 $f$ 在 $(0,\mathrm{e})$ 上递增，得 $f(\sqrt3)&lt;f(2)$，故①为真；
+② $\ln\pi&lt;\dfrac{\pi}{\mathrm{e}}\iff\dfrac{\ln\pi}{\pi}&lt;\dfrac{1}{\mathrm{e}}\iff f(\pi)&lt;f(\mathrm{e})$；
+由 $\mathrm{e}&lt;\pi$ 且 $f$ 在 $(\mathrm{e},+\infty)$ 上递减，得 $f(\pi)&lt;f(\mathrm{e})$，故②为真；
+③ $2^{\sqrt{15}}&lt;15\iff\sqrt{15}\ln2&lt;\ln15\iff\dfrac{\ln2}{\sqrt{15}}&lt;\dfrac{\ln15}{15}$，由 $f(16)&lt;f(15)$（$15&lt;16$ 且均在 $(\mathrm{e},+\infty)$ 上）得 $\dfrac{\ln2}{4}&lt;\dfrac{\ln15}{15}$，而 $\dfrac{\ln2}{\sqrt{15}}&lt;\dfrac{\ln2}{4}$（因 $\sqrt{15}&lt;4$），故③为真；
+④ $3\mathrm{e}\ln2&lt;4\sqrt2\iff\dfrac{\ln8}{4\sqrt2}&lt;\dfrac{1}{\mathrm{e}}$，而 $\dfrac{\ln8}{4\sqrt2}=\dfrac{\ln\sqrt8}{\sqrt8}\cdot\dfrac{\sqrt8}{4\sqrt2}\cdot 2&lt;\dfrac{1}{\mathrm{e}}$（用到 $f(x)\leqslant\dfrac1{\mathrm{e}}$），故④为真．
+**原书判定②为假、共 $3$ 个真命题，故选 C。**</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S220" t="n">
+        <v>5</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-041-V3</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V220" s="2" t="inlineStr">
+        <is>
+          <t>★ **本题存在原书答案争议，按原书 C 录入，标记为存疑。**
+数值验证四个命题分别为：
+① $\ln3\approx1.098612&lt;\sqrt3\ln2\approx1.200566$ → 真；
+② $\ln\pi\approx1.144730&lt;\pi/\mathrm{e}\approx1.155727$ → **真**；
+③ $2^{\sqrt{15}}\approx14.6516&lt;15$ → 真；
+④ $3\mathrm{e}\ln2\approx5.652508&lt;4\sqrt2\approx5.656854$ → 真．
+四个命题数值上全部成立，真命题应为 $4$ 个（选 D），与原书答案 C（$3$ 个）矛盾。
+原书详解判②为假，依据是「由 $\mathrm{e}&lt;\pi$ 可得 $f(\mathrm{e})&lt;f(\pi)$」，但 $f(\mathrm{e})=\frac1{\mathrm{e}}$ 是 $f$ 的最大值，必有 $f(\mathrm{e})&gt;f(\pi)$，**该处不等号方向写反了**，据此得出的「②为假」不成立。
+另注：详解中「由 $f(16)&lt;f(15)$ 可得 $f(2)&lt;f(15)$」同样写反（实际 $f(2)\approx0.3466&gt;f(15)\approx0.1805$）。
+因③的具体形式（$2^{\sqrt{15}}$ 的上标含矢量绘制的根号）无法从破碎文本百分百确认（若实为 $2^{15}&lt;15$ 则③为假，此时真命题恰为 $3$ 个、答案 C 自洽），故此处按原书答案 C 录入，留待复核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>M-H0221</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>M-T-041(函数与导数 / 幂指对比较大小 · 构造函数：lnx/x型函数)</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>（$2022$·天津三中三模）设 $a=\dfrac{3(2-\ln3)}{\mathrm{e}^{2}}$，$b=\dfrac{1}{\mathrm{e}}$，$c=\dfrac{\ln2}{2}$，则 $a,b,c$ 的大小顺序为（　　）</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>$a&lt;c&lt;b$</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>$c&lt;a&lt;b$</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>$b&lt;a&lt;c$</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>设 $f(x)=\dfrac{\ln x}{x}$，则 $f'(x)=\dfrac{1-\ln x}{x^{2}}$．
+当 $0&lt;x&lt;\mathrm{e}$ 时 $f'(x)&gt;0$，$f$ 递增；当 $x&gt;\mathrm{e}$ 时 $f'(x)&lt;0$，$f$ 递减．
+化形：$a=\dfrac{3(2-\ln3)}{\mathrm{e}^{2}}=\dfrac{3(\ln\mathrm{e}^{2}-\ln3)}{\mathrm{e}^{2}}=\dfrac{3\ln\frac{\mathrm{e}^{2}}{3}}{\mathrm{e}^{2}}=\dfrac{\ln\frac{\mathrm{e}^{2}}{3}}{\frac{\mathrm{e}^{2}}{3}}=f\!\left(\dfrac{\mathrm{e}^{2}}{3}\right)$；
+$b=\dfrac{1}{\mathrm{e}}=f(\mathrm{e})$，$c=\dfrac{\ln2}{2}=f(2)$．
+由 $2&lt;\dfrac{\mathrm{e}^{2}}{3}&lt;\mathrm{e}$（$\dfrac{\mathrm{e}^{2}}{3}\approx2.463$），且 $f$ 在 $(0,\mathrm{e})$ 上递增，得 $f(2)&lt;f\!\left(\dfrac{\mathrm{e}^{2}}{3}\right)&lt;f(\mathrm{e})$．
+故 $c&lt;a&lt;b$，故选 B．</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S221" t="n">
+        <v>5</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-041-V4</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V221" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = 3 2 - ln3  e2 」，分子是 $3(2-\ln3)$ 还是 $\frac32-\ln3$ 无法分辨。由详解「$a=f(\frac{\mathrm{e}^2}{3})=\frac{3\ln(\mathrm{e}^2/3)}{\mathrm{e}^2}$」确认为 $3(2-\ln3)$：$\ln(\mathrm{e}^2/3)=2-\ln3$，乘 $3$ 再除 $\mathrm{e}^2$ 正好还原。数值校验：$a\approx0.36597$、$b\approx0.36788$、$c\approx0.34657$，与答案 B 吻合。注意与 V5 的区别：V4 的 $c=\frac{\ln2}{2}$，V5 的 $c=\frac{\ln3}{3}$，其余相同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>M-H0222</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>M-T-041(函数与导数 / 幂指对比较大小 · 构造函数：lnx/x型函数)</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>（$2022$·江苏·扬州中学高二期中）$a=\dfrac{3(2-\ln3)}{\mathrm{e}^{2}}$，$b=\dfrac{1}{\mathrm{e}}$，$c=\dfrac{\ln3}{3}$，则 $a,b,c$ 的大小顺序为（　　）</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>$a&lt;c&lt;b$</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>$c&lt;a&lt;b$</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>$b&lt;a&lt;c$</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>设 $f(x)=\dfrac{\ln x}{x}$，则 $f'(x)=\dfrac{1-\ln x}{x^{2}}$，$f$ 在 $(0,\mathrm{e})$ 上递增、在 $(\mathrm{e},+\infty)$ 上递减，$x=\mathrm{e}$ 时取最大值 $\dfrac{1}{\mathrm{e}}$．
+同 V4 化形得 $a=f\!\left(\dfrac{\mathrm{e}^{2}}{3}\right)$，$b=f(\mathrm{e})=\dfrac{1}{\mathrm{e}}$，$c=f(3)=\dfrac{\ln3}{3}$．
+因 $\dfrac{\mathrm{e}^{2}}{3}\approx2.463&lt;\mathrm{e}&lt;3$，且 $b=f(\mathrm{e})$ 为最大值，故 $b$ 最大．
+比较 $a$ 与 $c$：设 $f(x)=t$ 有两个解 $x_{1}&lt;x_{2}$，则 $x_{1}&lt;\mathrm{e}&lt;x_{2}$．构造 $g(x)=\ln x-\dfrac{2(x-1)}{x+1}$（$x&gt;1$），由导数可得 $g(x)&gt;0$，从而 $\dfrac{\ln x_{2}-\ln x_{1}}{x_{2}-x_{1}}&gt;\dfrac{2}{x_{1}+x_{2}}$，取 $x_{1}=\dfrac{\mathrm{e}^{2}}{3}$、$x_{2}=3$ 即可判得 $f\!\left(\dfrac{\mathrm{e}^{2}}{3}\right)&lt;f(3)$，即 $a&lt;c$．
+综上 $a&lt;c&lt;b$，故选 A．</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S222" t="n">
+        <v>5</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-041-V5</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V222" s="2" t="inlineStr">
+        <is>
+          <t>★ 与 V4 同型，仅 $c$ 不同（V4 是 $\frac{\ln2}{2}$，本题是 $\frac{\ln3}{3}$），但答案从 B 变为 A —— 因为 $f(3)&gt;f(2)$（$2&lt;\mathrm{e}&lt;3$，且 $3$ 离 $\mathrm{e}$ 更近）。提取文本作「a = 3(2 - ln3) e2 ,b = 1 e ,c = ln3 3 」，分数全塌。由详解「$a=f(\frac{\mathrm{e}^2}{3})$、$b=f(\mathrm{e})$、$c=f(3)$」还原。数值校验：$a\approx0.365969$、$c\approx0.366204$、$b\approx0.367879$，三者极接近（$a$ 与 $c$ 仅差 $0.00024$），普通估值无法分辨，必须靠详解给出的 $g(x)=\ln x-\frac{2(x-1)}{x+1}$ 技巧，与答案 A 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>M-H0223</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>M-T-042(函数与导数 / 幂指对比较大小 · 构造函数综合)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>已知实数 $a$、$b$，满足 $a=\log_{5}6+\log_{6}25$，$3^{a}+4^{a}=5^{b}$，则关于 $a$、$b$ 下列判断正确的是（　　）</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;2$</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>$b&lt;a&lt;2$</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>$2&lt;a&lt;b$</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>$2&lt;b&lt;a$</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr">
+        <is>
+          <t>先证 $a&gt;2$：令 $t=\log_{5}6&gt;1$，则 $\log_{6}25=\log_{6}5^{2}=2\log_{6}5=\dfrac{2}{t}$，
+于是 $a=t+\dfrac{2}{t}\geqslant2\sqrt{t\cdot\dfrac{2}{t}}=2\sqrt2&gt;2$．
+再证 $a&gt;b$：构造 $f(x)=\left(\dfrac{3}{5}\right)^{x}+\left(\dfrac{4}{5}\right)^{x}-1$，$x\in\mathbb R$．
+因 $0&lt;\dfrac35&lt;1$、$0&lt;\dfrac45&lt;1$，故 $f(x)$ 在 $\mathbb R$ 上单调递减，且 $f(2)=\dfrac{9}{25}+\dfrac{16}{25}-1=0$．
+由 $a&gt;2$ 得 $f(a)&lt;f(2)=0$，即 $\left(\dfrac35\right)^{a}+\left(\dfrac45\right)^{a}&lt;1$，亦即 $3^{a}+4^{a}&lt;5^{a}$．
+又 $3^{a}+4^{a}=5^{b}$，故 $5^{b}&lt;5^{a}$，得 $b&lt;a$．
+最后证 $b&gt;2$：由 $a&gt;2$ 得 $5^{b}=3^{a}+4^{a}&gt;3^{2}+4^{2}=25=5^{2}$，故 $b&gt;2$．
+综上 $a&gt;b&gt;2$，即 $2&lt;b&lt;a$，故选 D．</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S223" t="n">
+        <v>5</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-042-E1</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V223" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = log6 + log25，3a+ 4a= 5b」，底数与真数全部塌成同行，$\log_{6}25$ 与 $\log_{26}25$ 无法区分。由详解「$a=\log_56+\log_36 25=\log_56+2\log_65=t+\frac2t&gt;2\sqrt2$」确认为 $\log_{5}6+\log_{6}25$。数值校验：$a\approx2.90977$、由 $3^a+4^a=5^b$ 得 $b\approx2.72987$，$a&gt;b&gt;2$ 与答案 D 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>M-H0224</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>M-T-042(函数与导数 / 幂指对比较大小 · 构造函数综合)</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>若 $2020^{x}-2020^{y}&lt;2021^{-x}-2021^{-y}$（$x,y\in\mathbb R$），则（　　）</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>$\ln(y-x+1)&gt;0$</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>$\ln(y-x+1)&lt;0$</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>$\ln|x-y|&gt;0$</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>$\ln|x-y|&lt;0$</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>由 $2020^{x}-2020^{y}&lt;2021^{-x}-2021^{-y}$ 移项得
+$2020^{x}-2021^{-x}&lt;2020^{y}-2021^{-y}$．
+令 $f(x)=2020^{x}-2021^{-x}$．因 $y=2020^{x}$ 在 $\mathbb R$ 上递增、$y=2021^{-x}=\left(\dfrac{1}{2021}\right)^{x}$ 在 $\mathbb R$ 上递减，故 $-2021^{-x}$ 递增，从而 $f(x)$ 在 $\mathbb R$ 上单调递增．
+由 $f(x)&lt;f(y)$ 得 $x&lt;y$，即 $y-x&gt;0$，于是 $y-x+1&gt;1$，故 $\ln(y-x+1)&gt;\ln1=0$，A 正确、B 错误．
+又 $|x-y|=y-x$ 与 $1$ 的大小关系无法确定（例如 $x=0,y=0.5$ 时 $|x-y|=0.5&lt;1$；$x=0,y=3$ 时 $|x-y|=3&gt;1$），故 C、D 均无法确定．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S224" t="n">
+        <v>5</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-042-V1</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V224" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「2020x- 2020y&lt; 2021-x- 2021-y」，指数全塌成同行。由详解「令 $f(x)=2020^x-2021^{-x}$，则 $f(x)$ 在 $\mathbb R$ 上单调递增，且 $f(x)&lt;f(y)$，∴$x&lt;y$」还原。关键是把 $-2021^{-x}$ 与 $-2020^{y}$ 交叉移项 —— 不移项则无法构造函数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>M-H0225</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>M-T-042(函数与导数 / 幂指对比较大小 · 构造函数综合)</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a+2^{a}=2$，$b+3^{b}=2$，则 $b\lg a$ 与 $a\lg b$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>$b\lg a&lt;a\lg b$</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>$b\lg a=a\lg b$</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>$b\lg a&gt;a\lg b$</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>不确定</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>令 $f(x)=x+2^{x}$，$g(x)=x+3^{x}$，二者在 $\mathbb R$ 上均单调递增．
+当 $x&gt;0$ 时 $3^{x}&gt;2^{x}$，故 $g(x)&gt;f(x)$；当 $x&lt;0$ 时 $3^{x}&lt;2^{x}$，故 $g(x)&lt;f(x)$．
+由 $f(a)=2$、$g(b)=2$ 且 $g(0)=f(0)=1&lt;2$，$f(1)=3&gt;2$、$g(1)=4&gt;2$，知 $a,b\in(0,1)$；又 $g(a)&gt;f(a)=2=g(b)$，故 $a&gt;b$，即 $0&lt;b&lt;a&lt;1$．
+于是 $a^{b}&gt;b^{b}$（底大指数同正）、$b^{b}&gt;b^{a}$（底 $b\in(0,1)$、指数小者值大），故 $a^{b}&gt;b^{a}$．
+两边取常用对数：$\lg\left(a^{b}\right)&gt;\lg\left(b^{a}\right)$，即 $b\lg a&gt;a\lg b$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S225" t="n">
+        <v>5</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-042-V2</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V225" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「blga 与algb 的大小关系」，$\lg$ 与 $a$、$b$ 的从属关系不清。由详解「由 $a^b&gt;b^a$，得 $\lg(a^b)&gt;\lg(b^a)$，即 $b\lg a&gt;a\lg b$」确认为 $b\lg a$ 与 $a\lg b$。数值校验：解 $a+2^a=2$ 得 $a\approx0.54300$，解 $b+3^b=2$ 得 $b\approx0.41769$；$b\lg a\approx-0.110772$、$a\lg b\approx-0.205874$，$b\lg a&gt;a\lg b$ 与答案 C 一致。注意两值均为负，比较时容易看错方向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>M-H0226</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>M-T-043(函数与导数 / 幂指对比较大小 · 放缩(难点))</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>若 $a=\log_{2}3$，$b=\log_{3}4$，$c=\log_{4}5$，则 $a,b,c$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>$b&lt;c&lt;a$</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>$b&lt;a&lt;c$</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>$c&lt;b&lt;a$</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>由 $\log_{2}3&gt;\log_{2}2=1$、$\log_{3}4&gt;\log_{3}3=1$、$\log_{4}5&gt;\log_{4}4=1$，知 $a,b,c$ 均大于 $1$．
+比较 $a$ 与 $c$：$c=\log_{4}5=\log_{2^{2}}5=\dfrac{1}{2}\log_{2}5=\log_{2}\sqrt5$，而 $a=\log_{2}3&gt;\log_{2}\sqrt5$（因 $3&gt;\sqrt5$），故 $a&gt;c&gt;1$．
+比较 $a$ 与 $b$：$a=\log_{2}3&gt;\log_{2}2\sqrt2=\dfrac32$，$b=\log_{3}4&lt;\log_{3}3\sqrt3=\dfrac32$，故 $a&gt;\dfrac32&gt;b&gt;1$．
+比较 $b$ 与 $c$：因 $4^{4}=256&gt;243=3^{5}$，故 $4\log_{3}4=\log_{3}4^{4}&gt;\log_{3}3^{5}=5$，即 $b&gt;\dfrac54$；
+因 $4^{5}=1024&gt;625=5^{4}$，故 $4\log_{4}5=\log_{4}5^{4}&lt;\log_{4}4^{5}=5$，即 $c&lt;\dfrac54$．
+综上 $a&gt;\dfrac32&gt;b&gt;\dfrac54&gt;c&gt;1$，即 $c&lt;b&lt;a$，故选 D．</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S226" t="n">
+        <v>5</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-043-E1</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V226" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = log3，b = log4，c = log5」，底数全丢，与 $\log_23$、$\log_34$、$\log_45$ 无法区分。由详解「$c=\log_45=\frac12\log_25=\log_2\sqrt5$，而 $a=\log_23&gt;\log_2\sqrt5$」与「$a&gt;\frac32&gt;b$、$b&gt;\frac54&gt;c$」三段放缩确认。数值校验：$a=\log_23\approx1.58496$、$b=\log_34\approx1.26186$、$c=\log_45\approx1.16096$，与答案 D 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>M-H0227</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>M-T-043(函数与导数 / 幂指对比较大小 · 放缩(难点))</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>设 $a=\log_{2019}2020$，$b=\log_{2020}2019$，$c=2019^{\frac{1}{2000}}$，则 $a,b,c$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>$a&gt;c&gt;b$</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>$c&gt;b&gt;a$</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>由 $\log_{2019}2020&gt;\log_{2019}2019=1$、$\log_{2019}2020&lt;\log_{2019}2019^{2}=2$，得 $1&lt;a&lt;2$；
+由 $\log_{2020}2019&lt;\log_{2020}2020=1$，得 $b&lt;1$；
+由 $c=2019^{\frac{1}{2000}}&gt;2019^{0}=1$，得 $c&gt;1$．
+故 $b$ 最小，只需比较 $a$ 与 $c$：
+$a=\log_{2019}2020=\dfrac{\ln2020}{\ln2019}=1+\dfrac{\ln\frac{2020}{2019}}{\ln2019}\approx1+\dfrac{0.000495}{7.610}\approx1.000065$；
+$c=2019^{\frac{1}{2000}}=\mathrm{e}^{\frac{\ln2019}{2000}}=\mathrm{e}^{0.003805}\approx1.00381$．
+故 $c&gt;a&gt;b$，故选 C．</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S227" t="n">
+        <v>5</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-043-V1</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V227" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「c = 20191 a,b,c / 2000」，指数 $\frac{1}{2000}$ 被拆成两行，极易误读成 $2019\cdot\frac{1}{2000}$ 或 $2019^{1}$。由详解「$c=2019^{\frac1{2000}}&gt;2019^0=1$」确认为分数指数。数值校验：$a\approx1.000065$、$b\approx0.999935$、$c\approx1.003812$，$c&gt;a&gt;b$ 与答案 C 一致。注意 $a$ 与 $1$ 仅差 $6.5\times10^{-5}$，靠估算很容易判错方向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>M-H0228</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>M-T-043(函数与导数 / 幂指对比较大小 · 放缩(难点))</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>设 $a=\log_{4}3$，$b=\log_{5}2$，$c=\log_{8}5$，则（　　）</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>$b&lt;c&lt;a$</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>$b&lt;a&lt;c$</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>$c&lt;a&lt;b$</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>比较 $a$ 与 $c$：化同底 $64=4^{3}=8^{2}$，
+$a=\log_{4}3=\log_{4^{3}}3^{3}=\log_{64}27$，$c=\log_{8}5=\log_{8^{2}}5^{2}=\log_{64}25$．
+由 $27&gt;25$ 得 $\log_{64}27&gt;\log_{64}25$，即 $a&gt;c$．
+比较 $b$ 与 $c$：$b=\log_{5}2&lt;\log_{5}\sqrt5=\dfrac12$，$c=\log_{8}5&gt;\log_{8}\sqrt8=\dfrac12$，故 $b&lt;\dfrac12&lt;c$．
+综上 $b&lt;c&lt;a$，故选 B．</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S228" t="n">
+        <v>5</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-043-V2</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V228" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = log3，b = log2，c = log5」，三个底数全丢，与 $\log_43$、$\log_52$、$\log_85$ 无法区分。由详解「$a=\log_43=\log_{64}27$、$c=\log_85=\log_{64}25$」确认底数为 $4,5,8$。数值校验：$a\approx0.79248$、$b\approx0.43068$、$c\approx0.77398$，与答案 B 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>M-H0229</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>M-T-043(函数与导数 / 幂指对比较大小 · 放缩(难点))</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a=2^{\sqrt3}$，$b=\dfrac52$，$c=\log_{2}5$，$d=2\sqrt2$，则下列大小关系正确的为（　　）</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;d&gt;b$</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>$a&gt;c&gt;d&gt;b$</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>$a&gt;d&gt;c&gt;b$</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>$a&gt;d&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>$a=2^{\sqrt3}$，$d=2\sqrt2=2^{\frac32}$．由 $\sqrt3\approx1.732&gt;\dfrac32=1.5$ 且 $y=2^{x}$ 递增，得 $a&gt;d$．
+$d=2\sqrt2=\sqrt8$，$b=\dfrac52=\sqrt{\dfrac{25}{4}}$．由 $8&gt;\dfrac{25}{4}=6.25$ 得 $d&gt;b$．
+$b=\dfrac52=\log_{2}2^{\frac52}=\log_{2}\sqrt{32}$，$c=\log_{2}5=\log_{2}\sqrt{25}$．由 $\sqrt{32}&gt;\sqrt{25}$ 且 $y=\log_{2}x$ 递增，得 $b&gt;c$．
+综上 $a&gt;d&gt;b&gt;c$，故选 D．</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S229" t="n">
+        <v>5</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-043-V3</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V229" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = 2 3，b = ，c = log5，d = 2 2」，$2^{\sqrt3}$ 的指数、$\frac52$、$2\sqrt2$ 的分数与根号全部塌成平文本。由详解「$d=2\sqrt2=2^{\frac32}&lt;2^{\sqrt3}=a$」「$d=2\sqrt2=\sqrt8&gt;\sqrt{\frac{25}4}=\frac52=b$」「$b=\frac52=\log_2\sqrt{32}&gt;\log_2\sqrt{25}=\log_25=c$」三段确认四个量。数值校验：$a\approx3.32200$、$d\approx2.82843$、$b=2.5$、$c\approx2.32193$，$a&gt;d&gt;b&gt;c$ 与答案 D 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>M-H0230</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>M-T-044(函数与导数 / 幂指对比较大小 · 函数奇偶性和单调性等综合)</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>已知 $f(x)$ 为 $\mathbb R$ 上的奇函数，$g(x)=xf(x)$，若 $g(x)$ 在区间 $(-\infty,0)$ 上单调递减．若 $a=g(2\pi)$，$b=g\!\left(2\sqrt3\right)$，$c=g(1)$，则 $a,b,c$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>$c&lt;b&lt;a$</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>$b&lt;a&lt;c$</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>$b&lt;c&lt;a$</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>因 $f(x)$ 为奇函数，有 $f(-x)=-f(x)$，于是
+$g(-x)=(-x)f(-x)=(-x)\bigl[-f(x)\bigr]=xf(x)=g(x)$，故 $g(x)$ 为偶函数．
+又 $g(x)$ 在 $(-\infty,0)$ 上单调递减，由偶函数的对称性知 $g(x)$ 在 $(0,+\infty)$ 上单调递增．
+由 $2\pi\approx6.283&gt;2\sqrt3\approx3.464&gt;1$，得
+$g(2\pi)&gt;g\!\left(2\sqrt3\right)&gt;g(1)$，即 $a&gt;b&gt;c$，亦即 $c&lt;b&lt;a$．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S230" t="n">
+        <v>5</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-044-E1</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V230" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「b = g (2 3)」，$2\sqrt3$ 的根号丢失，易误读成 $g(23)$ 或 $g(2^3)$。由详解「又 $2\pi&gt;2\sqrt3&gt;1$」确认为 $2\sqrt3$。数值校验：$2\pi\approx6.2832$、$2\sqrt3\approx3.4641$、$1$，顺序与答案 B 一致。**关键陷阱**：偶函数在 $(-\infty,0)$ 递减则在 $(0,+\infty)$ 递增（单调性相反），若照搬「递减」会得出完全相反的结论。</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>M-H0231</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>M-T-044(函数与导数 / 幂指对比较大小 · 函数奇偶性和单调性等综合)</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x-3^{-x}$，若 $a=f\!\left(3^{0.2}\right)$，$b=f\!\left(0.2^{3}\right)$，$c=f\!\left(\log_{0.2}3\right)$，则 $a,b,c$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>$b&gt;a&gt;c$</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>$c&gt;b&gt;a$</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=1+3^{-x}\ln3&gt;0$ 恒成立，故 $f(x)$ 在 $\mathbb R$ 上单调递增．
+比较自变量：
+由 $3^{1}&gt;3^{0.2}&gt;3^{0}=1$，得 $3^{0.2}&gt;1$；
+由 $0&lt;0.2^{3}&lt;0.2^{0}=1$，得 $0&lt;0.2^{3}&lt;1$；
+由底数 $0.2\in(0,1)$，对数函数递减，且 $3&gt;1$，得 $\log_{0.2}3&lt;\log_{0.2}1=0$．
+故 $3^{0.2}&gt;0.2^{3}&gt;\log_{0.2}3$．
+由 $f$ 递增，得 $f\!\left(3^{0.2}\right)&gt;f\!\left(0.2^{3}\right)&gt;f\!\left(\log_{0.2}3\right)$，即 $a&gt;b&gt;c$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S231" t="n">
+        <v>5</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-044-V1</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V231" s="2" t="inlineStr">
+        <is>
+          <t>★ **函数形式系反推确定，需留意。**提取文本作「f (x)= x -3 - x 」，分数/指数全部塌成平文本，仅凭文本无法确定 $f$ 究竟是什么。
+详解给出两条线索：①「函数在 $(-\infty,3]$ 上单调递增」；②答案 A（$a&gt;b&gt;c$）。对四个候选逐一数值验证（自变量 $3^{0.2}\approx1.24573$、$0.2^{3}=0.008$、$\log_{0.2}3\approx-0.68261$）：
+| 候选 | $a$ | $b$ | $c$ | 顺序 |
+|---|---|---|---|---|
+| $x-3^{-x}$ | $0.9913$ | $-0.9832$ | $-2.7994$ | **$a&gt;b&gt;c$ ✓** |
+| $x^{3}-x$ | $0.6875$ | $-0.0080$ | $0.3645$ | $a&gt;c&gt;b$ ✗ |
+| $3^{x}-x$ | $2.6840$ | $1.0008$ | $1.1550$ | $a&gt;c&gt;b$ ✗ |
+| $x^{-3}-x$ | $-0.7284$ | $1.95\times10^{6}$ | $-2.4614$ | $b&gt;a&gt;c$ ✗ |
+**只有 $f(x)=x-3^{-x}$ 同时满足递增性与答案 A**，据此录入。该函数 $f'(x)=1+3^{-x}\ln3&gt;0$ 确实全程递增，与详解描述吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>M-H0232</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>M-T-044(函数与导数 / 幂指对比较大小 · 函数奇偶性和单调性等综合)</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 满足 $f(x)+f(-x)=0$，且当 $x\in(-\infty,0)$ 时，$f(x)+xf'(x)&lt;0$ 成立，若 $a=2^{0.6}\cdot f\!\left(2^{0.6}\right)$，$b=(\ln2)\cdot f(\ln2)$，$c=\left(\log_{\frac12}8\right)\cdot f\!\left(\log_{\frac12}8\right)$，则 $a,b,c$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>$c&gt;b&gt;a$</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>$a&gt;c&gt;b$</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(x)+f(-x)=0$ 且 $f$ 在 $\mathbb R$ 上连续，知 $f$ 为奇函数．
+令 $g(x)=x\cdot f(x)$，则
+$g(-x)=(-x)\cdot f(-x)=(-x)\cdot\bigl[-f(x)\bigr]=x\cdot f(x)=g(x)$，故 $g(x)$ 为偶函数．
+又 $g'(x)=f(x)+x\cdot f'(x)$，由已知当 $x\in(-\infty,0)$ 时 $g'(x)&lt;0$，故 $g(x)$ 在 $(-\infty,0)$ 上单调递减；
+由 $g$ 连续且为偶函数，得 $g(x)$ 在 $(0,+\infty)$ 上单调递增．
+于是 $a=g\!\left(2^{0.6}\right)$，$b=g(\ln2)$，$c=g\!\left(\log_{\frac12}8\right)=g(-3)=g(3)$（偶函数）．
+由 $2^{0.6}\approx1.516&gt;1$、$0&lt;\ln2\approx0.693&lt;1$、$-\log_{\frac12}8=\log_{2}8=3$，得 $3&gt;2^{0.6}&gt;\ln2&gt;0$．
+由 $g$ 在 $(0,+\infty)$ 上递增，得 $g(3)&gt;g\!\left(2^{0.6}\right)&gt;g(\ln2)$，即 $c&gt;a&gt;b$．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S232" t="n">
+        <v>5</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-044-V2</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V232" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = (20.6)⋅f (20.6)，b = (ln2) ⋅f(ln2)，c = (log)⋅f (log)」，$2^{0.6}$ 的指数与 $\log_{\frac12}8$ 的底数、真数全丢，第三个式子整个塌成「(log)⋅f (log)」。由详解「$c=g(\log_{\frac12}8)=g(-\log_2 8)=g(-3)$」与「$\ln2&lt;1&lt;2^{0.6}&lt;-\log_{\frac12}8=3$」还原。数值校验：自变量 $|{-3}|=3&gt;2^{0.6}\approx1.51572&gt;\ln2\approx0.69315$，与答案 D 一致。**关键**：$c$ 的自变量是负数，必须先由偶函数化为 $g(3)$ 再比较。</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>M-H0233</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>M-T-044(函数与导数 / 幂指对比较大小 · 函数奇偶性和单调性等综合)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>已知 $f(x)=f(2-x)$，$x\in\mathbb R$，当 $x\in[1,+\infty)$ 时，$f(x)$ 为增函数．设 $a=f(1)$，$b=f(2)$，$c=f(-1)$，则 $a,b,c$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>$a&gt;b&gt;c$</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>$b&gt;a&gt;c$</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>$c&gt;a&gt;b$</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>$c&gt;b&gt;a$</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(x)=f(2-x)$，令 $x=-1$ 得 $f(-1)=f\bigl(2-(-1)\bigr)=f(3)$，即 $c=f(3)$．
+（一般地，$f(x)=f(2-x)$ 表明 $f$ 的图象关于直线 $x=\dfrac{x+(2-x)}{2}=1$ 对称．）
+因 $1&lt;2&lt;3$，且 $f(x)$ 在 $[1,+\infty)$ 上为增函数，得
+$f(3)&gt;f(2)&gt;f(1)$，即 $c&gt;b&gt;a$．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S233" t="n">
+        <v>5</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-044-V3</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V233" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f x  = f 2 - x  ，x ∈1,+∞  时，f x  为增函数」，函数记号的括号、区间端点全部丢失，与「$f(x)=f(2)-x$」或「$f(x)=f(2-x)$」无法区分。由详解「∵$f(x)=f(2-x)$，∴$f(-1)=f(3)$」确认为 $f(2-x)$。数值关系：$1&lt;2&lt;3$ 且 $f$ 在 $[1,+\infty)$ 递增，故 $f(3)&gt;f(2)&gt;f(1)$，与答案 D 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>M-H0234</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>M-T-045(函数与导数 / 幂指对比较大小 · 三角函数值比较大小  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>三个数 $\cos\dfrac32$，$\sin\dfrac{1}{10}$，$\sin\dfrac74$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>$\cos\dfrac32&gt;\sin\dfrac{1}{10}&gt;\sin\dfrac74$</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>$\cos\dfrac32&gt;\sin\dfrac74&gt;\sin\dfrac{1}{10}$</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>$\cos\dfrac32&lt;\sin\dfrac{1}{10}&lt;\sin\dfrac74$</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>$\sin\dfrac74&gt;\cos\dfrac32&gt;\sin\dfrac{1}{10}$</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>化为正弦：$\cos\dfrac32=\sin\left(\dfrac{\pi}{2}-\dfrac32\right)$，$\sin\dfrac74=\sin\left(\pi-\dfrac74\right)$．
+估算三个角：
+$\dfrac{\pi}{2}-\dfrac32\approx1.5708-1.5=0.0708$，$\dfrac{1}{10}=0.1$，$\pi-\dfrac74\approx3.1416-1.75=1.3916$．
+由 $0&lt;0.0708&lt;0.1&lt;1.3916&lt;\dfrac{\pi}{2}$，且 $y=\sin x$ 在 $\left[0,\dfrac{\pi}{2}\right]$ 上单调递增，得
+$\sin\left(\dfrac{\pi}{2}-\dfrac32\right)&lt;\sin\dfrac{1}{10}&lt;\sin\left(\pi-\dfrac74\right)$，即 $\cos\dfrac32&lt;\sin\dfrac{1}{10}&lt;\sin\dfrac74$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S234" t="n">
+        <v>5</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-045-E1</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V234" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「三个数cos 3 2 ，sin 1 10 ，sin 7 4 的大小关系」，三个分数全部塌成「3 2」「1 10」「7 4」，与 $\frac32$、$\frac{1}{10}$、$\frac74$ 无法区分。由详解「$\cos\frac32=\sin(\frac{\pi}{2}-\frac32)$，$\sin\frac74=\sin(\pi-\frac74)$」「$\frac{\pi}{2}-\frac32\approx0.071$、$\frac{1}{10}=0.1$、$\pi-\frac74\approx1.39$」还原。数值校验：$\cos1.5\approx0.070737$、$\sin0.1\approx0.099833$、$\sin1.75\approx0.983986$，与答案 C 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>M-H0235</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>M-T-045(函数与导数 / 幂指对比较大小 · 三角函数值比较大小  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a=\sin\dfrac45$，$b=\dfrac43\sin\dfrac34$，$c=\dfrac43\cos\dfrac34$，则 $a,b,c$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>$a&lt;b&lt;c$</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>$b&lt;c&lt;a$</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>$a&lt;c&lt;b$</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>$b&lt;a&lt;c$</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>先比 $b,c$：由 $\dfrac34&lt;\dfrac{\pi}{4}$，且 $y=\sin x$ 在 $\left(0,\dfrac{\pi}{2}\right)$ 上递增、$y=\cos x$ 递减，得
+$\sin\dfrac34&lt;\sin\dfrac{\pi}{4}=\cos\dfrac{\pi}{4}&lt;\cos\dfrac34$，故 $b=\dfrac43\sin\dfrac34&lt;\dfrac43\cos\dfrac34=c$．
+再比 $a,b$：令 $f(x)=\dfrac{\sin x}{x}$，则 $f'(x)=\dfrac{x\cos x-\sin x}{x^{2}}$．
+当 $x\in\left(0,\dfrac{\pi}{2}\right)$ 时 $\tan x&gt;x$，即 $\sin x&gt;x\cos x$，故 $f'(x)&lt;0$，$f$ 在 $\left(0,\dfrac{\pi}{2}\right)$ 上递减．
+由 $\dfrac34&lt;\dfrac45$ 得 $f\!\left(\dfrac45\right)&lt;f\!\left(\dfrac34\right)$，即 $\dfrac{\sin\frac45}{\frac45}&lt;\dfrac{\sin\frac34}{\frac34}$，
+亦即 $\dfrac54\sin\dfrac45&lt;\dfrac43\sin\dfrac34=b$，于是 $a=\sin\dfrac45&lt;\dfrac45\,b&lt;b$．
+综上 $a&lt;b&lt;c$，故选 A．</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S235" t="n">
+        <v>5</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-045-V1</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V235" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a = sin 4 5 ,b = 4 3 sin 3 4 ,c = 4 3 cos 3 4 」，三个分数与系数全部塌成平文本。由详解「$\frac12=\sin\frac{\pi}{6}&lt;\sin\frac34&lt;\sin\frac{\pi}{4}=\cos\frac{\pi}{4}&lt;\cos\frac34$，所以 $b&lt;c$」与「构造 $f(x)=\frac{1}{x}\cdot\sin x$，$f$ 在 $[\frac34,1]$ 递减，$f(\frac45)&lt;f(\frac34)$」还原。数值校验：$a=\sin0.8\approx0.71736$、$b\approx0.90885$、$c\approx0.97559$，与答案 A 吻合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>M-H0236</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>M-T-045(函数与导数 / 幂指对比较大小 · 三角函数值比较大小  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>设 $x,y\in(0,\pi)$，若 $\sin(\sin x)=\cos(\cos y)$，则 $\cos(\sin x)$ 与 $\sin(\cos y)$ 的大小关系为（　　）</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>$\cos(\sin x)=\sin(\cos y)$</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>$\cos(\sin x)&gt;\sin(\cos y)$</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>$\cos(\sin x)&lt;\sin(\cos y)$</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>以上均不对</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P236" s="2" t="inlineStr">
+        <is>
+          <t>设 $\alpha=\sin x$，$\beta=\cos y$．因 $x,y\in(0,\pi)$，故 $\alpha\in(0,1]$，$\beta\in(-1,1)$．
+由 $\sin(\sin x)=\cos(\cos y)$ 得 $\sin\alpha=\cos\beta=\sin\left(\dfrac{\pi}{2}-\beta\right)$，而 $\dfrac{\pi}{2}-\beta\in\left(\dfrac{\pi}{2}-1,\dfrac{\pi}{2}+1\right)$．
+故 $\alpha=\dfrac{\pi}{2}-\beta$ 或 $\alpha=\pi-\left(\dfrac{\pi}{2}-\beta\right)=\dfrac{\pi}{2}+\beta$．
+**情形一**　$\alpha=\dfrac{\pi}{2}-\beta$：
+$\cos(\sin x)=\cos\alpha=\cos\left(\dfrac{\pi}{2}-\beta\right)=\sin\beta=\sin(\cos y)$，两者相等．
+**情形二**　$\alpha=\dfrac{\pi}{2}+\beta$：
+$\cos(\sin x)=\cos\alpha=\cos\left(\dfrac{\pi}{2}+\beta\right)=-\sin\beta$，而 $\sin(\cos y)=\sin\beta$，于是
+① $\beta\in(-1,0)$ 时，$-\sin\beta&gt;\sin\beta$，故 $\cos(\sin x)&gt;\sin(\cos y)$；
+② $\beta=0$ 时，$-\sin\beta=\sin\beta=0$，故 $\cos(\sin x)=\sin(\cos y)$；
+③ $\beta\in(0,1)$ 时，$-\sin\beta&lt;\sin\beta$，故 $\cos(\sin x)&lt;\sin(\cos y)$．
+三种结果都可能出现，故大小关系不确定，选 D．</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S236" t="n">
+        <v>5</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-045-V2</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V236" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「sin sinx  = cos cosy  ，则cos sinx  与 sin cosy  的大小关系」，函数记号的括号全部丢失，与 $\sin x\cdot\sin$ 之类的乘积形式无法区分。由详解「设 $\alpha=\sin x$，$\beta=\cos y$，$\sin\alpha=\cos\beta=\sin(\frac{\pi}{2}-\beta)$」确认为复合函数。详解明确列出三种情形（$&gt;$、$=$、$&lt;$ 均可能），故选 D。**这题的考点是分类讨论的完备性** —— 只解出 $\alpha=\frac{\pi}{2}-\beta$ 而漏掉 $\alpha=\frac{\pi}{2}+\beta$，就会错选 A。</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>M-H0237</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>幂指对比较大小</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>M-T-045(函数与导数 / 幂指对比较大小 · 三角函数值比较大小  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>$\sin3$，$\cos(\sin2)$，$\tan(\cos3)$ 的大小关系是（　　）</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>$\cos(\sin2)&gt;\sin3&gt;\tan(\cos3)$</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>$\cos(\sin2)&gt;\tan(\cos3)&gt;\sin3$</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>$\sin3&gt;\cos(\sin2)&gt;\tan(\cos3)$</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>$\tan(\cos3)&gt;\sin3&gt;\cos(\sin2)$</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P237" s="2" t="inlineStr">
+        <is>
+          <t>先判 $\tan(\cos3)$ 的符号：由 $\dfrac{\pi}{2}&lt;3&lt;\pi$ 得 $-1&lt;\cos3&lt;0$，故 $\tan(\cos3)&lt;0$．
+再化同名：由 $\dfrac{\pi}{2}&lt;2&lt;\dfrac{3\pi}{4}$ 得 $\dfrac{\sqrt2}{2}&lt;\sin2&lt;1$，于是
+$\cos(\sin2)=\sin\left(\dfrac{\pi}{2}-\sin2\right)$，$\sin3=\sin(\pi-3)$．
+比较三个角：
+$\pi-3\approx0.1416$，$\dfrac{\pi}{2}-\sin2\approx1.5708-0.9093=0.6615$，且 $\dfrac{\pi}{2}-1\approx0.5708$．
+由 $0&lt;\pi-3&lt;\dfrac{\pi}{2}-1&lt;\dfrac{\pi}{2}-\sin2&lt;\dfrac{\pi}{2}$，且 $y=\sin x$ 在 $\left[0,\dfrac{\pi}{2}\right]$ 上递增，得
+$\sin(\pi-3)&lt;\sin\left(\dfrac{\pi}{2}-\sin2\right)$，即 $\sin3&lt;\cos(\sin2)$．
+又 $\sin3=\sin(\pi-3)&gt;0&gt;\tan(\cos3)$，故
+$\tan(\cos3)&lt;0&lt;\sin3&lt;\cos(\sin2)$，即 $\cos(\sin2)&gt;\sin3&gt;\tan(\cos3)$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S237" t="n">
+        <v>5</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-045-V3</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>教辅录入-第14批</t>
+        </is>
+      </c>
+      <c r="V237" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「sin3，cos sin2  ，tan cos3  的大小关系」，复合函数的括号丢失。由详解「$\frac{\pi}{2}&lt;3&lt;\pi$，$-1&lt;\cos3&lt;0$，$\tan(\cos3)&lt;0$」「$\cos(\sin2)=\sin(\frac{\pi}{2}-\sin2)$，$\sin3=\sin(\pi-3)$」与「$0&lt;\frac{\pi}{2}-3&lt;\frac{\pi}{2}-1&lt;\frac{\pi}{2}-\sin2&lt;\frac{\pi}{2}$」还原。数值校验：$\cos(\sin2)\approx0.614300$、$\sin3\approx0.141120$、$\tan(\cos3)\approx-1.523652$，与答案 A 吻合。**关键**：$\tan(\cos3)$ 的自变量 $\cos3\in(-1,0)$ 是负数，这直接决定了它是三个数里唯一的负值、必定最小。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V237"/>
+  <dimension ref="A1:V249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23423,6 +23423,1282 @@
         </is>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>M-H0238</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>M-T-060(函数与导数 / 零点与图像交点 · “放大镜”函数的交点)</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 为偶函数，且当 $x&gt;0$ 时，$f(x)=\begin{cases}1-x, &amp; 0\leqslant x&lt;1,\\\dfrac13 f(x-1), &amp; x\geqslant1,\end{cases}$则当 $x\in(-2,2)$ 时，方程 $f(x)=\left(\dfrac13\right)^{|x|}$ 的根有几个？（　　）</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>$3$ 个</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>$5$ 个</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>$7$ 个</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>$9$ 个</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P238" s="2" t="inlineStr">
+        <is>
+          <t>由题意，当 $x&gt;0$ 时
+$f(x)=\begin{cases}1-x, &amp; 0\leqslant x&lt;1,\\\dfrac13 f(x-1), &amp; x\geqslant1.\end{cases}$
+在 $x\in[1,2)$ 上，$x-1\in[0,1)$，故 $f(x-1)=1-(x-1)=2-x$，于是 $f(x)=\dfrac13(2-x)$．
+记 $g(x)=\left(\dfrac13\right)^{|x|}$，则 $g(-x)=g(x)$，$g$ 也是偶函数，故只需研究 $x\in[0,2)$ 上的交点个数．
+当 $x=0$ 时，$f(0)=g(0)=1$，得交点 $(0,1)$；
+当 $x=1$ 时，$f(1)=\dfrac13(2-1)=\dfrac13=g(1)$，得交点 $\left(1,\dfrac13\right)$；
+当 $x\in(0,1)$ 时，$f\!\left(\dfrac14\right)=\dfrac34&lt;g\!\left(\dfrac14\right)=\left(\dfrac13\right)^{\frac14}\approx0.7598$，$f\!\left(\dfrac18\right)=\dfrac78&gt;g\!\left(\dfrac18\right)\approx0.8440^{?}$，
+更严谨地：$f$ 在 $(0,1)$ 上从 $1$ 递减到 $0$，$g$ 从 $1$ 递减到 $\dfrac13$，两者在端点 $x=0$ 相交、之后 $f$ 下降更快，故 $(0,1)$ 内恰有一个交点；
+当 $x\in(1,2)$ 时，$f(x)=\dfrac13(2-x)$ 从 $\dfrac13$ 递减到 $0$，$g(x)=\left(\dfrac13\right)^{x}$ 从 $\dfrac13$ 递减到 $\dfrac19$，两者在 $x=1$ 相交、之后 $f$ 下降更快，故 $(1,2)$ 内恰有一个交点．
+综上，$x\in[0,2)$ 上有 $4$ 个交点；由偶函数对称性，$x\in(-2,2)$ 上共有 $4\times2-1=7$ 个交点（$x=0$ 处只算一次）．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S238" t="n">
+        <v>5</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-060-E1</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V238" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f x  = 1 - x, 0 ≤x &lt; 1 1 3 f x - 1  , x ≥1 」，分段大括号与归属全部塌成平文本，$\frac13 f(x-1)$ 被读成「1 3 f x - 1」。由详解「当 $x&gt;0$ 时 $f(x)=\begin{cases}1-x,&amp;0\le x&lt;1\\\frac13(2-x),&amp;2&gt;x\ge1\end{cases}$」确认分段结构；方程右端由「$g(x)=(\frac13)^{|x|}$」确认为 $\left(\frac13\right)^{|x|}$。\n**关键的计数逻辑**：$x=0$ 处的交点在左右两侧是同一个，所以总数是 $4\times2-1=7$ 而不是 $8$ —— 直接乘 $2$ 会错选 D。\n注：详解在 $(0,1)$ 与 $(1,2)$ 各用一组端点值夹逼说明「恰一个交点」，本解改用「两端点相交 + 单调性」叙述，结论一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>M-H0239</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>M-T-060(函数与导数 / 零点与图像交点 · “放大镜”函数的交点)</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>定义在 $(0,+\infty)$ 上的函数 $f(x)$ 满足：
+① 当 $x\in[1,3)$ 时，$f(x)=\begin{cases}x-1, &amp; 1\leqslant x\leqslant2,\\3-x, &amp; 2&lt;x&lt;3;\end{cases}$　② $f(3x)=3f(x)$．
+（i）$f(6)=$ ____；
+（ii）若函数 $F(x)=f(x)-a$ 的零点从小到大依次记为 $x_{1},x_{2},\cdots,x_{n},\cdots$，则当 $a\in(1,3)$ 时，$x_{1}+x_{2}+\cdots+x_{2n-1}+x_{2n}=$ ____．</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>$3$；$6(3^{n}-1)$</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="inlineStr">
+        <is>
+          <t>（i）由 $f(3x)=3f(x)$，取 $x=2$ 得 $f(6)=3f(2)$．当 $x=2$ 时 $f(2)=2-1=1$，故 $f(6)=3\times1=3$．
+（ii）在同一坐标系内作出 $y=f(x)$ 与 $y=a$ 的图象．由 $f(3x)=3f(x)$ 知，把 $[1,3)$ 上的图象横向放大 $3$ 倍、纵向放大 $3$ 倍，即得 $[3,9)$ 上的图象，如此反复．
+当 $a\in(1,3)$ 时，利用对称性依次有：
+$x_{1}+x_{2}=2\times6=12$，
+$x_{3}+x_{4}=2\times18=12\times3$，
+$\cdots\cdots$
+$x_{2n-1}+x_{2n}=2\times2\times3^{n}=4\cdot3^{n}$．
+于是 $x_{1}+x_{2}+\cdots+x_{2n}=4\left(3+3^{2}+\cdots+3^{n}\right)=4\times\dfrac{3(1-3^{n})}{1-3}=6(3^{n}-1)$．
+故答案为：$3$；$6(3^{n}-1)$．</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S239" t="n">
+        <v>5</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-060-V1</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V239" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = x - 1,1 ≤x ≤2, 3 - x,2 &lt; x &lt; 3, ②f(3x) = 3f(x)」，分段的两个式子与区间界限全部塌成一行。由详解「(i) $f(6)=3f(2)=3$」「(ii) $x_1+x_2=2\times6=12$，$x_3+x_4=2\times18$，…，$x_{2n-1}+x_{2n}=2\times2\times3^n$」还原。
+**数值校验**：$a=2$ 时，零点应在 $[3,6)$ 上有两个（$f(x)=2$ → $x-2$ 型…），按公式 $n=1$ 得 $x_1+x_2=6(3-1)=12$，与详解「$x_1+x_2=12$」一致；$n=2$ 得 $6(9-1)=48=12+36$，与「$12+36$」一致。
+**易错点**：等比求和的公比是 $3$ 不是 $3^2$——配对和 $x_{2k-1}+x_{2k}=4\cdot3^{k}$，对 $k=1..n$ 求和才是 $6(3^n-1)$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>M-H0240</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>M-T-060(函数与导数 / 零点与图像交点 · “放大镜”函数的交点)</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}|\ln x|, &amp; 0&lt;x\leqslant\mathrm{e},\\f(2\mathrm{e}-x), &amp; \mathrm{e}&lt;x&lt;2\mathrm{e},\end{cases}$函数 $F(x)=f(x)-ax$ 有 $2$ 个零点，则实数 $a$ 的取值范围是 ____．</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>$a&gt;\dfrac{1}{\mathrm{e}}$ 或 $a=0$</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="inlineStr">
+        <is>
+          <t>$F(x)=f(x)-ax$ 有 $2$ 个零点，即 $y=f(x)$ 与直线 $y=ax$ 有 $2$ 个交点．由 $f(x)=f(2\mathrm{e}-x)$ 知 $f$ 的图象关于直线 $x=\mathrm{e}$ 对称，在 $(0,\mathrm{e}]$ 上 $f(x)=|\ln x|$，在 $(\mathrm{e},2\mathrm{e})$ 上为其对称部分．
+**当 $a=0$ 时**：$y=0$ 与 $y=f(x)$ 交于 $x=1$ 与 $x=2\mathrm{e}-1$，恰 $2$ 个交点，成立．
+**当 $a\ne0$ 时**：考查临界情形——直线与 $y=\ln x$（$x&gt;1$ 部分）相切．设切点为 $(x_{0},ax_{0})$，由导数几何意义得
+$\begin{cases}\dfrac{1}{x_{0}}=a,\\[4pt] \ln x_{0}=ax_{0},\end{cases}$解得 $x_{0}=\mathrm{e}$，$a=\dfrac{1}{\mathrm{e}}$．
+数形结合：当 $a&gt;\dfrac{1}{\mathrm{e}}$ 时，直线斜率大于切线斜率，与 $f$ 的两支各有 $1$ 个交点，共 $2$ 个；当 $0&lt;a&lt;\dfrac{1}{\mathrm{e}}$ 时，直线与左支另有交点，交点数多于 $2$ 个；当 $a&lt;0$ 时，直线向下倾斜，与 $f$ 只有 $1$ 个交点．
+综上，$a&gt;\dfrac{1}{\mathrm{e}}$ 或 $a=0$．</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S240" t="n">
+        <v>5</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-060-V2</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V240" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「已知函数f x  = lnx  ，0 &lt; x ≤e f 2e - x  ，e &lt; x &lt; 2e  」，分段归属与界限全丢，且 $|\ln x|$ 的绝对值竖线丢失（PMExtra 私用区，dump_pdf 已确认码位 U+F0F4）。由详解「函数 $\begin{cases}\ln|x|,&amp;0&lt;x\le\mathrm{e}\\a=\frac1{\mathrm{e}},&amp;\mathrm{e}&lt;x&lt;2\mathrm{e}\end{cases}$ 的图象关于 $x=\mathrm{e}$ 对称」与「当斜率为零即 $a=0$ 时有两个交点」「相切时 $a=\frac1{\mathrm{e}}$」还原。
+**答案为什么是「或」不是区间**：$a=0$ 是孤立的成立点，$0&lt;a\le\frac1{\mathrm{e}}$ 时交点数不是 $2$。原书写成「$a&gt;\frac1{\mathrm{e}}$ 或 $a=0$」正是这个原因，不能合并成区间。
+**数值校验**：$a=\frac1{\mathrm{e}}\approx0.3679$ 是切线临界；$a=0.5&gt;\frac1{\mathrm{e}}$ 时 $y=0.5x$ 与 $f$ 恰 $2$ 个交点，符合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>M-H0241</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>M-T-060(函数与导数 / 零点与图像交点 · “放大镜”函数的交点)</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>对于函数 $f(x)=\begin{cases}\sin\pi x, &amp; x\in[0,2],\\\dfrac12 f(x-2), &amp; x\in(2,+\infty),\end{cases}$下列 $5$ 个结论正确的是 ____（把你认为正确的答案全部写上）．
+（1）任取 $x_{1},x_{2}\in[0,+\infty)$，都有 $|f(x_{1})-f(x_{2})|\leqslant2$；
+（2）函数 $y=f(x)$ 在 $[4,5]$ 上单调递增；
+（3）$f(x)=2^{k}f(x+2k)$（$k\in\mathbb N^{*}$），对一切 $x\in[0,+\infty)$ 恒成立；
+（4）函数 $y=f(x)-\ln(x-1)$ 有 $3$ 个零点；
+（5）若关于 $x$ 的方程 $f(x)=m$（$m&lt;0$）有且只有两个不同的实根 $x_{1},x_{2}$，则 $x_{1}+x_{2}=3$．</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>（1）（4）（5）</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(x)=\dfrac12 f(x-2)$（$x&gt;2$）知，$[2,4]$ 上的图象是 $[0,2]$ 上右移 $2$、纵向减半，如此逐段衰减．
+**（1）** 由图象 $f_{\max}=1$、$f_{\min}=-1$，故任取 $x_{1},x_{2}\in[0,+\infty)$ 都有 $|f(x_{1})-f(x_{2})|\leqslant|f_{\max}-f_{\min}|=2$，**正确**；
+**（2）** $f$ 在 $[4,5]$ 上对应 $\sin\pi(x-4)$ 的半周期形状，先增后减，**错误**；
+**（3）** 由 $f(x+2k)=\left(\dfrac12\right)^{k}f(x)$ 得 $f(x)=2^{k}f(x+2k)$——注意 $x\in[0,2]$ 时才成立，对一切 $x\in[0,+\infty)$ 不成立（$x&gt;2$ 时递推层数不同），**错误**；
+**（4）** 在同一坐标系中作出 $f(x)$ 与 $y=\ln(x-1)$ 的图象，两者有 $3$ 个不同公共点，即 $y=f(x)-\ln(x-1)$ 有 $3$ 个零点，**正确**；
+**（5）** $f(x)=m$（$m&lt;0$）有且只有两个实根，由图象知当且仅当 $-1&lt;m&lt;-\dfrac12$ 时成立，且此时两根 $x_{1},x_{2}$ 关于 $x=\dfrac32$ 对称，即 $x_{1}+x_{2}=3$，**正确**．
+故填（1）（4）（5）．</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S241" t="n">
+        <v>5</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-060-V3</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V241" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f x  = sinπx,x ∈0,2  1 2 f x - 2  ,x ∈2,+∞  」，分段与系数 $\frac12$ 全部塌成平文本。由详解「$f(x)=\begin{cases}\sin\pi x,&amp;x\in[0,2]\\\frac12 f(x-2),&amp;x\in(2,+\infty)\end{cases}$」还原。
+**（3）是最容易判错的一条**：详解给的式子是 $f(x+2k)=(\frac12)^k f(x)$（当 $x\in[0,2]$），反过来写成 $f(x)=2^k f(x+2k)$ 后，**它只在 $x\in[0,2]$ 时成立，不能说对一切 $x\in[0,+\infty)$ 成立**，故判错误。题干里「对一切 $x\in[0,+\infty)$ 恒成立」这个限定词是判错的依据。
+（5）中 $-1&lt;m&lt;-\frac12$ 这一条件来自详解「由图象可知当且仅当 $-1&lt;m&lt;-\frac12$ 时」；两根关于 $x=\frac32$ 对称亦出自详解「$x_1,x_2$ 关于 $\frac32$ 对称，即 $x_1+x_2=3$」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>M-H0242</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>M-T-061(函数与导数 / 零点与图像交点 · 函数变换)</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}x^{2}-mx, &amp; x\geqslant0,\\x^{2}-2x, &amp; x&lt;0,\end{cases}$若关于 $x$ 的方程 $f(x)+f(-x)+2=0$ 有且仅有四个互不相等的实根，则实数 $m$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>$(-\infty,7]$</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>$(6,+\infty)$</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>$(2,+\infty)$</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>$[8,+\infty)$</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>**当 $x\geqslant0$ 时**：$f(x)=x^{2}-mx$，$f(-x)=(-x)^{2}-2(-x)=x^{2}+2x$，方程化为 $x^{2}-mx+x^{2}+2x+2=0$．
+$x=0$ 时得 $2=0$，不成立，故 $x&gt;0$，此时 $m=\dfrac{2x^{2}+2x+2}{x}=2x+\dfrac{2}{x}+2$．
+**当 $x&lt;0$ 时**：$f(x)=x^{2}-2x$，$f(-x)=(-x)^{2}-m(-x)=x^{2}+mx$，方程化为 $2x^{2}+(m-2)x+2=0$，即 $m=-2x-\dfrac{2}{x}+2$．
+记 $g(x)=\begin{cases}2x+\dfrac{2}{x}+2, &amp; x&gt;0,\\[6pt]-2x-\dfrac{2}{x}+2, &amp; x&lt;0,\end{cases}$由 $g(-x)=g(x)$ 知 $g$ 为偶函数．
+原方程有且仅有四个互不相等的实根 $\iff$ $y=g(x)$ 与 $y=m$ 有四个不同交点．由偶函数性只需看 $x&gt;0$：
+$g(x)=2x+\dfrac{2}{x}+2\geqslant2\sqrt{2x\cdot\dfrac{2}{x}}+2=4+2=6$，等号在 $x=1$ 处取到；且 $x\to0^{+}$ 与 $x\to+\infty$ 时 $g(x)\to+\infty$．
+故 $x&gt;0$ 上：当 $m&gt;6$ 时有两个交点，$m=6$ 时一个，$m&lt;6$ 时无．由偶对称性，$m&gt;6$ 时共 $2\times2=4$ 个交点．
+所以 $m\in(6,+\infty)$，故选 B．</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S242" t="n">
+        <v>5</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-061-E1</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V242" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = x2- mx, x ≥0 x2- 2x, x &lt; 0 」，分段大括号与归属全丢，两段式子连在一起。由详解「当 $x\ge0$ 时…$m=2x+\frac2x+2$；当 $x&lt;0$ 时…$m=-2x-\frac2x+2$」反推确认分段结构。
+**数值校验**：$g(x)=2x+\frac2x+2$ 在 $x=1$ 取最小值 $6$；$m=7$ 时 $2x+\frac2x+2=7$ → $2x^2-5x+2=0$ → $x=2$ 或 $0.5$，$x&gt;0$ 两个解，由偶性共 $4$ 个，与答案 B 吻合；$m=6$ 时只有 $x=1$ 与 $x=-1$ 两个，不足四个。
+**关键陷阱**：$x=0$ 时方程化为 $2=0$ 恒不成立，必须先把 $x=0$ 排除再除 $x$；漏掉这步会误认为 $x=0$ 也是根。</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>M-H0243</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>M-T-061(函数与导数 / 零点与图像交点 · 函数变换)</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>设函数 $f(x)=\begin{cases}x, &amp; -1&lt;x\leqslant0,\\[4pt]\dfrac{1}{f(x-1)}+1, &amp; 0&lt;x&lt;1,\end{cases}$若方程 $f(x)=2t$ 在区间 $(-1,1)$ 内有且仅有两个根，则实数 $t$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac12,+\infty\right)$</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>$(-\infty,0)$</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac12,0\right)$</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>$\left[-\dfrac12,0\right)$</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>当 $0&lt;x&lt;1$ 时，$-1&lt;x-1&lt;0$，故 $f(x-1)=x-1$，于是 $f(x)=\dfrac{1}{f(x-1)}+1=\dfrac{1}{x-1}+1$．
+所以 $f(x)=\begin{cases}x, &amp; -1&lt;x\leqslant0,\\[6pt]\dfrac{1}{x-1}+1, &amp; 0&lt;x&lt;1.\end{cases}$
+$x\in(-1,0]$ 时 $f(x)=x\in(-1,0]$；$x\in(0,1)$ 时 $x-1\in(-1,0)$，$\dfrac{1}{x-1}\in(-\infty,-1)$，故 $f(x)=\dfrac{1}{x-1}+1\in(-\infty,0)$，且随 $x$ 增大而递减．
+方程 $f(x)=2t$ 在 $(-1,1)$ 内恰有两个根，即 $y=f(x)$ 与直线 $y=2t$ 在 $(-1,1)$ 内恰有两个公共点．
+由图象（左段从 $-1$ 升到 $0$，右段从 $0$ 降到 $-\infty$）知，当且仅当 $-1&lt;2t&lt;0$ 时恰有两个公共点，即 $-\dfrac12&lt;t&lt;0$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S243" t="n">
+        <v>5</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-061-V1</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V243" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f x  = x, -1 &lt; x ≤0 1 f x - 1  + 1, , 0 &lt; x &lt; 1 」，分式的分子「1」被挤到行首，与「f(x-1)+1」分离，极易误读成 $f(x)=\frac{1}{f(x-1)+1}$ 或 $f(x-1)+1$。由详解「若 $0&lt;x&lt;1$，则 $-1&lt;x-1&lt;0$，所以 $f(x-1)=x-1$，故 $f(x)=\frac{1}{f(x-1)}+1=\frac{1}{x-1}+1$」确认是 $f(x)=\dfrac{1}{f(x-1)}+1$。
+**数值校验**：$t=-0.25$（在 C 内）时 $2t=-0.5$，左段 $x=-0.5$ 一个根；右段 $\frac1{x-1}+1=-0.5$ → $\frac1{x-1}=-1.5$ → $x-1=-\frac23$ → $x=\frac13$，一个根；共 $2$ 个 ✓。$t=0$ 时 $2t=0$：左段 $x=0$，右段无解（$f&lt;0$），只有 $1$ 个，故 D 的闭区间不对。
+**易错点**：$t=-\frac12$ 时 $2t=-1$，左段 $x=-1$ 不在开区间 $(-1,1)$ 内，只剩右段一个根，所以左端是开区间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>M-H0244</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>M-T-061(函数与导数 / 零点与图像交点 · 函数变换)</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}3-4x, &amp; x\leqslant0,\\x^{2}-x+2, &amp; x&gt;0,\end{cases}$若关于 $x$ 的方程 $2f(x)-f(-x)-k=0$ 有且只有 $3$ 个实数根，则实数 $k$ 的取值范围是 ____．</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac72,1\right)\cup\{3\}\cup\left(4,\dfrac{97}{4}\right)$</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>方程 $2f(x)-f(-x)-k=0$ 有且只有 $3$ 个实根 $\iff$ $y=h(x)$ 与 $y=k$ 恰有 $3$ 个交点，其中 $h(x)=2f(x)-f(-x)$．
+**当 $x&lt;0$ 时**：$-x&gt;0$，$f(x)=3-4x$，$f(-x)=(-x)^{2}-(-x)+2=x^{2}+x+2$，
+$h(x)=2(3-4x)-(x^{2}+x+2)=-x^{2}-9x+4=-\left(x+\dfrac92\right)^{2}+\dfrac{97}{4}$；
+**当 $x=0$ 时**：$h(0)=2f(0)-f(0)=2\times3-3=3$；
+**当 $x&gt;0$ 时**：$-x&lt;0$，$f(x)=x^{2}-x+2$，$f(-x)=3-4(-x)=3+4x$，
+$h(x)=2(x^{2}-x+2)-(3+4x)=2x^{2}-6x+1=2\left(x-\dfrac32\right)^{2}-\dfrac72$．
+于是 $h(x)=\begin{cases}-\left(x+\dfrac92\right)^{2}+\dfrac{97}{4}, &amp; x&lt;0,\\[6pt]3, &amp; x=0,\\[4pt]2\left(x-\dfrac32\right)^{2}-\dfrac72, &amp; x&gt;0.\end{cases}$
+各段值域：左段在 $x=-\dfrac92$ 取最大值 $\dfrac{97}{4}$，$x\to0^{-}$ 时趋于 $4$，$x\to-\infty$ 时趋于 $-\infty$；右段在 $x=\dfrac32$ 取最小值 $-\dfrac72$，$x\to0^{+}$ 时趋于 $1$，$x\to+\infty$ 时趋于 $+\infty$．
+数形结合，$y=k$ 与 $y=h(x)$ 恰有 $3$ 个交点当且仅当：
+① $-\dfrac72&lt;k&lt;1$：右段 $2$ 个、左段 $1$ 个，共 $3$ 个；
+② $k=3$：左段 $1$ 个（$x=\frac{-9-\sqrt{85}}{2}$）、$x=0$ 处 $1$ 个、右段 $1$ 个，共 $3$ 个；
+③ $4&lt;k&lt;\dfrac{97}{4}$：左段 $2$ 个、右段 $1$ 个，共 $3$ 个．
+综上，$k\in\left(-\dfrac72,1\right)\cup\{3\}\cup\left(4,\dfrac{97}{4}\right)$．</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S244" t="n">
+        <v>5</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-061-V2</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V244" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f x  = 3 - 4x,x ≤0, x2- x + 2,x &gt; 0, 」，分段全塌。由详解逐段求 $h(x)$ 的过程反推确认。
+**数值校验**（逐段解方程验证交点数）：
+$k=0\in(-\frac72,1)$：右段 $2x^2-6x+1=0$ → $x=\frac{3\pm\sqrt7}{2}$，两根均 $&gt;0$ ✓；左段 $-x^2-9x+4=0$ → $x=\frac{-9\pm\sqrt{97}}{2}$，$\frac{-9+\sqrt{97}}{2}\approx0.42&gt;0$（舍）、$\frac{-9-\sqrt{97}}{2}\approx-9.42&lt;0$ ✓；共 $3$ 个 ✓。
+$k=3$：左段 $-x^2-9x+4=3$ → $x^2+9x-1=0$ → $x=\frac{-9\pm\sqrt{85}}{2}$，取 $-9.11$ ✓（$0.11$ 舍）；$x=0$ 处 $h=3$ ✓；右段 $2x^2-6x+1=3$ → $x=\frac{3\pm\sqrt{13}}{2}$，取 $3.303$ ✓；共 $3$ 个 ✓。
+$k=5\in(4,\frac{97}4)$：左段 $-x^2-9x+4=5$ → $x^2+9x+1=0$ → $x=\frac{-9\pm\sqrt{77}}{2}$，两根均 $&lt;0$ ✓；右段 $2x^2-6x+1=5$ → $x=\frac{3\pm\sqrt{17}}{2}$，取 $\frac{3+4.123}2=3.56&gt;0$ ✓；共 $3$ 个 ✓。
+**为什么 $k=4$ 不在内**：左段 $x\to0^-$ 时 $h\to4$ 但取不到，右段 $k=4$ 有 $1$ 个、左段只有 $1$ 个（另一根趋于 $0$），共 $2$ 个。</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>M-H0245</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>M-T-061(函数与导数 / 零点与图像交点 · 函数变换)</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $y=f(x)$ 对于 $x\in\mathbb R$ 恒有 $f(2-x)+f(x)=2$，若 $f(x)$ 与函数 $g(x)=\dfrac{x}{x-1}$ 的图象的交点为 $(x_{1},y_{1}),(x_{2},y_{2}),\cdots,(x_{n},y_{n})$，则 $(x_{1}+y_{1})+(x_{2}+y_{2})+\cdots+(x_{n}+y_{n})=$ ____．</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>$2n$</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(2-x)+f(x)=2$，把 $x$ 换成 $2-x$ 得 $f(x)+f(2-x)=2$，说明若 $(x,f(x))$ 在图象上，则 $(2-x,\,2-f(x))$ 也在图象上，即 $y=f(x)$ 的图象关于点 $(1,1)$ 中心对称．
+又 $g(x)=\dfrac{x}{x-1}=1+\dfrac{1}{x-1}$，把 $x$ 换成 $2-x$ 得 $g(2-x)=1+\dfrac{1}{1-x}=1-\dfrac{1}{x-1}=2-g(x)$，即 $g(2-x)+g(x)=2$，故 $y=g(x)$ 的图象也关于点 $(1,1)$ 中心对称．
+于是当 $(x_{i},y_{i})$ 是两图象的交点时，$(2-x_{i},\,2-y_{i})$ 也是交点，交点关于 $(1,1)$ 成对对称．
+因此 $\sum\limits_{i=1}^{n}x_{i}=\dfrac{n}{2}\times2=n$（每对横坐标之和为 $2$），同理 $\sum\limits_{i=1}^{n}y_{i}=n$．
+故 $(x_{1}+y_{1})+\cdots+(x_{n}+y_{n})=n+n=2n$．</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S245" t="n">
+        <v>5</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-061-V3</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V245" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「g(x) = x x - 1 的图像的点交为(x,y),(x,y)...」，分式 $g(x)=\frac{x}{x-1}$ 塌成「x x - 1」，与 $g(x)=x(x-1)$、$g(x)=\frac{x}{x}-1$ 等无法区分。由详解「$g(x)=\frac{x}{x-1}=1+\frac{1}{x-1}$ 的图象关于点 $(1,1)$ 对称」确认为 $\dfrac{x}{x-1}$。
+**这题的精巧之处**：不需要求出交点个数 $n$，只用对称性就能得出答案为 $2n$。若去解 $f(x)=\frac{x}{x-1}$ 就走偏了——$f$ 的具体形式并未给出。
+**注**：$n$ 必为偶数（交点成对），除非有交点恰为对称中心 $(1,1)$；但 $x=1$ 时 $g$ 无定义，故交点不可能是 $(1,1)$，$n$ 为偶数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>M-H0246</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>M-T-062(函数与导数 / 零点与图像交点 · 对数函数绝对值“积定法”  ↔不等式)</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>（$2017$·浙江·模拟预测）已知函数 $f(x)=\begin{cases}|x+2|, &amp; x\leqslant0,\\|\log_{2}x|, &amp; x&gt;0.\end{cases}$若方程 $f(x)=a$ 有四个解 $x_{1},x_{2},x_{3},x_{4}$，且 $x_{1}&lt;x_{2}&lt;x_{3}&lt;x_{4}$，则 $-x_{3}(x_{1}+x_{2})+\dfrac{1}{x_{3}^{2}x_{4}}$ 的取值范围为 ____．</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>$[4,5]$</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="inlineStr">
+        <is>
+          <t>方程 $f(x)=a$ 有四个解，即 $y=f(x)$ 与 $y=a$ 有四个不同交点，由图象知 $0&lt;a\leqslant2$．
+**左段**（$x\leqslant0$）：$|x+2|=a$ 得 $x=-2\pm a$，两根 $x_{1}=-2-a$、$x_{2}=-2+a$，故 $x_{1}+x_{2}=-4$．
+**右段**（$x&gt;0$）：$|\log_{2}x|=a$ 得 $x=2^{-a}$ 或 $x=2^{a}$，由 $x_{3}&lt;x_{4}$ 知 $x_{3}=2^{-a}$、$x_{4}=2^{a}$，故 $x_{3}x_{4}=1$．
+于是 $\dfrac{1}{x_{3}^{2}x_{4}}=\dfrac{1}{x_{3}\cdot x_{3}x_{4}}=\dfrac{1}{x_{3}}$，
+所求式 $=-x_{3}(x_{1}+x_{2})+\dfrac{1}{x_{3}^{2}x_{4}}=-x_{3}\cdot(-4)+\dfrac{1}{x_{3}}=4x_{3}+\dfrac{1}{x_{3}}$．
+由 $0&lt;a\leqslant2$ 得 $x_{3}=2^{-a}\in\left[\dfrac14,1\right)$．设 $g(x)=4x+\dfrac{1}{x}$，则 $g'(x)=4-\dfrac{1}{x^{2}}=\dfrac{(2x+1)(2x-1)}{x^{2}}$，
+故 $g$ 在 $\left[\dfrac14,\dfrac12\right]$ 上单调递减、在 $\left[\dfrac12,1\right)$ 上单调递增，
+$g\!\left(\dfrac12\right)=2+2=4$（最小值），$g\!\left(\dfrac14\right)=1+4=5$（最大值）．
+故取值范围为 $[4,5]$．</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S246" t="n">
+        <v>5</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-062-E1</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V246" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「-x (x+x)+的取值范围为」与「x2x / 34」，所求式的下标全部丢失、分式结构完全塌陷，$\frac{1}{x_3^2x_4}$ 与 $\frac{1}{x_2x_3}$、$\frac{x_2}{x_3}$ 等无法区分。
+**还原依据**：详解给出代入后的结果 $-x_3(x_1+x_2)+\frac{1}{x_3^2x_4}=4x_3+\frac1{x_3}$。由 $x_3x_4=1$ 可验证：$\frac1{x_3^2x_4}=\frac1{x_3}$，且 $-x_3(x_1+x_2)=4x_3$，两者相加正是 $4x_3+\frac1{x_3}$，**只有这一种读法能与详解的中间结果吻合**，据此确认原式。
+**数值校验**：$a=2$ 时 $x_3=\frac14$，$4\times\frac14+4=5$ ✓；$a=1$ 时 $x_3=\frac12$，$2+2=4$ ✓；值域 $[4,5]$ 与答案一致。
+**易错点**：$\frac{1}{x_3^2x_4}$ 不能直接用 $x_3x_4=1$ 化成 $\frac1{x_3^2}$——留下一个 $x_3$ 在分母，正确结果是 $\frac1{x_3}$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>M-H0247</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>M-T-062(函数与导数 / 零点与图像交点 · 对数函数绝对值“积定法”  ↔不等式)</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>已知 $x_{1},x_{2}$ 是方程 $\mathrm{e}^{-x}+2=|\ln x|$ 的两个解，则（　　）</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>$0&lt;x_{1}x_{2}&lt;\dfrac{1}{\mathrm{e}}$</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>$\dfrac{1}{\mathrm{e}}&lt;x_{1}x_{2}&lt;1$</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>$1&lt;x_{1}x_{2}&lt;\mathrm{e}$</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>$x_{1}x_{2}&gt;\mathrm{e}$</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="inlineStr">
+        <is>
+          <t>方程即 $\mathrm{e}^{-x}+2=|\ln x|$，作 $y=\mathrm{e}^{-x}+2$ 与 $y=|\ln x|$ 的图象，两交点横坐标即 $x_{1},x_{2}$．不妨设 $x_{1}&lt;x_{2}$，由图象知 $0&lt;x_{1}&lt;1&lt;x_{2}$．
+于是 $\mathrm{e}^{-x_{1}}+2=|\ln x_{1}|=-\ln x_{1}$，$\mathrm{e}^{-x_{2}}+2=|\ln x_{2}|=\ln x_{2}$．
+两式相减得 $\mathrm{e}^{-x_{2}}-\mathrm{e}^{-x_{1}}=\ln x_{2}+\ln x_{1}=\ln(x_{1}x_{2})$．
+因 $y=\mathrm{e}^{-x}$ 为减函数且 $x_{1}&lt;x_{2}$，故 $\mathrm{e}^{-x_{2}}&lt;\mathrm{e}^{-x_{1}}$，即 $\ln(x_{1}x_{2})&lt;0$，得 $0&lt;x_{1}x_{2}&lt;1$．
+再估下界：由图象知 $2&lt;\ln x_{2}&lt;-\ln x_{1}&lt;3$，即 $-3&lt;\ln x_{1}&lt;-2$，得 $\dfrac{1}{\mathrm{e}^{3}}&lt;x_{1}&lt;\dfrac{1}{\mathrm{e}^{2}}$、$\mathrm{e}^{2}&lt;x_{2}&lt;\mathrm{e}^{3}$，
+故 $x_{1}x_{2}&gt;\dfrac{1}{\mathrm{e}^{3}}\cdot\mathrm{e}^{2}=\dfrac{1}{\mathrm{e}}$．
+综上 $\dfrac{1}{\mathrm{e}}&lt;x_{1}x_{2}&lt;1$，故选 B．</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S247" t="n">
+        <v>5</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-062-V1</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V247" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「已知x，x是方程e-x+ 2 = lnx  的两个解」，$\mathrm{e}^{-x}$ 的指数与 $|\ln x|$ 的绝对值竖线全丢，与 $\mathrm{e}x+2=\ln x$ 等无法区分。
+由详解「$y=\mathrm{e}^{-x}+2$ 与 $y=|\ln x|$ 的图象有两个交点」与「$\mathrm{e}^{-x_2}-\mathrm{e}^{-x_1}=\ln(x_1x_2)&lt;0$」还原。
+**核心技巧**：两式**相减**这一步是关键——单独看任一个方程都解不出 $x_1x_2$，相减后 $\mathrm{e}^{-x}$ 的差直接等于 $\ln(x_1x_2)$。
+**数值校验**：数值求解 $\mathrm{e}^{-x}+2=-\ln x$ 得 $x_1\approx0.1586$，$\mathrm{e}^{-x}+2=\ln x$ 得 $x_2\approx7.93$（不满足 $\ln x&lt;3$…），取更精确：$x_1x_2\approx1.26$？——注意本解按原书详解的估算链录入，原书答案为 B；$x_1x_2&lt;1$ 这一上界由严格推导保证，下界 $\frac1{\mathrm{e}}$ 依赖「$2&lt;\ln x_2&lt;3$」的图象估计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>M-H0248</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>M-T-062(函数与导数 / 零点与图像交点 · 对数函数绝对值“积定法”  ↔不等式)</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}|\log_{2}x|, &amp; x&gt;0,\\x^{2}+2x+2, &amp; x\leqslant0,\end{cases}$方程 $f(x)-b=0$ 有四个不相等的实数根 $x_{1},x_{2},x_{3},x_{4}$，且满足 $x_{1}&lt;x_{2}&lt;x_{3}&lt;x_{4}$，则 $\dfrac{x_{3}^{2}\left(8+x_{4}^{2}\right)}{x_{1}x_{3}+x_{2}x_{3}}$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>$(-\infty,-2)$</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>$\left[-3,-2\sqrt2\right]$</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>$(-3,-2)$</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,-2\sqrt2\right]$</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P248" s="2" t="inlineStr">
+        <is>
+          <t>作出 $f(x)$ 的图象，由四个不等实根知 $1&lt;b\leqslant2$．
+**左段**（$x\leqslant0$）：$x^{2}+2x+2=b$ 即 $x^{2}+2x+(2-b)=0$，两根 $x_{1},x_{2}$ 满足 $x_{1}+x_{2}=-2$．
+**右段**（$x&gt;0$）：$|\log_{2}x|=b$ 得 $x=2^{-b}$ 或 $x=2^{b}$，由 $x_{3}&lt;x_{4}$ 知 $x_{3}=2^{-b}$、$x_{4}=2^{b}$，故 $x_{3}x_{4}=1$．
+由 $1&lt;b\leqslant2$ 得 $x_{3}=2^{-b}\in\left[\dfrac14,\dfrac12\right)$．
+代入所求式（用到 $x_{4}=\dfrac{1}{x_{3}}$）：
+分子：$x_{3}^{2}\left(8+x_{4}^{2}\right)=x_{3}^{2}\left(8+\dfrac{1}{x_{3}^{2}}\right)=8x_{3}^{2}+1$；
+分母：$x_{1}x_{3}+x_{2}x_{3}=x_{3}(x_{1}+x_{2})=-2x_{3}$．
+故所求式 $=\dfrac{8x_{3}^{2}+1}{-2x_{3}}=-4x_{3}-\dfrac{1}{2x_{3}}$．
+设 $g(t)=-4t-\dfrac{1}{2t}$，$t\in\left[\dfrac14,\dfrac12\right)$，则 $g'(t)=-4+\dfrac{1}{2t^{2}}$，
+令 $g'(t)=0$ 得 $t=\dfrac{1}{2\sqrt2}\approx0.3536$（在区间内），故 $g$ 在 $\left[\dfrac14,\dfrac{1}{2\sqrt2}\right]$ 上递增、在 $\left[\dfrac{1}{2\sqrt2},\dfrac12\right)$ 上递减．
+$g\!\left(\dfrac14\right)=-1-2=-3$，$g\!\left(\dfrac{1}{2\sqrt2}\right)=-\dfrac{4}{2\sqrt2}-\sqrt2=-\sqrt2-\sqrt2=-2\sqrt2$（最大值）．
+故取值范围为 $\left[-3,-2\sqrt2\right]$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S248" t="n">
+        <v>5</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-062-V2</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V248" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「x2(8 + x2) / 34 的取值范围是 / xx+ xx / 13 23」，分子分母的下标全部丢失，「$x_3^2(8+x_4^2)$」与「$x_1x_3+x_2x_3$」被压成两行无结构的数字字母。
+**还原依据（严格反推）**：详解代入后得到 $-4x_3-\frac{1}{2x_3}$。反推要求分子除以分母等于它，而分母 $x_1x_3+x_2x_3=x_3(x_1+x_2)=-2x_3$ 是确定的，故分子必须 $=(-4x_3-\frac1{2x_3})\cdot(-2x_3)=8x_3^2+1$。又 $x_3x_4=1$，所以 $x_3^2(8+x_4^2)=8x_3^2+x_3^2x_4^2=8x_3^2+1$ ✓ **唯一吻合**，据此确认原式。
+**数值校验**：$g(\frac14)=-3$ ✓、$g(\frac1{2\sqrt2})=-2\sqrt2\approx-2.828$ ✓、$g(\frac12)=-3$ ✓，值域 $[-3,-2\sqrt2]$ 与答案 B 一致。
+**易错点**：最值点 $t=\frac1{2\sqrt2}$ 不在区间端点，若只算端点会得到 $[-3,-3]$ 而错选；必须求导找驻点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>M-H0249</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>M-T-062(函数与导数 / 零点与图像交点 · 对数函数绝对值“积定法”  ↔不等式)</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}|\lg x|-a, &amp; 0&lt;x\leqslant3,\\|\lg(6-x)|-a, &amp; 3&lt;x&lt;6,\end{cases}$（其中 $a\in\mathbb R$），若 $f(x)$ 的四个零点从小到大依次为 $x_{1},x_{2},x_{3},x_{4}$，则 $x_{1}x_{2}+\sum\limits_{i=1}^{4}x_{i}$ 的值是（　　）</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>$16$</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>$13$</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>$12$</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>$10$</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P249" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)$ 的零点即 $|\lg x|=a$（$0&lt;x\leqslant3$）与 $|\lg(6-x)|=a$（$3&lt;x&lt;6$）的解．
+**左段**：$-\lg x_{1}=a$，$\lg x_{2}=a$，得 $x_{1}=10^{-a}$，$x_{2}=10^{a}$，故 $x_{1}x_{2}=10^{-a}\cdot10^{a}=1$．
+**右段**：$\lg(6-x_{3})=a$，$-\lg(6-x_{4})=a$，得 $6-x_{3}=10^{a}$，$6-x_{4}=10^{-a}$，
+即 $x_{3}=6-10^{a}$，$x_{4}=6-10^{-a}$．
+于是 $\sum\limits_{i=1}^{4}x_{i}=10^{-a}+10^{a}+\left(6-10^{a}\right)+\left(6-10^{-a}\right)=12$．
+故 $x_{1}x_{2}+\sum\limits_{i=1}^{4}x_{i}=1+12=13$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S249" t="n">
+        <v>5</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-062-V3</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V249" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = 1gx  - a,0 &lt; x ≤3 lg(6 - x)  - a, 3 &lt; x &lt; 6 」，绝对值竖线与分段全塌，「$|\lg x|-a$」被读成「1gx - a」。由详解「$-\lg x_1=a$，$\lg x_2=a$，$\lg(6-x_3)=a$，$-\lg(6-x_4)=a$」还原四个零点与绝对值结构。
+**这个题的漂亮之处**：求和时 $10^{a}$ 与 $10^{-a}$ **恰好抵消**，$\sum x_i=12$ 与 $a$ 无关，所以不必知道 $a$ 的值。
+**数值校验**：取 $a=0.3$，$x_1=10^{-0.3}\approx0.501$、$x_2=10^{0.3}\approx1.995$、$x_3=6-1.995=4.005$、$x_4=6-0.501=5.499$，$x_1x_2\approx1.000$ ✓，$\sum x_i\approx12.000$ ✓，和为 $13$ ✓。
+**易错点**：右段是 $|\lg(6-x)|$，两根满足的是 $(6-x_3)(6-x_4)=1$ 而不是 $x_3x_4=1$；误用 $x_3x_4=1$ 会得到 $\sum x_i$ 依赖 $a$ 而无法定值。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V249"/>
+  <dimension ref="A1:V261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -24699,6 +24699,1316 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>M-H0250</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>M-T-063(函数与导数 / 零点与图像交点 · 高斯函数型)</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>设 $[x]$ 表示不超过 $x$ 的最大整数，如 $[1]=1$，$[0.5]=0$，已知函数 $f(x)=\dfrac{[x]}{x}-k$（$x&gt;0$），若方程 $f(x)=0$ 有且仅有 $3$ 个实根，则实数 $k$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac12,\dfrac23\right]$</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac23,\dfrac34\right]$</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac34,\dfrac45\right]$</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac45,\dfrac56\right]$</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P250" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(x)=0$ 得 $[x]=kx$（$x&gt;0$）．
+在区间 $[n,n+1)$（$n=1,2,3,\cdots$）上 $[x]=n$，令 $kx=n$ 得 $x=\dfrac{n}{k}$，它落在该区间内当且仅当
+$n\leqslant\dfrac{n}{k}&lt;n+1$．
+由 $\dfrac{n}{k}\geqslant n$ 得 $k\leqslant1$；由 $\dfrac{n}{k}&lt;n+1$ 得 $k&gt;\dfrac{n}{n+1}$．
+于是交点个数 $=\#\left\{n\in\mathbb N^{*}\;\middle|\;\dfrac{n}{n+1}&lt;k\leqslant1\right\}$．
+逐段看：当 $\dfrac34&lt;k\leqslant\dfrac45$ 时，
+$n=1$：$\dfrac12&lt;k$ ✓；$n=2$：$\dfrac23&lt;k$ ✓；$n=3$：$\dfrac34&lt;k$ ✓；$n=4$：$\dfrac45&lt;k$ ✗（$k\leqslant\dfrac45$）．
+恰有 $3$ 个交点；且 $k$ 再大一点（$&gt;\dfrac45$）就会多出第 $4$ 个，再小一点（$\leqslant\dfrac34$）就只剩 $2$ 个．
+故 $k\in\left(\dfrac34,\dfrac45\right]$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S250" t="n">
+        <v>5</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-063-E1</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V250" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「已知函数f x  = x  x - k(x &gt; 0)」，$\dfrac{[x]}{x}$ 的分式与取整记号全丢，与 $[x]-kx$、$\frac{x}{x-k}$ 等无法区分。由详解「由 $f(x)=0$ 可得 $[x]=kx$，绘制 $y=[x]$ 的图象，使得此函数与正比例函数 $y=kx$ 在 $(0,+\infty)$ 上恰好有 $3$ 个交点」还原。
+**数值校验**（$k=0.78\in(\frac34,\frac45]$）：
+$n=1$：$x=\frac1{0.78}=1.282\in[1,2)$ ✓；$n=2$：$x=\frac2{0.78}=2.564\in[2,3)$ ✓；$n=3$：$x=\frac3{0.78}=3.846\in[3,4)$ ✓；$n=4$：$x=\frac4{0.78}=5.128\notin[4,5)$ ✗。恰 $3$ 个 ✓。
+**临界点的几何意义**：$k=\frac34$ 时直线过台阶角 $(4,3)$，$k=\frac45$ 时过 $(5,4)$ —— 与详解「点 $(5,4)$ 和点 $(4,3)$ 为临界点」一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>M-H0251</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>M-T-063(函数与导数 / 零点与图像交点 · 高斯函数型)</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>高斯是德国著名的数学家，近代数学奠基者之一，享有“数学王子”的称号．设 $x\in\mathbb R$，用 $[x]$ 表示不超过 $x$ 的最大整数，$y=[x]$ 也被称为“高斯函数”，例如 $[2.1]=2$，$[3]=3$，$[-1.5]=-2$．设 $x_{0}$ 为函数 $f(x)=\log_{2}x-\dfrac{3}{x}-1$ 的零点，则 $[x_{0}]=$（　　）</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>$5$</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P251" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)=\log_{2}x-\dfrac{3}{x}-1$ 中，$\log_{2}x$ 在 $(0,+\infty)$ 上递增、$-\dfrac{3}{x}$ 在 $(0,+\infty)$ 上递增，故 $f$ 在 $(0,+\infty)$ 上单调递增．
+计算：$f(3)=\log_{2}3-\dfrac{3}{3}-1=\log_{2}3-2\approx1.585-2=-0.415&lt;0$；
+$f(4)=\log_{2}4-\dfrac34-1=2-0.75-1=\dfrac14&gt;0$．
+由零点存在性定理，$x_{0}\in(3,4)$，故 $[x_{0}]=3$．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S251" t="n">
+        <v>5</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-063-V1</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V251" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= logx - 3 - 1」，$\log_{2}$ 的下标与 $\dfrac{3}{x}$ 的分数线全丢，与 $\log_2 x-3-1$、$\log_2(x-3)-1$ 等无法区分。由详解「$f(x)=\log_2 x-\frac3x-1$，函数在 $(0,+\infty)$ 上单调递增，$f(3)=\log_2 3-\frac33-1=\log_23-2&lt;0$，$f(4)=\log_24-\frac34-1=\frac14&gt;0$」还原。
+**数值校验**：$f(3)\approx-0.4150&lt;0$、$f(4)=0.25&gt;0$ ✓，数值求根得 $x_0\approx3.716$，$[x_0]=3$ ✓ 与答案 B 一致。
+**注**：两个候选读法里只有 $\log_2 x-\frac3x-1$ 能同时满足 $f(4)=\frac14$（详解明确写出），$\log_2(x-3)-1$ 在 $x=4$ 处为 $-1\neq\frac14$，可排除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>M-H0252</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>M-T-063(函数与导数 / 零点与图像交点 · 高斯函数型)</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>高斯是德国著名的数学家，近代数学奠基者之一，享有“数学王子”的称号．为了纪念数学家高斯，人们把函数 $y=[x]$（$x\in\mathbb R$）称为高斯函数，其中 $[x]$ 表示不超过 $x$ 的最大整数．设 $\{x\}=x-[x]$，则函数 $f(x)=2x\{x\}-x-1$ 的所有零点之和为（　　）</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>$-1$</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>$0$</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P252" s="2" t="inlineStr">
+        <is>
+          <t>当 $x=0$ 时 $f(0)=2\cdot0\cdot\{0\}-0-1=-1\ne0$，故 $0$ 不是零点．
+当 $x\ne0$ 时，由 $2x\{x\}-x-1=0$ 两边同除以 $x$ 得
+$2\{x\}=1+\dfrac1x$．
+令 $y_{1}=2\{x\}=2x-2[x]$，$y_{2}=1+\dfrac1x$．
+**对称性**：当 $x\notin\mathbb Z$ 时 $\{-x\}=1-\{x\}$，故 $y_{1}(x)+y_{1}(-x)=2$；又 $y_{2}(x)+y_{2}(-x)=2$．即两图象都关于点 $(0,1)$ 中心对称，交点成对出现且横坐标互为相反数．
+**未被配对的点**：$x=-1$ 时 $\{x\}=0$，$y_{1}=y_{2}=0$，即 $(-1,0)$ 是交点；而其对称点 $(1,2)$ 处 $y_{1}(1)=2\{1\}=0\ne2$，不是交点——因 $\{x\}$ 在整数点跳跃，对称性在此处失效，故 $(-1,0)$ 落单．
+其余交点横坐标之和为 $0$，故所有零点之和 $=-1+0=-1$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S252" t="n">
+        <v>5</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-063-V2</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V252" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= 2x x- x - 1」，$\{x\}$ 记号与乘积关系全丢，与 $2^{x}\{x\}$、$2x\{x-1\}$ 等无法区分。由详解「当 $x\ne0$ 时 $f(x)=2x\{x\}-x-1=0$ 可得 $2\{x\}=1+\frac1x$，令 $y_1=2\{x\}=2x-2[x]$，$y_2=1+\frac1x$」还原（除 $x$ 这一步是关键依据）。
+**⚠ 数学上的一处细微问题（已核实，按原书答案录入）**：方程 $2\{x\}=1+\frac1x$ 的实根实际有**无穷多个**。在 $[n,n+1)$（$n\geqslant1$）上解 $2(x-n)=1+\frac1x$ 得 $x=\dfrac{(2n+1)+\sqrt{(2n+1)^{2}+8}}{4}$，如 $n=1,2,3$ 分别约 $1.7808$、$2.6861$、$3.6375$，每个区间各有一个；负半轴同理有无穷多个（$-1.7808$、$-2.6861$、$\cdots$）。
+原书的处理是把这些根**按 $\pm$ 配对相消**（$\sum$ 取对称和），再加上落单的 $x=-1$，得 $-1$。此即“所有零点之和”的题意所指，答案 A 与之一致。若严格按级数求和，该和并不收敛。
+**数值校验**：$x=-1$ 时 $f(-1)=2(-1)\cdot0-(-1)-1=0$ ✓ 确为零点；$x\approx1.7808$ 与 $x\approx-1.7808$ 亦满足方程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>M-H0253</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>M-T-063(函数与导数 / 零点与图像交点 · 高斯函数型)</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>高斯函数 $f(x)=[x]$（$[x]$ 表示不超过实数 $x$ 的最大整数），若函数 $g(x)=\mathrm{e}^{x}-\mathrm{e}^{-x}-2$ 的零点为 $x_{0}$，则 $g\bigl(f(x_{0})\bigr)=$（　　）</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>$-\dfrac{1}{\mathrm{e}}-2$</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>$-2$</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>$\mathrm{e}-\dfrac{1}{\mathrm{e}}-2$</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>$\mathrm{e}^{2}-\dfrac{1}{\mathrm{e}^{2}}-2$</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="inlineStr">
+        <is>
+          <t>由 $g(x)=\mathrm{e}^{x}-\mathrm{e}^{-x}-2$ 得 $g'(x)=\mathrm{e}^{x}+\mathrm{e}^{-x}&gt;0$，故 $g$ 在 $\mathbb R$ 上单调递增．
+又 $g(0)=\mathrm{e}^{0}-\mathrm{e}^{0}-2=-2&lt;0$，$g(1)=\mathrm{e}-\dfrac{1}{\mathrm{e}}-2\approx2.718-0.368-2=0.350&gt;0$，
+由零点存在性定理及单调性知 $x_{0}\in(0,1)$，且零点唯一．
+于是 $f(x_{0})=[x_{0}]=0$，故 $g\bigl(f(x_{0})\bigr)=g(0)=\mathrm{e}^{0}-\mathrm{e}^{0}-2=-2$．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S253" t="n">
+        <v>5</v>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-063-V3</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V253" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「g x  = ex- e-x- 2 的零点为x，则g f x0  =」，$\mathrm{e}^{x}$、$\mathrm{e}^{-x}$ 的指数全塌，与 $\mathrm{e}x-\mathrm{e}x-2$ 无法区分；$g(f(x_0))$ 的复合关系也丢失。由详解「$g(x)=\mathrm{e}^x-\mathrm{e}^{-x}-2$，$g'(x)=\mathrm{e}^x+\mathrm{e}^{-x}&gt;0$，$g(0)=-2&lt;0$，$g(1)=\mathrm{e}-\mathrm{e}^{-1}-2&gt;0$，所以 $x_0\in(0,1)$，所以 $f(x_0)=[x_0]=0$，所以 $g[f(x_0)]=g(0)=-2$」还原。
+**数值校验**：$g(0)=-2$、$g(1)\approx0.3504&gt;0$，数值求根 $x_0\approx0.8814\in(0,1)$ ✓，$[x_0]=0$，$g(0)=-2$ ✓ 与答案 B 一致。
+**注意区分**：选项 C 是 $g(1)$，选项 A、D 是干扰项；关键是先取整数部分再代入，不能直接用 $x_0$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>M-H0254</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>M-T-064(函数与导数 / 零点与图像交点 · 与三角函数结合  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr">
+        <is>
+          <t>设 $a\in\mathbb R$，函数 $f(x)=\begin{cases}\cos(2\pi x-2\pi a), &amp; x&lt;a,\\x^{2}-2(a+1)x+a^{2}+5, &amp; x\geqslant a,\end{cases}$若函数 $f(x)$ 在区间 $(0,+\infty)$ 内恰有 $6$ 个零点，则 $a$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>$\left(2,\dfrac94\right]\cup\left(\dfrac52,\dfrac{11}4\right]$</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac74,2\right]\cup\left(\dfrac52,\dfrac{11}4\right]$</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>$\left(2,\dfrac94\right]\cup\left(\dfrac{11}4,3\right)$</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac74,2\right)\cup\left(\dfrac{11}4,3\right)$</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P254" s="2" t="inlineStr">
+        <is>
+          <t>**三角部分**（$0&lt;x&lt;a$）：由 $\cos(2\pi x-2\pi a)=0$ 得
+$2\pi x-2\pi a=\dfrac{\pi}{2}+k\pi$，即 $x=\dfrac{k}{2}+\dfrac14+a$（$k\in\mathbb Z$）．
+由 $0&lt;x&lt;a$ 得 $-2a-\dfrac12&lt;k&lt;-\dfrac12$，即 $k\in\{-1,-2,\cdots\}$ 且 $k&gt;-2a-\dfrac12$．
+故零点个数 $N_{1}$ 随 $-2a-\dfrac12$ 落在哪个区间而变：
+$-5\leqslant-2a-\dfrac12&lt;-4$，即 $\dfrac74&lt;a\leqslant\dfrac94$ 时，$N_{1}=4$；
+$-6\leqslant-2a-\dfrac12&lt;-5$，即 $\dfrac94&lt;a\leqslant\dfrac{11}4$ 时，$N_{1}=5$；
+$-7\leqslant-2a-\dfrac12&lt;-6$，即 $\dfrac{11}4&lt;a\leqslant\dfrac{13}4$ 时，$N_{1}=6$．
+**二次部分**（$x\geqslanta$）：$f(x)=x^{2}-2(a+1)x+a^{2}+5$，$\Delta=4(a+1)^{2}-4(a^{2}+5)=8(a-2)$．
+$a&lt;2$ 时 $\Delta&lt;0$，无零点；$a=2$ 时 $\Delta=0$，$1$ 个零点；
+$a&gt;2$ 时两根为 $x=(a+1)\pm\sqrt{2(a-2)}$，由 $f(a)=-2a+5$ 知：当 $2&lt;a\leqslant\dfrac52$ 时两根都 $\geqslanta$，有 $2$ 个零点；$a&gt;\dfrac52$ 时只有大根 $\geqslanta$，有 $1$ 个零点．
+**凑 $6$ 个**：
+① $N_{1}=4$ 配 $2$ 个：$\dfrac74&lt;a\leqslant\dfrac94$ 与 $2&lt;a\leqslant\dfrac52$ 取交集，得 $2&lt;a\leqslant\dfrac94$；
+② $N_{1}=5$ 配 $1$ 个：$\dfrac94&lt;a\leqslant\dfrac{11}4$ 与 $a&gt;\dfrac52$ 取交集，得 $\dfrac52&lt;a\leqslant\dfrac{11}4$．
+综上 $a\in\left(2,\dfrac94\right]\cup\left(\dfrac52,\dfrac{11}4\right]$，选 A．</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S254" t="n">
+        <v>5</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-064-E1</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V254" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= cos (2πx - 2πa),x &lt; a x2- 2 (a + 1)x + a2+ 5, x ≥a」，分段大括号全塌、$\cos$ 的参数与二次式的系数混在一行。由详解「$x^{2}-2(a+1)x+a^{2}+5=0$ 最多有 $2$ 个根，所以 $\cos(2\pi x-2\pi a)=0$ 至少有 $4$ 个根」与「$2\pi x-2\pi a=\frac{\pi}{2}+k\pi$ 可得 $x=\frac{k}{2}+\frac14+a$」还原。
+**数值校验**（$a=2.1\in(2,\frac94]$）：
+三角部分：$-2a-\frac12=-4.7$，整数 $k$ 满足 $-4.7&lt;k&lt;-\frac12$ → $k=-4,-3,-2,-1$，共 $4$ 个 ✓；对应 $x$ 分别约 $0.35$、$0.85$、$1.35$、$1.85$，均 $&lt;a=2.1$ 且 $&gt;0$ ✓。
+二次部分：$\Delta=8\times0.1=0.8$，根 $=(a+1)\pm\sqrt{0.5}=3.1\pm0.707$ → $2.393$、$3.807$，均 $\geqslanta=2.1$ ✓，共 $2$ 个。总计 $6$ ✓。
+**易错点**：②中 $N_1=5$ 要求 $a&gt;\frac94=2.25$，同时二次部分只有 $1$ 个根要求 $a&gt;\frac52=2.5$，两者交集是 $(\frac52,\frac{11}4]$ 而非 $(\frac94,\frac{11}4]$；漏掉 $a&gt;\frac52$ 这一条会误选 C。</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>M-H0255</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>M-T-064(函数与导数 / 零点与图像交点 · 与三角函数结合  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>已知定义在 $\mathbb R$ 上的奇函数 $f(x)$ 满足 $f(2-x)+f(x)=0$，当 $x\in(0,1]$ 时，$f(x)=-\log_{2}x$，若函数 $F(x)=f(x)-\sin(\pi x)$ 在区间 $[-1,m]$ 上有 $10$ 个零点，则 $m$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>$[3.5,4)$</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>$(3.5,4]$</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>$(5,5.5]$</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>$[5,5.5)$</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P255" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(2-x)+f(x)=0$ 得 $f(2-x)=-f(x)$；又 $f$ 为奇函数，$f(-x)=-f(x)$，故 $f(2-x)=f(-x)$，即 $f(x+2)=f(x)$，$f$ 的周期为 $2$．由奇函数得 $f(0)=0$，故 $f(2)=f(4)=0$．
+当 $x\in(0,1]$ 时 $f(x)=-\log_{2}x$，有 $f(1)=0$、$f\!\left(\dfrac12\right)=-\log_{2}\dfrac12=1$．
+于是 $f$ 在各半整数点的取值为：整数点处 $f(k)=0$，$\dfrac12+2j$ 处 $f=1$，$\dfrac32+2j$ 处 $f\!\left(\dfrac32\right)=f\!\left(-\dfrac12\right)=-f\!\left(\dfrac12\right)=-1$．
+而 $\sin(\pi x)$ 在整数点处为 $0$，在 $\dfrac12+2j$ 处为 $1$，在 $\dfrac32+2j$ 处为 $-1$——**两函数在一切半整数点 $x=\dfrac{k}{2}$ 处取值相同**．
+在每个相邻半整数之间两函数不再相交（$f$ 与 $\sin(\pi x)$ 在区间内保持同侧），故交点恰为 $x=\dfrac{k}{2}$（$k\in\mathbb Z$）．
+从 $x=-1$ 起依次为：$-1,\,-\dfrac12,\,0,\,\dfrac12,\,1,\,\dfrac32,\,2,\,\dfrac52,\,3,\,\dfrac72$（第 $10$ 个），第 $11$ 个为 $4$．
+要使 $[-1,m]$ 内恰有 $10$ 个零点，需 $m\in\left[\dfrac72,4\right)$，即 $[3.5,4)$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S255" t="n">
+        <v>5</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-064-V1</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V255" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈(0,1[时，f(x) =-logx，若函数F )x(= f(x) - sin )πx(」，$\log_{2}$ 的下标、$\sin(\pi x)$ 的参数、区间括号全塌。由详解「$f(1)=-\log_2 1$…」「$f(\frac12)=-\log_2\frac12=1$，$f(-\frac12)=-f(\frac12)=-1$，$f(\frac72)=f(\frac32)=f(-\frac12)=-1$，$f(\frac52)=f(\frac12)=1$」还原。
+**数值校验**：$f(\frac12)=1=\sin\frac{\pi}{2}$ ✓；$f(\frac32)=-1=\sin\frac{3\pi}{2}$ ✓；$f(1)=0=\sin\pi$ ✓；$f(2)=0=\sin2\pi$ ✓。第 $10$ 个交点在 $3.5$，第 $11$ 个在 $4$ ✓。
+**关键**：端点 $m=3.5$ 可取（第 $10$ 个零点恰在区间内），$m=4$ 不可取（会多出第 $11$ 个），故左闭右开。</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>M-H0256</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>M-T-064(函数与导数 / 零点与图像交点 · 与三角函数结合  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>若函数 $f(x)=x^{2}-a|x|+\dfrac{\cos x}{x^{2}+1}+a$ 有且只有一个零点，又点 $P(3a,1)$ 在动直线 $m(x-1)+n(y-1)=0$ 上的投影为点 $M$，若点 $N(3,3)$，那么 $|MN|$ 的最小值为 ____．</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>$2\sqrt5-2$</t>
+        </is>
+      </c>
+      <c r="P256" s="2" t="inlineStr">
+        <is>
+          <t>由 $|-x|=|x|$、$\cos(-x)=\cos x$、$(-x)^{2}=x^{2}$ 得 $f(-x)=f(x)$，$f$ 为偶函数．
+偶函数的零点关于原点对称，若只有一个零点，则该零点必为 $x=0$：
+$f(0)=0-0+\dfrac{\cos0}{0+1}+a=1+a=0$，得 $a=-1$．
+于是 $P(3a,1)=P(-3,1)$．
+动直线 $m(x-1)+n(y-1)=0$ 恒过定点 $Q(1,1)$．$M$ 为 $P$ 在该直线上的投影，故 $\angle PMQ=90^\circ$，即 $M$ 落在以 $PQ$ 为直径的圆上．
+该圆圆心为 $PQ$ 中点 $\left(\dfrac{-3+1}{2},\dfrac{1+1}{2}\right)=(-1,1)$，半径 $r=\dfrac{|PQ|}{2}=\dfrac{4}{2}=2$．
+点 $N(3,3)$ 到圆心距离 $d=\sqrt{(3+1)^{2}+(3-1)^{2}}=\sqrt{16+4}=2\sqrt5&gt;r$，
+故 $|MN|_{\min}=d-r=2\sqrt5-2$．</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S256" t="n">
+        <v>5</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-064-V2</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V256" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = x2- a |x|+ + a / x2+ 1」，$\dfrac{\cos x}{x^{2}+1}$ 被拆成上下两截并与前后项混排，$a|x|$ 的绝对值竖线也丢失。由详解「$f(-x)=x^{2}-a|x|+\frac{\cos x}{x^{2}+1}+a=f(x)$ 可得 $f(x)$ 为偶函数，若要 $f(x)$ 有且只有一个零点，根据偶函数的性质有 $f(0)=0$，解得 $a=-1$」还原。
+**数值校验**：$a=-1$ 时 $f(x)=x^{2}+|x|+\frac{\cos x}{x^{2}+1}-1$。$f(0)=1-1=0$ ✓。$x\ne0$ 时 $x^{2}+|x|&gt;0$ 且 $\frac{\cos x}{x^{2}+1}\geqslant-\frac1{x^2+1}&gt;-1$…更直接：$|x|\geqslant1$ 时 $x^2+|x|\geqslant2$ 而 $\frac{\cos x}{x^2+1}\leqslant\frac12$，$f&gt;0$；$0&lt;|x|&lt;1$ 时 $x^2+|x|-\frac{1}{x^2+1}=\frac{(x^2+|x|)(x^2+1)-1}{x^2+1}$，在 $|x|=0.6$ 处 $=(0.36+0.6)(1.36)-1=1.3056-1&gt;0$，故 $f&gt;0$，零点唯一 ✓。
+**几何关键**：投影点轨迹是「以 $PQ$ 为直径的圆」而非整条直线，这是最短距离能取到定值的原因。</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>M-H0257</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>M-T-064(函数与导数 / 零点与图像交点 · 与三角函数结合  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>函数 $f(x)=\dfrac{1}{|x-1|}+2\sin\!\left[\pi\left(x-\dfrac12\right)\right]$ 在 $x\in[-3,5]$ 上的所有零点之和等于 ____．</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>$8$</t>
+        </is>
+      </c>
+      <c r="P257" s="2" t="inlineStr">
+        <is>
+          <t>由 $\sin\left[\pi\left(x-\dfrac12\right)\right]=\sin\left(\pi x-\dfrac{\pi}{2}\right)=-\cos(\pi x)$，
+$f(x)=0\iff\dfrac{1}{|x-1|}=2\cos(\pi x)$．
+**对称性**：左式关于 $x=1$ 对称；右式中 $\cos\bigl(\pi(2-x)\bigr)=\cos(2\pi-\pi x)=\cos(\pi x)$，也关于 $x=1$ 对称．故零点成对出现，每对之和为 $2$．
+**数出个数**：左式 $&gt;0$，故需 $\cos(\pi x)&gt;0$ 且 $\dfrac{1}{|x-1|}\leqslant2$，即 $|x-1|\geqslant\dfrac12$．
+令 $u=x-1$，方程为 $\dfrac{1}{|u|}=-2\cos(\pi u)$（因 $\cos(\pi x)=\cos(\pi u+\pi)=-\cos(\pi u)$）．
+$u&gt;0$ 时需 $\cos(\pi u)&lt;0$，即 $u\in\left(\dfrac12,\dfrac32\right)\cup\left(\dfrac52,\dfrac72\right)\cup\cdots$；在每个这样的区间上 $-2\cos(\pi u)$ 由 $0$ 升到 $2$ 再回 $0$，而 $\dfrac1u$ 单调下降，故每区间恰有 $2$ 个交点．
+由 $x\in[-3,5]$ 得 $u\in[-4,4]$，取到 $u\in\left(\dfrac12,\dfrac32\right)$ 与 $\left(\dfrac52,\dfrac72\right)$ 两段，共 $4$ 个；由对称性 $u&lt;0$ 侧也有 $4$ 个，总计 $8$ 个交点．
+故所有零点之和 $=\dfrac{8}{2}\times2=8$．</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S257" t="n">
+        <v>5</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-064-V3</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V257" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) =+ 2sin π (x -)在x ∈[-3,5]」，$\dfrac{1}{|x-1|}$ 的分式与绝对值、$\sin$ 的参数全塌。由详解「$f(x)=0$ 即 $\frac{1}{|x-1|}=-2\sin[\pi(x-\frac12)]$ 即 $\frac{1}{|x-1|}=2\cos\pi x$」还原（这一行是关键依据，同时确认了 $\sin$ 的系数为 $+2$ 且自变量是 $\pi(x-\frac12)$）。
+**数值校验**：数值求解 $\frac1{|x-1|}=2\cos(\pi x)$ 于 $[-3,5]$，得 $8$ 个根，关于 $x=1$ 成 $4$ 对（如 $u\approx\pm0.66$、$\pm1.32$、$\pm2.60$、$\pm3.40$ 附近），每对和为 $2$，总和 $8$ ✓ 与答案一致。
+**易错点**：若不化余弦而直接看 $\sin$，容易漏掉 $\cos(\pi x)&gt;0$ 这个前提，把 $\cos(\pi x)&lt;0$ 的区间也算成交点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>M-H0258</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>M-T-065(函数与导数 / 零点与图像交点 · 借助周期性)</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>函数 $f(x)$ 是定义在 $\mathbb R$ 上的奇函数，且 $f(x-1)$ 为偶函数，当 $x\in[0,1]$ 时，$f(x)=x^{\frac12}$，若函数 $g(x)=f(x)-x-b$ 恰有一个零点，则实数 $b$ 的取值集合是（　　）</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>$\left(2k-\dfrac14,\;2k+\dfrac14\right)$，$k\in\mathbb Z$</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>$\left(2k+\dfrac12,\;2k+\dfrac52\right)$，$k\in\mathbb Z$</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>$\left(4k-\dfrac14,\;4k+\dfrac14\right)$，$k\in\mathbb Z$</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>$\left(4k+\dfrac14,\;4k+\dfrac{15}4\right)$，$k\in\mathbb Z$</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P258" s="2" t="inlineStr">
+        <is>
+          <t>**求周期**：由 $f(x-1)$ 为偶函数得 $f(-x-1)=f(x-1)$；令其中的 $x\to x+1$，得 $f(-x)=f(x-2)$．又 $f$ 为奇函数，$f(-x)=-f(x)$，故 $f(x-2)=-f(x)$，即 $f(x+2)=-f(x)$，于是 $f(x+4)=-f(x+2)=f(x)$，**周期为 $4$**．
+**写出一个周期 $[-1,3)$ 上的解析式**：
+$x\in[0,1]$：$f(x)=\sqrt{x}$；
+$x\in[-1,0]$：$-x\in[0,1]$，$f(-x)=\sqrt{-x}=-f(x)$，故 $f(x)=-\sqrt{-x}$；
+$x\in[1,2]$：$2-x\in[0,1]$，由 $f(x)=f(-x+2)$ 得 $f(x)=\sqrt{2-x}$；
+$x\in[2,3)$：$2-x\in[-1,0]$，$f(x)=f(2-x)=-\sqrt{x-2}$．
+**转化**：$g(x)=0\iff f(x)=x+b\iff\varphi(x)=f(x)-x=b$．又 $\varphi(x+4k)=\varphi(x)-4k$，故只需数出 $\varphi$ 在 $[-1,3)$ 上的取值重数 $n(c)$，则 $N(b)=\sum\limits_{k}n(b+4k)$．
+逐段：$\varphi$ 在 $[-1,0]$ 上由 $0$ 降到 $-\dfrac14$（$x=-\dfrac14$ 处）再回到 $0$；在 $[0,1]$ 上由 $0$ 升到 $\dfrac14$（$x=\dfrac14$ 处）再回到 $0$；在 $[1,2]$ 上由 $0$ 单调降到 $-2$；在 $[2,3)$ 上由 $-2$ 单调降到 $-4$．
+于是 $c\in\left(-\dfrac14,0\right)$ 时 $n(c)=3$，$c=-\dfrac14$ 时 $n(c)=2$，$c\in\left(-2,-\dfrac14\right]$ 时 $n(c)=1$，$c\in[-4,-2]$ 时 $n(c)=1$，$c\in\left(0,\dfrac14\right)$ 时 $n(c)=2$，$c=\dfrac14$ 时 $n(c)=1$．
+要使 $N(b)=1$，只能落在一个周期贡献 $1$ 个、其余周期贡献 $0$ 的区间，即需 $-\dfrac{15}4&lt;b&lt;-\dfrac14$（端点 $b=-\dfrac{15}4$ 时 $b+4=\dfrac14$ 又贡献 $1$ 个，共 $2$ 个；$b=-\dfrac14$ 时 $n=2$，亦不合）．
+再由 $b\to b+4$ 的平移不变性，$b\in\left(4k-\dfrac{15}4,\;4k-\dfrac14\right)$，即 $\left(4k+\dfrac14,\;4k+\dfrac{15}4\right)$（$k\in\mathbb Z$）．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S258" t="n">
+        <v>5</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-065-E1</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V258" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈01f x= x1g x= f x- x - b / 当[，]时，()2」，$x^{\frac12}$ 的指数与分段区间全塌，四个选项的 $4k+\frac{15}4$ 也压成 「1 15 / 44」两截。由详解「$f(-x)=-f(x)$，$f(-x-1)=f(x-1)$，$f(x-2)=-f(x)$，即 $f(x+2)=-f(x)$，∴$f(x+4)=f(x)$，∴$f(x)$ 的周期为 $4$」与「$x\in[0,1]$ 时 $f(x)=x^{\frac12}=\sqrt{x}$」还原。
+**数值校验**（取 $b=-2\in(-\frac{15}4,-\frac14)$）：$\varphi(x)=-2$ 在 $[1,2]$ 上恰一解（$f(x)=x-2$，$\sqrt{2-x}=x-2$ → $x\approx1.618$），其余周期贡献 $0$，共 $1$ 个 ✓。
+端点核查：$b=-\frac14$ 时直线与 $f$ 在 $x=-\frac14$ 处相切，另在 $[1,2]$ 上还有一个交点，共 $2$ 个 ✗；$b=-\frac{15}4$ 时除 $[2,3)$ 上一解外，$b+4=\frac14$ 又在 $[0,1]$ 上产生相切，共 $2$ 个 ✗。故两端均为开区间 ✓。
+**核心陷阱**：只看到「相切」会得到 $b=-\frac14$ 之类的孤立值，但相切处其实是 $2$ 个交点（切点 + 另一段上的交点），必须整周期地数交点重数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>M-H0259</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>M-T-065(函数与导数 / 零点与图像交点 · 借助周期性)</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>定义在 $\mathbb R$ 上的偶函数 $f(x)$ 满足 $f(2-x)=f(x)$，且当 $x\in[1,2]$ 时，$f(x)=\ln x-x+1$，若函数 $g(x)=f(x)+mx$ 有 $7$ 个零点，则实数 $m$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac{1-\ln2}{8},\dfrac{1-\ln2}{6}\right)\cup\left(\dfrac{\ln2-1}{6},\dfrac{\ln2-1}{8}\right)$</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac{\ln2-1}{6},\dfrac{\ln2-1}{8}\right)$</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac{1-\ln2}{8},\dfrac{1-\ln2}{6}\right)$</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac{1-\ln2}{8},\dfrac{\ln2-1}{6}\right)$</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(2-x)=f(x)$ 与 $f$ 为偶函数（$f(-x)=f(x)$）得 $f(2-x)=f(-x)$，即 $f(x+2)=f(x)$，**周期为 $2$**．
+当 $x\in[1,2]$ 时 $f'(x)=\dfrac1x-1\leqslant0$，$f$ 递减，$f(1)=\ln1-1+1=0$，$f(2)=\ln2-2+1=\ln2-1\approx-0.307$．
+由周期性与偶性，$f$ 的图象是以 $2$ 为周期、在 $[\ln2-1,\,0]$ 之间起伏的波：**奇数点处取最大值 $0$，偶数点处取最小值 $\ln2-1$**．
+$g(x)=0\iff f(x)=-mx$，即 $y=f(x)$ 与过原点的直线 $y=-mx$ 的交点个数．
+随直线绕原点转动，每当它扫过一个波谷点，交点数就变化 $2$．由详解所列的临界位置：
+过 $A(-6,\ln2-1)$ 时 $6$ 个交点，此时 $-m=\dfrac{\ln2-1}{-6}$，即 $m=\dfrac{\ln2-1}{6}$；
+过 $B(-8,\ln2-1)$ 时 $8$ 个交点，此时 $m=\dfrac{\ln2-1}{8}$；
+过 $C(6,\ln2-1)$ 时 $6$ 个交点，此时 $m=\dfrac{1-\ln2}{6}$；
+过 $D(8,\ln2-1)$ 时 $8$ 个交点，此时 $m=\dfrac{1-\ln2}{8}$．
+于是恰有 $7$ 个交点对应两段：
+$m\in\left(\dfrac{1-\ln2}{8},\dfrac{1-\ln2}{6}\right)$ 或 $m\in\left(\dfrac{\ln2-1}{6},\dfrac{\ln2-1}{8}\right)$
+（注意 $\ln2-1&lt;0$，故 $\dfrac{\ln2-1}{6}&lt;\dfrac{\ln2-1}{8}$）．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S259" t="n">
+        <v>5</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-065-V1</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V259" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈[1,2]时，f(x) = lnx - x + 1」，区间与式子尚完整，但四个选项的分式被压成多行数字（「1 - ln2 1 - ln2ln2 - 1 ln2 - 1 / 8668」），分母 $6$、$8$ 与分子 $\pm(1-\ln2)$ 的配对完全丢失。
+**还原依据**：详解明确给出四个临界点 $A(-6,\ln2-1)$、$B(-8,\ln2-1)$、$C(6,\ln2-1)$、$D(8,\ln2-1)$ 及其对应的交点数 $6,8,6,8$，并给出结论 $m\in(\frac{1-\ln2}{8},\frac{1-\ln2}{6})\cup(\frac{\ln2-1}{6},\frac{\ln2-1}{8})$。据此反推选项 A 为并集形式，B、C 各为其中一半，D 为交叉干扰项。
+**数值校验**：$\ln2-1\approx-0.3069$。$\frac{1-\ln2}{8}\approx0.03836$、$\frac{1-\ln2}{6}\approx0.05115$；$\frac{\ln2-1}{6}\approx-0.05115$、$\frac{\ln2-1}{8}\approx-0.03836$。取 $m=0.045$（在第一段内）：直线 $y=-0.045x$，与振幅 $0.307$、周期 $2$ 的波相交，在 $x&gt;0$ 侧约 $x&lt;6.8$ 范围内相交，数得约 $7$ 个 ✓。
+**关键**：交点数从 $6$ 跳到 $8$（跨过波谷点时一次增加 $2$），中间不存在 $7$ 个的临界值，故两个开区间内恒为 $7$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>M-H0260</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>M-T-065(函数与导数 / 零点与图像交点 · 借助周期性)</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>已知定义域为 $\mathbb R$ 的奇函数 $f(x)$ 满足 $f(x+1)=f(3-x)$，当 $x\in(0,2]$ 时，$f(x)=-x^{2}+4$，则函数 $y=f(x)-a$（$a\in\mathbb R$）在区间 $[-4,8]$ 上的零点个数最多时，所有零点之和为 ____．</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>$14$</t>
+        </is>
+      </c>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(x+1)=f(3-x)$，令 $t=3-x$ 即 $x=3-t$，得 $f(4-t)=f(t)$，即 $f(-u)=f(u+4)$（取 $u=-t$）．又 $f$ 为奇函数，$f(-u)=-f(u)$，故 $f(u+4)=-f(u)$，于是 $f(u+8)=-f(u+4)=f(u)$，**周期为 $8$**．
+当 $x\in(0,2]$ 时 $f(x)=-x^{2}+4$，有 $f(2)=0$、$f(1)=3$；由奇函数 $f(0)=0$、$f(-2)=-f(2)=0$；由 $f(u+4)=-f(u)$ 得 $f(4)=-f(0)=0$、$f(6)=-f(2)=0$．
+**零点个数**：即 $y=f(x)$ 与水平线 $y=a$ 在 $[-4,8]$ 上的交点数．$f$ 在一个周期内取遍 $[-4,4]$，水平线越靠近 $0$ 交点越多；当 $a=0$ 时交点最多（穿过所有极值之间的上升段与下降段）．
+此时零点为 $f(x)=0$ 的点：由周期性，$x=-4,\,-2,\,0,\,2,\,4,\,6,\,8$ 共 $7$ 个．
+（验证：$f(-4)=f(4)=0$，$f(-2)=f(6)=-f(2)=0$，$f(0)=0$，$f(2)=0$，$f(4)=-f(0)=0$，$f(6)=-f(2)=0$，$f(8)=f(0)=0$．）
+所有零点之和 $=-4+(-2)+0+2+4+6+8=14$．</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S260" t="n">
+        <v>5</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-065-V2</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V260" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈0,2f x=-x2 + 4y = f x- a a ∈R / ([时，)(，则函数)()(」，区间括号、平方上标、复合关系全塌。由详解「$f(-x)=-f(x)$，$f(x+4)=f(-x)$，∴$f(x+4)=-f(x)$，∴函数 $f(x)$ 为周期函数，且周期为 $8$」与「当 $x\in(0,2]$ 时，$f(x)=-x^{2}+4$」还原。
+**数值/结构校验**：$f(2)=-4+4=0$ ✓；$f(0)=0$（奇）✓；$f(4)=-f(0)=0$ ✓；$f(6)=-f(2)=0$ ✓；$f(8)=f(0)=0$ ✓；$f(-2)=-f(2)=0$ ✓；$f(-4)=f(4)=0$ ✓。共 $7$ 个零点，和 $=14$ ✓。
+**注**：区间 $(0,2]$ 写成闭区间会与奇函数 $f(0)=0$ 冲突（$-0^2+4=4\ne0$），故左端点必须开。</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>M-H0261</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>M-T-065(函数与导数 / 零点与图像交点 · 借助周期性)</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $y=f(x)$ 的定义域是 $[0,+\infty)$，满足
+$f(x)=\begin{cases}2x, &amp; 0\leqslant x&lt;1,\\x^{2}-4x+5, &amp; 1\leqslant x&lt;3,\\-2x+8, &amp; 3\leqslant x&lt;4,\end{cases}$且 $f(x+4)=f(x)+a$．若存在实数 $k$，使函数 $g(x)=f(x)+k$ 在区间 $[0,2021]$ 上恰好有 $2021$ 个零点，则实数 $a$ 的取值范围为 ____．</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac{1}{505},\dfrac{1}{504}\right)$</t>
+        </is>
+      </c>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>$g(x)=0\iff f(x)=-k$，即水平线 $y=-k$ 与 $y=f(x)$ 的交点个数．
+**一个周期内**：在 $[0,4)$ 上，$f$ 的图象为
+$[0,1)$：$2x$ 由 $0$ 升到 $2$；
+$[1,3)$：$(x-2)^{2}+1$ 由 $2$ 降到 $1$（$x=2$）再升到 $2$；
+$[3,4)$：$-2x+8$ 由 $2$ 降到 $0$．
+水平线 $y=c$ 若满足 $1&lt;c&lt;2$，则与三段分别交 $1$、$2$、$1$ 次，每周期恰 $4$ 个交点．
+由 $f(x+4)=f(x)+a$，第 $j$ 个周期 $[4j,4j+4)$ 上的图象是基础图象上移 $ja$，故需 $-k\in(1+ja,\,2+ja)$ 对所有 $j=0,1,\cdots,504$ 同时成立．
+$2021=4\times505+1$，即 $505$ 个完整周期（$j=0\sim504$）各 $4$ 个交点共 $2020$ 个，再由 $[2020,2021]$ 这 $\frac14$ 个周期补上最后 $1$ 个．
+**当 $a\geqslant0$ 时**：$-k&gt;1+ja$ 的最严条件在 $j=504$，即 $-k&gt;1+504a$；$-k&lt;2+ja$ 的最严条件在 $j=0$，即 $-k&lt;2$．需 $1+504a&lt;2$，得 $a&lt;\dfrac1{504}$．此时 $-k\in(1+504a,2)$ 非空，且 $[2020,2021]$ 上 $f$ 由 $505a$ 升到 $2+505a$，因 $-k&gt;1+504a&gt;505a$（$a&lt;1$ 时）且 $-k&lt;2&lt;2+505a$，恰 $1$ 个交点．得 $a\in\left[0,\dfrac1{504}\right)$．
+**当 $a&lt;0$ 时**：$-k&gt;1+ja$ 的最严条件在 $j=0$，即 $-k&gt;1$；$-k&lt;2+ja$ 的最严条件在 $j=505$，即 $-k&lt;2+505a$．需 $1&lt;2+505a$，得 $a&gt;-\dfrac1{505}$．此时 $-k\in(1,\,2+505a)$ 非空，且 $-k&gt;1&gt;505a$（$a&lt;0$），末段仍恰 $1$ 个交点．得 $a\in\left(-\dfrac1{505},0\right)$．
+综上，$a\in\left(-\dfrac1{505},\dfrac1{504}\right)$．</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S261" t="n">
+        <v>5</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-065-V3</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>教辅录入-第15批</t>
+        </is>
+      </c>
+      <c r="V261" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x)= 2x,0 ≤x &lt; 1 / x2- 4x + 5, 1 ≤x &lt; 3, 且f(x + 4) = f(x) + a / -2x + 8,3 ≤x &lt; 4」，分段大括号全塌、$x^2$ 上标丢失；答案「(- 1 , 1) / 505504」也被拆成两截。由详解「由 $f(x+4)=f(x)+a$ 知，函数 $f(x)$ 是以 $4$ 为周期、且每个周期上下平移 $|a|$ 个单位」「在每个周期都有 $4$ 个交点，即 $-k\in(1,2)$ 时满足条件」还原分段与答案。
+**数值校验**：$a=0$ 时 $f(2018)=f(2)+504\cdot0=1&lt;2$ ✓，$f(2021)=f(1)+505\cdot0=2&gt;1$ ✓，属区间内；$a=\frac1{504}\approx0.001984$ 时 $f(2018)=1+504\cdot\frac1{504}=2$，不满足 $&lt;2$，故右端开 ✓；$a=-\frac1{505}\approx-0.001980$ 时 $f(2021)=2+505\cdot(-\frac1{505})=1$，不满足 $&gt;1$，故左端开 ✓。
+**为什么两边不对称**：右侧只需 $505$ 个完整周期中的**极小值** $&lt;2$（共 $504$ 次平移），左侧需末段**极大值** $&gt;1$（共 $505$ 次平移），平移次数差 $1$，故分母是 $504$ 与 $505$ 而不是同一个数。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V261"/>
+  <dimension ref="A1:V275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -26009,6 +26009,1599 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>M-H0262</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>M-T-049(函数与导数 / 对称性与周期性 · 轴对称)</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=2\mathrm{e}^{|x-2|}-\dfrac{a}{2}\left(2^{x-2}+2^{2-x}\right)-a^{2}$ 有唯一零点，则负实数 $a=$（　　）</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>$-2$</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>$-\dfrac12$</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>$-1$</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>$-\dfrac12$ 或 $-1$</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>设 $t=x-2$，则 $|x-2|=|t|$，$2^{x-2}+2^{2-x}=2^{t}+2^{-t}$，
+$f(x)=2\mathrm{e}^{|t|}-\dfrac{a}{2}\left(2^{t}+2^{-t}\right)-a^{2}$．
+令 $g(t)=2\mathrm{e}^{|t|}-\dfrac{a}{2}\left(2^{t}+2^{-t}\right)$，则 $g(-t)=g(t)$，$g$ 为偶函数．
+$f$ 有唯一零点 $\iff$ $g(t)=a^{2}$ 有唯一解．由偶性，解必关于 $t=0$ 成对出现，唯一解只能是 $t=0$：
+$g(0)=2\mathrm{e}^{0}-\dfrac{a}{2}(1+1)=2-a=a^{2}$，
+即 $a^{2}+a-2=0$，解得 $a=-2$ 或 $a=1$．
+题设 $a$ 为**负实数**，故 $a=-2$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S262" t="n">
+        <v>5</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-049-E1</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V262" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= 2e |x-2|- a (2x-2+ 22-x)- a2」，$\mathrm{e}^{|x-2|}$ 的指数与绝对值、$2^{x-2}$ 的上标全丢，$\dfrac{a}{2}$ 的分数线也丢失（详解里写作「$\frac12 a$」）。由详解「设 $x-2=t$，则 $f(x)=2\mathrm{e}^{|t|}-\frac12 a(2^t+2^{-t})-a^2$ 有唯一零点，则 $2\mathrm{e}^{|t|}-\frac12 a(2^t+2^{-t})=a^2$；$g(t)$ 为偶函数；此交点的横坐标为 $0$，∴$2-a=a^2$，解得 $a=-2$ 或 $a=1$（舍去）」还原。
+**数值校验**：$a=-2$ 时 $f(x)=2\mathrm{e}^{|x-2|}+(2^{x-2}+2^{2-x})-4$。$x=2$：$2\cdot1+(1+1)-4=0$ ✓ 确为零点；$x=3$：$2\mathrm{e}+(2+0.5)-4\approx5.44+2.5-4=3.94&gt;0$；$x=2.5$：$2\mathrm{e}^{0.5}+(2^{0.5}+2^{-0.5})-4\approx3.30+2.12-4=1.42&gt;0$。两侧均为正，零点唯一 ✓。
+**排除 $a=1$**：题设「负实数」已排除，不依赖计算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>M-H0263</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>M-T-049(函数与导数 / 对称性与周期性 · 轴对称)</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=(x^{2}-4x)\left(\mathrm{e}^{x-2}-\mathrm{e}^{2-x}\right)+x+1$ 在区间 $[-1,5]$ 的值域为 $[m,M]$，则 $m+M=$（　　）</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>$6$</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>$8$</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>先看辅助函数 $h(u)=(u^{2}-4)\left(\mathrm{e}^{u}-\mathrm{e}^{-u}\right)+u$：
+$h(-u)=\bigl((-u)^{2}-4\bigr)\left(\mathrm{e}^{-u}-\mathrm{e}^{u}\right)-u=(u^{2}-4)\cdot\left[-\left(\mathrm{e}^{u}-\mathrm{e}^{-u}\right)\right]-u=-h(u)$，
+故 $h$ 为奇函数，图象关于原点对称，在对称区间上最大值与最小值之和为 $0$．
+再把 $f$ 化成 $h$ 的平移形式（注意 $x^{2}-4x=(x-2)^{2}-4$）：
+$f(x)=\bigl[(x-2)^{2}-4\bigr]\left(\mathrm{e}^{x-2}-\mathrm{e}^{2-x}\right)+x+1$
+$\phantom{f(x)}=h(x-2)+3$．
+即 $f$ 的图象由 $h$ 的图象**向右平移 $2$ 个单位、向上平移 $3$ 个单位**得到，故 $f$ 关于点 $(2,3)$ 中心对称．
+区间 $[-1,5]$ 的中点恰为 $\dfrac{-1+5}{2}=2$，关于 $x=2$ 对称，
+所以 $m+M=2\times3=6$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S263" t="n">
+        <v>5</v>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-049-V1</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V263" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= (x2- 4x)(ex-2- e2-x)+ x + 1」，$\mathrm{e}^{x-2}$、$\mathrm{e}^{2-x}$ 的指数与 $x^2$ 的上标全塌，区间 $[-1,5]$ 的括号还算完整。由详解「$y=(x^2-4)(\mathrm{e}^x-\mathrm{e}^{-x})+x$ 在 $[-3,3]$ 上为奇函数，图象关于原点对称，$f(x)=[(x-2)^2-4](\mathrm{e}^{x-2}-\mathrm{e}^{2-x})+x-2+3$ 是将上述函数图象向右平移 $2$ 个单位、向上平移 $3$ 个单位得到，所以 $f(x)$ 图象关于 $(2,3)$ 对称，则 $m+M=6$」还原。
+**结构校验**：$x^2-4x=(x-2)^2-4$ ✓；$x+1=(x-2)+3$ ✓，故 $f(x)=h(x-2)+3$ 成立。区间 $[-1,5]$ 中点 $=2$ ✓ 与对称中心横坐标一致，这是 $m+M=2\times3$ 能成立的前提。
+**数值校验**：$x=2$ 时 $f(2)=(4-8)(1-1)+3=3$（即中心点）；$x=5$：$f(5)=(25-20)(\mathrm{e}^3-\mathrm{e}^{-3})+6\approx5\times20.04+6=106.2$；$x=-1$：$f(-1)=(1+4)(\mathrm{e}^{-3}-\mathrm{e}^3)+0\approx5\times(-20.04)=-100.2$；$f(5)+f(-1)\approx6=2\times3$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>M-H0264</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>M-T-049(函数与导数 / 对称性与周期性 · 轴对称)</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$（$x\in\mathbb R$）满足 $f(x)=f(a-x)$，若函数 $y=\left|x^{2}-ax-5\right|$ 与 $y=f(x)$ 图象的交点为 $(x_{1},y_{1})$，$(x_{2},y_{2})$，$\cdots$，$(x_{m},y_{m})$，且 $\sum\limits_{i=1}^{m}x_{i}=2m$，则 $a=$（　　）</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P264" s="2" t="inlineStr">
+        <is>
+          <t>**两条对称轴**：
+由 $f(x)=f(a-x)$ 知 $y=f(x)$ 关于直线 $x=\dfrac{a}{2}$ 对称；
+又 $x^{2}-ax-5=\left(x-\dfrac{a}{2}\right)^{2}-\dfrac{a^{2}}{4}-5$，取绝对值后 $y=\left|x^{2}-ax-5\right|$ 也关于 $x=\dfrac{a}{2}$ 对称．
+**交点配对**：两图象都关于同一直线对称，故交点成对关于该直线对称，每对横坐标之和为 $2\cdot\dfrac{a}{2}=a$．
+当 $m$ 为偶数时，共 $\dfrac{m}{2}$ 对，$\sum x_{i}=\dfrac{m}{2}\cdot a=\dfrac{ma}{2}$；
+当 $m$ 为奇数时，$m-1$ 个交点配成 $\dfrac{m-1}{2}$ 对，余下 $1$ 个交点落在对称轴上（横坐标为 $\dfrac{a}{2}$），
+$\sum x_{i}=\dfrac{m-1}{2}\cdot a+\dfrac{a}{2}=\dfrac{ma}{2}$．
+两种情形都得 $\sum x_{i}=\dfrac{ma}{2}$．
+由题设 $\sum x_{i}=2m$，得 $\dfrac{ma}{2}=2m$，即 $a=4$．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S264" t="n">
+        <v>5</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-049-V2</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V264" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) (x ∈R) 满足f(x) = f(a - x)，若函数y = |x2- ax- 5| 与y = f(x) 图象的交点为(x，y)，(x，y)，⋯，(x，y)，且x= 2m」，绝对值竖线、平方上标、$\sum$ 与下标 $i$ 全丢，求和式 $\sum_{i=1}^{m}x_i$ 被压成「x= 2m」。由详解「$f(x)$ 的图象关于直线 $x=\frac{a}{2}$ 对称，又 $y=|x^2-ax-5|$ 的图象关于直线 $x=\frac{a}{2}$ 对称」与「当 $m$ 为偶数时…$x_1+x_2+\cdots+x_m=m\cdot\frac{a}{2}=2m$，解得 $a=4$」还原。
+**结构校验**：$x^2-ax-5=(x-\frac{a}{2})^2-\frac{a^2}{4}-5$ ✓，取绝对值后确实关于 $x=\frac{a}{2}$ 对称 ✓。
+**关键**：$m$ 为奇数时那个「落在对称轴上的交点」不能漏，补上 $\frac{a}{2}$ 后结果仍是 $\frac{ma}{2}$，所以不用知道 $m$ 的奇偶就能解出 $a$——这是本题的设计巧妙之处。</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>M-H0265</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>M-T-049(函数与导数 / 对称性与周期性 · 轴对称)</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac{\sin\pi x}{(x^{2}+1)(x^{2}-2x+2)}$，下面是关于此函数的有关命题，其中正确的有（　　）
+① 函数 $f(x)$ 是周期函数；
+② 函数 $f(x)$ 既有最大值又有最小值；
+③ 函数 $f(x)$ 的定义域为 $\mathbb R$，且其图象有对称轴；
+④ 对于任意的 $x\in(-1,0)$，$f'(x)&lt;0$（$f'(x)$ 是函数 $f(x)$ 的导函数）</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>②③</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>①③</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>②④</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>①②③</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>**定义域**：$x^{2}+1&gt;0$，$x^{2}-2x+2=(x-1)^{2}+1&gt;0$，分母恒不为 $0$，故定义域为 $\mathbb R$，③的前半句成立．
+**对称轴**：验证 $f(1-x)$：
+分子 $\sin\bigl(\pi(1-x)\bigr)=\sin(\pi-\pi x)=\sin\pi x$；
+分母 $(1-x)^{2}+1=x^{2}-2x+2$，$(1-x)^{2}-2(1-x)+2=(1-2x+x^{2})-2+2x+2=x^{2}+1$；
+故分母 $=\left(x^{2}-2x+2\right)\left(x^{2}+1\right)$，与原分母相同．
+于是 $f(1-x)=f(x)$，图象关于直线 $x=\dfrac12$ 对称，③成立．
+**最值**：$f$ 在 $\mathbb R$ 上连续，且 $x\to\pm\infty$ 时 $|f(x)|\leqslant\dfrac{1}{(x^{2}+1)\cdot1}\to0$，故 $f$ 必取到最大值与最小值，②成立．
+**非周期**：$f$ 的零点为一切整数 $x=0,\pm1,\pm2,\cdots$，但 $|f|$ 在这些零点附近的振幅随 $|x|$ 增大而衰减（如 $f\!\left(\dfrac12\right)=\dfrac{1}{\frac54\cdot\frac54}=\dfrac{16}{25}$，而 $f\!\left(\dfrac{5}{2}\right)$ 明显更小），不满足周期函数的要求，①错误．
+④ 由对称性，$f$ 在 $\left(-1,-\dfrac12\right)$ 与 $\left(-\dfrac12,0\right)$ 上单调性相反，$f'(x)&lt;0$ 不可能恒成立，④错误．
+综上，②③正确，选 A．</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S265" t="n">
+        <v>5</v>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-049-V3</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V265" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= sinπx / (x2+ 1)(x2- 2x + 2)」，$\sin\pi x$ 尚完整，但分母的平方上标全塌、分式关系被拆成两行；四个序号命题也挤在一起。由详解「函数 $f(x)$ 定义域为 $\mathbb R$」「又因为函数满足 $f(x)=\frac{\sin\pi x}{(x^2+1)(x^2-2x+2)}=\frac{\sin\pi(1-x)}{[(1-x)^2+1][(1-x)^2-2(1-x)+2]}=f(1-x)$，所以函数关于直线 $x=\frac12$ 对称」「故②③正确」还原。
+**完整展开验证（这题的关键一步）**：
+$(1-x)^2-2(1-x)+2=(1-2x+x^2)-2+2x+2=x^2+1$ ✓
+$(1-x)^2+1=x^2-2x+2$ ✓
+两因子相乘 $(x^2-2x+2)(x^2+1)$ 与原分母一致 ✓，故 $f(1-x)=f(x)$ 成立。
+**数值校验**：$f(\frac12)=\frac{\sin(\pi/2)}{(\frac14+1)(\frac14-1+2)}=\frac{1}{\frac54\cdot\frac54}=\frac{16}{25}=0.64$；$f(0)=0$，$f(1)=\frac{0}{2\cdot1}=0$，$f(-1)=\frac{0}{2\cdot5}=0$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>M-H0266</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>M-T-050(函数与导数 / 对称性与周期性 · 中心对称和轴对称构造出周期性)</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 为定义域为 $\mathbb R$ 的偶函数，且满足 $f\!\left(\dfrac12+x\right)=f\!\left(\dfrac32-x\right)$，当 $x\in[-1,0]$ 时，$f(x)=-x$．若函数 $F(x)=f(x)+\dfrac{x+4}{1-2x}$ 在区间 $[-9,10]$ 上的所有零点之和为 ____．</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>$5$</t>
+        </is>
+      </c>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>**求周期**：由 $f\!\left(\dfrac12+x\right)=f\!\left(\dfrac32-x\right)$，令 $t=\dfrac12+x$ 则 $\dfrac32-x=2-t$，得 $f(t)=f(2-t)$，即 $f$ 关于直线 $x=1$ 对称．
+又 $f$ 为偶函数，$f(-x)=f(x)$，于是
+$f(x+2)=f\bigl(2-(-x)\bigr)=f(-x)=f(x)$，
+故 $T=2$．结合 $x\in[-1,0]$ 时 $f(x)=-x$ 及偶性，得 $f(x)=|x-2k|$（$x\in[2k-1,2k+1]$，$k\in\mathbb Z$），值域 $[0,1]$．
+**转化零点**：$F(x)=0\iff f(x)=-\dfrac{x+4}{1-2x}=\dfrac{x+4}{2x-1}$．记 $h(x)=\dfrac{x+4}{2x-1}=\dfrac12+\dfrac{9}{2(2x-1)}$．
+**对称性**：
+对 $f$，由 $f(x)=|x-2k|$ 可验 $f\!\left(\dfrac12+u\right)+f\!\left(\dfrac12-u\right)=1$，即 $f$ 关于点 $\left(\dfrac12,\dfrac12\right)$ 中心对称；
+对 $h$，$h\!\left(\dfrac12+u\right)+h\!\left(\dfrac12-u\right)=\left(\dfrac12+\dfrac{9}{4u}\right)+\left(\dfrac12-\dfrac{9}{4u}\right)=1$，也关于 $\left(\dfrac12,\dfrac12\right)$ 中心对称．
+**配对求和**：两图象交点成对关于 $\left(\dfrac12,\dfrac12\right)$ 对称，每对横坐标之和为 $1$．
+由图象（$f$ 值域 $[0,1]$，$h$ 在 $[-9,10]$ 上从 $\approx0.26$ 降到 $\approx0.38$ 再在 $x=\frac12$ 处断开、两支分别趋向 $\pm\infty$）可知共有 $10$ 个交点，即 $5$ 对，故所有零点之和 $=5\times1=5$．</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S266" t="n">
+        <v>5</v>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-050-E1</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V266" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本把 $F(x)$ 拆成三行：「F(x) = f(x) + / x + 4 / 在区间[-9, 10] 上的所有零点之和为．1 - 2x」，分子 $x+4$ 与分母 $1-2x$ 分离；$f(\frac12+x)=f(\frac32-x)$ 的分数也全丢成「f( + x) = f( - x) / 2 2」（中间的 $\frac12$、$\frac32$ 被压成孤立的「1」「3」）。由详解「足 $f(\frac12+x)=f(\frac32-x)$，∴$f(x)=f(2-x)$，又因函数 $f(x)$ 为偶函数，∴$f(x)=f(-x)=f(2+x)$，即 $f(x)=f(2+x)$，∴$T=2$；令 $F(x)=0$，$f(x)=\frac{x+4}{2x-1}$，即求 $y=f(x)$ 与 $y=\frac{x+4}{2x-1}$ 交点横坐标之和；$y=\frac{x+4}{2x-1}=\frac12+\frac{9}{2(2x-1)}$；由图象可知有 $10$ 个交点，并且关于 $(\frac12,\frac12)$ 中心对称，其和为 $\frac{10}{2}=5$」还原。
+**结构校验**：$\frac{x+4}{2x-1}=\frac{\frac12(2x-1)+\frac12+4}{2x-1}=\frac12+\frac{9}{2(2x-1)}$ ✓。$f(\frac12+u)+f(\frac12-u)=1$：取 $u=0.3$，$f(0.8)=0.8$、$f(0.2)=0.2$，和 $=1$ ✓；取 $u=0.7$，$f(1.2)=|1.2-2|=0.8$、$f(-0.2)=0.2$，和 $=1$ ✓。
+**注意**：$x=\frac12$ 是 $h$ 的渐近线，交点不会落在此处，所以 $10$ 个交点恰好配成 $5$ 对、没有落单的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>M-H0267</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>M-T-050(函数与导数 / 对称性与周期性 · 中心对称和轴对称构造出周期性)</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>定义在 $\mathbb R$ 上的奇函数 $f(x)$ 满足 $f(2-x)=f(x)$，且在 $[0,1]$ 上单调递减．若方程 $f(x)=-1$ 在 $[0,1]$ 上有实数根，则方程 $f(x)=-1$ 在区间 $[-1,11]$ 上所有实根之和是（　　）</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>$30$</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>$14$</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>$12$</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>$6$</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>**周期与对称性**：由 $f(2-x)=f(x)$ 知 $f$ 关于直线 $x=1$ 对称；又 $f$ 为奇函数，$f(-x)=-f(x)$，故
+$f(x+2)=f\bigl(-(x+2)\bigr)$ 的反号…更直接地：$f(x+2)=f\bigl(2-(-x)\bigr)=f(-x)=-f(x)$，
+于是 $f(x+4)=-f(x+2)=f(x)$，**$T=4$**．
+**一个周期内的根**：取周期 $[-1,3]$．由 $f$ 在 $[0,1]$ 上递减且为奇函数，$f(0)=0$，$f(2)=f(2-2)=f(0)=0$；
+$x\in(0,1)$ 时 $f(x)&lt;0$，$x\in(1,2)$ 时 $f(x)&lt;0$，$x\in(-1,0)$ 与 $x\in(2,3)$ 时 $f(x)&gt;0$．
+故 $f(x)=-1$ 在 $(0,1)$ 与 $(1,2)$ 各有一根（$f$ 在两段上单调，各至多一根），在 $(-1,0)$、$(2,3)$ 上无根，共 $2$ 根．
+由关于 $x=1$ 对称，这两根之和为 $2$．
+**三个周期**：$[-1,11]$ 长度 $12=3\times4$，即 $[-1,3]$、$[3,7]$、$[7,11]$．设第一周期两根为 $r_{1},r_{2}$（$r_{1}+r_{2}=2$），则三周期的根依次为 $r_{1},r_{2}$、$r_{1}+4,r_{2}+4$、$r_{1}+8,r_{2}+8$．
+总和 $=(r_{1}+r_{2})+(r_{1}+r_{2}+8)+(r_{1}+r_{2}+16)=2+10+18=30$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S267" t="n">
+        <v>5</v>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-050-V1</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V267" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干里「则方程f )x(= 1 在区间[-1,11]上」的 $=-1$ 被提取成了 $=1$（负号丢失），但**详解从头到尾讨论的都是 $f(x)=-1$**，且答案 $30$ 只与 $f(x)=-1$ 相容，据此还原。
+★ 区间 $[0,1]$ 在提取文本里作「[0,1(」，右括号是私用区字符，已还原。
+**数值/结构校验**：由 $f(x+2)=-f(x)$ 得 $f(2)= -f(0)=0$，与 $f(2)=f(2-2)=f(0)=0$ 一致 ✓。$x\in(0,1)$：$f$ 递减且 $f(0)=0$ → $f(x)&lt;0$ ✓ 可能有 $f(x)=-1$ 的根；$x\in(1,2)$：由关于 $x=1$ 对称，$f(x)=f(2-x)$，$2-x\in(0,1)$，故 $f(x)&lt;0$ ✓；$x\in(-1,0)$：奇函数，$f(x)=-f(-x)$，$-x\in(0,1)$，$f(-x)&lt;0$ → $f(x)&gt;0$ ✓ 无根。总和 $2+10+18=30$ ✓ 与答案 A 一致。
+**周期判定**：$f(x+2)=f(2-(-x))=f(-x)=-f(x)$ 这一步是关键，合并使用「对称轴 $x=1$」与「奇函数」两个条件，缺一不可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>M-H0268</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>M-T-050(函数与导数 / 对称性与周期性 · 中心对称和轴对称构造出周期性)</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>已知定义域为 $\mathbb R$ 的函数 $f(x)$ 的图象关于原点对称，且 $f(3-x)+f(-x)=0$．若曲线 $y=f(x)$ 在 $\bigl(6,f(6)\bigr)$ 处切线的斜率为 $4$，则曲线 $y=f(x)$ 在 $\bigl(-2022,f(-2022)\bigr)$ 处的切线方程为（　　）</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>$y=-4x-8088$</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>$y=4x+8088$</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>$y=-\dfrac14 x-\dfrac{1011}{2}$</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>$y=\dfrac14 x+\dfrac{1011}{2}$</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>由图象关于原点对称知 $f$ 为奇函数，$f(0)=0$．
+**求周期**：已知 $f(3-x)+f(-x)=0\;(1)$；将其中的 $x$ 换成 $x-3$，得 $f(6-x)+f(3-x)=0\;(2)$．
+$(2)-(1)$ 得 $f(6-x)-f(-x)=0$，即 $f(6-x)=f(-x)$．令 $u=-x$，得 $f(6+u)=f(u)$，**$T=6$**．
+**定点**：$-2022=-337\times6$，故 $f(-2022)=f(0)=0$．
+**定斜率**：$f$ 可导且以 $6$ 为周期，对 $f(x+6)=f(x)$ 两边求导得 $f'(x+6)=f'(x)$，即 $f'$ 也以 $6$ 为周期．
+故 $f'(-2022)=f'(0)=f'(6)=4$（题设 $x=6$ 处切线斜率为 $4$）．
+**写方程**：过点 $\bigl(-2022,0\bigr)$、斜率为 $4$ 的切线为
+$y-0=4\bigl(x+2022\bigr)$，即 $y=4x+8088$．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S268" t="n">
+        <v>5</v>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-050-V2</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V268" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本把选项 C、D 压成两截：「C. y =- x - / 4242」与「D. y = x + / 4242」，实为 $y=-\frac14x-\frac{1011}{2}$ 与 $y=\frac14x+\frac{1011}{2}$（$\frac{1011}{2}=505.5$，提取时分子 $1011$、$1$ 与分母 $4$、$2$ 散开成「4 2 4 2」）。由详解「因为 $f(3-x)+f(-x)=0$，$f(6-x)+f(3-x)=0$，两式相减可得 $f(6-x)=f(-x)$，故 $T=6$，故 $f(-2022)=f(0)=0$；因为 $f'(-2022)=f'(0)=f'(6)=4$，故所求切线方程为 $y=4x+8088$」还原。
+**数值校验**：$-2022=-337\times6$ ✓，故 $f(-2022)=f(0)=0$ ✓；$4\times2022=8088$ ✓ 与选项 B 一致。干扰项 A 是斜率取 $-4$ 的结果，C/D 是把周期误判或斜率误取 $\pm\frac14$ 的结果。
+**关键**：「原函数与导函数具有相同的周期性」这一步不能省，否则无法把 $x=6$ 处的斜率搬到 $x=-2022$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>M-H0269</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>M-T-050(函数与导数 / 对称性与周期性 · 中心对称和轴对称构造出周期性)</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>若函数 $y=f(x)$ 是 $\mathbb R$ 上的奇函数，又 $y=f(x+1)$ 为偶函数，且 $-1\leqslant x_{1}&lt;x_{2}\leqslant1$ 时，$\bigl[f(x_{1})-f(x_{2})\bigr](x_{1}-x_{2})&gt;0$，比较 $f(2017)$，$f(2018)$，$f(2019)$ 的大小为（　　）</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>$f(2017)&lt;f(2018)&lt;f(2019)$</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>$f(2018)&lt;f(2017)&lt;f(2019)$</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>$f(2018)&lt;f(2019)&lt;f(2017)$</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>$f(2019)&lt;f(2018)&lt;f(2017)$</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>**周期**：$f$ 为奇函数，故 $f(-x)=-f(x)$；$f(x+1)$ 为偶函数，故 $f(-x+1)=f(x+1)$．
+于是 $f(x+2)=f\bigl((x+1)+1\bigr)=f\bigl(-(x+1)+1\bigr)=f(-x)=-f(x)$，
+进而 $f(x+4)=-f(x+2)=f(x)$，**$T=4$**．
+**单调性**：当 $-1\leqslant x_{1}&lt;x_{2}\leqslant1$ 时 $x_{1}-x_{2}&lt;0$，由 $\bigl[f(x_{1})-f(x_{2})\bigr](x_{1}-x_{2})&gt;0$ 得 $f(x_{1})-f(x_{2})&lt;0$，即 $f(x_{1})&lt;f(x_{2})$，
+故 $f$ 在 $[-1,1]$ 上**严格递增**．
+**化到 $[-1,1]$**：
+$f(2017)=f(1+4\times504)=f(1)$；
+$f(2018)=f(2+4\times504)=f(2)$，而 $f(2)=f(-2+4)=f(-2+2\cdot2)$…更直接地：由 $f(x+2)=-f(x)$ 与 $f$ 为奇函数，$f(2)=-f(0)=0$，故 $f(2018)=0=f(0)$；
+$f(2019)=f(-1+4\times505)=f(-1)$．
+**比较**：$f$ 在 $[-1,1]$ 上递增且 $f(0)=0$，故 $f(-1)&lt;f(0)&lt;f(1)$，即 $f(2019)&lt;f(2018)&lt;f(2017)$．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S269" t="n">
+        <v>5</v>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-050-V3</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V269" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「-1 ≤x&lt; x≤1 时，[f(x) - f(x)] (x- x) &gt; 0」，下标 $1$、$2$ 全丢，与「$[f(x)-f(x)](x-x)&gt;0$」无从区分；$2017$、$2018$、$2019$ 尚完整。由详解「函数 $y=f(x)$ 的周期 $T=4$」「当 $-1\leqslant x_1&lt;x_2\leqslant1$ 时，$[f(x_1)-f(x_2)](x_1-x_2)&gt;0$ 可知函数 $y=f(x)$ 在 $[-1,1]$ 上为增函数」与「$f(2017)=f(1+4\times504)=f(1)$，$f(2018)=f(2+4\times504)=f(2)=f(0)$，$f(2019)=f(-1+4\times505)=f(-1)$，∴$f(2019)&lt;f(2018)&lt;f(2017)$」还原。
+**结构校验**：$f(x+2)=f(-(x+1)+1)$ 这一步用了 $f(x+1)$ 为偶函数（$f(1+t)=f(1-t)$，取 $t=x+1$）→ $f(x+2)=f(-x)$ ✓，再用奇性 → $=-f(x)$ ✓。故 $f(2)=-f(0)=0$，$f(2018)=f(2)=0=f(0)$ ✓。
+**数值化举例**（取 $f(x)=\sin\frac{\pi x}{2}$，满足奇、$f(x+1)$ 偶、$[-1,1]$ 递增）：$f(2017)=f(1)=1$，$f(2018)=f(2)=0$，$f(2019)=f(-1)=-1$，确实 $-1&lt;0&lt;1$ 即 $f(2019)&lt;f(2018)&lt;f(2017)$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>M-H0270</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>M-T-051(函数与导数 / 对称性与周期性 · 函数周期性问题1)</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>（2008·湖北·高考真题（文））已知 $f(x)$ 在 $\mathbb R$ 上是奇函数，且 $f(x+4)=f(x)$，当 $x\in(0,2)$ 时，$f(x)=2x^{2}$，则 $f(7)=$（　　）</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>$-2$</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>$-98$</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>$98$</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>由 $f(x+4)=f(x)$ 知 $f$ 以 $4$ 为周期，故
+$f(7)=f(7-4\times2)=f(-1)$．
+又 $f$ 为奇函数，$f(-1)=-f(1)$；而 $1\in(0,2)$，
+$f(1)=2\times1^{2}=2$，故 $f(7)=-2$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>较难</t>
+        </is>
+      </c>
+      <c r="S270" t="n">
+        <v>5</v>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-051-E1</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V270" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈(0,2) 时，f(x) = 2x2，则f(7) =」，$2x^{2}$ 的上标丢失（写成 2x2），与 $2x\cdot2$、$2x+2$ 无法区分。由详解「$f(7)=f(7-4\times2)=f(-1)=-f(1)$，而 $f(1)=2$，即 $f(7)=-2$」还原：$f(1)=2$ 只有 $f(x)=2x^{2}$ 能给出（$2\times1^{2}=2$），$2x\cdot2=4$、$2x+2=4$ 均不符 ✓。
+**干扰项**：C 的 $-98$ 是把 $f(7)$ 直接代入 $2x^{2}$ 得 $98$ 再取负；D 的 $98$ 是忘了奇函数这一步。</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>M-H0271</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>M-T-051(函数与导数 / 对称性与周期性 · 函数周期性问题1)</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>（2021·全国·模拟预测（文））已知定义在 $\mathbb R$ 上的偶函数 $f(x)$，对 $\forall x\in\mathbb R$，有 $f(x+6)=f(x)+f(3)$ 成立，当 $0\leqslant x\leqslant3$ 时，$f(x)=2x-6$，则 $f(2021)=$（　　）</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>$0$</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>$-2$</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>$-4$</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>**先证 $f(3)=0$**：在 $f(x+6)=f(x)+f(3)$ 中令 $x=-3$，得
+$f(3)=f(-3)+f(3)$．又 $f$ 为偶函数，$f(-3)=f(3)$，故
+$f(3)=f(3)+f(3)=2f(3)$，得 $f(3)=0$．
+（也可由 $x\in[0,3]$ 时 $f(x)=2x-6$ 直接算 $f(3)=2\times3-6=0$，两种途径一致。）
+**周期**：于是 $f(x+6)=f(x)+0=f(x)$，$f$ 以 $6$ 为周期．
+**求值**：$2021=6\times337-1$，故
+$f(2021)=f(-1)=f(1)$（偶性）$=2\times1-6=-4$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S271" t="n">
+        <v>5</v>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-051-V1</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V271" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当0 ≤x ≤3 时，f(x) = 2x - 6，则f (2021)=」，这一题的区间与式子尚完整，但 $\forall$、$\leqslant$ 等符号残缺。由详解「令 $x=-3$，则 $f(3)=f(-3)+f(3)=2f(3)$，所以 $f(3)=0$，故 $f(x+6)=f(x)$，所以 $f(x)$ 是周期为 $6$ 的周期函数，故 $f(2021)=f(6\times337-1)=f(-1)=f(1)=2\times1-6=-4$」还原。
+**数值校验**：$f(3)=2\times3-6=0$ ✓ 与「令 $x=-3$ 推出 $f(3)=0$」一致；$2021=6\times337-1=2022-1$ ✓；$f(1)=2-6=-4$ ✓ 与答案 C 一致。
+**关键**：$f(x+6)=f(x)+f(3)$ 本身不是周期条件，必须先证 $f(3)=0$ 才能用周期性——这正是结论 4 的用法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>M-H0272</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>M-T-051(函数与导数 / 对称性与周期性 · 函数周期性问题1)</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>（2021·江西·三模（理））已知函数 $f(x)$ 的图象关于原点对称，且满足 $f(x+1)+f(3-x)=0$，且当 $x\in(2,4)$ 时，$f(x)=-\log_{\frac12}(x-1)+m$，若 $\dfrac{f(2021)-1}{2}=f(-1)$，则 $m=$（　　）</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>$\dfrac43$</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>$\dfrac34$</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>$-\dfrac43$</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>$-\dfrac34$</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="inlineStr">
+        <is>
+          <t>**周期**：图象关于原点对称 $\Rightarrow$ $f$ 为奇函数，$f(-x)=-f(x)$．
+由 $f(x+1)+f(3-x)=0$ 得 $f(x+1)=-f(3-x)=f(x-3)$（奇性），
+即 $f(x+1)=f(x-3)$，令 $u=x-3$ 得 $f(u+4)=f(u)$，**$T=4$**．
+**求 $f(1)$**：$f(2021)=f(1+4\times505)=f(1)$；又 $f(-1)=-f(1)$．
+代入条件：$\dfrac{f(1)-1}{2}=-f(1)$，即 $f(1)-1=-2f(1)$，$3f(1)=1$，得 $f(1)=\dfrac13$．
+**求 $m$**：由奇性与周期，$f(1)=-f(-1)=-f(3)$（因 $f(-1)=f(-1+4)=f(3)$）．
+而 $3\in(2,4)$，故 $f(3)=-\log_{\frac12}(3-1)+m=-\log_{\frac12}2+m$．
+$\log_{\frac12}2=-1$（因 $\left(\dfrac12\right)^{-1}=2$），故 $f(3)=1+m$．
+于是 $f(1)=-(1+m)=-1-m=\dfrac13$，解得 $m=-\dfrac43$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S272" t="n">
+        <v>5</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-051-V2</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V272" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈(2，4) 时，f(x) =-log(x-1) + m」，$\log_{\frac12}$ 的底数被拆到下一行（「1 2」分离），与 $-\log(x-1)+m$、$-\log_2(x-1)+m$ 无法区分；条件「$\frac{f(2021)-1}{2}=f(-1)$」也被拆成「f(2021) - 1 / 2」与「= f(-1)」两处。由详解「因为 $f(x+1)=-f(3-x)=f(x-3)$，故函数 $f(x)$ 的周期为 $4$，则 $f(2021)=f(1)$；而 $f(-1)=-f(1)$，所以由 $\frac{f(2021)-1}{2}=f(-1)$ 可得 $f(1)=\frac13$；而 $f(1)=-f(3)=\log_{\frac12}(3-1)-m=\frac13$，解得 $m=-\frac43$」还原。
+**底数的判定（本题最关键的一步）**：详解写 $f(1)=-f(3)=\log_{\frac12}(3-1)-m$。若底数为 $\dfrac12$：$\log_{\frac12}2=-1$，$f(3)=-(-1)+m=1+m$，$f(1)=-(1+m)=\frac13\Rightarrow m=-\frac43$ ✓ **与答案 C 吻合**；若底数为 $2$：$\log_2 2=1$，$f(3)=-1+m$，$f(1)=1-m=\frac13\Rightarrow m=\frac23$，四个选项里没有 $\frac23$ ✗。故底数为 $\dfrac12$ 确凿。
+**数值校验**：$m=-\frac43$ 时 $f(3)=1-\frac43=-\frac13$，$f(1)=\frac13$ ✓；$\frac{f(2021)-1}{2}=\frac{\frac13-1}{2}=-\frac13=f(-1)$ ✓（$f(-1)=-f(1)=-\frac13$）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>M-H0273</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>M-T-051(函数与导数 / 对称性与周期性 · 函数周期性问题1)</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>（2021·四川·石室中学模拟预测（理））已知定义域为 $\mathbb R$ 的奇函数 $f(x)$ 满足 $f(x+4)-f(x)=f(2)$，当 $x\in(0,2)$ 时，$f(x)=2x^{2}-3x+1$，则函数 $y=f(x)$ 在 $[-4,4]$ 上零点的个数为（　　）</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>$10$</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>$11$</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>$12$</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>$13$</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t>**先证 $f(2)=0$**：在 $f(x+4)-f(x)=f(2)$ 中令 $x=-2$，得
+$f(2)-f(-2)=f(2)$，即 $f(-2)=0$．又 $f$ 为奇函数，$f(2)=-f(-2)=0$．
+**周期**：于是 $f(x+4)-f(x)=0$，即 $f(x+4)=f(x)$，$f$ 以 $4$ 为周期．
+**一个周期内的零点**：$x\in(0,2)$ 时 $f(x)=2x^{2}-3x+1=(2x-1)(x-1)$，零点为 $x=\dfrac12$ 与 $x=1$；
+由奇性 $f(0)=0$，$f\!\left(-\dfrac12\right)=-f\!\left(\dfrac12\right)=0$，$f(-1)=-f(1)=0$；又 $f(2)=f(-2)=0$．
+**推广到 $[-4,4]$**：零点集合为 $\left\{\pm\dfrac12+4k,\ \pm1+4k,\ 4k,\ 2+4k\right\}$（$k\in\mathbb Z$），落在 $[-4,4]$ 内的有
+$-4,\ -3.5,\ -3,\ -2,\ -1,\ -0.5,\ 0,\ 0.5,\ 1,\ 2,\ 3,\ 3.5,\ 4$，共 $13$ 个．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S273" t="n">
+        <v>5</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-051-V3</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V273" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈(0,2) 时，f(x) = 2x2- 3x + 1」，$2x^{2}$ 的上标丢失（写成 2x2）。由详解「令 $x=-2$，得 $f(-2+4)=f(-2)+f(2)$，即 $f(2)=f(-2)+f(2)$，所以 $f(-2)=0$；又因为 $f(x)$ 为奇函数，所以 $f(2)=-f(-2)=0$，所以 $f(x+4)=f(x)+f(2)=f(x)$」与零点列举「$-4,-3.5,-3,-2,-1,-0.5,0,0.5,1,2,3,3.5,4$，共 $13$ 个零点」还原。
+**结构校验**：$2x^{2}-3x+1=(2x-1)(x-1)$ ✓，零点 $\frac12,1$ 均在 $(0,2)$ 内 ✓。零点集合验证：由 $T=4$ 与奇性，$f(3.5)=f(-0.5)=0$、$f(-3.5)=f(0.5)=0$、$f(3)=f(-1)=0$、$f(-3)=f(1)=0$、$f(4)=f(0)=0$、$f(-4)=f(0)=0$ ✓。数一遍：$-4,-3.5,-3,-2,-1,-0.5,0,0.5,1,2,3,3.5,4$ = 13 个 ✓。
+**注意**：$f(2)=0$ 必须单独证出来，不能靠 $x\in(0,2)$ 的表达式（$2$ 不在开区间内）；这是本题第一个坎。</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>M-H0274</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>M-T-052(函数与导数 / 对称性与周期性 · 函数周期性问题2：综合)</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>（2021·全国·高考真题）已知函数 $f(x)$ 的定义域为 $\mathbb R$，$f(x+2)$ 为偶函数，$f(2x+1)$ 为奇函数，则（　　）</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>$f\!\left(-\dfrac12\right)=0$</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>$f(-1)=0$</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>$f(2)=0$</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>$f(4)=0$</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>**由 $f(x+2)$ 为偶函数**：$f(2+x)=f(2-x)$，即 $f$ 关于直线 $x=2$ 对称；换写得 $f(x+3)=f(1-x)$．
+**由 $f(2x+1)$ 为奇函数**：$f(1-2x)=-f(2x+1)$；令 $t=2x$，得 $f(1-t)=-f(1+t)$，即 $f$ 关于点 $(1,0)$ 中心对称．
+取 $t=0$ 得 $f(1)=-f(1)$，故 **$f(1)=0$**．
+**推周期**：由 $f(x+3)=f(1-x)$ 与 $f(1-x)=-f(1+x)$，得
+$f(x+3)=-f(x+1)$，令 $u=x+1$ 即 $f(u+2)=-f(u)$，
+于是 $f(u+4)=-f(u+2)=f(u)$，**$T=4$**．
+**判定各选项**：$f(-1)=f(-1+4)=f(3)=f(1+2)=-f(1)=0$，故 B 正确；
+$f\!\left(-\dfrac12\right)$、$f(2)$、$f(4)$ 均无法由已知条件确定（题中未给出足够信息），A、C、D 不能选．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S274" t="n">
+        <v>5</v>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-052-E1</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V274" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x + 2)为偶函数，f (2x + 1)为奇函数，则()」与「A. f (-)= 0」，选项 A 的 $f(-\frac12)$ 被拆成「f (-)」+「1 / 2」两处。由详解「因为函数 $f(x+2)$ 为偶函数，则 $f(2+x)=f(2-x)$，可得 $f(x+3)=f(1-x)$；因为函数 $f(2x+1)$ 为奇函数，则 $f(1-2x)=-f(2x+1)$，所以 $f(1-x)=-f(x+1)$；所以 $f(x+3)=-f(x+1)=f(x-1)$，即 $f(x)=f(x+4)$；因为函数 $F(x)=f(2x+1)$ 为奇函数，则 $F(0)=f(1)=0$，故 $f(-1)=-f(1)=0$，其它三个选项未知」还原。
+**数值/结构校验**：$F(x)=f(2x+1)$ 为奇函数 → $F(0)=f(1)=0$ ✓；$f(-1)=f(3)$（$T=4$）$=f(1+2)=-f(1)=0$ ✓ 与答案 B 一致。
+**为什么其它三个不能选**：本题只给了对称性与奇偶性，没有给出任何区间的具体表达式，所以除了能由对称中心直接定位的 $x=1$（及其周期平移点 $x=1+2k$，含 $x=-1$）之外，其余点的函数值确实无法确定。这是高考真题常见的「只问必然成立」的考法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>M-H0275</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>M-T-052(函数与导数 / 对称性与周期性 · 函数周期性问题2：综合)</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>（2021·全国·高考真题（理））设函数 $f(x)$ 的定义域为 $\mathbb R$，$f(x+1)$ 为奇函数，$f(x+2)$ 为偶函数，当 $x\in[1,2]$ 时，$f(x)=ax^{2}+b$．若 $f(0)+f(3)=6$，则 $f\!\left(\dfrac92\right)=$（　　）</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>$-\dfrac94$</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>$-\dfrac32$</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>$\dfrac74$</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>$\dfrac52$</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="inlineStr">
+        <is>
+          <t>**对称性**：$f(x+1)$ 为奇函数 $\Rightarrow$ $f(1+x)=-f(1-x)$，即 $f$ 关于点 $(1,0)$ 中心对称，得 $f(-x)=-f(2+x)\;(1)$；
+$f(x+2)$ 为偶函数 $\Rightarrow$ $f(2+x)=f(2-x)$，即 $f$ 关于直线 $x=2$ 对称，得 $f(-x)=f(4+x)\;(2)$．
+联立 $(1)(2)$：$f(x+4)=-f(x+2)$，即 $f(x+2)=-f(x)$，**$T=4$**．
+**求 $a,b$**：由 $(1)$ 取 $x=0$ 得 $f(1)=-f(1)$，故 $f(1)=0$，即 $a+b=0$；
+由 $(1)$ 取 $x=1$ 得 $f(0)=-f(3)$；又由 $(2)$ 取 $x=-1$ 得 $f(3)=f(1)$，故 $f(0)=-f(1)=0$…
+改用例行做法：由 $(1)$ 取 $x=1$ 得 $f(-1)=-f(3)$，由 $f(x+2)=-f(x)$ 取 $x=-1$ 得 $f(1)=-f(-1)$，故 $f(3)=f(1)$；
+由 $(1)$ 取 $x=0$ 得 $f(0)=-f(2)$．于是
+$f(0)+f(3)=-f(2)+f(1)=-(4a+b)+(a+b)=-3a=6$，得 $a=-2$；
+代入 $a+b=0$ 得 $b=2$．故 $x\in[1,2]$ 时 $f(x)=-2x^{2}+2$．
+**求值**：$f\!\left(\dfrac92\right)=f\!\left(\dfrac92-4\right)=f\!\left(\dfrac12\right)$；
+由 $(1)$ 取 $x=-\dfrac12$ 得 $f\!\left(\dfrac12\right)=-f\!\left(\dfrac32\right)$；
+而 $\dfrac32\in[1,2]$，$f\!\left(\dfrac32\right)=-2\times\left(\dfrac32\right)^{2}+2=-\dfrac92+2=-\dfrac52$，
+故 $f\!\left(\dfrac92\right)=\dfrac52$．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S275" t="n">
+        <v>5</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-052-V1</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>教辅录入-第19批</t>
+        </is>
+      </c>
+      <c r="V275" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈[1,2]时，f(x) = ax2+ b．若f (0)+ f (3)= 6，则f()=() / 2」，$ax^{2}$ 的上标丢失，$f(\frac92)$ 的参数被拆到下一行（孤立的「9」）。由详解「令 $x=1$，由①得 $f(0)=-f(2)=-(4a+b)$，由②得 $f(3)=f(1)=a+b$；因为 $f(0)+f(3)=6$，所以 $-(4a+b)+a+b=6\Rightarrow a=-2$；令 $x=0$，由①得 $f(1)=-f(1)\Rightarrow f(1)=0\Rightarrow b=2$，所以 $f(x)=-2x^{2}+2$；$f(\frac92)=f(\frac12)$，再利用 $f(-x)=-f(2+x)$，令 $x=-\frac12$ 代入：$\frac{f(\frac12)}{2}=-f(\frac32)=\frac52$」还原。
+**数值校验**：$a=-2,b=2$ ✓；$f(1)=-2+2=0$ ✓；$f(2)=-8+2=-6$，$f(0)=-f(2)=6$，$f(3)=f(1)=0$，$f(0)+f(3)=6$ ✓ 与题设一致；$f(\frac32)=-2\times\frac94+2=-\frac92+2=-\frac52$ ✓；$f(\frac12)=-f(\frac32)=\frac52$ ✓ 与答案 D 一致。
+**⚠ M-T-052-V2 与本题完全同题**（同年同卷同题，题干、选项、答案均相同），属教辅重复排版，不重复录入，已标记跳过。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V275"/>
+  <dimension ref="A1:V282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -27602,6 +27602,831 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>M-H0276</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>M-T-053(函数与导数 / 对称性与周期性 · 画图：放大镜)</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>设函数 $y=f(x)$ 的定义域为 $D$，如果存在非零常数 $T$，对于任意 $x\in D$，都有 $f(x+T)=T\cdot f(x)$，则称函数 $y=f(x)$ 是“似周期函数”，非零常数 $T$ 为函数 $y=f(x)$ 的“似周期”．现有下面四个关于“似周期函数”的命题：
+① 如果“似周期函数” $y=f(x)$ 的“似周期”为 $-1$，那么它是周期为 $2$ 的周期函数；
+② 函数 $f(x)=2^{x}$ 是“似周期函数”；
+③ 如果函数 $f(x)=\cos\omega x$ 是“似周期函数”，那么“$\omega=2k\pi,\ k\in\mathbb Z$ 或 $\omega=(2k+1)\pi,\ k\in\mathbb Z$”．
+以上正确结论的个数是（　　）</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>$0$</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="inlineStr">
+        <is>
+          <t>**①**：由“似周期”为 $-1$ 得 $f(x-1)=(-1)\cdot f(x)=-f(x)$，
+于是 $f(x-2)=-f(x-1)=f(x)$，故 $f$ 是周期为 $2$ 的周期函数，**①正确**．
+**②**：若 $f(x)=2^{x}$ 是“似周期函数”，则存在非零常数 $T$ 使
+$2^{x+T}=T\cdot2^{x}$ 恒成立，即 $2^{T}=T$．
+但 $2^{T}&gt;0$ 且 $2^{T}&gt;T$ 对一切实数 $T$ 成立（$T&gt;0$ 时指数函数增长快于自身，$T\leqslant0$ 时左边 $&gt;0\geqslant$ 右边），**无解**，故**②错误**．
+**③**：若 $f(x)=\cos\omega x$ 是“似周期函数”，则存在非零常数 $T$ 使
+$\cos\bigl(\omega(x+T)\bigr)=T\cos\omega x$ 恒成立．
+左边 $=\cos\omega x\cos\omega T-\sin\omega x\sin\omega T$，比较系数得
+$\begin{cases}\cos\omega T=T,\\ \sin\omega T=0.\end{cases}$
+由 $\sin\omega T=0$ 得 $\omega T=k\pi$（$k\in\mathbb Z$），此时 $T=\cos(k\pi)=(-1)^{k}$．
+$k$ 为偶数时 $T=1$，$\omega=k\pi=2n\pi$；$k$ 为奇数时 $T=-1$，$\omega=\dfrac{k\pi}{T}=-(2n+1)\pi$，即 $\omega=(2m+1)\pi$（符号可吸收进 $m$）．
+故 $\omega=2k\pi$ 或 $\omega=(2k+1)\pi$，**③正确**．
+综上，正确结论共 $2$ 个，选 C．</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S276" t="n">
+        <v>5</v>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-053-E1</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>教辅录入-第20批</t>
+        </is>
+      </c>
+      <c r="V276" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「②函数f(x) = 2x是“似周期函数”」与「③如果函数f(x) = cosωx 是“似周期函数”」，$2^{x}$ 的上标、$\cos\omega x$ 的 $\omega$ 尚可辨认，但 $2^{T}=T$ 这一步在提取文本里被压成「2x+T = T ⋅2x / 2T = T」。由详解「$2^{x+T}=T\cdot2^{x}$ 恒成立，故 $2^{T}=T$ 成立，但无解，故②错误」与「$\cos\omega x\cdot\cos\omega T-\sin\omega x\cdot\sin\omega T=T\cos\omega x$ 恒成立，故 $\begin{cases}\cos\omega T=T\\ \sin\omega T=0\end{cases}$，故 $\omega=2k\pi,k\in\mathbb Z$ 或 $\omega=(2k+1)\pi,k\in\mathbb Z$，故③正确」还原。
+**数值校验**：$2^{T}=T$ 确实无解——$T=2$ 时 $4\neq2$，$T=4$ 时 $16\neq4$，$T&lt;0$ 时左边 $&gt;0&gt;$ 右边 ✓。$T=1,\omega=2\pi$：$\cos(2\pi(x+1))=\cos(2\pi x+2\pi)=\cos2\pi x=1\cdot\cos2\pi x$ ✓。$T=-1,\omega=\pi$：$\cos(\pi(x-1))=\cos(\pi x-\pi)=-\cos\pi x=(-1)\cdot\cos\pi x$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>M-H0277</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>M-T-053(函数与导数 / 对称性与周期性 · 画图：放大镜)</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 满足当 $x\leqslant0$ 时，$2f(x-2)=f(x)$，且当 $x\in(-2,0]$ 时，$f(x)=|x+1|-1$；当 $x&gt;0$ 时，$f(x)=\log_{a}x$（$a&gt;0$ 且 $a\neq1$）．若函数 $f(x)$ 的图象上关于原点对称的点恰好有 $3$ 对，则 $a$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>$(625,+\infty)$</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>$(4,64)$</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>$(9,625)$</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>$(9,64)$</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="inlineStr">
+        <is>
+          <t>**转化为方程**：设 $P=(t,f(t))$（$t&gt;0$）在图象上，则 $f(t)=\log_{a}t$；它关于原点的对称点为 $(-t,-\log_{a}t)$，
+该点也在图象上 $\iff$ $f(-t)=-\log_{a}t$．
+**负半轴的分段值域**：由 $2f(x-2)=f(x)$ 即 $f(x)=2f(x-2)$，得 $f(u+2)=\dfrac{f(u)}{2}$，图象每往左 $2$ 个单位、纵向**缩小为 $\frac12$**．
+在 $(-2,0]$ 上 $f(x)=|x+1|-1$，值域 $[-1,0]$；
+在 $(-4,-2]$ 上值域为 $\left[-\dfrac12,0\right]$；
+在 $(-6,-4]$ 上值域为 $\left[-\dfrac14,0\right]$．
+**数交点**：$y=-\log_{a}t$ 在 $t&gt;0$ 上单调（$a&gt;1$ 时递减）．要恰有 $3$ 对，需它依次穿过上面三段各一次、且不进入第四段：
+$-\log_{a}3&gt;-\dfrac12$（在第 2 段内取到）且 $-\log_{a}5&lt;-\dfrac14$（不到第 3 段底部）．
+由 $a&gt;1$：$-\log_{a}3&gt;-\dfrac12\iff\log_{a}3&lt;\dfrac12\iff 3&lt;a^{1/2}\iff a&gt;9$；
+$-\log_{a}5&lt;-\dfrac14\iff\log_{a}5&gt;\dfrac14\iff 5&gt;a^{1/4}\iff a&lt;625$．
+综上 $9&lt;a&lt;625$，选 C．
+（$0&lt;a&lt;1$ 时对称后的图象不可能与负半轴部分有 $3$ 个交点，舍去。）</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S277" t="n">
+        <v>5</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-053-V1</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>教辅录入-第20批</t>
+        </is>
+      </c>
+      <c r="V277" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「-log3 &gt;- 1 / a2，解得9 &lt; a &lt; 625」与「-log5 &lt;-4 / a」——**分数线丢失导致分子分母分裂**：实为 $-\log_a3&gt;-\dfrac12$ 与 $-\log_a5&lt;-\dfrac14$（「1/2」拆成「1」与「2」，「1/4」拆成「1」与「4」）。由详解「当 $a&gt;1$ 时…则 $-\log_a3&gt;-\frac12$，$-\log_a5&lt;-\frac14$，解得 $9&lt;a&lt;625$，故选 C」还原。
+**验算（这是判定分数线归属的关键）**：
+若按 $-\log_a3&gt;-\frac12$：$\log_a3&lt;\frac12\Rightarrow a&gt;3^2=9$ ✓ 下界恰为 9；
+若按 $-\log_a3&gt;-1$（误读）：$a&gt;3$，得不到 9 ✗。
+若按 $-\log_a5&lt;-\frac14$：$\log_a5&gt;\frac14\Rightarrow a&lt;5^4=625$ ✓ 上界恰为 625；
+若按 $-\log_a5&lt;-4$（误读）：$\log_a5&gt;4\Rightarrow a&lt;5^{1/4}$，与 $a&gt;9$ 矛盾 ✗。
+两条都只有「分子分母合起来读」才能对上答案 $(9,625)$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>M-H0278</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>M-T-053(函数与导数 / 对称性与周期性 · 画图：放大镜)</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>设函数 $f(x)$ 的定义域为 $\mathbb R$，满足 $f(x+1)=2f(x)$，且当 $x\in(0,1]$ 时，$f(x)=x(x-1)$．若对任意 $x\in(-\infty,m]$，都有 $f(x)\geqslant-\dfrac12$，则 $m$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,\dfrac32\right]$</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,\dfrac{10-\sqrt2}{4}\right]$</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,\dfrac52\right]$</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,\dfrac{10+\sqrt2}{4}\right]$</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>**放大规律**：$f(x+1)=2f(x)\Rightarrow f(x)=2f(x-1)$，即图象向右平移 $1$ 个单位、纵坐标变为原来的 $2$ 倍．
+**第 3 段**：当 $2&lt;x\leqslant3$ 时，$x-2\in(0,1]$，
+$f(x)=2f(x-1)=4f(x-2)=4(x-2)(x-3)$．
+**解方程**：令 $4(x-2)(x-3)=-\dfrac12$，即 $x^{2}-5x+6=-\dfrac18$，$x^{2}-5x+\dfrac{49}{8}=0$，
+$x=\dfrac{5\pm\sqrt{25-24.5}}{2}=\dfrac{5\pm\sqrt{0.5}}{2}=\dfrac{10\pm\sqrt2}{4}$．
+两根为 $\dfrac{10-\sqrt2}{4}\approx2.146$ 与 $\dfrac{10+\sqrt2}{4}\approx2.854$．
+**定 $m$**：$f$ 在 $(2,3]$ 上先降后升（开口向上），在两根之间 $f(x)&lt;-\dfrac12$．
+要使对任意 $x\in(-\infty,m]$ 都有 $f(x)\geqslant-\dfrac12$，$m$ 不能越过第一个“下陷”的起点，故 $m\leqslant\dfrac{10-\sqrt2}{4}$．
+即 $m\in\left(-\infty,\dfrac{10-\sqrt2}{4}\right]$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S278" t="n">
+        <v>5</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-053-V2</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>教辅录入-第20批</t>
+        </is>
+      </c>
+      <c r="V278" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈(0,1] 时，f(x) = x(x - 1)」（这一段完整）与「令4(x - 2) (x - 3) =- 1 / 2，解得 x= 10 -2 / 1 4，x= 10 +2 / 2 4」，$-\frac12$ 与两根的分数线全丢（「1 / 2」分裂、根式 $\sqrt2$ 的「2」被当成数字）。由详解「当 $2&lt;x\leqslant3$ 时，$f(x)=4f(x-2)=4(x-2)(x-3)$，令 $4(x-2)(x-3)=-\frac12$，解得 $x=\frac{10-\sqrt2}{4}$，$x=\frac{10+\sqrt2}{4}$；所以要使对任意 $x\in(-\infty,m]$，都有 $f(x)\geqslant-\frac12$，则 $m\leqslant\frac{10-\sqrt2}{4}$」还原。
+**数值校验**：$4(x-2)(x-3)=-\frac12$ → $x^2-5x+\frac{49}{8}=0$，$\Delta=25-\frac{49}{2}=0.5$，$x=\frac{5\pm\sqrt{0.5}}{2}$ ✓；$\frac{10\pm\sqrt2}{4}=\frac{5\pm\sqrt{0.5}}{2}$ ✓（分子分母同乘 2）。$x=2.5$：$4\times0.5\times(-0.5)=-1&lt;-\frac12$ ✓ 确在两根之间下陷。
+**⚠ 选项 A、C 的说明**：提取文本里 A、C 只剩「3[」「5[」与分母「2」，按上下文还原为 $\frac32$ 与 $\frac52$——它们与 B、D 构成递增序列 $\frac32&lt;\frac{10-\sqrt2}{4}&lt;\frac52&lt;\frac{10+\sqrt2}{4}$，作为干扰项合理。答案 B 由详解确凿，不受影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>M-H0279</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>M-T-053(函数与导数 / 对称性与周期性 · 画图：放大镜)</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
+        <is>
+          <t>定义在 $\mathbb R$ 上的函数 $f(x)$ 满足 $f(x+1)=\dfrac12 f(x)$，且当 $x\in[0,1)$ 时，$f(x)=1-|2x-1|$．则使得 $f(x)\leqslant\dfrac1{16}$ 在 $[m,+\infty)$ 上恒成立的 $m$ 的最小值是（　　）</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>$\dfrac72$</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>$\dfrac92$</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>$\dfrac{13}4$</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>$\dfrac{15}4$</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>**分段解析式**：由 $f(x+1)=\dfrac12f(x)$ 得，当 $x\in[n,n+1)$（$n\in\mathbb Z$）时
+$f(x)=\dfrac{1}{2^{n}}\Bigl[1-\bigl|2(x-n)-1\bigr|\bigr]=\dfrac{1}{2^{n}}\bigl[1-|2x-2n-1|\bigr]$．
+**值域上界**：该段最大值为 $\dfrac{1}{2^{n}}$（在 $x=n+\dfrac12$ 处取到）．当 $n\geqslant4$ 时 $\dfrac{1}{2^{n}}\leqslant\dfrac1{16}$，自然满足．
+**第 $3$ 段**（$x\in[3,4)$，$n=3$）：$f(x)=\dfrac18\bigl[1-|2x-7|\bigr]$，令 $f(x)=\dfrac1{16}$：
+$\dfrac18\bigl[1-|2x-7|\bigr]=\dfrac1{16}\Rightarrow 1-|2x-7|=\dfrac12\Rightarrow |2x-7|=\dfrac12$，
+得 $2x-7=\pm\dfrac12$，即 $x=\dfrac{15}4$ 或 $x=\dfrac{13}4$．
+该段上 $f$ 先降到 $-\frac18\cdot0$…实际是先减后增（顶点在 $x=\frac72$ 处取最大值 $\frac18$），在 $\left[\dfrac72,4\right)$ 上从 $\dfrac18$ 递减到 $0$，故 $x\geqslant\dfrac{15}4$ 时 $f(x)\leqslant\dfrac1{16}$．
+结合图象（$x\geqslant\frac{15}4$ 之后各段整体不超过 $\frac1{16}$），$m$ 的最小值为 $\dfrac{15}4$，选 D．</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S279" t="n">
+        <v>5</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-053-V3</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>教辅录入-第20批</t>
+        </is>
+      </c>
+      <c r="V279" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「定义在R 上函数q 满足f (x + 1)= f (x) / 2，且当x ∈[0,1(时，f (x)= 1 - |2x - 1|. 则使得f (x)≤ 在[m,+∞(上恒成立的m 的最小值是() / 16」，$\frac12$ 与 $\frac1{16}$ 的分数线全丢（「1 / 2」「1 / 16」分裂），「函数q」是「函数f」的误认（草体 f 与 q 形近）。由详解「在区间 $[n,n+1)$（$n\in\mathbb Z$）上，$f(x)=\frac{1}{2^n}[1-|2x-2n+1|]$，…所以当 $n\geqslant4$ 时 $f(x)\leqslant\frac{1}{16}$；在 $[\frac72,4)$ 上，由 $f(x)=\frac18[1-|2x-7|]=\frac{1}{16}$，得 $x=\frac{15}4$；由图象可知当 $x\geqslant\frac{15}4$ 时，$f(x)\leqslant\frac1{16}$」还原。
+**结构校验**：$f(x)=\frac{1}{2^n}[1-|2x-2n-1|]$，代入 $n=3$：$\frac18[1-|2x-7|]$ ✓ 与详解一致。$x=\frac72=3.5$：$|7-7|=0$，$f=\frac18$（最大值）✓；$x=4$：$|8-7|=1$，$f=0$ ✓；$x=\frac{15}4=3.75$：$|7.5-7|=0.5$，$f=\frac18\times0.5=\frac1{16}$ ✓ 恰取等号。
+**选项**：四个选项 $\frac72,\frac92,\frac{13}4,\frac{15}4$ 由「7 9 13 15 / 2 2 4 4」还原（分子与分母分离），答案 D 与详解一致 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>M-H0280</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>M-T-054(函数与导数 / 对称性与周期性 · 利用对称解决恒成立和存在型)</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\lg\left(x+\sqrt{x^{2}+1}\right)$，且对于任意的 $x\in(1,2]$，
+$f\!\left(\dfrac{x+1}{x-1}\right)+f\!\left(\dfrac{m}{(x-1)^{2}(x-6)}\right)&gt;0$ 恒成立，则 $m$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>$(-\infty,0)$</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>$(-\infty,0]$</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>$[4,+\infty)$</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>$(12,+\infty)$</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P280" s="2" t="inlineStr">
+        <is>
+          <t>**奇偶性**：定义域为 $\mathbb R$，且
+$f(-x)=\lg\left(\sqrt{x^{2}+1}-x\right)=\lg\dfrac{1}{\sqrt{x^{2}+1}+x}=-\lg\left(x+\sqrt{x^{2}+1}\right)=-f(x)$，
+故 $f$ 为奇函数；又 $x+\sqrt{x^{2}+1}$ 在 $(0,+\infty)$ 上递增，$\lg$ 递增，故 $f$ 在 $\mathbb R$ 上**单调递增**．
+**化不等式**：由奇性 $-f(u)=f(-u)$，原不等式等价于
+$f\!\left(\dfrac{x+1}{x-1}\right)&gt;f\!\left(-\dfrac{m}{(x-1)^{2}(x-6)}\right)$，
+再由单调性得 $\dfrac{x+1}{x-1}&gt;-\dfrac{m}{(x-1)^{2}(x-6)}$．
+**去分母**：$x\in(1,2]$ 时 $x-1&gt;0$、$x-6&lt;0$，故 $(x-1)^{2}(x-6)&lt;0$，两边同乘要**变号**：
+$(x+1)(x-1)(x-6)&lt;-m$ 恒成立．
+**求上确界**：设 $g(x)=(x+1)(x-1)(x-6)=x^{3}-6x^{2}-x+6$，
+$g'(x)=3x^{2}-12x-1=3(x-2)^{2}-13$，当 $1&lt;x\leqslant2$ 时 $g'(x)&lt;0$，$g$ 单调递减，
+故 $g(x)$ 的上确界为 $\lim\limits_{x\to1^{+}}g(x)=0$（**取不到**，$g(1)=0$ 但 $x=1$ 不在定义区间内）．
+**定 $m$**：需 $0\leqslant-m$，即 $m\leqslant0$，得 $m\in(-\infty,0]$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S280" t="n">
+        <v>5</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-054-E1</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>教辅录入-第20批</t>
+        </is>
+      </c>
+      <c r="V280" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「已知函数f(x) = lg(x +x2+ 1)，且对于任意的x ∈(1，2]，f()+ f&gt; 0 恒成立，则m 的取值范围为 / x - 1((x - 1)2(x - 6))」，根号 $\sqrt{x^2+1}$ 丢失（变成 x +x2+ 1），两个分式的分子与分母分离到不同行。由详解「$f(x)$ 的定义域为 $\mathbb R$，$f(-x)=\lg(\sqrt{x^2+1}-x)=\lg\frac{1}{x^2+1+x}=-\lg(x+\sqrt{x^2+1})=-f(x)$，∴$f(x)$ 为奇函数，又 $f(x)$ 在 $(0,+\infty)$ 上单调递增」与「$f(\frac{x+1}{x-1})&gt;-f(\frac{m}{(x-1)^2(x-6)})=f(-\frac{m}{(x-1)^2(x-6)})$，∴$\frac{x+1}{x-1}&gt;\frac{-m}{(x-1)^2(x-6)}$」还原。
+**关键细节**：详解写「$g(x)$ 的最大值为从负数无限接近于 $0$，$g(x)_{\max}&lt;0$，∴$0\leqslant-m$，$m\leqslant0$」——
+这里上确界 $0$ **取不到**，所以是 $0\leqslant -m$（可以取等号，因 $g(x)&lt;0$ 严格成立时 $-m$ 只需 $\geqslant\sup g=0$），答案含 $0$，选 B 而非 A。
+**数值校验**：$g(x)=x^3-6x^2-x+6$，$g(1)=1-6-1+6=0$ ✓；$g(2)=8-24-2+6=-12$ ✓ 递减；$g'(1)=3-12-1=-10&lt;0$ ✓。$m=0$ 时：需 $(x+1)(x-1)(x-6)&lt;0$，而 $x\in(1,2]$ 时该式 $&lt;0$ ✓ 恒成立。$m=1$ 时：需 $g(x)&lt;-1$，$x\to1^+$ 时 $g\to0&gt;-1$ ✗ 不成立 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>M-H0281</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>M-T-054(函数与导数 / 对称性与周期性 · 利用对称解决恒成立和存在型)</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac{2^{x}+m}{2^{x}+1}$（$0\leqslant x\leqslant1$），函数 $g(x)=(m-1)x$（$1\leqslant x\leqslant2$）．若任意的 $x_{1}\in[0,1]$，存在 $x_{2}\in[1,2]$，使得 $f(x_{1})=g(x_{2})$，则实数 $m$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>$\left(1,\dfrac53\right]$</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>$[2,3]$</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>$\left[2,\dfrac52\right]$</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac53,\dfrac52\right]$</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P281" s="2" t="inlineStr">
+        <is>
+          <t>**题意转化**：任意 $x_{1}\in[0,1]$ 都能找到 $x_{2}\in[1,2]$ 使 $f(x_{1})=g(x_{2})$，即 $f$ 在 $[0,1]$ 上的值域是 $g$ 在 $[1,2]$ 上值域的**子集**．
+**$f$ 的值域**：$f(x)=\dfrac{2^{x}+m}{2^{x}+1}=1+\dfrac{m-1}{2^{x}+1}$．
+$x=0$ 时 $f=1+\dfrac{m-1}{2}=\dfrac{m+1}{2}$；$x=1$ 时 $f=1+\dfrac{m-1}{3}=\dfrac{m+2}{3}$．
+当 $m&lt;1$ 时 $m-1&lt;0$，$f$ 递增，值域 $\left[\dfrac{m+1}{2},\dfrac{m+2}{3}\right]$；
+当 $m&gt;1$ 时 $m-1&gt;0$，$f$ 递减，值域 $\left[\dfrac{m+2}{3},\dfrac{m+1}{2}\right]$．
+**$g$ 的值域**：$g(x)=(m-1)x$ 是一次函数，$m&lt;1$ 时递减，值域 $[2m-2,\,m-1]$；$m&gt;1$ 时递增，值域 $[m-1,\,2m-2]$．
+**情况一 $m&lt;1$**：需 $\left[\dfrac{m+1}{2},\dfrac{m+2}{3}\right]\subseteq[2m-2,\,m-1]$，
+即 $\begin{cases}\dfrac{m+1}{2}\geqslant2m-2\\[4pt]\dfrac{m+2}{3}\leqslant m-1\end{cases}$$\Rightarrow\begin{cases}m\leqslant\frac53\\ m\geqslant\frac52\end{cases}$，无解．
+**情况二 $m&gt;1$**：需 $\left[\dfrac{m+2}{3},\dfrac{m+1}{2}\right]\subseteq[m-1,\,2m-2]$，
+即 $\begin{cases}\dfrac{m+1}{2}\leqslant2m-2\\[4pt]\dfrac{m+2}{3}\geqslant m-1\end{cases}$$\Rightarrow\begin{cases}m\geqslant\frac53\\ m\leqslant\frac52\end{cases}$，得 $\dfrac53\leqslant m\leqslant\dfrac52$．
+**情况三 $m=1$**：$f\equiv1$，$g\equiv0$，值域不相交，不满足．
+综上 $m\in\left[\dfrac53,\dfrac52\right]$，选 D．</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S281" t="n">
+        <v>5</v>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-054-V1</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>教辅录入-第20批</t>
+        </is>
+      </c>
+      <c r="V281" s="2" t="inlineStr">
+        <is>
+          <t>★ **选项用 `--chars` 按 x 坐标对齐才还原出来**。提取文本只剩「A. 1,B. 2,3C. 2,D. ,」加一行孤立的「3232」（分母）与「5 55 5」（分子）。按 x 坐标配对：x≈347.8 → $\frac53$；x≈460.0 → $\frac52$；x≈508.4 → $\frac53$；x≈520.6 → $\frac52$。
+于是 A $=\left(1,\frac53\right]$、B $=[2,3]$、C $=\left[2,\frac52\right]$、D $=\left[\frac53,\frac52\right]$，其中 D 与详解答案完全一致 ✓。
+**数值校验**：$m=2$（在 $[\frac53,\frac52]=[1.667,2.5]$ 内）：$f$ 值域 $[\frac{2+2}{3},\frac{2+1}{2}]=[\frac43,1.5]$，$g$ 值域 $[1,2]$，$[\frac43,1.5]\subseteq[1,2]$ ✓。$m=3$（超出）：$f$ 值域 $[\frac53,2]$，$g$ 值域 $[2,4]$，$\frac53&lt;2$ ✗ 不含 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>M-H0282</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>M-T-054(函数与导数 / 对称性与周期性 · 利用对称解决恒成立和存在型)</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>已知 $f(x)$ 是定义在 $\mathbb R$ 上的函数，且 $f(x+1)$ 关于直线 $x=-1$ 对称．当 $x\geqslant0$ 时，
+$f(x)=\begin{cases}2^{-\frac14x^{2}+1}, &amp; 0\leqslant x&lt;2,\\ 2-\log_{2}x, &amp; x\geqslant2,\end{cases}$
+若对任意的 $x\in[m,m+1]$，不等式 $f(2-2x)\geqslant f(x+m)$ 恒成立，则实数 $m$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>$\left[-\dfrac14,0\right]$</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac12,1\right]$</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>$[1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac12,+\infty\right)$</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P282" s="2" t="inlineStr">
+        <is>
+          <t>**单调性**：当 $0\leqslant x&lt;2$ 时，指数 $-\dfrac14x^{2}+1$ 递减、$y=2^{u}$ 递增，故 $f$ 递减，且 $f(x)&gt;2^{-\frac14\cdot4+1}=2^{0}=1$；
+当 $x\geqslant2$ 时 $f(x)=2-\log_{2}x$ 递减，且 $f(x)\leqslant f(2)=2-1=1$．
+两段衔接处 $f(2)=1$ 与前段的极限一致，故 $f$ 在 $[0,+\infty)$ 上**单调递减**．
+**偶性**：$f(x+1)$ 关于 $x=-1$ 对称，即把图象左移 $1$ 后对称轴是 $x=0$，故 $f$ 本身关于 $x=0$ 对称，$f$ 为**偶函数**．
+**化不等式**：$f(2-2x)\geqslant f(x+m)$ $\iff$ $f(|2-2x|)\geqslant f(|x+m|)$，
+由 $f$ 在 $[0,+\infty)$ 上递减得 $|2-2x|\leqslant|x+m|$，平方得 $(2-2x)^{2}\leqslant(x+m)^{2}$，
+整理：$3x^{2}-(8+2m)x+4-m^{2}\leqslant0$．
+设 $g(x)=3x^{2}-(8+2m)x+4-m^{2}$（开口向上），要在 $[m,m+1]$ 上恒 $\leqslant0$，只需两端点 $\leqslant0$：
+$g(m)=3m^{2}-(8+2m)m+4-m^{2}=-8m+4\leqslant0\Rightarrow m\geqslant\dfrac12$；
+$g(m+1)=3(m+1)^{2}-(8+2m)(m+1)+4-m^{2}=-4m-1\leqslant0\Rightarrow m\geqslant-\dfrac14$．
+取交集得 $m\geqslant\dfrac12$，即 $m\in\left[\dfrac12,+\infty\right)$，选 D．</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S282" t="n">
+        <v>5</v>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-054-V2</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>教辅录入-第20批</t>
+        </is>
+      </c>
+      <c r="V282" s="2" t="inlineStr">
+        <is>
+          <t>★ **选项用 `--chars` 按 x 坐标对齐还原**：提取文本只剩「A. - ,0(B. ,1」加分母「4」「2」。
+按 x 坐标：x≈71.6（分子 '1'）+ x≈71.4（分母 '4'）+ 负号 → $-\dfrac14$；x≈176.7（分子 '1'）+ x≈176.6（分母 '2'）→ $\dfrac12$。
+故 A $=\left[-\frac14,0\right]$、B $=\left[\frac12,1\right]$，C、D 据文本「C. [1,+∞) D. [?,+∞)」+ 分母 '2' 得 C $=[1,+\infty)$、D $=\left[\frac12,+\infty\right)$，与详解答案 D 一致 ✓。
+**结构校验**：$g(m)=3m^2-8m-2m^2+4-m^2=-8m+4$ ✓；$g(m+1)=3(m^2+2m+1)-(8+2m)(m+1)+4-m^2=3m^2+6m+3-2m^2-10m-8+4-m^2=-4m-1$ ✓。取 $m=\frac12$：$g(\frac12)=-4+4=0$ ✓ 恰为边界。
+**注意易错点**：$f$ 为**减**函数，所以 $f(a)\geqslant f(b)\Rightarrow a\leqslant b$（用绝对值后），方向别搞反。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V282"/>
+  <dimension ref="A1:V299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28427,6 +28427,1865 @@
         </is>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>M-H0283</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>M-T-055(函数与导数 / 对称性与周期性 · 函数整数问题)</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr">
+        <is>
+          <t>定义：$N\{f(x)\otimes g(x)\}$ 表示不等式 $f(x)&lt;g(x)$ 的解集中的整数解之和．若 $f(x)=|\log_{2}x|$，$g(x)=a(x-1)^{2}+2$，$N\{f(x)\otimes g(x)\}=6$，则实数 $a$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>$(-\infty,-1]$</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>$(\log_{2}3-2,\,0)$</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>$(2-\log_{2}6,\,0]$</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac{\log_{2}3-2}{4},\,0\right]$</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P283" s="2" t="inlineStr">
+        <is>
+          <t>**确定整数解**：和为 $6$ 的连续正整数只能是 $1+2+3$，故解集中的整数恰为 $1,2,3$．
+**讨论 $a$**：
+$a&gt;0$ 时，$g(x)=a(x-1)^{2}+2$ 当 $x\to+\infty$ 时趋于 $+\infty$，而 $f(x)=|\log_{2}x|$ 增长慢，解集含无穷多个整数，和必大于 $6$，舍去；
+$a=0$ 时，$g\equiv2$，由 $|\log_{2}x|&lt;2$ 得 $\dfrac14&lt;x&lt;4$，其中整数为 $1,2,3$，和为 $6$，符合题意；
+$a&lt;0$ 时，$g$ 是开口向下的抛物线，需 $3$ 在解集内而 $4$ 不在：
+$\begin{cases}f(3)&lt;g(3)\\ f(4)\geqslant g(4)\end{cases}$$\iff\begin{cases}|\log_{2}3|&lt;4a+2\\ |\log_{2}4|\geqslant9a+2\end{cases}$$\iff\begin{cases}\log_{2}3&lt;4a+2\\ 2\geqslant9a+2\end{cases}$
+解得 $\dfrac{\log_{2}3-2}{4}&lt;a\leqslant0$．
+综合 $a=0$ 与 $a&lt;0$ 两段，得 $a\in\left[\dfrac{\log_{2}3-2}{4},\,0\right]$，选 D．</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S283" t="n">
+        <v>5</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-055-E1</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V283" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「N f(x) ⊗g(x)= 6 表示不等式|logx| &lt; a(x - 1)2+ 2 的解集中整数解之和为6」，$|\log_2 x|$ 的绝对值竖线与底数 $2$ 全丢；选项 D 的 $\frac{\log_2 3-2}{4}$ 被拆成「log3 - 2」+ 分母「4」。由详解「$N=6$ 表示不等式 $|\log_2x|&lt;a(x-1)^2+2$ 的解集中整数解之和为 $6$」与「只需满足 $f(3)&lt;g(3)$、$f(4)\geqslant g(4)$，即 $\log_2 3&lt;4a+2$、$2\geqslant9a+2$，解得 $\frac{\log_2 3-2}{4}&lt;a\leqslant0$」还原。
+**数值校验**：$a=0$ 时 $g\equiv2$，$|\log_2x|&lt;2\Rightarrow\frac14&lt;x&lt;4$，整数 $1,2,3$ 和为 $6$ ✓。$a=-0.1$（在 $[(\log_2 3-2)/4,0]=[-0.301,0]$ 内，因 $\frac{1.585-2}{4}=-0.104$）：$g(3)=-0.4+2=1.6&gt;\log_2 3=1.585$ ✓ 含 3；$g(4)=-0.9+2=1.1&lt;2=|\log_24|$ ✓ 不含 4。
+**边界**：$a=\frac{\log_2 3-2}{4}$ 时 $f(3)=g(3)$，$3$ 不在解集内（严格小于），答案为闭区间是按原书录入，详解原文写「$\frac{\log_2 3-2}{4}&lt;a\leqslant0$」（左开），选项 D 给左闭，二者略有出入，**按原书选项 D 录入**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>M-H0284</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>M-T-055(函数与导数 / 对称性与周期性 · 函数整数问题)</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr">
+        <is>
+          <t>定义在 $\mathbb R$ 上的奇函数 $f(x)$ 满足 $f(2+x)=f(2-x)$，当 $x\in[0,2]$ 时，$f(x)=-4x^{2}+8x$．若在区间 $[a,b]$ 上存在 $m$（$m\geqslant3$）个不同的整数 $x_{i}$（$i=1,2,\cdots,m$），满足 $\sum\limits_{i=1}^{m-1}\bigl|f(x_{i+1})-f(x_{i})\bigr|\geqslant72$，则 $b-a$ 的最小值为（　　）</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>$15$</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>$16$</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>$17$</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>$18$</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P284" s="2" t="inlineStr">
+        <is>
+          <t>**周期**：由 $f(2+x)=f(2-x)$ 得 $f(x)=f(4-x)$；又 $f$ 为奇函数 $f(-x)=-f(x)$，故
+$f(x+4)=f\bigl(4-(x+4)\bigr)=f(-x)=-f(x)$，
+于是 $f(x+8)=-f(x+4)=f(x)$，**$T=8$**．
+**一个周期内的取值**：$x\in[0,2]$ 时 $f(x)=-4x^{2}+8x$，
+$f(0)=0$，$f(1)=4$，$f(2)=0$；由奇性 $f(-1)=-4$，$f(-2)=0$；
+由 $f(x+4)=-f(x)$ 得 $f(3)=-f(-1)=4$，$f(5)=f(1+4)=-f(1)=-4$，$f(6)=f(2+4)=-f(2)=0$，$f(7)=-f(3)=-4$．
+**相邻整数差的和**：沿 $x=-1,0,1,2,3,\cdots$ 排列，
+$|f(0)-f(-1)|+|f(1)-f(0)|+|f(2)-f(1)|+|f(3)-f(2)|=4+4+4+4=16$（每 $4$ 个间隔贡献 $16$）．
+要总和 $\geqslant72$，需 $\dfrac{72}{16}=4.5$ 组，即**至少跨越两个完整周期再多一点**．
+取 $x_{i}$ 依次为 $-1,1,2,5,7,\cdots$ 时跨度最省，实测需 $b-a=18$（$2\dfrac14$ 个周期 $=18$）．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S284" t="n">
+        <v>5</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-055-V1</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V284" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「a,bm(m ≥3) / 若在区间][上，存在 / m∑=1 / 个不同的整数x(i = 1,2,...,m)，满足 |f(x) - f(x)|≥72」，求和符号与上下标全丢，求和式 $\sum_{i=1}^{m-1}|f(x_{i+1})-f(x_i)|$ 被压成「|f(x) - f(x)|」。由详解「$f(x+4)=-f(x)$，则 $f(x+8)=-f(x+4)=-[-f(x)]=f(x)$，∴$f(x)$ 的周期为 $8$」「比如，当不同整数 $x_i$ 分别为 $-1,1,2,5,7\cdots$ 时，$b-a$ 取最小值，$f(-1)=-4,f(1)=4,f(2)=0$，至少需要二又四分之一个周期，则 $b-a$ 的最小值为 $18$」还原。
+**数值校验**：$f(1)=-4+8=4$ ✓，$f(-1)=-f(1)=-4$ ✓，$f(2)=-16+16=0$ ✓；$f(3)=f(4-1)=f(-1)=-4$… 由 $f(x)=f(4-x)$ 有 $f(3)=f(1)=4$，而由 $f(x+4)=-f(x)$ 有 $f(3)=-f(-1)=4$ ✓ 一致。每 $4$ 个间隔 $4\times4=16$，$2.25$ 个周期 $=18$ ✓。
+**⚠ 说明**：本题求和的严格推导依赖图象（哪些整数点参与、顺序如何），详解只给了「二又四分之一个周期」的结论与示例点列，录入按原书答案 $18$ 及该结论，review 中如实标注推理链来源。</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>M-H0285</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>M-T-055(函数与导数 / 对称性与周期性 · 函数整数问题)</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr">
+        <is>
+          <t>已知偶函数 $f(x)$ 满足 $f(3+x)=f(3-x)$，且当 $x\in[0,3]$ 时，$f(x)=x\mathrm e^{-\frac{x}{2}}$，若关于 $x$ 的不等式在 $[-150,150]$ 上有且只有 $150$ 个整数解，则实数 $t$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>$\left(0,\ \mathrm e^{-\frac12}\right)$</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>$\left(\mathrm e^{-\frac12},\ 3\mathrm e^{-\frac32}\right)$</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>$\left(3\mathrm e^{-\frac32},\ 2\mathrm e^{-1}\right)$</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>$\left(\mathrm e^{-\frac12},\ 2\mathrm e^{-1}\right)$</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P285" s="2" t="inlineStr">
+        <is>
+          <t>**化简不等式**：$f^{2}(x)-t\,f(x)&gt;0\iff f(x)\bigl[f(x)-t\bigr]&gt;0$．在 $[0,3]$ 上 $f(x)=x\mathrm e^{-x/2}\geqslant0$，且由对称性推广后 $f\geqslant0$，故等价于 $f(x)&gt;t$．
+**周期**：由 $f(3+x)=f(3-x)$ 得 $f$ 关于 $x=3$ 对称；又 $f$ 为偶函数 $f(-x)=f(x)$，故
+$f(3+x)=f(3-x)=f(x-3)$，
+即 $f(x+6)=f(x)$，**$T=6$**．
+**每周期几个整数解**：$[-150,150]$ 长度 $300=50\times6$，共 $150$ 个整数解 $\Rightarrow$ **每个周期恰 $3$ 个**．
+**一个周期内的整数点**：取 $[0,6)$，$x=0,1,2,3,4,5$．
+$f(0)=0$，$f(1)=\mathrm e^{-1/2}\approx0.6065$，$f(2)=2\mathrm e^{-1}\approx0.7358$，$f(3)=3\mathrm e^{-3/2}\approx0.6694$；
+由关于 $x=3$ 对称：$f(4)=f(2)$，$f(5)=f(1)$．
+**定 $t$**：要恰有 $3$ 个点满足 $f&gt;t$，按值从大到小是 $f(2)=f(4)&gt;f(3)&gt;f(1)=f(5)&gt;f(0)$，故需
+$f(3)&gt;t\geqslant f(1)$，即 $\mathrm e^{-1/2}\leqslant t&lt;3\mathrm e^{-3/2}$．
+（原书取开区间）故选 B．</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S285" t="n">
+        <v>5</v>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-055-V2</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V285" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「已知偶函数f(x) 满足f(3 + x) = f(3 - x)，且当x ∈[0,3] 时，f(x) = xe- x x[-150,150]150 / 2」，$f(x)=x\mathrm e^{-x/2}$ 的指数被拆走，**题干里的不等式 $f^2(x)-tf(x)&gt;0$ 整个丢失**（只剩「150 个整数解」）。由详解「关于 $x$ 的不等式 $f^2(x)-tf(x)&gt;0$ 在 $[-150,150]$ 上有且只有 $150$ 个整数解，即 $f(x)&gt;t$ 在 $[-150,150]$ 上有且只有 $150$ 个整数解，所以每个周期内恰有三个整数解」补回不等式并还原。
+**导数校验**：$f'(x)=\mathrm e^{-x/2}-\frac{x}{2}\mathrm e^{-x/2}=\left(1-\frac{x}{2}\right)\mathrm e^{-x/2}$ ✓ 与详解一致，故 $f$ 在 $(0,2)$ 增、$(2,3)$ 减 ✓。
+**数值校验**：$\mathrm e^{-1/2}=0.6065$，$3\mathrm e^{-3/2}=0.6694$，$2\mathrm e^{-1}=0.7358$；$f(2)=0.7358&gt;f(3)=0.6694&gt;f(1)=0.6065&gt;f(0)=0$ ✓。$t=0.64$（在 $(0.6065,0.6694)$ 内）：$&gt;t$ 的是 $f(2),f(3),f(4)$ 共 $3$ 个 ✓。$t=0.6$：$f(1),f(5)$ 也 $&gt;t$，共 $5$ 个 ✗ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>M-H0286</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>M-T-055(函数与导数 / 对称性与周期性 · 函数整数问题)</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
+        <is>
+          <t>定义在 $\mathbb R$ 上的偶函数 $f(x)$ 满足 $f(5-x)=f(x+3)$，且
+$f(x)=\begin{cases}-2x^{2}+4x, &amp; 0\leqslant x&lt;1,\\ x-2\ln x, &amp; 1\leqslant x\leqslant4,\end{cases}$
+若关于 $x$ 的不等式 $f^{2}(x)+(a+1)f(x)+a&lt;0$ 在 $[-20,20]$ 上有且仅有 $15$ 个整数解，则实数 $a$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>$(-1,\ \ln2-2]$</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>$[2\ln3-3,\ 2\ln2-2)$</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>$(2\ln3-3,\ 2\ln2-2]$</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>$[2-2\ln2,\ 3-2\ln3)$</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P286" s="2" t="inlineStr">
+        <is>
+          <t>**周期**：由 $f(5-x)=f(x+3)$ 知 $f$ 关于直线 $x=\dfrac{5+3}{2}=4$ 对称；又 $f$ 为偶函数，两个对称性（对称轴 $x=0$ 与 $x=4$）推出
+$T=2|4-0|=8$．$[-20,20]$ 长度 $40=5\times8$，共 $15$ 个整数解$\Rightarrow$ **每个周期恰 $3$ 个**．
+**因式分解**：$f^{2}+(a+1)f+a=\bigl[f(x)+1\bigr]\bigl[f(x)+a\bigr]&lt;0$．
+若 $-a\leqslant0$（即 $a\geqslant0$），则 $f+a$ 与 $f+1$ 同号或 $f+1$ 恒正时无解，不合；故 $-a&gt;0$，解为
+$-1&lt;f(x)&lt;-a$．
+**一个周期 $[-4,4]$ 内的 $f$ 值**：
+$x\in[0,1)$：$f=-2x^{2}+4x$ 递增，$f(0)=0$，$\lim\limits_{x\to1^-}f=2$；
+$x\in[1,4]$：$f=x-2\ln x$，$f'(x)=1-\dfrac2x$，在 $[1,2)$ 递减、$(2,4]$ 递增，
+$f(1)=1$，$f(2)=2-2\ln2\approx0.614$，$f(3)=3-2\ln3\approx0.803$，$f(4)=4-2\ln4\approx1.227$．
+由偶性可得 $[-4,0]$ 上的值．
+**数整数解**：要 $-1&lt;f(x)&lt;-a$ 恰有 $3$ 个整数点，需 $-a$ 恰好卡在 $f(2)$ 与 $f(3)$ 之间（使 $x=\pm2$ 等 $3$ 个点落入）：
+$2-2\ln2&lt;-a\leqslant3-2\ln3$，
+即 $2\ln3-3\leqslant a&lt;2\ln2-2$．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S286" t="n">
+        <v>5</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-055-V3</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V286" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「定义在R 上的偶函数f (x)满足f (5 - x)= f (x + 3)，且f (x)= 分段{-2x2+ 4x, 0 ≤x &lt; 1 / x - 2lnx,1 ≤x ≤4}」，$-2x^2$ 的上标丢失、不等式 $f^2(x)+(a+1)f(x)+a&lt;0$ 的上标也丢失（写成 f 2(x)）。由详解「由 $f(5-x)=f(x+3)$ 得函数图象关于直线 $x=4$ 对称，又函数为偶函数，∴函数是周期函数，且周期为 $8$，区间 $[-20,20]$ 含有 $5$ 个周期」与「由 $f^2(x)+(a+1)f(x)+a&lt;0$ 得 $[f(x)+1][f(x)+a]&lt;0$，若 $-a\leqslant0$ 则原不等式无解，故 $-a&gt;0$，$-1&lt;f(x)&lt;-a$；要使得不等式 $-1&lt;f(x)&lt;-a$ 在 $[-4,4]$ 上有 $3$ 个整数解，则 $2-2\ln2&lt;-a\leqslant3-2\ln3$，即 $2\ln3-3\leqslanta&lt;2\ln2-2$」还原。
+**数值校验**：$f(2)=2-2\ln2=2-1.386=0.614$ ✓；$f(3)=3-2\ln3=3-2.197=0.803$ ✓；$f(1)=1-0=1$ ✓；$f(4)=4-2\ln4=4-2.773=1.227$ ✓。$2\ln3-3=-0.803$，$2\ln2-2=-0.614$，$a\in[-0.803,-0.614)$ ✓ 与答案 B 一致。
+**注意**：选项 A 的 $(-1,\ln2-2]$ 与 D 的 $[2-2\ln2,3-2\ln3)$ 符号写反了（把 $f$ 值当成了 $a$ 值），是典型干扰项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>M-H0287</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>M-T-056(函数与导数 / 零点与图像交点 · 水平线法：参变分离)</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}2^{x}-2^{-x}, &amp; x&gt;1,\\ 2^{-x}-2^{x}, &amp; x\leqslant1,\end{cases}$函数 $g(x)=f(x)-m$，则下列说法错误的是（　　）</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>若 $m\leqslant-\dfrac32$，则函数 $g(x)$ 无零点</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>若 $m&gt;-\dfrac32$，则函数 $g(x)$ 有零点</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>若 $-\dfrac32&lt;m\leqslant\dfrac32$，则函数 $g(x)$ 有一个零点</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>若 $m&gt;\dfrac32$，则函数 $g(x)$ 有两个零点</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P287" s="2" t="inlineStr">
+        <is>
+          <t>**左支**（$x\leqslant1$）：$f(x)=2^{-x}-2^{x}$．$2^{-x}$ 递减、$-2^{x}$ 递减，故 $f$ 递减；
+$x\to-\infty$ 时 $f\to+\infty$，$f(1)=2^{-1}-2=-\dfrac32$，值域 $\left[-\dfrac32,+\infty\right)$．
+**右支**（$x&gt;1$）：$f(x)=2^{x}-2^{-x}$．$2^{x}$ 递增、$-2^{-x}$ 递增，故 $f$ 递增；
+$\lim\limits_{x\to1^{+}}f=2-\dfrac12=\dfrac32$，$x\to+\infty$ 时 $f\to+\infty$，值域 $\left(\dfrac32,+\infty\right)$．
+**数交点**（$g(x)=0\iff f(x)=m$）：
+$m&lt;-\dfrac32$：$0$ 个；$m=-\dfrac32$：左支 $1$ 个（$x=1$）；
+$-\dfrac32&lt;m\leqslant\dfrac32$：左支 $1$ 个；
+$m&gt;\dfrac32$：左、右各 $1$ 个，共 $2$ 个．
+**判选项**：A 说 $m\leqslant-\dfrac32$ 时无零点，但 $m=-\dfrac32$ 时有 $1$ 个零点，**A 错误**；B、C、D 均与上表一致．
+故说法错误的是 A，选 A．</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S287" t="n">
+        <v>5</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-056-E1</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V287" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= 分段{ 1 / 2x - , x &gt; 1 ; 1 / - 2x, x ≤1 } / 2x」，分子分母被拆散，看上去像 $\frac{1}{2x}$ 之类，**但那是 $2^{x}$ 与 $2^{-x}$ 的上标丢失后又被排版拆开**。
+**还原依据**：选项全是 $\pm\frac32$ 的临界值。$2^{1}-2^{-1}=2-\frac12=\frac32$、$2^{-1}-2^{1}=\frac12-2=-\frac32$——这两个数正好是 $x=1$ 处两支的端点值，与选项完全吻合 ✓。若按 $\frac{1}{2x}$ 理解，$x=1$ 处是 $\pm\frac12$，对不上 $\frac32$ ✗。
+**详解佐证**：「观察可知：当 $m=-\frac32$ 时，函数 $g(x)$ 有一个零点，故 A 错误」——恰与 $f(1)=-\frac32$ 一致 ✓。
+**数值校验**：$m=2&gt;\frac32$：左支 $2^{-x}-2^x=2$ → 令 $u=2^x$，$1/u-u=2$ → $u^2+2u-1=0$ → $u=\sqrt2-1$ → $x=\log_2(\sqrt2-1)&lt;0\leqslant1$ ✓ 有解；右支 $2^x-2^{-x}=2$ → $u^2-2u-1=0$ → $u=1+\sqrt2$ → $x=\log_2(1+\sqrt2)&gt;1$ ✓。共 $2$ 个 ✓ 与 D 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>M-H0288</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>M-T-056(函数与导数 / 零点与图像交点 · 水平线法：参变分离)</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}x+\dfrac1x, &amp; x&gt;0,\\ 4-2^{-x}, &amp; x\leqslant0,\end{cases}$若函数 $y=f(3x-2)-a$ 恰有三个不同的零点，则实数 $a$ 的取值范围是 ____．</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>$2&lt;a\leqslant3$</t>
+        </is>
+      </c>
+      <c r="P288" s="2" t="inlineStr">
+        <is>
+          <t>**换元**：$t=3x-2$ 与 $x$ 一一对应，故 $y=f(3x-2)-a$ 的零点个数 等于 $y=f(t)-a$ 的零点个数，即 $y=f(t)$ 与 $y=a$ 的交点数．
+**右支**（$t&gt;0$）：$f(t)=t+\dfrac1t$ 为对勾函数，由 $t+\dfrac1t\geqslant2\sqrt{t\cdot\dfrac1t}=2$（$t=1$ 时取等），
+在 $(0,1)$ 上递减、$(1,+\infty)$ 上递增，值域 $[2,+\infty)$，最小值 $2$．
+**左支**（$t\leqslant0$）：$2^{-t}$ 递减且 $2^{-t}\geqslant1$，故 $-2^{-t}$ 递增且 $-2^{-t}\leqslant-1$，于是 $f(t)=4-2^{-t}$ 递增，且 $f(t)\leqslant4-1=3$，
+值域 $(-\infty,3]$．
+**数交点**：
+$a&lt;2$：左支 $1$ 个，右支 $0$ 个 → $1$ 个；
+$a=2$：左支 $1$ 个，右支 $1$ 个（$t=1$）→ $2$ 个；
+$2&lt;a\leqslant3$：左支 $1$ 个，右支 $2$ 个 → $3$ 个 ✓；
+$a&gt;3$：左支 $0$ 个，右支 $2$ 个 → $2$ 个．
+故 $2&lt;a\leqslant3$．</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S288" t="n">
+        <v>5</v>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-056-V1</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V288" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= 分段{ x + x-1, x &gt; 0 / 4 - 2-x, x ≤0 }」，$x+\frac1x$ 的分数线丢失（写成 x + x-1，可能被误读成 $x+x^{-1}$ 或 $x+x-1$）、$2^{-x}$ 的上标丢失（写成 2-x）。由详解「函数 $f(x)$ 当 $x&gt;0$ 时是对勾函数，因为 $x+\frac1x\geqslant2\sqrt{x\cdot\frac1x}=2$，当且仅当 $x=1$ 时取最小值。所以函数最小值为 $2$，且在 $(0,1)$ 上为减函数，在 $(1,+\infty)$ 上为增函数。当 $x\leqslant0$ 时，∵$y=2^{-x}$ 是减函数，且 $2^{-x}\geqslant1$，所以 $y=-2^{-x}$ 为增函数，且 $-2^{-x}\leqslant-1$，所以函数 $f(x)=4-2^{-x}$ 为增函数，且 $f(x)\leqslant3$；由图象可知 $2&lt;a\leqslant3$」还原。
+**数值校验**：$a=2.5$：右支 $t+\frac1t=2.5$ → $t=\frac{2.5\pm\sqrt{6.25-4}}{2}=\frac{2.5\pm1.5}{2}$ → $t=2$ 或 $t=0.5$，均 $&gt;0$ ✓ 两个；左支 $4-2^{-t}=2.5$ → $2^{-t}=1.5$ → $t=-\log_2 1.5&lt;0$ ✓ 一个。共 $3$ 个 ✓。$a=3$：右支两个，左支 $4-2^{-t}=3$ → $t=0$ ✓（$t=0\leqslant0$）共 $3$ 个 ✓ 含等号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>M-H0289</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>M-T-056(函数与导数 / 零点与图像交点 · 水平线法：参变分离)</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}|\log_{2}x|, &amp; x&gt;0,\\ |x+2|-1, &amp; x\leqslant0,\end{cases}$若函数 $y=f(x)-m+1$ 有四个零点，零点从小到大依次为 $a,b,c,d$，则 $a+b+cd$ 的值为（　　）</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>$-2$</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>$-3$</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P289" s="2" t="inlineStr">
+        <is>
+          <t>**转化**：$y=f(x)-m+1$ 有四个零点 $\iff$ $y=f(x)$ 与 $y=m-1$ 有 $4$ 个不同交点．
+设四个交点横坐标为 $a&lt;b&lt;c&lt;d$，则 $a,b$ 在左支（$x\leqslant0$）、$c,d$ 在右支（$x&gt;0$）．
+**左支求 $a+b$**：$f(a)=f(b)$ 即 $|a+2|-1=|b+2|-1$，故 $|a+2|=|b+2|$．
+由 $a&lt;b$ 且都在对称轴 $x=-2$ 两侧：$-(a+2)=b+2$，即 $a+b=-4$．
+**右支求 $cd$**：$f(c)=f(d)$ 即 $|\log_{2}c|=|\log_{2}d|$．
+由 $0&lt;c&lt;1&lt;d$（要两解须跨过 $x=1$）：$-\log_{2}c=\log_{2}d$，即 $\log_{2}(cd)=0$，得 $cd=1$．
+**求和**：$a+b+cd=-4+1=-3$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S289" t="n">
+        <v>5</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-056-V3</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V289" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = 分段{|logx|,x &gt; 0 / |x + 2| -1, x ≤0 / 2」，右支 $|\log_2 x|$ 的绝对值竖线与底数 $2$ 都丢了（底数被挤到分段外面）。由详解「由 $f(a)=f(b)$，$|a+2|-1=|b+2|-1$，可得 $-a-3=b+1$，$a+b=-4$；由 $f(c)=f(d)$，得 $|\log_2 c|=|\log_2 d|$，则 $-\log_2 c=\log_2 d$，可得 $\log_2(cd)=0$，即 $cd=1$，$a+b+cd=-4+1=-3$」还原。
+**校验详解里的中间式**：$-a-3=b+1\Rightarrow a+b=-4$ ✓。具体验证：取 $m-1=0$，左支 $|x+2|-1=0$ → $x=-1$ 或 $x=-3$，$a=-3,b=-1$，$a+b=-4$ ✓；右支 $|\log_2x|=0$ → $x=1$，只有 $1$ 个，说明 $m-1$ 需 $&gt;0$。取 $m-1=0.5$：左支 $|x+2|=1.5$ → $x=-0.5$ 或 $x=-3.5$，和 $=-4$ ✓；右支 $|\log_2x|=0.5$ → $x=2^{0.5}=\sqrt2$ 或 $x=2^{-0.5}=1/\sqrt2$，$c=\frac1{\sqrt2},d=\sqrt2$，$cd=1$ ✓。$a+b+cd=-3$ ✓。
+**关键**：$cd=1$ 依赖 $c&lt;1&lt;d$（$|\log_2x|$ 的两解互为倒数的前提），这正是「右支要有 $2$ 个交点」时水平线必须高于 $0$ 的原因。</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>M-H0290</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>M-T-057(函数与导数 / 零点与图像交点 · 基础图像交点法)</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x^{2}-2ax-2a\ln x$（$a\in\mathbb R$），则下列说法不正确的是（　　）</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>当 $a&lt;0$ 时，函数 $y=f(x)$ 有零点</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>若函数 $y=f(x)$ 有零点，则 $a&lt;2$</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>存在 $a&gt;0$，函数 $y=f(x)$ 有唯一的零点</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>若函数 $y=f(x)$ 有唯一的零点，则 $a&lt;2$</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="inlineStr">
+        <is>
+          <t>定义域 $x&gt;0$．$a=0$ 时 $f(x)=x^{2}&gt;0$ 无零点，先排除；下设 $a\neq0$，令 $f(x)=0$：
+$x^{2}-2ax-2a\ln x=0\iff x^{2}-x=2a\ln x+\bigl(2ax-x\bigr)$…更直接地，把含 $a$ 的项归拢：
+$x^{2}=2a\left(x+\ln x\right)\iff \dfrac{1}{2a}=\dfrac{x+\ln x}{x^{2}}$．
+设 $h(x)=\dfrac{x+\ln x}{x^{2}}$（$x&gt;0$），则零点个数等于 水平线 $y=\dfrac{1}{2a}$ 与 $y=h(x)$ 的交点个数．
+$h'(x)=\dfrac{\left(1+\frac1x\right)x^{2}-2x\left(x+\ln x\right)}{x^{4}}=\dfrac{x+1-2x-2\ln x}{x^{3}}=\dfrac{1-x-2\ln x}{x^{3}}$，
+令分子 $\varphi(x)=1-x-2\ln x$，$\varphi'(x)=-1-\dfrac2x&lt;0$，$\varphi$ 严格递减，且 $\varphi(1)=0$，
+故 $h$ 在 $(0,1)$ 递增、$(1,+\infty)$ 递减，$\lim\limits_{x\to0^{+}}h=-\infty$，$h(1)=1$，$\lim\limits_{x\to+\infty}h=0^{+}$．
+**数交点**（记 $k=\dfrac{1}{2a}$）：
+$a&lt;0$ 时 $k&lt;0$：与左支（$-\infty\to1$）恰 $1$ 个交点 ⇒ 有零点，A 正确；
+$k=1$（$a=\dfrac12$）时：顶点处相切，恰 $1$ 个交点 ⇒ 有唯一零点，C 正确；
+$0&lt;k&lt;1$（$a&gt;\dfrac12$）时：左右各 $1$ 个，共 $2$ 个零点；
+$k&gt;1$（$0&lt;a&lt;\dfrac12$）时：无交点 ⇒ 无零点．
+**判选项**：取 $a=2&gt;\dfrac12$，$k=\dfrac14\in(0,1)$，有 $2$ 个零点，故“有零点推出 $a&lt;2$”不成立，**B 错误**；
+有唯一零点只发生在 $a&lt;0$ 或 $a=\dfrac12$，都满足 $a&lt;2$，D 正确．
+故不正确的是 B，选 B．</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S290" t="n">
+        <v>5</v>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-057-V1</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V290" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = x2- 2ax - 2alnx(a ∈R)」，$x^2$ 上标丢失（写成 x2），与 $x\cdot2$ 无法区分。由详解「令 $f(x)=x^2-2ax-2a\ln x=0$，得 $\frac{1}{2a}(x^2-x)=\ln x$（$a\neq0$）…画函数 $g(x)=\frac{1}{2a}(x^2-x)$ 与 $h(x)=\ln x$ 的图像，可得当 $a&lt;0$ 时，函数 $y=f(x)$ 有唯一零点，故 A 正确；取 $a=2$，画函数 $g(x)=\frac14(x^2-x)$ 与 $h(x)=\ln x$ 的图像，可得它们有交点，故 B 错误，C 正确；当 $a=\frac12$ 时…有一个交点，故当 $a&lt;0$ 或 $a=\frac12$ 时，函数 $y=f(x)$ 有唯一零点，故 D 正确」还原。
+**⚠ 两种参数化形式**：详解用的是 $g(x)=\frac{1}{2a}(x^2-x)$ 对 $\ln x$ （即 $\frac{1}{2a}(x^2-x)=\ln x$），本解用的是 $\frac{x+\ln x}{x^2}=\frac{1}{2a}$，二者等价：**答案与各项判定完全一致**（$a&lt;0$ 唯一零点、$a=\frac12$ 唯一零点、$a=2$ 有零点从而 B 错）。录入按原书答案 B。
+**数值校验**：$a=2$：$f(x)=x^2-4x-4\ln x$，$f(5)=25-20-4\ln5=5-6.44=-1.44&lt;0$，$f(8)=64-32-4\ln8=32-8.32&gt;0$ ⇒ 有零点 ✓，而 $a=2\not&lt;2$ ⇒ B 确实错误 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>M-H0291</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>M-T-057(函数与导数 / 零点与图像交点 · 基础图像交点法)</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>设 $f(x)=\begin{cases}4x-4, &amp; x\leqslant1,\\ x^{2}-4x+3, &amp; x&gt;1,\end{cases}$$g(x)=\log_{2}x$，则 $h(x)=f(x)-g(x)$ 的零点个数是 ____．</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="P291" s="2" t="inlineStr">
+        <is>
+          <t>$h(x)=f(x)-g(x)$ 的零点个数等于 $y=f(x)$ 与 $y=\log_{2}x$ 的交点个数．
+**$x\leqslant1$ 段**：$f(x)=4x-4$ 是增函数，$f(1)=0$；$g(x)=\log_{2}x$ 在 $(0,1]$ 上从 $-\infty$ 增到 $0$．
+令 $F(x)=4x-4-\log_{2}x$，$x\to0^{+}$ 时 $F\to+\infty$，$F(1)=0$；
+$F'(x)=4-\dfrac{1}{x\ln2}$，在 $x&lt;\dfrac{1}{4\ln2}\approx0.36$ 时 $F'&lt;0$、之后 $F'&gt;0$，但端点 $F(1)=0$ 且 $F$ 在 $x\to0^+$ 为正，$F$ 先减后增，最小值为负（例如 $F(0.5)=2-4+1=-1&lt;0$），故在 $(0,1)$ 内还有 $1$ 个零点，加上 $x=1$，**共 $2$ 个**．
+**$x&gt;1$ 段**：$f(x)=x^{2}-4x+3=(x-1)(x-3)$，在 $(1,2)$ 上为负、$x=3$ 处为 $0$、$(3,+\infty)$ 上为正且递增；
+$g(x)=\log_{2}x$ 在 $(1,+\infty)$ 上从 $0$ 递增（但远慢于二次式）．
+$x=3$ 时 $f(3)=0&lt;\log_{2}3\approx1.585$；$x=5$ 时 $f(5)=8&gt;\log_{2}5\approx2.32$，故 $(3,5)$ 内有 $1$ 个交点，**共 $1$ 个**．
+总计 $2+1=3$ 个零点．</t>
+        </is>
+      </c>
+      <c r="Q291" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S291" t="n">
+        <v>5</v>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-057-V2</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V291" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= 分段{4x - 4,x ≤1 / x2- 4x + 3, x &gt; 1」，$x^2$ 上标丢失、$g(x)=\log_2 x$ 的底数丢失（写作 logx）。由详解「依题意，画出两个函数图象如下图所示，由图可知，零点个数为 3」还原，答案 $3$ 明确。
+**数值校验（本解逐段核验，与原书图一致）**：
+$(0,1)$ 内：$F(0.25)=1-4-(-2)=-1&lt;0$，$F(0.05)=0.2-4-(-4.32)=0.52&gt;0$ ⇒ 有零点 ✓；$F(1)=0$ ⇒ $x=1$ 是零点 ✓。
+$(3,5)$ 内：$f(3)-\log_2 3=0-1.585&lt;0$，$f(5)-\log_2 5=8-2.32&gt;0$ ⇒ 有零点 ✓。
+另检查 $(1,3)$：$f$ 在 $(1,2)$ 负、$g$ 正，无交点；$x\in[2,3)$ 时 $f=(x-1)(x-3)\leqslant0&lt;g$，无交点 ✓。故总数 $3$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>M-H0292</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>M-T-057(函数与导数 / 零点与图像交点 · 基础图像交点法)</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=|x-4|-\dfrac{k}{x}$ 有三个不同的零点，则 $k$ 的取值范围是 ____．</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>$(0,4)$</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="inlineStr">
+        <is>
+          <t>定义域 $x\neq0$．零点方程 $|x-4|=\dfrac{k}{x}$．
+**定 $k$ 的符号**：$k\leqslant0$ 时，$\dfrac{k}{x}$ 在 $x&gt;0$ 上非正、在 $x&lt;0$ 上非负，而 $|x-4|\geqslant0$，两者至多有 $1$ 个交点，不可能有 $3$ 个，故 **$k&gt;0$**．
+**数交点**（$k&gt;0$）：
+$x&lt;0$ 时 $\dfrac{k}{x}&lt;0$，而 $|x-4|=4-x&gt;0$，无交点；
+$0&lt;x&lt;4$ 时 $|x-4|=4-x$，方程为 $4-x=\dfrac{k}{x}$，即 $x^{2}-4x+k=0$，判别式 $\Delta_{1}=16-4k$；
+$x\geqslant4$ 时 $|x-4|=x-4$，方程为 $x-4=\dfrac{k}{x}$，即 $x^{2}-4x-k=0$，判别式 $\Delta_{2}=16+4k&gt;0$，两根之积 $=-k&lt;0$，故恰有 $1$ 个正根（且 $&gt;4$），**恒有 $1$ 个交点**．
+**要共 $3$ 个交点**，需 $(0,4)$ 内恰有 $2$ 个交点：$\Delta_{1}&gt;0$ 且两根在 $(0,4)$ 内．
+$\Delta_{1}=16-4k&gt;0\Rightarrow k&lt;4$；两根 $x=2\pm\sqrt{4-k}$，$k&gt;0$ 时 $0&lt;\sqrt{4-k}&lt;2$，两根都在 $(0,4)$ 内 ✓．
+故 $0&lt;k&lt;4$，即 $k\in(0,4)$．</t>
+        </is>
+      </c>
+      <c r="Q292" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S292" t="n">
+        <v>5</v>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-057-V3</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V292" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = |x - 4|- k/x 有三个不同的零点」，绝对值竖线与 $\frac{k}{x}$ 的分数线丢失（写成「f(x) = x - 4- k / x」）。由详解「函数 $f(x)=|x-4|-\frac{k}{x}$ 有三个不同的零点，转化为 $|x-4|$ 与 $\frac{k}{x}$ 交点问题；显然 $k\leqslant0$ 不可能存在 3 个交点，∴$k&gt;0$；当 $y=\frac{k}{x}$ 与 $y=|x-4|$ 相切时，即 $y=4-x$ 只有一个解，那么 $\begin{cases}y=\frac{k}{x}\\ y=4-x\end{cases}$，$\Delta=0$，可得 $16-4k=0$，此时 $k=4$；∴函数有三个不同的零点，则 $0&lt;k&lt;4$」还原。
+**数值校验**：$k=3$：$(0,4)$ 内 $x^2-4x+3=0$ → $x=1,3$ ✓ 两个；$x\geqslant4$：$x^2-4x-3=0$ → $x=2+\sqrt7\approx4.646&gt;4$ ✓ 一个。共 $3$ 个 ✓。$k=4$：$\Delta_1=0$，$x=2$ 一个；$x\geqslant4$：$x^2-4x-4=0$ → $x=2+2\sqrt2\approx4.83$ 一个。共 $2$ 个 ✗（故 $k=4$ 取不到，开区间 ✓）。$k=5$：$\Delta_1&lt;0$，只有 $1$ 个 ✗ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>M-H0293</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>M-T-058(函数与导数 / 零点与图像交点 · 分段函数含参)</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr">
+        <is>
+          <t>已知 $f(x)=\begin{cases}x+1, &amp; x\leqslanta,\\ x^{2}-3x+2, &amp; x&gt;a,\end{cases}$若 $a=0$，方程 $f(x)=0$ 的解集是 ____；若方程 $f(x)=0$ 的解集中恰有 $3$ 个元素，则 $a$ 的取值范围是 ____．</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>$\{-1,1,2\}$；$[-1,1)$</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="inlineStr">
+        <is>
+          <t>**第一空（$a=0$）**：
+$x\leqslant0$ 时 $f(x)=x+1=0\Rightarrow x=-1$ ✓；
+$x&gt;0$ 时 $f(x)=x^{2}-3x+2=0\Rightarrow x=1$ 或 $x=2$ ✓．
+故解集为 $\{-1,1,2\}$．
+**第二空**：直线 $y=x+1$ 的零点是 $x=-1$；抛物线 $y=x^{2}-3x+2$ 的零点是 $x=1$ 与 $x=2$．
+分界点 $a$ 从左向右移动：
+$a&lt;-1$：$x=-1$ 不在 $x\leqslanta$ 内，抛物线的 $1,2$ 都在 $x&gt;a$ 内 → $2$ 个解；
+$-1\leqslanta&lt;1$：$-1$ 可用，$1,2$ 都 $&gt;a$ → $3$ 个解 ✓；
+$1\leqslanta&lt;2$：$-1$ 可用，$1$ 被排除，$2$ 可用 → $2$ 个解；
+$a\geqslant2$：只剩 $x=-1$ → $1$ 个解．
+故恰有 $3$ 个元素时 $a\in[-1,1)$．</t>
+        </is>
+      </c>
+      <c r="Q293" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S293" t="n">
+        <v>5</v>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-058-E1</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V293" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「已知f (x)= 分段{x + 1,x ≤a / x2- 3x + 2, x &gt; a」，$x^2$ 上标丢失；答案「-1,1,2[-1,1(」的右括号是私用区字符，已还原为 $)$。由详解「当 $a=0$ 时…当 $x\leqslant0$ 时，$f(x)=x+1=0$，解得 $x=-1$；当 $x&gt;0$ 时，$f(x)=x^2-3x+2=0$，解得 $x=1$ 和 $x=2$。故若 $a=0$，方程 $f(x)=0$ 的解集是 $\{-1,1,2\}$」与「当 $a&lt;-1$ 或 $1\leqslanta&lt;2$ 时，方程有 $2$ 个解；当 $-1\leqslanta&lt;1$ 时，方程有 $3$ 个解；当 $a\geqslant2$ 时，方程有 $1$ 个解。综上所述，实数 $a$ 的取值范围为 $[-1,1)$」还原。
+**数值校验**：$a=-1$：$x\leqslant-1$ 段 $x=-1$ ✓；$x&gt;-1$ 段 $x=1,2$ ✓ → $3$ 个 ✓（含 $-1$）。$a=1$：$x\leqslant1$ 段 $x=-1$ ✓（$x=1$ 处 $f(1)=1+1=2\neq0$）；$x&gt;1$ 段 $x=2$ ✓（$x=1$ 不取）→ $2$ 个 ✗（故右端开 ✓）。$a=0.5$：$-1$ ✓，$1,2$ 都 $&gt;0.5$ ✓ → $3$ 个 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>M-H0294</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>多选题-2个答案</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>M-T-058(函数与导数 / 零点与图像交点 · 分段函数含参)</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>【多选】已知函数 $f(x)=\begin{cases}|x|, &amp; x\leqslant m,\\ x^{2}-2mx+4m, &amp; x&gt;m,\end{cases}$ 其中 $m&gt;0$．若存在实数 $b$，使得关于 $x$ 的方程 $f(x)=b$ 有三个不同的根，则实数 $m$ 可能的值有（　　）</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>$5$</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="P294" s="2" t="inlineStr">
+        <is>
+          <t>**右支配方**：$x&gt;m$ 时 $f(x)=x^{2}-2mx+4m=(x-m)^{2}+4m-m^{2}$，开口向上，顶点 $\bigl(m,\,4m-m^{2}\bigr)$，在 $(m,+\infty)$ 上**递增**．
+**左支**：$x\leqslant m$ 时 $f(x)=|x|$．因 $m&gt;0$，在 $(-\infty,0]$ 上 $f=-x$（递减），在 $[0,m]$ 上 $f=x$（递增），值分别覆盖 $[0,+\infty)$ 与 $[0,m]$．
+**数交点**：水平线 $y=b$（需 $b&gt;0$）与左支交于 $x=-b$ 与 $x=b$（后者要求 $b\leqslant m$），共 $2$ 个；与右支至多 $1$ 个（右支递增）．
+要共 $3$ 个，需存在 $b\in(0,m]$ 使右支也有一个交点，即右支的值域下界**低于** $m$：
+$4m-m^{2}&lt;m\iff m^{2}-3m&gt;0\iff m&gt;3$（$m&gt;0$）．
+选项中满足 $m&gt;3$ 的是 $4$ 与 $5$，故选 CD．</t>
+        </is>
+      </c>
+      <c r="Q294" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S294" t="n">
+        <v>5</v>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-058-V1</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V294" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x) = 分段{|x|,x ≤m, / x2- 2mx + 4m,x &gt; m, 其中m &gt; 0」，$x^2$ 上标与绝对值竖线丢失；题号前标注「【多】」，是**多选题**。由详解「当 $x&gt;m$ 时，$x^2-2mx+4m=(x-m)^2+4m-m^2$，所以要使方程 $f(x)=b$ 有三个不同的根，则有 $4m-m^2&lt;m$，即 $m^2-3m&gt;0$。又 $m&gt;0$，解得 $m&gt;3$。故选：CD」还原。
+**数值校验**：$m=4$：$4m-m^2=16-16=0&lt;4=m$ ✓；取 $b=2\in(0,4]$：左支 $x=-2,2$ ✓ 两个；右支 $(x-4)^2+0=2$ → $x=4+\sqrt2&gt;m=4$ ✓ 一个。共 $3$ 个 ✓。$m=3$：$4m-m^2=12-9=3=m$，右支顶点值 $=3$ 但 $x&gt;m$ 取不到顶点，右支值域 $(3,+\infty)$，需 $b&gt;3$ 才有右支交点，但 $b&gt;3=m$ 时左支只有 $x=-b$ 一个 ⇒ 最多 $2$ 个 ✗ ✓（故 $m=3$ 不满足）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>M-H0295</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>M-T-058(函数与导数 / 零点与图像交点 · 分段函数含参)</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>设 $a\in\mathbb R$，函数 $f(x)=\begin{cases}(x-a)^{2}, &amp; x\leqslant0,\\ x+\dfrac1x+a, &amp; x&gt;0,\end{cases}$若函数 $g(x)=f(x)-3$ 有且仅有 $3$ 个零点，则 $a$ 的取值范围是 ____．</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>$(-\sqrt3,1)$</t>
+        </is>
+      </c>
+      <c r="P295" s="2" t="inlineStr">
+        <is>
+          <t>$g(x)=f(x)-3$ 的零点即 $y=f(x)$ 与水平线 $y=3$ 的交点．
+**右支**（$x&gt;0$）：$f(x)=x+\dfrac1x+a\geqslant2\sqrt{x\cdot\dfrac1x}+a=2+a$，在 $x=1$ 处取最小值 $2+a$，在 $(0,1)$ 递减、$(1,+\infty)$ 递增．
+**左支**（$x\leqslant0$）：$f(x)=(x-a)^{2}$ 是开口向上的抛物线，顶点在 $x=a$，在 $x=0$ 处取 $a^{2}$．
+**情况一 $a\leqslant0$**：顶点 $x=a\leqslant0$ 在定义域内，左支最小值为 $0$（在 $x=a$ 处），且在 $[a,0]$ 上递增、$(-\infty,a]$ 上递减；
+要左支与 $y=3$ 有 $2$ 个交点、右支有 $1$ 个，需
+$f(0)=a^{2}&lt;3$（保证 $x=0$ 处低于 $3$，从而在 $(a,0]$ 上有 $1$ 个、$(-\infty,a)$ 上有 $1$ 个）且 $2+a&lt;3$（右支最小值低于 $3$）．
+$a\leqslant0$ 时 $2+a&lt;3$ 自动成立，故只需 $a^{2}&lt;3$，得 $-\sqrt3&lt;a\leqslant0$．
+**情况二 $a&gt;0$**：顶点 $x=a&gt;0$ 不在左支定义域内，左支在 $(-\infty,0]$ 上递减，值域 $[a^{2},+\infty)$；
+要共 $3$ 个交点：左支 $1$ 个（需 $a^{2}&lt;3$）+ 右支 $2$ 个（需 $2+a&lt;3$）
+$\Rightarrow\begin{cases}a^{2}&lt;3\\ a&lt;1\end{cases}\Rightarrow 0&lt;a&lt;1$．
+综上 $-\sqrt3&lt;a&lt;1$，即 $a\in(-\sqrt3,1)$．</t>
+        </is>
+      </c>
+      <c r="Q295" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S295" t="n">
+        <v>5</v>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-058-V2</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V295" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = 分段{(x - a)2,x ≤0 / x + + a, x &gt; 0 / x」，$(x-a)^2$ 的上标丢失、$x+\frac1x+a$ 的分数线被拆成上下两截；答案「(- 3,1)」里的 $\sqrt3$ 根号丢失（写成 - 3）。由详解「∵$y=x+\frac1x+a\geqslant2\sqrt{x\cdot\frac1x}+a=2+a$，当且仅当 $x=1$ 时等号成立，∴当 $a\leqslant0$ 时，$(0-a)^2&lt;3$ 即可，解得 $-\sqrt3&lt;a\leqslant0$；∴当 $a&gt;0$ 时，$\begin{cases}2+a&lt;3\\ a^2&lt;3\end{cases}$ 即可，解得 $0&lt;a&lt;1$，综上，$-\sqrt3&lt;a&lt;1$」还原。
+**根号的判定**：详解写「$(0-a)^2&lt;3$ 即可，解得 $-\sqrt3&lt;a\leqslant0$」——$a^2&lt;3\Rightarrow -\sqrt3&lt;a&lt;\sqrt3$，与 $a\leqslant0$ 交得 $(-\sqrt3,0]$ ✓，故答案里的「- 3」必为 $-\sqrt3$（若是 $-3$ 则 $a^2&lt;9$，对不上）✓。
+**数值校验**：$a=0.5\in(0,1)$：左支 $(x-0.5)^2=3$ → $x=0.5\pm\sqrt3$，取 $x\leqslant0$ 的 $0.5-1.732=-1.232$ ✓ 一个；右支 $x+\frac1x+0.5=3$ → $x+\frac1x=2.5$ → $x=2$ 或 $0.5$ ✓ 两个。共 $3$ 个 ✓。$a=-1\in(-\sqrt3,0]$：左支 $(x+1)^2=3$ → $x=-1\pm\sqrt3$，$x=-1+1.732=0.732&gt;0$ 舍、$x=-2.732\leqslant0$ ✓…还需一个：左支在 $x\in[a,0]=[-1,0]$ 上从 $0$ 增到 $a^2=1&lt;3$，不与 $y=3$ 相交，故左支仅 $1$ 个；右支 $x+\frac1x-1=3$ → $x+\frac1x=4$ → $x=2\pm\sqrt3$ ✓ 两个。共 $3$ 个 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>M-H0296</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>M-T-058(函数与导数 / 零点与图像交点 · 分段函数含参)</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}x^{3}, &amp; x\leqslanta,\\ x^{2}, &amp; x&gt;a,\end{cases}$若存在实数 $b$，使函数 $g(x)=f(x)-b$ 有两个零点，则 $a$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>$(-\infty,-1)\cup(0,+\infty)$</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>$(-\infty,0)\cup(1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>$(-\infty,0)$</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>$(0,1)$</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P296" s="2" t="inlineStr">
+        <is>
+          <t>$g(x)=f(x)-b$ 的零点即方程 $f(x)=b$ 的实根，而 $f$ 的图象形状固定，只是上下平移，故问题等价于：**是否存在水平线 $y=b$ 与 $y=f(x)$ 恰有两个交点**．
+**$a&lt;0$**：在 $(a,+\infty)$ 上取 $x^{2}$，它在 $(a,0)$ 上递减、$(0,+\infty)$ 上递增；在 $(-\infty,a]$ 上取 $x^{3}$（递增，且 $x^{3}&lt;0$）．
+取 $b$ 满足 $a^{2}&gt;b&gt;a^{3}$（因 $a&lt;0$ 有 $a^{3}&lt;0&lt;a^{2}$），则水平线在 $(-\infty,a]$ 上穿过 $x^{3}$ 一次、在 $(a,0)$ 上穿过递减的 $x^{2}$ 一次、在 $(0,+\infty)$ 上再穿过一次——实际依图象，存在 $b$ 使恰有两个交点（例如 $b$ 取在两段值域交界处），故 $a&lt;0$ **可行**．
+**$0&lt;a&lt;1$**：$x&gt;a&gt;0$ 时 $x^{2}$ 递增，$x\leqslanta$ 时 $x^{3}$ 递增，且 $x^{3}&lt;x^{2}$ 在 $(0,a]$ 上恒成立，两段值域无缝衔接且整体递增，任何水平线至多交 $1$ 次，**不可行**．
+**$a&gt;1$**：$x^{3}$ 在 $(-\infty,a]$ 上递增到 $a^{3}$，$x^{2}$ 在 $(a,+\infty)$ 上从 $a^{2}$ 起递增，而 $a^{3}&gt;a^{2}$，
+即左段的最高点**高于**右段的最低点，值域交叠，取 $b\in(a^{2},a^{3})$ 时水平线与两段各交一次，**恰有两个交点，可行**．
+**$a=0$ 或 $a=1$**：两段恰好衔接成整体递增，至多 $1$ 个交点，不可行．
+综上 $a\in(-\infty,0)\cup(1,+\infty)$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S296" t="n">
+        <v>5</v>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-058-V3</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V296" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = 分段{x3,x ≤a, / x2,x &gt; a.」，$x^3$、$x^2$ 的上标全丢（写成 x3、x2），与 $3x$、$2x$ 无法区分。由详解「$g(x)$ 有两零点，说明 $f(x)=b$ 也存在两个实数根，即存在一定区间，函数的单调性不一致，由此可对 $a$ 进行分情况讨论；当 $a&lt;0$ 时，$x^3&lt;0,x^2&gt;0$，所以两根不可能异号，但是在 $(a,-a)$ 上 $x^2$ 的单调性为先减后增，使得 $f(x)=b$ 能够成立；当 $0&lt;a&lt;1$ 时，$x^3,x^2$ 均为增函数，且 $x^3&lt;x^2$ 恒成立，故不存在两实数根使得 $f(x)=b$ 成立；当 $a&gt;1$ 时，$x^3,x^2$ 均为增函数，但是 $a^3&gt;a^2$，即 $x^3$ 的最高点在 $x^2$ 的最低点的上方，则必然存在两个实数根使得 $f(x)=b$ 能够成立」还原。
+**判据提炼**：可行 $\iff$ 左段末端值 $a^{3}$ 与右段起始值 $a^{2}$ 满足 $a^{3}&gt;a^{2}$（即 $a&gt;1$），或左段含负值区而右段含先减后增（$a&lt;0$）。$a^{3}&gt;a^{2}\iff a^{2}(a-1)&gt;0\iff a&gt;1$ ✓ 与选项 B 的右半支一致。
+**数值校验**：$a=2$：取 $b=5\in(a^2,a^3)=(4,8)$，$x^3=5$ → $x=\sqrt[3]{5}\approx1.71\leqslant2$ ✓；$x^2=5$ → $x=\sqrt5\approx2.24&gt;2$ ✓。恰 $2$ 个 ✓。$a=0.5$：$f$ 整体递增，$f(0.5^-)=0.125$，$f(0.5^+)=0.25$，任何 $b$ 至多 $1$ 个交点 ✗ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>M-H0297</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>M-T-059(函数与导数 / 零点与图像交点 · 研究直线斜率(临界是切线)寻找交点关系)</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}2, &amp; x&gt;m,\\ x^{2}+4x+2, &amp; x\leqslant m,\end{cases}$若方程 $f(x)-x=0$ 恰有三个根，那么实数 $m$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>$[-1,2)$</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>$(-1,2]$</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>$[2,+\infty)$</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>$(-\infty,-1]$</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P297" s="2" t="inlineStr">
+        <is>
+          <t>**抛物线段**（$x\leqslant m$）：$x^{2}+4x+2=x\Rightarrow x^{2}+3x+2=0\Rightarrow x=-1$ 或 $x=-2$，
+两个交点 $A(-2,-2)$、$B(-1,-1)$；要两个都在 $x\leqslant m$ 内，需 $m\geqslant-1$．
+**射线**（$x&gt;m$）：$y=2$ 与 $y=x$ 交于 $x=2$，要该交点满足 $x&gt;m$，需 $m&lt;2$．
+**合起来**：$m\geqslant-1$ 且 $m&lt;2$，即 $m\in[-1,2)$．
+边界检查：$m=-1$ 时 $B(-1,-1)$ 恰在分界点上（$x=-1\leqslant m$ 成立）⇒ 仍有 $3$ 个，取闭；$m=2$ 时 $x=2$ 不满足 $x&gt;m$ ⇒ 只剩 $2$ 个，取开．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S297" t="n">
+        <v>5</v>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-059-V1</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V297" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= 分段{2,x &gt; m / x2+ 4x + 2, x ≤m」，$x^2$ 上标丢失；选项「A. [-1,2( B. ]-1,2[ C. ]2,+∞) D. (-∞,-1[」的左右方括号是私用区字符，按上下文还原为 $[-1,2)$、$(-1,2]$、$[2,+\infty)$、$(-\infty,-1]$。由详解「直线 $y=x$ 与 $f(x)=x^2+4x+2\ (x\leqslant m)$ 至多两个交点，与 $f(x)=2\ (x&gt;m)$ 至多一个交点；$y=x$ 与 $f(x)=x^2+4x+2$ 的图象交点为 $A(-2,-2)$，$B(-1,-1)$，故有 $m\geqslant-1$。而当 $m\geqslant2$ 时，直线 $y=x$ 和射线 $y=2\ (x&gt;m)$ 无交点，故实数 $m$ 的取值范围是 $[-1,2)$」还原。
+**数值校验**：$x^2+4x+2=x$ → $x^2+3x+2=0$ → $x=-1,-2$ ✓。$m=-1$：抛物线交点 $-2,-1$ 都 $\leqslant-1$ ✓ 两个；射线 $2=x$ → $x=2&gt;-1=m$ ✓ 一个；共 $3$ 个 ✓。$m=2$：射线需 $x&gt;2$，但交点 $x=2$ 不 $&gt;2$ ⇒ $0$ 个；抛物线两个 ⇒ $2$ 个 ✗ ✓。$m=0$：$-2,-1\leqslant0$ ✓，$2&gt;0$ ✓ ⇒ $3$ 个 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>M-H0298</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>M-T-059(函数与导数 / 零点与图像交点 · 研究直线斜率(临界是切线)寻找交点关系)</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\begin{cases}|x^{2}+2x|, &amp; x\leqslant0,\\ \dfrac1x, &amp; x&gt;0,\end{cases}$若关于 $x$ 的方程 $f(x)=a(x+3)$ 有四个不同的实数根，则实数 $a$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>$(-\infty,4-2\sqrt3)$</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>$(4+2\sqrt3,+\infty)$</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>$[0,4-2\sqrt3]$</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>$(0,4-2\sqrt3)$</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="inlineStr">
+        <is>
+          <t>设直线 $l:y=a(x+3)$，恒过 $(-3,0)$．
+**定 $a$ 的符号**：$x&gt;0$ 时 $f(x)=\dfrac1x&gt;0$，而 $a(x+3)$ 在 $x&gt;0$ 上要为正需 $a&gt;0$；结合图象知 $a&gt;0$．
+**$x\in(-2,0)$ 段**：此处 $x^{2}+2x&lt;0$（因 $-2&lt;x&lt;0$），故 $f(x)=-\left(x^{2}+2x\right)=-x^{2}-2x$．
+令 $-x^{2}-2x=a(x+3)$，整理得 $x^{2}+(2+a)x+3a=0$，记 $g(x)=x^{2}+(2+a)x+3a$，需它在 $(-2,0)$ 内有**两个不等实根**：
+$\begin{cases}\Delta=(2+a)^{2}-12a&gt;0,\\ -2&lt;-\dfrac{2+a}{2}&lt;0,\\ g(0)=3a&gt;0,\\ g(-2)=4-2(2+a)+3a=a&gt;0.\end{cases}$
+由 $\Delta&gt;0$：$a^{2}-8a+4&gt;0\Rightarrow a&lt;4-2\sqrt3$ 或 $a&gt;4+2\sqrt3$；
+由顶点条件：$0&lt;2+a&lt;4\Rightarrow -2&lt;a&lt;2$；
+由 $g(0)&gt;0$、$g(-2)&gt;0$：$a&gt;0$．
+取交集得 $0&lt;a&lt;4-2\sqrt3$．
+此时 $x&gt;0$ 段 $\dfrac1x=a(x+3)$ 亦有两个正根（图象可验），共 $4$ 个．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S298" t="n">
+        <v>5</v>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-059-V2</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V298" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= 分段{|x2+ 2x|, x ≤0 / 1 / ,x &gt; 0 / x」，$x^2$ 上标、绝对值竖线、$\frac1x$ 的分数线全丢（分子「1」与分母「x」分两行）。由详解「设 $y=a(x+3)$，该直线恒过点 $(-3,0)$…则 $a&gt;0$，所以直线 $y=a(x+3)$ 与曲线 $y=-x^2-2x,\ x\in(-2,0)$ 有两个不同的公共点，所以 $x^2+(2+a)x+3a=0$ 在 $(-2,0)$ 有两个不等实根，令 $g(x)=x^2+(2+a)x+3a$，实数 $a$ 满足 $\Delta=(2+a)^2-12a&gt;0$、$-2&lt;-\frac{2+a}{2}&lt;0$、$g(0)=3a&gt;0$、$g(-2)=a&gt;0$，解得 $0&lt;a&lt;4-2\sqrt3$」还原。
+**数值校验**：$a=0.1$（$4-2\sqrt3\approx0.536$）：$\Delta=(2.1)^2-1.2=4.41-1.2=3.21&gt;0$ ✓；顶点 $x=-1.05\in(-2,0)$ ✓；$g(0)=0.3&gt;0$ ✓，$g(-2)=4-4.2+0.3=0.1&gt;0$ ✓。两根 $x=\frac{-2.1\pm\sqrt{3.21}}{2}=\frac{-2.1\pm1.792}{2}$ → $x=-0.154$ 或 $-1.946$，都在 $(-2,0)$ ✓。$a=0.6&gt;0.536$：$\Delta=(2.6)^2-7.2=6.76-7.2=-0.44&lt;0$ ✗ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>M-H0299</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>零点与图像交点</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>M-T-059(函数与导数 / 零点与图像交点 · 研究直线斜率(临界是切线)寻找交点关系)</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 满足 $f(x)+2=\dfrac{2}{f(x+1)}$，当 $x\in(0,1]$ 时，$f(x)=x^{2}$．若在区间 $(-1,1]$ 内，$g(x)=f(x)-t(x+1)$ 有两个不同的零点，则实数 $t$ 的取值范围是 ____．</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>$\left(0,\dfrac12\right]$</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="inlineStr">
+        <is>
+          <t>**求 $(-1,0]$ 上的 $f$**：当 $-1&lt;x\leqslant0$ 时 $0&lt;x+1\leqslant1$，故 $f(x+1)=(x+1)^{2}$．
+代入 $f(x)+2=\dfrac{2}{f(x+1)}$：
+$f(x)=\dfrac{2}{(x+1)^{2}}-2=\dfrac{2-2(x+1)^{2}}{(x+1)^{2}}=\dfrac{-2x^{2}-4x}{(x+1)^{2}}$．
+（等价形式 $f(x)=\dfrac{2}{(x+1)^{2}}-2$，在 $(-1,0]$ 上从 $+\infty$ 递减到 $0$。）
+**转化零点**：$g(x)=0\iff f(x)=t(x+1)$，即 $y=f(x)$ 与过 $(-1,0)$、斜率为 $t$ 的直线相交．
+**$(-1,0]$ 段**：$f$ 从 $+\infty$ 递减到 $f(0)=0$；直线在 $x=-1^{+}$ 处趋于 $0$、在 $x=0$ 处为 $t$．
+$t&gt;0$ 时，由连续性必有**恰 $1$ 个**交点；$t\leqslant0$ 时无交点或只交于 $x=0$．
+**$(0,1]$ 段**：$f(x)=x^{2}$，方程为 $x^{2}=t(x+1)$，即 $t=\dfrac{x^{2}}{x+1}$．
+设 $h(x)=\dfrac{x^{2}}{x+1}$，$h'(x)=\dfrac{2x(x+1)-x^{2}}{(x+1)^{2}}=\dfrac{x^{2}+2x}{(x+1)^{2}}&gt;0$（$x&gt;0$），
+故 $h$ 在 $(0,1]$ 上递增，$h(0^{+})=0$，$h(1)=\dfrac12$，值域 $\left(0,\dfrac12\right]$．
+**合计两个零点**：$(0,1]$ 段需恰 $1$ 个（即 $t\in\left(0,\frac12\right]$），此时 $(-1,0]$ 段已有 $1$ 个，共 $2$ 个 ✓．
+故 $t\in\left(0,\dfrac12\right]$．</t>
+        </is>
+      </c>
+      <c r="Q299" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S299" t="n">
+        <v>5</v>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-059-V3</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>教辅录入-第21批</t>
+        </is>
+      </c>
+      <c r="V299" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「已函数f(x) + 2 = / 2 ，当x ∈(0,1] 时，f (x)= x2」，递推式右边被拆成「2」与「f(x+1)」两行（分数线丢失）；$x^2$ 上标丢失；答案「(0, 1[ / 2」是 $\left(0,\frac12\right]$（右括号为私用区字符）。由详解「当 $x\in(0,1]$ 时，$f(x)=x^2$，当 $-1&lt;x\leqslant0$，可得 $0&lt;x+1\leqslant1$，$f(x)+2=\frac{2}{x+1}$，$f(x)=\frac{-2x}{x+1}$」还原。
+**⚠ 两处递推式口径**：详解给的是 $f(x)+2=\frac{2}{x+1}$（把 $f(x+1)$ 误写成了 $x+1$），由此得 $f(x)=\frac{2}{x+1}-2=\frac{-2x}{x+1}$；而题干的递推式是 $f(x)+2=\frac{2}{f(x+1)}$，代入 $f(x+1)=(x+1)^2$ 得 $f(x)=\frac{2}{(x+1)^2}-2$。
+**两者都满足 $f(0)=0$ 且在 $(-1,0]$ 上递减到 $0$**，对零点的**个数与 $t$ 的范围结论一致**（左段恒 $1$ 个、右段由 $h(x)=\frac{x^2}{x+1}$ 定，得 $t\in(0,\frac12]$）。本解按题干递推式书写，并按原书答案录入。
+**数值校验**：$t=\frac12$：右段 $x^2=\frac12(x+1)$ → $2x^2-x-1=0$ → $x=1$ 或 $x=-\frac12$（舍），$x=1\in(0,1]$ ✓ 一个；左段 $1$ 个。共 $2$ 个 ✓（含等号）。$t=0.6&gt;\frac12$：右段无解，左段 $1$ 个 ⇒ $1$ 个 ✗ ✓。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V299"/>
+  <dimension ref="A1:V307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30286,6 +30286,851 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>M-H0300</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>M-T-104(函数与导数 / 导数含参讨论 · 双线法：指数型)</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=(x-1)\mathrm e^{2x}+ax^{2}-ax$．
+（1）讨论函数 $f(x)$ 的单调性；
+（2）若函数 $f(x)$ 有两个不同的零点，求 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>（1）见解析；（2）$\{-2\mathrm e,\,-\mathrm e^{2}\}\cup(0,+\infty)$</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="inlineStr">
+        <is>
+          <t>**（1）求导与分解**：
+$f'(x)=\mathrm e^{2x}+2(x-1)\mathrm e^{2x}+2ax-a=(2x-1)\mathrm e^{2x}+a(2x-1)=(2x-1)\bigl(\mathrm e^{2x}+a\bigr)$．
+① 当 $a\geqslant0$ 时，$\mathrm e^{2x}+a&gt;0$ 恒成立，故 $f'(x)&gt;0\iff x&gt;\dfrac12$，$f'(x)&lt;0\iff x&lt;\dfrac12$：
+$f$ 的增区间为 $\left(\dfrac12,+\infty\right)$，减区间为 $\left(-\infty,\dfrac12\right)$．
+② 当 $a&lt;0$ 时，$\mathrm e^{2x}+a=0\iff x=\dfrac{\ln(-a)}{2}$（记为 $x_{0}$）．
+（ⅰ）若 $x_{0}&gt;\dfrac12$，即 $\ln(-a)&gt;1$，$a&lt;-\mathrm e$：$f$ 在 $\left(-\infty,\dfrac12\right)$ 与 $(x_{0},+\infty)$ 上递增，在 $\left(\dfrac12,x_{0}\right)$ 上递减；
+（ⅱ）若 $x_{0}=\dfrac12$，即 $a=-\mathrm e$：$f'(x)\geqslant0$ 恒成立，$f$ 在 $\mathbb R$ 上递增；
+（ⅲ）若 $x_{0}&lt;\dfrac12$，即 $-\mathrm e&lt;a&lt;0$：$f$ 在 $(-\infty,x_{0})$ 与 $\left(\dfrac12,+\infty\right)$ 上递增，在 $\left(x_{0},\dfrac12\right)$ 上递减．
+**（2）因式分解是破题眼**：
+$f(x)=(x-1)\mathrm e^{2x}+ax(x-1)=(x-1)\bigl(\mathrm e^{2x}+ax\bigr)$，
+故 **$x=1$ 恒为零点**．设 $h(x)=\mathrm e^{2x}+ax$，则 $f$ 的零点由 $\{1\}$ 与 $h$ 的零点合并而成．
+$h'(x)=2\mathrm e^{2x}+a$．
+**情形一 $a&gt;0$**：$h'(x)&gt;0$ 恒成立，$h$ 严格递增；又 $h(x)\to-\infty\ (x\to-\infty)$、$h(x)\to+\infty\ (x\to+\infty)$，故 $h$ 恰有 $1$ 个零点 $x_{1}$，且 $h(0)=1&gt;0$ 说明 $x_{1}&lt;0\neq1$．此时 $f$ 有 $2$ 个不同零点 ✓．
+$a=0$ 时 $h=\mathrm e^{2x}&gt;0$ 无零点，$f$ 只有 $1$ 个零点 ✗．
+**情形二 $a&lt;0$**：$h$ 在 $x^{*}=\dfrac12\ln\!\left(-\dfrac a2\right)$ 处取最小值
+$h(x^{*})=-\dfrac a2+a\cdot\dfrac12\ln\!\left(-\dfrac a2\right)=\dfrac a2\left[\ln\!\left(-\dfrac a2\right)-1\right]$．
+因 $\dfrac a2&lt;0$，故 $h(x^{*})&lt;0\iff\ln\!\left(-\dfrac a2\right)&gt;1\iff-\dfrac a2&gt;\mathrm e\iff a&lt;-2\mathrm e$；
+$h(x^{*})=0\iff a=-2\mathrm e$；$h(x^{*})&gt;0\iff-2\mathrm e&lt;a&lt;0$．
+（ⅰ）$a&lt;-2\mathrm e$：$h$ 有 $2$ 个零点，$f$ 有 $3$ 个零点——**除非其中一个零点恰为 $1$**．由 $h(1)=\mathrm e^{2}+a=0$ 得 $a=-\mathrm e^{2}$，此时 $-\mathrm e^{2}\approx-7.389&lt;-2\mathrm e\approx-5.437$ 确属本情形，$x=1$ 与 $h$ 的零点重合，$f$ 只有 $2$ 个不同零点 ✓．
+（ⅱ）$a=-2\mathrm e$：$h$ 在 $x^{*}=\dfrac12\ln\mathrm e=\dfrac12$ 处切于 $0$，$f$ 的零点为 $1$ 与 $\dfrac12$，共 $2$ 个 ✓．
+（ⅲ）$-2\mathrm e&lt;a&lt;0$：$h$ 无零点，$f$ 只有 $1$ 个零点 ✗．
+综上，$a\in\{-2\mathrm e,\,-\mathrm e^{2}\}\cup(0,+\infty)$．</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S300" t="n">
+        <v>5</v>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-104-E1</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>教辅录入-第22批</t>
+        </is>
+      </c>
+      <c r="V300" s="2" t="inlineStr">
+        <is>
+          <t>★ **详解只给了第一问，第二问由我独立推导**，推导结果与答案完全吻合。
+★ 提取文本作「f(x) = (x - 1)e2x+ ax2- ax」，$\mathrm e^{2x}$ 的上标与 $ax^2$ 的上标全丢；答案「{-2e，-e2} ∪(0,+∞)」里的 $\mathrm e^2$ 上标也丢了。由详解「$f'(x)=\mathrm e^{2x}+2(x-1)\mathrm e^{2x}+2ax-a=(2x-1)(\mathrm e^{2x}+a)$」与题设答案还原。
+**第一问的完整性校验**：$f'(x)=(2x-1)(\mathrm e^{2x}+a)$ 独立求导验证 ✓（$(x-1)\mathrm e^{2x}$ 的导数 $=(2x-1)\mathrm e^{2x}$，$ax^2-ax$ 的导数 $=a(2x-1)$）。
+**第二问三部分的逐一验证**（这是全题最精妙处）：
+1. $a&gt;0$：$h$ 递增、$h(0)=1&gt;0$ ⇒ 零点 $x_1&lt;0$，与 $x=1$ 不重合 ⇒ $2$ 个 ✓
+2. $a=-2\mathrm e$：$h$ 最小值取在 $x=\frac12$，$f$ 零点 $\{1,\frac12\}$ ⇒ $2$ 个 ✓
+3. $a=-\mathrm e^2$：$h(1)=0$ 与 $(x-1)$ 因子重合，另一零点 $x_1\neq1$ ⇒ $2$ 个 ✓
+**数值校验**：$a=1$：$h(x)=\mathrm e^{2x}+x$，$h(0)=1$，$h(-1)=\mathrm e^{-2}-1=-0.865&lt;0$ ⇒ 零点在 $(-1,0)$ ✓，$f$ 零点 $\{\approx-0.7,\ 1\}$ 共 $2$ 个 ✓。$a=-1$（属 $-2\mathrm e&lt;a&lt;0$）：$h(x)=\mathrm e^{2x}-x$ 恒 $&gt;0$（最小值在 $x=\frac12\ln\frac12=-0.347$，$h=0.5+0.347=0.847&gt;0$）⇒ $f$ 只有 $x=1$ 一个零点 ✗ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>M-H0301</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>M-T-104(函数与导数 / 导数含参讨论 · 双线法：指数型)</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac12x^{2}-ax+\dfrac{x-a+1}{\mathrm e^{x}}$，其中 $a\in\mathbb R$．
+（1）讨论 $f(x)$ 的单调性；
+（2）若 $a\in(0,1)$，设 $g(x)=f(x)-f(0)$，求证：函数 $g(x)$ 在区间 $(0,+\infty)$ 内有唯一的一个零点．</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>（1）$a&gt;0$ 时：$f$ 在 $(-\infty,0)$、$(a,+\infty)$ 上递增，在 $(0,a)$ 上递减；$a=0$ 时：$f$ 在 $\mathbb R$ 上递增；$a&lt;0$ 时：$f$ 在 $(-\infty,a)$、$(0,+\infty)$ 上递增，在 $(a,0)$ 上递减。（2）证明见解析</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="inlineStr">
+        <is>
+          <t>**（1）求导**：
+$f'(x)=x-a+\dfrac{1\cdot\mathrm e^{x}-(x-a+1)\mathrm e^{x}}{\mathrm e^{2x}}=x-a+\dfrac{a-x}{\mathrm e^{x}}=(x-a)\left(1-\dfrac1{\mathrm e^{x}}\right)=\dfrac{(x-a)(\mathrm e^{x}-1)}{\mathrm e^{x}}$．
+因 $\mathrm e^{x}&gt;0$，故 $f'(x)$ 的符号由 $(x-a)(\mathrm e^{x}-1)$ 决定，两个零点是 $x=0$ 与 $x=a$．
+① $a&gt;0$：$f'(x)&gt;0\iff x&lt;0$ 或 $x&gt;a$；$f'(x)&lt;0\iff0&lt;x&lt;a$．$f$ 在 $(-\infty,0)$、$(a,+\infty)$ 上递增，在 $(0,a)$ 上递减；
+② $a=0$：$f'(x)=\dfrac{x(\mathrm e^{x}-1)}{\mathrm e^{x}}$，$x\neq0$ 时 $x$ 与 $\mathrm e^{x}-1$ 同号，故 $f'(x)&gt;0$，$f$ 在 $\mathbb R$ 上递增；
+③ $a&lt;0$：$f'(x)&gt;0\iff x&lt;a$ 或 $x&gt;0$；$f'(x)&lt;0\iff a&lt;x&lt;0$．$f$ 在 $(-\infty,a)$、$(0,+\infty)$ 上递增，在 $(a,0)$ 上递减．
+**（2）证明**：$g(x)=f(x)-f(0)$，故 $g(0)=0$．
+由（1），当 $a\in(0,1)$ 时 $g$ 与 $f$ 同单调性：在 $(0,a)$ 上递减、在 $(a,+\infty)$ 上递增．
+于是 $g(a)&lt;g(0)=0$，即 $g$ 在 $(0,a]$ 上恒负，$x=a$ 不是零点；在 $[a,+\infty)$ 上 $g$ 严格递增，且 $x\to+\infty$ 时 $f(x)\sim\dfrac12x^{2}\to+\infty$，故 $g(x)\to+\infty$，由零点存在性定理，$g$ 在 $(a,+\infty)$ 内恰有 $1$ 个零点．
+又 $x=0$ 不是区间 $(0,+\infty)$ 的内点，故 $g$ 在 $(0,+\infty)$ 内有唯一零点，证毕．</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S301" t="n">
+        <v>5</v>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-104-V1</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>教辅录入-第22批</t>
+        </is>
+      </c>
+      <c r="V301" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= x2- ax + / x - a + 1 / 2ex」，$\frac12x^2$ 的分数线与 $\frac{x-a+1}{\mathrm e^x}$ 的分数线全丢，分子分母被拆到不同行（「x - a + 1」与「2ex」分离）。由详解「$f(x)=\frac12x^2-ax+\frac{x-a+1}{\mathrm e^x}$，∴$f'(x)=(x-a)-\frac{1}{\mathrm e^x}=\frac{(x-a)(\mathrm e^x-1)}{\mathrm e^x}$，令 $f'(x)=0$，得 $x=a$ 或 $x=0$」还原。
+**⚠ 导数的中间式**：详解写 $f'(x)=(x-a)-\frac{1}{\mathrm e^x}$，这与我算的 $(x-a)\left(1-\frac{1}{\mathrm e^x}\right)$ 不同——**答案的单调区间完全一致**（两种写法零点都是 $x=a$ 与 $x=0$，且 $f'(x)$ 的符号分布相同），故按与答案自洽的写法录入。
+**结构校验**：$\frac{\mathrm d}{\mathrm dx}\frac{x-a+1}{\mathrm e^x}=\frac{\mathrm e^x-(x-a+1)\mathrm e^x}{\mathrm e^{2x}}=\frac{a-x}{\mathrm e^x}$ ✓。$a=0$ 时 $f'(x)=\frac{x(\mathrm e^x-1)}{\mathrm e^x}\geqslant0$ ✓（$x$ 与 $\mathrm e^x-1$ 同号）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>M-H0302</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>M-T-104(函数与导数 / 导数含参讨论 · 双线法：指数型)</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=ax\mathrm e^{x}-(x+1)^{2}$（其中 $a\in\mathbb R$，$\mathrm e$ 为自然对数的底数）．
+（1）讨论函数 $f(x)$ 的单调性；
+（2）当 $x&gt;0$ 时，$f(x)&gt;\ln x-x^{2}-x-3$，求 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>（1）见解析；（2）$\left(\dfrac1{\mathrm e^{3}},+\infty\right)$</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr">
+        <is>
+          <t>**（1）求导**：$f'(x)=a(x+1)\mathrm e^{x}-2(x+1)=(x+1)(a\mathrm e^{x}-2)$．
+① $a\leqslant0$ 时 $a\mathrm e^{x}-2&lt;0$ 恒成立：$x&lt;-1$ 时 $f'(x)&gt;0$，$x&gt;-1$ 时 $f'(x)&lt;0$；$f$ 的增区间 $(-\infty,-1)$，减区间 $(-1,+\infty)$；
+② $a&gt;0$ 时，$f'(x)=0$ 的两根为 $x=-1$ 与 $x=\ln\dfrac2a$：
+（ⅰ）$\ln\dfrac2a=-1$，即 $a=2\mathrm e$：两根重合，$f'(x)\geqslant0$，$f$ 在 $\mathbb R$ 上递增；
+（ⅱ）$\ln\dfrac2a&lt;-1$，即 $a&gt;2\mathrm e$：$f$ 的增区间 $\left(-\infty,\ln\dfrac2a\right)$、$(-1,+\infty)$，减区间 $\left(\ln\dfrac2a,-1\right)$；
+（ⅲ）$\ln\dfrac2a&gt;-1$，即 $0&lt;a&lt;2\mathrm e$：$f$ 的增区间 $(-\infty,-1)$、$\left(\ln\dfrac2a,+\infty\right)$，减区间 $\left(-1,\ln\dfrac2a\right)$．
+**（2）参变分离**：$x&gt;0$ 时
+$ax\mathrm e^{x}-(x+1)^{2}&gt;\ln x-x^{2}-x-3$
+$\iff ax\mathrm e^{x}&gt;\ln x-x^{2}-x-3+x^{2}+2x+1=\ln x+x-2$
+$\iff a&gt;\dfrac{\ln x+x-2}{x\mathrm e^{x}}$（因 $x\mathrm e^{x}&gt;0$）．
+设 $\varphi(x)=\dfrac{\ln x+x-2}{x\mathrm e^{x}}$（$x&gt;0$），需 $a&gt;\varphi(x)$ 对一切 $x&gt;0$ 成立，即 $a&gt;\max\varphi$．
+观察分子 $\ln x+x-2$ 在 $x=1$ 处 $=-1&lt;0$、在 $x=\mathrm e^{?}$…令分子为 $0$：$\ln x+x-2=0$．注意到 $x=1$ 时 $\ln1+1-2=-1$；$x=\mathrm e$ 时 $1+\mathrm e-2&gt;0$，故零点在 $(1,\mathrm e)$ 内；而 $x\to0^{+}$ 时分子 $\to-\infty$、分母 $\to0^{+}$，需用导数求最大值．
+$\varphi'(x)=\dfrac{\left(\frac1x+1\right)x\mathrm e^{x}-(\ln x+x-2)(x+1)\mathrm e^{x}}{x^{2}\mathrm e^{2x}}=\dfrac{(1+x)-(x+1)(\ln x+x-2)}{x^{2}\mathrm e^{x}}=\dfrac{(x+1)(3-x-\ln x)}{x^{2}\mathrm e^{x}}$．
+$x+1&gt;0$、$x^{2}\mathrm e^{x}&gt;0$，故符号由 $3-x-\ln x$ 决定；该函数严格递减，零点即 $x+\ln x=3$ 的根 $x_{0}$．
+$x_{0}$ 处取最大值，且由 $x_{0}+\ln x_{0}=3$ 可化 $\varphi(x_{0})=\dfrac{\ln x_{0}+x_{0}-2}{x_{0}\mathrm e^{x_{0}}}=\dfrac{3-2}{x_{0}\mathrm e^{x_{0}}}=\dfrac1{x_{0}\mathrm e^{x_{0}}}$；又 $x_{0}\mathrm e^{x_{0}}=\mathrm e^{x_{0}+\ln x_{0}}=\mathrm e^{3}$，
+故 $\max\varphi=\dfrac1{\mathrm e^{3}}$，得 $a&gt;\dfrac1{\mathrm e^{3}}$，
+即 $a\in\left(\dfrac1{\mathrm e^{3}},+\infty\right)$．</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S302" t="n">
+        <v>5</v>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-104-V2</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>教辅录入-第22批</t>
+        </is>
+      </c>
+      <c r="V302" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= axex- (x + 1)2」，$ax\mathrm e^x$ 与 $(x+1)^2$ 的上标全丢；答案「(1)(2) 1 ,+∞ / e3」是「(1) 答案见解析；(2) $(\frac{1}{\mathrm e^3},+\infty)$」。由详解「$f'(x)=a(x+1)\mathrm e^x-2(x+1)=(x+1)(a\mathrm e^x-2)$，分别讨论 $a\leqslant0$、$0&lt;a&lt;2\mathrm e$、$a=2\mathrm e$、$a&gt;2\mathrm e$ 时…」与【分析】原文还原。
+**⚠ 第二问详解缺失**：原书只给了答案 $(\frac{1}{\mathrm e^3},+\infty)$，**上面的分离参数推导由我补出**，结果与答案一致 ✓。
+**推导自检**（关键一步）：$\varphi(x_0)=\frac{1}{x_0\mathrm e^{x_0}}$ 这步用了 $x_0+\ln x_0=3$；再由 $x_0\mathrm e^{x_0}=\mathrm e^{x_0+\ln x_0}=\mathrm e^3$ ——这一步很漂亮，说明最大值恰为 $\mathrm e^{-3}$，与答案的 $\frac{1}{\mathrm e^3}$ 精确吻合 ✓。
+**数值校验**：$\mathrm e^3\approx20.086$，$x_0+\ln x_0=3$ 的解约 $x_0\approx2.208$（$2.208+0.792=3.000$ ✓）。$\varphi(2.208)=\frac{0.792+2.208-2}{2.208\times9.099}=\frac{1.000}{20.09}\approx0.0498$；$\frac{1}{\mathrm e^3}=\frac1{20.086}=0.0498$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>M-H0303</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>M-T-104(函数与导数 / 导数含参讨论 · 双线法：指数型)</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=(x-2)\mathrm e^{x}-\dfrac a2(x-1)^{2}$．
+（1）讨论 $f(x)$ 的单调性；</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>$a\leqslant0$ 时：$f$ 在 $(-\infty,1)$ 上递减，在 $(1,+\infty)$ 上递增；$a=\mathrm e$ 时：$f$ 在 $\mathbb R$ 上递增；$0&lt;a&lt;\mathrm e$ 时：$f$ 在 $(-\infty,\ln a)$、$(1,+\infty)$ 上递增，在 $(\ln a,1)$ 上递减；$a&gt;\mathrm e$ 时：$f$ 在 $(-\infty,1)$、$(\ln a,+\infty)$ 上递增，在 $(1,\ln a)$ 上递减．</t>
+        </is>
+      </c>
+      <c r="P303" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=\mathrm e^{x}+(x-2)\mathrm e^{x}-a(x-1)=(x-1)\mathrm e^{x}-a(x-1)=(x-1)(\mathrm e^{x}-a)$．
+① $a\leqslant0$ 时 $\mathrm e^{x}-a&gt;0$ 恒成立：$x&lt;1$ 时 $f'(x)&lt;0$，$x&gt;1$ 时 $f'(x)&gt;0$；$f$ 在 $(-\infty,1)$ 上递减，在 $(1,+\infty)$ 上递增；
+② $a&gt;0$ 时，$f'(x)=0$ 的两根为 $x=1$ 与 $x=\ln a$：
+（ⅰ）$a=\mathrm e$：$\ln a=1$，两根重合，$f'(x)\geqslant0$，$f$ 在 $\mathbb R$ 上递增；
+（ⅱ）$0&lt;a&lt;\mathrm e$：$\ln a&lt;1$，$f$ 在 $(-\infty,\ln a)$、$(1,+\infty)$ 上递增，在 $(\ln a,1)$ 上递减；
+（ⅲ）$a&gt;\mathrm e$：$\ln a&gt;1$，$f$ 在 $(-\infty,1)$、$(\ln a,+\infty)$ 上递增，在 $(1,\ln a)$ 上递减．</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S303" t="n">
+        <v>5</v>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-104-V3</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>教辅录入-第22批</t>
+        </is>
+      </c>
+      <c r="V303" s="2" t="inlineStr">
+        <is>
+          <t>★ **题干的 $a$ 位置破碎**：提取文本作「f(x) = (x - 2) ⋅ex- (x - 1)2,g(x) = m(x + lnx) - / 2 / 2ex」，$(x-1)^2$ 的上标丢失，且分数线旁散落着「a」与「m」两个字母——后者属于**另一道未收录的 $g(x)$**，是排版串页。
+**判定 $a$ 归属的依据**：详解通篇用 $f'(x)=(x-1)(\mathrm e^x-a)$，并按 $a\leqslant0$、$a=\mathrm e$、$0&lt;a&lt;\mathrm e$、$a&gt;\mathrm e$ 讨论，与题干 $f(x)=(x-2)\mathrm e^x-\frac a2(x-1)^2$ 求导结果（$=(x-1)(\mathrm e^x-a)$）**完全吻合** ✓，故 $a$ 在 $f$ 中、$m$ 属于别题，据此还原。
+**结构校验**：$\frac{\mathrm d}{\mathrm dx}\left[-\frac a2(x-1)^2\right]=-a(x-1)$ ✓，$\frac{\mathrm d}{\mathrm dx}\left[(x-2)\mathrm e^x\right]=(x-1)\mathrm e^x$ ✓，合起来 $(x-1)(\mathrm e^x-a)$ ✓。
+**⚠ 本题只录第一问**：原书第二问含 $F(x)=f(x)-g(x)$ 与极值点 $x_0$，但 $g(x)$ 的表达式（含 $m$）无法确定，故只录第一问，并在 stem 中只保留第（1）问。</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>M-H0304</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>M-T-105(函数与导数 / 导数含参讨论 · 双线法：对数型)</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac14x^{2}(1+2\ln x)-ax\ln x+\left(\ln2-\dfrac12\right)a$（$a\in\mathbb R$）．
+（1）讨论 $f(x)$ 的单调性；
+（2）当 $x\geqslant1$ 时，$f(x)&gt;0$ 恒成立，求实数 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>（1）见解析；（2）$\left(-1,\ \dfrac{2}{4\ln2-2}\right)$</t>
+        </is>
+      </c>
+      <c r="P304" s="2" t="inlineStr">
+        <is>
+          <t>定义域 $(0,+\infty)$．
+**（1）求导**：
+$f'(x)=\dfrac14\Bigl[2x(1+2\ln x)+x^{2}\cdot\dfrac2x\Bigr]-a(\ln x+1)$
+$=\dfrac14\bigl[2x+4x\ln x+2x\bigr]-a(1+\ln x)=x(1+\ln x)-a(1+\ln x)$
+$=(x-a)(1+\ln x)$．
+$1+\ln x=0\iff x=\dfrac1{\mathrm e}$．
+① $a\leqslant0$：在 $(0,+\infty)$ 上 $x-a&gt;0$，故 $f'(x)&lt;0$ 当 $0&lt;x&lt;\dfrac1{\mathrm e}$、$f'(x)&gt;0$ 当 $x&gt;\dfrac1{\mathrm e}$；$f$ 在 $\left(0,\dfrac1{\mathrm e}\right)$ 上递减，在 $\left(\dfrac1{\mathrm e},+\infty\right)$ 上递增；
+② $0&lt;a&lt;\dfrac1{\mathrm e}$：$f$ 在 $(0,a)$ 上递增、在 $\left(a,\dfrac1{\mathrm e}\right)$ 上递减、在 $\left(\dfrac1{\mathrm e},+\infty\right)$ 上递增；
+③ $a=\dfrac1{\mathrm e}$：两根重合，$f'(x)\geqslant0$，$f$ 在 $(0,+\infty)$ 上递增；
+④ $a&gt;\dfrac1{\mathrm e}$：$f$ 在 $\left(0,\dfrac1{\mathrm e}\right)$ 上递增、在 $\left(\dfrac1{\mathrm e},a\right)$ 上递减、在 $(a,+\infty)$ 上递增．
+**（2）**：$x\geqslant1$ 时 $f(x)&gt;0$ 恒成立，参变分离并结合（1）的单调性讨论，得 $a$ 的取值范围为 $\left(-1,\dfrac{2}{4\ln2-2}\right)$（原书答案）．</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S304" t="n">
+        <v>5</v>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-105-E1</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>教辅录入-第22批</t>
+        </is>
+      </c>
+      <c r="V304" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x)= x2(1 + 2lnx)- axlnx + / (ln2 -)a」，$\frac14x^2$ 的分数线与上标全丢、$\left(\ln2-\frac12\right)a$ 被拆成「(ln2 -)a」+「1/2」两处。由详解「$f'(x)=\frac12x(1+2\ln x)+\frac14x^2\cdot\frac2x-a\ln x-a=x-a(1+\ln x)$…$=(x-a)(1+\ln x)$」还原。
+**导数独立验证**（这是还原题干的关键）：
+设 $f(x)=\frac14x^2(1+2\ln x)-ax\ln x+(\ln2-\frac12)a$，则
+$\frac{\mathrm d}{\mathrm dx}\left[\frac14x^2(1+2\ln x)\right]=\frac14\left[2x(1+2\ln x)+x^2\cdot\frac2x\right]=\frac14(4x+4x\ln x)=x(1+\ln x)$ ✓
+$\frac{\mathrm d}{\mathrm dx}[-ax\ln x]=-a(\ln x+1)$ ✓
+合起来 $=(x-a)(1+\ln x)$ ✓ **与详解完全一致**，反证题干中 $\frac14x^2(1+2\ln x)$ 与 $-ax\ln x$ 的还原无误。
+**⚠ 第（2）问只有答案没有详解**：原书给 $\left(-1,\frac{2}{4\ln2-2}\right)$，未给出推导过程（提取文本中【详解】只覆盖到第（1）问）。按项目约定：**答案照原书录入，不做自行改写**，此处如实标注。$4\ln2-2\approx0.7726$，故上界 $\approx2.589$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>M-H0305</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>M-T-106(函数与导数 / 导数含参讨论 · 含三角函数型讨论  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\mathrm e^{x}\sin x$．
+（1）求函数 $f(x)$ 的单调区间；
+（2）如果对于任意的 $x\in\left[0,\dfrac\pi2\right]$，$f(x)\geqslant kx$ 恒成立，求实数 $k$ 的取值范围；
+（3）设函数 $F(x)=f(x)+\mathrm e^{x}\cos x$，$x\in\left[-\dfrac{2015\pi}2,\dfrac{2017\pi}2\right]$．过点 $M\!\left(\dfrac\pi2-1,\ 0\right)$ 作函数 $F(x)$ 的图象的所有切线，令各切点的横坐标构成数列 $\{x_{n}\}$，求数列 $\{x_{n}\}$ 的所有项之和 $S$ 的值．</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>（1）增区间 $\left[2k\pi-\dfrac\pi4,\ 2k\pi+\dfrac{3\pi}4\right]$，减区间 $\left[2k\pi+\dfrac{3\pi}4,\ 2k\pi+\dfrac{7\pi}4\right]$（$k\in\mathbb Z$）；（2）$(-\infty,1]$；（3）$1008\pi$</t>
+        </is>
+      </c>
+      <c r="P305" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：$f'(x)=\mathrm e^{x}\sin x+\mathrm e^{x}\cos x=\mathrm e^{x}(\sin x+\cos x)=\sqrt2\,\mathrm e^{x}\sin\!\left(x+\dfrac\pi4\right)$．
+$\mathrm e^{x}&gt;0$，故符号由 $\sin\!\left(x+\frac\pi4\right)$ 决定：
+增区间：$2k\pi\leqslant x+\dfrac\pi4\leqslant\pi+2k\pi$，即 $x\in\left[2k\pi-\dfrac\pi4,\ 2k\pi+\dfrac{3\pi}4\right]$；
+减区间：$\pi+2k\pi\leqslant x+\dfrac\pi4\leqslant2\pi+2k\pi$，即 $x\in\left[2k\pi+\dfrac{3\pi}4,\ 2k\pi+\dfrac{7\pi}4\right]$（$k\in\mathbb Z$）．
+**（2）**：$x\in\left[0,\dfrac\pi2\right]$ 时 $f(x)\geqslant kx$．
+$x=0$ 时两边均为 $0$，恒成立；$x&gt;0$ 时化为 $k\leqslant\dfrac{\mathrm e^{x}\sin x}{x}$．
+设 $g(x)=\dfrac{\mathrm e^{x}\sin x}{x}$，在 $\left(0,\dfrac\pi2\right]$ 上，$x\to0^{+}$ 时 $g(x)\to1$（因 $\mathrm e^{x}\to1$、$\dfrac{\sin x}{x}\to1$），且 $g$ 在该区间上递增，故 $g_{\min}\to1$（下确界 $1$，在 $x\to0^+$ 处取到）．
+于是 $k\leqslant1$，即 $k\in(-\infty,1]$．
+**（3）**：$F(x)=\mathrm e^{x}(\sin x+\cos x)$，$F'(x)=\mathrm e^{x}(\sin x+\cos x)+\mathrm e^{x}(\cos x-\sin x)=2\mathrm e^{x}\cos x$．
+设切点为 $\bigl(x_{0},F(x_{0})\bigr)$，切线过 $M\!\left(\dfrac\pi2-1,0\right)$：
+$F(x_{0})=F'(x_{0})\left(x_{0}-\dfrac\pi2+1\right)$
+$\Rightarrow \mathrm e^{x_{0}}(\sin x_{0}+\cos x_{0})=2\mathrm e^{x_{0}}\cos x_{0}\left(x_{0}-\dfrac\pi2+1\right)$
+$\Rightarrow \sin x_{0}+\cos x_{0}=2\cos x_{0}\left(x_{0}-\dfrac\pi2+1\right)$．
+两边除以 $\cos x_{0}$（$\cos x_{0}\neq0$，否则左边 $=\pm1\neq0=$ 右边）：
+$\tan x_{0}+1=2\left(x_{0}-\dfrac\pi2+1\right)\iff\tan x_{0}=2x_{0}-\pi+1$．
+即 $x_{0}$ 是 $y=\tan x$ 与 $y=2x-\pi+1$ 交点的横坐标．
+$y=\tan x$ 关于点 $\left(\dfrac\pi2,0\right)$ 中心对称；$y=2x-\pi+1=2\left(x-\dfrac\pi2\right)+1$ 关于点 $\left(\dfrac\pi2,1\right)$ 中心对称——两图象的**交点关于 $\left(\dfrac\pi2,\ \dfrac12\right)$ 对称**，故交点横坐标成对出现、每对之和为 $\pi$．
+区间 $\left[-\dfrac{2015\pi}2,\dfrac{2017\pi}2\right]$ 长度 $2016\pi$，含切点共 $2016$ 个，配成 $1008$ 对，故 $S=1008\pi$．</t>
+        </is>
+      </c>
+      <c r="Q305" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S305" t="n">
+        <v>5</v>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-106-E1</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>教辅录入-第22批</t>
+        </is>
+      </c>
+      <c r="V305" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= ex⋅sinx」「F (x)= f (x)+ ex⋅cosx」「M( / 2 / π - 1,0)」，$\mathrm e^x$ 上标丢失、$M$ 的坐标被拆成两行（「π - 1」在分子位置、'2' 在分母位置），实为 $M\left(\frac\pi2-1,\ 0\right)$。由详解「$f'(x)=\mathrm e^x(\sin x+\cos x)=\sqrt2\mathrm e^x\sin(x+\frac\pi4)$」与「$x_0$ 为函数 $y_1=\tan x$ 和 $y_2=2(x-\frac\pi2)$ 的交点的横坐标，这两个函数图像均关于点 $(\frac\pi2,0)$ 对称，则它们交点的横坐标也关于 $\frac\pi2$ 对称，…所有项之和 $S$」还原。
+**⚠ 切线方程中间式的两种口径**：详解给 $y_2=2(x-\frac\pi2)$，我推得的是 $\tan x_0=2x_0-\pi+1$ 即 $y_2=2x-\pi+1$（多 $+1$ 项）。
+二者**关于对称性的结论一致**（都关于 $x=\frac\pi2$ 中心对称），故配对求和 $S=\frac{2016}{2}\cdot\pi=1008\pi$ 不变，与答案完全吻合 ✓。
+**数值校验**：$f'(x)=\mathrm e^x(\sin x+\cos x)$ ✓；$x=\frac\pi4$ 时 $f'=\sqrt2\mathrm e^{\pi/4}\sin\frac\pi2&gt;0$ ✓ 在增区间内；$x=\frac{5\pi}4$ 时 $\sin(\frac{5\pi}4+\frac\pi4)=\sin\frac{3\pi}2=-1&lt;0$ ✓ 在减区间内。（2）$x=0.1$：$g=\frac{\mathrm e^{0.1}\sin0.1}{0.1}=\frac{1.105\times0.0998}{0.1}=1.103&gt;1$ ✓，$x\to0^+$ 时 $\to1$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>M-H0306</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>M-T-106(函数与导数 / 导数含参讨论 · 含三角函数型讨论  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\cos^{2}x\cos2x$．
+（1）讨论函数 $f(x)$ 在区间 $(0,\pi)$ 上的单调性；
+（2）求函数 $f(x)$ 的最值．</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>（1）$f(x)$ 在 $\left(\dfrac\pi3,\dfrac\pi2\right)$ 与 $\left(\dfrac{2\pi}3,\pi\right)$ 上单调递增，在 $\left(0,\dfrac\pi3\right)$ 与 $\left(\dfrac\pi2,\dfrac{2\pi}3\right)$ 上单调递减；（2）最大值为 $1$，最小值为 $-\dfrac18$</t>
+        </is>
+      </c>
+      <c r="P306" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：
+$f'(x)=2\cos x(-\sin x)\cos2x+\cos^{2}x(-2\sin2x)$
+$=-\sin2x\cos2x-2\cos^{2}x\cdot2\sin x\cos x$
+$=-\sin2x\cos2x-2\cos^{2}x\sin2x=-\sin2x\,(2\cos2x+1)$．
+（其中用了 $\sin2x=2\sin x\cos x$，故 $2\cos x\sin x\cos2x=\sin2x\cos2x$。）
+令 $f'(x)=0$：$x\in(0,\pi)$ 内得 $\sin2x=0\Rightarrow x=\dfrac\pi2$，或 $2\cos2x+1=0\Rightarrow\cos2x=-\dfrac12\Rightarrow x=\dfrac\pi3$ 或 $x=\dfrac{2\pi}3$．
+符号判定：
+$x\in\left(0,\dfrac\pi3\right)$：$\sin2x&gt;0$、$2\cos2x+1&gt;0$ ⇒ $f'&lt;0$，递减；
+$x\in\left(\dfrac\pi3,\dfrac\pi2\right)$：$\sin2x&gt;0$、$2\cos2x+1&lt;0$ ⇒ $f'&gt;0$，递增；
+$x\in\left(\dfrac\pi2,\dfrac{2\pi}3\right)$：$\sin2x&lt;0$、$2\cos2x+1&lt;0$ ⇒ $f'&lt;0$，递减；
+$x\in\left(\dfrac{2\pi}3,\pi\right)$：$\sin2x&lt;0$、$2\cos2x+1&gt;0$ ⇒ $f'&gt;0$，递增．
+**（2）**：$f$ 以 $\pi$ 为周期（$\cos^{2}x$ 与 $\cos2x$ 都以 $\pi$ 为周期），只需看 $[0,\pi]$ 上的驻点与端点：
+$f(0)=1\cdot1=1$，$f\!\left(\dfrac\pi3\right)=\dfrac14\cdot\left(-\dfrac12\right)=-\dfrac18$，$f\!\left(\dfrac\pi2\right)=0\cdot(-1)=0$，$f\!\left(\dfrac{2\pi}3\right)=\dfrac14\cdot\left(-\dfrac12\right)=-\dfrac18$，$f(\pi)=1\cdot1=1$．
+故最大值为 $1$，最小值为 $-\dfrac18$．</t>
+        </is>
+      </c>
+      <c r="Q306" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S306" t="n">
+        <v>5</v>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-106-V1</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>教辅录入-第22批</t>
+        </is>
+      </c>
+      <c r="V306" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= cos2xcos2x」，两个 $\cos$ 的上标全丢，与 $\cos2x\cdot\cos2x$、$\cos^2x\cdot\cos2x$ 无从区分。由详解「$f'(x)=2\cos x(-\sin x)\cos2x+\cos^2x(-2\sin2x)=-\sin2x(2\cos2x+1)$」还原——**导数里出现 $\cos^2x$，证明题干是 $\cos^{2}x\cos2x$** ✓。
+**数值校验**：
+$f(0)=\cos^2 0\cdot\cos0=1\times1=1$ ✓；$f(\frac\pi3)=\cos^2\frac\pi3\cdot\cos\frac{2\pi}3=(0.5)^2\times(-0.5)=-0.125=-\frac18$ ✓；$f(\frac\pi2)=0\times(-1)=0$ ✓；$f(\frac{2\pi}3)=(0.5)^2\times\cos\frac{4\pi}3=0.25\times(-0.5)=-\frac18$ ✓。
+最大值检验：令 $u=\cos^2x\in[0,1]$，$\cos2x=2u-1$，$f=u(2u-1)=2u^2-u$，在 $u\in[0,1]$ 上最小值在 $u=\frac14$ 处 $=2\cdot\frac1{16}-\frac14=-\frac18$ ✓，最大值在 $u=1$ 处 $=1$ ✓。**与答案完全吻合**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>M-H0307</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>M-T-106(函数与导数 / 导数含参讨论 · 含三角函数型讨论  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>已知 $f(x)=\sin2x+2\cos x$，$x\in(0,\pi)$．
+（1）求 $f(x)$ 的单调区间；</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>$f(x)$ 在 $\left(0,\dfrac\pi6\right)$ 与 $\left(\dfrac{5\pi}6,\pi\right)$ 上单调递增，在 $\left(\dfrac\pi6,\dfrac{5\pi}6\right)$ 上单调递减</t>
+        </is>
+      </c>
+      <c r="P307" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=2\cos2x-2\sin x=2\left(1-2\sin^{2}x\right)-2\sin x=-4\sin^{2}x-2\sin x+2=-2\left(2\sin^{2}x+\sin x-1\right)$
+$=-2(2\sin x-1)(\sin x+1)$．
+$x\in(0,\pi)$ 时 $\sin x\in(0,1]$，故 $\sin x+1&gt;0$ 恒成立，$f'(x)$ 的符号由 $-(2\sin x-1)$ 决定：
+$f'(x)&gt;0\iff2\sin x-1&lt;0\iff\sin x&lt;\dfrac12\iff x\in\left(0,\dfrac\pi6\right)\cup\left(\dfrac{5\pi}6,\pi\right)$；
+$f'(x)&lt;0\iff\sin x&gt;\dfrac12\iff x\in\left(\dfrac\pi6,\dfrac{5\pi}6\right)$．
+故 $f$ 的增区间为 $\left(0,\dfrac\pi6\right)$ 与 $\left(\dfrac{5\pi}6,\pi\right)$，减区间为 $\left(\dfrac\pi6,\dfrac{5\pi}6\right)$．</t>
+        </is>
+      </c>
+      <c r="Q307" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S307" t="n">
+        <v>5</v>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-106-V2</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>教辅录入-第22批</t>
+        </is>
+      </c>
+      <c r="V307" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= sin2x + 2cosx,x ∈(0,π)」，$\sin2x$ 尚完整（$2$ 是系数而非上标），但需与 $\sin^2x$ 区分。由详解「$f'(x)=2\cos2x-2\sin x=2-4\sin^2x-2\sin x=-2(2\sin x-1)(\sin x+1)$」还原——**导数含 $\cos2x$，证明题干是 $\sin2x$（而非 $\sin^2x$）** ✓。
+**⚠ 因式分解的符号校验**（这里极易错）：
+$-2(2\sin x-1)(\sin x+1)=-2(2\sin^2x+2\sin x-\sin x-1)=-2(2\sin^2x+\sin x-1)=-4\sin^2x-2\sin x+2$ ✓ 与 $2-4\sin^2x-2\sin x$ 一致 ✓。
+**数值校验**：$x=\frac\pi6$：$\sin x=0.5$，$f'=0$ ✓ 驻点；$x=\frac\pi2$：$\sin x=1$，$f'=-2(2-1)(1+1)=-4&lt;0$ ✓ 递减；$x\to\pi^-$：$\sin x\to0$，$f'\to-2(0-1)(0+1)=+2&gt;0$ ✓ 递增。$f(\frac\pi6)=\sin\frac\pi3+2\cos\frac\pi6=0.866+1.732=2.598$；$f(\frac{5\pi}6)=\sin\frac{5\pi}3+2\cos\frac{5\pi}6=-0.866-1.732=-2.598$ ✓ 递减趋势对。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V307"/>
+  <dimension ref="A1:V315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -31131,6 +31131,819 @@
         </is>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>M-H0308</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>M-T-107(函数与导数 / 导数含参讨论 · 二阶求导讨论型)</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\mathrm e^{x}-ax^{2}$（$a\in\mathbb R$）．
+（1）讨论函数 $f(x)$ 的导函数 $f'(x)$ 的单调性；
+（2）设 $g(x)=\cos x+x-f(x)$，若 $x=0$ 为 $g(x)$ 的极小值点，求实数 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>（1）见解析；（2）$(1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="P308" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：$f'(x)=\mathrm e^{x}-2ax$，记 $F(x)=f'(x)$，则 $F'(x)=\mathrm e^{x}-2a$．
+① $a\leqslant0$ 时 $F'(x)=\mathrm e^{x}-2a&gt;0$ 恒成立，$f'(x)$ 在 $(-\infty,+\infty)$ 上是增函数；
+② $a&gt;0$ 时，$F'(x)&gt;0\iff x&gt;\ln(2a)$，$F'(x)&lt;0\iff x&lt;\ln(2a)$，$f'(x)$ 在 $(\ln(2a),+\infty)$ 上是增函数，在 $(-\infty,\ln(2a))$ 上是减函数．
+**（2）**：$g(x)=\cos x+x-\mathrm e^{x}+ax^{2}$，
+$g'(x)=-\sin x+1-\mathrm e^{x}+2ax$，且 $g'(0)=-0+1-1+0=0$．
+记 $G(x)=g'(x)$，则 $G'(x)=-\cos x-\mathrm e^{x}+2a$，$G'(0)=-1-1+2a=2a-2$．
+① 当 $2a-2&gt;0$ 即 $a&gt;1$ 时：由连续性，存在 $\delta&gt;0$，在 $(-\delta,\delta)$ 上 $G'(x)&gt;0$，故 $G$ 在该区间上递增；
+又 $G(0)=0$，故 $x\in(-\delta,0)$ 时 $G(x)&lt;0$、$x\in(0,\delta)$ 时 $G(x)&gt;0$，即 $g'$ 在 $x=0$ 处由负变正，**$x=0$ 是 $g$ 的极小值点** ✓．
+② 当 $2a-2&lt;0$ 即 $a&lt;1$ 时：同理在 $x=0$ 附近 $G'(x)&lt;0$，$G$ 递减，$g'$ 由正变负，$x=0$ 是**极大值**点 ✗．
+③ 当 $a=1$ 时：$G'(x)=-\cos x-\mathrm e^{x}+2$，$G''(x)=\sin x-\mathrm e^{x}$，在 $x\in(-\delta,0)$ 上…直接看 $G'(x)=2-\cos x-\mathrm e^{x}$，
+$x&gt;0$ 小时 $\mathrm e^{x}&gt;1+x$、$\cos x&lt;1$，故 $G'(x)&lt;2-1-(1+x)=-x&lt;0$；同理由 $\mathrm e^{x}&lt;\dfrac1{1-x}$、$\cos x&gt;1-\dfrac{x^{2}}2$（$x&lt;0$），得 $x&lt;0$ 时 $G'(x)&lt;0$ 亦成立，故 $G$ 在 $0$ 附近递减，$x=0$ 为极大值点 ✗．
+综上 $a\in(1,+\infty)$．</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S308" t="n">
+        <v>5</v>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-107-E1</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>教辅录入-第23批</t>
+        </is>
+      </c>
+      <c r="V308" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= ex- ax2」，$\mathrm e^x$ 与 $ax^2$ 的上标全丢。由详解「$f'(x)=\mathrm e^x-2ax$，令 $F(x)=\mathrm e^x-2ax$，则 $F'(x)=\mathrm e^x-2a$」与【分析】「求出 $g'(x)=-\sin x+1-\mathrm e^x+2ax$，令 $G(x)=-\sin x+1-\mathrm e^x+2ax$，则 $G'(x)=-\cos x-\mathrm e^x+2a$，令 $h(x)=G'(x)$，再对 $2a-2$ 分两种情况讨论」还原。
+**⚠ 第(2)问详解缺失**：原书详解只覆盖到第(1)问（提取文本中【详解】在 (1) 后就结束了），第(2)问**只有答案 $(1,+\infty)$ 与【分析】的思路提示**。上面的完整论证由我按【分析】的框架补出。核心判据：
+$g'(0)=0$ 恒成立，但 $x=0$ 要成为**极小**值点，需要 $g'$ 在 $0$ 处**由负变正**，即 $g''$ 在 $0$ 附近为正 $\iff g''(0)=2a-2&gt;0\iff a&gt;1$ ✓ 与答案吻合。
+**边界 $a=1$ 的判定**（最微妙）：此时一阶判据失效（$g''(0)=0$），需看更高阶。$g'(x)=-\sin x+1-\mathrm e^x+2x$，
+$x=0.1$：$-\sin0.1+1-\mathrm e^{0.1}+0.2=-0.0998+1-1.1052+0.2=-0.0050&lt;0$；
+$x=-0.1$：$0.0998+1-0.9048-0.2=-0.0050&lt;0$。
+两侧 $g'$ 同号（都 $&lt;0$），故 $g$ 在 $0$ 附近**单调递减**，$x=0$ 不是极值点 ✗ ✓。故 $a=1$ 应排除，答案取开区间 $(1,+\infty)$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>M-H0309</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>M-T-107(函数与导数 / 导数含参讨论 · 二阶求导讨论型)</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\ln x-\ln a$，$g(x)=a\mathrm e^{x}$，其中 $a$ 为常数．函数 $y=f(x)$ 与 $x$ 轴的交点为 $A$，函数 $y=g(x)$ 的图象与 $y$ 轴的交点为 $B$，函数 $y=f(x)$ 在 $A$ 点的切线与函数 $y=g(x)$ 在点 $B$ 处的切线互相平行．
+（1）求 $a$ 的值；
+（2）求函数 $F(x)=f(x)-g(x-1)$ 的单调区间．</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>（1）$a=1$；（2）单调递增区间为 $(0,1)$，单调递减区间为 $(1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="P309" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：$f(x)=\ln x-\ln a$ 的定义域为 $(0,+\infty)$，$f'(x)=\dfrac1x$；令 $f(x)=0$ 得 $x=a$，故 $A(a,0)$，$f$ 在 $A$ 处的切线斜率为 $f'(a)=\dfrac1a$．
+$g(x)=a\mathrm e^{x}$ 与 $y$ 轴交于 $B(0,a)$，$g'(x)=a\mathrm e^{x}$，故 $g$ 在 $B$ 处的切线斜率为 $g'(0)=a$．
+两切线平行：$\dfrac1a=a\Rightarrow a^{2}=1\Rightarrow a=\pm1$；又 $a&gt;0$（否则 $\ln a$ 无意义），故 **$a=1$**．
+**（2）**：由（1）知 $f(x)=\ln x$，$g(x)=\mathrm e^{x}$，
+$F(x)=\ln x-\mathrm e^{x-1}$，定义域 $(0,+\infty)$，
+$F'(x)=\dfrac1x-\mathrm e^{x-1}=\dfrac{1-x\mathrm e^{x-1}}{x}$．
+设 $h(x)=1-x\mathrm e^{x-1}$，则 $h'(x)=-\mathrm e^{x-1}-x\mathrm e^{x-1}=-(1+x)\mathrm e^{x-1}&lt;0$（$x&gt;0$），故 $h$ 在 $(0,+\infty)$ 上**严格递减**；又 $h(1)=1-1\cdot\mathrm e^{0}=0$，
+于是 $0&lt;x&lt;1$ 时 $h(x)&gt;0$ 即 $F'(x)&gt;0$；$x&gt;1$ 时 $h(x)&lt;0$ 即 $F'(x)&lt;0$．
+故 $F$ 的单调递增区间为 $(0,1)$，单调递减区间为 $(1,+\infty)$．</t>
+        </is>
+      </c>
+      <c r="Q309" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S309" t="n">
+        <v>5</v>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-107-V1</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>教辅录入-第23批</t>
+        </is>
+      </c>
+      <c r="V309" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= lnx - lna，g (x)= aex」与「F (x)= lnx - ex-1，x ∈(0,+∞)∴F′x= 1 - ex-1= 1 - xex-1 / ()xx」，$\mathrm e^x$、$\mathrm e^{x-1}$ 的上标全丢（写成 ex、ex-1）。由详解「$f(x)$ 与坐标轴交点为 $(a,0)$，$f'(x)=\frac1a$，$g(x)$ 与坐标轴交点为 $(0,a)$，$g'(0)=a$，∴$\frac1a=a$ 解得 $a=\pm1$，又 $a&gt;0$，故 $a=1$」与「$F(x)=\ln x-\mathrm e^{x-1}$，$x\in(0,+\infty)$；$F'(x)=\frac1x-\mathrm e^{x-1}=\frac{1-x\mathrm e^{x-1}}{x}$；令 $h(x)=1-x\mathrm e^{x-1}$，显然函数 $h(x)$ 在区间 $(0,+\infty)$ 上单调递减，且 $h(1)=0$」还原。
+**数值校验**：$h(1)=1-1\times\mathrm e^0=0$ ✓；$h(0.5)=1-0.5\times\mathrm e^{-0.5}=1-0.3033=0.6967&gt;0$ ✓；$h(2)=1-2\times\mathrm e^{1}=1-5.4366=-4.4366&lt;0$ ✓。$h'(x)=-(1+x)\mathrm e^{x-1}&lt;0$ 对 $x&gt;0$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>M-H0310</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>M-T-107(函数与导数 / 导数含参讨论 · 二阶求导讨论型)</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=(x+2)\ln x-2x$．
+（1）判断 $f(x)$ 在 $(2,+\infty)$ 上的单调性；</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>在 $(2,+\infty)$ 上为单调增函数</t>
+        </is>
+      </c>
+      <c r="P310" s="2" t="inlineStr">
+        <is>
+          <t>定义域 $(0,+\infty)$．
+$f'(x)=\ln x+(x+2)\cdot\dfrac1x-2=\ln x+1+\dfrac2x-2=\ln x+\dfrac2x-1$．
+再求导：$f''(x)=\dfrac1x-\dfrac2{x^{2}}=\dfrac{x-2}{x^{2}}$．
+当 $x&gt;2$ 时 $f''(x)&gt;0$，故 $f'(x)$ 在 $(2,+\infty)$ 上为**增函数**；
+于是 $x&gt;2$ 时 $f'(x)&gt;f'(2)=\ln2+\dfrac22-1=\ln2&gt;0$．
+故 $f(x)$ 在 $(2,+\infty)$ 上为单调增函数．</t>
+        </is>
+      </c>
+      <c r="Q310" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S310" t="n">
+        <v>5</v>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-107-V2</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>教辅录入-第23批</t>
+        </is>
+      </c>
+      <c r="V310" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= (x + 2)lnx - 2x」与「f′x= lnx + 2 - 1 … fx= x - 2 / x2」，$f'(x)=\ln x+\frac2x-1$ 的分数线丢失（「2」与「x」分离），$f''(x)=\frac{x-2}{x^2}$ 被拆成两行。由详解「$f'(x)=\ln x+\frac2x-1$，$f''(x)=\frac{x-2}{x^2}$，∴当 $x&gt;2$ 时，$f''(x)&gt;0$，∴$f'(x)$ 在 $(2,+\infty)$ 上为增函数，∴$x&gt;2$ 时，$f'(x)&gt;f'(2)=\ln2&gt;0$，∴$f(x)$ 在 $(2,+\infty)$ 上为单调增函数」还原。
+**导数独立验证**：$f(x)=(x+2)\ln x-2x$ ⇒ $f'=\ln x+(x+2)/x-2=\ln x+1+2/x-2=\ln x+2/x-1$ ✓；$f''=1/x-2/x^2=(x-2)/x^2$ ✓ 与详解一致。
+$f'(2)=\ln2+1-1=\ln2\approx0.693&gt;0$ ✓。
+**⚠ 只录第（1）问**：原书第（2）问为「$x&gt;\mathrm e^{2}$ 时，求证 $f(x)&gt;\cdots$」，待证不等式在提取文本中破碎（只见「-2x 1 -」与「ex」两段残片，无法判断是 $-2x(1-\frac{\mathrm e^{x}}x)$ 还是别的形式），故不录，如实标注。</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>M-H0311</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>M-T-107(函数与导数 / 导数含参讨论 · 二阶求导讨论型)</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=(x+a)\ln(x+1)-ax$．
+（1）若 $a=2$，求 $f(x)$ 的单调区间；
+（2）若 $a\leqslant-2$，$-1&lt;x&lt;0$，求证：$f(x)&gt;2x(1-\mathrm e^{-x})$．</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>（1）单调递增区间为 $(-1,+\infty)$，不存在递减区间；（2）证明见解析</t>
+        </is>
+      </c>
+      <c r="P311" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：定义域 $(-1,+\infty)$．$a=2$ 时 $f(x)=(x+2)\ln(x+1)-2x$，
+$f'(x)=\ln(x+1)+\dfrac{x+2}{x+1}-2=\ln(x+1)+1+\dfrac1{x+1}-2=\ln(x+1)-\dfrac{x}{x+1}$，
+$f''(x)=\dfrac1{x+1}-\dfrac{(x+1)-x}{(x+1)^{2}}=\dfrac1{x+1}-\dfrac1{(x+1)^{2}}=\dfrac{x}{(x+1)^{2}}$．
+$x\in(-1,0)$ 时 $f''(x)&lt;0$，$f'$ 递减；$x\in(0,+\infty)$ 时 $f''(x)&gt;0$，$f'$ 递增．
+故 $f'(x)\geqslant f'(0)=\ln1-0=0$，即 $f'(x)\geqslant0$ 恒成立，
+$f$ 的单调递增区间为 $(-1,+\infty)$，不存在递减区间．
+**（2）**：设 $\varphi(a)=f(x)$（把 $x$ 固定），则 $\dfrac{\partial f}{\partial a}=\ln(x+1)-x$．
+由 $\ln(1+t)\leqslant t$（$t&gt;-1$），取 $t=x$ 得 $\ln(x+1)-x\leqslant0$，故 $f$ 关于 $a$ **递减**；$a\leqslant-2$ 时 $f(x)\geqslant f(x)\big|_{a=-2}$．
+于是只需证 $a=-2$ 的情形：
+$(x-2)\ln(x+1)+2x&gt;2x(1-\mathrm e^{-x})\iff (x-2)\ln(x+1)&gt;-2x\mathrm e^{-x}$．
+令 $t=-x\in(0,1)$，上式化为 $(t+2)\ln\dfrac1{1-t}&gt;2t\mathrm e^{t}$，即 
+$(t+2)\sum_{n\geqslant1}\dfrac{t^{n}}{n}&gt;2t\sum_{n\geqslant0}\dfrac{t^{n}}{n!}$．
+左端 $t^{n}$（$n\geqslant2$）的系数为 $\dfrac2n+\dfrac1{n-1}$，右端为 $\dfrac2{(n-1)!}$；
+$n=1$：左 $2$，右 $2$，相等；$n=2$：左 $1+1=2$，右 $2$，相等；
+$n\geqslant3$：左 $\geqslant\dfrac1{n-1}&gt;\dfrac2{(n-1)!}=$ 右（因 $(n-1)!&gt;2(n-1)$）．
+故左端 $-$ 右端 $=\sum_{n\geqslant3}\bigl[\cdots\bigr]t^{n}&gt;0$（$t&gt;0$），不等式成立，证毕．</t>
+        </is>
+      </c>
+      <c r="Q311" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S311" t="n">
+        <v>5</v>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-107-V3</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>教辅录入-第23批</t>
+        </is>
+      </c>
+      <c r="V311" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = (x + a)ln(x + 1) - ax」与「f'(x) = ln(1 + x) -x / x + 1，f''(x) =1 -1 = / x + 1 / (x + 1)2 / x」，$\frac{x}{x+1}$ 与 $\frac{x}{(x+1)^2}$ 的分数线丢失。由详解「$f'(x)=\ln(1+x)+\frac{x+2}{x+1}-2=\ln(1+x)-\frac{x}{x+1}$，$f''(x)=\frac1{x+1}-\frac1{(x+1)^2}=\frac{x}{(x+1)^2}$」还原。
+**导数独立验证**：$f=(x+2)\ln(x+1)-2x$ ⇒ $f'=\ln(x+1)+\frac{x+2}{x+1}-2$ ✓；$\frac{x+2}{x+1}-2=\frac{x+2-2x-2}{x+1}=\frac{-x}{x+1}$ ✓ 故 $f'=\ln(1+x)-\frac{x}{x+1}$ ✓。$f''=\frac1{x+1}-\frac{(x+1)-x}{(x+1)^2}=\frac1{x+1}-\frac1{(x+1)^2}=\frac{x}{(x+1)^2}$ ✓。
+**⚠ 第（2）问详解不完整**：原书【详解】只给了第（1）问，【分析】只给了「设 $g(x)=\ln(1+x)-x$，证明 $g(x)\leqslant0$，要证明 $f(x)&gt;2x(1-\mathrm e^{-x})$ 只需证明 $(x-2)\ln(1+x)&gt;-2x\mathrm e^{-x}$」。
+**上面的完整证明由我按该思路补出**（$a$ 的单调性归约 + 幂级数比较）。
+**数值校验**（关键不等式 $(x-2)\ln(1+x)&gt;-2x\mathrm e^{-x}$，$-1&lt;x&lt;0$）：
+$x=-0.5$：左 $=(-2.5)\ln0.5=1.7329$，右 $=-2(-0.5)\mathrm e^{0.5}=1.6487$ ✓；
+$x=-0.1$：左 $=(-2.1)\ln0.9=0.22126$，右 $=0.2\mathrm e^{0.1}=0.22103$ ✓（**很接近**，正因 $n=1,2$ 项系数相等，差从 $t^3$ 项才开始）；
+$x=-0.9$：左 $=(-2.9)\ln0.1=6.6776$，右 $=1.8\mathrm e^{0.9}=4.4273$ ✓。
+$x\to0^{-}$ 时差 $\sim\frac{t^{3}}6&gt;0$ ✓ 与级数首项 $\frac16t^3$ 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>M-H0312</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>M-T-108(函数与导数 / 导数含参讨论 · 已知单调性求参)</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac a3x^{3}-ax^{2}+x+1$．
+（1）若 $f(x)$ 在 $(-\infty,+\infty)$ 上是增函数，求 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>$0&lt;a\leqslant1$（原书答案；严格应为 $0\leqslanta\leqslant1$，见 review）</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=ax^{2}-2ax+1$．要求 $f'(x)\geqslant0$ 对一切 $x\in\mathbb R$ 成立．
+① $a=0$：$f'(x)=1&gt;0$，成立；
+② $a&gt;0$：$f'$ 是开口向上的二次函数，最小值在 $x=\dfrac{2a}{2a}=1$ 处，
+$f'(x)_{\min}=f'(1)=a-2a+1=1-a\geqslant0\Rightarrow a\leqslant1$，故 $0&lt;a\leqslant1$；
+③ $a&lt;0$：$f'$ 开口向下，$x\to+\infty$ 时 $f'(x)\to-\infty$，不可能恒 $\geqslant0$，舍去．
+综上（含 $a=0$ 的情形）$0\leqslanta\leqslant1$；原书答案写作 $0&lt;a\leqslant1$．</t>
+        </is>
+      </c>
+      <c r="Q312" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S312" t="n">
+        <v>5</v>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-108-E1</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>教辅录入-第23批</t>
+        </is>
+      </c>
+      <c r="V312" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= x 3- ax 2+ x + 1」，$\frac a3x^3$ 的分数线、$x^3$ 与 $ax^2$ 的上标全丢，「a」与「3」被拆到相邻行。由详解「$f'(x)=ax^2-2ax+1$」反推：$\frac{\mathrm d}{\mathrm dx}\left(\frac a3x^3\right)=ax^2$ ✓、$\frac{\mathrm d}{\mathrm dx}(-ax^2)=-2ax$ ✓、$\frac{\mathrm d}{\mathrm dx}(x+1)=1$ ✓，故题干确为 $f(x)=\frac a3x^3-ax^2+x+1$ ✓。
+**⚠ 原书自相矛盾（已标记，供复核）**：
+详解写「当 $a=0$ 时，$f'(x)=1&gt;0$，故结论成立」，但末尾「综上得 $a$ 的取值范围是 $0&lt;a\leqslant1$」把 $a=0$ 排除了。
+$a=0$ 时 $f(x)=x+1$ 确实是 $\mathbb R$ 上的增函数，**结论成立是事实**，故严格答案应为 $0\leqslanta\leqslant1$。
+按项目约定**答案照原书录入**（$0&lt;a\leqslant1$），此处如实标注矛盾，供日后与原书核对。**建议列入 D 类存疑。**</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>M-H0313</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>M-T-108(函数与导数 / 导数含参讨论 · 已知单调性求参)</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\ln(ax+1)+\dfrac{x^{3}}3-x^{2}-ax$（$a\in\mathbb R$）．
+（1）若 $y=f(x)$ 在 $[4,+\infty)$ 上为增函数，求实数 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>$0&lt;a\leqslant4+3\sqrt2$</t>
+        </is>
+      </c>
+      <c r="P313" s="2" t="inlineStr">
+        <is>
+          <t>$f'(x)=\dfrac a{ax+1}+x^{2}-2x-a$．要求在 $[4,+\infty)$ 上 $f'(x)\geqslant0$．
+需 $ax+1&gt;0$（对数定义域），以下解得 $a&gt;0$，该条件自动满足．
+$f'(x)\geqslant0\iff\dfrac a{ax+1}+x^{2}-2x-a\geqslant0$，两边乘 $ax+1&gt;0$：
+$a+(x^{2}-2x-a)(ax+1)\geqslant0$
+$\Rightarrow a+ax^{3}-2ax^{2}-a^{2}x+x^{2}-2x-a\geqslant0$
+$\Rightarrow ax^{3}-2ax^{2}+x^{2}-a^{2}x-2x\geqslant0$
+$\Rightarrow x\bigl[ax^{2}+(1-2a)x-a^{2}-2\bigr]\geqslant0$．
+因 $x\geqslant4&gt;0$，等价于 $h(x)=ax^{2}+(1-2a)x-a^{2}-2\geqslant0$ 在 $[4,+\infty)$ 恒成立．
+由答案 $a&gt;0$，此时 $h$ 是开口向上的二次函数，对称轴 $x=\dfrac{2a-1}{2a}=1-\dfrac1{2a}&lt;1&lt;4$，故 $h$ 在 $[4,+\infty)$ 上**单调递增**，只需 $h(4)\geqslant0$：
+$h(4)=16a+4(1-2a)-a^{2}-2=-a^{2}+8a+2\geqslant0$
+$\Rightarrow a^{2}-8a-2\leqslant0\Rightarrow 4-3\sqrt2\leqslant a\leqslant4+3\sqrt2$．
+结合 $a&gt;0$，得 $0&lt;a\leqslant4+3\sqrt2$．</t>
+        </is>
+      </c>
+      <c r="Q313" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S313" t="n">
+        <v>5</v>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-108-V1</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>教辅录入-第23批</t>
+        </is>
+      </c>
+      <c r="V313" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = ln(ax + 1) + / x3 / - x2- ax(a ∈R)．3」，$\frac{x^3}{3}$ 的分数线与上标全丢，分子「x3」与分母「3」分离。由详解「$f'(x)=\frac{a}{ax+1}+x^2-2x-a$」反推：$x^2$ 项来自 $\frac{x^3}{3}$ ✓、$-2x$ 来自 $-x^2$ ✓、$-a$ 来自 $-ax$ ✓，故题干还原无误。
+**⚠ 详解的常数项笔误**：详解写「$h(x)=ax^2+(1-2a)x-a^2-2a&gt;0$」，末尾多了一个 $a$。按 $-a^2-2a$ 算：$h(4)=16a+4-8a-a^2-2a=-a^2+6a+4$，得 $0&lt;a\leqslant3+\sqrt{13}\approx6.606$，**与答案 $4+3\sqrt2\approx8.243$ 不符** ✗；
+按 $-a^2-2$ 算：$h(4)=-a^2+8a+2$，得 $a\leqslant4+3\sqrt2$ ✓ **与答案吻合**。
+故取 $-a^2-2$，并在此如实标注原书笔误。
+**数值校验**：$a=8$（$&lt;8.243$）：$h(4)=-64+64+2=2&gt;0$ ✓；$a=9$（超出）：$h(4)=-81+72+2=-7&lt;0$ ✗ ✓。另验 $f'(4)$（$a=8$）：$\frac{8}{33}+16-8-8=0.242&gt;0$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>M-H0314</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>M-T-108(函数与导数 / 导数含参讨论 · 已知单调性求参)</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\ln(x-1)+\dfrac a{x+2}$（$a\in\mathbb R$）．
+（1）若函数 $f(x)$ 在定义域上是单调递增函数，求实数 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>$a\leqslant12$</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="inlineStr">
+        <is>
+          <t>定义域为 $(1,+\infty)$．$f'(x)=\dfrac1{x-1}-\dfrac a{(x+2)^{2}}$．
+要在 $(1,+\infty)$ 上恒有 $f'(x)\geqslant0$，即
+$a\leqslant\dfrac{(x+2)^{2}}{x-1}$ 对一切 $x&gt;1$ 成立．
+设 $g(x)=\dfrac{(x+2)^{2}}{x-1}$（$x&gt;1$），求其最小值．
+**方法1（基本不等式）**：令 $u=x-1&gt;0$，则 $x+2=u+3$，
+$g(x)=\dfrac{(u+3)^{2}}u=\dfrac{u^{2}+6u+9}u=u+6+\dfrac9u\geqslant2\sqrt{u\cdot\dfrac9u}+6=6+6=12$，
+当且仅当 $u=\dfrac9u$ 即 $u=3$、$x=4$ 时取等号，故 $g_{\min}=12$．
+**方法2（导数）**：$g'(x)=\dfrac{2(x+2)(x-1)-(x+2)^{2}}{(x-1)^{2}}=\dfrac{(x+2)(x-4)}{(x-1)^{2}}$，
+$1&lt;x&lt;4$ 时 $g'&lt;0$，$x&gt;4$ 时 $g'&gt;0$，故 $g$ 在 $x=4$ 处取最小值 $g(4)=\dfrac{36}{3}=12$．
+综上 $a\leqslant12$．</t>
+        </is>
+      </c>
+      <c r="Q314" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S314" t="n">
+        <v>5</v>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-108-V2</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>教辅录入-第23批</t>
+        </is>
+      </c>
+      <c r="V314" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = ln()+ / 3x + 2 / (a ∈R)．」，$\ln$ 的参数与分式被拆散，**多出一个「3」**（疑为相邻行的排版残片）。由详解「函数定义域为 $(1,+\infty)$，$f'(x)=\frac1{x-1}-\frac a{(x+2)^2}$」**反推锁定题干**：
+$\frac1{x-1}$ 只能来自 $\ln(x-1)$ ✓；$-\frac a{(x+2)^2}$ 只能来自 $+\frac a{x+2}$ ✓；定义域 $(1,+\infty)$ 与 $\ln(x-1)$ 一致 ✓。
+若按「$3x+2$」理解则为 $\frac a{3x+2}$，导数是 $-\frac{3a}{(3x+2)^2}$，与详解不符 ✗。
+**数值校验**：$g(4)=\frac{(4+2)^2}{4-1}=\frac{36}{3}=12$ ✓；$g(2)=\frac{16}{1}=16&gt;12$ ✓；$g(7)=\frac{81}{6}=13.5&gt;12$ ✓。$a=12$ 时：$f'(x)=\frac1{x-1}-\frac{12}{(x+2)^2}$，$x=4$ 处 $=\frac13-\frac{12}{36}=0$ ✓ 恰取等；$x=2$ 处 $=1-\frac{12}{16}=0.25&gt;0$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>M-H0315</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>M-T-108(函数与导数 / 导数含参讨论 · 已知单调性求参)</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x^{2}+ax-\ln x$（$a\in\mathbb R$）．
+（1）若函数 $f(x)$ 在 $[1,2]$ 上是减函数，求实数 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>$a\leqslant-\dfrac72$</t>
+        </is>
+      </c>
+      <c r="P315" s="2" t="inlineStr">
+        <is>
+          <t>定义域 $(0,+\infty)$．$f'(x)=2x+a-\dfrac1x=\dfrac{2x^{2}+ax-1}{x}$．
+在 $[1,2]$ 上 $x&gt;0$，故 $f'(x)\leqslant0\iff h(x)=2x^{2}+ax-1\leqslant0$．
+$h$ 是开口向上的二次函数，在区间 $[1,2]$ 上的最大值必在端点取得，故只需：
+$\begin{cases}h(1)=2+a-1=a+1\leqslant0\\ h(2)=8+2a-1=2a+7\leqslant0\end{cases}$$\Rightarrow\begin{cases}a\leqslant-1\\ a\leqslant-\dfrac72\end{cases}$
+取交集得 $a\leqslant-\dfrac72$．</t>
+        </is>
+      </c>
+      <c r="Q315" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S315" t="n">
+        <v>5</v>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-108-V3</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>教辅录入-第23批</t>
+        </is>
+      </c>
+      <c r="V315" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= x2+ ax - lnx,a ∈R」，$x^2$ 的上标丢失。由详解「$f'(x)=2x+a-\frac1x=\frac{2x^2+ax-1}{x}\leqslant0$ 在 $[1,2]$ 上恒成立，令 $h(x)=2x^2+ax-1$，有 $h(1)\leqslant0$、$h(2)\leqslant0$，得 $a\leqslant-1$、$a\leqslant-\frac72$，得 $a\leqslant-\frac72$」还原——导数里的 $2x^2$ 反证题干是 $x^2$ 而非 $2x$ ✓。
+**数值校验**：$a=-\frac72=-3.5$：$h(1)=2-3.5-1=-2.5\leqslant0$ ✓；$h(2)=8-7-1=0$ ✓ 恰取等；$h(1.5)=4.5-5.25-1=-1.75&lt;0$ ✓。$a=-3$（$&gt;-\frac72$）：$h(2)=8-6-1=1&gt;0$ ✗ 故不满足 ✓。$f'(2)=\frac{8-7-1}{2}=0$ ✓。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V315"/>
+  <dimension ref="A1:V322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -31944,6 +31944,717 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>M-H0316</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>M-T-109(函数与导数 / 导数含参讨论 · 不确定单调增或减求参)</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x^{2}+a\ln x$．设 $g(x)=f(x)+\dfrac2x$，若 $g(x)$ 在 $[1,+\infty)$ 上是单调函数，求实数 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>$[0,+\infty)$</t>
+        </is>
+      </c>
+      <c r="P316" s="2" t="inlineStr">
+        <is>
+          <t>$g(x)=x^{2}+a\ln x+\dfrac2x$，定义域 $(0,+\infty)$，
+$g'(x)=2x+\dfrac ax-\dfrac2{x^{2}}$．
+**（ⅰ）若为单调增函数**：$g'(x)\geqslant0$ 在 $[1,+\infty)$ 上恒成立，
+$\dfrac ax\geqslant\dfrac2{x^{2}}-2x\Rightarrow a\geqslant\dfrac2x-2x^{2}$．
+设 $\varphi(x)=\dfrac2x-2x^{2}$，$\varphi'(x)=-\dfrac2{x^{2}}-4x&lt;0$（$x\geqslant1$），故 $\varphi$ 递减，
+$\varphi_{\max}=\varphi(1)=2-2=0$，于是 $a\geqslant0$．
+**（ⅱ）若为单调减函数**：$g'(x)\leqslant0$ 恒成立，即 $a\leqslant\dfrac2x-2x^{2}$ 对所有 $x\geqslant1$ 成立．
+但 $x\to+\infty$ 时 $\dfrac2x-2x^{2}\to-\infty$，无解，**不可能**．
+综上 $a\in[0,+\infty)$．</t>
+        </is>
+      </c>
+      <c r="Q316" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S316" t="n">
+        <v>5</v>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-109-E1</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>教辅录入-第24批</t>
+        </is>
+      </c>
+      <c r="V316" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = x2+ alnx.(2) 若g(x) = f(x) + 在[1，+∞) 上是单调函数」，$x^2$ 上标丢失、$\frac2x$ 的分数线被拆成「2」与「x」两行。由详解「$g'(x)=2x+\frac ax-\frac2{x^2}$，若 $g(x)$ 为 $[1,+\infty)$ 上的单调增函数，则 $g'(x)\geqslant0$ 恒成立，即 $a\geqslant\frac2x-2x^2$ 恒成立，设 $\varphi(x)=\frac2x-2x^2$，因为 $\varphi(x)$ 在 $[1,+\infty)$ 上单调递减，所以 $\varphi(x)_{\max}=\varphi(1)=0$，所以 $a\geqslant0$；若 $g(x)$ 为单调减函数，则 $g'(x)\leqslant0$ 在 $[1,+\infty)$ 上恒成立，不可能」还原。
+**导数校验**：$\frac{\mathrm d}{\mathrm dx}\left(\frac2x\right)=-\frac2{x^2}$，$\frac{\mathrm d}{\mathrm dx}(a\ln x)=\frac ax$ ✓ 与详解一致，
+这也反证 $g$ 中加的是 $+\frac2x$（若是 $+2x$ 则导数里不会有 $-\frac2{x^2}$）✓。
+**数值校验**：$a=0$：$g'(x)=2x-\frac2{x^2}$，$x=1$ 处 $=0$ ✓ 恰取等；$x=2$ 处 $=4-0.5=3.5&gt;0$ ✓。$a=-0.1$（超出）：$g'(1)=2-0.1-2=-0.1&lt;0$ ✗ 非增 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>M-H0317</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>M-T-109(函数与导数 / 导数含参讨论 · 不确定单调增或减求参)</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x(x+a)-\ln x$，其中 $a$ 为常数．若 $f(x)$ 在区间 $\left(\dfrac12,1\right)$ 上是单调函数，求实数 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>$(-\infty,-1]\cup[1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="P317" s="2" t="inlineStr">
+        <is>
+          <t>$f(x)=x^{2}+ax-\ln x$，定义域 $(0,+\infty)$，
+$f'(x)=2x+a-\dfrac1x=\dfrac{2x^{2}+ax-1}{x}$．
+在区间 $\left(\dfrac12,1\right)$ 上 $x&gt;0$，故 $f'$ 的符号由 $h(x)=2x^{2}+ax-1$ 决定．
+**① 若为增函数**：需 $h(x)\geqslant0$，即 $a\geqslant\dfrac1x-2x$ 在 $\left(\dfrac12,1\right)$ 上恒成立．
+设 $y=\dfrac1x-2x$，其导数 $y'=-\dfrac1{x^{2}}-2&lt;0$，故 $y$ 递减，在 $\left(\dfrac12,1\right)$ 上 $y&lt;y\!\left(\dfrac12\right)=2-1=1$，
+于是只需 $a\geqslant1$．
+**② 若为减函数**：需 $h(x)\leqslant0$ 恒成立．$h$ 开口向上，在区间上的最大值在端点取得：
+$\begin{cases}h\!\left(\dfrac12\right)=\dfrac12+\dfrac a2-1\leqslant0\Rightarrow a\leqslant1\\[4pt] h(1)=2+a-1\leqslant0\Rightarrow a\leqslant-1\end{cases}$$\Rightarrow a\leqslant-1$．
+综上 $a\in(-\infty,-1]\cup[1,+\infty)$．</t>
+        </is>
+      </c>
+      <c r="Q317" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S317" t="n">
+        <v>5</v>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-109-V1</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>教辅录入-第24批</t>
+        </is>
+      </c>
+      <c r="V317" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = x(x + a) −lnx」，尚可辨认；但详解里区间写成「$(\frac12,1)$」而题干一度被识别为「$(\frac12,1)$」✓。由详解「①当 $f(x)$ 是增函数时，$f'(x)=2x+a-\frac1x=\frac{2x^2+ax-1}{x}\geqslant0$ 在 $(\frac12,1)$ 上恒成立，即 $a\geqslant\frac1x-2x$ 在 $(\frac12,1)$ 上恒成立，∵$y=\frac1x-2x$ 在 $(\frac12,1)$ 上是减函数，∴$y&lt;1$，∴$a\geqslant1$；②当 $f(x)$ 是减函数时，$2x^2+ax-1\leqslant0$ 在 $(\frac12,1)$ 上恒成立，设 $g(x)=2x^2+ax-1$，则 $g(\frac12)\leqslant0$、$g(1)\leqslant0$，解得 $a\leqslant-1$」还原。
+**数值校验**：$a=1$：$h(\frac12)=0.5+0.5-1=0$ ✓ 恰取等，$f$ 为增 ✓；$h(0.75)=2(0.5625)+0.75-1=0.875&gt;0$ ✓。$a=-1$：$h(1)=2-1-1=0$ ✓，$h(\frac12)=0.5-0.5-1=-1&lt;0$ ✓，$f$ 为减 ✓。$a=0$（在 $(-1,1)$ 内）：$h(\frac12)=-0.5&lt;0$ 但 $h(1)=1&gt;0$ ⇒ 先减后增，非单调 ✗ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>M-H0318</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>M-T-109(函数与导数 / 导数含参讨论 · 不确定单调增或减求参)</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=-\ln x-ax^{2}+4x$（$a&gt;0$）．
+（1）若 $f(x)$ 是定义域上的单调函数，求 $a$ 的取值范围；
+（2）若 $f(x)$ 在定义域上有两个极值点 $x_{1},x_{2}$，证明：$f(x_{1})+f(x_{2})&gt;3+2\ln2$．</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>（1）$[2,+\infty)$；（2）证明见解析</t>
+        </is>
+      </c>
+      <c r="P318" s="2" t="inlineStr">
+        <is>
+          <t>定义域 $(0,+\infty)$．$f'(x)=-\dfrac1x-2ax+4=\dfrac{-2ax^{2}+4x-1}{x}$．
+**（1）**：$x&gt;0$，故符号由 $-2ax^{2}+4x-1$ 决定．
+**递减**：$f'(x)\leqslant0$ 恒成立 $\iff 2a\geqslant\dfrac{4x-1}{x^{2}}=-\dfrac1{x^{2}}+\dfrac4x$．
+令 $t=\dfrac1x&gt;0$，右端 $=-t^{2}+4t=-(t-2)^{2}+4\leqslant4$，故 $2a\geqslant4$，即 $a\geqslant2$．
+**递增**：$f'(x)\geqslant0$ 恒成立 $\iff 2a\leqslant-t^{2}+4t$ 恒成立．但 $-t^{2}+4t$ 在 $t\to+\infty$ 时 $\to-\infty$，**无最小值**，故无解．
+综上 $a\in[2,+\infty)$．
+**（2）**：两个极值点即 $-2ax^{2}+4x-1=0$ 有两个正根，
+$\Delta=16-8a&gt;0\Rightarrow a&lt;2$；又 $a&gt;0$，故 $0&lt;a&lt;2$．
+由韦达定理：$x_{1}+x_{2}=\dfrac4{2a}=\dfrac2a$，$x_{1}x_{2}=\dfrac{-1}{-2a}=\dfrac1{2a}$，
+$x_{1}^{2}+x_{2}^{2}=(x_{1}+x_{2})^{2}-2x_{1}x_{2}=\dfrac4{a^{2}}-\dfrac1a$．
+于是
+$f(x_{1})+f(x_{2})=-\ln(x_{1}x_{2})-a\left(x_{1}^{2}+x_{2}^{2}\right)+4(x_{1}+x_{2})$
+$=-\ln\dfrac1{2a}-a\left(\dfrac4{a^{2}}-\dfrac1a\right)+\dfrac8a=\ln(2a)-\dfrac4a+1+\dfrac8a=\ln(2a)+\dfrac4a+1$．
+设 $H(a)=\ln(2a)+\dfrac4a+1$（$0&lt;a&lt;2$），$H'(a)=\dfrac1a-\dfrac4{a^{2}}=\dfrac{a-4}{a^{2}}&lt;0$（因 $a&lt;2&lt;4$），
+故 $H$ 在 $(0,2)$ 上递减，$H(a)&gt;H(2)=\ln4+2+1=3+2\ln2$．
+即 $f(x_{1})+f(x_{2})&gt;3+2\ln2$，证毕．</t>
+        </is>
+      </c>
+      <c r="Q318" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S318" t="n">
+        <v>5</v>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-109-V2</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>教辅录入-第24批</t>
+        </is>
+      </c>
+      <c r="V318" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) =-lnx - ax2+ 4x(a &gt; 0)」，$ax^2$ 上标丢失。由详解「$f'(x)=-\frac1x-2ax+4=\frac{-2ax^2+4x-1}{x}$」与【分析】「利用韦达定理求出 $x_1+x_2=\frac2a$，$x_1x_2=\frac1{2a}$，再求出 $f(x_1)+f(x_2)=\ln(2a)+\frac4a+1$，求出函数的最小值即得证」还原。
+**推导自检**：$x_1^2+x_2^2=\frac4{a^2}-\frac1a$ ✓ → $-a(\cdot)=-\frac4a+1$ ✓ → 加上 $\frac8a$ 得 $\frac4a+1$ ✓ **与详解的 $\frac4a+1$ 完全吻合**。
+**数值校验**：$a=1$：$-2x^2+4x-1=0$ → $x=\frac{4\pm\sqrt{16-8}}{4}=1\pm\frac{\sqrt2}2$，$x_1=0.2929$、$x_2=1.7071$ ✓ 两根都正 ✓。$H(1)=\ln2+4+1=5.693$；$3+2\ln2=4.386$ ✓ 大于。$a=1.9$：$H=\ln3.8+\frac4{1.9}+1=1.335+2.105+1=4.440&gt;4.386$ ✓（接近边界 2）。$a\to2^-$：$H\to\ln4+3=4.386$ ✓ 恰为下确界。</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>M-H0319</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>M-T-109(函数与导数 / 导数含参讨论 · 不确定单调增或减求参)</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\mathrm e^{x}-ax^{2}-bx-1$（$a,b\in\mathbb R$）．
+（1）设 $g(x)=f'(x)$，若 $g(x)$ 是 $(0,2)$ 上的单调函数，求 $a$ 的取值范围；
+（2）若 $f(2)=0$，函数 $f(x)$ 在 $(0,2)$ 上有零点，求 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>（1）$a\leqslant\dfrac12$ 或 $a\geqslant\dfrac{\mathrm e^{2}}2$；（2）$\dfrac{\mathrm e^{2}-3}4&lt;a&lt;\dfrac{\mathrm e^{2}+1}4$</t>
+        </is>
+      </c>
+      <c r="P319" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：$g(x)=f'(x)=\mathrm e^{x}-2ax-b$，$g'(x)=\mathrm e^{x}-2a$．
+$g$ 在 $(0,2)$ 上单调 $\iff g'\geqslant0$ 恒成立或 $g'\leqslant0$ 恒成立：
+$g'\geqslant0$：$2a\leqslant\mathrm e^{x}$ 对 $x\in(0,2)$ 恒成立 $\Rightarrow 2a\leqslant1$，即 $a\leqslant\dfrac12$；
+$g'\leqslant0$：$2a\geqslant\mathrm e^{x}$ 恒成立 $\Rightarrow 2a\geqslant\mathrm e^{2}$，即 $a\geqslant\dfrac{\mathrm e^{2}}2$．
+故 $a\leqslant\dfrac12$ 或 $a\geqslant\dfrac{\mathrm e^{2}}2$．
+**（2）**：$f(0)=\mathrm e^{0}-0-0-1=0$；由 $f(2)=0$ 得
+$\mathrm e^{2}-4a-2b-1=0\Rightarrow b=\dfrac{\mathrm e^{2}-4a-1}2$．
+已有零点 $x=0$ 与 $x=2$，要在 $(0,2)$ 内还有零点，$f$ 在 $(0,2)$ 上**不单调**，故 $g=f'$ 在 $(0,2)$ 内至少有两个零点．
+由（1）的补集，需 $\dfrac12&lt;a&lt;\dfrac{\mathrm e^{2}}2$；此时 $g'$ 的零点为 $x=\ln(2a)\in(0,2)$，
+$g$ 先减后减…实际 $g'(x)=\mathrm e^{x}-2a$ 递增，故 $g$ 在 $(0,\ln2a)$ 上递减、在 $(\ln2a,2)$ 上递增，
+要 $g$ 在 $(0,2)$ 内有两个零点，需
+$\begin{cases}g(0)&gt;0\\ g(\ln2a)&lt;0\\ g(2)&gt;0\end{cases}$．
+$g(0)=1-b=1-\dfrac{\mathrm e^{2}-4a-1}2=\dfrac{3+4a-\mathrm e^{2}}2&gt;0\Rightarrow a&gt;\dfrac{\mathrm e^{2}-3}4$；
+$g(2)=\mathrm e^{2}-4a-b=\mathrm e^{2}-4a-\dfrac{\mathrm e^{2}-4a-1}2=\dfrac{\mathrm e^{2}-4a+1}2&gt;0\Rightarrow a&lt;\dfrac{\mathrm e^{2}+1}4$；
+$g(\ln2a)=2a-2a\ln(2a)-b&lt;0$（中间条件，与上述区间相容）．
+故 $\dfrac{\mathrm e^{2}-3}4&lt;a&lt;\dfrac{\mathrm e^{2}+1}4$．</t>
+        </is>
+      </c>
+      <c r="Q319" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S319" t="n">
+        <v>5</v>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-109-V3</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>教辅录入-第24批</t>
+        </is>
+      </c>
+      <c r="V319" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = ex- ax2- bx - 1」，$\mathrm e^x$ 与 $ax^2$ 上标全丢；答案「(1)a ≤1 a ≥e2 (2) e2- 3 &lt; a &lt; e2+ 1 / 2 或2 ；44」是「(1) $a\leqslant\frac12$ 或 $a\geqslant\frac{\mathrm e^2}2$；(2) $\frac{\mathrm e^2-3}4&lt;a&lt;\frac{\mathrm e^2+1}4$」。由详解「$g(x)=f'(x)=\mathrm e^x-2ax-b$，∴$g'(x)=\mathrm e^x-2a$，∵$g(x)$ 在 $(0,2)$ 上单调，∴$g'(x)\geqslant0$ 或 $g'(x)\leqslant0$ 在 $(0,2)$ 上恒成立，即 $a\leqslant\frac{\mathrm e^x}2$ 或 $a\geqslant\frac{\mathrm e^x}2$ 在 $(0,2)$ 上恒成立，∴$a\leqslant\frac12$ 或 $a\geqslant\frac{\mathrm e^2}2$」与【分析】还原。
+**数值校验**：$\frac{\mathrm e^2-3}4=\frac{7.389-3}4=1.097$；$\frac{\mathrm e^2+1}4=\frac{8.389}4=2.097$；$\frac12=0.5$、$\frac{\mathrm e^2}2=3.694$ —— $(1.097,2.097)\subset(0.5,3.694)$ ✓ 与（1）的补集相容 ✓。
+$a=1.5$（在区间内）：$b=\frac{7.389-6-1}2=0.195$；$g(0)=1-0.195=0.805&gt;0$ ✓；$g(2)=7.389-6-0.195=1.194&gt;0$ ✓；$\ln(2a)=\ln3=1.099$，$g(1.099)=3-3(1.099)-0.195=-0.492&lt;0$ ✓ 三个条件都满足。</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>M-H0320</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>M-T-110(函数与导数 / 导数含参讨论 · 存在单调增(减)区间)</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x+a\ln x$ 在 $x=1$ 处的切线与直线 $x+2y=0$ 垂直，函数 $g(x)=f(x)+\dfrac12x^{2}-bx$．
+（1）求实数 $a$ 的值；
+（2）若函数 $g(x)$ 存在单调递减区间，求实数 $b$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>（1）$a=1$；（2）$(3,+\infty)$</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：$f'(x)=1+\dfrac ax$，在 $x=1$ 处切线斜率为 $f'(1)=1+a$．
+直线 $x+2y=0$ 即 $y=-\dfrac x2$，斜率为 $-\dfrac12$；与之垂直的直线斜率为 $2$，
+故 $1+a=2$，得 $a=1$．
+**（2）**：由（1）$f(x)=x+\ln x$，
+$g(x)=x+\ln x+\dfrac12x^{2}-bx=\ln x+\dfrac12x^{2}-(b-1)x$（$x&gt;0$），
+$g'(x)=\dfrac1x+x-(b-1)=\dfrac{x^{2}-(b-1)x+1}{x}$．
+「存在单调递减区间」$\iff$ $g'(x)&lt;0$ 在 $(0,+\infty)$ 上**有解**$\iff$ $\mu(x)=x^{2}-(b-1)x+1$ 能取负值（注意 $x&gt;0$）．
+$\mu(0)=1&gt;0$，开口向上，故需
+$\begin{cases}\Delta=(b-1)^{2}-4&gt;0\\ \text{对称轴 } \dfrac{b-1}2&gt;0\end{cases}$$\Rightarrow\begin{cases}b&gt;3\ \text{或}\ b&lt;-1\\ b&gt;1\end{cases}\Rightarrow b&gt;3$．
+故 $b\in(3,+\infty)$．</t>
+        </is>
+      </c>
+      <c r="Q320" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S320" t="n">
+        <v>5</v>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-110-E1</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>教辅录入-第24批</t>
+        </is>
+      </c>
+      <c r="V320" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= x + alnx 在x = 1 处的切线与直线x + 2y = 0 垂直，函数g (x)= f (x)+ x2- bx」，$\frac12x^2$ 的分数线与上标丢失（写成 x2），一度会误读成 $+x^2$。由详解「$g(x)=\ln x+\frac12x^2-(b-1)x$（$x&gt;0$），$g'(x)=\frac1x+x-(b-1)=\frac{x^2-(b-1)x+1}{x}$」**反推锁定为 $\frac12x^2$** ✓（若是 $+x^2$ 则导数里 $x$ 的系数是 $2$ 而非 $1$）。
+**数值校验**：$a=1$ 时 $f'(1)=1+1=2$ ✓ 与直线 $x+2y=0$ 垂直 ✓。$b=4$（$&gt;3$）：$\mu(x)=x^2-3x+1$，$\Delta=9-4=5&gt;0$，根 $x=\frac{3\pm\sqrt5}2$，两根间 $\mu&lt;0$ ✓ 存在递减区间 ✓。$b=3$：$\mu=x^2-2x+1=(x-1)^2\geqslant0$，$g'\geqslant0$ 恒成立，无递减区间 ✗ ✓（故取开区间）。$b=2$：$\mu=x^2-x+1$，$\Delta=1-4&lt;0$，恒正 ✗ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>M-H0321</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>M-T-110(函数与导数 / 导数含参讨论 · 存在单调增(减)区间)</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=ax-\dfrac{1+x}{\mathrm e^{x}}$．
+（1）若曲线 $y=f(x)$ 在点 $\bigl(0,f(0)\bigr)$ 处的切线方程为 $y=x+b$，求实数 $a,b$ 的值；
+（2）若函数 $f(x)$ 在区间 $(0,2)$ 上存在单调增区间，求实数 $a$ 的取值范围；
+（3）若 $f(x)$ 在区间 $(0,2)$ 上存在极大值，求实数 $a$ 的取值范围（直接写出结果）．</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>（1）$a=1,\ b=-1$；（2）$\left(-\dfrac1{\mathrm e},+\infty\right)$；（3）$\left(-\dfrac1{\mathrm e},\ -\dfrac2{\mathrm e^{2}}\right)$</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：$f'(x)=a-\dfrac{1\cdot\mathrm e^{x}-(1+x)\mathrm e^{x}}{\mathrm e^{2x}}=a-\dfrac{-x}{\mathrm e^{x}}=a+\dfrac x{\mathrm e^{x}}$．
+$f'(0)=a+0=a$；切线 $y=x+b$ 的斜率为 $1$，故 $a=1$．
+$f(0)=0-\dfrac{1+0}{1}=-1$，切点为 $(0,-1)$，代入切线：$-1=0+b$，故 $b=-1$．
+**（2）**：「存在单调增区间」$\iff$ $f'(x)=a+\dfrac x{\mathrm e^{x}}&gt;0$ 在 $(0,2)$ 上**有解**，
+即只需 $f'(x)$ 在 $(0,2)$ 上的**最大值** $&gt;0$．
+设 $h(x)=\dfrac x{\mathrm e^{x}}$，$h'(x)=\dfrac{1-x}{\mathrm e^{x}}$：
+$x\in(0,1)$ 时 $h'&gt;0$，$h$ 递增；$x\in(1,2)$ 时 $h'&lt;0$，$h$ 递减；
+故 $h$ 在 $x=1$ 处取最大值 $h(1)=\dfrac1{\mathrm e}$．
+于是 $f'_{\max}=a+\dfrac1{\mathrm e}&gt;0$，即 $a&gt;-\dfrac1{\mathrm e}$，
+$a\in\left(-\dfrac1{\mathrm e},+\infty\right)$．
+**（3）**：$f$ 在 $(0,2)$ 上存在极大值，需 $f'$ 在 $(0,2)$ 内由正变负．结合 $h$ 先增后减的形状，
+得 $a\in\left(-\dfrac1{\mathrm e},\ -\dfrac2{\mathrm e^{2}}\right)$（原书答案）．</t>
+        </is>
+      </c>
+      <c r="Q321" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S321" t="n">
+        <v>5</v>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-110-V2</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>教辅录入-第24批</t>
+        </is>
+      </c>
+      <c r="V321" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = ax -． / ex / 1 + x」与「f′(x) = a -= + a / ex ex / 1 - (1 + x) x」，$\frac{1+x}{\mathrm e^x}$ 的分数线丢失，分子「1 + x」与分母「ex」分列两行；导数那行更乱：实际是 $f'(x)=a-\frac{1-(1+x)}{\mathrm e^x}=a+\frac{x}{\mathrm e^x}$，中间的「1 - (1 + x)」就是分子化简过程。由详解「$f'(x)=a-\frac{1-(1+x)}{\mathrm e^x}=\frac{x}{\mathrm e^x}+a$，所以 $f'(0)=a$；切线斜率为 1，即 $a=1$，$f(0)=-1=b$」还原。
+**导数独立验证**：$\frac{\mathrm d}{\mathrm dx}\frac{1+x}{\mathrm e^x}=\frac{\mathrm e^x-(1+x)\mathrm e^x}{\mathrm e^{2x}}=\frac{-x}{\mathrm e^x}$ ✓，故 $f'=a-\frac{-x}{\mathrm e^x}=a+\frac{x}{\mathrm e^x}$ ✓。
+**数值校验**：$h(1)=\frac1{\mathrm e}=0.3679$ ✓；$h(2)=\frac2{\mathrm e^2}=0.2707$ ✓；$h(0.5)=\frac{0.5}{\mathrm e^{0.5}}=0.3033$ ✓ 均小于 $h(1)$。（3）的下界 $-\frac2{\mathrm e^2}=-0.2707$ 正是 $-h(2)$——即要求 $f'(2)=a+h(2)&lt;0$（右端为负才能出现极大值）✓ 与（2）的上界 $a&gt;-\frac1{\mathrm e}$ 组合自洽 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>M-H0322</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>M-T-110(函数与导数 / 导数含参讨论 · 存在单调增(减)区间)</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x\ln x-ax^{2}$，$a\in\mathbb R$．
+（1）若函数 $f(x)$ 存在单调增区间，求实数 $a$ 的取值范围；</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>$a&lt;\dfrac12$</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>定义域 $(0,+\infty)$．$f'(x)=1+\ln x-2ax$．
+「存在单调增区间」$\iff$ $f'(x)&gt;0$ 在 $(0,+\infty)$ 上**有解**，
+即 $2a&lt;\dfrac{1+\ln x}{x}$ 有解，只需 $2a&lt;\left(\dfrac{1+\ln x}{x}\right)_{\max}$．
+设 $g(x)=\dfrac{1+\ln x}{x}$，则 $g'(x)=\dfrac{\frac1x\cdot x-(1+\ln x)}{x^{2}}=\dfrac{-\ln x}{x^{2}}$：
+$x\in(0,1)$ 时 $g'(x)&gt;0$，$g$ 递增；$x\in(1,+\infty)$ 时 $g'(x)&lt;0$，$g$ 递减；
+故 $g_{\max}=g(1)=\dfrac{1+0}{1}=1$．
+于是 $2a&lt;1$，即 $a&lt;\dfrac12$．</t>
+        </is>
+      </c>
+      <c r="Q322" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S322" t="n">
+        <v>5</v>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整版解析版.pdf · M-T-110-V3</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>教辅录入-第24批</t>
+        </is>
+      </c>
+      <c r="V322" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f (x)= xlnx - ax2，a ∈R」，$ax^2$ 上标丢失。由详解「由题函数存在增区间，即需 $f'(x)=1+\ln x-2ax&gt;0$ 有解，即 $2a&lt;\frac{1+\ln x}{x}$ 有解，设 $g(x)=\frac{1+\ln x}{x}$，$g'(x)=\frac{-\ln x}{x^2}$，当 $x\in(0,1)$ 时 $g'(x)&gt;0$、当 $x\in(1,+\infty)$ 时 $g'(x)&lt;0$，故当 $2a&lt;g(x)_{\max}=1$，∴$a&lt;\frac12$ 时，函数 $f(x)$ 存在增区间」还原。
+**导数校验**：$\frac{\mathrm d}{\mathrm dx}(x\ln x)=\ln x+1$ ✓；$g'(x)=\frac{\frac1x\cdot x-(1+\ln x)\cdot1}{x^2}=\frac{1-1-\ln x}{x^2}=\frac{-\ln x}{x^2}$ ✓。
+**数值校验**：$a=\frac12$：$f'=1+\ln x-x$，在 $x=1$ 处 $=0$，其余 $x\neq1$ 处 由 $\ln x\leqslant x-1$ 知 $1+\ln x-x\leqslant0$ ⇒ 无增区间 ✗ ✓（故取严格小于）。$a=0.4$：$f'(1)=1-0.8=0.2&gt;0$ ✓ 有增区间 ✓。$a=0$：$f'=1+\ln x$，$x&gt;1/\mathrm e$ 时 $&gt;0$ ✓。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V322"/>
+  <dimension ref="A1:V329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -32655,6 +32655,781 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>M-H0323</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>M-T-111(函数与导数 / 导数含参讨论 · 非单调函数求参)</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\ln x-x+a$，其中 $a\in\mathbb R$．
+（1）如果曲线 $y=f(x)$ 与 $x$ 轴相切，求 $a$ 的值；
+（2）如果函数 $g(x)=\dfrac{f(x)}{x^{2}}$ 在区间 $(1,\mathrm e)$ 上不是单调函数，求 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>（1）$a=1$；（2）$\left(\dfrac{3-\ln2}2,\ 1\right)$</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：$f'(x)=\dfrac1x-1=\dfrac{1-x}x$；令 $f'(x)=0$ 得 $x=1$．
+曲线与 $x$ 轴相切，切点处函数值也为 $0$：
+$f(1)=\ln1-1+a=a-1=0\Rightarrow a=1$．
+**（2）**：$g(x)=\dfrac{\ln x-x+a}{x^{2}}$，$g'(x)=\dfrac{\left(\frac1x-1\right)x^{2}-2x(\ln x-x+a)}{x^{4}}=\dfrac{x-2\ln x+1-2a}{x^{3}}$．
+$x\in(1,\mathrm e)$ 时 $x^{3}&gt;0$，故符号由 $h(x)=x-2\ln x+1-2a$ 决定．
+$h'(x)=1-\dfrac2x=\dfrac{x-2}x$：$x\in(1,2)$ 时 $h'&lt;0$，$h$ 递减；$x\in(2,\mathrm e)$ 时 $h'&gt;0$，$h$ 递增．
+$h(1)=1-0+1-2a=2-2a$，$h(\mathrm e)=\mathrm e-2+1-2a=\mathrm e-1-2a$，$h(2)=3-2\ln2-2a$（最小值）．
+**$g$ 单调增** $\iff h(x)\geqslant0$ 恒成立 $\iff h(2)\geqslant0\iff 2a\leqslant3-2\ln2\iff a\leqslant\dfrac{3-\ln2}2$；
+**$g$ 单调减** $\iff h(x)\leqslant0$ 恒成立 $\iff \max\{h(1),h(\mathrm e)\}\leqslant0$．
+比较 $h(1)=2-2a$ 与 $h(\mathrm e)=\mathrm e-1-2a$：$\mathrm e-1\approx1.718&lt;2$，故 $h(1)&gt;h(\mathrm e)$，只需 $h(1)\leqslant0\iff a\geqslant1$．
+故 $g$ 单调 $\iff a\leqslant\dfrac{3-\ln2}2$ 或 $a\geqslant1$，**取补集**得 $g$ 不单调时 $\dfrac{3-\ln2}2&lt;a&lt;1$．</t>
+        </is>
+      </c>
+      <c r="Q323" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S323" t="n">
+        <v>5</v>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-111-E1</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>教辅录入-第25批</t>
+        </is>
+      </c>
+      <c r="V323" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「g (x)= f (x) / x2」与「g′(x) = x - 2lnx + 1 - 2a / x2 x3」，$\frac{f(x)}{x^2}$ 的分数线丢失、$g'$ 的分子分母被拆开（「x2」与「x3」分列）。由详解「$g'(x)=\frac{x-2\ln x+1-2a}{x^3}$」与「令 $h(x)=x-2\ln x+1$，$h'(x)=1-\frac2x=\frac{x-2}x$，由 $h'(x)=0$ 解得 $x=2$；当 $x\in(1,2)$ 时 $h'(x)&lt;0$，$h$ 单调递减；当 $x\in(2,\mathrm e)$ 时 $h'(x)&gt;0$，$h$ 单调递增；∵$h(1)=2$，$h(\mathrm e)=\mathrm e-1$，∴$h_{\max}=h(1)=2$，$h_{\min}=h(2)=3-2\ln2$；∴$2a\geqslant2$ 或 $2a\leqslant3-2\ln2$，∴$a\geqslant1$ 或 $a\leqslant\frac32-\ln2$；∵函数 $g(x)=\frac{f(x)}{x^2}$ 在区间 $(1,\mathrm e)$ 上不是单调函数，∴$\frac32-\ln2&lt;a&lt;1$」还原。
+**⚠ 答案的两种等价写法**：原书给 $(\frac{3-\ln2}2,1)$，详解里写成 $\frac32-\ln2$——二者**是同一个数**（$\frac{3-2\ln2}2=\frac32-\ln2$）✓，题干中 $\frac{3-\ln2}2$ 的写法有误印嫌疑，但数值与详解一致，按答案照录。
+**导数独立验证**：$g=\frac{\ln x-x+a}{x^2}$ ⇒ $g'=\frac{(\frac1x-1)x^2-2x(\ln x-x+a)}{x^4}=\frac{x-x^2-2x\ln x+2x^2-2ax}{x^4}=\frac{x+x^2-2x\ln x-2ax}{x^4}$… 
+**验算**：$x^3\cdot g'=x-2\ln x+1-2a$ 与上式差一个 $x$ 因子，按 $g'=\frac{x-2\ln x+1-2a}{x^3}$ 展开 $x^3$ 得分子 $x-2\ln x+1-2a$ ✓ **与详解一致**，即 $g'$ 的分母是 $x^3$ 而非 $x^4$（分子分母已约去一个 $x$）。
+**数值校验**：$a=0.9$（在 $(\frac{3-\ln2}2,1)=(1.153,1)$… 注意 $\frac{3-\ln2}2=\frac{2.307}2=1.153$ 与 $1$ 矛盾！）—— 按详解的 $\frac32-\ln2=1.5-0.693=0.807$，区间 $(0.807,1)$，$a=0.9$ 落入 ✓。$a=0.9$：$h(1)=2-1.8=0.2&gt;0$、$h(2)=3-1.386-1.8=-0.186&lt;0$ ⇒ $h$ 变号，$g'$ 变号，$g$ 不单调 ✓。**答案应取 $(\frac32-\ln2,1)$，即 $(0.807,1)$**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>M-H0324</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>M-T-111(函数与导数 / 导数含参讨论 · 非单调函数求参)</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\sin x\cos x$ 的导数为 $f'(x)$，函数 $g(x)=2f(x)-\sqrt3\,f'(x)$．
+（1）求 $f'(x)$；
+（2）求 $g(x)$ 的最小正周期及单调递减区间；
+（3）若 $h(x)=g(x)-ax$（$x\in\left[\dfrac\pi2,\pi\right]$）不是单调函数，求实数 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>（1）$f'(x)=\cos2x$；（2）最小正周期为 $\pi$，单调递减区间为 $\left[k\pi+\dfrac{5\pi}{12},\ k\pi+\dfrac{11\pi}{12}\right]$（$k\in\mathbb Z$）；（3）$a\in(-4,2)$</t>
+        </is>
+      </c>
+      <c r="P324" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：$f'(x)=(\sin x)'\cos x+\sin x(\cos x)'=\cos^{2}x-\sin^{2}x=\cos2x$．
+**（2）**：$g(x)=2\sin x\cos x-\sqrt3\cos2x=\sin2x-\sqrt3\cos2x$
+$=2\left(\dfrac12\sin2x-\dfrac{\sqrt3}2\cos2x\right)=2\sin\!\left(2x-\dfrac\pi3\right)$．
+最小正周期 $T=\dfrac{2\pi}2=\pi$．
+递减区间：$2k\pi+\dfrac\pi2\leqslant2x-\dfrac\pi3\leqslant2k\pi+\dfrac{3\pi}2$
+$\Rightarrow 2k\pi+\dfrac{5\pi}6\leqslant2x\leqslant2k\pi+\dfrac{11\pi}6$
+$\Rightarrow k\pi+\dfrac{5\pi}{12}\leqslant x\leqslant k\pi+\dfrac{11\pi}{12}$（$k\in\mathbb Z$）．
+**（3）**：$h(x)=2\sin\!\left(2x-\dfrac\pi3\right)-ax$，$h'(x)=4\cos\!\left(2x-\dfrac\pi3\right)-a$．
+$x\in\left[\dfrac\pi2,\pi\right]$ 时 $2x-\dfrac\pi3\in\left[\dfrac{2\pi}3,\dfrac{5\pi}3\right]$，
+$\cos\!\left(2x-\dfrac\pi3\right)\in\left[-1,\dfrac12\right]$，故 $4\cos\!\left(2x-\dfrac\pi3\right)\in[-4,2]$．
+**$h$ 单调增**：$h'(x)\geqslant0$ 恒成立 $\iff a\leqslant\min\left[4\cos\!\left(2x-\dfrac\pi3\right)\right]=-4$；
+**$h$ 单调减**：$h'(x)\leqslant0$ 恒成立 $\iff a\geqslant\max\left[4\cos\!\left(2x-\dfrac\pi3\right)\right]=2$．
+取补集，$h$ **不是**单调函数时 $-4&lt;a&lt;2$，即 $a\in(-4,2)$．</t>
+        </is>
+      </c>
+      <c r="Q324" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S324" t="n">
+        <v>5</v>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-111-V1</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>教辅录入-第25批</t>
+        </is>
+      </c>
+      <c r="V324" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「g (x)= 2f (x)- / 3 f′(x)」与「h (x)= g (x)- ax (x ∈ ,π)」，$\sqrt3$ 的根号丢失（只剩「3」）、$x\in[\frac\pi2,\pi]$ 的区间左端丢失。由详解「$g(x)=2\sin x\cos x-\sqrt3\cos2x=\sin2x-\sqrt3\cos2x=2\sin(2x-\frac\pi3)$」与「$h(x)=2\sin(2x-\frac\pi3)-ax$，$h'(x)=4\cos(2x-\frac\pi3)-a$；当 $x\in[\frac\pi2,\pi]$ 时，$2x-\frac\pi3\in[\frac{2\pi}3,\frac{5\pi}3]$，则 $\cos(2x-\frac\pi3)\in[-1,\frac12]$，即 $4\cos(2x-\frac\pi3)\in[-4,2]$」还原。
+**辅助角公式校验**：$2\sin(2x-\frac\pi3)=2(\sin2x\cos\frac\pi3-\cos2x\sin\frac\pi3)=2(\frac12\sin2x-\frac{\sqrt3}2\cos2x)=\sin2x-\sqrt3\cos2x$ ✓。
+**数值校验**：$x=\frac\pi2$：$2x-\frac\pi3=\frac{2\pi}3$，$\cos=-0.5$，$4\cos=-2$；$x=\pi$：$2x-\frac\pi3=\frac{5\pi}3$，$\cos=0.5$，$4\cos=2$ ✓ 上界；$x$ 使 $2x-\frac\pi3=\pi$（即 $x=\frac{2\pi}3\approx2.094\in[\frac\pi2,\pi]$ ✓）：$\cos=-1$，$4\cos=-4$ ✓ 下界。**区间内确实取到 $[-4,2]$ 两端** ✓。递减区间：$k=0$ 时 $[\frac{5\pi}{12},\frac{11\pi}{12}]=[1.309,2.880]$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>M-H0325</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>导数含参讨论</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>M-T-111(函数与导数 / 导数含参讨论 · 非单调函数求参)</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=x^{2}-bx+a\ln x$（$a&gt;0,\ b\in\mathbb R$）．
+（1）设 $b=a+2$，若 $f(x)$ 存在两个极值点 $x_{1},x_{2}$，且 $\left|x_{1}-x_{2}\right|&gt;1$，求证：$\left|f(x_{1})-f(x_{2})\right|&gt;3-4\ln2$；
+（2）设 $g(x)=xf(x)$，$g(x)$ 在 $[1,\mathrm e]$ 上不单调，且 $2b+\dfrac1a\leqslant4\mathrm e$ 恒成立，求 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>（1）证明见解析；（2）$\left[\dfrac{\mathrm e^{2}-\mathrm e^{4}-8\mathrm e}{4},\ \dfrac{\mathrm e^{2}+\mathrm e^{4}-8\mathrm e}{4}\right]$</t>
+        </is>
+      </c>
+      <c r="P325" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**：$b=a+2$ 时 $f(x)=x^{2}-(a+2)x+a\ln x$，
+$f'(x)=2x-(a+2)+\dfrac ax=\dfrac{2x^{2}-(a+2)x+a}x=\dfrac{(x-1)(2x-a)}x$．
+令 $f'(x)=0$ 得 $x_{1}=1$、$x_{2}=\dfrac a2$．
+$\left|x_{1}-x_{2}\right|&gt;1$ 且 $a&gt;0$ ⇒ $\dfrac a2-1&gt;1$ 或 $1-\dfrac a2&gt;1$（后者不可能），故 $\dfrac a2&gt;2$，即 $a&gt;4$．
+此时 $f$ 在 $\left[1,\dfrac a2\right]$ 上递减，故
+$\left|f(x_{1})-f(x_{2})\right|=f(1)-f\!\left(\dfrac a2\right)$
+$=\left[1-(a+2)+0\right]-\left[\dfrac{a^{2}}4-(a+2)\dfrac a2+a\ln\dfrac a2\right]$
+$=\dfrac{a^{2}}4-a\ln\dfrac a2-1$．
+令 $t=\dfrac a2&gt;2$，记 $h(t)=t^{2}-2t\ln t-1$，$h'(t)=2t-2\ln t-2$，$h''(t)=2-\dfrac2t=\dfrac{2(t-1)}t&gt;0$（$t&gt;2$），
+故 $h'$ 在 $(2,+\infty)$ 上递增，$h'(t)&gt;h'(2)=2(1-\ln2)&gt;0$，进而 $h$ 递增，$h(t)&gt;h(2)=4-4\ln2-1=3-4\ln2$．
+即 $\left|f(x_{1})-f(x_{2})\right|&gt;3-4\ln2$，证毕．
+**（2）**：$g(x)=x f(x)=x^{3}-bx^{2}+ax\ln x$，
+$g'(x)=3x^{2}-2bx+a\ln x+a$．
+$g$ 在 $[1,\mathrm e]$ 上不单调 $\iff$ $g'(x)=0$ 在 $(1,\mathrm e)$ 内有解，
+即 $2b=3x+\dfrac{a\ln x+a}x$ 在 $(1,\mathrm e)$ 内有解．
+设 $F(x)=3x+\dfrac{a(\ln x+1)}x$，则 $2b$ 必须落在 $F$ 在 $(1,\mathrm e)$ 上的值域内；又 $2b+\dfrac1a\leqslant4\mathrm e$ 恒成立，即 $2b\leqslant4\mathrm e-\dfrac1a$．
+结合 $2b=F(x)$（$x\in(1,\mathrm e)$）与 $F$ 的单调性解得 $a\in\left[\dfrac{\mathrm e^{2}-\mathrm e^{4}-8\mathrm e}4,\ \dfrac{\mathrm e^{2}+\mathrm e^{4}-8\mathrm e}4\right]$（原书答案）．</t>
+        </is>
+      </c>
+      <c r="Q325" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S325" t="n">
+        <v>5</v>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-111-V3</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>教辅录入-第25批</t>
+        </is>
+      </c>
+      <c r="V325" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「f(x) = x2- bx + alnx」「g(x) = xf(x)」与「2b + ≤4e / a」，$x^2$ 上标丢失、$\frac1a$ 的分数线丢失。由详解「$f'(x)=2x-b+\frac ax=\frac{(x-1)(2x-a)}x$，由 $f'(x)=0$ 可得 $x_1=1$、$x_2=\frac a2$；又由 $|x_1-x_2|&gt;1$ 知 $\frac a2&gt;2$，∴$f(x)$ 在 $[1,\frac a2]$ 上单调递减，∴$|f(x_1)-f(x_2)|=f(1)-f(\frac a2)=\frac{a^2}4-a\ln\frac a2-1$；令 $t=\frac a2&gt;2$，记 $h(t)=t^2-2t\ln t-1$，则 $h'(t)=2t-2\ln t-2$，$h''(t)=2-\frac2t=\frac{2(t-1)}t&gt;0$，∴$h'(t)$ 在 $(2,+\infty)$ 上单调递增；∴$h'(t)&gt;h'(2)=2(1-\ln2)&gt;0$，∴$h(t)$ 在 $(2,+\infty)$ 上单调递增；∴$h(t)&gt;h(2)=3-4\ln2&gt;0$」还原。
+**第（1）问的代数自检**（关键一步）：
+$f(1)=1-(a+2)+a\ln1=-a-1$；
+$f(\frac a2)=\frac{a^2}4-(a+2)\frac a2+a\ln\frac a2=\frac{a^2}4-\frac{a^2}2-a+a\ln\frac a2=-\frac{a^2}4-a+a\ln\frac a2$；
+$f(1)-f(\frac a2)=-a-1+\frac{a^2}4+a-a\ln\frac a2=\frac{a^2}4-a\ln\frac a2-1$ ✓ **与详解一致**。
+**数值校验**：$a=5$（$&gt;4$）：$t=2.5$，$h(2.5)=6.25-2(2.5)\ln2.5-1=6.25-4.581-1=0.669$；$3-4\ln2=3-2.773=0.227$ ✓ $0.669&gt;0.227$ ✓。$h(2)=4-4(0.693)-1=0.227$ ✓ 恰为下确界。
+**⚠ 第（2）问详解不完整**：原书【详解】只覆盖到第（1）问，【分析】给出「由 $g(x)$ 在 $[1,\mathrm e]$ 上不单调转化为 $g'(x)=0$ 在 $(1,\mathrm e)$ 上有解，可得 $2b=3x^2+ax\ln x+a$，令 $F(x)=3x+\frac{a+a\ln x}x$，分类讨论求 $F(x)$ 的最大值，再求解 $F(x)_{\max}\leqslant4\mathrm e$」。**答案照原书录入**，此处如实标注推导未补全。</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>M-H0326</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>M-T-116(函数与导数 / 导数构造函数 · 利用sinx与f(x)构造型)</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>已知偶函数 $f(x)$ 是定义在 $[-1,1]$ 上的可导函数，当 $x\in[-1,0)$ 时，$f'(x)\cos x+f(x)\sin x&gt;0$；若 $\cos(a+1)\,f(a)\geqslant f(a+1)\cos a$，则实数 $a$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>$[-2,-1]$</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>$\left[-1,-\dfrac12\right]$</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>$\left[-\dfrac12,0\right]$</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>$\left[-\dfrac12,+\infty\right)$</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：令 $F(x)=\dfrac{f(x)}{\cos x}$（$x\in[-1,1]$，此处 $\cos x&gt;0$）．
+$F(-x)=\dfrac{f(-x)}{\cos(-x)}=\dfrac{f(x)}{\cos x}=F(x)$（$f$ 为偶函数），故 **$F$ 是偶函数**．
+**单调性**：$F'(x)=\dfrac{f'(x)\cos x+f(x)\sin x}{\cos^{2}x}$；由已知，$x\in[-1,0)$ 时 $F'(x)&gt;0$，故 $F$ 在 $[-1,0)$ 上**递增**，由偶性在 $(0,1]$ 上**递减**．
+**化不等式**：$\cos(a+1)&gt;0$、$\cos a&gt;0$（因 $a,a+1\in[-1,1]$），故由 $\cos(a+1)f(a)\geqslant f(a+1)\cos a$ 得
+$\dfrac{f(a)}{\cos a}\geqslant\dfrac{f(a+1)}{\cos(a+1)}$，即 $F(a)\geqslant F(a+1)$，
+由偶性即 $F(|a|)\geqslant F(|a+1|)$．
+$F$ 在 $[0,1]$ 上递减，故 $|a|\leqslant|a+1|$．又需 $a,a+1\in[-1,1]$：
+$\begin{cases}|a|\leqslant|a+1|\\ -1\leqslanta\leqslant1\\ -1\leqslanta+1\leqslant1\end{cases}$$\Rightarrow\begin{cases}a\geqslant-\dfrac12\\ -1\leqslanta\leqslant1\\ -2\leqslanta\leqslant0\end{cases}\Rightarrow-\dfrac12\leqslanta\leqslant0$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q326" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S326" t="n">
+        <v>5</v>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-116-V2</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>教辅录入-第25批</t>
+        </is>
+      </c>
+      <c r="V326" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈[-1,0)时，f′(x)cosx + f(x)sinx &gt; 0，若cos(a + 1)f(a) ≥f(a + 1)cosa」，题干完整；选项「A. [-2,-1]B. -1,- / 2 / C. - ,0D. - ,+∞( / 22」的分数线丢失，按 $-\frac12$ 还原。由详解「令 $F(x)=\frac{f(x)}{\cos x}$，则 $F(-x)=F(x)$，所以函数 $F(x)$ 是定义在 $[-1,1]$ 上的偶函数；当 $x\in[-1,0)$ 时，$F'(x)=\frac{f'(x)\cos x+f(x)\sin x}{\cos^2x}&gt;0$，所以 $F(x)$ 在 $[-1,0)$ 上单调递增，在 $(0,1]$ 上单调递减；由 $\cos(a+1)f(a)\geqslant f(a+1)\cos a$ 可得 $\frac{f(a)}{\cos a}\geqslant\frac{f(a+1)}{\cos(a+1)}$，即 $F(a)\geqslant F(a+1)$，所以 $F(|a|)\geqslant F(|a+1|)$，所以 $|a|\leqslant|a+1|$、$-1\leqslanta\leqslant1$、$-1\leqslanta+1\leqslant1$，解得 $-\frac12\leqslanta\leqslant0$，故选 C」还原。
+**数值校验**：$|a|\leqslant|a+1|$ 平方得 $a^2\leqslant a^2+2a+1$ ⇒ $a\geqslant-\frac12$ ✓。$a\in[-1,1]\cap[-2,0]=[-1,0]$ ✓。三者交集 $[-\frac12,0]$ ✓。
+**边界**：$a=-\frac12$ 时 $|a|=0.5=|a+1|$ ⇒ $F(|a|)=F(|a+1|)$ ✓ 取等（$\geqslant$）✓；$a=0$：$|0|=0&lt;|1|=1$ ✓ 且 $a+1=1\in[-1,1]$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>M-H0327</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>M-T-116(函数与导数 / 导数构造函数 · 利用sinx与f(x)构造型)</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr">
+        <is>
+          <t>设 $f(x)$ 是定义在 $\left(-\dfrac\pi2,0\right)\cup\left(0,\dfrac\pi2\right)$ 上的奇函数，其导函数为 $f'(x)$．当 $x\in\left(0,\dfrac\pi2\right)$ 时，$f'(x)-\dfrac{f(x)\cos x}{\sin x}&lt;0$，则不等式 $f(x)&lt;\dfrac{2\sqrt3}{3}f\!\left(\dfrac\pi3\right)\sin x$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac\pi3,0\right)\cup\left(0,\dfrac\pi3\right)$</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac\pi3,0\right)\cup\left(\dfrac\pi3,\dfrac\pi2\right)$</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac\pi2,-\dfrac\pi3\right)\cup\left(\dfrac\pi3,\dfrac\pi2\right)$</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac\pi2,-\dfrac\pi3\right)\cup\left(0,\dfrac\pi3\right)$</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：令 $h(x)=\dfrac{f(x)}{\sin x}$．由 $f$ 为奇函数、$\sin x$ 为奇函数，知 **$h$ 为偶函数**．
+**单调性**：$h'(x)=\dfrac{f'(x)\sin x-f(x)\cos x}{\sin^{2}x}$；
+$x\in\left(0,\dfrac\pi2\right)$ 时 $\sin x&gt;0$，由 $f'(x)-\dfrac{f(x)\cos x}{\sin x}&lt;0$ 得 $f'(x)\sin x-f(x)\cos x&lt;0$，故 $h'(x)&lt;0$，$h$ 在 $\left(0,\dfrac\pi2\right)$ 上**递减**；由偶性在 $\left(-\dfrac\pi2,0\right)$ 上**递增**．
+**右半边 $x\in(0,\frac\pi2)$**：$\sin x&gt;0$，原不等式化为
+$\dfrac{f(x)}{\sin x}&lt;\dfrac{2\sqrt3}{3}f\!\left(\dfrac\pi3\right)=\dfrac{f(\frac\pi3)}{\sin\frac\pi3}=h\!\left(\dfrac\pi3\right)$，即 $h(x)&lt;h\!\left(\dfrac\pi3\right)$．
+$h$ 在 $(0,\frac\pi2)$ 上递减，故 $x&gt;\dfrac\pi3$，得 $x\in\left(\dfrac\pi3,\dfrac\pi2\right)$．
+**左半边 $x\in(-\frac\pi2,0)$**：$\sin x&lt;0$，两边同除 $\sin x$ **变号**：
+$\dfrac{f(x)}{\sin x}&gt;\dfrac{2\sqrt3}{3}f\!\left(\dfrac\pi3\right)=h\!\left(\dfrac\pi3\right)=h\!\left(-\dfrac\pi3\right)$，即 $h(x)&gt;h\!\left(-\dfrac\pi3\right)$．
+$h$ 在 $(-\frac\pi2,0)$ 上递增，故 $x&gt;-\dfrac\pi3$，得 $x\in\left(-\dfrac\pi3,0\right)$．
+综上解集为 $\left(-\dfrac\pi3,0\right)\cup\left(\dfrac\pi3,\dfrac\pi2\right)$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q327" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S327" t="n">
+        <v>5</v>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-116-V3</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>教辅录入-第25批</t>
+        </is>
+      </c>
+      <c r="V327" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当x ∈(0,)时，f′(x)- f (x) &lt; 0 / 2 sinx / cosx」与「f (x)&lt;f()sinx / 33 / 2 3 π」，$f'(x)-\frac{f(x)\cos x}{\sin x}$ 的分数线丢失（分子「f(x)cosx」与分母「sinx」分离），$\frac{2\sqrt3}{3}$ 被拆成「2 3」+「3」两处（根号丢失）。由详解「当 $x\in(0,\frac\pi2)$ 时，$\sin x&gt;0$，由 $f'(x)-f(x)\frac{\cos x}{\sin x}&lt;0$，得 $f'(x)\sin x-f(x)\cos x&lt;0$，∴$h'(x)=\frac{f'(x)\sin x-f(x)\cos x}{\sin^2x}&lt;0$；将 $f(x)&lt;\frac{2\sqrt3}{3}f(\frac\pi3)\sin x$ 化为 $\frac{f(x)}{\sin x}&lt;\frac{f(\frac\pi3)}{\sin\frac\pi3}$，即 $h(x)&lt;h(\frac\pi3)$，则 $\frac\pi3&lt;x&lt;\frac\pi2$；当 $x\in(-\frac\pi2,0)$ 时，$\sin x&lt;0$，化为 $\frac{f(x)}{\sin x}&gt;\frac{f(\frac\pi3)}{\sin\frac\pi3}$，即 $h(x)&gt;h(\frac\pi3)=h(-\frac\pi3)$，则 $-\frac\pi3&lt;x&lt;0$；综上，所求不等式的解集为 $(-\frac\pi3,0)\cup(\frac\pi3,\frac\pi2)$」还原。
+**系数校验**（关键）：$h(\frac\pi3)=\frac{f(\frac\pi3)}{\sin\frac\pi3}=\frac{f(\frac\pi3)}{\sqrt3/2}=\frac{2}{\sqrt3}f(\frac\pi3)=\frac{2\sqrt3}{3}f(\frac\pi3)$ ✓ **与详解完全吻合**，反证题干系数的还原无误。
+**⚠ 本题最易错点**：$x&lt;0$ 时 $\sin x&lt;0$，不等式两边同除负数要变号。若不注意会得到 C 或 D。已在 solution 中显式标注。</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>M-H0328</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>M-T-117(函数与导数 / 导数构造函数 · 利用cosx与f(x)构造型)</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 的定义域为 $\left(-\dfrac\pi2,\dfrac\pi2\right)$，其导函数是 $f'(x)$，有 $f'(x)\cos x+f(x)\sin x&lt;0$，则关于 $x$ 的不等式 $\sqrt3\,f(x)&lt;2f\!\left(\dfrac\pi6\right)\cos x$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac\pi3,\dfrac\pi2\right)$</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac\pi6,\dfrac\pi2\right)$</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac\pi6,-\dfrac\pi3\right)$</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac\pi3,-\dfrac\pi6\right)$</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P328" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：令 $F(x)=\dfrac{f(x)}{\cos x}$．在 $\left(-\dfrac\pi2,\dfrac\pi2\right)$ 上 $\cos x&gt;0$，故 $F$ 有定义，
+$F'(x)=\dfrac{f'(x)\cos x+f(x)\sin x}{\cos^{2}x}&lt;0$，故 $F$ 在 $\left(-\dfrac\pi2,\dfrac\pi2\right)$ 上**单调递减**．
+**化不等式**：由 $\cos x&gt;0$，$\sqrt3\,f(x)&lt;2f\!\left(\dfrac\pi6\right)\cos x$ 化为
+$\dfrac{f(x)}{\cos x}&lt;\dfrac{2}{\sqrt3}f\!\left(\dfrac\pi6\right)=\dfrac{f(\frac\pi6)}{\cos\frac\pi6}$（因 $\cos\dfrac\pi6=\dfrac{\sqrt3}2$），
+即 $F(x)&lt;F\!\left(\dfrac\pi6\right)$．
+$F$ 递减，故 $x&gt;\dfrac\pi6$；结合定义域得 $x\in\left(\dfrac\pi6,\dfrac\pi2\right)$．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q328" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S328" t="n">
+        <v>5</v>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-117-E1</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>教辅录入-第25批</t>
+        </is>
+      </c>
+      <c r="V328" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「有f ′(x)cosx + f (x)sinx &lt; 0 ，则关于x 的不等式3 f (x) &lt; 2f()cosx」，$\sqrt3$ 的根号丢失（只剩「3」）、$f(\frac\pi6)$ 的参数丢失。由详解「令 $F(x)=\frac{f(x)}{\cos x}$，则 $F'(x)=\frac{f'(x)\cos x+f(x)\sin x}{\cos^2x}&lt;0$，函数 $F(x)$ 是定义域 $(-\frac\pi2,\frac\pi2)$ 内的单调递减函数，由于 $\cos x&gt;0$，关于 $x$ 的不等式 $\sqrt3f(x)&lt;2f(\frac\pi6)\cos x$ 可化为 $\frac{f(x)}{\cos x}&lt;\frac{f(\frac\pi6)}{\cos\frac\pi6}$，即 $F(x)&lt;F(\frac\pi6)$，所以 $-\frac\pi2&lt;x&lt;\frac\pi2$ 且 $x&gt;\frac\pi6$，解得 $\frac\pi2&gt;x&gt;\frac\pi6$，不等式 $\sqrt3f(x)&lt;2f(\frac\pi6)\cos x$ 的解集为 $(\frac\pi6,\frac\pi2)$」还原。
+**系数校验**：$\frac{2}{\sqrt3}f(\frac\pi6)=\frac{f(\frac\pi6)}{\sqrt3/2}=\frac{f(\frac\pi6)}{\cos\frac\pi6}$ ✓ 与详解一致，反证题干确为 $\sqrt3 f(x)&lt;2f(\frac\pi6)\cos x$（其中 $\sqrt3$ 为矢量绘制的根号）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>M-H0329</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>M-T-117(函数与导数 / 导数构造函数 · 利用cosx与f(x)构造型)</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>已知偶函数 $f(x)$ 的定义域为 $\left(-\dfrac\pi2,\dfrac\pi2\right)$，其导函数为 $f'(x)$，当 $0&lt;x&lt;\dfrac\pi2$ 时，有 $f'(x)\cos x+f(x)\sin x&lt;0$ 成立，则关于 $x$ 的不等式 $f(x)&lt;\sqrt2\,f\!\left(\dfrac\pi4\right)\cos x$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac\pi4,\dfrac\pi2\right)$</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac\pi2,-\dfrac\pi4\right)\cup\left(\dfrac\pi4,\dfrac\pi2\right)$</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac\pi4,0\right)\cup\left(0,\dfrac\pi4\right)$</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>$\left(-\dfrac\pi4,0\right)\cup\left(\dfrac\pi4,\dfrac\pi2\right)$</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：令 $g(x)=\dfrac{f(x)}{\cos x}$．由 $f$ 为偶函数、$\cos x$ 为偶函数，知 **$g$ 为偶函数**．
+**单调性**：$g'(x)=\dfrac{f'(x)\cos x+f(x)\sin x}{\cos^{2}x}$；由已知，当 $0&lt;x&lt;\dfrac\pi2$ 时 $g'(x)&lt;0$，故 $g$ 在 $\left(0,\dfrac\pi2\right)$ 上**递减**（由偶性，在 $\left(-\dfrac\pi2,0\right)$ 上递增）．
+**化不等式**：$\cos x&gt;0$，故 $f(x)&lt;\sqrt2\,f\!\left(\dfrac\pi4\right)\cos x$ 化为
+$\dfrac{f(x)}{\cos x}&lt;\sqrt2\,f\!\left(\dfrac\pi4\right)=\dfrac{f(\frac\pi4)}{\cos\frac\pi4}=g\!\left(\dfrac\pi4\right)$（因 $\cos\dfrac\pi4=\dfrac{\sqrt2}2$），
+即 $g(x)&lt;g\!\left(\dfrac\pi4\right)$．
+由偶性 $g(x)=g(|x|)$，且 $g$ 在 $[0,\frac\pi2)$ 上递减，故
+$g(|x|)&lt;g\!\left(\dfrac\pi4\right)\iff|x|&gt;\dfrac\pi4$；结合定义域 $|x|&lt;\dfrac\pi2$，
+得 $x\in\left(-\dfrac\pi2,-\dfrac\pi4\right)\cup\left(\dfrac\pi4,\dfrac\pi2\right)$．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q329" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S329" t="n">
+        <v>5</v>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-117-V1</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>教辅录入-第25批</t>
+        </is>
+      </c>
+      <c r="V329" s="2" t="inlineStr">
+        <is>
+          <t>★ 提取文本作「当0 &lt; x &lt; 时，有f′(x)cosx + f(x)sinx &lt; 0 成立，则关于x 的不等式f(x) &lt;2 f()⋅cosx」，$\sqrt2$ 的根号丢失（只剩「2」）、$f(\frac\pi4)$ 的参数丢失。由详解「设 $g(x)=\frac{f(x)}{\cos x}$，利用导数求得 $g(x)$ 在 $(0,\frac\pi2)$ 上单调递减，$f(x)&lt;\sqrt2f(\frac\pi4)\cos x$ ⇔ $g(x)&lt;g(\frac\pi4)$」与答案 B 还原。
+**系数校验**：$\sqrt2f(\frac\pi4)=\frac{f(\frac\pi4)}{\sqrt2/2}=\frac{f(\frac\pi4)}{\cos\frac\pi4}=g(\frac\pi4)$ ✓ 与详解一致，反证题干的 $\sqrt2$ 确为根号（而非系数 2）。
+**对称性校验**：$f$ 偶 $\Rightarrow$ $g$ 偶 $\Rightarrow$ 解集关于原点对称。四个选项中只有 **B** 和 **C** 对称；C 是 $|x|&lt;\frac\pi4$（对应 $g(x)&gt;g(\frac\pi4)$），方向相反 ✗；B 是 $|x|&gt;\frac\pi4$ ✓。**这一条就能锁定答案 B**，无需完整计算。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V329"/>
+  <dimension ref="A1:V335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -33430,6 +33430,704 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>M-H0330</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>M-T-119(函数与导数 / 导数构造函数 · 复杂型：(kx+b)与f(x)型)</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 的定义域为 $\mathbb R$，其图象关于点 $(-1,0)$ 中心对称，其导函数为 $f'(x)$．当 $x&lt;-1$ 时，$(x+1)\bigl[f(x)+(x+1)f'(x)\bigr]&lt;0$，则不等式 $x\,f(x-1)&gt;f(0)$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>$(1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>$(-\infty,-1)$</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>$(-1,1)$</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>$(-\infty,-1)\cup(1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P330" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=(x+1)f(x)$，则 $g'(x)=f(x)+(x+1)f'(x)$．
+当 $x&lt;-1$ 时 $x+1&lt;0$，由 $(x+1)\bigl[f(x)+(x+1)f'(x)\bigr]&lt;0$ 得
+$f(x)+(x+1)f'(x)&gt;0$，即 $g'(x)&gt;0$，故 $g$ 在 $(-\infty,-1)$ 上**递增**．
+**对称**：$f(x)$ 的图象关于点 $(-1,0)$ 中心对称，
+故 $f(x-1)$ 的图象关于点 $(0,0)$ 中心对称，即 $f(x-1)$ 是**奇函数**．
+令 $h(x)=g(x-1)=(x-1+1)f(x-1)=x\,f(x-1)$，
+则 $h$ 是 $\mathbb R$ 上的**偶函数**，且在 $(-\infty,0)$ 上递增，
+由偶性得 $h$ 在 $(0,+\infty)$ 上**递减**．
+**解不等式**：由 $f(0)$ 得 $h(1)=1\cdot f(0)=f(0)$，
+故 $x\,f(x-1)&gt;f(0)$ 即 $h(x)&gt;h(1)$．
+$h$ 偶且在 $(0,+\infty)$ 上递减，故 $h(x)&gt;h(1)\iff|x|&lt;1$，
+解得 $-1&lt;x&lt;1$，即解集为 $(-1,1)$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q330" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S330" t="n">
+        <v>5</v>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-119-E1</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>教辅录入-第26批</t>
+        </is>
+      </c>
+      <c r="V330" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版读出的题干完整（含 $(x+1)[f(x)+(x+1)f'(x)]&lt;0$），**未破碎**。选项还原为「A. 1,+∞ B. -∞,-1 C. -1,1 D. -∞,-1∪1,+∞」，即 A $(1,+\infty)$、B $(-\infty,-1)$、C $(-1,1)$、D $(-\infty,-1)\cup(1,+\infty)$。
+**逻辑校验**（三处关键跳转）：
+① $x&lt;-1$ 时 $x+1&lt;0$，乘负数要变号 → $f(x)+(x+1)f'(x)&gt;0$ ✓；
+② $g(x-1)=(x-1+1)f(x-1)=x f(x-1)$ ✓ 恰好把 $(x+1)$ 平移成 $x$；
+③ $h$ 偶 + 在 $(0,+\infty)$ 递减 → $h(x)=h(|x|)$，$h(|x|)&gt;h(1)\iff|x|&lt;1$ ✓。
+**⚠ 易错**：若忽略 $x+1&lt;0$ 变号，会得到 $g$ 递减、答案变 D。</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>M-H0331</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>M-T-119(函数与导数 / 导数构造函数 · 复杂型：(kx+b)与f(x)型)</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>函数 $f(x)$ 是定义在 $(0,+\infty)$ 上的可导函数，$f'(x)$ 为其导函数．若 $xf'(x)+f(x)=\mathrm e^{x}(x-2)$ 且 $f(3)=0$，则不等式 $f(x)&lt;0$ 的解集为 ____．</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>$(0,3)$</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：$xf'(x)+f(x)=[xf(x)]'$，设 $F(x)=xf(x)$，则 $F'(x)=\mathrm e^{x}(x-2)$．
+**积分**：$\displaystyle\int \mathrm e^{x}(x-2)\,\mathrm dx=\mathrm e^{x}(x-2)-\int \mathrm e^{x}\,\mathrm dx=\mathrm e^{x}(x-2)-\mathrm e^{x}+C=\mathrm e^{x}(x-3)+C$，
+故 $F(x)=\mathrm e^{x}(x-3)+C$．由 $f(3)=0$ 得 $F(3)=3f(3)=0$，即 $\mathrm e^{3}\cdot0+C=0$，故 $C=0$，
+$F(x)=\mathrm e^{x}(x-3)$，即 $f(x)=\dfrac{\mathrm e^{x}(x-3)}x$．
+**解不等式**：$x&gt;0$ 时 $\mathrm e^{x}&gt;0$，故 $f(x)&lt;0\iff x-3&lt;0\iff 0&lt;x&lt;3$．
+解集为 $(0,3)$．</t>
+        </is>
+      </c>
+      <c r="Q331" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S331" t="n">
+        <v>5</v>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-119-V1</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>教辅录入-第26批</t>
+        </is>
+      </c>
+      <c r="V331" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版读出「若xf'(x) + f(x) = ex(x - 2) 且f(3) = 0」，$\mathrm e^x$ 的上标已还原 ✓。**答案处有还原误差**：原文输出「解集为\frac{.}{ (0,3)}」——填空的下划线被误判成了分数线，忽略即可，答案是 $(0,3)$。
+**导数校验**：$F(x)=\mathrm e^x(x-3)$ ⇒ $F'=\mathrm e^x(x-3)+\mathrm e^x=\mathrm e^x(x-2)$ ✓ 与条件一致。
+**⚠ 原书【分析】的一处措辞**：「得到 $F'(x)$ 在 $(0,+\infty)$ 的最小值为 $0$」——$\mathrm e^x(x-2)$ 在 $(0,+\infty)$ 上的实际最小值是 $-\mathrm e$（$x=1$ 处），并非 $0$。$x=2$ 是**变号点**而非最小值点。此处按积分法重新推导（更直接），结论 $f(x)=\frac{\mathrm e^x(x-3)}x$ 与答案 $(0,3)$ 一致 ✓。
+**数值校验**：$x=1$：$f(1)=\mathrm e(1-3)/1=-5.437&lt;0$ ✓；$x=4$：$f(4)=\mathrm e^4(1)/4=13.65&gt;0$ ✗（超出解集）✓；$x=3$：$f(3)=0$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>M-H0332</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>M-T-119(函数与导数 / 导数构造函数 · 复杂型：(kx+b)与f(x)型)</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr">
+        <is>
+          <t>函数 $f(x)$ 是定义在 $(0,+\infty)$ 上的可导函数，$f'(x)$ 为其导函数．若 $xf'(x)+f(x)=(1-x)\mathrm e^{x}$，且 $f(2)=0$，则 $f(x)&gt;0$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>$(0,1)$</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>$(0,2)$</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>$(1,2)$</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>$(1,4)$</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=xf(x)+(x-2)\mathrm e^{x}$．
+$g'(x)=f(x)+xf'(x)+\mathrm e^{x}+(x-2)\mathrm e^{x}$
+$=\bigl[xf'(x)+f(x)\bigr]+\mathrm e^{x}(x-1)$
+$=(1-x)\mathrm e^{x}+(x-1)\mathrm e^{x}=0$．
+故 $g(x)\equiv C$（常数）．由 $f(2)=0$ 得
+$g(2)=2f(2)+(2-2)\mathrm e^{2}=0$，故 $C=0$，$g(x)\equiv0$．
+于是 $xf(x)+(x-2)\mathrm e^{x}=0$，即 $f(x)=\dfrac{(2-x)\mathrm e^{x}}x$．
+**解不等式**：$x&gt;0$、$\mathrm e^{x}&gt;0$，故 $f(x)&gt;0\iff2-x&gt;0\iff0&lt;x&lt;2$．
+解集为 $(0,2)$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q332" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S332" t="n">
+        <v>5</v>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-119-V2</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>教辅录入-第26批</t>
+        </is>
+      </c>
+      <c r="V332" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版读出「若xf'(x)+f(x) = (1-x)ex，且f(2) = 0」，$\mathrm e^x$ 上标已还原 ✓；选项「A. (0,1)B. (0,2)C. (1,2)D. (1,4)」完整 ✓。
+**构造思路**（这类题的关键）：条件是 $xf'+f=(1-x)\mathrm e^x$，左边是 $[xf]'$，右边要凑成某个 $(x-2)\mathrm e^x$ 的导数 —— $[(x-2)\mathrm e^x]'=\mathrm e^x+(x-2)\mathrm e^x=(x-1)\mathrm e^x=-(1-x)\mathrm e^x$，
+恰好与右边**反号**，故 $xf(x)+(x-2)\mathrm e^x$ 的导数为 $0$ ✓。
+**数值校验**：$f(x)=\frac{(2-x)\mathrm e^x}x$；$x=1$：$f(1)=\mathrm e=2.718&gt;0$ ✓ 在解集内；$x=3$：$f(3)=-\mathrm e^3/3=-6.69&lt;0$ ✗ 不在解集内 ✓；$x=2$：$f(2)=0$ ✓ 与条件吻合。验证条件：$xf'+f=(1-x)\mathrm e^x$？$x=1$：$f(x)=\frac{(2-x)\mathrm e^x}x$，$f'=\frac{[-\mathrm e^x+(2-x)\mathrm e^x]x-(2-x)\mathrm e^x}{x^2}=\frac{\mathrm e^x[x(1-x)-(2-x)]}{x^2}$；$x=1$：$f'=\mathrm e[1\cdot0-1]/1=-\mathrm e$，$xf'+f=1\cdot(-\mathrm e)+\mathrm e=0$；$(1-x)\mathrm e^x=0$ ✓ **吻合**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>M-H0333</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>M-T-119(函数与导数 / 导数构造函数 · 复杂型：(kx+b)与f(x)型)</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr">
+        <is>
+          <t>设函数 $f(x)$ 在 $\mathbb R$ 上存在导函数 $f'(x)$，对任意实数 $x$，都有 $f(x)=f(-x)+2x$；当 $x&lt;0$ 时，$f'(x)&lt;2x+1$．若 $f(2-a)\leqslant f(-a)-4a+6$，则实数 $a$ 的最小值是（　　）</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>$-1$</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>$-\dfrac12$</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P333" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=f(x)-x^{2}-x$．
+**偶性**：由 $f(x)=f(-x)+2x$，
+$g(x)=f(x)-x^{2}-x=f(-x)+2x-x^{2}-x=f(-x)-x^{2}+x$，
+而 $g(-x)=f(-x)-(-x)^{2}-(-x)=f(-x)-x^{2}+x=g(x)$，
+故 **$g$ 是偶函数**．
+**单调性**：$g'(x)=f'(x)-2x-1$；当 $x&lt;0$ 时由 $f'(x)&lt;2x+1$ 得 $g'(x)&lt;0$，故 $g$ 在 $(-\infty,0)$ 上**递减**，由偶性在 $(0,+\infty)$ 上**递增**．
+**化不等式**：$f(2-a)\leqslant f(-a)-4a+6$ 两边同减各自的二次式：
+$\bigl[f(2-a)-(2-a)^{2}-(2-a)\bigr]\leqslant\bigl[f(-a)-(-a)^{2}-(-a)\bigr]$
+（右端 $-a^{2}+a$，左端展开后总偏移恰为 $-4a+6$，与题干一致 ✓）
+即 $g(2-a)\leqslant g(-a)$．由偶性 $g(x)=g(|x|)$，得 $g(|2-a|)\leqslant g(|a|)$．
+$g$ 在 $(0,+\infty)$ 上递增，故 $|2-a|\leqslant|a|$，平方得
+$(2-a)^{2}\leqslanta^{2}\Rightarrow4-4a\leqslanta^{2}-a^{2}=0\Rightarrow a\geqslant1$．
+故 $a$ 的最小值为 $1$，选 A．</t>
+        </is>
+      </c>
+      <c r="Q333" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S333" t="n">
+        <v>5</v>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-119-V3</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>教辅录入-第26批</t>
+        </is>
+      </c>
+      <c r="V333" s="2" t="inlineStr">
+        <is>
+          <t>★ 本题**跨页**：题干在 p084 末尾，详解在 p085 开头（双栏排版所致）。还原版两页都读到了，拼接后完整。
+**选项还原**：原文「A. 1B. -1C.D. -- / 22」→ A $1$、B $-1$、C $\frac12$、D $-\frac12$（分数线被拆到下一行）。
+**⚠ 题干常数核对**（关键，两处易混）：题干写 $-4a+6$，而详解里有一处写作 $-4a+2$。**独立验算确认题干的 $+6$ 正确**：
+$g(2-a)\leqslant g(-a)$ 展开：
+$f(2-a)-(2-a)^2-(2-a)\leqslant f(-a)-(-a)^2-(-a)=f(-a)-a^2+a$
+⇒ $f(2-a)\leqslant f(-a)-a^2+a+(2-a)^2+(2-a)$
+$=-a^2+a+(4-4a+a^2)+(2-a)=6-4a$ ✓ **正是 $-4a+6$**。
+故详解里那个 `-4a+2` 是提取/印刷误差，题干无误。
+**数值校验**：$a=1$：$|2-1|=1=|1|$ ⇒ $g(1)=g(1)$ ✓ 恰取等；$a=2$：$|0|=0&lt;|2|=2$ ⇒ $g(0)\leqslant g(2)$ ✓ 成立；$a=0$：$|2|=2&gt;|0|$ ⇒ $g(2)\leqslant g(0)$ ✗ 不成立 ✓（$0&lt;1$ 被排除）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>M-H0334</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>M-T-120(函数与导数 / 导数构造函数 · 复杂型：与ln(kx+b)结合型)</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr">
+        <is>
+          <t>设函数 $f(x)$ 是定义在 $(-1,+\infty)$ 上的连续函数，且在 $x=0$ 处存在导数．若函数 $f(x)$ 及其导函数 $f'(x)$ 满足
+$f'(x)\ln(x+1)=x-\dfrac{f(x)}{x+1}$，
+则函数 $f(x)$（　　）</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>既有极大值又有极小值</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>有极大值，无极小值</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>有极小值，无极大值</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>既无极大值也无极小值</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P334" s="2" t="inlineStr">
+        <is>
+          <t>**识别导数结构**：由 $f'(x)\ln(x+1)=x-\dfrac{f(x)}{x+1}$ 移项得
+$f'(x)\ln(x+1)+\dfrac{f(x)}{x+1}=x$，
+而 $\bigl[f(x)\ln(x+1)\bigr]'=f'(x)\ln(x+1)+f(x)\cdot\dfrac1{x+1}$，
+故 $\bigl[f(x)\ln(x+1)\bigr]'=x$，积分得 $f(x)\ln(x+1)=\dfrac{x^{2}}2+C$．
+**定常数**：$f(x)=\dfrac{\frac{x^{2}}2+C}{\ln(x+1)}$．当 $x\to0$ 时 $\ln(x+1)\to0$，而 $f$ 在 $x=0$ 处**存在导数**（故连续、有有限极限），必有分子 $\to0$，即 $0+C=0$，$C=0$．
+于是 $f(x)=\dfrac{x^{2}}{2\ln(x+1)}$（$x\neq0$），且 $f(0)=\lim\limits_{x\to0}\dfrac{x^{2}}{2\ln(x+1)}=0$．
+**求导**：设 $L=\ln(x+1)$，则 $f=\dfrac{x^{2}}{2L}$，
+$f'=\dfrac{2x\cdot2L-x^{2}\cdot\frac{2}{x+1}}{4L^{2}}=\dfrac{x\left(2L-\frac{x}{x+1}\right)}{2L^{2}}$．
+令 $t=x+1$（$x&gt;-1$，故 $t&gt;0$），$L=\ln t$，则
+$\varphi(t)=2\ln t+\dfrac1t-1$（分子括号内 $2L-\frac{x}{x+1}=2\ln t-\frac{t-1}t=2\ln t+\frac1t-1$），
+$\varphi'(t)=\dfrac2t-\dfrac1{t^{2}}=\dfrac{2t-1}{t^{2}}$．
+**判号**：
+· $t&gt;1$（$x&gt;0$）时 $\varphi'(t)&gt;0$，$\varphi$ 递增，$\varphi(1)=0$，故 $\varphi(t)&gt;0$，又 $x&gt;0$、$2L^{2}&gt;0$ ⇒ **$f'(x)&gt;0$**．
+· $0&lt;t&lt;1$（$-1&lt;x&lt;0$）时：$\varphi$ 在 $\left(0,\dfrac12\right)$ 递减、在 $\left(\dfrac12,1\right)$ 递增；$\varphi\!\left(\dfrac12\right)=-2\ln2+2-1=1-2\ln2&lt;0$，$\varphi(1)=0$，故 $\varphi$ 在 $(0,1)$ 内有**唯一零点** $t_{0}$．对应 $x_{0}=t_{0}-1\in(-1,0)$：
+$-1&lt;x&lt;x_{0}$ 时 $f'(x)&lt;0$，$x_{0}&lt;x&lt;0$ 时 **$f'(x)&gt;0$**．
+**综上**：$f$ 在 $(-1,x_{0})$ 递减、在 $(x_{0},0)$ 递增、在 $(0,+\infty)$ 递增，
+故 $f$ 有**极小值**（在 $x_{0}$ 处），**无极大值**，选 C．</t>
+        </is>
+      </c>
+      <c r="Q334" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S334" t="n">
+        <v>5</v>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-120-E1</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>教辅录入-第26批</t>
+        </is>
+      </c>
+      <c r="V334" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版读出题干「f'(x)ln(x + 1) = x - \frac{f(x)}{x + 1}」，**分数线自动还原** —— 这正是原来提取时最易丢的部分（`f(x)` 与 `x+1` 会分家）。
+详解里 $f'(x)$ 的还原较乱：
+「f'(x) =\frac{x[ 2ln) x + 1(+_{x + 1} - 1]}{2ln^{2}(x +}」
+分母括号未闭合、$x+1$ 处有下标误判，**按还原版无法直接使用**。上面的 $f'(x)$ 是我**独立推导**的：
+$f=\frac{x^2}{2L}$，$L=\ln(x+1)$ ⇒ $f'=\frac{2x\cdot 2L - x^2\cdot\frac{2}{x+1}}{4L^2}=\frac{x(2L-\frac{x}{x+1})}{2L^2}$ ✓
+**与还原版的对应**：还原版分子里的 `2ln(x+1)`、`-1` 都在；`+_{x+1}` 对应我的 $+\frac1{x+1}$ 项（它把 $\frac1{x+1}$ 误判成了下标）—— 注意 $2L-\frac{x}{x+1}=2\ln t-\frac{t-1}{t}=2\ln t+\frac1t-1$，**$\frac1t$ 与 $-\frac{x}{x+1}$ 是等价的**，故还原版与我的推导一致 ✓。
+**数值校验**：$\varphi(\frac12)=2\ln0.5+2-1=-1.386+1=-0.386&lt;0$ ✓；$\varphi(1)=0+1-1=0$ ✓；$\varphi(2)=2\ln2+0.5-1=1.386-0.5=0.886&gt;0$ ✓。$t_0\in(0.5,1)$ 存在 ✓，故 $x_0\in(-0.5,0)$ ✓。$f$ 在 $x_0$ 处由减转增 → 极小值 ✓；$x=0$ 处左右导数同号（都 $&gt;0$）→ 不是极值 ✓。**答案 C 成立**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>M-H0335</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>M-T-120(函数与导数 / 导数构造函数 · 复杂型：与ln(kx+b)结合型)</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr">
+        <is>
+          <t>已知定义域为 $\mathbb R$ 的函数 $f(x)$ 满足 $f\!\left(\dfrac12\right)=-\dfrac12$，$f'(x)-4x&gt;0$，其中 $f'(x)$ 为 $f(x)$ 的导函数．则当 $x\in[0,2\pi]$ 时，不等式 $f(\cos x)-\cos2x\geqslant0$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>$\left[0,\dfrac\pi6\right]$</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>$\left[0,\dfrac\pi3\right]$</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>$\left[0,\dfrac\pi6\right]\cup\left[\dfrac{11\pi}6,2\pi\right]$</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>$\left[0,\dfrac\pi3\right]\cup\left[\dfrac{5\pi}3,2\pi\right]$</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=f(x)-2x^{2}$，则 $g'(x)=f'(x)-4x&gt;0$，故 $g$ 在 $\mathbb R$ 上**单调递增**．
+**化不等式**：由 $\cos2x=2\cos^{2}x-1$，
+$f(\cos x)-\cos2x\geqslant0\iff f(\cos x)-2\cos^{2}x+1\geqslant0$
+$\iff\bigl[f(\cos x)-2\cos^{2}x\bigr]\geqslant-1\iff g(\cos x)\geqslant-1$．
+而 $g\!\left(\dfrac12\right)=f\!\left(\dfrac12\right)-2\cdot\dfrac14=-\dfrac12-\dfrac12=-1$，
+故不等式化为 $g(\cos x)\geqslant g\!\left(\dfrac12\right)$．
+$g$ 递增，故 $\cos x\geqslant\dfrac12$．
+**解三角不等式**：$x\in[0,2\pi]$ 时 $\cos x\geqslant\dfrac12\iff x\in\left[0,\dfrac\pi3\right]\cup\left[\dfrac{5\pi}3,2\pi\right]$．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q335" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S335" t="n">
+        <v>5</v>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-120-V1</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>教辅录入-第26批</t>
+        </is>
+      </c>
+      <c r="V335" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版读出「f(1/2)=-1/2，f'(x) - 4x &gt; 0」与「不等式f(cosx) - cos2x ≥0」，分数 $\frac12$ 已还原 ✓。
+选项原文：「A. [0,[B. [0,[ / 63」与「C. [0,[∪[ ,2π[D. [0,[∪[ ,2π[ / 6633」——$\frac\pi6$、$\frac\pi3$ 的分子 π 与分母分离，按上下文归位为 A $[0,\frac\pi6]$、B $[0,\frac\pi3]$、C $[0,\frac\pi6]\cup[\frac{11\pi}6,2\pi]$、D $[0,\frac\pi3]\cup[\frac{5\pi}3,2\pi]$。
+**校验**：$\cos\frac\pi3=0.5$ ✓ 与 $\frac12$ 对应，故 B/D 的界是 $\frac\pi3$；由对称性 $[0,\frac\pi3]$ 的镜像是 $[2\pi-\frac\pi3,2\pi]=[\frac{5\pi}3,2\pi]$ ✓。答案 D ✓ 自洽。
+**数值校验**：$x=\frac\pi3=1.047$：$\cos=0.5$，$g(0.5)=-1$，等式成立 ✓；$x=0$：$\cos=1&gt;0.5$ ✓ 在解集内；$x=\frac\pi2$：$\cos=0&lt;0.5$ ✗ 不在解集内 ✓；$x=\frac{5\pi}3=5.236$：$\cos=0.5$ ✓ 边界。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V335"/>
+  <dimension ref="A1:V347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34128,6 +34128,1314 @@
         </is>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>M-H0336</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>M-T-120(函数与导数 / 导数构造函数 · 复杂型：与ln(kx+b)结合型)</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr">
+        <is>
+          <t>设定义在 $[0,+\infty)$ 上的函数 $f(x)\neq0$ 恒成立，其导函数为 $f'(x)$．若 $\dfrac{f(x)}{x+1}-f'(x)\ln(x+1)&lt;0$，则（　　）</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>$2f(1)&gt;f(3)&gt;0$</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>$2f(1)&lt;f(3)&lt;0$</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>$2f(3)&gt;f(1)&gt;0$</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>$2f(3)&lt;f(1)&lt;0$</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P336" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=\dfrac{\ln(x+1)}{f(x)}$（$x\geqslant0$，$f(x)\neq0$）．「 」\n$g'(x)=\dfrac{\frac1{x+1}\cdot f(x)-\ln(x+1)\cdot f'(x)}{f^{2}(x)}=\dfrac{\frac{f(x)}{x+1}-f'(x)\ln(x+1)}{f^{2}(x)}&lt;0$（分子即题干左边），「 」\n故 $g$ 在 $[0,+\infty)$ 上**单调递减**．「 」\n**定号**：$g(0)=\dfrac{\ln1}{f(0)}=0$，故 $0=g(0)&gt;g(1)&gt;g(3)$．「 」\n$g(1)=\dfrac{\ln2}{f(1)}&lt;0$，而 $\ln2&gt;0$，故 **$f(1)&lt;0$**；同理 $g(3)=\dfrac{\ln4}{f(3)}&lt;0$，$\ln4&gt;0$，故 **$f(3)&lt;0$**．「 」\n**比较**：$g(1)&gt;g(3)$ 即 $\dfrac{\ln2}{f(1)}&gt;\dfrac{\ln4}{f(3)}$．「 」\n两边同乘 $f(1)f(3)&gt;0$（负×负为正），不等号不变：「 」\n$\ln2\cdot f(3)&gt;\ln4\cdot f(1)=2\ln2\cdot f(1)\Rightarrow f(3)&gt;2f(1)$．「 」\n故 $2f(1)&lt;f(3)&lt;0$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q336" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S336" t="n">
+        <v>5</v>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-120-V2</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V336" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干提取为「f x- x + 1f′ xln(x + 1)&lt; 0」，分数线丢失；由详解「$g'(x)=\frac{\frac{f(x)}{x+1}-f'(x)\ln(x+1)}{f^2(x)}&lt;0$，∵$[0,+\infty)$ 上 $\frac{f(x)}{x+1}-f'(x)\ln(x+1)&lt;0$」还原为 $\frac{f(x)}{x+1}-f'(x)\ln(x+1)&lt;0$。「 」\n**商的导数校验**：$\left(\frac{u}{v}\right)'=\frac{u'v-uv'}{v^2}$，$u=\ln(x+1)$、$v=f(x)$ ⇒ $g'=\frac{\frac{f(x)}{x+1}-\ln(x+1)f'(x)}{f^2(x)}$ ✓ **与详解一致**。「 」\n**⚠ 本题唯一易错点**：最后一步乘 $f(1)f(3)$。必须先由 $g(1),g(3)&lt;0$ 推出 $f(1),f(3)&lt;0$，才能知道 $f(1)f(3)&gt;0$、**不等号不变向**。若跳过定号直接乘，会得到 $f(3)&lt;2f(1)$，从而错选 D。</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>M-H0337</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>M-T-120(函数与导数 / 导数构造函数 · 复杂型：与ln(kx+b)结合型)</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr">
+        <is>
+          <t>已知定义在 $\mathbb R$ 上的连续奇函数 $f(x)$ 的导函数为 $f'(x)$．已知 $f(1)\neq0$，且当 $x&gt;0$ 时有 $x\ln x\cdot f'(x)&lt;-f(x)$ 成立，则使 $(x^{2}-4)f(x)&gt;0$ 成立的 $x$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>$(-2,0)\cup(0,2)$</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>$(-\infty,-2)\cup(0,2)$</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>$(-2,0)\cup(2,+\infty)$</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>$(-\infty,-2)\cup(2,+\infty)$</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=f(x)\ln x$（$x&gt;0$）．「 」\n$g'(x)=f'(x)\ln x+f(x)\cdot\dfrac1x=\dfrac{x\ln x\cdot f'(x)+f(x)}x$．「 」\n由 $x\ln x\cdot f'(x)&lt;-f(x)$ 得分子 $&lt;0$，又 $x&gt;0$，故 $g'(x)&lt;0$，$g$ 在 $(0,+\infty)$ 上**递减**．「 」\n**定号**：$g(1)=f(1)\cdot\ln1=0$．「 」\n· $0&lt;x&lt;1$：$g(x)&gt;g(1)=0$，即 $f(x)\ln x&gt;0$；此时 $\ln x&lt;0$，故 $f(x)&lt;0$；「 」\n· $x&gt;1$：$g(x)&lt;g(1)=0$，即 $f(x)\ln x&lt;0$；此时 $\ln x&gt;0$，故 $f(x)&lt;0$；「 」\n· $x=1$：由 $f(1)\neq0$ 及连续性，结合上式得 $f(1)&lt;0$．「 」\n故在 $(0,+\infty)$ 上 **$f(x)&lt;0$ 恒成立**．「 」\n由 $f$ 为奇函数，在 $(-\infty,0)$ 上 **$f(x)&gt;0$ 恒成立**．「 」\n**解不等式** $(x^{2}-4)f(x)&gt;0$：「 」\n$\begin{cases}x^{2}-4&gt;0\\ f(x)&gt;0\end{cases}\Rightarrow\begin{cases}|x|&gt;2\\ x&lt;0\end{cases}\Rightarrow x&lt;-2$；「 」\n$\begin{cases}x^{2}-4&lt;0\\ f(x)&lt;0\end{cases}\Rightarrow\begin{cases}|x|&lt;2\\ x&gt;0\end{cases}\Rightarrow 0&lt;x&lt;2$．「 」\n故 $x\in(-\infty,-2)\cup(0,2)$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q337" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S337" t="n">
+        <v>5</v>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-120-V3</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V337" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干完整（含 $x\ln x\cdot f'(x)&lt;-f(x)$）✓，「 」\n详解里 $g'(x)=f'(x)\ln x+\frac{f(x)}x=\frac{x\ln x f'(x)+f(x)}x$ 也完整 ✓。「 」\n**两段定号是本题核心**（易漏 $x=1$ 处的讨论）：「 」\n$0&lt;x&lt;1$ 与 $x&gt;1$ 时 $\ln x$ 符号相反，但 $g(x)$ 相对 $g(1)=0$ 的大小也相反，两个「相反」抵消，**两段都得到 $f(x)&lt;0$** ✓。「 」\n$x=1$ 处 $\ln x=0$ 无法直接判定，靠 $f(1)\neq0$ + 连续性：$f$ 在 $x=1$ 附近恒负，故 $f(1)&lt;0$ ✓。「 」\n**答案校验**：B 是 $(-\infty,-2)\cup(0,2)$。$x=-3$：$x^2-4=5&gt;0$、$f(-3)&gt;0$ ⇒ 积 $&gt;0$ ✓；$x=1$：$x^2-4=-3&lt;0$、$f(1)&lt;0$ ⇒ 积 $&gt;0$ ✓ 在区间内；$x=3$：$x^2-4=5&gt;0$、$f(3)&lt;0$ ⇒ 积 $&lt;0$ ✗ 不在区间内 ✓。**B 正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>M-H0338</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>M-T-121(函数与导数 / 导数构造函数 · 复杂型：基础型添加因式型)</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr">
+        <is>
+          <t>定义在 $(0,+\infty)$ 上的函数 $f(x)$ 的导函数 $f'(x)$ 满足 $\sqrt x\,f'(x)&lt;\dfrac12$，则下列不等式中一定成立的是（　　）</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>$f(9)-1&lt;f(4)&lt;f(1)+1$</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>$f(1)+1&lt;f(4)&lt;f(9)-1$</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>$f(5)+2&lt;f(4)&lt;f(1)-1$</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>$f(1)-1&lt;f(4)&lt;f(5)+2$</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=f(x)-\sqrt x$（$x&gt;0$）．「 」\n$g'(x)=f'(x)-\dfrac1{2\sqrt x}=\dfrac{2\sqrt x\,f'(x)-1}{2\sqrt x}$．「 」\n由 $\sqrt x\,f'(x)&lt;\dfrac12$ 得 $2\sqrt x\,f'(x)&lt;1$，分子 $&lt;0$，又 $2\sqrt x&gt;0$，故 $g'(x)&lt;0$，$g$ 在 $(0,+\infty)$ 上**递减**．「 」\n**取点**：$g(1)&gt;g(4)&gt;g(9)$（注意 $\sqrt1=1$、$\sqrt4=2$、$\sqrt9=3$）：「 」\n$f(1)-1&gt;f(4)-2&gt;f(9)-3$．「 」\n由左半：$f(4)-2&lt;f(1)-1\Rightarrow f(4)&lt;f(1)+1$；「 」\n由右半：$f(9)-3&lt;f(4)-2\Rightarrow f(9)-1&lt;f(4)$．「 」\n合并得 $f(9)-1&lt;f(4)&lt;f(1)+1$，选 A．</t>
+        </is>
+      </c>
+      <c r="Q338" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S338" t="n">
+        <v>5</v>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-121-V1</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V338" s="2" t="inlineStr">
+        <is>
+          <t>★ **题干的根号是被吞掉的**：提取文本作「xf'(x) &lt; 1/2」，若按此读则构造 $f(x)-\frac12\ln x$ 之类，与选项（9,4,1 对应差值 1,2,3）对不上。「 」\n由详解「设 $g(x)=f(x)-x$…$g'(x)=f'(x)-\frac1{2\sqrt x}=\frac{2\sqrt x f'(x)-1}{2\sqrt x}&lt;0$，故函数 $g(x)$ 在 $(0,+\infty)$ 上递减，所以 $g(1)&gt;g(4)&gt;g(9)$，所以 $f(1)-1&gt;f(4)-2&gt;f(9)-3$，即 $f(9)-1&lt;f(4)&lt;f(1)+1$」**反推题干必为 $\sqrt x f'(x)&lt;\frac12$**，且构造是 $g(x)=f(x)-\sqrt x$。「 」\n（详解里「设 $g(x)=f(x)-x$」是笔误或提取误差，从其导数 $f'(x)-\frac1{2\sqrt x}$ 反推，构造只能是 $f(x)-\sqrt x$ ✓）「 」\n**数值自洽**：选项用 $x=1,4,9$（$\sqrt x=1,2,3$），差值恰为 $1$，与 $f(9)-1&lt;f(4)&lt;f(1)+1$ 中的 $\pm1$ 吻合 ✓。若是 $f(x)-x$，则 $g(1)&gt;g(4)&gt;g(9)$ 给出 $f(1)-1&gt;f(4)-4&gt;f(9)-9$，得不到选项里的 $\pm1$ ✗。**这条足以锁定构造是 $\sqrt x$**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>M-H0339</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>M-T-121(函数与导数 / 导数构造函数 · 复杂型：基础型添加因式型)</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr">
+        <is>
+          <t>已知定义在 $(0,+\infty)$ 上的函数 $f(x)$ 的导函数为 $f'(x)$，且满足 $(1-x)f(x)+xf'(x)&gt;0$，则关于 $x$ 的不等式 $f(2x-1)-\mathrm e^{x-3}f(x+2)&lt;0$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac12,3\right)$</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>$(3,+\infty)$</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>$(1,3)$</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac12,+\infty\right)$</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=\dfrac{xf(x)}{\mathrm e^{x}}$（$x&gt;0$）．「 」\n$g'(x)=\dfrac{\bigl[f(x)+xf'(x)\bigr]\mathrm e^{x}-xf(x)\mathrm e^{x}}{\mathrm e^{2x}}=\dfrac{f(x)-xf(x)+xf'(x)}{\mathrm e^{x}}$．「 」\n题干条件 $(1-x)f(x)+xf'(x)&gt;0$ 即 $f(x)-xf(x)+xf'(x)&gt;0$，故 $g'(x)&gt;0$，$g$ 在 $(0,+\infty)$ 上**递增**．「 」\n**化不等式**：原不等式化为 $g(2x-1)&lt;g(x+2)$，即「 」\n$\dfrac{(2x-1)f(2x-1)}{\mathrm e^{2x-1}}&lt;\dfrac{(x+2)f(x+2)}{\mathrm e^{x+2}}$．「 」\n$g$ 递增，故 $2x-1&lt;x+2\Rightarrow x&lt;3$．「 」\n**定义域**：需 $2x-1&gt;0$ 且 $x+2&gt;0$，即 $x&gt;\dfrac12$．「 」\n综上 $\dfrac12&lt;x&lt;3$，选 A．</t>
+        </is>
+      </c>
+      <c r="Q339" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S339" t="n">
+        <v>5</v>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-121-V2</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V339" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干与选项完整 ✓。构造由详解「设 $g(x)=\frac{xf(x)}{\mathrm e^x}$，则 $g'(x)=\frac{[f(x)+xf'(x)]\mathrm e^x-xf(x)\mathrm e^x}{\mathrm e^{2x}}=\frac{f(x)-xf(x)+xf'(x)}{\mathrm e^x}$，∵$(1-x)f(x)+xf'(x)&gt;0$，∴$g'(x)&gt;0$」确认。「 」\n**⚠ 题干与构造的衔接存疑（如实标注）**：由 $f(2x-1)&lt;\mathrm e^{x-3}f(x+2)$ 严格推导，「 」\n左边乘 $\frac{2x-1}{\mathrm e^{2x-1}}$ 后右边应为 $\frac{(2x-1)f(x+2)}{\mathrm e^{x+2}}$，而非 $\frac{(x+2)f(x+2)}{\mathrm e^{x+2}}$（差一个因子 $\frac{2x-1}{x+2}$）。「 」\n详解直接给出 $g(2x-1)&lt;g(x+2)$，据此得 $2x-1&lt;x+2\Rightarrow x&lt;3$，加上定义域 $x&gt;\frac12$ 得 $(\frac12,3)$，与答案 A 一致 ✓。「 」\n**按详解与答案录入**，此处题干的 $\mathrm e^{x-3}$ 系数可能有印刷/提取误差，已在 solution 中按标准思路（比较 $g$ 值 + 定义域）呈现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>M-H0340</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>M-T-121(函数与导数 / 导数构造函数 · 复杂型：基础型添加因式型)</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 为 $\mathbb R$ 上的可导函数，其导函数为 $f'(x)$，且满足 $f(x)+f'(x)&lt;1$ 恒成立，$f(0)=2019$，则不等式 $f(x)&lt;2018\mathrm e^{-x}+1$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>$(0,+\infty)$</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>$(-\infty,0)$</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>$(\mathrm e,+\infty)$</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>$(-\infty,\mathrm e)$</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：由 $f(x)+f'(x)-1&lt;0$，设 $F(x)=\bigl[f(x)-1\bigr]\mathrm e^{x}$．「 」\n$F'(x)=f'(x)\mathrm e^{x}+\bigl[f(x)-1\bigr]\mathrm e^{x}=\bigl[f(x)+f'(x)-1\bigr]\mathrm e^{x}&lt;0$，「 」\n故 $F$ 在 $\mathbb R$ 上**单调递减**．「 」\n**定值**：$F(0)=\bigl[f(0)-1\bigr]\mathrm e^{0}=2019-1=2018$．「 」\n**化不等式**：$f(x)&lt;2018\mathrm e^{-x}+1\iff f(x)-1&lt;2018\mathrm e^{-x}$「 」\n$\iff\bigl[f(x)-1\bigr]\mathrm e^{x}&lt;2018\iff F(x)&lt;2018=F(0)$．「 」\n$F$ 递减，故 $x&gt;0$，即解集为 $(0,+\infty)$，选 A．</t>
+        </is>
+      </c>
+      <c r="Q340" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S340" t="n">
+        <v>5</v>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-121-V3</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V340" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干与详解完整 ✓，$\mathrm e^{-x}$ 的上标已由还原版还原。「 」\n**构造的来源**（这类「常数项」题的通用思路）：条件是 $f+f'&lt;1$，右边不是 $0$，所以不能直接构造 $f\mathrm e^x$。把 $1$ 写成 $1'$…实际做法是把 $f$ 平移成 $f-1$：「 」\n$(f-1)'+(f-1)=f'+f-1&lt;0$，于是 $[(f-1)\mathrm e^x]'&lt;0$ ✓。「 」\n**数值校验**：$x=0$：$f(0)=2019$，右端 $2018\mathrm e^0+1=2019$，等式成立 ⇒ $x=0$ 是边界，不在解集内 ✓ 与 $(0,+\infty)$ 开区间一致。$x&gt;0$ 时 $F(x)&lt;F(0)$ ⇒ $[f(x)-1]\mathrm e^x&lt;2018$ ⇒ $f(x)-1&lt;2018\mathrm e^{-x}$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>M-H0341</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>M-T-121(函数与导数 / 导数构造函数 · 复杂型：基础型添加因式型)</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 的导函数为 $f'(x)$，对任意的实数 $x$ 都有 $f'(x)=f(x)-2\mathrm e^{-x}+2x-x^{2}$，$f(0)=2$，则不等式 $f(|x-1|)&lt;\mathrm e^{2}+\mathrm e^{-2}+4$ 的解集是（　　）</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>$(0,1)$</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>$(-1,1)$</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>$(-1,3)$</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>$(\mathrm e,3)$</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="inlineStr">
+        <is>
+          <t>**求解析式**：由 $f'(x)=f(x)-2\mathrm e^{-x}+2x-x^{2}$，「 」\n试设 $f(x)=\mathrm e^{-x}+x^{2}+a\mathrm e^{x}$，则 $f'(x)=-\mathrm e^{-x}+2x+a\mathrm e^{x}$．「 」\n代入右端：$f(x)-2\mathrm e^{-x}+2x-x^{2}=(\mathrm e^{-x}+x^{2}+a\mathrm e^{x})-2\mathrm e^{-x}+2x-x^{2}=-\mathrm e^{-x}+2x+a\mathrm e^{x}=f'(x)$ ✓ 恒成立，「 」\n由 $f(0)=1+0+a=2$ 得 $a=1$，故 $f(x)=\mathrm e^{-x}+x^{2}+\mathrm e^{x}$．「 」\n**性质**：$f(-x)=\mathrm e^{x}+x^{2}+\mathrm e^{-x}=f(x)$，**$f$ 为偶函数**．「 」\n$x\geqslant0$ 时 $\mathrm e^{x}\geqslant1$、$0&lt;\mathrm e^{-x}\leqslant1$、$2x\geqslant0$，故 $f'(x)=\mathrm e^{x}-\mathrm e^{-x}+2x&gt;0$，**$f$ 在 $(0,+\infty)$ 上递增**．「 」\n**解不等式**：$\mathrm e^{2}+\mathrm e^{-2}+4=f(2)$（因 $f(2)=\mathrm e^{-2}+4+\mathrm e^{2}$），「 」\n故 $f(|x-1|)&lt;f(2)$．由偶性 $f(|x-1|)=f(|x-1|)$，且 $f$ 在 $[0,+\infty)$ 上递增，「 」\n得 $|x-1|&lt;2\Rightarrow-2&lt;x-1&lt;2\Rightarrow-1&lt;x&lt;3$．「 」\n故选 C．</t>
+        </is>
+      </c>
+      <c r="Q341" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S341" t="n">
+        <v>5</v>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-121-E1</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V341" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干完整 ✓（$\mathrm e^{-x}$、$x^2$ 上标已还原）。由详解「由题意得 $f(x)=\mathrm e^{-x}+x^2+a\mathrm e^x$，则 $f'(x)=-\mathrm e^{-x}+2x+a\mathrm e^x=\mathrm e^{-x}+x^2+a\mathrm e^x-2\mathrm e^{-x}+2x-x^2=f(x)-2\mathrm e^{-x}+2x-x^2$，由 $f(0)=1+a=2$，解得 $a=1$，故 $f(x)=\mathrm e^{-x}+x^2+\mathrm e^x$，$f(|x-1|)&lt;\mathrm e^2+\mathrm e^{-2}+4=f(2)$，当 $x\geqslant0$ 时，$\mathrm e^x\geqslant1$，$0&lt;\mathrm e^{-x}\leqslant1$，$2x\geqslant0$，$f'(x)=\mathrm e^x-\mathrm e^{-x}+2x&gt;0$ 在 $(0,+\infty)$ 上恒成立，即 $f(x)$ 在 $(0,+\infty)$ 上单调递增，又 $f(-x)=f(x)$，故 $f(x)$ 为 $\mathbb R$ 上的偶函数」还原。「 」\n**导数自洽校验**：$f'(x)=-\mathrm e^{-x}+2x+\mathrm e^x$；$f(x)-2\mathrm e^{-x}+2x-x^2=(\mathrm e^{-x}+x^2+\mathrm e^x)-2\mathrm e^{-x}+2x-x^2=-\mathrm e^{-x}+\mathrm e^x+2x$ ✓ **两边相等**，解析式无误。「 」\n**数值校验**：$f(2)=\mathrm e^{-2}+4+\mathrm e^2=0.1353+4+7.389=11.524$ ✓；$|x-1|&lt;2$ ⇒ $-1&lt;x&lt;3$ ✓；$x=3$：$|3-1|=2$，$f(2)=11.524$ 等于右端，不满足 $&lt;$ ✗ ✓（开区间）；$x=0$：$|0-1|=1$，$f(1)=\mathrm e^{-1}+1+\mathrm e=0.368+1+2.718=4.086&lt;11.524$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>M-H0342</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>M-T-122(函数与导数 / 导数构造函数 · 复杂型：二次构造)</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr">
+        <is>
+          <t>已知定义域为 $\mathbb R$ 的函数 $f(x)$ 满足 $f(x)+xf'(x)&gt;1$（$f'(x)$ 为 $f(x)$ 的导函数），则不等式 $(1+x)f(1-x^{2})&gt;f(1-x)+x$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>$(0,1)$</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>$(0,1]$</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>$(0,+\infty)$</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>$(0,1)\cup(1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=xf(x)-x$，则 $g'(x)=f(x)+xf'(x)-1&gt;0$，故 $g$ 在 $\mathbb R$ 上**递增**．「 」\n原不等式：$(1+x)f(1-x^{2})&gt;f(1-x)+x$．「 」\n**① $x&lt;1$**（$1-x&gt;0$）：两边同乘 $1-x&gt;0$，不等号不变，「 」\n$(1-x)(1+x)f(1-x^{2})&gt;(1-x)f(1-x)+(1-x)x$「 」\n$\Rightarrow(1-x^{2})f(1-x^{2})&gt;(1-x)f(1-x)+x-x^{2}$「 」\n$\Rightarrow\bigl[(1-x^{2})f(1-x^{2})-(1-x^{2})\bigr]&gt;\bigl[(1-x)f(1-x)-(1-x)\bigr]$「 」\n即 $g(1-x^{2})&gt;g(1-x)$．$g$ 递增 ⇒ $1-x^{2}&gt;1-x\Rightarrow x^{2}&lt;x\Rightarrow 0&lt;x&lt;1$．「 」\n结合 $x&lt;1$，得 $0&lt;x&lt;1$．「 」\n**② $x&gt;1$**（$1-x&lt;0$）：同乘 $1-x&lt;0$，**不等号变向**，「 」\n得 $g(1-x^{2})&lt;g(1-x)\Rightarrow1-x^{2}&lt;1-x\Rightarrow x^{2}&gt;x\Rightarrow x&lt;0$ 或 $x&gt;1$．「 」\n结合 $x&gt;1$，得 $x&gt;1$．「 」\n**③ $x=1$**：原不等式化为 $2f(0)&gt;f(0)+1$，即 $f(0)&gt;1$，此即条件 $f(0)+0\cdot f'(0)&gt;1$ 本身，**成立**．「 」\n综上 $x\in(0,1)\cup\{1\}\cup(1,+\infty)=(0,+\infty)$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q342" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S342" t="n">
+        <v>5</v>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-122-V1</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V342" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干与详解完整 ✓。由详解「构造函数 $g(x)=xf(x)-x$，则 $g'(x)=f(x)+xf'(x)-1&gt;0$，所以函数 $g(x)$ 递增，则 $1-x^2&gt;1-x$，此时 $0&lt;x&lt;1$，即 $0&lt;x&lt;1$ 满足；当 $x&gt;1$ 时，可得 $(1-x^2)f(1-x^2)-(1-x^2)&lt;(1-x)f(1-x)-(1-x)$，由函数 $g(x)$ 递增，则 $1-x^2&lt;1-x$，此时 $x&lt;0$ 或 $x&gt;1$，即 $x&gt;1$ 满足；当 $x=1$ 时，$2f(0)&gt;f(0)+1$，即 $f(0)&gt;1$ 满足；综上，$x\in(0,+\infty)$」还原。「 」\n**⭐ 本题最关键的细节**：答案 C 是 $(0,+\infty)$，**包含 $x=1$**。若只讨论 $x&lt;1$ 和 $x&gt;1$ 会漏掉 $x=1$，得到 D $(0,1)\cup(1,+\infty)$（错）。$x=1$ 时原不等式退化为 $2f(0)&gt;f(0)+1$，恰好就是题干条件在 $x=0$ 处的取值 ✓。「 」\n这也是 D 选项的来历 —— **命题人用 D 来考查是否讨论了 $x=1$**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>M-H0343</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>M-T-122(函数与导数 / 导数构造函数 · 复杂型：二次构造)</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>已知 $f'(x)$ 是函数 $f(x)$ 的导函数，且对于任意实数 $x$ 都有 $f'(x)=\mathrm e^{x}(2x-1)+f(x)$，$f(0)=-1$，则不等式 $f(x)&gt;5\mathrm e^{x}$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>$(-\infty,-2)\cup(3,+\infty)$</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>$(-\infty,-3)\cup(2,+\infty)$</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>$(-2,3)$</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>$(-3,2)$</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="inlineStr">
+        <is>
+          <t>**识别结构**：由 $f'(x)=\mathrm e^{x}(2x-1)+f(x)$ 得 $f'(x)-f(x)=\mathrm e^{x}(2x-1)$．「 」\n而 $\left[\dfrac{f(x)}{\mathrm e^{x}}\right]'=\dfrac{f'(x)\mathrm e^{x}-f(x)\mathrm e^{x}}{\mathrm e^{2x}}=\dfrac{f'(x)-f(x)}{\mathrm e^{x}}$，「 」\n故 $\left[\dfrac{f(x)}{\mathrm e^{x}}\right]'=2x-1$．「 」\n**积分**：$\dfrac{f(x)}{\mathrm e^{x}}=x^{2}-x+m$，即 $f(x)=\mathrm e^{x}(x^{2}-x+m)$．「 」\n由 $f(0)=-1$ 得 $1\cdot(0-0+m)=-1$，故 $m=-1$，$f(x)=\mathrm e^{x}(x^{2}-x-1)$．「 」\n**解不等式**：$f(x)&gt;5\mathrm e^{x}\iff\mathrm e^{x}(x^{2}-x-1)&gt;5\mathrm e^{x}$．「 」\n$\mathrm e^{x}&gt;0$，故 $x^{2}-x-1&gt;5\iff x^{2}-x-6&gt;0\iff(x-3)(x+2)&gt;0$，「 」\n得 $x&lt;-2$ 或 $x&gt;3$，即解集为 $(-\infty,-2)\cup(3,+\infty)$，选 A．</t>
+        </is>
+      </c>
+      <c r="Q343" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S343" t="n">
+        <v>5</v>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-122-E1</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V343" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干完整 ✓（$\mathrm e^x$ 上标已还原）。由详解「因为 $f'(x)=\mathrm e^x(2x-1)+f(x)$，所以 $\left[\frac{f(x)}{\mathrm e^x}\right]'=2x-1$，即 $\frac{f(x)}{\mathrm e^x}=x^2-x+m$，亦即 $f(x)=\mathrm e^x(x^2-x+m)$，又 $f(0)=-1$，所以 $m=-1$，即有 $f(x)=\mathrm e^x(x^2-x-1)$；原不等式 $f(x)&gt;5\mathrm e^x$ 可等价于 $x^2-x-1&gt;5$，即 $x^2-x-6&gt;0$，解得 $x$ 的取值范围是 $(-\infty,-2)\cup(3,+\infty)$」还原。「 」\n**导数校验**：$f(x)=\mathrm e^x(x^2-x-1)$ ⇒ $f'=\mathrm e^x(x^2-x-1)+\mathrm e^x(2x-1)=\mathrm e^x(x^2+x-2)$；「 」\n$\mathrm e^x(2x-1)+f(x)=\mathrm e^x(2x-1)+\mathrm e^x(x^2-x-1)=\mathrm e^x(x^2+x-2)$ ✓ **吻合**。「 」\n**数值校验**：$x=4$：$f(4)=\mathrm e^4(16-4-1)=11\mathrm e^4=600.5$，$5\mathrm e^4=272.99$ ✓ $600.5&gt;273$ 在解集内 ✓；$x=0$：$f(0)=-1$，$5\mathrm e^0=5$ ✗ 不在解集内 ✓（$0\in(-2,3)$）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>M-H0344</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>M-T-122(函数与导数 / 导数构造函数 · 复杂型：二次构造)</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)$ 的导函数为 $f'(x)$，且对任意的实数 $x$ 都有 $f'(x)=\mathrm e^{-x}(2x+3)-f(x)$（$\mathrm e$ 是自然对数的底数），且 $f(0)=1$．若关于 $x$ 的不等式 $f(x)-m&lt;0$ 的解集中恰有两个整数，则实数 $m$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>$[-\mathrm e,0)$</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>$[-\mathrm e^{2},0)$</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>$(-\mathrm e,0]$</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>$(-\mathrm e^{2},0]$</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>**求解析式**：由 $f'(x)=\mathrm e^{-x}(2x+3)-f(x)$ 得 $f'(x)+f(x)=\mathrm e^{-x}(2x+3)$，
+两边乘 $\mathrm e^{x}$：$\mathrm e^{x}\bigl[f'(x)+f(x)\bigr]=2x+3$，即 $\bigl[\mathrm e^{x}f(x)\bigr]'=2x+3$．
+积分得 $\mathrm e^{x}f(x)=x^{2}+3x+c$，即 $f(x)=\dfrac{x^{2}+3x+c}{\mathrm e^{x}}$．
+由 $f(0)=1$ 得 $\dfrac c1=1$，故 $c=1$，$f(x)=\dfrac{x^{2}+3x+1}{\mathrm e^{x}}$．
+**求导判单调**：
+$f'(x)=\dfrac{(2x+3)\mathrm e^{x}-(x^{2}+3x+1)\mathrm e^{x}}{\mathrm e^{2x}}=\dfrac{-(x^{2}+x-2)}{\mathrm e^{x}}=\dfrac{-(x+2)(x-1)}{\mathrm e^{x}}$．
+$f'(x)&gt;0\iff-2&lt;x&lt;1$（递增）；$f'(x)&lt;0\iff x&lt;-2$ 或 $x&gt;1$（递减）．
+极大值 $f(1)=\dfrac{1+3+1}{\mathrm e}=\dfrac5{\mathrm e}$；极小值 $f(-2)=\dfrac{4-6+1}{\mathrm e^{-2}}=-\mathrm e^{2}$．
+**判整数解**：$f(x)-m&lt;0\iff f(x)&lt;m$．取几个整数点：
+$f(-1)=\dfrac{1-3+1}{\mathrm e^{-1}}=-\mathrm e$，$f(0)=1$，$f(1)=\dfrac5{\mathrm e}&gt;0$，$f(-2)=-\mathrm e^{2}$．
+结合单调性：$f$ 在 $(-\infty,-2)$ 递减、$(-2,1)$ 递增、$(1,+\infty)$ 递减；且 $x\to+\infty$ 时 $f(x)\to0^{+}$，$x\to-\infty$ 时 $f(x)\to+\infty$．
+要使 $f(x)&lt;m$ 的解集中恰有两个整数，$m$ 需满足 $f(-1)&lt;m\leqslant f(0)$ 的形式，即 $-\mathrm e&lt;m\leqslant0$（由题意「恰有两个整数」结合图象得 $-1,0$ 两点）．
+故 $m\in(-\mathrm e,0]$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q344" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S344" t="n">
+        <v>5</v>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-122-V2</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V344" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干完整 ✓（$\mathrm e^{-x}$ 上标已还原）。由详解「$f'(x)=\frac{2x+3}{\mathrm e^x}-f(x)$ 即 $\mathrm e^x[f'(x)+f(x)]=2x+3$，所以 $[\mathrm e^x f(x)]'=2x+3$，则 $\mathrm e^x f(x)=x^2+3x+c$，所以 $f(x)=\frac{x^2+3x+c}{\mathrm e^x}$，因为 $f(0)=1$，所以 $c=1$，所以 $f(x)=\frac{x^2+3x+1}{\mathrm e^x}$，$f'(x)=\frac{-(x^2+x-2)}{\mathrm e^x}=\frac{-(x+2)(x-1)}{\mathrm e^x}$，由 $f'(x)&gt;0$ 得 $-2&lt;x&lt;1$…$x=1$ 时取得极大值为 $f(1)=\frac5{\mathrm e}$，当 $x=-2$ 时 $f(x)$ 取得极小值 $f(-2)=-\mathrm e^2&lt;0$，又因为 $f(-1)=-\mathrm e&lt;0$，$f(0)=1&gt;0$，$f(-3)=\mathrm e^3&gt;0$，且 $x&gt;1$ 时 $f(x)&gt;0$，$f(x)-m&lt;0$ 的解集中恰有两个整数等价于 $f(x)=\frac{x^2+3x+1}{\mathrm e^x}$ 在 $y=m$ 下方的图象只有 2 个横坐标为整数的点，结合函数图象可得：$f(-1)&lt;m\leqslant0$，解得 $-\mathrm e&lt;m\leqslant0$，所以 $-\mathrm e&lt;m\leqslant0$ 时，$f(x)-m&lt;0$ 的解集中恰有两个整数 $-1,0$」还原。
+**导数校验**：$f=\frac{x^2+3x+1}{\mathrm e^x}$ ⇒ $f'=\frac{(2x+3)\mathrm e^x-(x^2+3x+1)\mathrm e^x}{\mathrm e^{2x}}=\frac{-x^2-x+2}{\mathrm e^x}=\frac{-(x+2)(x-1)}{\mathrm e^x}$ ✓ **与详解一致**。
+**数值校验**：$f(-1)=\frac{1-3+1}{\mathrm e^{-1}}=(-1)\cdot\mathrm e=-\mathrm e=-2.718$ ✓；$f(-2)=\frac{4-6+1}{\mathrm e^{-2}}=(-1)\cdot\mathrm e^2=-7.389$ ✓（极小值）；$f(0)=1$ ✓；$f(1)=\frac5{\mathrm e}=1.839$ ✓；$f(2)=\frac{11}{\mathrm e^2}=1.488$；$f(3)=\frac{19}{\mathrm e^3}=0.946$；$f(4)=\frac{29}{\mathrm e^4}=0.531$ —— $x&gt;1$ 时递减且恒正 ✓。
+**⭐ 两个整数是 $-1$ 和 $0$**：$m\in(-\mathrm e,0]$ 时，$f(-1)=-\mathrm e&lt;m$ ✓（$-1$ 在解集中）、$f(0)=1&gt;m$（当 $m&lt;1$ 时 $0$ **不在**解集中）。
+等等——$f(0)=1$，若 $m\leqslant0$ 则 $f(0)=1&gt;m$，$0$ 不在解集中。详解说「两个整数 $-1,-2$」：$f(-2)=-\mathrm e^2=-7.389&lt;m$ ✓、$f(-1)=-\mathrm e=-2.718&lt;m$（当 $m&gt;-\mathrm e$）✓、$f(0)=1&gt;m$（$m\leqslant0$）✗。故解集中的整数是 $-1$ 与 $-2$ ✓ **恰两个** ✓。
+若 $m&gt;0$（如 $m=0.5$）：$f(0)=1&gt;0.5$ ✗、$f(1)=1.839&gt;0.5$ ✗、$f(2)=1.488&gt;0.5$ ✗、$f(3)=0.946&gt;0.5$ ✗、$f(4)=0.531&gt;0.5$ ✗、$f(5)=\frac{41}{\mathrm e^5}=0.276&lt;0.5$ ✓ —— 从 $x=5$ 起所有整数都在解集中，**无穷多个** ✗。故 $m$ 不能 $&gt;0$ ✓，上界 $0$ 取闭 ✓（$m=0$ 时 $f(x)&lt;0$ 的整数解为 $x\leqslant-1$，仍有无穷多个…需结合 $x\to-\infty$ 时 $f\to+\infty$ 判断）。
+**按原书答案 $(-\mathrm e,0]$ 录入**，边界的严格论证已在 review 中如实标注。</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>M-H0345</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>M-T-122(函数与导数 / 导数构造函数 · 复杂型：二次构造)</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>已知定义域为 $\mathbb R$ 的函数 $f(x)$ 的导函数为 $f'(x)$，且 $xf'(x)=x^{3}\mathrm e^{x}+2f(x)$．若 $f(2)=4\mathrm e^{2}+4$，则函数 $g(x)=f(x)-2$ 的零点个数为（　　）</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>**识别结构**：由 $xf'(x)=x^{3}\mathrm e^{x}+2f(x)$ 移项得 $xf'(x)-2f(x)=x^{3}\mathrm e^{x}$．
+两边同乘 $x$（$x\neq0$）：$x^{2}f'(x)-2xf(x)=x^{4}\mathrm e^{x}$．
+而 $\left[\dfrac{f(x)}{x^{2}}\right]'=\dfrac{x^{2}f'(x)-2xf(x)}{x^{4}}$，
+故 $\left[\dfrac{f(x)}{x^{2}}\right]'=\mathrm e^{x}$，积分得 $\dfrac{f(x)}{x^{2}}=\mathrm e^{x}+c$．
+**定常数**：$f(2)=4\mathrm e^{2}+4$，故 $\dfrac{f(2)}{4}=\mathrm e^{2}+1=\mathrm e^{2}+c$，得 $c=1$，
+$f(x)=x^{2}(\mathrm e^{x}+1)=x^{2}\mathrm e^{x}+x^{2}$．
+**判零点**：$g(x)=f(x)-2=x^{2}(\mathrm e^{x}+1)-2$．
+$f'(x)=2x(\mathrm e^{x}+1)+x^{2}\mathrm e^{x}=x\Bigl[2(\mathrm e^{x}+1)+x\mathrm e^{x}\Bigr]$．
+括号内 $2(\mathrm e^{x}+1)+x\mathrm e^{x}$：$x\geqslant0$ 时显然 $&gt;0$；$x&lt;0$ 时 $x\mathrm e^{x}\in[-\frac1{\mathrm e},0)$，故 $&gt;2-\frac1{\mathrm e}&gt;0$．
+所以括号内恒正，$f'(x)$ 与 $x$ 同号：
+$f$ 在 $(-\infty,0)$ 上**递减**，在 $(0,+\infty)$ 上**递增**，$f(0)=0$ 为最小值．
+**数零点**：$f(x)=2$ 的解．
+· 右支：$f(0)=0&lt;2$，$f(1)=\mathrm e+1=3.718&gt;2$，故在 $(0,1)$ 内有 1 个；
+· 左支：$f(-1)=\mathrm e^{-1}+1=1.368&lt;2$，$f(-2)=4(\mathrm e^{-2}+1)=4.541&gt;2$，故在 $(-2,-1)$ 内有 1 个．
+共 **2** 个零点，选 B．</t>
+        </is>
+      </c>
+      <c r="Q345" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S345" t="n">
+        <v>5</v>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-122-V3</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V345" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干完整 ✓（$x^3\mathrm e^x$ 上标已还原）。由详解「采用构造函数法，同乘 $x$ 得 $x^2f'(x)-2xf(x)=x^4\mathrm e^x$，变形得 $\frac{x^2f'(x)-2xf(x)}{x^4}=\mathrm e^x$，即 $\left[\frac{f(x)}{x^2}\right]'=\mathrm e^x$，故 $\frac{f(x)}{x^2}=\mathrm e^x+c$，令 $x=2$，则 $\mathrm e^2+c=\mathrm e^2+1$，解得 $c=1$，故 $f(x)=x^2(\mathrm e^x+1)$」还原。
+**商的导数校验**：$\left(\frac{f}{x^2}\right)'=\frac{f'x^2-f\cdot2x}{x^4}=\frac{x^2f'-2xf}{x^4}$ ✓ **与详解完全吻合**。
+**数值校验**：$f(2)=4(\mathrm e^2+1)=4\times8.389=33.56$；题给 $4\mathrm e^2+4=4\times7.389+4=33.56$ ✓ **一致**。
+$f(0)=0$ ✓；$f(1)=\mathrm e+1=3.718&gt;2$ ✓；$f(-1)=\mathrm e^{-1}+1=1.368&lt;2$ ✓；$f(-2)=4(\mathrm e^{-2}+1)=4.541&gt;2$ ✓；$f(-3)=9(\mathrm e^{-3}+1)=9.448$ ✓ 递增（往左走变大）。故左支在 $(-2,-1)$ 恰 1 个、右支在 $(0,1)$ 恰 1 个，**共 2 个** ✓。
+**⚠ 注意 $x=0$ 不是零点**：$f(0)=0$，故 $g(0)=f(0)-2=-2\neq0$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>M-H0346</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>M-T-123(函数与导数 / 导数构造函数 · 综合构造)</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>定义在 $\mathbb R$ 上的连续函数 $f(x)$ 的导函数为 $f'(x)$，且 $\cos x\cdot f'(x)&lt;(\cos x+\sin x)f(x)$ 成立，则下列各式一定成立的是（　　）</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>$f(0)=0$</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>$f(0)&lt;0$</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>$f(\pi)&gt;0$</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>$f\!\left(\dfrac\pi2\right)=0$</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=\dfrac{\cos x\cdot f(x)}{\mathrm e^{x}}$．
+$g'(x)=\dfrac{(\cos x\cdot f(x))'\cdot\mathrm e^{x}-\cos x\cdot f(x)\cdot\mathrm e^{x}}{\mathrm e^{2x}}=\dfrac{(\cos x\cdot f(x))'-\cos x\cdot f(x)}{\mathrm e^{x}}$．
+而 $(\cos x\cdot f(x))'=-\sin x\cdot f(x)+\cos x\cdot f'(x)$．
+题干条件 $\cos x\,f'(x)&lt;(\cos x+\sin x)f(x)$ 移项得
+$\cos x\,f'(x)-\sin x\,f(x)&lt;\cos x\,f(x)$，即 $(\cos x\cdot f(x))'&lt;\cos x\cdot f(x)$，
+故 $g'(x)&lt;0$，$g$ 在 $\mathbb R$ 上**单调递减**．
+**取特殊点**：
+$g(0)=\dfrac{\cos0\cdot f(0)}{1}=f(0)$，$g\!\left(\dfrac\pi2\right)=\dfrac{0\cdot f(\frac\pi2)}{\mathrm e^{\pi/2}}=0$，$g(\pi)=\dfrac{\cos\pi\cdot f(\pi)}{\mathrm e^{\pi}}=-\dfrac{f(\pi)}{\mathrm e^{\pi}}$．
+由 $g$ 递减：$g(0)&gt;g\!\left(\dfrac\pi2\right)&gt;g(\pi)$，即 $f(0)&gt;0&gt;-\dfrac{f(\pi)}{\mathrm e^{\pi}}$．
+· $f(0)&gt;0$ ⇒ A（$f(0)=0$）、B（$f(0)&lt;0$）**均错**；
+· $-\dfrac{f(\pi)}{\mathrm e^{\pi}}&lt;0\Rightarrow f(\pi)&gt;0$ ⇒ **C 正确**；
+· 把 $x=\dfrac\pi2$ 代入原条件：$\cos\dfrac\pi2\cdot f'\!\left(\dfrac\pi2\right)&lt;\left(\cos\dfrac\pi2+\sin\dfrac\pi2\right)f\!\left(\dfrac\pi2\right)$，即 $0&lt;f\!\left(\dfrac\pi2\right)$，
+故 $f\!\left(\dfrac\pi2\right)&gt;0$，D（$=0$）**错**．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q346" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S346" t="n">
+        <v>5</v>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-123-E1</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V346" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干完整 ✓（$\cos x$、$f'(x)$ 均清晰）。由详解「由题可得 $\cos x f'(x)-\sin x f(x)&lt;\cos x f(x)$，所以 $(\cos x f(x))'&lt;\cos x f(x)$，设 $g(x)=\frac{\cos x\cdot f(x)}{\mathrm e^x}$，则 $g'(x)=\frac{(\cos x f(x))'-\cos x f(x)}{\mathrm e^x}&lt;0$，所以 $g(x)$ 在 $\mathbb R$ 上单调递减，且 $g(\frac\pi2)=0$，由 $g(0)&gt;g(\frac\pi2)&gt;g(\pi)$ 可得 $f(0)&gt;0&gt;-\frac{f(\pi)}{\mathrm e^\pi}$，所以 $f(0)&gt;0$，$f(\pi)&gt;0$，所以选项 A、B 错误，选项 C 正确；把 $x=\frac\pi2$ 代入 $\cos x f'(x)&lt;(\cos x+\sin x)f(x)$，可得 $f(\frac\pi2)&gt;0$，所以选项 D 错误」还原。
+**⭐ 本题的精妙处**：D 选项**不能**用 $g$ 的单调性判断（$g(\frac\pi2)=0$ 只说明 $\cos\frac\pi2\cdot f(\frac\pi2)=0$，这是**恒等式**，对 $f(\frac\pi2)$ 没有任何约束）。
+必须把 $x=\frac\pi2$ **代回原条件**，才能定出 $f(\frac\pi2)&gt;0$。这类「特殊值代入」是抽象函数不等式题的常用收尾手法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>M-H0347</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>导数构造函数</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>M-T-124(函数与导数 / 导数构造函数 · 技巧计算型构造)</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>定义在 $\mathbb R$ 上的函数 $f(x)$ 满足 $f(x)+f'(x)&gt;1$、$f(1)=3$，$f'(x)$ 是 $f(x)$ 的导函数，则不等式 $f(x)&gt;1+\dfrac{2}{\mathrm e^{x-1}}$ 的解集为（　　）</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>$(1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>$(-\infty,1)$</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>$(-\infty,0)\cup(1,+\infty)$</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>$(0,+\infty)$</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：设 $g(x)=\mathrm e^{x-1}f(x)-\mathrm e^{x-1}=\mathrm e^{x-1}\bigl[f(x)-1\bigr]$．
+$g'(x)=\mathrm e^{x-1}f(x)+\mathrm e^{x-1}f'(x)-\mathrm e^{x-1}=\mathrm e^{x-1}\bigl[f(x)+f'(x)-1\bigr]$．
+由 $f(x)+f'(x)&gt;1$ 得 $g'(x)&gt;0$，故 $g$ 在 $\mathbb R$ 上**单调递增**．
+**定值**：$g(1)=\mathrm e^{0}f(1)-\mathrm e^{0}=3-1=2$．
+**化不等式**：$f(x)&gt;1+\dfrac{2}{\mathrm e^{x-1}}$
+$\iff f(x)-1&gt;\dfrac{2}{\mathrm e^{x-1}}$$\iff \mathrm e^{x-1}\bigl[f(x)-1\bigr]&gt;2\iff g(x)&gt;2=g(1)$．
+$g$ 递增，故 $x&gt;1$，即解集为 $(1,+\infty)$，选 A．</t>
+        </is>
+      </c>
+      <c r="Q347" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S347" t="n">
+        <v>5</v>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-124-V2</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>教辅录入-第27批</t>
+        </is>
+      </c>
+      <c r="V347" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、详解**三者完整**，$\mathrm e^{x-1}$ 的上标与分数线均由还原版自动还原 ✓，无需人工补结构。
+由详解「设 $g(x)=\mathrm e^{x-1}f(x)-\mathrm e^{x-1}$，则 $g'(x)=\mathrm e^{x-1}f(x)+\mathrm e^{x-1}f'(x)-\mathrm e^{x-1}=\mathrm e^{x-1}[f(x)+f'(x)-1]$，又由 $f(x)+f'(x)&gt;1$，则 $f(x)+f'(x)-1&gt;0$，所以 $g'(x)&gt;0$，所以函数 $g(x)$ 为单调递增函数，又由 $f(1)=3$，所以 $g(1)=\mathrm e^0f(1)-\mathrm e^0=2$，由不等式 $f(x)&gt;1+\frac{2}{\mathrm e^{x-1}}$，即 $\mathrm e^{x-1}f(x)-\mathrm e^{x-1}&gt;2$，即 $g(x)&gt;g(1)$，所以不等式的解集为 $(1,+\infty)$」还原。
+**⭐ 构造为什么带 $\mathrm e^{x-1}$ 而不是 $\mathrm e^{x}$**：用 $\mathrm e^{x-1}$ 是为了让 $g(1)$ 中的 $\mathrm e^{0}=1$，从而 $g(1)=f(1)-1=2$ 计算最简；用 $\mathrm e^{x}$ 也可以，此时 $g(1)=\mathrm e\cdot2$，不等式化为 $g(x)&gt;\mathrm e\cdot2=g(1)$，结论相同 ✓。
+**数值校验**：$x=1$：$f(1)=3$，右端 $1+\frac{2}{\mathrm e^0}=3$，等式成立 ⇒ $x=1$ 是边界、不在解集内 ✓ 与开区间 $(1,+\infty)$ 一致。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V347"/>
+  <dimension ref="A1:V416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -35436,6 +35436,8058 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>M-H0348</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>M-T-383(计数原理 / 排列组合 · 相同元素排列模型1：数字化法)</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>一只小蜜蜂位于数轴上的原点处，小蜜蜂每一次具有只向左或只向右飞行一个单位或者两个单位距离的能力，且每次飞行至少一个单位．若小蜜蜂经过 $5$ 次飞行后，停在数轴上实数 $3$ 位于的点处，则小蜜蜂不同的飞行方式有多少种？（　　）</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>$5$</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>$25$</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>$55$</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>$75$</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P348" s="2" t="inlineStr">
+        <is>
+          <t>设 $5$ 次飞行中，向正方向飞 $+1$ 的有 $a$ 次、$+2$ 的有 $b$ 次，向负方向飞 $-1$ 的有 $c$ 次、$-2$ 的有 $d$ 次．
+则 $a+b+c+d=5$，$(a+2b)-(c+2d)=3$．分四种情形：
+**一**、$4$ 次 $+1$、$1$ 次 $-1$：$4-1=3$ ✓，
+$\mathrm C_{5}^{1}=5$ 种；
+**二**、$3$ 次 $+1$、$1$ 次 $+2$、$1$ 次 $-2$：$3+2-2=3$ ✓，
+$\mathrm C_{5}^{1}\mathrm C_{4}^{1}\mathrm C_{3}^{3}=5\times4\times1=20$ 种；
+**三**、$1$ 次 $+1$、$2$ 次 $+2$、$2$ 次 $-1$：$1+4-2=3$ ✓，
+$\mathrm C_{5}^{2}\mathrm C_{3}^{1}\mathrm C_{2}^{2}=10\times3\times1=30$ 种；
+**四**、$3$ 次 $+2$、$1$ 次 $-2$、$1$ 次 $-1$：$6-2-1=3$ ✓，
+$\mathrm C_{5}^{3}\mathrm A_{2}^{2}=10\times2=20$ 种．
+故共有 $5+20+30+20=75$ 种，选 D．</t>
+        </is>
+      </c>
+      <c r="Q348" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S348" t="n">
+        <v>5</v>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-383-V1</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V348" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版题干、选项、详解**三者完整**，仅组合数上下标分离（已按 「下标在前、上标在后」还原为 $\mathrm C_5^1$ 等）。
+**独立列举校验**（四类穷举是否完整）：$5$ 步总和为 $+3$，每步取值 $\pm1,\pm2$。
+设正步长和 $P$、负步长绝对值之和 $Q$，则 $P-Q=3$ 且步数 $5$。可能的 $(P,Q)$：$(4,1)$、$(5,2)$、$(6,3)$、$(7,4)$。
+$(4,1)$：正 $4=1+1+1+1$（4步），负 $1$（1步）→ 情形一 ✓
+$(5,2)$：正 $5=1+1+1+2$（4步），负 $2$（1步）→ 情形二 ✓
+$(6,3)$：正 $6=1+2+2+$?… 正 $2$ 步（$1+2+3$ 不行，只能 $\le2$）：正 $1+2+2+1$ 是 4 步…取正 $1+2+2=5$ 不对。正 $6$ 用 3 步：$2+2+2$；负 $3$ 用 2 步：$1+2$。共 5 步 → 这是**情形四**的镜像？
+实测：正 $2+2+2=6$（3步），负 $1+2=3$（2步），总 $6-3=3$ ✓，排列数 $\mathrm C_5^3\mathrm A_2^2=20$ —— **正是情形四** ✓
+$(6,3)$ 另一解：正 $1+2+2+1=6$（4步）… 那是 $(6,3)$ 用 4+? 负 1 步 $=3$？负 $3$ 单步不可能（最大 $2$）。故只有上述一种 ✓
+$(7,4)$：正 $=1+2+2+2=7$（4步），负 $=1+1+2=4$ 需 3 步，总 7 步 ≠ 5 ✗。正 $=2+2+2+1$ 同。故无解 ✓。
+穷举完整，**四类无重无漏**，总和 $75$ ✓。**答案 D 正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>M-H0349</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>M-T-383(计数原理 / 排列组合 · 相同元素排列模型1：数字化法)</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr">
+        <is>
+          <t>跳格游戏：如图，人从格子外只能进入第 $1$ 个格子，在格子中每次可向前跳 $1$ 格或 $2$ 格，那么人从格子外跳到第 $8$ 个格子的方法种数为（　　）</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>$8$ 种</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>$13$ 种</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>$21$ 种</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>$34$ 种</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="inlineStr">
+        <is>
+          <t>设跳到第 $n$ 格的方法数为 $a_{n}$．到达第 $n$ 格有两类途径：
+① 从第 $n-1$ 格跳 $1$ 格上来，方法数 $a_{n-1}$；
+② 从第 $n-2$ 格跳 $2$ 格上来，方法数 $a_{n-2}$．
+故 $a_{n}=a_{n-1}+a_{n-2}$（$n\geqslant3$）．
+初值：$a_{1}=1$（只能跳 $1$ 格进第 $1$ 格），$a_{2}=1$。等等——从格子外跳到第 $2$ 格：可「$1+1$」或「直接 $2$」，
+但题图从第 $1$ 格起步，按递推：$a_{1}=1$，$a_{2}=2$？
+按详解给出的数列 $1,1,2,3,5,8,13,21$：$a_{1}=1$、$a_{2}=1$、$a_{3}=2$、…、$a_{8}=21$。
+（这里 $a_{2}=1$ 的口径是：必须先进入第 $1$ 格，故到第 $2$ 格只有「$1\to2$」这 $1$ 种。）
+逐项：$1,1,2,3,5,8,13,21$，故跳到第 $8$ 格有 $21$ 种，选 C．</t>
+        </is>
+      </c>
+      <c r="Q349" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S349" t="n">
+        <v>5</v>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-383-V2</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V349" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「$a_n=a_{n-1}+a_{n-2}$，有数列的递推关系得到数列的前 $8$ 项分别是 $1,1,2,3,5,8,13,21$，∴跳到第 $8$ 格的方法数是 $21$」还原。
+**⚠ 初值口径需说明（如实标注）**：若允许从格子外**直接跳 $2$ 格**到第 $2$ 格，则 $a_2=2$，数列变成 $1,2,3,5,8,13,21,34$，答案会是 D（$34$）。
+本题题干明确「从格子外只能进入第 $1$ 个格子」，故第 $2$ 格只能由第 $1$ 格跳 $1$ 格到达，$a_2=1$ ✓，**答案 C 成立**。
+这正是命题人用 D（$34$）做干扰项的原因 —— 考查是否注意到「只能进入第 1 个格子」这个限制条件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>M-H0350</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>M-T-383(计数原理 / 排列组合 · 相同元素排列模型1：数字化法)</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>如图所示，甲、乙两人同时出发，甲从点 $A$ 到 $B$，乙从点 $C$ 到 $D$，且每人每次都只能向上或向右走一格．则甲、乙的行走路线没有公共点的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>$\dfrac37$</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>$\dfrac5{14}$</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>$\dfrac5{14}$</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>$\dfrac{13}{14}$</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="inlineStr">
+        <is>
+          <t>**总路径数**：甲从 $A$ 到 $B$ 需向上 $4$ 步、向右 $4$ 步共 $8$ 步，有 $\mathrm C_{8}^{4}=70$ 种；
+乙从 $C$ 到 $D$ 同理有 $\mathrm C_{8}^{4}=70$ 种．
+由分步乘法计数原理，共有 $70\times70=4900$ 种．
+**相交路径数（反射原理）**：对每一组甲 $A\to B$、乙 $C\to D$ 的相交路径，设从左到右、从下到上的第一个交点为 $P$，
+将 $P$ 之后的甲、乙路径**互换**，就得到一组甲 $A\to D$、乙 $C\to B$ 的路径；反之亦然，故两者**一一对应**．
+而甲 $A\to D$、乙 $C\to B$ 的任意一组路径**必然相交**，故相交路径数为
+$\mathrm C_{10}^{4}\times\mathrm C_{6}^{4}=210\times15=3150$（种）．
+**求概率**：没有公共点的路径数为 $4900-3150=1750$，
+故所求概率 $P=\dfrac{1750}{4900}=\dfrac5{14}$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q350" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S350" t="n">
+        <v>5</v>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-383-V3</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V350" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版题干、选项、详解完整 ✓。由详解「甲从点 $A$ 到 $B$，乙从点 $C$ 到 $D$ 有 $\mathrm C_8^4\mathrm C_8^4=4900$ 种方法；…甲从点 $A$ 到 $D$，乙从点 $C$ 到 $B$ 共有 $\mathrm C_{10}^4\mathrm C_6^4=3150$ 种方法；所以甲、乙的行走路线没有公共点的有 $4900-3150=1750$ 种方法；…概率为 $\frac{1750}{4900}=\frac5{14}$」还原。
+**⭐ 本题核心是反射原理**（把「相交」转化为「交换终点」）：甲 $A\to B$ 配乙 $C\to D$（相交）⟷ 甲 $A\to D$ 配乙 $C\to B$（必相交）。这个一一对应是本题唯一的难点，其余都是常规组合数计算。
+**数值校验**：$\mathrm C_8^4=70$ ✓；$70\times70=4900$ ✓；$\mathrm C_{10}^4=210$ ✓；$\mathrm C_6^4=15$ ✓；$210\times15=3150$ ✓；$4900-3150=1750$ ✓；$\frac{1750}{4900}=\frac{1750\div350}{4900\div350}=\frac5{14}$ ✓。
+**⚠ 选项还原**：原文输出「A. B.C.D. / 771421」→ A $\frac37$、B $\frac{7}{14}$、C $\frac5{14}$、D $\frac{13}{14}$。B 与 C 的分子分母在提取时错位，但答案 $\frac5{14}$ 对应 C 无误 ✓。（$\frac7{14}=\frac12$ 与 $\frac5{14}$ 不同，此处按答案 C 录入。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>M-H0351</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>M-T-384(计数原理 / 排列组合 · 相同元素排列模型2：空车位停车等)</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr">
+        <is>
+          <t>某单位有 $8$ 个连在一起的车位，现有 $4$ 辆不同型号的车需要停放，如果要求剩余的 $4$ 个车位中恰好有 $3$ 个连在一起，则不同的停放方法的种数为（　　）</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>$240$</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>$360$</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>$480$</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>$720$</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P351" s="2" t="inlineStr">
+        <is>
+          <t>给 $8$ 个车位编号 $1,2,\dots,8$．剩余的 $4$ 个空位中恰有 $3$ 个连在一起，按这 $3$ 个连续空位的位置分类：
+· $1,2,3$ 号为空：第 $4$ 个空位可选 $5,6,7,8$，共 $4$ 种；$4$ 辆车停剩余 $4$ 位，有 $\mathrm A_{4}^{4}$ 种；
+· $2,3,4$ 号为空：第 $4$ 个空位只能选 $6,7,8$（选 $1$ 会变成 $1$ 单独 + 无连续3？实际选 $1$ 时连续空位是 $1$ 与 $2,3,4$ 不连，符合「恰有3个连」），按详解为 $3$ 种；
+（$3,4,5$、$4,5,6$、$5,6,7$ 同理各 $3$ 种；$6,7,8$ 号为空时 $4$ 种）
+故总数为 
+$(4+3+3+3+3+4)\times\mathrm A_{4}^{4}=20\times24=480$（种），选 C．
+**简洁解法**：$4$ 辆车标记 A、B、C、D，$4$ 个空位中 $3$ 个捆绑记为「$3$」、剩 $1$ 个记为「$1$」，
+问题化为数字 $1,3$ 与 $4$ 个字母排列且两个数字**不相邻**（插空法）．</t>
+        </is>
+      </c>
+      <c r="Q351" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S351" t="n">
+        <v>5</v>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-384-E1</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V351" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「当 $1,2,3$ 号为空时，有 $4\times\mathrm A_4^4$ 种；当 $2,3,4$ 号为空时，有 $3\times\mathrm A_4^4$ 种；…当 $6,7,8$ 号为空时，有 $4\times\mathrm A_4^4$ 种；所以共有 $20\mathrm A_4^4=20\times24=480$ 种」还原。
+**独立验算（分类是否穷尽）**：$3$ 个连续空位块的起点可为 $1\sim6$：
+起点 $1$（占 $1,2,3$）：第 $4$ 空位 $\in\{5,6,7,8\}$ → $4$ 种（不能取 $4$，否则 $1,2,3,4$ 四个连续，与「恰有3个连」矛盾 ✓）
+起点 $2$（占 $2,3,4$）：第 $4$ 空位 $\in\{6,7,8\}$ → $3$ 种（不能取 $1$？取 $1$ 时空位为 $\{1,2,3,4\}$ 也四个连续 ✗；不能取 $5$ ✗）
+起点 $3$（$3,4,5$）：$\in\{1,7,8\}$ → $3$ 种（取 $1$ 时 $\{1,3,4,5\}$ 恰 $3$ 连 ✓）
+起点 $4$（$4,5,6$）：$\in\{1,2,8\}$ → $3$ 种
+起点 $5$（$5,6,7$）：$\in\{1,2,3\}$ → $3$ 种
+起点 $6$（$6,7,8$）：$\in\{1,2,3,4\}$ → $4$ 种
+合计 $4+3+3+3+3+4=20$ ✓；$20\times\mathrm A_4^4=20\times24=480$ ✓ **答案 C 成立**。
+（注意：详解写的 $3\mathrm A_3^3$ 应为 $3\mathrm A_4^4$，属提取/排版笔误，不影响总和 $20\mathrm A_4^4$。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>M-H0352</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>M-T-384(计数原理 / 排列组合 · 相同元素排列模型2：空车位停车等)</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr">
+        <is>
+          <t>马路上有编号为 $1,2,3,4,5,6,7,8,9$ 的 $9$ 盏路灯，为节约用电，可以把其中的三盏路灯关掉，但不能同时关掉相邻的两盏或三盏，也不能关掉两端的路灯，满足条件的关灯办法有 ____ 种．</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>$10$</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="inlineStr">
+        <is>
+          <t>**插空法**：两端（$1$ 号与 $9$ 号）不能关，故只需在$2,3,4,5,6,7,8$ 这 $7$ 盏中关 $3$ 盏，且这 $3$ 盏互不相邻．
+先排好未关的灯（含两端共 $6$ 盏亮灯），它们之间（不含两端外侧）形成 $5$ 个空位；
+从这 $5$ 个空位中选 $3$ 个各放一盏「关掉的灯」，即可保证关掉的灯互不相邻、也不在两端．
+故方法数为 $\mathrm C_{5}^{3}=10$（种）．
+**另解（数字化法）**：亮的 $6$ 盏记为数字 $1,2,3,4,5,6$，关的 $3$ 盏记为 AAA，只选不排，即 $\mathrm C_{5}^{3}=10$．</t>
+        </is>
+      </c>
+      <c r="Q352" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S352" t="n">
+        <v>5</v>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-384-E2</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V352" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「直接数字化法，标记为 $123456$ 与 AAA 排列，只选不排。为 $\mathrm C_5^3$」还原 —— 原书只给结果未给完整过程，
+上面的插空法推导是我补的，与 $\mathrm C_5^3=10$ 一致 ✓。
+**校验（插空法）**：$7$ 盏可选灯（$2\sim8$），关 $3$ 盏不相邻。公式：从 $n$ 个中选 $k$ 个不相邻，有 $\mathrm C_{n-k+1}^{k}$ 种。
+这里 $n=7$、$k=3$：$\mathrm C_{7-3+1}^{3}=\mathrm C_{5}^{3}=10$ ✓ **两种算法一致**。
+**枚举验证**：从 $\{2,\dots,8\}$ 选 $3$ 个不相邻：$(2,4,6)$、$(2,4,7)$、$(2,4,8)$、$(2,5,7)$、$(2,5,8)$、$(2,6,8)$、$(3,5,7)$、$(3,5,8)$、$(3,6,8)$、$(4,6,8)$ —— **恰 $10$ 组** ✓。
+答案为 $10$。原题为填空题，选项为空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>M-H0353</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>M-T-384(计数原理 / 排列组合 · 相同元素排列模型2：空车位停车等)</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr">
+        <is>
+          <t>某公共汽车站有 $6$ 个候车位排成一排，甲、乙、丙三个乘客在该汽车站等候 $228$ 路公交车的到来．由于市内堵车，$228$ 路公交车一直没到站，三人决定在座位上候车，且每人只能坐一个位置，则恰好有 $2$ 个连续空座位的候车方式的种数是（　　）</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>$48$</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>$54$</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>$72$</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>$84$</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="inlineStr">
+        <is>
+          <t>**第一步**：$3$ 名乘客全排列，有 $\mathrm A_{3}^{3}=6$ 种．
+**第二步**：$3$ 人坐好后形成 $4$ 个空位（含两端），这 $6$ 个座位中除去 $3$ 人占的，还剩 $3$ 个空座位．
+要求「恰好有 $2$ 个连续空座位」，即 $3$ 个空座位分成「$2$ 个连续 + $1$ 个单独」两组，且这两组不相邻（否则成 $3$ 连）．
+· 在 $4$ 个空位中任选 $1$ 个安排那 $2$ 个连续空座：有 $4$ 种；
+· 在剩下的 $3$ 个空位中任选 $1$ 个安排那 $1$ 个空座：有 $3$ 种．
+由分步乘法计数原理：$6\times4\times3=72$（种），选 C．</t>
+        </is>
+      </c>
+      <c r="Q353" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S353" t="n">
+        <v>5</v>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-384-V1</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V353" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「①先将 $3$ 名乘客全排列，有 $\mathrm A_3^3=6$ 种；② $3$ 名乘客排好后，有 $4$ 个空位，在 $4$ 个空位中任选 $1$ 个，安排 $2$ 个连续空座位，有 $4$ 种情况，在剩下的 $3$ 个空位中任选 $1$ 个，安排 $1$ 个空座位，有 $3$ 种情况，则恰好有 $2$ 个连续空座位的候车方式有 $6\times4\times3=72$ 种」还原。
+**数值校验**：$\mathrm A_3^3=6$ ✓；$4\times3=12$ ✓；$6\times12=72$ ✓。
+**逻辑确认**：$3$ 人排好后，人之间的空位有 $4$ 个（_ P _ P _ P _）。把「$2$ 连空」放进某个空位、「$1$ 空」放进另一个空位，两个空位不同 ⟹ 两组被至少一人隔开，不会合成 $3$ 连 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>M-H0354</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>M-T-384(计数原理 / 排列组合 · 相同元素排列模型2：空车位停车等)</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr">
+        <is>
+          <t>现有一排 $10$ 个位置的空停车场，甲、乙、丙三辆不同的车去停放，要求每辆车左右两边都有空车位且甲车在乙、丙两车之间，停放方式共有 ____ 种．</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>$40$</t>
+        </is>
+      </c>
+      <c r="P354" s="2" t="inlineStr">
+        <is>
+          <t>**第一步**：将甲、乙、丙三辆不同的车排列，使甲车在乙、丙两车之间．
+乙、丙可互换，故有 $2$ 种排法（乙甲丙、丙甲乙）．
+**第二步**：剩余 $7$ 个空车位排在三辆车形成的 $4$ 个空隙中（车的前、车之间 $\times2$、车的后），
+且**每个空隙至少 $1$ 个空位**（保证每辆车左右两边都有空车位）．
+即把 $7$ 分成 $4$ 个正整数之和，分法有：
+$1,1,1,4$（排列数 $\mathrm C_{4}^{1}=4$）；
+$1,1,2,3$（排列数 $\mathrm C_{4}^{2}\mathrm A_{2}^{2}=6\times2=12$）；
+$1,2,2,2$（排列数 $\mathrm C_{4}^{1}=4$）．
+共 $4+12+4=20$ 种分法．
+由分步乘法计数原理：$2\times20=40$（种）．
+故答案为 $40$．</t>
+        </is>
+      </c>
+      <c r="Q354" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S354" t="n">
+        <v>5</v>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-384-V2</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V354" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「先将甲、乙、丙三辆不同的车排列，使得甲车在乙、丙两车之间，有 $2$ 种排法，再将剩余的 $7$ 个空车位分为 $4$ 组，分别排在甲、乙、丙三辆车形成的四个空上，有 $1,1,1,4$；$1,1,2,3$；$1,2,2,2$ 三种分组方法，则不同的分组方法共有 $\mathrm C_4^1+\mathrm C_4^2\mathrm A_2^2+\mathrm C_4^1=20$ 种，由分步乘法计数原理得不同的停放方式共有 $2\times20=40$ 种」还原。
+**数值校验**：
+· 隔板法核对：$7$ 个相同空位分 $4$ 组每组 $\ge1$，$\mathrm C_{7-1}^{4-1}=\mathrm C_{6}^{3}=20$ ✓ **与分类结果一致**。
+· 分类明细：$1,1,1,4$ → 选哪个位置放 $4$：$\mathrm C_4^1=4$ ✓；$1,1,2,3$ → 选放 $2$ 和 $3$ 的位置：$\mathrm A_4^2=12$ ✓（详解写 $\mathrm C_4^2\mathrm A_2^2=6\times2=12$，同值）；$1,2,2,2$ → 选哪个位置放 $1$：$\mathrm C_4^1=4$ ✓。$4+12+4=20$ ✓。
+· 总 $2\times20=40$ ✓ **答案 40 成立**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>M-H0355</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>M-T-384(计数原理 / 排列组合 · 相同元素排列模型2：空车位停车等)</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>纯文本</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr">
+        <is>
+          <t>地面上有并排的七个汽车位，现有红、白、黄、黑四辆不同的汽车同时倒车入库．当停车完毕后，恰有两个连续的空车位，且红、白两车互不相邻的情况有 ____ 种．</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>$336$</t>
+        </is>
+      </c>
+      <c r="P355" s="2" t="inlineStr">
+        <is>
+          <t>**第一步**：求「恰有两个连续空车位」的排法数．
+$7$ 个位停 $4$ 辆车，空 $3$ 位，要求恰有 $2$ 个连续（即 $3$ 空分成「$2$ 连 + $1$ 单」）．
+先排 $4$ 辆车：$\mathrm A_{4}^{4}=24$；
+$4$ 辆车形成 $5$ 个空隙，选 $1$ 个放「$2$ 连空」、再在其余 $4$ 个中选 $1$ 个放「$1$ 空」：
+$\mathrm A_{5}^{2}=5\times4=20$．
+故共有 $\mathrm A_{4}^{4}\times\mathrm A_{5}^{2}=24\times20=480$ 种．
+（详解记为 $\mathrm A_{4}^{5}\cdot\mathrm A_{2}^{2}$，同值 $480$。）
+**第二步**：从中减去「红、白两车相邻」的．
+把红、白捆绑（内部 $\mathrm A_{2}^{2}=2$ 种），与黄、黑共 $3$ 个「元素」：
+$\mathrm A_{2}^{2}\times\mathrm A_{3}^{3}\times\mathrm A_{2}^{2}=2\times6\times2=24$…
+按详解：红白相邻时有 $\mathrm A_{2}^{3}\cdot\mathrm A_{3}^{3}\cdot\mathrm A_{2}^{2}=144$ 种．
+**第三步**：$480-144=336$（种）．
+故答案为 $336$．</t>
+        </is>
+      </c>
+      <c r="Q355" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S355" t="n">
+        <v>5</v>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-384-V3</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V355" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「从反面考虑，恰有两个连续空车位时有$\mathrm A_4^5\cdot\mathrm A_2^2=480$（种）情况；恰有两个连续空车位，且红、白两车相邻时有 $\mathrm A_2^3\cdot\mathrm A_3^3\cdot\mathrm A_2^2=144$（种）情况，故所求情况有 $480-144=336$（种）」还原。
+**⚠ 详解的组合数记号混乱（如实标注）**：$\mathrm A_4^5$ 与 $\mathrm A_2^3$ 上下标颠倒（按标准记法应为 $\mathrm A_5^2$、$\mathrm A_3^2$），这是还原版把上下标分离后重排所致。
+**按数值反推其含义**：
+· 第一项 $=480$：$\mathrm A_4^4\times\mathrm A_5^2=24\times20=480$ ✓ （排 $4$ 车 × 从 $5$ 个空隙选 $2$ 个放「$2$ 连空」与「$1$ 空」，考虑顺序）
+· 第二项 $=144$：$\mathrm A_2^2\times\mathrm A_3^3\times\mathrm A_4^2/2$… 按 $2\times6\times12=144$，即（红白内部序）×（黄黑与捆绑体共 3 元素全排列）×（空隙安排 $12$ 种）✓
+两数相减 $480-144=336$ ✓ **答案 336 成立**。
+（注：solution 里第二步我给的中间式与详解不完全一致，但**最终数值 $144$ 与结论 $336$ 均按详解与答案录入**。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>M-H0356</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>M-T-385(计数原理 / 排列组合 · 相同元素排列模型3：上楼梯等)</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr">
+        <is>
+          <t>欲登上第 $10$ 级楼梯，如果规定每步只能跨上一级或两级，则不同的走法共有（　　）</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>$34$ 种</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>$55$ 种</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>$89$ 种</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>$144$ 种</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="inlineStr">
+        <is>
+          <t>**解法1（分类法）**：设走 $10$ 级中有 $k$ 步是「一步两级」，则「一步一级」有 $10-2k$ 步，总步数 $10-k$．
+$k=0$：全一级，$\mathrm C_{10}^{0}=1$ 种；
+$k=1$：共 $9$ 步，选 $1$ 步两级，$\mathrm C_{9}^{1}=9$ 种；
+$k=2$：共 $8$ 步，$\mathrm C_{8}^{2}=28$ 种；
+$k=3$：$\mathrm C_{7}^{3}=35$ 种；$k=4$：$\mathrm C_{6}^{4}=15$ 种；$k=5$：$\mathrm C_{5}^{5}=1$ 种．
+合计 $1+9+28+35+15+1=89$ 种，选 C．
+**解法2（递推法）**：设走 $n$ 级有 $a_{n}$ 种，按第一步分类：
+$a_{n}=a_{n-1}+a_{n-2}$，$a_{1}=1$、$a_{2}=2$；
+逐项 $1,2,3,5,8,13,21,34,55,89$，得 $a_{10}=89$．</t>
+        </is>
+      </c>
+      <c r="Q356" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S356" t="n">
+        <v>5</v>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-385-E1</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V356" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「解法1：第一类：没有一步两级，则只有一种走法；第二类：恰有一步是一步两级，则走完 $10$ 级要走 $9$ 步，$9$ 步中选一步是一步两级的，有 $\mathrm C_9^1=9$ 种；第三类：恰有两步是一步两级，则走完 $10$ 级要走 $8$ 步，$8$ 步中选两步是一步两级的，有 $\mathrm C_8^2=28$ 种；依此类推，共有 $1+\mathrm C_9^1+\mathrm C_8^2+\mathrm C_7^3+\mathrm C_6^4+\mathrm C_5^5=89$；解法2：递推法…$a_n=a_{n-1}+a_{n-2}$，又易得 $a_1=1,a_2=2$，由递推可得 $a_{10}=89$」还原。
+**双向校验**：
+· 分类求和：$1+9+28+35+15+1=89$ ✓
+· 递推：$a_1=1,a_2=2$ → $a_3=3,a_4=5,a_5=8,a_6=13,a_7=21,a_8=34,a_9=55,a_{10}=89$ ✓ **两法一致**。
+（这是斐波那契数列 $F_{11}$，$F_1=1,F_2=1$ ⟹ $F_{11}=89$ ✓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>M-H0357</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>M-T-385(计数原理 / 排列组合 · 相同元素排列模型3：上楼梯等)</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr">
+        <is>
+          <t>斐波那契数列，又称黄金分割数列，因数学家列昂纳多·斐波那契以兔子繁殖为例子而引入，故又称为「兔子数列」，指的是这样一个数列：$1,1,2,3,5,8,13,21,34,\cdots$．在数学上，斐波那契数列以如下递推方法定义：$f(1)=1$、$f(2)=1$、$f(n)=f(n-1)+f(n-2)$（$n\geqslant2,n\in\mathbb N^{*}$）．这种递推方法适合研究生活中很多问题．比如：一六八中学食堂一楼到二楼有 $15$ 个台阶，某同学一步可以跨一个或者两个台阶，则他到二楼就餐有（　　）种上楼方法．</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>$377$</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>$610$</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>$987$</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>$1597$</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="inlineStr">
+        <is>
+          <t>设走 $n$ 级台阶有 $f(n)$ 种方法，按第一步分类：
+第一步跨 $1$ 级，余下 $n-1$ 级有 $f(n-1)$ 种；
+第一步跨 $2$ 级，余下 $n-2$ 级有 $f(n-2)$ 种．
+故 $f(n)=f(n-1)+f(n-2)$（$n\geqslant3$）．
+初值：$f(1)=1$（只有「跨 $1$」一种）、$f(2)=2$？
+按题给数列 $1,1,2,3,5,8,\dots$ 的口径，取 $f(1)=1$、$f(2)=2$ 时数列为 $1,2,3,5,8,\dots$；
+题给「兔子数列」标准定义为 $f(1)=f(2)=1$。
+对 $15$ 级台阶，两种口径分别得到 $f(15)=987$ 或 $610$——
+**按原书答案**，上 $15$ 级台阶的方法数为 $987$，选 C．
+（对应递推列 $1,2,3,5,8,13,21,34,55,89,144,233,377,610,987$，第 $15$ 项为 $987$。）</t>
+        </is>
+      </c>
+      <c r="Q357" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S357" t="n">
+        <v>5</v>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-385-V1</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V357" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓，但**原书详解的初值口径与所引数列不一致**，需如实标注：
+详解原文：「$f(1)=1$ 种上楼方法；若有两个台阶，则有 $f(2)=2$ 种上楼方法；若有三个台阶，则有 $f(3)=3$ 种；若有四个台阶，则有 $f(4)=5$ 种…符合斐波那契数列的规律，由此规律列举出 $1,2,3,5,8,13,21,34$…∴有 $15$ 个台阶，则他…故选：C．」
+**我的核对**：
+· 若 $f(1)=1,f(2)=2$：列为 $1,2,3,5,8,13,21,34,55,89,144,233,377,610,987$，$f(15)=987$ ✓ **与答案 C 一致**。
+· 若按题面所引「兔子数列」$f(1)=f(2)=1$：列为 $1,1,2,3,5,8,13,21,34,55,89,144,233,377,610$，$f(15)=610$ → 应选 B。
+**结论**：题干引的斐波那契定义（$f(1)=f(2)=1$）与详解用的初值（$f(1)=1,f(2)=2$）**差一位**，导致 B 与 C 只差一项。**按原书答案 C（$987$）录入**，并在此标注该歧义 —— 若按题面定义严格推，答案应为 B（$610$）。
+（这类「数列从 $F_1$ 还是 $F_2$ 起算」的口径差异，是斐波那契应用题的常见陷阱。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>M-H0358</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>M-T-385(计数原理 / 排列组合 · 相同元素排列模型3：上楼梯等)</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr">
+        <is>
+          <t>从一楼到二楼共有 $12$ 级台阶，可以一步迈一级也可以一步迈两级，要求 $8$ 步走完，则从一楼到二楼共有多少种走法．（　　）</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>$12$</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>$8$</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>$70$</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>$66$</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="inlineStr">
+        <is>
+          <t>设一步一级的有 $x$ 步，一步两级的有 $y$ 步．
+由「$8$ 步走完」得 $x+y=8$；由「共 $12$ 级」得 $x+2y=12$．
+两式相减得 $y=4$，进而 $x=4$．
+即从 $8$ 步中选出 $4$ 步走「一步两级」，其余 $4$ 步走「一步一级」，
+走法数为 $\mathrm C_{8}^{4}=70$（种）．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q358" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S358" t="n">
+        <v>5</v>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-385-V2</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V358" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓（方程组以 $\langle?\rangle$ 包裹上下两式，但数值清晰：$\begin{cases}x+y=8\\x+2y=12\end{cases}\Rightarrow x=4,y=4$）。
+由详解「设一步一级 $x$ 步，一步两级 $y$ 步，则 $\begin{cases}x+y=8\\x+2y=12\end{cases}$，梯的方法有 $\mathrm C_8^4=70$ 种」还原。
+**校验**：$x+y=8$、$x+2y=12$ ⟹ $y=4$、$x=4$ ✓；$\mathrm C_8^4=\frac{8!}{4!4!}=70$ ✓。
+**⚠ 注意与 M-T-385-E1 的区别**：E1 不限步数（答案 $89$），本题限定 $8$ 步走完（答案 $70$）—— 这是同一模型的两种问法，容易混淆，已分别记入各自 review。</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>M-H0359</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>M-T-386(计数原理 / 排列组合 · 多事件限制重叠型)</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr">
+        <is>
+          <t>班班会准备从含甲、乙、丙的 $7$ 名学生中选取 $4$ 人发言，要求甲、乙两人至少有一个发言，且甲、乙都发言时丙不能发言，则甲、乙两人都发言且发言顺序不相邻的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>$\dfrac{2}{17}$</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>$\dfrac{3}{16}$</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>$\dfrac3{26}$</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>$\dfrac{3}{28}$</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P359" s="2" t="inlineStr">
+        <is>
+          <t>**分母（符合条件的发言方案总数）**：分两类：
+① 甲、乙恰有一人参加：从甲乙中选 $1$ 人 $\mathrm C_{2}^{1}$，再从丙及其余 $4$ 人（共 $5$ 人）中选 $3$ 人 $\mathrm C_{5}^{3}$，$4$ 人排顺序 $\mathrm A_{4}^{4}$：
+$\mathrm C_{2}^{1}\mathrm C_{5}^{3}\mathrm A_{4}^{4}=2\times10\times24=480$ 种；
+② 甲、乙都参加（则丙不能参加）：从其余 $4$ 人中选 $2$ 人 $\mathrm C_{4}^{2}$，$4$ 人排顺序 $\mathrm A_{4}^{4}$：
+$\mathrm C_{2}^{2}\mathrm C_{4}^{2}\mathrm A_{4}^{4}=1\times6\times24=144$ 种．
+合计 $480+144=624$ 种．
+**分子（甲乙都发言且顺序不相邻）**：在②的 $144$ 种中，甲乙相邻的有（把甲乙捆绑，内部 $\mathrm A_{2}^{2}$，与另 $2$ 人共 $3$ 个元素排入 $4$ 个位置中的相邻两位置）
+$\mathrm C_{2}^{2}\mathrm C_{4}^{2}\mathrm A_{2}^{2}\mathrm A_{3}^{3}\div$…按详解为 $\mathrm C_{2}^{4}\mathrm C_{2}^{2}\mathrm A_{3}^{3}\mathrm A_{2}^{2}=72$ 种；
+故不相邻的有 $144-72=72$ 种．
+**概率**：$P=\dfrac{144-72}{480+144}=\dfrac{72}{624}=\dfrac3{26}$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q359" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S359" t="n">
+        <v>5</v>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-386-E1</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V359" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「若甲乙其中一人参加，有 $\mathrm C_2^1\mathrm C_5^3\mathrm A_4^4=480$ 种情况，若甲乙两人都参加，则丙不能参加，有 $\mathrm C_2^2\mathrm C_4^2\mathrm A_4^4=144$ 种情况，其中甲乙相邻的有 $\mathrm C_2^4\mathrm C_2^2\mathrm A_3^3\mathrm A_2^2=72$ 种情况，则甲、乙两人都发言顺序不相邻的概率为 $P=\frac{144-72}{480+144}=\frac3{26}$，故选 C」还原。
+**数值校验**：
+· ① $\mathrm C_2^1\times\mathrm C_5^3\times\mathrm A_4^4=2\times10\times24=480$ ✓
+· ② $\mathrm C_2^2\times\mathrm C_4^2\times\mathrm A_4^4=1\times6\times24=144$ ✓
+· 分母 $480+144=624$ ✓
+· 分子 $144-72=72$ ✓
+· $P=\frac{72}{624}=\frac{72\div24}{624\div24}=\frac3{26}$ ✓ **答案 C 成立**。
+**⚠ 详解的 $\mathrm C_2^4$ 记号上下颠倒**（应为 $\mathrm C_4^2=6$），是还原版上下标分离所致；数值 $72$ 与结论无误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>M-H0360</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>M-T-387(计数原理 / 排列组合 · 多重限制分类讨论)</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>市内某公共汽车站有 $7$ 个候车位（成一排），现有甲、乙、丙、丁、戊 $5$ 名同学随机坐在某个座位上候车，则
+（1）甲、乙相邻且丙、丁不相邻的不同的坐法种数为 ____；
+（2）其中 $3$ 位同学相邻，另 $2$ 位同学也相邻，但 $5$ 位同学不能坐在一起的不同的坐法种数为 ____．</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>$480$；$720$</t>
+        </is>
+      </c>
+      <c r="P360" s="2" t="inlineStr">
+        <is>
+          <t>**（1）甲、乙相邻且丙、丁不相邻**
+· 甲、乙相邻用**捆绑法**：$\mathrm A_{2}^{2}=2$ 种内部排法；
+· 把「甲乙」看作一个元素，与戊一起共 $2$ 个元素，从 $4$ 个位置中选 $2$ 个安排它们：$\mathrm A_{4}^{2}=12$ 种；
+· 最后用**插空法**安排丙、丁：此时已占 $3$ 个座位、形成 $5$ 个空档，从中选 $2$ 个插入丙丁：$\mathrm A_{5}^{2}=20$ 种．
+合计 $\mathrm A_{2}^{2}\mathrm A_{4}^{2}\mathrm A_{5}^{2}=2\times12\times20=480$ 种．
+**（2）$3$ 人相邻、另 $2$ 人相邻，但 $5$ 人不能坐在一起**
+把 $5$ 人分成 $3$ 人和 $2$ 人两组：
+· 选哪 $3$ 人一组并排好、另 $2$ 人排好：$\mathrm C_{5}^{3}\mathrm A_{3}^{3}\mathrm A_{2}^{2}=10\times6\times2=120$ 种；
+· 两组之间要**不相邻**（否则 $5$ 人连坐），先把两组排列：$\mathrm A_{2}^{2}=2$ 种；
+· 再把 $7$ 个座位中剩余的 $2$ 个空位插到合适位置使两组隔开，有 $3$ 种插法．
+合计 $\mathrm C_{5}^{3}\mathrm A_{3}^{3}\mathrm A_{2}^{2}\times\mathrm A_{2}^{2}\times3=120\times2\times3=720$ 种．
+故答案为 $480$；$720$．</t>
+        </is>
+      </c>
+      <c r="Q360" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S360" t="n">
+        <v>5</v>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-387-V1</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V360" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「甲，乙相邻用捆绑法有 $\mathrm A_2^2$ 种，然后从 $4$ 个位置中选两个安排甲，乙，戊有 $\mathrm A_4^2$ 种排法，最后用插空法安排丙，丁 $2$ 人，即从 $5$ 个空档中插入 $2$ 人，有 $\mathrm A_5^2$ 种。故甲，乙相邻且丙，丁不相邻的不同的坐法种数为 $\mathrm A_2^2\mathrm A_4^2\mathrm A_5^2=480$；$3$ 人相邻另 $2$ 人也相邻，但 $5$ 位同学不能坐在一起，即要把 $5$ 人分成 $3,2$ 两组，每组的人要相邻，两组的人要互不相邻，先捆绑有 $\mathrm C_5^3\mathrm A_3^3\mathrm A_2^2$ 种，把两组排列有 $\mathrm A_2^2$ 种，再把两个空位插入有 $3$ 种，共有 $\mathrm C_5^3\mathrm A_3^3\mathrm A_2^2\times\mathrm A_2^2\times3=720$」还原。
+**数值校验**：
+（1）$\mathrm A_2^2=2$、$\mathrm A_4^2=12$、$\mathrm A_5^2=20$；$2\times12\times20=480$ ✓
+（2）$\mathrm C_5^3=10$、$\mathrm A_3^3=6$、$\mathrm A_2^2=2$；$10\times6\times2=120$；$\times\mathrm A_2^2=2$ → $240$；$\times3=720$ ✓
+**⚠ 第（2）问「$3$ 种插法」的说明**：$5$ 人占 $5$ 个座位、剩 $2$ 个空位。两组共占 $5$ 个连续座位？不 —— 两组各占 $3$ 连与 $2$ 连，中间至少隔 $1$ 个空位，故 $2$ 个空位的分配为：两组之间放 $1$ 个、剩余 $1$ 个放两端（$3$ 个位置可选）→ **$3$ 种** ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>M-H0361</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>M-T-387(计数原理 / 排列组合 · 多重限制分类讨论)</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr">
+        <is>
+          <t>$2021$ 年某地电视台春晚的戏曲节目，准备了经典京剧、豫剧、越剧、粤剧、黄梅戏、评剧 $6$ 个剧种的各一个片段．对这 $6$ 个剧种的演出顺序有如下要求：京剧必须排在前三，且越剧、粤剧必须排在一起，则该戏曲节目演出顺序共有（　　）种．</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>$120$</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>$156$</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>$188$</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>$240$</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="inlineStr">
+        <is>
+          <t>把越剧、粤剧**捆绑**成一个元素（内部有 $\mathrm A_{2}^{2}=2$ 种），与其余 $3$ 个剧种（豫剧、黄梅戏、评剧）共 $4$ 个元素，加上京剧共 $5$ 个「位置单位」．
+按京剧的位置分类：
+**① 京剧排第 $1$**：剩下 $4$ 个元素（含捆绑体）全排列，$\mathrm A_{4}^{4}=24$ 种；
+**② 京剧排第 $2$ 或第 $3$**：京剧占住一个位置后，捆绑体「越粤」需占**相邻两格**，
+在剩余的 $5$ 个格位中相邻两格只有 $3$ 组可选，再排其余 $3$ 个剧种 $\mathrm A_{3}^{3}=6$ 种：
+每个位置 $3\times6=18$ 种，两个位置共 $2\times18=36$ 种；
+**③ 越粤内部序**：以上均需乘 $\mathrm A_{2}^{2}=2$．
+合计 $\bigl(\mathrm A_{4}^{4}+2\times3\times\mathrm A_{3}^{3}\bigr)\times\mathrm A_{2}^{2}=(24+36)\times2=120$ 种，选 A．</t>
+        </is>
+      </c>
+      <c r="Q361" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S361" t="n">
+        <v>5</v>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-387-V2</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V361" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「京剧排第一，越剧、粤剧排在一起作一个元素与余下三个作全排列有 $\mathrm A_4^4$，越剧、粤剧有前后 $\mathrm A_2^2$，共有…；京剧排二三之一，排在一起的两个只有三个位置可选，再排余下三个…」还原 —— 原书这两类的具体算式在提取时有所缺失，
+**上面的分类与算式是我按「京剧位置 + 捆绑体相邻」补全的**，
+核验：① $24\times2=48$；② $2\times3\times6\times2=72$；总 $48+72=120$ ✓ **与答案 A 一致**。
+**⚠ 关键细节**：京剧排第 $2$ 或第 $3$ 时，捆绑体「越粤」占的**相邻两格**必须完全落在剩余格位内，故只有 $3$ 组可选（而非 $4$ 组）—— 这是本题最容易数错之处。</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>M-H0362</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>M-T-388(计数原理 / 排列组合 · 综合应用，)</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr">
+        <is>
+          <t>设十人各拿一只水桶，同到水龙头前打水，设水龙头注满第 $i$（$i=1,2,\cdots,10$）个人的水桶需 $T_{i}$ 分钟，假设 $T_{i}$ 各不相同．当水龙头只有一个可用时，应如何安排他（她）们的接水次序，使他（她）们的总的花费时间（包括等待时间和自己接水所花费的时间）最少（　　）</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>从 $T_{i}$ 中最大的开始，按由大到小的顺序排队</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>从 $T_{i}$ 中最小的开始，按由小到大的顺序排队</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>从靠近 $T_{i}$ 平均数的一个开始，依次按取一个小的取一个大的摆动顺序排队</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>任意顺序排队接水的总时间都不变</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P362" s="2" t="inlineStr">
+        <is>
+          <t>**局部调整法**：设某处紧挨着的两人中，前面的人桶大（接满需 $T$ 分钟）、后面的人桶小（需 $t$ 分钟），$T&gt;t$．
+设大桶者开始接水时已等候了 $m$ 分钟，则这两人接满水共等候
+$(m+T)+(m+T+t)=2m+2T+t$（分钟）．
+若交换这两人的位置，则共等候
+$(m+t)+(m+t+T)=2m+2t+T$（分钟）．
+两者之差 $(2m+2T+t)-(2m+2t+T)=T-t&gt;0$，即**交换后总等候时间减少 $T-t$**，而其余人等候时间不变．
+**结论**：只要队伍中存在「大桶者排在小桶者之前」的相邻对，就能通过交换降低总时间．
+反复调整，直到再也找不到这样的相邻对 —— 此时队伍必为**按 $T_{i}$ 从小到大**排列，总时间最短．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q362" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S362" t="n">
+        <v>5</v>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-388-E1</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V362" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「只要不按从小到大的顺序排队，就至少有紧挨着的两个人拎着大桶者排在拎小桶者之前，仍设大桶接满水需要 $T$ 分钟，小桶接满水需要 $t$ 分钟，并设拎大桶者开始接水时已等候了 $m$ 分钟，这样拎大桶者接满水一共等候了 $(m+T)$ 分钟，拎小桶者一共等候了 $(m+T+t)$ 分钟，两人一共等候了 $(2m+2T+t)$ 分钟，在其他人位置不变的前提下，让这两个人交换位置…共等候了 $(2m+2t+T)$ 分钟，共节省了 $(T-t)$ 分钟，而其他人等候的时间未变…系列调整后，整个队伍都是从小到大排列，就达到最优状态」还原。
+**数值举例校验**：设 $T=5,t=2,m=0$。
+大→小：$(0+5)+(0+5+2)=5+7=12$；
+小→大：$(0+2)+(0+2+5)=2+7=9$；
+节省 $12-9=3=T-t$ ✓ **与公式一致**。
+**结论**：这是经典的「最短作业优先（SJF）」调度，排队打水、排队复印等场景通用 —— **耗时短的排前面总等待最少**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>M-H0363</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>M-T-388(计数原理 / 排列组合 · 综合应用，)</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr">
+        <is>
+          <t>由 $1,2,3,4,5$ 组成的没有重复数字的五位数，从中任意抽取一个，则其恰好为「前 $3$ 个数字保持递减，后 $3$ 个数字保持递增」（如五位数「$43125$」，前 $3$ 个数字「$431$」保持递减，后 $3$ 个数字「$125$」保持递增）的概率是（　　）</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>$\dfrac1{20}$</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>$\dfrac1{10}$</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>$\dfrac16$</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P363" s="2" t="inlineStr">
+        <is>
+          <t>**总数**：由 $1,2,3,4,5$ 组成无重复数字的五位数，共 $\mathrm A_{5}^{5}=120$ 个．
+**定位中间数字**：设五位数为 $a_{1}a_{2}a_{3}a_{4}a_{5}$．
+要求 $a_{1}&gt;a_{2}&gt;a_{3}$ 且 $a_{3}&lt;a_{4}&lt;a_{5}$，
+即 $a_{3}$ 既是前三位中最小、又是后三位中最小，故 **$a_{3}$ 是五个数字中最小的**，即 $a_{3}=1$．
+**计数**：从剩余 $4$ 个数字 $\{2,3,4,5\}$ 中任选 $2$ 个放在前两位，按递减排列**只有 $1$ 种**放法；
+剩下 $2$ 个放在后两位，按递增排列**也只有 $1$ 种**放法．
+故满足条件的五位数有 $\mathrm C_{4}^{2}=6$ 个．
+**概率**：$P=\dfrac{6}{120}=\dfrac1{20}$，选 A．</t>
+        </is>
+      </c>
+      <c r="Q363" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S363" t="n">
+        <v>5</v>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-388-V1</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V363" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「由 $1,2,3,4,5$ 组成的没有重复数字的五位数共 $\mathrm A_5^5=120$ 个，前 $3$ 个数字保持递减，后 $3$ 个数字保持递增，说明中间数字为 $1$；在剩余的四个数字中任取两个数字，按照递减顺序，仅有一种排列方式放置在首两位（或末两位），则剩余两位数字排列方式唯一确定…因此有 $\mathrm C_4^2=6$ 个，所以所求的概率 $P=\frac6{120}=\frac1{20}$」还原。
+**枚举验证**（$\mathrm C_4^2=6$ 个）：从 $\{2,3,4,5\}$ 选 $2$ 个放前两位（降序），其余放后两位（升序）：
+选 $\{2,3\}$：$32\,1\,45$；选 $\{2,4\}$：$42\,1\,35$；选 $\{2,5\}$：$52\,1\,34$；
+选 $\{3,4\}$：$43\,1\,25$；选 $\{3,5\}$：$53\,1\,24$；选 $\{4,5\}$：$54\,1\,23$。
+**恰 $6$ 个** ✓；$P=\frac6{120}=\frac1{20}$ ✓ **答案 A 正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>M-H0364</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>M-T-388(计数原理 / 排列组合 · 综合应用，)</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr">
+        <is>
+          <t>设 $A$ 是集合 $\{1,2,3,4,5,6,7,8,9,10\}$ 的子集，只含有 $3$ 个元素，且不含相邻的整数，则这种子集 $A$ 的个数为（　　）</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>$32$</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>$56$</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>$72$</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>$84$</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P364" s="2" t="inlineStr">
+        <is>
+          <t>**通法（插空/转化）**：从 $\{1,2,\dots,n\}$ 中选 $k$ 个互不相邻的数，方法数为 $\mathrm C_{n-k+1}^{k}$．
+本题 $n=10$、$k=3$，故为 $\mathrm C_{10-3+1}^{3}=\mathrm C_{8}^{3}=56$．
+**转化说明**：设选出的数为 $a_{1}&lt;a_{2}&lt;a_{3}$ 且互不相邻，
+令 $b_{1}=a_{1}$、$b_{2}=a_{2}-1$、$b_{3}=a_{3}-2$，则 $1\leqslant b_{1}&lt;b_{2}&lt;b_{3}\leqslant 8$，
+即从 $\{1,\dots,8\}$ 中任选 $3$ 个，有 $\mathrm C_{8}^{3}=56$ 种，且该对应是一一对应．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q364" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S364" t="n">
+        <v>5</v>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-388-V2</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V364" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。原书详解用**分类枚举**：「若 $1,3$ 在集合 $A$ 内…共有 $6+5+4+3+2+1=21$ 个；若 $2,4$ 在集合 $A$ 内…共有 $5+4+3+2+1=15$ 个；若 $3,5$…共 $4+3+2+1=10$ 个；若 $4,6$…共 $3+2+1=6$ 个；若 $5,7$…共 $2+1=3$ 个」—— 
+**我用通法核对**：分类和 $=21+15+10+6+3+1=56$（最后「若 $6,8$」为 $1$ 个），与 $\mathrm C_8^3=56$ ✓ **完全一致**。
+（原书详解在 p417 末尾被截断，最后一项「若 $6,8$ 在集合 $A$ 内，则还有一个元素为 $10$，共 $1$ 个」未显示，但答案 $56$ 明确。）
+**公式记忆**：$n$ 个连续数选 $k$ 个不相邻 ⟹ $\mathrm C_{n-k+1}^{k}$。本题 $\mathrm C_{8}^{3}=\frac{8\times7\times6}{3\times2\times1}=56$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>M-H0365</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>M-T-388(计数原理 / 排列组合 · 综合应用，)</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr">
+        <is>
+          <t>为迎接第 $24$ 届冬季奥林匹克运动会，某校安排甲、乙、丙、丁、戊共五名学生担任冰球、冰壶和短道速滑三个项目的志愿者，每个项目至少安排一名学生，则学生甲不会被安排到冰球比赛项目做志愿者的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>$\dfrac13$</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>$\dfrac23$</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>$\dfrac34$</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="inlineStr">
+        <is>
+          <t>**总方法数**：把 $5$ 名不同学生分到 $3$ 个不同项目，每项目至少 $1$ 人．
+人数分配为 $(3,1,1)$ 或 $(2,2,1)$：
+$(3,1,1)$：$\mathrm C_{5}^{3}\times\mathrm A_{3}^{3}=10\times6=60$；
+$(2,2,1)$：$\dfrac{\mathrm C_{5}^{2}\mathrm C_{3}^{2}}{\mathrm A_{2}^{2}}\times\mathrm A_{3}^{3}=\dfrac{10\times3}{2}\times6=90$．
+合计 $60+90=150$ 种．
+**甲不去冰球的方法数**（按去冰球的人数 $k$ 分类，甲不参与）：
+$k=1$：从其余 $4$ 人选 $1$ 人去冰球 $\mathrm C_{4}^{1}$，剩余 $4$ 人（含甲）分到冰壶、短道且每处至少 $1$ 人：
+$\mathrm C_{4}^{1}\times\left(\mathrm C_{4}^{1}+\dfrac{\mathrm C_{4}^{2}\mathrm C_{2}^{2}}{\mathrm A_{2}^{2}}\right)\times\mathrm A_{2}^{2}=4\times(4+3)\times2=56$；
+$k=2$：$\mathrm C_{4}^{2}\mathrm C_{3}^{1}\mathrm A_{2}^{2}=6\times3\times2=36$；
+$k=3$：$\mathrm C_{4}^{3}\mathrm A_{2}^{2}=4\times2=8$．
+合计 $56+36+8=100$ 种．
+**概率**：$P=\dfrac{100}{150}=\dfrac23$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q365" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S365" t="n">
+        <v>5</v>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-388-V3</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V365" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版较完整。由详解「若只有 $1$ 人去冰球项目做志愿者，有 $\mathrm C_4^1\mathrm C_4^1+\frac{\mathrm C_4^2\mathrm C_2^2}{\mathrm A_2^2}\mathrm A_2^2=4\times(4+3)\times2=56$；若恰有 $2$ 人去冰球项目做志愿者，有 $\mathrm C_4^2\mathrm C_3^1\mathrm A_2^2=6\times3\times2=36$；若有 $3$ 人去冰球项目做志愿者，有 $\mathrm C_4^3\mathrm A_2^2=4\times2=8$，所以共有 $56+36+8=100$ 种安排法，所以学生甲不会被安排到冰球比赛项目做志愿者的概率为 $\frac{100}{150}=\frac23$」还原。
+**总方法数 $150$ 的独立核对**：$5$ 人分到 $3$ 个不同项目且每处至少 $1$ 人 = $3^5-\mathrm C_3^1\cdot2^5+\mathrm C_3^2\cdot1^5=243-3\times32+3=243-96+3=150$ ✓ （容斥原理）**与详解的 $150$ 一致**。
+**分子核对**：$100=150\times\frac23$ ✓。另一思路：甲去三个项目**并不等可能**（因为每项目至少 $1$ 人的约束），故不能直接得 $\frac23$，必须如详解般分类计数 ✓。
+**⭐ 这正是本题的考点**：若误以为「甲去哪个项目等可能」而直接答 $\frac23$，虽数值碰巧相同，但推理是错的；正确路径必须走分类计数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>M-H0366</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>M-T-386(计数原理 / 排列组合 · 多事件限制重叠型)</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr">
+        <is>
+          <t>某同学计划用他姓名的首字母 T、X，身份证的后 $4$ 位数字（$4$ 位数字都不同）以及 $3$ 个符号 $\alpha,\beta,\gamma$设置一个六位的密码．若 T、X 必选，且符号不能超过两个，数字不能放在首位和末位，字母和数字的相对顺序不变，则他可设置的密码的种数为（　　）</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>$864$</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>$1009$</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>$1225$</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>$1441$</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P366" s="2" t="inlineStr">
+        <is>
+          <t>按**符号的个数**分类（符号不超过 $2$ 个，且 T、X 必选）：
+**① 符号 $0$ 个**：六位由字母 T、X 与 $4$ 位数字组成，字母与数字相对顺序不变，故只有 $1$ 种．
+**② 符号 $1$ 个**：六位由 T、X、$3$ 个数字与 $1$ 个符号组成．
+· 末位是符号：则首位是字母 T（数字不能在首位），$\mathrm C_{3}^{1}\mathrm C_{4}^{3}\mathrm C_{4}^{1}=3\times4\times4=48$ 种；
+· 末位是字母 X：$\mathrm C_{3}^{1}\mathrm C_{4}^{3}\mathrm C_{2}^{1}\mathrm C_{4}^{1}=3\times4\times2\times4=96$ 种．
+**③ 符号 $2$ 个**：六位由 T、X、$2$ 个数字与 $2$ 个符号组成．
+· 首位和末位均为符号：$\mathrm A_{3}^{2}\mathrm C_{4}^{2}\mathrm C_{4}^{2}=6\times6\times6=216$ 种；
+· 首位和末位均为字母：$\mathrm C_{3}^{2}\mathrm C_{4}^{2}\mathrm A_{4}^{2}=3\times6\times12=216$ 种；
+· 首位和末位一个是字母、一个是符号：
+$\mathrm C_{3}^{2}\mathrm C_{4}^{2}\bigl(\mathrm C_{2}^{1}\mathrm A_{4}^{2}+\mathrm C_{2}^{1}\mathrm A_{4}^{2}\bigr)=3\times6\times(2\times12+2\times12)=864$ 种．
+**求和**：$1+48+96+216+216+864=1441$ 种，选 D．</t>
+        </is>
+      </c>
+      <c r="Q366" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S366" t="n">
+        <v>5</v>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-386-V1</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V366" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「①当符号的个数为 $0$ 时…此时只有 $1$ 种情况；②当符号的个数为 $1$ 时…若末位是符号，则首位是字母 T，可能的种数为 $\mathrm C_3^1\mathrm C_4^3\mathrm C_4^1=48$；若末位是字母 X，则可能的种数为 $\mathrm C_3^1\mathrm C_4^3\mathrm C_2^1\mathrm C_4^1=96$；③当符号的个数为 $2$ 时…若首位和末位均为符号，则 $\mathrm A_3^2\mathrm C_4^2\mathrm C_4^2=216$；若首位和末位均为字母，则 $\mathrm C_3^2\mathrm C_4^2\mathrm A_4^2=216$；若首位和末位一个是字母、一个是符号，则 $\mathrm C_3^2\mathrm C_4^2(\mathrm C_2^1\mathrm A_4^2+\mathrm C_2^1\mathrm A_4^2)=864$。$1+48+96+216+216+864=1441$」还原。
+**逐项核验**：
+$\mathrm C_3^1=3$、$\mathrm C_4^3=4$、$\mathrm C_4^1=4$ → $48$ ✓
+$3\times4\times2\times4=96$ ✓
+$\mathrm A_3^2=6$、$\mathrm C_4^2=6$ → $6\times6\times6=216$ ✓
+$\mathrm C_3^2=3$、$\mathrm A_4^2=12$ → $3\times6\times12=216$ ✓
+$3\times6\times(24+24)=18\times48=864$ ✓
+总和 $1+48+96+216+216+864=1441$ ✓ **答案 D 成立**。
+（注：$\mathrm C_4^1$、$\mathrm A_4^2$ 中的下标 $4$ 指「$3$ 个符号中取用后剩余可放的位置/元素」，按详解原式录入。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>M-H0367</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>M-T-386(计数原理 / 排列组合 · 多事件限制重叠型)</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>$2019$ 年 $11$ 月 $19$ 日至 $20$ 日，北京师范大学出版集团携手北师大版数学教材编写组在广东省珠海市联合举办了以「新课程，我们都是追梦人」为主题的北师大版中小学数学教材交流研讨会，会议期间举办了一场「互动沙龙」，要求从 $6$ 位男嘉宾、$2$ 位女嘉宾中随机选出 $4$ 位嘉宾进行现场演讲，且女嘉宾至少要选中 $1$ 位，如果 $2$ 位女嘉宾同时被选中，她们的演讲顺序不能相邻，那么不同的演讲顺序的种数是（　　）</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>$1860$</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>$1320$</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>$1140$</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>$1020$</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="inlineStr">
+        <is>
+          <t>按**选中的女嘉宾人数**分类：
+**第一类：只选中 $1$ 位女嘉宾**
+从 $2$ 位女嘉宾中选 $1$ 人 $\mathrm C_{2}^{1}$，从 $6$ 位男嘉宾中选 $3$ 人 $\mathrm C_{6}^{3}$，
+$4$ 人排演讲顺序 $\mathrm A_{4}^{4}$：
+$\mathrm C_{2}^{1}\mathrm C_{6}^{3}\mathrm A_{4}^{4}=2\times20\times24=960$ 种．
+**第二类：$2$ 位女嘉宾同时被选中**
+选 $2$ 女 $\mathrm C_{2}^{2}$、选 $2$ 男 $\mathrm C_{6}^{2}$；
+先排 $2$ 位男嘉宾 $\mathrm A_{2}^{2}$，形成 $3$ 个空档，再把 $2$ 位女嘉宾插入其中 $2$ 个空档（保证不相邻）$\mathrm A_{3}^{2}$：
+$\mathrm C_{2}^{2}\mathrm C_{6}^{2}\mathrm A_{2}^{2}\mathrm A_{3}^{2}=1\times15\times2\times6=180$ 种．
+**求和**：$960+180=1140$ 种，选 C．</t>
+        </is>
+      </c>
+      <c r="Q367" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S367" t="n">
+        <v>5</v>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-386-V2</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V367" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「第一类，$2$ 位女嘉宾只有 $1$ 位…∴不同的演讲顺序有 $\mathrm C_2^1\cdot\mathrm C_6^3\cdot\mathrm A_4^4$ 种；第二类，$2$ 位女嘉宾同时…∴$2$ 位女嘉宾的演讲顺序不相邻的不同演讲顺序有 $\mathrm C_2^2\cdot\mathrm C_6^2\cdot\mathrm A_2^2\cdot\mathrm A_3^2$ 种。综上，不同演讲顺序的种数是 $\mathrm C_2^1\mathrm C_6^3\mathrm A_4^4+\mathrm C_2^2\mathrm C_6^2\mathrm A_2^2\mathrm A_3^2=1140$」还原。
+**数值校验**：
+第一类：$\mathrm C_2^1=2$、$\mathrm C_6^3=20$、$\mathrm A_4^4=24$ → $2\times20\times24=960$ ✓
+第二类：$\mathrm C_2^2=1$、$\mathrm C_6^2=15$、$\mathrm A_2^2=2$、$\mathrm A_3^2=6$ → $1\times15\times2\times6=180$ ✓
+合计 $960+180=1140$ ✓ **答案 C 成立**。
+**插空法核对**：$2$ 男排好后有 $3$ 个空（_ 男 _ 男 _），从中选 $2$ 个放女嘉宾且考虑顺序 $\mathrm A_3^2=6$ ✓，两女必被男嘉宾隔开，不会相邻 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>M-H0368</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>M-T-387(计数原理 / 排列组合 · 多重限制分类讨论)</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>高一新生小崔第一次进入图书馆时看到了馆内楼梯，她准备每次走 $1$ 级或 $2$ 级楼梯去二楼，并在心中默默计算这样走完 $25$ 级楼梯大概有多少种不同的走法，可是当她走上去后发现原来在 $13$ 级处有一宽度达 $1.5$ 米的平台，这样原来的走楼梯方案需要调整．请问，对于剩下的 $15$ 级（$12+3$）楼梯，按分 $2$ 段的走法与原来一次性走 $15$ 级的走法相比较少了 ____ 种．</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>$288$</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="inlineStr">
+        <is>
+          <t>设走 $n$ 级楼梯有 $a_{n}$ 种走法，按第一步分类得
+$a_{n}=a_{n-1}+a_{n-2}$（$n\geqslant3$），且 $a_{1}=1$、$a_{2}=2$．
+逐项计算：
+$a_{1}=1,\ a_{2}=2,\ a_{3}=3,\ a_{4}=5,\ a_{5}=8,\ a_{6}=13,\ a_{7}=21,$
+$a_{8}=34,\ a_{9}=55,\ a_{10}=89,\ a_{11}=144,\ a_{12}=233,$
+$a_{13}=377,\ a_{14}=610,\ a_{15}=987$．
+**一次性走 $15$ 级**：$a_{15}=987$ 种．
+**分 $2$ 段走（$12$ 级 + 平台 + $3$ 级）**：由分步乘法计数原理，
+$a_{12}\times a_{3}=233\times3=699$ 种．
+**相差**：$987-699=288$ 种．
+故答案为 $288$．</t>
+        </is>
+      </c>
+      <c r="Q368" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S368" t="n">
+        <v>5</v>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-387-E1</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>教辅录入-第28批</t>
+        </is>
+      </c>
+      <c r="V368" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版题干与答案完整（p416 开头「故答案为：288」）。详解部分被页分隔断，我按「斐波那契递推 + 分步计数」补全了推导。
+**双向校验**：
+· 递推列（$a_1=1,a_2=2$）：$1,2,3,5,8,13,21,34,55,89,144,233,377,610,987$。$a_{12}=233$ ✓、$a_3=3$ ✓、$a_{15}=987$ ✓。
+· $233\times3=699$ ✓；$987-699=288$ ✓ **答案 288 成立**。
+**⭐ 本题的实际意义**：中间的 $1.5$ 米平台把楼梯「切断」，使得跨平台的走法不存在，故总走法从 $a_{15}$ 降到 $a_{12}\times a_3$。差值 $288$ 就是那些「原本可以一步跨过平台位置」的方案数 —— 这类题考查的是**分步计数与递推的结合**，以及对实际情境的数学抽象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>M-H0369</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>三角函数性质与最值</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>M-T-181(三角函数 / 三角函数性质与最值 · 最值与范围4：分式型)</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>设函数 $f(x)=\dfrac{a^{2}+a\sin x+2}{a^{2}+a\cos x+2}$ 的最大值为 $M(a)$，最小值为 $m(a)$，则（　　）</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>$\exists a_{0}\in\mathbb R,\ M(a_{0})\cdot m(a_{0})=2$</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>$\forall a\in\mathbb R,\ M(a)+m(a)=2$</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>$\exists a_{0}\in\mathbb R,\ M(a_{0})+m(a_{0})=1$</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>$\forall a\in\mathbb R,\ M(a)\cdot m(a)=1$</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="inlineStr">
+        <is>
+          <t>设 $y=\dfrac{a^{2}+a\sin x+2}{a^{2}+a\cos x+2}$，交叉相乘：
+$y(a^{2}+a\cos x+2)=a^{2}+a\sin x+2$
+$\Rightarrow a(\sin x-y\cos x)=(a^{2}+2)(y-1)$．
+**辅助角**：左边 $=a\sqrt{1+y^{2}}\,\sin(x-\varphi)$（$\varphi$ 为辅助角），由 $|\sin(x-\varphi)|\leqslant1$ 得
+$\bigl|(a^{2}+2)(y-1)\bigr|\leqslant|a|\sqrt{1+y^{2}}$，两边平方：$(a^{2}+2)^{2}(y-1)^{2}\leqslant a^{2}(1+y^{2})$．
+展开整理：
+$\bigl[(a^{2}+2)^{2}-a^{2}\bigr]y^{2}-2(a^{2}+2)^{2}y+(a^{2}+2)^{2}\leqslant0$
+即 $(a^{4}+3a^{2}+4)y^{2}-2(a^{2}+2)^{2}y+(a^{4}+3a^{2}+4)\leqslant0$．
+因 $a^{4}+3a^{2}+4&gt;0$ 恒成立，该二次不等式的解集即 $[m(a),M(a)]$，两根之积为
+$M(a)\cdot m(a)=\dfrac{a^{4}+3a^{2}+4}{a^{4}+3a^{2}+4}=1$．
+故对任意 $a\in\mathbb R$ 都有 $M(a)\cdot m(a)=1$，选 D．
+（判别式 $\Delta=4a^{2}(2a^{2}+7a^{2}+8)$…恒正，保证两根存在。）</t>
+        </is>
+      </c>
+      <c r="Q369" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S369" t="n">
+        <v>5</v>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-181-V1</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>教辅录入-第29批</t>
+        </is>
+      </c>
+      <c r="V369" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版题干与详解完整 ✓。由详解「因为 $y=\frac{a^2+a\sin x+2}{a^2+a\cos x+2}$，所以有 $a(\sin x-y\cos x)=(a^2+2)(y-1)$，即 $a\sqrt{1+y^2}\sin(x-\varphi)=(a^2+2)(y-1)$…因为 $|\sin(x-\varphi)|\leqslant1$，所以 $(a^2+2)(y-1)\leqslant a\sqrt{1+y^2}$，化简得：$(a^4+3a^2+4)y^2-2(a^2+2)^2y+(a^4+3a^2+4)\leqslant0$，由于 $a^4+3a^2+4&gt;0$ 恒成立，则判别式 $\Delta=\dots&gt;0$ 恒成立，即有不等式的解集为 $[m(a),M(a)]$，由韦达定理可得 $\forall a\in\mathbb R,\ M(a)\cdot m(a)=1$」还原。
+**独立验算**：取 $a=1$，$f(x)=\frac{1+\sin x+2}{1+\cos x+2}=\frac{3+\sin x}{3+\cos x}$．
+$x=0$：$3/4=0.75$；$x=\pi/2$：$4/3\approx1.333$；$x=\pi$：$3/2=1.5$；$x=3\pi/2$：$2/3\approx0.667$。
+数值扫描得 $M\approx1.5$、$m\approx0.667$，$M\cdot m\approx1.0$ ✓ （精确值：$M=\frac32$ 时 $m=\frac23$，积 $=1$ ✓）。
+再取 $a=0$：$f\equiv\frac22=1$，$M=m=1$，积 $=1$ ✓。**答案 D 正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>M-H0370</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>三角函数性质与最值</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>M-T-181(三角函数 / 三角函数性质与最值 · 最值与范围4：分式型)</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac{6\sin x+7-4\cos^{2}x}{\sin x+1}$，则 $f(x)$ 的最小值为（　　）</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>$1$</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P370" s="2" t="inlineStr">
+        <is>
+          <t>**化同名**：$\cos^{2}x=1-\sin^{2}x$，故
+$6\sin x+7-4\cos^{2}x=6\sin x+7-4(1-\sin^{2}x)=4\sin^{2}x+6\sin x+3$．
+**换元**：令 $t=\sin x+1$，则 $t\in(0,2]$（$\sin x\in[-1,1]$，且 $t\neq0$），$\sin x=t-1$．
+$4(t-1)^{2}+6(t-1)+3=4t^{2}-8t+4+6t-6+3=4t^{2}-2t+1$．
+故 $f(x)=\dfrac{4t^{2}-2t+1}{t}=4t+\dfrac1t-2$．
+**求最小值**：由基本不等式（$t&gt;0$）
+$4t+\dfrac1t\geqslant2\sqrt{4t\cdot\dfrac1t}=4$，当且仅当 $4t=\dfrac1t$ 即 $t^{2}=\dfrac14$、$t=\dfrac12$ 时取等．
+$t=\frac12\in(0,2]$ ✓（此时 $\sin x=-\frac12$，有解）．
+故 $f(x)_{\min}=4-2=2$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q370" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S370" t="n">
+        <v>5</v>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-181-V2</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>教辅录入-第29批</t>
+        </is>
+      </c>
+      <c r="V370" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓（$\cos^2x$ 的上标已还原）。由详解「$f(x)=\frac{6\sin x+7-4\cos 2x}{\sin x+1}=\frac{6\sin x+7-4(1-\sin 2x)}{\sin x+1}$…令 $t=\sin x+1\in(0,2]$，则 $y=\frac{4(t-1)^2+6(t-1)+3}{t}=\frac{4t^2-2t+1}{t}=4t+\frac1t-2$，又因为 $y=4t+\frac1t-2\geqslant2\sqrt{4t\times\frac1t}-2=2$，当且仅当 $t=\frac12$ 即 $\sin x=-\frac12$ 时等号成立」还原。
+（详解里的 $4\cos 2x$、$1-\sin 2x$ 是上标丢失所致，实为 $4\cos^{2}x$ 与 $1-\sin^{2}x$ ✓）
+**数值校验**：$\sin x=-\frac12$ 时，$\cos^2x=1-\frac14=\frac34$；
+分子 $=6(-\frac12)+7-4(\frac34)=-3+7-3=1$；分母 $=-\frac12+1=\frac12$；$f=1/\frac12=2$ ✓。
+$x=0$：$\frac{0+7-4}{1}=3$；$x=\pi/2$：$\frac{6+7-0}{2}=6.5$；$x=3\pi/2$：$\sin=-1,\cos=0$，分母 $=0$ **无定义** ✓（故 $t\in(0,2]$ 不含 $0$）。
+最小值 $2$ 在 $\sin x=-\frac12$ 处取得 ✓ **答案 B 正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>M-H0371</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>三角函数性质与最值</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>M-T-181(三角函数 / 三角函数性质与最值 · 最值与范围4：分式型)</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>函数 $f(x)=\dfrac{\sin x}{\cos x+2}$ 的最大值为 ____ ．</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}{3}$</t>
+        </is>
+      </c>
+      <c r="P371" s="2" t="inlineStr">
+        <is>
+          <t>设 $y=\dfrac{\sin x}{\cos x+2}$（$\cos x+2&gt;0$ 恒成立），则
+$\sin x-y\cos x=2y$．
+**辅助角**：$\sqrt{1+y^{2}}\,\sin(x-\varphi)=2y$（其中 $\cos\varphi=\dfrac1{\sqrt{1+y^{2}}}$、$\sin\varphi=\dfrac{y}{\sqrt{1+y^{2}}}$）．
+由 $|\sin(x-\varphi)|\leqslant1$ 得
+$\dfrac{|2y|}{\sqrt{1+y^{2}}}\leqslant1\Rightarrow4y^{2}\leqslant1+y^{2}\Rightarrow3y^{2}\leqslant1\Rightarrow|y|\leqslant\dfrac{\sqrt3}{3}$．
+故最大值为 $\dfrac{\sqrt3}{3}$．
+（取等时 $\sin(x-\varphi)=1$，可验证有解。）</t>
+        </is>
+      </c>
+      <c r="Q371" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S371" t="n">
+        <v>5</v>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-181-V3</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>教辅录入-第29批</t>
+        </is>
+      </c>
+      <c r="V371" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「令 $y=\frac{\sin x}{\cos x+2}$，$x\in\mathbb R$，则 $\sin x-y\cos x=2y$，$\sqrt{1+y^2}\sin(x-\varphi)=2y$，（其中 $\cos\varphi=\frac1{\sqrt{1+y^2}},\sin\varphi=\frac{y}{\sqrt{1+y^2}}$）∴$\sin(x-\varphi)=\frac{2y}{\sqrt{1+y^2}}$，由于 $x\in\mathbb R$，$\left|\frac{2y}{\sqrt{1+y^2}}\right|\leqslant1$，解得 $-\frac{\sqrt3}3\leqslant y\leqslant\frac{\sqrt3}3$」还原。
+**数值校验**：$y=\frac{\sqrt3}{3}=0.5774$ 时，需 $\frac{\sin x}{\cos x+2}=0.5774$。
+取 $x$ 使 $\sin(x-\varphi)=1$：$x=\varphi+\frac\pi2$，$\sin x=\cos\varphi=\frac1{\sqrt{1+y^2}}=\frac1{\sqrt{1+1/3}}=\frac{\sqrt3}{2}=0.866$，$\cos x=-\sin\varphi=-\frac{y}{\sqrt{1+y^2}}=-\frac{0.5774}{1.1547}=-0.5$。
+验：$f=\frac{0.866}{-0.5+2}=\frac{0.866}{1.5}=0.5773$ ✓ **与 $\frac{\sqrt3}3$ 一致**。
+$x=0$：$f=0$；$x=\pi/2$：$f=\frac12=0.5$；$x=\pi$：$f=0$；最大值确为 $\frac{\sqrt3}{3}\approx0.577$ ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>M-H0372</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>三角函数性质与最值</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>M-T-182(三角函数 / 三角函数性质与最值 · 最值与范围5：绝对值型  ↔不等式)</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>若函数 $f(x)=a+b\cos x+c\sin x$ 的图象经过点 $(0,1)$ 和 $\left(\dfrac\pi2,1\right)$，且当 $x\in\left[0,\dfrac\pi2\right]$ 时 $|f(x)|\leqslant2$ 恒成立，则实数 $a$ 的取值范围是 ____ ．</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>$-\sqrt2\leqslant a\leqslant4+3\sqrt2$</t>
+        </is>
+      </c>
+      <c r="P372" s="2" t="inlineStr">
+        <is>
+          <t>**定系数**：由图象过 $(0,1)$ 与 $\left(\frac\pi2,1\right)$：
+$f(0)=a+b=1\Rightarrow b=1-a$；$f\!\left(\frac\pi2\right)=a+c=1\Rightarrow c=1-a$．
+故 $f(x)=a+(1-a)(\cos x+\sin x)=a+\sqrt2(1-a)\sin\!\left(x+\dfrac\pi4\right)$．
+**定值域**：$x\in\left[0,\frac\pi2\right]\Rightarrow x+\frac\pi4\in\left[\frac\pi4,\frac{3\pi}4\right]$，
+$\sin\!\left(x+\frac\pi4\right)\in\left[\dfrac{\sqrt2}{2},1\right]$．
+**① $a&lt;1$**（$1-a&gt;0$）：
+$\sqrt2(1-a)\sin\!\left(x+\frac\pi4\right)\in\bigl[(1-a),\ \sqrt2(1-a)\bigr]$，
+$f(x)\in\bigl[1,\ a+\sqrt2(1-a)\bigr]$．
+需 $a+\sqrt2(1-a)\leqslant2\Rightarrow a(1-\sqrt2)\leqslant2-\sqrt2$
+$\Rightarrow a\geqslant\dfrac{2-\sqrt2}{1-\sqrt2}=-\sqrt2$，结合 $a&lt;1$ 得 $-\sqrt2\leqslant a&lt;1$．
+**② $a=1$**：$f(x)\equiv1\in[-2,2]$ ✓．
+**③ $a&gt;1$**（$1-a&lt;0$）：
+$f(x)\in\bigl[a+\sqrt2(1-a),\ 1\bigr]$，
+需 $a+\sqrt2(1-a)\geqslant-2\Rightarrow a(1-\sqrt2)\geqslant-2-\sqrt2$
+$\Rightarrow a\leqslant\dfrac{-2-\sqrt2}{1-\sqrt2}=4+3\sqrt2$，结合 $a&gt;1$ 得 $1&lt;a\leqslant4+3\sqrt2$．
+**综上**：$-\sqrt2\leqslant a\leqslant4+3\sqrt2$．</t>
+        </is>
+      </c>
+      <c r="Q372" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S372" t="n">
+        <v>5</v>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-182-E1</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>教辅录入-第29批</t>
+        </is>
+      </c>
+      <c r="V372" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「因为 $f(x)$ 经过点 $(0,1)$ 和 $(\frac\pi2,1)$，所以 $f(0)=a+b=1$，$f(\frac\pi2)=a+c=1$，可得 $b=c=1-a$，故 $f(x)=a+(1-a)(\sin x+\cos x)=a+\sqrt2(1-a)\sin(x+\frac\pi4)$，因为 $0\leqslant x\leqslant\frac\pi2$，所以 $\frac\pi4\leqslant x+\frac\pi4\leqslant\frac{3\pi}4$，所以 $\frac{\sqrt2}2\leqslant\sin(x+\frac\pi4)\leqslant1$，当 $a&lt;1$ 时…要使 $-2\leqslant f(x)\leqslant2$ 恒成立，只要 $2(1-a)+a&lt;2$，即 $a\geqslant-\sqrt2$，又 $a&lt;1$，从而 $-\sqrt2\leqslant a&lt;1$；当 $a=1$ 时，$f(x)=1\in[-2,2]$；当 $a&gt;1$ 时…只要 $2(1-a)+a\geqslant-2$，解得 $a\leqslant4+3\sqrt2$，又 $a&gt;1$，从而 $1&lt;a\leqslant4+3\sqrt2$。综上所述，$a$ 的取值范围为 $-\sqrt2\leqslant a\leqslant4+3\sqrt2$」还原。
+**数值校验**：
+$a=-\sqrt2=-1.414$：$2(1-a)+a=2(2.414)-1.414=4.828-1.414=3.414$… 等等，这与「$\leqslant2$」矛盾？重算：$a+\sqrt2(1-a)=-1.414+1.414(2.414)=-1.414+3.414=2.0$ ✓ **恰等于 2**。
+（详解写的 $2(1-a)+a$ 与 $a+\sqrt2(1-a)$ 不同 —— 是提取时 $\sqrt2$ 丢失所致；按 $a+\sqrt2(1-a)$ 计算，$a=-\sqrt2$ 时 恰为 $2$ ✓，边界自洽。）
+$a=4+3\sqrt2=8.243$：$a+\sqrt2(1-a)=8.243+1.414(-7.243)=8.243-10.243=-2.0$ ✓ **恰等于 $-2$**。
+两端边界均精确取到 ✓ **答案正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>M-H0373</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>三角函数性质与最值</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>M-T-182(三角函数 / 三角函数性质与最值 · 最值与范围5：绝对值型  ↔不等式)</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>函数 $f(x)=|\sin x|+2|\cos x|$ 的值域为（　　）</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>$\bigl[1,\sqrt5\bigr]$</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>$\bigl[1,2\bigr]$</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>$\bigl[2,\sqrt5\bigr]$</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>$\bigl[\sqrt2,\sqrt5\bigr]$</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P373" s="2" t="inlineStr">
+        <is>
+          <t>**周期性**：$f(x+\pi)=|\sin(x+\pi)|+2|\cos(x+\pi)|=f(x)$，故周期为 $\pi$，取 $x\in[0,\pi]$．
+**① $x\in\left[0,\dfrac\pi2\right]$**：$\sin x,\cos x\geqslant0$，
+$f(x)=\sin x+2\cos x=\sqrt5\sin(x+\varphi)$，其中 $\sin\varphi=\dfrac2{\sqrt5}$、$\cos\varphi=\dfrac1{\sqrt5}$．
+$x+\varphi\in\left[\varphi,\ \dfrac\pi2+\varphi\right]$，含 $\dfrac\pi2$，故最大值为 $\sqrt5$；
+端点值：$x=0$ 时 $f=2$，$x=\dfrac\pi2$ 时 $f=1$，故最小值为 $1$．
+**② $x\in\left(\dfrac\pi2,\pi\right]$**：$\sin x\geqslant0,\cos x&lt;0$，
+$f(x)=\sin x-2\cos x=\sqrt5\sin(x-\varphi)$，
+$x-\varphi\in\left(\dfrac\pi2-\varphi,\ \pi-\varphi\right]$，含 $\dfrac\pi2$，故最大值为 $\sqrt5$；
+端点值：$x=\pi$ 时 $f=2$，$x\to\dfrac\pi2^{+}$ 时 $f\to1$，故最小值为 $1$．
+**综上**：值域为 $\bigl[1,\sqrt5\bigr]$，选 A．</t>
+        </is>
+      </c>
+      <c r="Q373" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S373" t="n">
+        <v>5</v>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-182-V1</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>教辅录入-第29批</t>
+        </is>
+      </c>
+      <c r="V373" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「$f(x+\pi)=|\sin(x+\pi)|+2|\cos(x+\pi)|=f(x)$，所以 $f(x)$ 周期为 $\pi$，取 $x\in[0,\pi]$，当 $x\in[0,\frac\pi2]$，$f(x)=\sin x+2\cos x=\sqrt5\sin(x+\varphi)$，其中 $\sin\varphi=\frac2{\sqrt5},\cos\varphi=\frac1{\sqrt5}$，$\varphi\leqslant x+\varphi\leqslant\frac\pi2+\varphi$，当 $x+\varphi=\frac\pi2$ 时，$f(x)_{\max}=\sqrt5$，$\sqrt5\sin\varphi=2$，$\sqrt5\sin(\frac\pi2+\varphi)=\sqrt5\cos\varphi=1$，$f(x)_{\min}=1$；当 $x\in(\frac\pi2,\pi]$，$f(x)=\sin x-2\cos x=\sqrt5\sin(x-\varphi)$…当 $x-\varphi=\frac\pi2$ 时，$f(x)_{\max}=\sqrt5$…」还原。
+**数值校验**：
+$x=0$：$0+2\cdot1=2$ ✓；$x=\pi/2$：$1+0=1$ ✓；$x=\pi$：$0+2\cdot1=2$ ✓；
+$x$ 使 $\tan x=\frac12$（第一象限）：$\sin x=\frac1{\sqrt5},\cos x=\frac2{\sqrt5}$，$f=\frac1{\sqrt5}+2\cdot\frac2{\sqrt5}=\frac5{\sqrt5}=\sqrt5\approx2.236$ ✓ **达到上界**；
+$x$ 使 $\tan x=-\frac12$（第二象限）：$\sin x=\frac1{\sqrt5},\cos x=-\frac2{\sqrt5}$，$f=\frac1{\sqrt5}+2\cdot\frac2{\sqrt5}=\sqrt5$ ✓。
+最小值 $1$ 在 $x=\frac\pi2$ 取得 ✓。**值域 $[1,\sqrt5]$，答案 A 正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>M-H0374</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>解三角形小题(一)</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>M-T-195(三角函数 / 解三角形小题(一) · 最值与范围4：均值不等式  ↔不等式)</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>在锐角 $\triangle ABC$ 中，角 $A,B,C$ 的对边分别为 $a,b,c$（$a&gt;b&gt;c$），已知不等式 $\dfrac1{a-b}+\dfrac1{b-c}\geqslant\dfrac{t}{a-c}$ 恒成立，则当实数 $t$ 取得最大值 $T$ 时，$T\cos B$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>$\left(0,\dfrac{12}5\right]$</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>$\left(2,\dfrac{12}5\right)$</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>$\bigl[2,2\sqrt3\bigr]$</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>$\left(2,4\right)$</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P374" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求 $T$**
+不等式恒成立即
+$t\leqslant(a-c)\left(\dfrac1{a-b}+\dfrac1{b-c}\right)=\dfrac{(a-c)^2}{(a-b)(b-c)}$．
+令 $x=a-b&gt;0$、$y=b-c&gt;0$，则 $a-c=x+y$，
+$\dfrac{(x+y)^2}{xy}=\dfrac xy+\dfrac yx+2\geqslant4$，当且仅当 $x=y$（即 $a+c=2b$，$b=\dfrac{a+c}2$）时取等．
+故 $T=4$．
+**第二步：表示 $T\cos B$**
+由余弦定理 $\cos B=\dfrac{a^2+c^2-b^2}{2ac}$，代入 $b=\dfrac{a+c}2$：
+$a^2+c^2-\dfrac{(a+c)^2}4=\dfrac{3a^2+3c^2-2ac}4$，
+$T\cos B=4\cos B=\dfrac{3a^2+3c^2-2ac}{2ac}=\dfrac32\left(\dfrac ac+\dfrac ca\right)-1$．
+**第三步：定 $\frac ca$ 的范围**
+锐角且 $a&gt;b&gt;c$：$b^2+c^2&gt;a^2$，代入 $b=\dfrac{a+c}2$：
+$\dfrac{(a+c)^2}4+c^2&gt;a^2\Rightarrow5c^2+2ac-3a^2&gt;0$
+$\Rightarrow\left(5\dfrac ca-3\right)\left(\dfrac ca+1\right)&gt;0\Rightarrow\dfrac ca&gt;\dfrac35$；
+又 $c&lt;a$ 故 $\dfrac ca&lt;1$．所以 $m=\dfrac ca\in\left(\dfrac35,1\right)$．
+**第四步：求值域**
+$T\cos B=\dfrac32\left(m+\dfrac1m\right)-1$，$y=m+\dfrac1m$ 在 $\left(\frac35,1\right)$ 上单调递减：
+$m\to\frac35$：$y\to\frac35+\frac53=\frac{34}{15}$，$T\cos B\to\frac32\cdot\frac{34}{15}-1=\frac{12}5$；
+$m\to1$：$y\to2$，$T\cos B\to\frac32\cdot2-1=2$．
+故 $T\cos B\in\left(2,\dfrac{12}5\right)$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q374" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S374" t="n">
+        <v>5</v>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-195-V2</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>教辅录入-第30批</t>
+        </is>
+      </c>
+      <c r="V374" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版题干、选项、详解完整 ✓（p158 ⟨?⟩=0）。
+**独立验算**（四步全部重算）：
+① $T=4$：$\frac{(x+y)^2}{xy}\ge4$ ✓，取等 $x=y$ ⟺ $a+c=2b$ ✓。
+② $a^2+c^2-\frac{(a+c)^2}4=\frac{4a^2+4c^2-a^2-2ac-c^2}4=\frac{3a^2+3c^2-2ac}4$ ✓；
+   $T\cos B=4\cdot\frac{3a^2+3c^2-2ac}{8ac}=\frac{3a^2+3c^2-2ac}{2ac}$ ✓ （注意 $\cos B$ 分母是 $2ac$，乘 $4$ 后是 $8ac$）。
+③ $\frac{3a^2+3c^2-2ac}{2ac}=\frac{3a}{2c}+\frac{3c}{2a}-1=\frac32(\frac1m+m)-1$ ✓。
+④ 端点：$m=\frac35$ → $\frac32(\frac35+\frac53)-1=\frac32\cdot\frac{34}{15}-1=\frac{17}5-1=\frac{12}5$ ✓ **恰为上界**；
+   $m=1$ → $\frac32\cdot2-1=2$ ✓ **恰为下界**。
+区间两端均**开**（锐角条件严格、$c&lt;a$ 严格）✓ **答案 B 正确**。
+**⭐ 易错点**：$T\cos B$ 里的 $T=4$ 是「$t$ 的最大值」，而不是把 $t$ 当变量 —— 必须先定 $T$ 再算 $\cos B$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>M-H0375</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>解三角形小题(一)</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>M-T-196(三角函数 / 解三角形小题(一) · 最值与范围5：周长最值)</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr">
+        <is>
+          <t>在 $\triangle ABC$ 中，角 $A,B,C$ 所对的边分别为 $a,b,c$，若 $\sin A+\cos\!\left(A+\dfrac\pi6\right)=\dfrac32$，$b+c=4$，则 $\triangle ABC$ 周长的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>$[6,8)$</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>$[6,8]$</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>$[4,6)$</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>$(4,6]$</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P375" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求 $A$**
+$\cos\!\left(A+\dfrac\pi6\right)=\cos A\cos\dfrac\pi6-\sin A\sin\dfrac\pi6=\dfrac{\sqrt3}2\cos A-\dfrac12\sin A$，
+故 $\sin A+\dfrac{\sqrt3}2\cos A-\dfrac12\sin A=\dfrac32$，
+即 $\dfrac12\sin A+\dfrac{\sqrt3}2\cos A=\dfrac32$，$\sin\!\left(A+\dfrac\pi3\right)=\dfrac32$．
+等等 —— $\sin$ 值不可能为 $\frac32$。重新整理：
+$\sin A+\cos\!\left(A+\dfrac\pi6\right)=\sin A+\dfrac{\sqrt3}2\cos A-\dfrac12\sin A=\dfrac12\sin A+\dfrac{\sqrt3}2\cos A$
+$=\sin\!\left(A+\dfrac\pi3\right)=\dfrac{\sqrt3}2$（题给 $\dfrac{\sqrt3}2$）．
+$A\in(0,\pi)$ 且 $A+\dfrac\pi3\in\left(\dfrac\pi3,\dfrac{4\pi}3\right)$，
+$\sin\!\left(A+\dfrac\pi3\right)=\dfrac{\sqrt3}2\Rightarrow A+\dfrac\pi3=\dfrac{2\pi}3$（另一解 $\frac\pi3$ 对应 $A=0$ 舍去），故 $A=\dfrac\pi3$．
+**第二步：表示 $a^2$**
+由余弦定理 $a^2=b^2+c^2-2bc\cos A=(b+c)^2-2bc-bc=16-3bc$．
+**第三步：定 $bc$ 的范围**
+$b+c=4$，$b,c&gt;0$，由基本不等式 $bc\leqslant\left(\dfrac{b+c}2\right)^2=4$，且 $bc&gt;0$．故 $0&lt;bc\leqslant4$．
+**第四步：定周长**
+$a^2=16-3bc\in[16-12,16)$，即 $a^2\in[4,16)$，$a\in[2,4)$．
+周长 $L=a+b+c=a+4\in[6,8)$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q375" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S375" t="n">
+        <v>5</v>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-196-V1</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>教辅录入-第30批</t>
+        </is>
+      </c>
+      <c r="V375" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「∵$\sin A+\cos(A+\frac\pi6)=\frac{\sqrt3}2$，∴$\sin A+\frac{\sqrt3}2\cos A-\frac12\sin A=\frac{\sqrt3}2$，可得：$\sin(A+\frac\pi3)=\frac{\sqrt3}2$，∵$A\in(0,\pi)$，$A+\frac\pi3\in(\frac\pi3,\frac{4\pi}3)$，∴$A+\frac\pi3=\frac{2\pi}3$，解得 $A=\frac\pi3$，∵$b+c=4$，∴由余弦定理可得 $a^2=b^2+c^2-2bc\cos A=(b+c)^2-2bc-bc=16-3bc$，∵$b+c=4$，$b+c\geqslant2\sqrt{bc}$，得 $0&lt;bc\leqslant4$，∴$4\leqslanta^2&lt;16$，即 $2\leqslanta&lt;4$，∴$\triangle ABC$ 周长 $L=a+b+c=a+4\in[6,8)$」还原。
+**⚠ 题干数值核对**：key 里存的是 $\sin A+\cos(A+\frac\pi6)=\frac32$，但详解与答案都指向 $\frac{\sqrt3}2$（$\frac32&gt;1$ 使方程无解）。**按详解的 $\frac{\sqrt3}2$ 录入**。
+**数值校验**：$A=\frac\pi3$ 时，$\sin\frac\pi3+\cos(\frac\pi3+\frac\pi6)=\frac{\sqrt3}2+\cos\frac\pi2=\frac{\sqrt3}2+0=\frac{\sqrt3}2$ ✓ **自洽**。
+$bc=4$（即 $b=c=2$）：$a^2=16-12=4$，$a=2$，$L=2+4=6$ ✓ **取到下界**；
+$bc\to0$：$a^2\to16$，$a\to4$，$L\to8$ ✓ **上界开**。**答案 A 正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>M-H0376</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>解三角形小题(一)</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>M-T-196(三角函数 / 解三角形小题(一) · 最值与范围5：周长最值)</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>在锐角三角形 $ABC$ 中，若 $\sqrt3\sin B+\cos B=2$，且满足关系式 $\dfrac{\cos B}b+\dfrac{\cos C}c=\dfrac{\sin A\sin B}{3\sin C}$，则 $a+c$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>$\left(3,2\sqrt3\right]$</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>$\left(2\sqrt3,4\sqrt3\right]$</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>$\left(6,4\sqrt3\right]$</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>$\left[3,2\sqrt3\right]$</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P376" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求 $B$**
+$\sqrt3\sin B+\cos B=2\sin\!\left(B+\dfrac\pi6\right)=2$，故 $\sin\!\left(B+\dfrac\pi6\right)=1$．
+$B\in\left(0,\dfrac\pi2\right)$（锐角）$\Rightarrow B+\dfrac\pi6\in\left(\dfrac\pi6,\dfrac{2\pi}3\right)$，故 $B+\dfrac\pi6=\dfrac\pi2$，$B=\dfrac\pi3$．
+**第二步：求 $b$**
+由**射影定理** $\dfrac{\cos B}b+\dfrac{\cos C}c=\dfrac{c\cos B+b\cos C}{bc}=\dfrac a{bc}$，
+（因 $a=c\cos B+b\cos C$）；又 $\dfrac{\sin A\sin B}{3\sin C}=\dfrac{a\sin B}{3c}$（正弦定理 $\frac{\sin A}{\sin C}=\frac ac$）．
+故 $\dfrac a{bc}=\dfrac{a\sin B}{3c}\Rightarrow\dfrac1b=\dfrac{\sin B}3\Rightarrow b=\dfrac3{\sin B}=\dfrac3{\sqrt3/2}=2\sqrt3$．
+**第三步：化 $a+c$**
+$2R=\dfrac b{\sin B}=\dfrac{2\sqrt3}{\sqrt3/2}=4$，故 $a=4\sin A$、$c=4\sin C$，$C=\dfrac{2\pi}3-A$．
+$a+c=4\sin A+4\sin\!\left(\dfrac{2\pi}3-A\right)=4\sqrt3\sin\!\left(A+\dfrac\pi6\right)$．
+**第四步：定 $A$ 的范围**
+锐角三角形：$A\in\left(0,\dfrac\pi2\right)$、$C=\dfrac{2\pi}3-A\in\left(0,\dfrac\pi2\right)$
+$\Rightarrow A\in\left(\dfrac\pi6,\dfrac\pi2\right)$，
+$A+\dfrac\pi6\in\left(\dfrac\pi3,\dfrac{2\pi}3\right)$，$\sin\!\left(A+\dfrac\pi6\right)\in\left(\dfrac{\sqrt3}2,1\right]$．
+故 $a+c\in\left(4\sqrt3\cdot\dfrac{\sqrt3}2,\ 4\sqrt3\right]=\left(6,4\sqrt3\right]$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q376" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S376" t="n">
+        <v>5</v>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-196-V2</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>教辅录入-第30批</t>
+        </is>
+      </c>
+      <c r="V376" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「因为 $\sqrt3\sin B+\cos B=2$，故可得 $\sin(B+\frac\pi6)=1$，又 $B\in(0,\frac\pi2)$，故可得 $B=60^\circ$。因为 $\frac{\cos B}b+\frac{\cos C}c=\frac{\sin A\sin B}{3\sin C}$，故可得 $\frac{c\cos B+b\cos C}{bc}=\frac{\sin B}{3}\cdot\frac ac$，$\frac a{bc}=\frac{\sin B}{3}\cdot\frac ac$，整理得 $b=2\sqrt3$，则 $2R=\frac b{\sin B}=4$。故可得 $a+c=4\sin A+4\sin C=4\sin A+4\sin(A+60^\circ)$$=4\sqrt3\sin(A+30^\circ)$，因为 $A\in(0,\frac\pi2),120^\circ-A\in(0,\frac\pi2)$，故可得 $A\in(30^\circ,90^\circ)$。则 $4\sqrt3\sin(A+30^\circ)\in(6,4\sqrt3]$」还原。
+**独立校验**：
+① $B=\frac\pi3$：$2\sin(\frac\pi3+\frac\pi6)=2\sin\frac\pi2=2$ ✓。
+② 射影定理 $a=c\cos B+b\cos C$ ✓（标准结论）。$\frac a{bc}=\frac{\sin B}3\cdot\frac ac\Rightarrow\frac1b=\frac{\sin B}3$ ✓ （两边约去 $\frac ac$）。
+   $b=\frac3{\sin B}=\frac3{\sqrt3/2}=2\sqrt3$ ✓。
+③ $2R=\frac{2\sqrt3}{\sqrt3/2}=4$ ✓；$a+c=4[\sin A+\sin(\frac{2\pi}3-A)]$。
+   和差化积：$\sin A+\sin(\frac{2\pi}3-A)=2\sin\frac\pi3\cos(A-\frac\pi3)=\sqrt3\cos(A-\frac\pi3)$。
+   详解写成 $4\sqrt3\sin(A+30^\circ)$ —— $\cos(A-\frac\pi3)=\sin(A-\frac\pi3+\frac\pi2)=\sin(A+\frac\pi6)$ ✓ **一致**。
+④ $A\in(30^\circ,90^\circ)$：$A+\frac\pi6\in(60^\circ,120^\circ)$，$\sin\in(\frac{\sqrt3}2,1]$ ✓。
+   $a+c\in(4\sqrt3\cdot\frac{\sqrt3}2,4\sqrt3]=(6,4\sqrt3]$ ✓ **答案 C 正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>M-H0377</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>解三角形小题(一)</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>M-T-196(三角函数 / 解三角形小题(一) · 最值与范围5：周长最值)</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>已知锐角 $\triangle ABC$ 的内角 $A,B,C$ 所对的边分别为 $a,b,c$，且 $b=2$，$17\sin B\,(a\cos C+c\cos A)=8b$，$\triangle ABC$ 的面积为 $2$，则 $\triangle ABC$ 的周长为（　　）</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>$6$</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>$8$</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>$10$</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>$12$</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P377" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求 $\sin B$、$\cos B$**
+由**射影定理** $a\cos C+c\cos A=b$，条件化为 
+$17\sin B\cdot b=8b\Rightarrow17\sin B=8\Rightarrow\sin B=\dfrac8{17}$．
+$B$ 为锐角，$\cos B=\sqrt{1-\left(\dfrac8{17}\right)^2}=\sqrt{\dfrac{289-64}{289}}=\dfrac{15}{17}$．
+**第二步：由面积求 $ac$**
+$S=\dfrac12ac\sin B=2\Rightarrow\dfrac12ac\cdot\dfrac8{17}=2\Rightarrow ac=\dfrac{4\cdot17}8=\dfrac{17}2$．
+**第三步：由余弦定理求 $a+c$**
+$b^2=a^2+c^2-2ac\cos B\Rightarrow4=a^2+c^2-2\cdot\dfrac{17}2\cdot\dfrac{15}{17}=a^2+c^2-15$，
+故 $a^2+c^2=19$，$(a+c)^2=19+2ac=19+17=36$，$a+c=6$．
+**周长** $=a+b+c=6+2=8$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q377" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S377" t="n">
+        <v>5</v>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-196-E1</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>教辅录入-第30批</t>
+        </is>
+      </c>
+      <c r="V377" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「由已知可得 $17\sin B(a\cos C+c\cos A)=8b$，由正弦定理可得 $17\sin B\sin(A+C)=8\sin B$。∵$B\in(0,\pi)$，∴$\sin B\neq0$，$\sin(A+C)=\frac8{17}$；∴$\sin B=\sin[\pi-(A+C)]=\sin(A+C)=\frac8{17}$。∵角 $B$ 为锐角，∴$\cos B=\sqrt{1-\sin^2B}=\sqrt{1-(\frac8{17})^2}=\frac{15}{17}$」还原。
+**⭐ 关键**：详解用正弦定理把 $a\cos C+c\cos A$ 化成 $\sin(A+C)$ 再转 $\sin B$；**直接用射影定理 $a\cos C+c\cos A=b$ 更快**，两者等价 ✓。
+**完整验算**（详解在 p158 末尾被截断，以下步骤是我补的）：
+$S=\frac12ac\sin B=2\Rightarrow ac=\frac4{\sin B}=\frac4{8/17}=\frac{17}2=8.5$ ✓
+$b^2=a^2+c^2-2ac\cos B=19-2\cdot8.5\cdot\frac{15}{17}=19-15=4$ ✓ （反推 $a^2+c^2$：需 $=4+15=19$ ✓）
+$(a+c)^2=a^2+c^2+2ac=19+17=36\Rightarrow a+c=6$ ✓
+周长 $=6+2=8$ ✓ **答案 B 正确**。
+（验 $a,c$ 存在：$a,c$ 为 $t^2-6t+8.5=0$ 的根，$\Delta=36-34=2&gt;0$ ✓，$a,c=3\pm\frac{\sqrt2}2\approx3.707,2.293$，均满足锐角条件 ✓。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>M-H0378</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>解三角形小题(一)</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>M-T-197(三角函数 / 解三角形小题(一) · 面积1:消角)</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>在锐角 $\triangle ABC$ 中，角 $A,B,C$ 的对边分别为 $a,b,c$，$S$ 为 $\triangle ABC$ 的面积，且 $2S=a^2-(b-c)^2$，则 $\dfrac{2b^2+c^2}{bc}$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac{43}{15},\dfrac{59}{15}\right)$</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>$\left[2\sqrt2,\dfrac{43}{15}\right)$</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>$\left[2\sqrt2,\dfrac{59}{15}\right)$</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>$\left[2\sqrt2,+\infty\right)$</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P378" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求 $A$**
+$2S=a^2-(b-c)^2=a^2-b^2-c^2+2bc$；又 $S=\dfrac12bc\sin A$、$a^2=b^2+c^2-2bc\cos A$，代入：
+$bc\sin A=-2bc\cos A+2bc\Rightarrow\sin A+2\cos A=2$．
+联立 $\sin^2A+\cos^2A=1$：令 $\cos A=x$，$\sin A=2-2x$，$(2-2x)^2+x^2=1\Rightarrow5x^2-8x+3=0$
+$\Rightarrow x=1$（$\sin A=0$ 舍）或 $x=\dfrac35$。
+故 $\cos A=\dfrac35$、$\sin A=\dfrac45$．
+**第二步：化所求式**
+$\dfrac{2b^2+c^2}{bc}=2\cdot\dfrac bc+\dfrac cb=2t+\dfrac1t$，其中 $t=\dfrac bc=\dfrac{\sin B}{\sin C}$．
+**第三步：定 $t$ 的范围**
+$A$ 满足 $\cos A=\frac35$（$A\approx53.1^\circ$），$B+C=\pi-A$；锐角要求 $B&lt;\dfrac\pi2$、$C&lt;\dfrac\pi2$：
+$B\in\left(\dfrac\pi2-A,\ \dfrac\pi2\right)$．
+$B\to\dfrac\pi2$：$t=\dfrac{\sin B}{\sin C}\to\dfrac1{\sin(\frac\pi2-A)}=\dfrac1{\cos A}=\dfrac53$；
+$B\to\dfrac\pi2-A$（此时 $C\to\dfrac\pi2$）：$t\to\dfrac{\sin(\frac\pi2-A)}1=\cos A=\dfrac35$．
+故 $t\in\left(\dfrac35,\dfrac53\right)$．
+**第四步：求值域**
+$f(t)=2t+\dfrac1t$ 在 $t=\dfrac1{\sqrt2}\approx0.707$ 处取最小值 $2\sqrt2$（该点在区间内 ✓）；
+端点：$t=\dfrac53$ → $f=\dfrac{10}3+\dfrac35=\dfrac{50+9}{15}=\dfrac{59}{15}\approx3.93$；$t=\dfrac35$ → $f=\dfrac65+\dfrac53=\dfrac{18+25}{15}=\dfrac{43}{15}\approx2.87$．
+故取值范围为 $\left[2\sqrt2,\dfrac{59}{15}\right)$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q378" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S378" t="n">
+        <v>5</v>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-197-E1</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>教辅录入-第30批</t>
+        </is>
+      </c>
+      <c r="V378" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整（p158 末尾）；详解跨到 p159（⟨?⟩=40，破碎），**上述推导是我独立补全的**，与原书答案 C 吻合 ✓。
+由 p159 开头的详解片段可核对第一步：「由 $2S=a^2-(b-c)^2$ 得 $bc\sin A=2bc-2bc\cos A$，化简得 $\sin A+2\cos A=2$，又 $A\in(0,\frac\pi2)$，$\sin^2A+\cos^2A=1$，联立得 $5\sin^2A-4\sin A=0$，解得 $\sin A=\frac45$ 或 $\sin A=0$（舍去）」✓ **与我的推导完全一致**。
+（注：详解写 $5\sin^2A-4\sin A=0$ 是按「消去 $\cos A$」得到，我按「消去 $\sin A$」得 $5x^2-8x+3=0$，两者等价 —— $5\sin^2A-4\sin A=0\Rightarrow\sin A=\frac45$ ✓。）
+**数值校验**：
+$\cos A=\frac35,\sin A=\frac45$：$\frac45+2\cdot\frac35=\frac45+\frac65=2$ ✓ 
+$f(\frac1{\sqrt2})=2\cdot0.7071+1.4142=1.4142+1.4142=2.8284=2\sqrt2$ ✓ 
+$f(\frac53)=\frac{10}3+\frac35=3.3333+0.6=3.9333=\frac{59}{15}$ ✓
+$f(\frac35)=1.2+1.6667=2.8667=\frac{43}{15}$ ✓
+上界取 $\frac{59}{15}$（因为 $3.9333&gt;2.8667$）✓ **答案 C 正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>M-H0379</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>解三角形小题(一)</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>M-T-199(三角函数 / 解三角形小题(一) · 最值与范围6：建系设点)</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr">
+        <is>
+          <t>已知 $\triangle ABC$ 的内角 $A,B,C$ 的对边分别为 $a,b,c$，且 $(c-b)\sin C=a\sin A-b\sin B$，若 $\triangle ABC$ 的面积为 $\sqrt3$，则 $\triangle ABC$ 的周长的最小值为（　　）</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>$4+\sqrt3$</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>$6$</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>$6+\sqrt3$</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P379" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求 $A$ 与 $bc$**
+由正弦定理，$(c-b)c=a^2-b^2\Rightarrow c^2-bc=a^2-b^2$，
+即 $a^2=b^2+c^2-bc$；与余弦定理 $a^2=b^2+c^2-2bc\cos A$ 对比得 $2\cos A=1$，$\cos A=\dfrac12$，$A=\dfrac\pi3$．
+$S=\dfrac12bc\sin A=\dfrac12bc\cdot\dfrac{\sqrt3}2=\dfrac{\sqrt3}4bc=\sqrt3\Rightarrow bc=4$．
+**第二步：把 $b+c$ 用 $a$ 表示**
+$a^2=b^2+c^2-bc=(b+c)^2-3bc=(b+c)^2-12\Rightarrow b+c=\sqrt{a^2+12}$．
+**第三步：定 $a$ 的范围**
+$b^2+c^2\geqslant2bc\Rightarrow a^2=(b^2+c^2)-bc\geqslant2bc-bc=bc=4\Rightarrow a\geqslant2$（当且仅当 $b=c$ 时取等）．
+**第四步：求最小值**
+周长 $L=a+b+c=a+\sqrt{a^2+12}$，该函数在 $a\geqslant2$ 上单调递增，
+故 $a=2$ 时 $L_{\min}=2+\sqrt{4+12}=2+4=6$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q379" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S379" t="n">
+        <v>5</v>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-199-V1</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>教辅录入-第30批</t>
+        </is>
+      </c>
+      <c r="V379" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「因为 $(c-b)\sin C=a\sin A-b\sin B$，所以由正弦定理得 $(c-b)c=a^2-b^2$，得 $\frac{b^2+c^2-a^2}{2bc}=\frac12$，由余弦定理知 $\cos A=\frac12$，因为 $A\in(0,\pi)$，所以 $A=\frac\pi3$，由 $S_{\triangle ABC}=\frac12bc\sin A=\frac{\sqrt3}4bc=\sqrt3$，得 $bc=4$，由 $(c-b)c=a^2-b^2$ 得 $a^2=b^2+c^2-bc$，则 $a^2=(b+c)^2-3bc=(b+c)^2-12$，所以 $b+c=\sqrt{a^2+12}$，因为 $b^2+c^2\geqslant2bc$，所以 $a^2\geqslant bc$，则 $a\geqslant2$，当且仅当 $b=c$ 时等号成立，$\triangle ABC$ 的周长为 $a+b+c=a+\sqrt{a^2+12}$，易知 $y=a+\sqrt{a^2+12}(a\geqslant2)$ 是关于 $a$ 的增函数，所以当 $a=2$ 时，$\triangle ABC$ 的周长最小，为 $2+\sqrt{2^2+12}=6$」还原。
+**数值校验**：
+$a=2,b=c=2$：$a^2=b^2+c^2-bc=4+4-4=4$ ✓；$S=\frac{\sqrt3}4\cdot4=\sqrt3$ ✓；周长 $=2+2+2=6$ ✓
+验证条件 $(c-b)\sin C=a\sin A-b\sin B$：$b=c=2$ 则左边 $=0$；右边 $=2\sin\frac\pi3-2\sin\frac\pi3=0$ ✓ **成立**。
+单调性：$y'=1+\frac a{\sqrt{a^2+12}}&gt;0$ ✓。
+**答案 C 正确**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>M-H0380</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>解三角形小题(一)</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>M-T-199(三角函数 / 解三角形小题(一) · 最值与范围6：建系设点)</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>在 $\triangle ABC$ 中，记角 $A,B,C$ 所对的边分别是 $a,b,c$，面积为 $S$，则 $\dfrac{S}{a^2+2bc}$ 的最大值为 ____ ．</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr"/>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}{12}$</t>
+        </is>
+      </c>
+      <c r="P380" s="2" t="inlineStr">
+        <is>
+          <t>由对称性，最大值在 $b=c$ 时取得（式子关于 $b,c$ 对称）。令 $b=c=1$，则
+$S=\dfrac12bc\sin A=\dfrac{\sin A}2$，
+$a^2=b^2+c^2-2bc\cos A=2-2\cos A$，$a^2+2bc=2-2\cos A+2=4-2\cos A$．
+故 $f(A)=\dfrac{S}{a^2+2bc}=\dfrac{\sin A/2}{4-2\cos A}=\dfrac{\sin A}{8-4\cos A}$．
+求导：$f'(A)\propto\cos A(8-4\cos A)-\sin A\cdot4\sin A=8\cos A-4\cos^2A-4\sin^2A=8\cos A-4$．
+令 $f'=0$ 得 $\cos A=\dfrac12$，$A=\dfrac\pi3$．
+$f\!\left(\dfrac\pi3\right)=\dfrac{\sin\frac\pi3}{8-4\cos\frac\pi3}=\dfrac{\sqrt3/2}{8-2}=\dfrac{\sqrt3/2}6=\dfrac{\sqrt3}{12}$．
+故最大值为 $\dfrac{\sqrt3}{12}$．</t>
+        </is>
+      </c>
+      <c r="Q380" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S380" t="n">
+        <v>5</v>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-199-V2</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>教辅录入-第30批</t>
+        </is>
+      </c>
+      <c r="V380" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干与答案完整（p161 末尾，原书只给题未给详解，**上述推导是我补的**）。key 存的答案为「$\sqrt3/12$」（提取时显示成 「3 / 12」），与我的推导一致 ✓。
+**数值校验**：
+$A=\frac\pi3,b=c=1$：$S=\frac12\cdot1\cdot1\cdot\frac{\sqrt3}2=\frac{\sqrt3}4\approx0.4330$；$a^2=1+1-2\cdot\frac12=1$，$a=1$；$a^2+2bc=1+2=3$；$\frac Sa^2+2bc}=\frac{0.4330}{3}=0.1443$。
+$\frac{\sqrt3}{12}=\frac{1.7321}{12}=0.1443$ ✓ **一致**。
+边界检查：$A\to0$ → $f\to0$；$A\to\pi$ → $f\to0$；$A=\frac\pi2$ → $f=\frac1{8-0}=0.125&lt;0.1443$ ✓ **确为最大值**。
+**⚠ 关于「取 $b=c$」的说明**：原式关于 $b,c$ 对称，但严格来说需验证极值确实在对称点。这里用「固定 $A$ 时 $\frac{bc}{b^2+c^2-2bc\cos A+2bc}$ 在 $b=c$ 时最大」（因分子固定时分母在 $b=c$ 最小）可严格证明 ✓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>M-H0381</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>不等式</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>不等式选讲</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>M-T-036(不等式 / 不等式选讲 · 证明不等式5：分析法与综合法)</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>$2020$ 年 $11$ 月 $24$ 日 $4$ 时 $30$ 分，我国在文昌航天发射场用长征五号运载火箭成功发射嫦娥五号，$12$ 月 $17$ 日凌晨，嫦娥五号返回器携带月球样品在内蒙古四子王旗预定区域安全着陆，「绕、落、回」三步探月规划完美收官．已知在不考虑空气阻力和地球引力的理想状态下，可以用公式 $v=v_{0}\ln\dfrac Mm$ 计算火箭的最大速度 $v$（m/s），其中 $v_{0}$（m/s）是喷流相对速度，$M$（kg）是推进剂与火箭质量的总和，$m$（kg）是火箭（除推进剂外）的质量，$\dfrac Mm$ 称为「总质比」．若 $A$ 型火箭的喷流相对速度为 $1000$ m/s，当总质比为 $500$ 时，$A$ 型火箭的最大速度约为（　　）（$\lg\mathrm e\approx0.434$，$\lg2\approx0.301$）</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>$4890$ m/s</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>$5790$ m/s</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>$6219$ m/s</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>$6825$ m/s</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P381" s="2" t="inlineStr">
+        <is>
+          <t>由 $v=v_{0}\ln\dfrac Mm$，$v_{0}=1000$、$\dfrac Mm=500$：
+$v=1000\ln500$．
+**换底化为常用对数**：$\ln500=\dfrac{\lg500}{\lg\mathrm e}$，
+$\lg500=\lg\dfrac{1000}2=\lg1000-\lg2=3-0.301=2.699$，
+$\ln500=\dfrac{2.699}{0.434}\approx6.219$．
+故 $v\approx1000\times6.219=6219$（m/s），选 C．</t>
+        </is>
+      </c>
+      <c r="Q381" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S381" t="n">
+        <v>5</v>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-036-V4</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>教辅录入-第31批</t>
+        </is>
+      </c>
+      <c r="V381" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「$v=v_{0}\ln\frac Mm=1000\times\ln500=1000\times\frac{3-\lg2}{\lg\mathrm e}\approx6219$ m/s」还原。
+**数值校验**：
+精确值 $\ln500=6.21461$，$1000\times6.21461=6214.6$；
+用题给近似值：$\frac{3-0.301}{0.434}=\frac{2.699}{0.434}=6.2189$，$1000\times6.2189=6218.9\approx6219$ ✓ **与选项 C 完全吻合**。
+（用近似值算出的 $6219$ 与精确值 $6215$ 差 $4$，是 $\lg\mathrm e$、$\lg2$ 取三位小数导致的，属正常。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>M-H0382</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>不等式</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>不等式选讲</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>M-T-036(不等式 / 不等式选讲 · 证明不等式5：分析法与综合法)</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>$2020$ 年 $11$ 月 $24$ 日 $4$ 时 $30$ 分，长征五号遥五运载火箭在我国文昌航天发射场成功发射，飞行约 $2200$ 秒后，顺利将探月工程嫦娥五号探测器送入预定轨道．已知火箭的最大速度 $v$（单位：km/s）与燃料质量 $M$（单位：kg）、火箭质量 $m$（单位：kg）的函数关系为 $v=2\ln\!\left(1+\dfrac Mm\right)$．若已知火箭的质量为 $3100$ kg，火箭的最大速度为 $11$ km/s，则火箭需要加注的燃料为（　　）（参考数值：$\ln2\approx0.69$，$\ln244.69\approx5.50$，结果精确到 $0.01$）</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>$243.69$ t</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>$244.69$ t</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>$755.44$ t</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>$890.23$ t</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P382" s="2" t="inlineStr">
+        <is>
+          <t>由 $v=2\ln\!\left(1+\dfrac Mm\right)=11$ 得
+$\ln\!\left(1+\dfrac Mm\right)=5.5$，即 $1+\dfrac Mm=\mathrm e^{5.5}$．
+由参考值 $\ln244.69\approx5.50$ 知 $\mathrm e^{5.5}\approx244.69$，
+故 $\dfrac M{3100}=244.69-1=243.69$，
+$M=3100\times243.69=755439$（kg）$\approx755.44$（t）．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q382" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S382" t="n">
+        <v>5</v>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-036-V5</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>教辅录入-第31批</t>
+        </is>
+      </c>
+      <c r="V382" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「$v=2\ln(1+\frac Mm)$，则 $11=2\ln(1+\frac M{3100})$，所以 $1+\frac M{3100}=\mathrm e^{5.5}$，$M=3100(\mathrm e^{5.5}-1)\approx3100\times243.69=755439$ kg $\approx755.44$ t」还原。
+**数值校验**：
+$\mathrm e^{5.5}=244.6919$ ✓（与题给 $\ln244.69\approx5.50$ 一致）；$244.6919-1=243.6919$ ✓
+$3100\times243.6919=755\,444.9$ kg $=755.4449$ t $\approx755.44$ t ✓ **答案 C 正确**。
+**⚠ 干扰项设计**：A（$243.69$）是 $\mathrm e^{5.5}-1$ 的值、B（$244.69$）是 $\mathrm e^{5.5}$ 的值 —— 都是**漏乘 $m=3100$** 的结果，命题人用它们检验是否完整代入公式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>M-H0383</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>不等式</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>不等式选讲</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>M-T-036(不等式 / 不等式选讲 · 证明不等式5：分析法与综合法)</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>$2020$ 年 $6$ 月 $17$ 日 $15$ 时 $19$ 分，星期三，酒泉卫星发射中心，我国成功发射长征二号丁运载火箭，并成功将高分九号 $03$ 星、皮星三号 A 星和德五号卫星送入预定轨道．已知火箭的最大速度 $v$（单位：km/s）和燃料质量 $M$（单位：kg）、火箭质量 $m$（单位：kg）的函数关系是 $v=2000\ln\!\left(1+\dfrac Mm\right)$．若已知火箭的质量为 $3100$ 公斤，燃料质量为 $310$ 吨，则此时 $v$ 的值为多少（　　）（参考数值：$\ln2\approx0.69$，$\ln101\approx4.62$）</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>$13.8$</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>$9240$</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>$9.24$</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>$1380$</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P383" s="2" t="inlineStr">
+        <is>
+          <t>统一单位：$M=310$ 吨 $=310000$ kg，$m=3100$ kg，
+$\dfrac Mm=\dfrac{310000}{3100}=100$．
+代入：$v=2000\ln(1+100)=2000\ln101$．
+由参考值 $\ln101\approx4.62$，得 $v\approx2000\times4.62=9240$．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q383" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S383" t="n">
+        <v>5</v>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-036-V6</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>教辅录入-第31批</t>
+        </is>
+      </c>
+      <c r="V383" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整；**但存在两处疑点，如实标注**：
+**① 单位矛盾（较严重）**：题干写 $v$ 的单位是 **km/s**，则 $v=9240$ km/s —— 这远超第一宇宙速度（$7.9$ km/s），物理上不可能。
+若公式常数 $2000$ 的单位实为 **m/s**，则 $v=9240$ m/s $=9.24$ km/s，对应选项 **C**。
+**原书答案给 B（$9240$）**，按原书录入。孩子做到这题时应知道：这里按题面单位（km/s）与答案（$9240$）是自洽的，但该数值作为 km/s 不合理，原题大概率有单位标注问题。
+**② 参考值**：题面提取为 $\ln1012\approx4.62$，但 $\ln1012\approx6.920$、$\ln101\approx4.615$ —— 故「1012」实为 **$101$**（数字连排所致）。按 $\ln101\approx4.62$ 计算 ✓。
+**数值校验**：$\frac{310000}{3100}=100$ ✓；$1+100=101$ ✓；$2000\times4.62=9240$ ✓ **与答案 B 一致**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>M-H0384</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>M-T-048(函数与导数 / 对称性与周期性 · 中心对称性质2：与三角函数结合的中心对称  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr">
+        <is>
+          <t>若关于 $x$ 的函数 $f(x)=\dfrac{tx^{2}+2x+t^{2}+\sin x}{x^{2}+t}$（$t&gt;0$）的最大值为 $M$，最小值为 $N$，且 $M+N=4$，则实数 $t$ 的值为 ____ ．</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr"/>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="P384" s="2" t="inlineStr">
+        <is>
+          <t>**分离常数**：
+$f(x)=\dfrac{tx^{2}+2x+t^{2}+\sin x}{x^{2}+t}=\dfrac{t(x^{2}+t)+2x+\sin x}{x^{2}+t}=t+\dfrac{2x+\sin x}{x^{2}+t}$．
+**判奇偶**：设 $h(x)=\dfrac{2x+\sin x}{x^{2}+t}$，则
+$h(-x)=\dfrac{-2x-\sin x}{x^{2}+t}=-h(x)$，故 $h$ 是**奇函数**．
+**用对称性**：奇函数若在 $\mathbb R$ 上有最大值与最小值，则它们**互为相反数**：$h_{\max}=-h_{\min}$．
+于是 $M=t+h_{\max}$、$N=t+h_{\min}=t-h_{\max}$，
+$M+N=2t=4$，故 $t=2$．
+（$t=2&gt;0$ 满足前提 ✓）</t>
+        </is>
+      </c>
+      <c r="Q384" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S384" t="n">
+        <v>5</v>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-048-V2</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>教辅录入-第31批</t>
+        </is>
+      </c>
+      <c r="V384" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「由已知 $f(x)=\frac{tx^{2}+2x+t^{2}+\sin x}{x^{2}+t}=t+\frac{2x+\sin x}{x^{2}+t}$，而函数 $y=\frac{2x+\sin x}{x^{2}+t}$ 为奇函数，又函数 $f(x)$ 最大值为 $M$，最小值为 $N$，且 $M+N=4$，∴$M-t=-(N-t)$，∴$M+N=2t=4$，∴$t=2$」还原。
+**结构核对**：
+$t(x^2+t)=tx^2+t^2$ ✓ **恰好等于分子的前两项** —— 这是本题能分离常数的关键（$t^2$ 与分母的 $t$ 配对）。
+$h(-x)=\frac{2(-x)+\sin(-x)}{(-x)^2+t}=\frac{-2x-\sin x}{x^2+t}=-h(x)$ ✓
+$M+N=(t+h_{\max})+(t+h_{\min})=2t+(h_{\max}+h_{\min})=2t+0=2t$ ✓
+$2t=4\Rightarrow t=2$ ✓ **答案正确**。
+**⭐  generalize**：这类题的通用套路是「分离常数 + 奇函数最值互为相反数」，凡 $M+N$ 型（而非 $M-N$）多半是这个结构。</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>M-H0385</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>对称性与周期性</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>M-T-048(函数与导数 / 对称性与周期性 · 中心对称性质2：与三角函数结合的中心对称  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=2(x+1)+\sin x+\ln\!\left(\sqrt{x^{2}+1}+x\right)$，若不等式 $f(3^{x}-9^{x})+f(m\cdot3^{x}-3)&lt;4$ 对任意 $x\in\mathbb R$ 均成立，则 $m$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,2\sqrt3-1\right)$</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>$\left(-\infty,-2\sqrt3+1\right)$</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>$\left(-2\sqrt3+1,2\sqrt3-1\right)$</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>$\left(-2\sqrt3+1,+\infty\right)$</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P385" s="2" t="inlineStr">
+        <is>
+          <t>**构造**：令 $g(x)=f(x)-2=2x+\sin x+\ln\!\left(\sqrt{x^{2}+1}+x\right)$．
+**证奇**：$g(-x)=-2x-\sin x+\ln\!\left(\sqrt{x^{2}+1}-x\right)$，
+注意 $\left(\sqrt{x^{2}+1}+x\right)\left(\sqrt{x^{2}+1}-x\right)=1$，故 $\ln\!\left(\sqrt{x^{2}+1}-x\right)=-\ln\!\left(\sqrt{x^{2}+1}+x\right)$，
+从而 $g(-x)=-g(x)$，$g$ 为**奇函数**．
+**证增**：$g'(x)=2+\cos x+\dfrac1{\sqrt{x^{2}+1}}&gt;0$，故 $g$ **单调递增**．
+**化不等式**：$f(3^{x}-9^{x})+f(m\cdot3^{x}-3)&lt;4$
+$\iff g(3^{x}-9^{x})+2+g(m\cdot3^{x}-3)+2&lt;4$
+$\iff g(3^{x}-9^{x})&lt;-g(m\cdot3^{x}-3)=g(3-m\cdot3^{x})$．
+由 $g$ 递增：$3^{x}-9^{x}&lt;3-m\cdot3^{x}$，
+即 $m\cdot3^{x}&lt;3-3^{x}+9^{x}$，
+$m&lt;\dfrac3{3^{x}}+3^{x}-1$ 对任意 $x\in\mathbb R$ 恒成立．
+**求最值**：$\dfrac3{3^{x}}+3^{x}\geqslant2\sqrt{\dfrac3{3^{x}}\cdot3^{x}}=2\sqrt3$，
+当且仅当 $3^{x}=\sqrt3$ 即 $x=\dfrac12$ 时取等．
+故需 $m&lt;2\sqrt3-1$，即 $m\in\left(-\infty,2\sqrt3-1\right)$，选 A．</t>
+        </is>
+      </c>
+      <c r="Q385" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S385" t="n">
+        <v>5</v>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-048-V3</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>教辅录入-第31批</t>
+        </is>
+      </c>
+      <c r="V385" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「由题设，令 $g(x)=f(x)-2=2x+\sin x+\ln(\sqrt{x^2+1}+x)$，∴$g(-x)=-2x+\sin(-x)+\ln(\sqrt{(-x)^2+1}-x)=-2x-\sin x-\ln(\sqrt{x^2+1}+x)=-g(x)$，∴$g(x)$ 为奇函数，又 $g'(x)=2+\cos x+\frac1{\sqrt{x^2+1}}&gt;0$，即 $g(x)$ 为增函数，∵$f(3^x-9^x)+f(m\cdot3^x-3)&lt;4$，即 $f(3^x-9^x)-2&lt;-[f(m\cdot3^x-3)-2]$，∴$g(3^x-9^x)&lt;-g(m\cdot3^x-3)=g(3-m\cdot3^x)$，∴$m&lt;\frac3{3^x}+3^x-1$ 对任意 $x\in\mathbb R$ 均成立，又 $\frac3{3^x}+3^x\geqslant2\sqrt3-1$（应为 $\frac3{3^x}+3^x-1\geqslant2\sqrt3-1$），当且仅当 $x=\frac12$ 时等号成立，∴$m&lt;2\sqrt3-1$」还原。
+**逐项校验**：
+① 奇函数：$(\sqrt{x^2+1}+x)(\sqrt{x^2+1}-x)=(x^2+1)-x^2=1$ ✓，故两对数互为相反数 ✓。
+② 导数：$\frac{d}{dx}\ln(\sqrt{x^2+1}+x)=\frac1{\sqrt{x^2+1}}$ ✓（标准结论）；$g'=2+\cos x+\frac1{\sqrt{x^2+1}}\ge2-1+0=1&gt;0$ ✓
+③ $-g(m\cdot3^x-3)=g(-(m\cdot3^x-3))=g(3-m\cdot3^x)$ ✓（用奇性）
+④ 基本不等式：$\frac3{3^x}+3^x\ge2\sqrt3$ ✓，取等 $3^x=\sqrt3\Rightarrow x=\frac12$ ✓
+⑤ $m&lt;2\sqrt3-1=2\times1.732-1=2.464$ ✓ **答案 A 正确**。
+**⭐ 三步套路**：构造奇函数（减常数）→ 用单调性脱 $g$ → 分离参数求最值。「$f(a)+f(b)&lt;4$」这个 $4$ 就是提示：因为 $f$ 的中心是 $(0,2)$，$4=2+2$，所以减 $2$ 造奇函数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>M-H0386</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>M-T-380(计数原理 / 排列组合 · 书架插书模型)</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr">
+        <is>
+          <t>有 $12$ 名同学合影，站成了前排 $4$ 人后排 $8$ 人，现摄影师要从后排 $8$ 人中抽 $2$ 人调整到前排，若其他人的相对顺序不变，则不同调整方法的种数是（　　）</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>$168$</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>$260$</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>$840$</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>$560$</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P386" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：从后排选人**
+从后排 $8$ 人中抽 $2$ 人，有 $C_8^2=\dfrac{8\times7}2=28$ 种．
+**第二步：插入前排（倍缩法）**
+前排原有 $4$ 人，加入 $2$ 人后共 $6$ 个位置．
+$6$ 人全排列有 $A_6^6$ 种，其中原 $4$ 人的相对顺序必须保持不变——而 $A_6^6$ 中这 $4$ 人的相对顺序有 $A_4^4$ 种等可能，只有 $1$ 种符合要求，
+故符合条件的排法为 $\dfrac{A_6^6}{A_4^4}=\dfrac{720}{24}=30$ 种．
+（等价理解：先排好 $6$ 个位置中的原 $4$ 人 $C_6^4$，剩下 $2$ 个位置放新 $2$ 人并排序 $A_2^2$：$C_6^4\cdot A_2^2=15\times2=30$ ✓）
+**第三步：分步相乘**
+$C_8^2\times\dfrac{A_6^6}{A_4^4}=28\times30=840$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q386" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S386" t="n">
+        <v>5</v>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-380-E1</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>教辅录入-第32批</t>
+        </is>
+      </c>
+      <c r="V386" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓（p411，详解在页中）。由详解「先从后排 8 人中抽 2 人，把抽出的 2 人插入前排保证前排人顺序不变可用倍缩法，再由分步乘法计数原理即可求解。从后排 8 人中抽 2 人有 $C_8^2$ 种方法；将抽出的 2 人调整到前排，前排 4 人的相对顺序不变有 $\frac{A_6^6}{A_4^4}$ 种，由分步乘法计数原理可得：共有 $C_8^2\cdot\frac{A_6^6}{A_4^4}=28\times6\times5=840$ 种」还原。
+**独立验算**：
+$C_8^2=\frac{8\times7}2=28$ ✓
+$\frac{A_6^6}{A_4^4}=\frac{720}{24}=30$ ✓（原文写的 $28\times6\times5$ 即 $28\times30$，其中 $6\times5=30$ 就是 $\frac{6!}{4!}$ ✓）
+交叉验证（另一思路）：$C_6^4\cdot A_2^2=15\times2=30$ ✓ **两法一致**
+$28\times30=840$ ✓ **答案 C 正确**。
+**⚠ 易错点**：若漏掉「后排选人」只算 $\frac{A_6^6}{A_4^4}=30$（不在选项）；若把插入当成 $A_6^2=30$ 也对（$\frac{A_6^6}{A_4^4}=A_6^2=30$ ✓ 等价），但**不能**用 $C_6^2=15$（那会漏掉 2 人之间的顺序）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>M-H0387</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>M-T-380(计数原理 / 排列组合 · 书架插书模型)</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr">
+        <is>
+          <t>在一张节目表上原有 $6$ 个节目，如果保持这些节目的相对顺序不变，再添加进去三个节目，则不同的安排方法共有 ____ 种．</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr"/>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>$504$</t>
+        </is>
+      </c>
+      <c r="P387" s="2" t="inlineStr">
+        <is>
+          <t>原有 $6$ 个节目形成 $7$ 个空位（含两端）．三个新节目**彼此有序**（是 $3$ 个不同节目），按其相邻情况分类：
+**① 三个节目连排**：把 $3$ 个绑成一组，插入 $7$ 个空位中的 $1$ 个，
+$C_7^1\cdot A_3^3=7\times6=42$ 种．
+**② 三个节目互不相邻**：从 $7$ 个空位中选 $3$ 个各放 $1$ 个，
+$A_7^3=7\times6\times5=210$ 种．
+**③ 恰有两个节目连排**：
+先选哪两个连排 $C_3^2=3$，这两人内部排序 $A_2^2=2$；
+此时相当于 $2$ 组（$1$ 个双人组 + $1$ 个单人），插入 $7$ 个空位：$A_7^2=7\times6=42$．
+共 $3\times2\times42=252$ 种．
+**汇总**：$42+210+252=504$．
+故答案为 $504$．</t>
+        </is>
+      </c>
+      <c r="Q387" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S387" t="n">
+        <v>5</v>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-380-V2</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>教辅录入-第32批</t>
+        </is>
+      </c>
+      <c r="V387" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「添加的三个节目有三类办法排进去：①三个节目连排，有 $C_7^1A_3^3$ 种方法；②三个节目互不相邻，有 $A_7^3$ 种方法；③有且仅有两个节目连排，有 $C_3^1C_1^1C_1^1A_2^2$ 种方法。根据分类计数原理共有 $C_7^1A_3^3+A_7^3+C_3^1C_1^1C_1^1A_2^2=504$ 种」还原。
+**⚠ 详解第③类的式子有误（如实标注）**：原文写 $C_3^1C_1^1C_1^1A_2^2=3\times1\times1\times2=6$，但这**没有算插空的位置数**（$7$ 个空位选 $2$ 个），结果 $6\neq252$。
+正确应为 $C_3^2\cdot A_2^2\cdot A_7^2=3\times2\times42=252$ ✓。
+**我的三类验算**：
+① $C_7^1A_3^3=7\times6=42$ ✓
+② $A_7^3=210$ ✓
+③ $252$ ✓
+$42+210+252=504$ ✓ **与答案 504 完全吻合** —— 这说明**分类无误**，只是详解第③类的列式漏写了 $A_7^2$。
+**⭐ 另一思路验证**（插空总数法）：$9$ 个位置选 $3$ 个给新节目 $A_9^3=504$ ✓ —— 这与下一题（书架插书）是**同一个模型**，答案都是 504。</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>M-H0388</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>M-T-380(计数原理 / 排列组合 · 书架插书模型)</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr">
+        <is>
+          <t>书架上有排好顺序的 $6$ 本书，如果保持这 $6$ 本书的相对顺序不变，再放上 $3$ 本书，则不同的放法共有（　　）</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>$210$ 种</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>$252$ 种</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>$504$ 种</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>$505$ 种</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P388" s="2" t="inlineStr">
+        <is>
+          <t>**转化**：最终共有 $6+3=9$ 个位置．
+由于原来 $6$ 本书的相对顺序**必须保持不变**，所以只要确定新加的 $3$ 本书放在 $9$ 个位置中的哪 $3$ 个、以及这 $3$ 本之间的顺序，原 $6$ 本就自动按原序填入剩余 $6$ 个位置．
+**计算**：从 $9$ 个位置中选 $3$ 个并排列 $3$ 本新书：
+$A_9^3=9\times8\times7=504$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q388" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S388" t="n">
+        <v>5</v>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-380-V3</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>教辅录入-第32批</t>
+        </is>
+      </c>
+      <c r="V388" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「可看成一共有 9 本书，9 个位置，将 3 本书排列到这 9 个位置中的 3 个位置即可。可转换为将 3 本书排列到所有的 9 本书中的其中 3 个位置上，共 $A_9^3=504$ 种情况」还原。
+**独立验算**：$A_9^3=9\times8\times7=504$ ✓
+**交叉验证**（插空法，与上一题同模型）：
+原 6 本形成 7 个空，按 3 本新书的相邻情况分类：
+①三本连排：$C_7^1\cdot A_3^3=7\times6=42$
+②三本互不相邻：$A_7^3=210$
+③恰两本连排：$C_3^2\cdot A_2^2\cdot A_7^2=3\times2\times42=252$
+合计 $42+210+252=504$ ✓ **两法完全一致**。
+**答案 C（504）正确**。
+**⭐ 模型总结**：「保持原有顺序不变，插入 $k$ 个新元素」$\iff$ 从 $n+k$ 个位置中选 $k$ 个给新元素排列，即 $A_{n+k}^k$。本题 $A_9^3$、上一题 $A_9^3$（$n=6,k=3$）都是这个模型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>M-H0389</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>M-T-363(解析几何 / 离心率 · 判断横放竖放求参)</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr">
+        <is>
+          <t>已知实数 $1,m,9$ 成等比数列，则圆锥曲线 $\dfrac{x^{2}}{m}+y^{2}=1$ 的离心率为（　　）</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt6}{3}$</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt6}{3}$ 或 $2$</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt2}{2}$ 或 $3$</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P389" s="2" t="inlineStr">
+        <is>
+          <t>**求 $m$**：$1,m,9$ 成等比数列，故 $m^{2}=1\times9=9$，解得 $m=3$ 或 $m=-3$．
+**情形一：$m=3$**
+方程为 $\dfrac{x^{2}}3+y^{2}=1$，即 $\dfrac{x^{2}}3+\dfrac{y^{2}}1=1$，是焦点在 $x$ 轴上的椭圆（$3&gt;1$）．
+$a^{2}=3$、$b^{2}=1$，$c^{2}=a^{2}-b^{2}=2$，
+$e=\dfrac ca=\sqrt{\dfrac{c^{2}}{a^{2}}}=\sqrt{\dfrac23}=\dfrac{\sqrt6}{3}$．
+**情形二：$m=-3$**
+方程为 $-\dfrac{x^{2}}3+y^{2}=1$，即 $y^{2}-\dfrac{x^{2}}3=1$，是焦点在 $y$ 轴上的双曲线．
+$a^{2}=1$、$b^{2}=3$，$c^{2}=a^{2}+b^{2}=4$，
+$e=\dfrac ca=\sqrt{\dfrac41}=2$．
+**综上**：离心率为 $\dfrac{\sqrt6}{3}$ 或 $2$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q389" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S389" t="n">
+        <v>5</v>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-363-E1</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V389" s="2" t="inlineStr">
+        <is>
+          <t>★ 选项用**字符坐标**确认（p345 = PDF 页 344）：
+A：分子 `6`(y=114.6,x=71.0)、分母 `3`(y=124.5,x=68.0) → $\frac{\sqrt6}{3}$
+B：`2`(y=119.3,x=173.9) → $2$
+C：分子 `6`(y=136.0,x=71.0)、分母 `3`(y=145.8,x=68.0)、`或`(x=79.4)、`2`(x=90.0) → $\frac{\sqrt6}{3}$ 或 $2$
+D：分子 `2`(y=136.0,x=180.9)、分母 `2`(y=145.8,x=177.8)、`或`(x=189.2)、`3`(x=206.4) → $\frac{\sqrt2}{2}$ 或 $3$
+（提取版显示 `62 / 32`，与上述坐标吻合 ✓）
+**独立验算**：
+$m=3$：$e=\sqrt{1-\frac13}=\sqrt{\frac23}=\frac{\sqrt2}{\sqrt3}=\frac{\sqrt6}{3}\approx0.8165$ ✓
+$m=-3$：$e=\sqrt{1+\frac31}=\sqrt4=2$ ✓
+两个值都在选项 C 中 ✓ **答案 C 正确**。
+**⭐ 题型要点**：这是「判断横放竖放」的典型 —— 同一个方程因参数符号不同，可能是椭圆也可能是双曲线，必须分情况。</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>M-H0390</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>M-T-363(解析几何 / 离心率 · 判断横放竖放求参)</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr">
+        <is>
+          <t>已知双曲线 $M:\dfrac{x^{2}}{a}-\dfrac{y^{2}}{a+8}=1$（$a&gt;0$）的离心率为 $2$，则双曲线 $M$ 的渐近线方程是（　　）</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>$y=\pm\sqrt3\,x$</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>$y=\pm\dfrac{\sqrt3}{3}x$</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>$y=\pm3x$</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>$y=\pm\sqrt2\,x$</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P390" s="2" t="inlineStr">
+        <is>
+          <t>**注意记号**：方程 $\dfrac{x^{2}}a-\dfrac{y^{2}}{a+8}=1$ 中，
+实半轴平方 $a_{\text{实}}^{2}=a$，虚半轴平方 $b^{2}=a+8$，
+故 $c^{2}=a_{\text{实}}^{2}+b^{2}=a+(a+8)=2a+8$．
+（为避免混淆，下面把参数 $a$ 记为 $t$，则 $a_{\text{实}}^{2}=t$、$b^{2}=t+8$、$c^{2}=2t+8$。）
+**由离心率求 $t$**：
+$e^{2}=\dfrac{c^{2}}{a_{\text{实}}^{2}}=\dfrac{2t+8}{t}=4$
+$\Rightarrow2t+8=4t\Rightarrow t=4$．
+**求渐近线**：$a_{\text{实}}^{2}=4$、$b^{2}=4+8=12$，
+由 $\dfrac{x^{2}}4-\dfrac{y^{2}}{12}=0$ 得 $y=\pm\dfrac{b}{a_{\text{实}}}x=\pm\dfrac{\sqrt{12}}{2}x=\pm\dfrac{2\sqrt3}{2}x=\pm\sqrt3\,x$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q390" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S390" t="n">
+        <v>5</v>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-363-V1</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V390" s="2" t="inlineStr">
+        <is>
+          <t>★ 选项用**字符坐标**确认（PDF 页 344）：A 的 `3`(y=372.6,x=85.2) 前有根号 → $\sqrt3$；B 分子`3`(y=368.0,x=199.1)/分母`3`(y=377.8,x=196.1) → $\frac{\sqrt3}3$；C 的 `3`(y=390.0,x=78.7) 无根号 → $3$；D 的 `2`(y=390.0,x=197.3) → $\sqrt2$。
+**独立验算**：
+$e^2=\frac{2t+8}{t}=4\Rightarrow2t+8=4t\Rightarrow t=4$ ✓
+$a_{\text{实}}=2$、$b=\sqrt{12}=2\sqrt3$，$\frac{b}{a_{\text{实}}}=\frac{2\sqrt3}2=\sqrt3$ ✓
+渐近线 $y=\pm\sqrt3 x$ ✓ **答案 A 正确**。
+**⚠ 记号陷阱**：参数 $a$ 与「实半轴 $a_{\text{实}}$」重名，$a_{\text{实}}^{2}=a$ 而非 $a^{2}$ —— 直接写 $e=\frac ca=\frac{\sqrt{a+8}}{a}$ 会算错。</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>M-H0391</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>M-T-363(解析几何 / 离心率 · 判断横放竖放求参)</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr">
+        <is>
+          <t>已知曲线 $C:mx^{2}+3y^{2}=1$ 的离心率 $e=\sqrt3$，则实数 $m$ 值为（　　）</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>$\sqrt6$</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>$-\sqrt6$</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>$\dfrac32$</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>$-\dfrac32$</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t>**判型**：$e=\sqrt3&gt;1$，故曲线 $C$ 是**双曲线**．
+**化标准式**：$mx^{2}+3y^{2}=1\Rightarrow\dfrac{x^{2}}{1/m}+\dfrac{y^{2}}{1/3}=1$．
+要成为双曲线需 $\dfrac1m&lt;0$，即 $m&lt;0$，此时改写为
+$\dfrac{y^{2}}{1/3}-\dfrac{x^{2}}{-1/m}=1$，焦点在 $y$ 轴上，
+$a^{2}=\dfrac13$、$b^{2}=-\dfrac1m$，$c^{2}=a^{2}+b^{2}=\dfrac13-\dfrac1m$．
+**代入离心率**：
+$e^{2}=\dfrac{c^{2}}{a^{2}}=\dfrac{a^{2}+b^{2}}{a^{2}}=1+\dfrac{b^{2}}{a^{2}}=1+\dfrac{-1/m}{1/3}=1-\dfrac3m$．
+由 $e=\sqrt3$ 得 $e^{2}=3$：
+$1-\dfrac3m=3\Rightarrow-\dfrac3m=2\Rightarrow m=-\dfrac32$．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q391" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S391" t="n">
+        <v>5</v>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-363-V2</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V391" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干的 $e=\sqrt3$ 是**还原**出来的 —— 提取版写成 `e =3`（丢了根号）。判定依据：若 $e=3$ 则 $1-\frac3m=9\Rightarrow m=-\frac38$，不在任何选项中；而 $e=\sqrt3$ 给出 $m=-\frac32$ ✓ 与答案 D 吻合。
+**独立验算**：
+$m=-\frac32$：$-\frac32x^2+3y^2=1\Rightarrow\frac{y^2}{1/3}-\frac{x^2}{2/3}=1$
+$a^2=\frac13$、$b^2=\frac23$、$c^2=1$；$e=\frac{c}{a}=\frac1{1/\sqrt3}=\sqrt3$ ✓ **完全吻合**。
+**干扰项分析**：A($\sqrt6$)、B($-\sqrt6$) 来自把 $e^2=3$ 误作 $e=\frac{c^2}{a^2}$ 或在 $1-\frac3m$ 中算错；C($\frac32$) 是 D 漏了负号 —— 负号是关键（$m&gt;0$ 时是椭圆，$e&lt;1$，与 $e=\sqrt3$ 矛盾）。
+**答案 D 正确** ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>M-H0392</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>M-T-363(解析几何 / 离心率 · 判断横放竖放求参)</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr">
+        <is>
+          <t>设 $e$ 是椭圆 $x^{2}+my^{2}=1$（$m&gt;0$）的离心率，且 $e\in\left(0,\dfrac12\right)$，则实数 $m$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>$\left(0,\dfrac14\right)$</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac34,1\right)\cup\left(1,\dfrac43\right)$</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>$\left(0,1\right)\cup\left(1,2\right)$</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>$\left(\dfrac43,2\right)$</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P392" s="2" t="inlineStr">
+        <is>
+          <t>**化标准式**：$x^{2}+my^{2}=1\Rightarrow\dfrac{x^{2}}1+\dfrac{y^{2}}{1/m}=1$（$m&gt;0$）．
+**情形一：焦点在 $x$ 轴**（需 $1&gt;\dfrac1m$，即 $m&gt;1$）
+$a^{2}=1$、$b^{2}=\dfrac1m$，$e^{2}=1-\dfrac{b^{2}}{a^{2}}=1-\dfrac1m$．
+由 $0&lt;e&lt;\dfrac12$ 得 $0&lt;e^{2}&lt;\dfrac14$：
+$0&lt;1-\dfrac1m&lt;\dfrac14\Rightarrow\dfrac34&lt;\dfrac1m&lt;1\Rightarrow1&lt;m&lt;\dfrac43$．
+（结合前提 $m&gt;1$ ✓）
+**情形二：焦点在 $y$ 轴**（需 $\dfrac1m&gt;1$，即 $0&lt;m&lt;1$）
+$a^{2}=\dfrac1m$、$b^{2}=1$，$e^{2}=1-\dfrac{b^{2}}{a^{2}}=1-m$．
+$0&lt;1-m&lt;\dfrac14\Rightarrow\dfrac34&lt;m&lt;1$．
+（结合前提 $0&lt;m&lt;1$ ✓）
+**取并集**：$m\in\left(\dfrac34,1\right)\cup\left(1,\dfrac43\right)$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q392" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S392" t="n">
+        <v>5</v>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-363-V3</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V392" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整（key 里的 opts 与我的还原一致）。详解在 p345 右栏（双栏排版），给出「$m\in(\frac34,1)\cup(1,\frac43)$，故选 B」✓ **与我的推导完全一致**。
+**独立验算**：
+情形一：$m=1.2$（在 $(1,\frac43)$ 内）：$e^2=1-\frac1{1.2}=1-0.8333=0.1667$，$e=0.408&lt;0.5$ ✓
+情形二：$m=0.8$（在 $(\frac34,1)$ 内）：$e^2=1-0.8=0.2$，$e=0.447&lt;0.5$ ✓
+边界检查：$m=1$ 时 $e^2=0$（圆，$e=0$ 不在 $(0,\frac12)$）→ **必须挖去 $m=1$** ✓ 这正是选项 B 用两个开区间的原因。
+$m=\frac34$：$e^2=1-\frac34=\frac14$，$e=\frac12$ → 取不到 ✓ 开区间；$m=\frac43$：$e^2=1-\frac34=\frac14$，$e=\frac12$ → 取不到 ✓
+**答案 B 正确** ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>M-H0393</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>M-T-404(概率统计 / 概率小题 · 古典概型1：枚举法)</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr">
+        <is>
+          <t>已知数据 $1,2,3,4,x$（$0&lt;x&lt;5$）的平均数与中位数相等，从这 $5$ 个数中任取 $2$ 个，则这 $2$ 个数字之积大于 $5$ 的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>$\dfrac25$</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>$\dfrac35$</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>$\dfrac7{10}$</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P393" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求 $x$**
+平均数 $=\dfrac{1+2+3+4+x}5=2+\dfrac x5$．
+由 $0&lt;x&lt;5$ 知 $x\in(0,1)$，故平均数 $\in(2,3)$…更严谨地分情况看中位数：
+$1,2,3,4,x$ 五个数排序后，第 $3$ 个为中位数．
+$2+\dfrac x5\in(2,3)$，故中位数只能落在这个范围，
+对应 $2\leqslant x\leqslant3$ 的情形：排序为 $1,2,x,3,4$，中位数 $=x$．
+由 $2+\dfrac x5=x$ 得 $\dfrac{4x}5=2$，$x=\dfrac52$（落在 $[2,3]$ 内 ✓）．
+**第二步：枚举**
+五个数为 $1,2,\dfrac52,3,4$，任取 $2$ 个共 $C_5^2=10$ 种：
+$(1,2)$、$(1,\frac52)$、$(1,3)$、$(1,4)$、$(2,\frac52)$、$(2,3)$、$(2,4)$、$(\frac52,3)$、$(\frac52,4)$、$(3,4)$．
+**第三步：数积 $&gt;5$ 的**
+$(2,3)=6$、$(2,4)=8$、$(\frac52,3)=7.5$、$(\frac52,4)=10$、$(3,4)=12$，共 $5$ 种．
+（注意 $(2,\frac52)=5$ **不算**，题目要求「大于」$5$。）
+**概率**：$P=\dfrac5{10}=\dfrac12$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q393" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S393" t="n">
+        <v>5</v>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-404-E1</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V393" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干完整 ✓；选项由 ref_bank 的连排数字还原（`'25'`→$\frac25$ 等），再由详解「从这 5 个数中任取 2 个，结果有：(1,2),(1,\frac52),(1,3),(1,4),(2,\frac52),(2,3),(2,4),(\frac52,3),(\frac52,4),(3,4) 共 10 种，这 2 个数字之积大于 5 的结果有 (2,3),(2,4),(\frac52,3),(\frac52,4),(3,4) 共 5 种，所以所求概率为 $p=\frac5{10}=\frac12$」**交叉确认** ✓
+**独立验算**：
+① $x=\frac52$：$2+\frac{2.5}5=2+0.5=2.5=x$ ✓
+② 中位数：排序 $1,2,2.5,3,4$，第 3 个 $=2.5$ ✓ **等于平均数** ✓
+③ 积 $&gt;5$ 的种数：$6,8,7.5,10,12$ 共 5 个 ✓；$(2,2.5)=5$ 不算 ✓（严格大于）；$(1,4)=4$ 不算 ✓
+④ $P=\frac5{10}=\frac12$ ✓ **答案 B 正确**。
+**⭐ 易错点**：$(2,\frac52)$ 恰好等于 $5$，题目说「大于 5」不包含等号 —— 漏掉这点会数成 6 种得 $\frac35$（选项 C，陷阱）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>M-H0394</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>M-T-404(概率统计 / 概率小题 · 古典概型1：枚举法)</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\dfrac13x^{3}-(a-1)x^{2}+b^{2}x$，其中 $a\in\{1,2,3,4\}$，$b\in\{1,2,3\}$，则函数 $f(x)$ 在 $\mathbb R$ 上是增函数的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>$\dfrac14$</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>$\dfrac23$</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>$\dfrac34$</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P394" s="2" t="inlineStr">
+        <is>
+          <t>**转化条件**：$f$ 在 $\mathbb R$ 上增 $\iff f'(x)=x^{2}-2(a-1)x+b^{2}\geqslant0$ 恒成立．
+（注意：$f'$ 恒 $\geqslant0$ 而非 $&gt;0$，个别点取 $0$ 不影响单调性。）
+**判别式**：二次项系数 $1&gt;0$，故
+$\Delta=4(a-1)^{2}-4b^{2}\leqslant0\Rightarrow(a-1)^{2}\leqslant b^{2}$$\Rightarrow|a-1|\leqslant b$（因 $b&gt;0$）．
+**枚举**：$a\in\{1,2,3,4\}$、$b\in\{1,2,3\}$，共 $4\times3=12$ 组：
+$a=1$：$|0|=0\leqslant b$，$b=1,2,3$ 均可 → $3$ 组
+$a=2$：$|1|=1\leqslant b$，$b=1,2,3$ 均可 → $3$ 组
+$a=3$：$|2|=2\leqslant b$，$b=2,3$ → $2$ 组
+$a=4$：$|3|=3\leqslant b$，$b=3$ → $1$ 组
+合计 $3+3+2+1=9$ 组．
+**概率**：$P=\dfrac9{12}=\dfrac34$，选 D．</t>
+        </is>
+      </c>
+      <c r="Q394" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S394" t="n">
+        <v>5</v>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-404-V1</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V394" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干完整 ✓。由详解「原命题等价于 $f'(x)=x^{2}-2(a-1)x+b^{2}\geqslant0$ 在 R 恒成立，则 $\Delta=4(a-1)^{2}-4b^{2}\leqslant0\Rightarrow(a-1)^{2}\leqslant b^{2}$，符合上述不等式的有 (1,1),(1,2),(1,3),(2,1),(2,2),(2,3),(3,2),(3,3),(4,3)$\Rightarrow$ 所求概率 $P=\frac9{3\times4}=\frac34$，故选 D」还原。
+**独立验算**：
+① $f'(x)=x^2-2(a-1)x+b^2$ ✓（$\frac13x^3$ 导数 $x^2$，$-(a-1)x^2$ 导数 $-2(a-1)x$，$b^2x$ 导数 $b^2$）
+② $\Delta=[-2(a-1)]^2-4\cdot1\cdot b^2=4(a-1)^2-4b^2$ ✓
+③ 枚举 $9$ 组 ✓ **与详解列出的 9 组完全一致** ✓
+④ $P=\frac9{12}=\frac34$ ✓ **答案 D 正确**。
+**⭐ 易错点**：$f'(x)\geqslant0$ 用的是「$\geqslant$」不是「$&gt;$」—— 因为 $f'(x)=0$ 只在孤立点成立时函数仍严格递增（如 $y=x^3$），若错用 $\Delta&lt;0$ 会少算 $(a-1)^2=b^2$ 的情形。</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>M-H0395</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>M-T-404(概率统计 / 概率小题 · 古典概型1：枚举法)</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr">
+        <is>
+          <t>（$2013$ 新课标 I 理）从 $1,2,3,4$ 中任取 $2$ 个不同的数，则取出的 $2$ 个数之差的绝对值为 $2$ 的概率是（　　）</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>$\dfrac13$</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>$\dfrac14$</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>$\dfrac16$</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P395" s="2" t="inlineStr">
+        <is>
+          <t>**总数**：从 $1,2,3,4$ 中任取 $2$ 个不同的数，
+$C_4^2=\dfrac{4\times3}2=6$ 种：
+$(1,2)$、$(1,3)$、$(1,4)$、$(2,3)$、$(2,4)$、$(3,4)$．
+**符合条件的**：差的绝对值为 $2$ 的有 
+$(1,3)$：$|1-3|=2$ ✓；$(2,4)$：$|2-4|=2$ ✓．共 $2$ 种．
+**概率**：$P=\dfrac26=\dfrac13$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q395" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S395" t="n">
+        <v>5</v>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-404-V2</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V395" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、详解完整 ✓。由详解「任取两个不同的数有 (1,2),(1,3),(1,4),(2,3),(2,4),(3,4) 共 6 种，2 个数之差的绝对值为 2 的有 (1,3)，(2,4)，故 $P=\frac26=\frac13$」还原。
+**独立验算**：
+$C_4^2=6$ ✓；差为 2 的：$(1,3)$、$(2,4)$ 共 2 对 ✓（$(1,4)$ 差为 3、$(2,3)$ 差为 1，均不符）
+$P=\frac26=\frac13$ ✓ **答案 B 正确**。
+（注：ref_bank 存成 `'12','13','14','16'`，即 $\frac12,\frac13,\frac14,\frac16$，与上述还原一致 ✓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>M-H0396</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>M-T-404(概率统计 / 概率小题 · 古典概型1：枚举法)</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr">
+        <is>
+          <t>笼子中有 $2$ 只鸡和 $2$ 只兔，从中依次随机取出一只动物，直到 $4$ 只动物全部取出．如果将两只兔子中的某一只起名为「长耳朵」，则「长耳朵」恰好是第 $2$ 只被取出的动物的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>$\dfrac16$</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>$\dfrac13$</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>$\dfrac14$</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P396" s="2" t="inlineStr">
+        <is>
+          <t>**解法一（排列）**：把 $2$ 只鸡记为 $a_1,a_2$，$2$ 只兔记为「长耳朵」$H$ 和短耳朵 $h$．
+$4$ 只动物依次取出，所有可能的顺序共 $A_4^4=4!=24$ 种，等可能．
+$H$ 恰好在第 $2$ 位：固定 $H$ 在第 $2$ 位，其余 $3$ 只在余下 $3$ 个位置任意排列，共 $A_3^3=3!=6$ 种．
+$P=\dfrac6{24}=\dfrac14$，选 D．
+**解法二（对称性，更简洁）**：$4$ 个位置对 $H$ 而言完全对称，
+$H$ 落在第 $1,2,3,4$ 位的概率相等，故 $P(\text{第 }2\text{ 位})=\dfrac14$．</t>
+        </is>
+      </c>
+      <c r="Q396" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S396" t="n">
+        <v>5</v>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-404-V3</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V396" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（详解在 p397 末尾被截断，原文只到「把 2 只鸡记为 a₁,a₂，2 只兔子分别记为『长耳朵』H 和短耳朵 h，4…」）。
+**上述两种解法是我补的**，两种方法结果一致 ✓。
+**独立验算**：
+解法一：$4!=24$ ✓；$H$ 在第 2 位、其余 3 只排列 $3!=6$ ✓；$\frac6{24}=\frac14$ ✓
+解法二：$H$ 在 4 个位置等可能，各占 $\frac14$ ✓
+**答案 D 正确** ✓
+**⭐ 提速技巧**：这类「某特定元素落在第 $k$ 位」的概率，直接用对称性得 $\frac1n$，不必算排列数。本题 $n=4$ → $\frac14$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>M-H0397</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>M-T-406(概率统计 / 概率小题 · 几何概型1：长度角度)</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>在矩形 $ABCD$ 中，$AB&gt;BC$，在 $CD$ 边上随机取一点 $P$，若 $AB$ 是 $\triangle ABP$ 最大边的概率为 $\dfrac14$，则 $\dfrac{AD}{AB}=$（　　）</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>$\dfrac13$</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt2}2$</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt{15}}8$</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt{39}}8$</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P397" s="2" t="inlineStr">
+        <is>
+          <t>**建系**：设 $A(0,0)$、$B(a,0)$、$C(a,b)$、$D(0,b)$（$a=AB$、$b=AD$），由 $AB&gt;BC$ 知 $a&gt;b$．
+设 $P(p,b)$，$p\in[0,a]$．
+**转化条件**：$AB$ 是 $\triangle ABP$ 的最大边
+$\iff AP\leqslant AB$ 且 $BP\leqslant AB$（$AB=a$）．
+$AP=\sqrt{p^{2}+b^{2}}\leqslant a\Rightarrow p^{2}\leqslanta^{2}-b^{2}\Rightarrow p\leqslant\sqrt{a^{2}-b^{2}}$；
+$BP=\sqrt{(p-a)^{2}+b^{2}}\leqslant a\Rightarrow(p-a)^{2}\leqslanta^{2}-b^{2}$
+$\Rightarrow|p-a|\leqslant\sqrt{a^{2}-b^{2}}\Rightarrow p\geqslanta-\sqrt{a^{2}-b^{2}}$．
+**允许区间**：$p\in\bigl[a-\sqrt{a^{2}-b^{2}},\ \sqrt{a^{2}-b^{2}}\bigr]$，
+长度 $=2\sqrt{a^{2}-b^{2}}-a$（需 $\geqslant0$，即 $b\leqslant\frac{\sqrt3}2a$）．
+**列方程**：概率 $=\dfrac{2\sqrt{a^{2}-b^{2}}-a}{a}=\dfrac14$．
+令 $t=\dfrac ba=\dfrac{AD}{AB}$，则 $2\sqrt{1-t^{2}}-1=\dfrac14$：
+$2\sqrt{1-t^{2}}=\dfrac54\Rightarrow\sqrt{1-t^{2}}=\dfrac58\Rightarrow1-t^{2}=\dfrac{25}{64}$
+$\Rightarrow t^{2}=\dfrac{39}{64}\Rightarrow t=\dfrac{\sqrt{39}}8$．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q397" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S397" t="n">
+        <v>5</v>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-406-E1</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V397" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项完整；**详解在双栏排版中被截断，上述推导是我独立完成的**。
+**验算（代回）**：$t=\frac{\sqrt{39}}8\approx0.78062$，
+$P=2\sqrt{1-0.78062^{2}}-1=2\sqrt{1-0.60937}-1=2\sqrt{0.39063}-1$
+$=2\times0.625-1=1.25-1=0.25=\frac14$ ✓ **与题设完全吻合**。
+**排除其他选项**（代入 $P=2\sqrt{1-t^2}-1$）：
+$t=\frac13$：$P=2\sqrt{1-\frac19}-1=2\times0.94281-1=0.8856\neq\frac14$ ✗
+$t=\frac{\sqrt2}2$：$P=2\sqrt{0.5}-1=2\times0.70711-1=0.4142\neq\frac14$ ✗
+$t=\frac{\sqrt{15}}8\approx0.48412$：$P=2\sqrt{1-0.23438}-1=2\times0.875-1=0.75\neq\frac14$ ✗
+**答案 D 正确** ✓
+**⭐ 题型套路**：「某边是三角形最大边」⟺ 该边 $\geqslant$ 其余两边，建系后化为两个圆内区域取交集，得到一段区间长度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>M-H0398</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>M-T-406(概率统计 / 概率小题 · 几何概型1：长度角度)</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr">
+        <is>
+          <t>在区间 $[0,\pi]$ 上随机地取一个数 $x$，则事件「$-1\leqslant\tan x\leqslant\sqrt3$」发生的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>$\dfrac7{12}$</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>$\dfrac23$</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>$\dfrac13$</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>$\dfrac14$</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P398" s="2" t="inlineStr">
+        <is>
+          <t>**分段讨论**（$x=\dfrac\pi2$ 处 $\tan x$ 无定义，把 $[0,\pi]$ 分成两段）：
+**① $x\in\left[0,\dfrac\pi2\right)$**：$\tan x\geqslant0$，
+$\tan x\geqslant-1$ 自动成立；$\tan x\leqslant\sqrt3\Rightarrow x\leqslant\dfrac\pi3$．
+得 $x\in\left[0,\dfrac\pi3\right]$．
+**② $x\in\left(\dfrac\pi2,\pi\right]$**：$\tan x&lt;0$，
+$\tan x\leqslant\sqrt3$ 自动成立；$\tan x\geqslant-1\Rightarrow x\geqslant\dfrac{3\pi}4$（因 $\tan\dfrac{3\pi}4=-1$，且 $\tan$ 在此区间递增）．
+得 $x\in\left[\dfrac{3\pi}4,\pi\right]$．
+**求概率**：允许区间总长度
+$=\dfrac\pi3+\left(\pi-\dfrac{3\pi}4\right)=\dfrac\pi3+\dfrac\pi4=\dfrac{7\pi}{12}$，
+$P=\dfrac{7\pi/12}{\pi-0}=\dfrac7{12}$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q398" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S398" t="n">
+        <v>5</v>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-406-V2</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V398" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「∵$0\leqslant x\leqslant\pi$，∴由 $-1\leqslant\tan x\leqslant\sqrt3$ 得，$0\leqslant x\leqslant\frac\pi3$ 或 $\frac{3\pi}4\leqslant x\leqslant\pi$，则事件发生的概率为 $P=\frac{\frac\pi3-0+\pi-\frac{3\pi}4}{\pi-0}=\frac7{12}$，故选 A」还原。
+（题干的 $\sqrt3$ 在提取时丢根号显示为 `3`，按详解的 $\frac\pi3$ 判定为 $\sqrt3$ ✓）
+**独立验算**：
+$\tan\frac\pi3=\sqrt3$ ✓；$\tan\frac{3\pi}4=-1$ ✓
+$\frac\pi3+(\pi-\frac{3\pi}4)=\frac{4\pi}{12}+\frac{3\pi}{12}=\frac{7\pi}{12}$ ✓
+$P=\frac{7\pi/12}{\pi}=\frac7{12}\approx0.5833$ ✓ **答案 A 正确**。
+**⭐ 易错点**：$x=\frac\pi2$ 处 $\tan x$ 无定义，必须把区间断开；若误认为 $\tan x$ 在 $[0,\pi]$ 上连续递增，会漏掉 $[\frac{3\pi}4,\pi]$ 这段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>M-H0399</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>M-T-406(概率统计 / 概率小题 · 几何概型1：长度角度)</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr">
+        <is>
+          <t>任取 $k\in\left[-\sqrt3,\sqrt3\right]$，直线 $y=k(x+2)$ 与圆 $x^{2}+y^{2}=4$ 相交于 $A,B$ 两点，则 $|AB|\geqslant2\sqrt3$ 的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}2$</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>$\dfrac13$</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}3$</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P399" s="2" t="inlineStr">
+        <is>
+          <t>**弦长条件**：圆半径 $r=2$，弦长 $|AB|=2\sqrt{r^{2}-d^{2}}=2\sqrt{4-d^{2}}$，其中 $d$ 为圆心到直线的距离．
+$|AB|\geqslant2\sqrt3\Rightarrow2\sqrt{4-d^{2}}\geqslant2\sqrt3\Rightarrow4-d^{2}\geqslant3\Rightarrow d^{2}\leqslant1\Rightarrow d\leqslant1$．
+**表示 $d$**：直线 $y=k(x+2)$ 即 $kx-y+2k=0$；圆心 $O(0,0)$，
+$d=\dfrac{|k\cdot0-0+2k|}{\sqrt{k^{2}+1}}=\dfrac{2|k|}{\sqrt{1+k^{2}}}$．
+**解不等式**：
+$\dfrac{2|k|}{\sqrt{1+k^{2}}}\leqslant1\Rightarrow4k^{2}\leqslant1+k^{2}\Rightarrow3k^{2}\leqslant1\Rightarrow|k|\leqslant\dfrac1{\sqrt3}=\dfrac{\sqrt3}3$．
+**求概率**：$k$ 的取值区间 $[-\sqrt3,\sqrt3]$ 长度 $=2\sqrt3$；
+满足条件的区间 $\left[-\dfrac{\sqrt3}3,\dfrac{\sqrt3}3\right]$ 长度 $=\dfrac{2\sqrt3}3$．
+$P=\dfrac{2\sqrt3/3}{2\sqrt3}=\dfrac13$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q399" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S399" t="n">
+        <v>5</v>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-406-V3</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V399" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「因弦长 $|AB|=2\sqrt{r^{2}-d^{2}}=2\sqrt{4-d^{2}}\geqslant2\sqrt3$，故 $4-d^{2}\geqslant3$，即 $d^{2}\leqslant1$，$d\leqslant1$，而圆心 $O(0,0)$ 到直线 $kx-y+2k=0$ 的距离 $d=\frac{|2k|}{\sqrt{1+k^{2}}}=\frac{2|k|}{\sqrt{1+k^{2}}}$，所以 $\frac{2|k|}{\sqrt{1+k^{2}}}\leqslant1$」还原。
+（详解在此处被截断，以下为我补全：）
+$4k^2\le1+k^2\Rightarrow3k^2\le1\Rightarrow|k|\le\frac{\sqrt3}3$ ✓
+**独立验算**：
+$k=\frac{\sqrt3}3\approx0.57735$：$d=\frac{2\times0.57735}{\sqrt{1+0.33333}}=\frac{1.1547}{1.15470}=1.0$ ✓ **恰好取等**
+$|AB|=2\sqrt{4-1}=2\sqrt3$ ✓ **恰好等于 $2\sqrt3$**
+概率：区间 $[-\sqrt3,\sqrt3]$ 长 $2\sqrt3=3.4641$；$[-\frac{\sqrt3}3,\frac{\sqrt3}3]$ 长 $\frac{2\sqrt3}3=1.1547$；
+$P=\frac{1.1547}{3.4641}=\frac13$ ✓ **答案 C 正确**。
+**干扰项**：D $(\frac{\sqrt3}3)$ 是 $|k|$ 的临界值本身、B $(\frac{\sqrt3}2)$ 是 $\frac{\sqrt3}3$ 与 $\sqrt3$ 的混淆 —— 都是「没做最后的比值」的常见错法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>M-H0400</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>M-T-406(概率统计 / 概率小题 · 几何概型1：长度角度)</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr">
+        <is>
+          <t>（$2016$ 新课标Ⅰ理）某公司的班车在 $7{:}30$、$8{:}00$、$8{:}30$ 发车，小明在 $7{:}50$ 至 $8{:}30$ 之间到达发车站乘坐班车，且到达发车站的时刻是随机的，则他等车时间不超过 $10$ 分钟的概率是（　　）</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>$\dfrac13$</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>$\dfrac23$</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>$\dfrac34$</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P400" s="2" t="inlineStr">
+        <is>
+          <t>**建时间轴**（以 $7{:}00$ 为 $0$，单位：分钟）：
+发车时刻：$7{:}30\to30$、$8{:}00\to60$、$8{:}30\to90$；到达时刻 $t\in[50,90]$，总长度 $40$．
+**① $t\in[50,60]$**（$7{:}50\sim8{:}00$ 到达）：乘 $8{:}00$ 的车，
+等车时间 $=60-t\in[0,10]$，**全部 $\leqslant10$** ✓ → 区间长 $10$．
+**② $t\in[60,90]$**（$8{:}00\sim8{:}30$ 到达）：乘 $8{:}30$ 的车，
+等车时间 $=90-t$；$\leqslant10\Rightarrow t\geqslant80$，即 $t\in[80,90]$（$8{:}20\sim8{:}30$）→ 区间长 $10$．
+**合计**：满足条件的区间长 $=10+10=20$．
+**概率**：$P=\dfrac{20}{40}=\dfrac12$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q400" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S400" t="n">
+        <v>5</v>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-406-V4</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>教辅录入-第33批</t>
+        </is>
+      </c>
+      <c r="V400" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「由题意得图…由图得等车时间不超过 10 分钟的概率为 $\frac12$」还原 —— 详解依赖配图，**上述分段计算是我补的**。
+**独立验算**：
+到达区间 $[7{:}50,8{:}30]$ 长 $40$ 分钟 ✓
+① $7{:}50\sim8{:}00$ 到达：等 $8{:}00$ 车，等车 $0\sim10$ 分钟 → 全满足 ✓（$10$ 分钟）
+② $8{:}00\sim8{:}30$ 到达：等 $8{:}30$ 车，等车 $\le10$ → $8{:}20$ 之后到 ✓（$10$ 分钟）
+③ 边界检查：$8{:}00$ 整到 → 等 $30$ 分钟（乘 $8{:}30$ 车）✗ 不满足 ✓；$8{:}20$ 到 → 等 $10$ 分钟 ✓ 满足（含等号）
+$P=\frac{10+10}{40}=\frac{20}{40}=\frac12$ ✓ **答案 B 正确**。
+**⭐ 关键**：$8{:}00$ 之后到达的人**只能等 $8{:}30$ 的车**，不能直接接 $8{:}00$ 那班（已开走）—— 这是最容易搞错的地方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>M-H0401</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>M-T-295(立体几何 / 外接球 · 直棱柱模板：线面垂直(重点))</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr">
+        <is>
+          <t>在三棱锥 $P-ABC$ 中，$PA=PB=BC=4$，$AC=8$，$AB\perp BC$．平面 $PAB\perp$ 平面 $ABC$，若球 $O$ 是三棱锥 $P-ABC$ 的外接球，则球 $O$ 的表面积为（　　）</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>$25\pi$</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>$60\pi$</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>$72\pi$</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>$80\pi$</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P401" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：找底面的外心**
+在 $\triangle ABC$ 中，$AB\perp BC$，$AC=8$、$BC=4$，
+$AB=\sqrt{AC^{2}-BC^{2}}=\sqrt{64-16}=\sqrt{48}=4\sqrt3$．
+因 $\triangle ABC$ 是直角三角形（$\angle B=90^\circ$），其外心 $E$ 为斜边 $AC$ 的中点．
+**第二步：证 $PD\perp$ 底面**
+设 $D$ 为 $AB$ 中点．由 $PA=PB=4$ 知 $PD\perp AB$，
+$AD=BD=\dfrac{AB}2=2\sqrt3$，$PD=\sqrt{PA^{2}-AD^{2}}=\sqrt{16-12}=2$．
+又平面 $PAB\perp$ 平面 $ABC$ 且交线为 $AB$，故 $PD\perp$ 平面 $ABC$．
+**第三步：定位球心**
+球心 $O$ 在过 $E$ 且垂直平面 $ABC$ 的直线上（即 $OE\perp$ 底面）．
+$DE$ 是 $\triangle ABC$ 中位线（$D$、$E$ 为 $AB$、$AC$ 中点），故 $DE=\dfrac{BC}2=2$．
+过 $O$ 作 $OF\perp PD$，则四边形 $OFDE$ 是矩形，$OE=DF$、$OF=DE=2$．
+**第四步：求 $R$**
+$OP^{2}=OF^{2}+PF^{2}=2^{2}+(PD-DF)^{2}$，
+$OB^{2}=OE^{2}+BE^{2}=DF^{2}+\left(\dfrac{AC}2\right)^{2}=DF^{2}+4^{2}$．
+由 $OP=OB=R$：$4+(2-DF)^{2}=DF^{2}+16$，
+$4+4-4DF+DF^{2}=DF^{2}+16\Rightarrow-4DF=8\Rightarrow DF=-2$．
+（绝对值 $|DF|=2$，即球心在 $ED$ 延长线上距 $E$ 为 $2$ 处）
+$R^{2}=OE^{2}+BE^{2}=2^{2}+4^{2}=20$．
+**表面积**：$S=4\pi R^{2}=4\pi\times20=80\pi$，选 D．</t>
+        </is>
+      </c>
+      <c r="Q401" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S401" t="n">
+        <v>5</v>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-295-E1</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>教辅录入-第34批</t>
+        </is>
+      </c>
+      <c r="V401" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「设 $D,E$ 分别是 $AB,AC$ 的中点，由于 $PB=PA$，所以 $PD\perp AB$，由于平面 $PAB\perp$ 平面 $ABC$ 且交线为 $AB$，所以 $PD\perp$ 平面 $ABC$，由于 $AB\perp BC$，所以 $E$ 是 Rt△ABC 的外心，所以球心 $O$ 在过 $E$ 且与平面 $ABC$ 垂直的直线上，$AB=\sqrt{8^{2}-4^{2}}=4\sqrt3$，$AD=BD=2\sqrt3$，$PD=\sqrt{4^{2}-(2\sqrt3)^{2}}=2$，$DE=\frac{BC}2=2$，过 $O$ 作 $OF\perp PD$，且交点为 $F$，由于 $OF\parallel DE$，$OE\parallel DF$，所以四边形 $OFDE$ 是矩形，则 $OE=DF$。设外接球的半径为 $R$，所以 $R^{2}=2^{2}+(2-DF)^{2}=4^{2}+OE^{2}$，解得 $OE=DF=2$，$R^{2}=20$，$R=2\sqrt5$。所以外接球的表面积为 $4\pi R^{2}=80\pi$」还原。
+**独立验算**：
+$AB=\sqrt{64-16}=\sqrt{48}=4\sqrt3\approx6.928$ ✓
+$PD=\sqrt{16-12}=2$ ✓；$DE=4/2=2$ ✓
+$R^{2}=2^{2}+4^{2}=20$ ✓（$BE=\frac{AC}2=4$）
+$S=4\pi\times20=80\pi$ ✓ **答案 D 正确**。
+**⚠ 注意**：原文「解得 $OE=DF=2$」与我的 $DF=-2$ 符号相反 —— 这取决于 $F$ 在 $PD$ 上的位置假设（$F$ 在 $PD$ 延长线上时 $DF$ 取正），但 $|DF|=2$ 一致，$R^{2}=20$ 不变 ✓ **结论不受影响**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>M-H0402</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>M-T-295(立体几何 / 外接球 · 直棱柱模板：线面垂直(重点))</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr">
+        <is>
+          <t>已知三棱锥 $S-ABC$ 中，$\triangle ABC$ 为等边三角形，$SA\perp$ 平面 $ABC$，若三棱锥 $S-ABC$ 的最长棱为 $6$，直线 $SB$ 与平面 $ABC$ 所成角的余弦值为 $\dfrac{\sqrt6}6$，则三棱锥 $S-ABC$ 的外接球表面积为（　　）</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>$\dfrac{19\pi}2$</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>$\dfrac{19\pi}3$</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>$\dfrac{17\pi}3$</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>$\dfrac{17\pi}2$</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P402" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：定 $AB$ 与 $SA$**
+由 $SA\perp$ 平面 $ABC$，$SB$ 在平面 $ABC$ 上的射影为 $AB$，故 $SB$ 与平面 $ABC$ 所成角 $=\angle SBA$．
+$\cos\angle SBA=\dfrac{AB}{SB}=\dfrac{\sqrt6}6$，又最长棱 $SB=6$：
+$AB=6\times\dfrac{\sqrt6}6=\sqrt6$…
+（按原文数据：最长棱为 $6$，$\cos\angle SBA=\frac{AB}{6}=\frac{\sqrt6}6$）
+$AB=\sqrt6$ 时 $SA=\sqrt{SB^{2}-AB^{2}}=\sqrt{36-6}=\sqrt{30}$．
+但此时 $SC=\sqrt{SA^{2}+AC^{2}}=\sqrt{30+6}=6=SB$，即最长棱确为 $6$（$SB=SC=6$）✓
+**第二步：套直棱柱模板**
+$\triangle ABC$ 是边长为 $\sqrt6$ 的等边三角形，其外接圆半径
+$r=\dfrac{\sqrt6}{\sqrt3}=\sqrt2$（由 $2r=\frac a{\sin60^\circ}=\frac{\sqrt6}{\sqrt3/2}=2\sqrt2$）．
+把三棱锥补成直三棱柱，则
+$R^{2}=r^{2}+\left(\dfrac{SA}2\right)^{2}=2+\left(\dfrac{\sqrt{30}}2\right)^{2}=2+\dfrac{30}4=2+\dfrac{15}2=\dfrac{19}2$．
+$S=4\pi R^{2}=4\pi\times\dfrac{19}2=38\pi$ —— 不在选项中，说明上面理解有误。
+**按原书数据重算**（原文给出 $AB=1$、$SA=5$、$r=\frac{\sqrt3}3$）：
+$R^{2}=r^{2}+\left(\dfrac{SA}2\right)^{2}=\dfrac13+\dfrac{25}4=\dfrac{4+75}{12}=\dfrac{79}{12}$…仍不符。
+**采用原书结论**：$R^{2}=\dfrac{19}{12}$，
+$S=4\pi\times\dfrac{19}{12}=\dfrac{19\pi}3$，选 B．</t>
+        </is>
+      </c>
+      <c r="Q402" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S402" t="n">
+        <v>5</v>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-295-V1</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>教辅录入-第34批</t>
+        </is>
+      </c>
+      <c r="V402" s="2" t="inlineStr">
+        <is>
+          <t>**⚠⚠ 本题数据存在矛盾，按原书答案 B 录入，但标注存疑**。
+**矛盾的来由**：
+① 原文详解写「$\cos\angle SBA=\frac{AB}{6}=\frac{\sqrt6}6$，所以 $AB=1$」—— 但 $6\times\frac{\sqrt6}6=\sqrt6\approx2.449\neq1$。
+② 接着写「$SA=\sqrt{6-1}=\sqrt5$」—— 若 $AB=1$ 则 $SA=\sqrt{6^{2}-1}=\sqrt{35}$ 而非 $\sqrt5$。
+③ 原文给的 $r=\frac{\sqrt3}3$ 对应边长 $1$ 的等边三角形 ✓（$r=\frac1{\sqrt3}=\frac{\sqrt3}3$），与「$AB=1$」自洽，但与「$SB=6$、$\cos=\frac{\sqrt6}6$」矛盾。
+④ 原文最终 $r^{2}=\frac{19}{12}$，而 $\frac13+\frac{25}4=\frac{79}{12}\neq\frac{19}{12}$；$\frac13+\frac54=\frac{19}{12}$ ✓ —— 即原文实际用的是 $r^{2}=\frac13$ 与 $(\frac{SA}2)^{2}=\frac54$（$SA=\sqrt5$），**与前面推出的 $SA$ 不一致**。
+**我的判断**：该题在印刷或提取中数据失真（$\sqrt6$ 与 $1$、$\sqrt{30}$ 与 $\sqrt5$ 的差异都指向根号丢失）。
+**处理方式**：答案 B（$\frac{19\pi}3$）与原文最终算式 $\frac{19}{12}$ 自洽，按原书录入；但**不提供独立验算确认**，孩子做到这题若发现数据对不上，应以题目原始印刷为准。
+（已在此处如实记录，供后续复核。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>M-H0403</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>M-T-295(立体几何 / 外接球 · 直棱柱模板：线面垂直(重点))</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr">
+        <is>
+          <t>已知 $\triangle ABC$，$AB=AC=3$，$BC=4$，将它沿中线 $AD$ 折起得四面体 $A-BCD$，使得此时 $BC=2\sqrt3$，则四面体 $A-BCD$ 的外接球表面积为（　　）</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>$16\pi$</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>$18\pi$</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>$21\pi$</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>$36\pi$</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P403" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：折起后的几何关系**
+原 $\triangle ABC$ 中 $AB=AC=3$、$BC=4$，$D$ 为 $BC$ 中点，
+$BD=CD=2$，$AD=\sqrt{AB^{2}-BD^{2}}=\sqrt{9-4}=\sqrt5$．
+折起后（$BC$ 变为 $2\sqrt3$），因 $AD\perp BC$ 于 $D$，
+有 $AD\perp BD$、$AD\perp CD$，故 $AD\perp$ 平面 $BCD$．
+**第二步：求 $\triangle BCD$ 的外接圆半径 $r$**
+在 $\triangle BCD$ 中 $BD=CD=2$、$BC=2\sqrt3$，由余弦定理：
+$\cos\angle BDC=\dfrac{CD^{2}+BD^{2}-BC^{2}}{2\cdot CD\cdot BD}=\dfrac{4+4-12}{2\times2\times2}=\dfrac{-4}8=-\dfrac12$，
+故 $\angle BDC=120^\circ$，$\sin\angle BDC=\dfrac{\sqrt3}2$．
+由正弦定理：$2r=\dfrac{BC}{\sin\angle BDC}=\dfrac{2\sqrt3}{\sqrt3/2}=4$，故 $r=2$．
+**第三步：套直棱柱模板**
+$R^{2}=r^{2}+\left(\dfrac{AD}2\right)^{2}=2^{2}+\dfrac54=4+\dfrac54=\dfrac{21}4$．
+**表面积**：$S=4\pi R^{2}=4\pi\times\dfrac{21}4=21\pi$，选 C．</t>
+        </is>
+      </c>
+      <c r="Q403" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S403" t="n">
+        <v>5</v>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-295-V2</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>教辅录入-第34批</t>
+        </is>
+      </c>
+      <c r="V403" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「因为 $AB=AC=3$，$BC=4$，将它沿高 $AD$ 翻折，使得此时 $BC=2\sqrt3$，所以可得 $BD=CD=2$，$AD=\sqrt5$，在 △BCD 中，由余弦定理可得 $\cos\angle BDC=\frac{4+4-12}{2\times2\times2}=-\frac12$，所以 $\sin\angle BDC=\frac{\sqrt3}2$，设 △BCD 的外接圆的半径 $r$，则 $2r=\frac{BC}{\sin\angle BDC}=\frac{2\sqrt3}{\sqrt3/2}$，所以 $r=2$，因为 $BD\perp AD$，$CD\perp AD$，$BD\cap CD=D$，所以 $AD\perp$ 面 BCD，将此三棱锥放在直棱柱中，设其外接球的半径为 $R$，则 $R^{2}=r^{2}+(\frac{AD}2)^{2}=4+\frac54=\frac{21}4$，所以外接球的表面积 $S=4\pi R^{2}=4\pi\cdot\frac{21}4=21\pi$」还原。
+**独立验算**：
+$AD=\sqrt{9-4}=\sqrt5$ ✓
+$\cos\angle BDC=\frac{4+4-12}{8}=-\frac12$ ✓ → $\angle BDC=120^\circ$ ✓
+$2r=\frac{2\sqrt3}{\sqrt3/2}=2\sqrt3\times\frac2{\sqrt3}=4$ ✓ → $r=2$ ✓
+$R^{2}=4+\frac54=\frac{16+5}4=\frac{21}4$ ✓
+$S=4\pi\times\frac{21}4=21\pi$ ✓ **答案 C 正确**。
+**⭐ 题型要点**：「沿高折起」必得 $AD\perp$ 平面 $BCD$（折起后 $AD$ 仍垂直 $BD$、$CD$），这是套用直棱柱模板的关键。</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>M-H0404</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>M-T-295(立体几何 / 外接球 · 直棱柱模板：线面垂直(重点))</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr">
+        <is>
+          <t>已知三棱锥 $P-ABC$ 中，$AC\perp BC$，$AC=BC=4\sqrt2$，平面 $PAC\perp$ 平面 $ABC$．若三棱锥 $P-ABC$ 的外接球面积为 $68\pi$，则三棱锥 $P-ABC$ 的体积最大值为 ____ ．</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr"/>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>$\dfrac{64}3$</t>
+        </is>
+      </c>
+      <c r="P404" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：由球面积求 $R$**
+$4\pi R^{2}=68\pi\Rightarrow R^{2}=17\Rightarrow R=\sqrt{17}$．
+**第二步：定底面的外心**
+$\triangle ABC$ 中 $AC\perp BC$、$AC=BC=4\sqrt2$，是等腰直角三角形，斜边 $AB=\sqrt{32+32}=8$．
+外心 $M$ 为 $AB$ 中点，$BM=\dfrac{AB}2=4$．
+**第三步：定位球心**
+设 $E$ 为 $AC$ 中点，由平面 $PAC\perp$ 平面 $ABC$ 且交线 $AC$，当 $PE\perp AC$ 时 $PE\perp$ 平面 $ABC$（此时 $PA=PC$，$P$ 到底面距离最大）．
+设 $D$ 为 $\triangle PAC$ 的外心，球心 $O$ 满足 $OD\perp$ 平面 $PAC$、$OM\perp$ 平面 $ABC$，四边形 $OMED$ 为矩形，故 $OM=DE$．
+**第四步：求高 $PE$**
+$OB^{2}=R^{2}=17$，$OM^{2}=OB^{2}-BM^{2}=17-16=1\Rightarrow OM=1$，
+故 $DE=OM=1$．又 $OD=\sqrt{OP^{2}-PD^{2}}$，
+由原文：$OP^{2}-OD^{2}=3$（即 $PD^{2}=3$），且 $OM=DE=OB^{2}-BM^{2}$…
+取 $PE=PD+DE=\sqrt3+1$…
+**按原书结论**：$PE=PD+DE=4$，
+$V=\dfrac13S_{\triangle ABC}\cdot PE=\dfrac13\times\dfrac12\times4\sqrt2\times4\sqrt2\times4=\dfrac13\times16\times4=\dfrac{64}3$．
+故答案为 $\dfrac{64}3$．</t>
+        </is>
+      </c>
+      <c r="Q404" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S404" t="n">
+        <v>5</v>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-295-V3</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>教辅录入-第34批</t>
+        </is>
+      </c>
+      <c r="V404" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、答案完整 ✓（$\frac{64}3$ 在 key 的 ans 字段中）；**详解跨页**（p262 末尾 → p263 开头），关键步骤在 p263：
+「分别取 $AB$、$AC$ 的中点 $M$、$E$，连接 $PE$，则 $M$ 为三角形 $ABC$ 的外心，当 $P$ 到平面 $ABC$ 的距离最大时，三棱锥 $P-ABC$ 的体积最大，此时 $PE\perp AC$，即 $PA=PC$，由平面 $PAC\perp$ 平面 $ABC$，得 $PE\perp$ 平面 $ABC$，设 $D$ 为 △PAC 的外心，$O$ 为三棱锥 $P-ABC$ 的外接球的球心，由球的性质可知 $OD\perp$ 平面 $ABC$，$OM\perp$ 平面 $ABC$，则四边形 $OMED$ 为矩形，由三棱锥 $P-ABC$ 的外接球面积为 $68\pi$，得 $OB=OP=\sqrt{17}$，$PD=\sqrt3$，$OM=DE$，$OB^{2}-BM^{2}=1$，又 $PE=PD+DE=4$，∴$V_{P-ABC}=\frac13\times\frac12\times4\sqrt2\times4\sqrt2\times4=\frac{64}3$」
+**独立验算（体积部分）**：
+$S_{\triangle ABC}=\frac12\times4\sqrt2\times4\sqrt2=\frac12\times32=16$ ✓
+$V=\frac13\times16\times4=\frac{64}3$ ✓ **与答案完全一致**
+**其余量的核对**：
+$R^{2}=68\pi/4\pi=17$ ✓；$AB=\sqrt{32+32}=8$ ✓；$BM=4$ ✓
+$OM^{2}=OB^{2}-BM^{2}=17-16=1$ ✓ → $OM=DE=1$ ✓
+$PD=\sqrt3$（原文给出）、$PE=PD+DE=\sqrt3+1\approx2.732$ —— **与原文的 $PE=4$ 不符**。
+**⚠ 如实标注**：详解中 $PD=\sqrt3$ 与 $PE=4$ 不自洽（$\sqrt3+1\neq4$）。但**体积公式与答案 $\frac{64}3$ 自洽**，故按原书答案录入，$PD$ 的具体数值可能是提取失真。
+（$PE=4$ 与 $V=\frac{64}3$ 相互印证，应以 $PE=4$ 为准。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>M-H0405</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>轨迹方程</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>M-T-343(解析几何 / 轨迹方程 · 复数中的轨迹(新高考)  ↔复数)</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr">
+        <is>
+          <t>已知复平面内 $A$ 点对应的复数为 $2+\mathrm i$，$B$ 点对应的复数为 $1-\mathrm i$，$z=x+(y-2)\mathrm i$（$x,y\in\mathbb R$）．若 $\lvert z\rvert=1$，在 $z$ 的轨迹上任取一点 $C$，求 $\triangle ABC$ 的面积取值范围．</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>$S_{\triangle ABC}\in\left[\dfrac{5-\sqrt5}2,\ \dfrac{5+\sqrt5}2\right]$</t>
+        </is>
+      </c>
+      <c r="P405" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：定 $C$ 的轨迹**
+由 $z=x+(y-2)\mathrm i$、$\lvert z\rvert=1$ 得 $x^{2}+(y-2)^{2}=1$，即 $C$ 在圆心 $P(0,2)$、半径 $r=1$ 的圆上．
+**第二步：求直线 $AB$ 与 $\lvert AB\rvert$**
+$A(2,1)$、$B(1,-1)$，斜率 $k=\dfrac{1-(-1)}{2-1}=2$，
+直线 $AB$：$y-1=2(x-2)$，即 $2x-y-3=0$．
+$\lvert AB\rvert=\sqrt{(2-1)^{2}+(1+1)^{2}}=\sqrt{1+4}=\sqrt5$．
+**第三步：求圆心到直线的距离**
+$d=\dfrac{\lvert 2\times0-2-3\rvert}{\sqrt{2^{2}+(-1)^{2}}}=\dfrac5{\sqrt5}=\sqrt5$．
+**第四步：圆上点到直线距离的最值**
+因 $d=\sqrt5&gt;r=1$，圆与直线相离，故
+$h_{\min}=d-r=\sqrt5-1$，$h_{\max}=d+r=\sqrt5+1$．
+**第五步：面积范围**
+$S=\dfrac12\lvert AB\rvert\cdot h$：
+$S_{\min}=\dfrac12\sqrt5(\sqrt5-1)=\dfrac{5-\sqrt5}2$，
+$S_{\max}=\dfrac12\sqrt5(\sqrt5+1)=\dfrac{5+\sqrt5}2$．
+故 $S_{\triangle ABC}\in\left[\dfrac{5-\sqrt5}2,\ \dfrac{5+\sqrt5}2\right]$．</t>
+        </is>
+      </c>
+      <c r="Q405" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S405" t="n">
+        <v>5</v>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-343-E1</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>教辅录入-第34批</t>
+        </is>
+      </c>
+      <c r="V405" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「因为 $|z|=1$，所以 C 点轨迹为 $x^2+(y-2)^2=1$；又因为 A 点对应的复数为 $2+\mathrm i$，B 点对应的复数为 $1-\mathrm i$，则线段 AB 的方程为 $y=2x-3$（$1\le x\le2$），AB 的长度为 $\sqrt{(2-1)^2+(1+1)^2}=\sqrt5$。则知 $(0,2)$ 点到直线 AB 的距离为 $d=\frac{|2+3|}{\sqrt{1+2^2}}=\sqrt5$。则 $\frac12\cdot\sqrt5\cdot(\sqrt5-1)\le S_{\triangle ABC}\le\frac12\cdot\sqrt5\cdot(\sqrt5+1)$。则 $S\in[\frac{\sqrt5-5}2,\frac{\sqrt5+5}2]$」还原。
+**⚠ 详解答案式的印刷错误（如实标注）**：原文写 $\frac{\sqrt5-5}2$ 与 $\frac{\sqrt5+5}2$，但 $\frac{\sqrt5-5}2=\frac{2.236-5}2=-1.382&lt;0$ —— **面积不可能为负**。
+正确应为 $\frac{5-\sqrt5}2$ 与 $\frac{5+\sqrt5}2$ ✓。
+**独立验算**：
+圆心 $(0,2)$ 到 $2x-y-3=0$：$d=\frac{|0-2-3|}{\sqrt5}=\frac5{\sqrt5}=\sqrt5$ ✓
+$d=\sqrt5\approx2.236&gt;r=1$ ✓ 相离，距离最值 $[\sqrt5-1,\sqrt5+1]$ ✓
+$S_{\min}=\frac12\cdot\sqrt5\cdot(\sqrt5-1)=\frac{5-\sqrt5}2\approx1.382$ ✓
+$S_{\max}=\frac12\cdot\sqrt5\cdot(\sqrt5+1)=\frac{5+\sqrt5}2\approx3.618$ ✓
+**数值抽查**：取圆上最高点 $C(0,3)$：$S=\frac12|x_A(y_B-y_C)+x_B(y_C-y_A)+x_C(y_A-y_B)|$
+$=\frac12|2(-1-3)+1(3-1)+0|=\frac12|-8+2|=3$ —— 落在 $[1.382,3.618]$ 内 ✓
+**结论正确** ✓（仅答案式的两项顺序印反了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>M-H0406</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>轨迹方程</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>M-T-343(解析几何 / 轨迹方程 · 复数中的轨迹(新高考)  ↔复数)</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr">
+        <is>
+          <t>若复数 $z$ 满足 $\lvert z-1+\mathrm i\rvert=3$，则复数 $z$ 对应的点的轨迹围成图形的面积等于（　　）</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>$9$</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>$6\pi$</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>$9\pi$</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P406" s="2" t="inlineStr">
+        <is>
+          <t>**化为标准形式**：$\lvert z-1+\mathrm i\rvert=\lvert z-(1-\mathrm i)\rvert=3$．
+**几何意义**：$\lvert z-z_{0}\rvert=r$ 表示复平面上到定点 $Z_{0}$ 距离为定值 $r$ 的点的轨迹，即以 $Z_{0}$ 为圆心、$r$ 为半径的**圆**．
+此处 $z_{0}=1-\mathrm i$ 对应点 $(1,-1)$，$r=3$．
+**面积**：$S=\pi r^{2}=\pi\times3^{2}=9\pi$．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q406" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>适中</t>
+        </is>
+      </c>
+      <c r="S406" t="n">
+        <v>5</v>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-343-V1</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>教辅录入-第34批</t>
+        </is>
+      </c>
+      <c r="V406" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「复数 $z$ 满足 $|z-(1-\mathrm i)|=3$，表示复数 $z$ 对应的点的轨迹是以点 $(1,-1)$ 为圆心，半径为 3 的圆，所以围成图形的面积等于 $S=\pi\times3^{2}=9\pi$」还原。
+**独立验算**：$S=\pi r^2=\pi\times9=9\pi$ ✓ **答案 D 正确**。
+**干扰项**：A($3$) 是半径、B($9$) 是 $r^2$（漏乘 $\pi$）、C($6\pi$) 是误用周长 $2\pi r=6\pi$ —— 三个都是「没写对面积公式」的典型错误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>M-H0407</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>轨迹方程</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>M-T-343(解析几何 / 轨迹方程 · 复数中的轨迹(新高考)  ↔复数)</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr">
+        <is>
+          <t>已知复数 $z$ 满足 $\lvert z+\mathrm i\rvert+\lvert z-\mathrm i\rvert=2$，则 $z$ 的轨迹为（　　）</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>线段</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>直线</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>椭圆</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>椭圆的一部分</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P407" s="2" t="inlineStr">
+        <is>
+          <t>**几何意义**：$\lvert z+\mathrm i\rvert=\lvert z-(-\mathrm i)\rvert$ 是 $Z$ 到 $A(0,-1)$ 的距离；$\lvert z-\mathrm i\rvert$ 是 $Z$ 到 $B(0,1)$ 的距离．
+条件即 $\lvert ZA\rvert+\lvert ZB\rvert=2$．
+**比较常数与 $\lvert AB\rvert$**：$\lvert AB\rvert=2$，恰好 **$2a=\lvert AB\rvert$**．
+由三角形不等式：$\lvert ZA\rvert+\lvert ZB\rvert\geqslant\lvert AB\rvert=2$，等号成立**当且仅当 $Z$ 在线段 $AB$ 上**．
+故满足等号的点集正是**线段 $AB$**．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q407" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S407" t="n">
+        <v>5</v>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-343-V2</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>教辅录入-第34批</t>
+        </is>
+      </c>
+      <c r="V407" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版完整 ✓。由详解「设 $z=x+y\mathrm i$（$x,y\in\mathbb R$），由复数的几何意义可知，$|z+\mathrm i|+|z-\mathrm i|=2$ 表示点 $Z(x,y)$ 到定点 $A(0,-1)$ 与 $B(0,1)$ 的距离之和为 2，而 $|AB|=2$，故点 $Z$ 的轨迹为线段 $AB$」还原。
+**独立验算**：
+若 $2a&gt;|AB|=2$（如 $=3$）→ 椭圆；若 $2a=|AB|=2$ → **线段**；若 $2a&lt;|AB|$ → 无解。
+本题 $2a=2=|AB|$ ✓ **退化为线段**。
+**验证**：取 $Z=(0,0)$（线段中点）：$|Z A|+|ZB|=1+1=2$ ✓；取 $Z=(0,2)$（线段外）：$|2+1|+|2-1|=3+1=4\neq2$ ✗ ✓
+**答案 A 正确** ✓
+**⭐ 这是本题的命门**：学生一看「距离和为常数」就选椭圆（C），但必须**先比较常数与两定点距离**，等号时是线段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>M-H0408</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>轨迹方程</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>M-T-343(解析几何 / 轨迹方程 · 复数中的轨迹(新高考)  ↔复数)</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr">
+        <is>
+          <t>设非零复数 $Z_{0}$ 是复平面上一定点，$Z_{1}$ 为复平面上的动点，其轨迹方程 $\lvert Z_{1}-Z_{0}\rvert=\lvert Z_{1}\rvert$，$Z$ 为复平面上另一个动点满足 $Z_{1}Z=-1$，则 $Z$ 在复平面上的轨迹形状是（　　）</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>双曲线</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>圆</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>一条直线</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>抛物线</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P408" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：反解 $Z_{1}$**
+由 $Z_{1}Z=-1$ 得 $Z_{1}=-\dfrac1Z$（$Z\neq0$）．
+**第二步：代入轨迹方程**
+$\left\lvert-\dfrac1Z-Z_{0}\right\rvert=\left\lvert-\dfrac1Z\right\rvert$
+$\Rightarrow\left\lvert\dfrac1Z+Z_{0}\right\rvert=\dfrac1{\lvert Z\rvert}$．
+**第三步：两边同乘 $\lvert Z\rvert$**
+$\lvert Z\rvert\cdot\left\lvert\dfrac1Z+Z_{0}\right\rvert=\lvert 1+Z_{0}Z\rvert=1$．
+即 $\lvert Z_{0}Z+1\rvert=1$．
+**第四步：化为标准圆方程**
+$\left\lvert Z_{0}\right\rvert\cdot\left\lvert Z+\dfrac1{Z_{0}}\right\rvert=1$
+$\Rightarrow\left\lvert Z+\dfrac1{Z_{0}}\right\rvert=\dfrac1{\lvert Z_{0}\rvert}$．
+这是以 $-\dfrac1{Z_{0}}$ 对应的点为圆心、$\dfrac1{\lvert Z_{0}\rvert}$ 为半径的**圆**．
+故选 B．</t>
+        </is>
+      </c>
+      <c r="Q408" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S408" t="n">
+        <v>5</v>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-343-V3</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>教辅录入-第34批</t>
+        </is>
+      </c>
+      <c r="V408" s="2" t="inlineStr">
+        <is>
+          <t>★ 还原版题干与答案完整；**详解的式子破碎严重**（满是 $\langle?\rangle$ 与 $\frac{1}{0}$ 占位），但关键结论可辨：
+「因为 $Z_1Z=-1$，所以 $Z_1=-\frac1Z$，代入 $|Z_1-Z_0|=|Z_1|$，得 $|-\frac1Z-Z_0|=|-\frac1Z|$，两边同乘 $|Z|$，得 $\left|Z+\frac1{Z_0}\right|=\frac1{|Z_0|}$，所以 $Z$ 在复平面上的轨迹形状是以 $-\frac1{Z_0}$ 为圆心，$\frac1{|Z_0|}$ 为半径的圆」✓ **与我的推导完全一致**。
+**独立验算**：
+$Z_1=-\frac1Z$ ✓（由 $Z_1Z=-1$）
+$|Z_1-Z_0|=|-\frac1Z-Z_0|$，$|-Z_1|=|\frac1Z|=\frac1{|Z|}$ ✓
+同乘 $|Z|$：$|\cdot|\cdot|Z|=|-\frac1Z-Z_0|\cdot|Z|=|(-1-Z_0Z)/Z|\cdot|Z|$
+$=\frac{|1+Z_0Z|}{|Z|}\cdot|Z|=|1+Z_0Z|$ ✓；右端 $\frac1{|Z|}\cdot|Z|=1$ ✓
+故 $|1+Z_0Z|=1$，即 $|Z_0|\cdot|Z+\frac1{Z_0}|=1$ ✓
+→ $\left|Z+\frac1{Z_0}\right|=\frac1{|Z_0|}$ ✓ **是圆**
+**具体检验**：取 $Z_0=1$，则 $|Z+1|=1$，圆心 $(-1,0)$、半径 $1$。取圆上点 $Z=-2$：$Z_1=-\frac1{-2}=0.5$，$|Z_1-Z_0|=0.5=|Z_1|$ ✓ **满足原方程**
+**答案 B 正确** ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>M-H0409</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>圆锥曲线小题</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>M-T-331(解析几何 / 圆锥曲线小题 · 定比分点)</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr">
+        <is>
+          <t>已知椭圆 $\Gamma:\dfrac{x^{2}}{a^{2}}+\dfrac{y^{2}}{b^{2}}=1$（$a&gt;b&gt;0$）的左、右焦点分别为 $F_{1},F_{2}$，点 $A,B$ 在椭圆 $\Gamma$ 上，$\vec{AF_{1}}\cdot\vec{F_{1}F_{2}}=0$ 且 $\vec{AF_{2}}=\lambda\vec{F_{2}B}$，则当 $\lambda\in\left[2,3\right]$ 时，椭圆的离心率的取值范围为 ____ ．</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr"/>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac{\sqrt5}5,\ \dfrac{\sqrt3}3\right]$</t>
+        </is>
+      </c>
+      <c r="P409" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：定 $A$ 的坐标**
+$\vec{F_{1}F_{2}}=(2c,0)$，设 $A(x_{A},y_{A})$，
+$\vec{AF_{1}}=(-c-x_{A},\ -y_{A})$，由 $\vec{AF_{1}}\cdot\vec{F_{1}F_{2}}=0$ 得 $2c(-c-x_{A})=0$，即 $x_{A}=-c$．
+代入椭圆：$\dfrac{c^{2}}{a^{2}}+\dfrac{y_{A}^{2}}{b^{2}}=1\Rightarrow y_{A}^{2}=b^{2}\!\left(1-\dfrac{c^{2}}{a^{2}}\right)=\dfrac{b^{4}}{a^{2}}$，
+取 $A\!\left(-c,\ \dfrac{b^{2}}a\right)$．
+**第二步：由定比分点表示 $B$**
+$\vec{AF_{2}}=\left(2c,\ -\dfrac{b^{2}}a\right)$，设 $B(x,y)$，则 $\vec{F_{2}B}=(x-c,\ y)$．
+由 $\vec{AF_{2}}=\lambda\vec{F_{2}B}$：$x-c=\dfrac{2c}\lambda$、$y=-\dfrac{b^{2}}{\lambda a}$，
+即 $B\!\left(\dfrac{(\lambda+2)c}\lambda,\ -\dfrac{b^{2}}{\lambda a}\right)$．
+**第三步：代入椭圆方程**
+$\dfrac{(\lambda+2)^{2}c^{2}}{\lambda^{2}a^{2}}+\dfrac{b^{4}}{\lambda^{2}a^{2}b^{2}}=1$
+$\Rightarrow(\lambda+2)^{2}c^{2}+b^{2}=\lambda^{2}a^{2}$，
+代入 $b^{2}=a^{2}-c^{2}$：
+$(\lambda^{2}+4\lambda+4)c^{2}-c^{2}+a^{2}=\lambda^{2}a^{2}$
+$\Rightarrow(\lambda^{2}+4\lambda+3)c^{2}=(\lambda^{2}-1)a^{2}$
+$\Rightarrow\dfrac{c^{2}}{a^{2}}=\dfrac{\lambda^{2}-1}{\lambda^{2}+4\lambda+3}=\dfrac{(\lambda-1)(\lambda+1)}{(\lambda+1)(\lambda+3)}=\dfrac{\lambda-1}{\lambda+3}$．
+**第四步：求范围**
+$e^{2}=\dfrac{\lambda-1}{\lambda+3}=1-\dfrac4{\lambda+3}$，在 $\lambda\in[2,3]$ 上单调递增．
+$\lambda=2$：$e^{2}=\dfrac15$，$e=\dfrac{\sqrt5}5$；
+$\lambda=3$：$e^{2}=\dfrac26=\dfrac13$，$e=\dfrac{\sqrt3}3$．
+故 $e\in\left[\dfrac{\sqrt5}5,\ \dfrac{\sqrt3}3\right]$．</t>
+        </is>
+      </c>
+      <c r="Q409" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S409" t="n">
+        <v>5</v>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-331-E1</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>教辅录入-第35批</t>
+        </is>
+      </c>
+      <c r="V409" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「因为 $\vec{AF_{1}}\cdot\vec{F_{1}F_{2}}=0$，所以可设 $A(-c,\frac{b^{2}}a)$，$F_{2}(c,0)$，$B(x,y)$，由 $\vec{AF_{2}}=\lambda\vec{F_{2}B}$，得 $(2c,-\frac{b^{2}}a)=\lambda(x-c,y)$，即 $B(\frac{\lambda+2}\lambda c,-\frac{b^{2}}{\lambda a})$，因为 $B$ 在椭圆上，所以 $\frac{(1+\frac2\lambda)^{2}c^{2}}{a^{2}}+\frac{(-\frac{b^{2}}{\lambda a})^{2}}{b^{2}}=1$，即 $(\lambda+2)^{2}c^{2}+b^{2}=\lambda^{2}a^{2}$，即 $(\lambda^{2}+4\lambda+3)c^{2}=(\lambda^{2}-1)a^{2}$，即 $\frac ca=\frac{\lambda^{2}-1}{\lambda^{2}+4\lambda+3}=\frac{\lambda-1}{\lambda+3}=1-\frac4{\lambda+3}$ 在区间 $[2,3]$ 上为增函数」还原。
+**⚠ 原文笔误（如实标注）**：原文写「$\frac ca=\frac{\lambda-1}{\lambda+3}$」并直接得 $e\in[\frac{\sqrt5}5,\frac{\sqrt3}3]$ —— 但按 $\frac ca=\frac{\lambda-1}{\lambda+3}$，$\lambda=2$ 时应得 $e=\frac15\neq\frac{\sqrt5}5$。
+**正确应为 $\frac{c^{2}}{a^{2}}=\frac{\lambda-1}{\lambda+3}$**，即 $e=\sqrt{\frac{\lambda-1}{\lambda+3}}$：
+$\lambda=2$：$e^{2}=\frac15$ → $e=\frac1{\sqrt5}=\frac{\sqrt5}5$ ✓
+$\lambda=3$：$e^{2}=\frac13$ → $e=\frac1{\sqrt3}=\frac{\sqrt3}3$ ✓
+**与答案完全吻合** ✓ 故按 $e^{2}=\frac{\lambda-1}{\lambda+3}$ 录入。
+**独立验算**（取 $\lambda=2$ 反查）：$e=\frac{\sqrt5}5\approx0.4472$，$e^{2}=0.2$。取 $a=5$、$c=\sqrt5\approx2.236$、$b^{2}=25-5=20$、$b=2\sqrt5$。
+$A(-c,\frac{b^{2}}a)=(-2.236, 4)$；$B(\frac{4}{2}\cdot2.236, -\frac{20}{2\cdot5})=(4.472,-2)$。
+验 $B$ 在椭圆上：$\frac{4.472^{2}}{25}+\frac{4}{20}=\frac{20}{25}+0.2=0.8+0.2=1$ ✓ **成立**
+**结论正确** ✓（仅原文 $\frac ca$ 与 $\frac{c^{2}}{a^{2}}$ 的记号笔误）</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>M-H0410</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>圆锥曲线小题</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>M-T-331(解析几何 / 圆锥曲线小题 · 定比分点)</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>设双曲线 $C:\dfrac{x^{2}}{a^{2}}-\dfrac{y^{2}}{b^{2}}=1$（$a&gt;0,b&gt;0$）的右焦点为 $F$，过 $F$ 且斜率为 $\sqrt3$ 的直线交 $C$ 于 $A$、$B$ 两点，若 $\vec{AB}=5\vec{FB}$，则 $C$ 的离心率为 ____ ．</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr"/>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>$\dfrac65$</t>
+        </is>
+      </c>
+      <c r="P410" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：转化定比关系**
+$\vec{AB}=5\vec{FB}$：$B-A=5(B-F)\Rightarrow A=5F-4B$
+$\Rightarrow A-F=4(F-B)$，即 $F$ 在 $A$、$B$ 之间且 $|AF|=4|FB|$．
+设 $|FB|=m$，则 $|AF|=4m$、$|AB|=5m$．
+**第二步：用定义转化到准线距离**
+过 $A,B$ 分别作准线的垂线，垂足 $A_{1},B_{1}$．由双曲线定义 $\dfrac{|AF|}{|AA_{1}|}=\mathrm e$：
+$|AA_{1}|=\dfrac{4m}{\mathrm e}$，$|BB_{1}|=\dfrac{m}{\mathrm e}$．
+**第三步：构造直角三角形**
+过 $B$ 作 $BD\perp AA_{1}$ 于 $D$．因直线斜率为 $\sqrt3$，与 $x$ 轴（即准线垂线方向）夹角为 $60^\circ$，故 $\angle BAD=60^\circ$．
+$|AD|=|AA_{1}|-|BB_{1}|=\dfrac{4m}{\mathrm e}-\dfrac{m}{\mathrm e}=\dfrac{3m}{\mathrm e}$，
+又 $|AD|=|AB|\cos60^\circ=5m\times\dfrac12=\dfrac{5m}2$．
+**第四步：解 $\mathrm e$**
+$\dfrac{3m}{\mathrm e}=\dfrac{5m}2\Rightarrow \mathrm e=\dfrac65$．
+故答案为 $\dfrac65$．</t>
+        </is>
+      </c>
+      <c r="Q410" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S410" t="n">
+        <v>5</v>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-331-V1</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>教辅录入-第35批</t>
+        </is>
+      </c>
+      <c r="V410" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「由 $\vec{AB}=5\vec{FB}$ 可得 $AF=4FB$，设 $|AF|=4m$、$|BF|=m$，过 $A,B$ 分别做准线的垂线，垂足为 $A_{1},B_{1}$，由双曲线定义得 $|AA_{1}|=\frac{4m}{\mathrm e}$，$|BB_{1}|=\frac m{\mathrm e}$，过 $B$ 做 $BD$ 垂直于 $AA_{1}$ 垂足 $D$，因为 $AB$ 斜率为 $\sqrt3$，所以在 $\triangle ABD$ 中 $\angle BAD=60^\circ$，可得 $|AD|=\frac12|AB|$，即 $\frac{4m}{\mathrm e}-\frac m{\mathrm e}=\frac{3m}{\mathrm e}=\frac{5m}2$，解得 $\mathrm e=\frac65$」还原。
+**独立数值验证**（取 $a=5$，则 $\mathrm e=\frac65$ → $c=6$、$b^{2}=36-25=11$、$b=\sqrt{11}\approx3.3166$）：
+右焦点 $F(6,0)$，直线 $y=\sqrt3(x-6)$，代入 $\frac{x^{2}}{25}-\frac{y^{2}}{11}=1$：
+$\frac{x^{2}}{25}-\frac{3(x-6)^{2}}{11}=1$
+$11x^{2}-75(x^{2}-12x+36)=275$
+$-64x^{2}+900x-2700=275\Rightarrow64x^{2}-900x+2975=0$
+$x=\frac{900\pm\sqrt{810000-761600}}{128}=\frac{900\pm220}{128}$
+→ $x_{A}=8.75$、$x_{B}=5.3125$（均在右支 ✓）
+右支焦半径 $|PF|=\mathrm e\cdot x-a=\frac65x-5$：
+$|AF|=1.2\times8.75-5=10.5-5=5.5$
+$|BF|=1.2\times5.3125-5=6.375-5=1.375$
+$\frac{|AF|}{|BF|}=\frac{5.5}{1.375}=4.000$ ✓✓ **恰好等于 4**
+**答案 $\frac65$ 正确** ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>M-H0411</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>圆锥曲线小题</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>M-T-331(解析几何 / 圆锥曲线小题 · 定比分点)</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr">
+        <is>
+          <t>抛物线 $y^{2}=4x$，直线 $l$ 经过抛物线的焦点 $F$，与抛物线交于 $A$、$B$ 两点，若 $\vec{BA}=4\vec{BF}$，则 $\triangle OAB$（$O$ 为坐标原点）的面积为 ____ ．</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr"/>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>$\dfrac{4\sqrt3}3$</t>
+        </is>
+      </c>
+      <c r="P411" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：转化定比关系**
+$\vec{BA}=4\vec{BF}$：$A-B=4(F-B)$，即 $F$ 在 $BA$ 上距 $B$ 为 $\frac14$ 处，
+故 $|BF|:|FA|=1:3$．
+**第二步：参数化**
+$y^{2}=4x$ 即 $a=1$，焦点 $F(1,0)$；设 $A(t_{1}^{2},2t_{1})$、$B(t_{2}^{2},2t_{2})$．
+焦半径 $|FA|=a(1+t_{1}^{2})=1+t_{1}^{2}$、$|FB|=1+t_{2}^{2}$；焦点弦条件 $t_{1}t_{2}=-1$．
+**第三步：解 $t$**
+由 $|FA|=3|FB|$：$1+t_{1}^{2}=3(1+t_{2}^{2})$，代 $t_{1}=-\dfrac1{t_{2}}$，
+设 $u=t_{2}^{2}$：$1+\dfrac1u=3+3u\Rightarrow u+1=3u+3u^{2}$
+$\Rightarrow3u^{2}+2u-1=0\Rightarrow(3u-1)(u+1)=0\Rightarrow u=\dfrac13$．
+取 $t_{2}=\dfrac1{\sqrt3}$，则 $t_{1}=-\sqrt3$．
+**第四步：求面积**
+$y_{A}=2t_{1}=-2\sqrt3$、$y_{B}=2t_{2}=\dfrac2{\sqrt3}=\dfrac{2\sqrt3}3$，
+$|y_{A}-y_{B}|=2\sqrt3+\dfrac{2\sqrt3}3=\dfrac{8\sqrt3}3$．
+因 $O$、$F$ 都在 $x$ 轴上，$|OF|=1$，故以 $OF$ 为底：
+$S=\dfrac12|OF|\cdot|y_{A}-y_{B}|=\dfrac12\times1\times\dfrac{8\sqrt3}3=\dfrac{4\sqrt3}3$．
+故答案为 $\dfrac{4\sqrt3}3$．</t>
+        </is>
+      </c>
+      <c r="Q411" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S411" t="n">
+        <v>5</v>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-331-V2</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>教辅录入-第35批</t>
+        </is>
+      </c>
+      <c r="V411" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「联立可得 $y^{2}-4\sqrt3\,y-12=0$…则 $|y_{A}-y_{B}|=\frac{8\sqrt3}3$，故 $\triangle OAB$ 的面积 $S=\frac12\times|OF|\times|y_{A}-y_{B}|=\frac12\times1\times\frac{8\sqrt3}3=\frac{4\sqrt3}3$」还原。
+（详解的式子破碎，上述推导为**我独立完成**。）
+**独立验算**：
+① $t_{2}^{2}=\frac13$ → $B(\frac13,\frac{2}{\sqrt3})$；$t_{1}=-\sqrt3$ → $A(3,-2\sqrt3)$
+② 验在抛物线上：$(-2\sqrt3)^{2}=12=4\times3$ ✓；$(\frac{2}{\sqrt3})^{2}=\frac43=4\times\frac13$ ✓
+③ 验 $A,F,B$ 共线：$F(1,0)$、$B(\frac13,\frac{2}{\sqrt3})$，斜率 $=\frac{2/\sqrt3-0}{1/3-1}=\frac{2/\sqrt3}{-2/3}=-\frac3{\sqrt3}=-\sqrt3$；$A(3,-2\sqrt3)$：斜率 $=\frac{-2\sqrt3-0}{3-1}=-\sqrt3$ ✓ **三点共线** ✓
+④ $|BF|=\sqrt{(\frac13-1)^{2}+\frac43}=\sqrt{\frac49+\frac43}=\sqrt{\frac{16}{9}}=\frac43$；$|FA|=\sqrt{(3-1)^{2}+12}=\sqrt{16}=4$；$\frac{|FA|}{|BF|}=\frac4{4/3}=3$ ✓
+⑤ $S=\frac12\times1\times\frac{8\sqrt3}3=\frac{4\sqrt3}3\approx2.309$ ✓
+**另法验证**（行列式）：$S=\frac12|x_{A}y_{B}-x_{B}y_{A}|=\frac12|3\cdot\frac{2\sqrt3}3-\frac13\cdot(-2\sqrt3)|=\frac12|2\sqrt3+\frac{2\sqrt3}3|=\frac12\cdot\frac{8\sqrt3}3=\frac{4\sqrt3}3$ ✓ **两法一致**
+**答案 $\frac{4\sqrt3}3$ 正确** ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>M-H0412</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>圆锥曲线小题</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>M-T-331(解析几何 / 圆锥曲线小题 · 定比分点)</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr">
+        <is>
+          <t>直线过椭圆 $\dfrac{x^{2}}{a^{2}}+\dfrac{y^{2}}{b^{2}}=1$（$a&gt;0,b&gt;0$）的左焦点 $F$ 和上顶点 $A$，与圆心在原点的圆交于 $P,Q$ 两点，若 $PF=3FQ$，$\angle POQ=120^\circ$，则椭圆离心率为（　　）</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}3$</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt7}3$</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt{21}}7$</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P412" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：定直线 $FA$**
+$F(-c,0)$、$A(0,b)$，直线 $FA$：$\dfrac x{-c}+\dfrac yb=1$，即 $bx-cy+bc=0$，斜率 $k=\dfrac bc$．
+**第二步：由 $\angle POQ=120^\circ$ 得 $PM$ 与 $OM$ 的关系**
+设 $M$ 为 $PQ$ 中点，由垂径定理 $OM\perp PQ$，且 $OM$ 平分 $\angle POQ$，故 $\angle POM=60^\circ$、$\angle OPM=30^\circ$．
+在直角 $\triangle OPM$ 中：$\tan30^\circ=\dfrac{OM}{PM}\Rightarrow PM=\sqrt3\,OM$．
+**第三步：由 $PF=3FQ$ 得 $MF$**
+$P,F,Q$ 共线，$M$ 为 $PQ$ 中点．设 $PM=QM=s$，$F$ 在 $PQ$ 上且 $PF=3FQ$，可得 $MF=\dfrac s2$（$F$ 到近端为 $\frac{s}2$、
+到远端为 $\frac{3s}2$，比值为 $3$ ✓）．故 $MF=\dfrac{PM}2=\dfrac{\sqrt3}2OM$．
+**第四步：用 $\triangle OMF$ 的量联立**
+在直角 $\triangle OMF$ 中，$OF=c$：
+$OM=\dfrac{|b\cdot0-c\cdot0+bc|}{\sqrt{b^{2}+c^{2}}}=\dfrac{bc}a$，
+$MF=\sqrt{OF^{2}-OM^{2}}=\sqrt{c^{2}-\dfrac{b^{2}c^{2}}{a^{2}}}=c\sqrt{1-\dfrac{b^{2}}{a^{2}}}=c\cdot\dfrac ca=\dfrac{c^{2}}a$．
+代入 $MF=\dfrac{\sqrt3}2OM$：
+$\dfrac{c^{2}}a=\dfrac{\sqrt3}2\cdot\dfrac{bc}a\Rightarrow c=\dfrac{\sqrt3}2b\Rightarrow b=\dfrac{2c}{\sqrt3}$．
+**第五步：求离心率**
+$a^{2}=b^{2}+c^{2}=\dfrac{4c^{2}}3+c^{2}=\dfrac{7c^{2}}3$，
+$\mathrm e^{2}=\dfrac{c^{2}}{a^{2}}=\dfrac37$，$\mathrm e=\sqrt{\dfrac37}=\dfrac{\sqrt{21}}7$．
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q412" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S412" t="n">
+        <v>5</v>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-331-V3</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>教辅录入-第35批</t>
+        </is>
+      </c>
+      <c r="V412" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「∵椭圆的焦点在 $x$ 轴上，∴$a&gt;b&gt;0$，∴$F(-c,0)$、$A(0,b)$，故直线 $FA$ 的方程为 $\frac x{-c}+\frac yb=1$，即 $bx-cy+bc=0$，直线 $FA$（即 $PQ$）…则 $M$ 为 $PQ$ 的中点，∵$\angle POQ=120^\circ$，∴$\angle OPM=30^\circ$，…$\frac{OM}{PM}=\tan30^\circ$，…$k=\tan\angle MFO=\frac{OM}{MF}$…不妨令 $b=2\sqrt3\,t$、$c=3t$，则 $a=\sqrt{b^{2}+c^{2}}=\sqrt{21}\,t$，∴椭圆的离心率 $\mathrm e=\frac ca=\frac{\sqrt{21}}7$」还原。
+**独立验算**：
+① $b=\frac{2c}{\sqrt3}$ 与原文 $b=2\sqrt3 t$、$c=3t$ → $\frac bc=\frac{2\sqrt3}3=\frac2{\sqrt3}$ ✓ **一致**
+② $\mathrm e^{2}=\frac37$ → $\mathrm e=\sqrt{\frac37}=\frac{\sqrt3}{\sqrt7}=\frac{\sqrt{21}}7\approx0.6547$ ✓
+③ **数值反查**（取 $c=3$、$b=2\sqrt3$、$a=\sqrt{21}\approx4.5826$）：
+直线 $2\sqrt3x-3y+6\sqrt3=0$；$OM=\frac{6\sqrt3}{\sqrt{12+9}}=\frac{6\sqrt3}{\sqrt{21}}=2.2678$ ✓（$=\frac{bc}a$）
+$MF=\frac{c^{2}}a=\frac9{4.5826}=1.9639$ ✓
+$PM=\sqrt3\cdot OM=3.9279$；$\frac{MF}{PM}=\frac{1.9639}{3.9279}=0.500$ ✓ **恰为一半**
+$PF=PM+MF=5.8918$、$FQ=PM-MF=1.9640$；$\frac{PF}{FQ}=\frac{5.8918}{1.9640}=3.000$ ✓✓
+**答案 D 正确** ✓
+（注：$P$ 取在 $F$ 的另一侧，此时 $PF=3FQ$ 成立；若交换 $P,Q$ 命名则变为 $FQ=3PF$，不影响离心率。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>M-H0413</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>M-T-296(立体几何 / 外接球 · 垂面型)</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J413" s="2" t="inlineStr">
+        <is>
+          <t>在三棱锥 $P-ABC$ 中，$\triangle ABC$ 和 $\triangle PBC$ 都是边长为 $2\sqrt3$ 的正三角形，$PA=3\sqrt2$．若 $M$ 为三棱锥 $P-ABC$ 外接球上的动点，则点 $M$ 到平面 $ABC$ 距离的最大值为 ____ ．</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr"/>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>$\sqrt5+1$</t>
+        </is>
+      </c>
+      <c r="P413" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：证面面垂直**
+设 $T$ 为 $BC$ 中点．$\triangle ABC$、$\triangle PBC$ 均为边长 $2\sqrt3$ 的正三角形，
+故 $AT=PT=2\sqrt3\times\dfrac{\sqrt3}2=3$．
+由 $PA=3\sqrt2$ 得 $PA^{2}=18$，而 $AT^{2}+PT^{2}=9+9=18=PA^{2}$，
+故 $PT\perp AT$．又 $AT\perp BC$、$BC\cap PT=T$，所以 $AT\perp$ 面 $PBC$，
+从而面 $PBC\perp$ 面 $ABC$．
+**第二步：定球心**
+设 $O_{1}$、$O_{2}$ 分别为 $\triangle ABC$、$\triangle PBC$ 的外心．过 $O_{1}$ 作面 $ABC$ 的垂线、过 $O_{2}$ 作面 $PBC$ 的垂线，交点 $O$ 即球心．
+正三角形边长 $2\sqrt3$：外接圆半径 $=\dfrac{2\sqrt3}{\sqrt3}=2$，中心到边的距离 $=\dfrac13\times3=1$．
+故 $TO_{1}=TO_{2}=1$，四边形 $O_{1}TO_{2}O$ 为**边长 $1$ 的正方形**，$OO_{1}=1$．
+**第三步：求半径**
+$O_{2}P=2$（$\triangle PBC$ 外接圆半径），且 $OO_{2}\perp$ 面 $PBC$：
+$R=OP=\sqrt{OO_{2}^{2}+O_{2}P^{2}}=\sqrt{1+4}=\sqrt5$．
+**第四步：求最大距离**
+球心 $O$ 到平面 $ABC$ 的距离 $=OO_{1}=1$．
+球面上点到该平面的最大距离 $=R+OO_{1}=\sqrt5+1$．
+故答案为 $\sqrt5+1$．</t>
+        </is>
+      </c>
+      <c r="Q413" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5</v>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-296-E1</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>教辅录入-第35批</t>
+        </is>
+      </c>
+      <c r="V413" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「设 $BC$ 中点为 $T$，$\triangle ABC$ 的外心为 $O_{1}$，$\triangle PBC$ 的外心为 $O_{2}$，过点 $O_{1}$ 作面 $ABC$ 的垂线，过点 $O_{2}$ 作直线面 $PBC$ 的垂线，两条垂线的交点 $O$ 即为三棱锥 $P-ABC$ 外接球的球心，因为 $\triangle ABC$ 和 $\triangle PBC$ 都是边长为 $2\sqrt3$ 的正三角形，可得 $PT=AT=3$，又 $PA=3\sqrt2$，所以 $AT^{2}+PT^{2}=AP^{2}$，所以 $PT\perp AT$，又因为 $AT\perp BC$，$BC\cap PT=T$，所以 $AT\perp$ 面 $PBC$，因为 $AT\subset$ 平面 $ABC$，所以平面 $PBC\perp$ 平面 $ABC$，且 $TO_{1}=\frac13AT=1$，所以四边形 $O_{1}TO_{2}O$ 是边长为 $1$ 的正方形，所以外接球半径 $R=OP=\sqrt{OO_{2}^{2}+O_{2}P^{2}}=\sqrt{1+4}=\sqrt5$，$M$ 到平面 $ABC$ 的距离 $d\le R+OO_{1}=\sqrt5+1$，故答案为 $\sqrt5+1$」还原。
+**独立验算**：
+$AT=PT=2\sqrt3\cdot\frac{\sqrt3}2=3$ ✓；$AT^2+PT^2=18=PA^2=(3\sqrt2)^2$ ✓ → $PT\perp AT$ ✓
+正三角形边长 $2\sqrt3$：高 $=3$，外心到顶点 $=\frac23\cdot3=2$ ✓，到边 $=\frac13\cdot3=1$ ✓
+$TO_1=TO_2=1$ ✓ → 正方形 → $OO_1=OO_2=1$ ✓
+$R=\sqrt{OO_2^2+O_2P^2}=\sqrt{1+4}=\sqrt5$ ✓（$O_2P=2$）
+$d_{\max}=R+OO_1=\sqrt5+1$ ✓ **答案正确** ✓
+**⭐ 题型要点**：「两个共边的正三角形 + 第三边满足勾股」⟹ 面面垂直，这是垂面型中最常见的隐藏结构。</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>M-H0414</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>M-T-296(立体几何 / 外接球 · 垂面型)</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr">
+        <is>
+          <t>已知四棱锥 $P-ABCD$ 的底面 $ABCD$ 是边长为 $4$ 的正方形，$PH\perp$ 平面 $ABCD$，$PH=4$，$H$ 为 $AB$ 的中点，则该四棱锥的外接球表面积为（　　）</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>$32\pi$</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>$30\sqrt2\pi$</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>$41\pi$</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>$40\sqrt3\pi$</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P414" s="2" t="inlineStr">
+        <is>
+          <t>**建系**：$A(0,0,0)$、$B(4,0,0)$、$C(4,4,0)$、$D(0,4,0)$；$H$ 为 $AB$ 中点即 $H(2,0,0)$，由 $PH\perp$ 底面、$PH=4$ 得 $P(2,0,4)$．
+**定球心的位置**：底面 $ABCD$ 是正方形，其外心为中心 $O_{1}(2,2,0)$；球心 $O$ 在过 $O_{1}$ 且垂直底面的直线上，设 $O(2,2,t)$．
+**列方程**：$|OA|^{2}=|OP|^{2}$
+$|OA|^{2}=2^{2}+2^{2}+t^{2}=8+t^{2}$，
+$|OP|^{2}=(2-2)^{2}+(2-0)^{2}+(4-t)^{2}=4+(4-t)^{2}$．
+$8+t^{2}=4+16-8t+t^{2}\Rightarrow8t=12\Rightarrow t=\dfrac32$．
+**求表面积**：$R^{2}=8+\left(\dfrac32\right)^{2}=8+\dfrac94=\dfrac{41}4$，
+$S=4\pi R^{2}=4\pi\times\dfrac{41}4=41\pi$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q414" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5</v>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-296-V1</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>教辅录入-第35批</t>
+        </is>
+      </c>
+      <c r="V414" s="2" t="inlineStr">
+        <is>
+          <t>**⚠ 原题是三视图题（图未提取），题干已按详解重建为自足的文字描述**。
+详解给出几何体：「根据三视图可得原几何体如图所示，且 $PH\perp$ 平面 $ABCD$，$PH=4$，$H$ 为 $AB$ 的中点，四边形 $ABCD$ 为正方形，其边长为 $4$。设 $O_{1}$ 为正方形 $ABCD$ 的中心，$O_{2}$ 为 $\triangle PAB$ 的外心，则外接球的球心 $O$ 满足 $OO_{1}\perp$ 平面 $ABCD$，$OO_{2}\perp$ 平面 $PAB$，所以 $HO_{2}\parallel OO_{1}$，所以四边形 $HO_{2}OO_{1}$ 是…$(4-PO_{2})^{2}+4=PO_{2}^{2}$，故 $PO_{2}=\frac52$，…故外接球半径 $R^{2}=\dots=\frac{41}4$…选 C」
+**独立验算**（建系法，与详解方法不同）：
+$O(2,2,1.5)$：$|OA|^2=4+4+2.25=10.25$；$|OP|^2=0+4+(4-1.5)^2=4+6.25=10.25$ ✓ **相等**
+$R^2=10.25=\frac{41}4$ ✓ → $S=41\pi$ ✓ **答案 C 正确**
+**交叉验证** $\triangle PAB$ 的外接圆半径（详解给的 $PO_2=\frac52$）：
+$PA=PB=\sqrt{4^2+2^2}=2\sqrt5$、$AB=4$；面积 $=\frac12\cdot4\cdot4=8$；
+$R_c=\frac{PA\cdot PB\cdot AB}{4S}=\frac{2\sqrt5\cdot2\sqrt5\cdot4}{32}=\frac{80}{32}=\frac52$ ✓ **与详解一致**</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>M-H0415</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>M-T-296(立体几何 / 外接球 · 垂面型)</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J415" s="2" t="inlineStr">
+        <is>
+          <t>已知三棱锥 $A-BCD$ 中，平面 $ABD\perp$ 平面 $BCD$，且 $\triangle ABD$ 和 $\triangle BCD$ 都是边长为 $2$ 的等边三角形，则该三棱锥的外接球表面积为（　　）</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>$4\pi$</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>$\dfrac{16\pi}3$</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>$8\pi$</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>$\dfrac{20\pi}3$</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P415" s="2" t="inlineStr">
+        <is>
+          <t>**建系**（最直白）：令 $G$ 为 $BD$ 中点、置于原点，$BD$ 沿 $y$ 轴，
+$B(0,1,0)$、$D(0,-1,0)$；$\triangle BCD$ 在 $xy$ 平面内，$C(\sqrt3,0,0)$；
+由面 $ABD\perp$ 面 $BCD$ 且 $AG\perp BD$，得 $AG\perp$ 面 $BCD$，又 $AG=\sqrt3$，故 $A(0,0,\sqrt3)$．
+**求球心** $O(x,y,z)$：
+由 $|OB|=|OD|$ 得 $(y-1)^{2}=(y+1)^{2}\Rightarrow y=0$；
+由 $|OA|=|OB|$ 得 $y^{2}+(z-\sqrt3)^{2}=(y-1)^{2}+z^{2}$，代入 $y=0$：
+$z^{2}-2\sqrt3z+3=1+z^{2}\Rightarrow z=\dfrac1{\sqrt3}=\dfrac{\sqrt3}3$；
+由 $|OC|=|OB|$ 得 $(x-\sqrt3)^{2}+y^{2}=x^{2}+(y-1)^{2}$，代入 $y=0$：
+$x^{2}-2\sqrt3x+3=x^{2}+1\Rightarrow x=\dfrac1{\sqrt3}=\dfrac{\sqrt3}3$．
+故 $O\!\left(\dfrac{\sqrt3}3,\ 0,\ \dfrac{\sqrt3}3\right)$．
+**求半径**：$R^{2}=|OB|^{2}=\dfrac13+1+\dfrac13=\dfrac53$．
+**表面积**：$S=4\pi\times\dfrac53=\dfrac{20\pi}3$，选 D．</t>
+        </is>
+      </c>
+      <c r="Q415" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-296-V2</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>教辅录入-第35批</t>
+        </is>
+      </c>
+      <c r="V415" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「取 $BD$ 中点 $G$，连接 $AG$、$CG$，则 $AG\perp BD$，∵平面 $ABD\perp$ 平面 $BCD$，则 $AG\perp$ 平面 $BCD$，分别取 $\triangle ABD$ 与 $\triangle BCD$ 的外心 $E,F$，过 $E,F$ 分别作两面的垂线，相交于 $O$，则 $O$ 为三棱锥 $A-BCD$ 的外接球的球心。由 $\triangle ABD$ 与 $\triangle BCD$ 均为边长为 $2$ 的等边三角形，可得 $OE=OF=\frac13CG=\frac{\sqrt3}3$，∴$CE=\frac{2\sqrt3}3$，∴$R=OC=\sqrt{OE^{2}+CE^{2}}=\sqrt{\frac13+\frac43}$，∴三棱锥 $A-BCD$ 的外接球的表面积为 $4\pi\times R^{2}=4\pi\times\frac53=\frac{20\pi}3$」还原。
+（注：$CE=\frac{2\sqrt3}3$ 即等边三角形（边长 $2$）的外接圆半径 $=\frac23\times\sqrt3=\frac{2\sqrt3}3$ ✓）
+**独立验算**（建系法）：
+$O(\frac{\sqrt3}3,0,\frac{\sqrt3}3)\approx(0.5774,0,0.5774)$
+$|OA|^2=0+0+(\sqrt3-0.5774)^2=(1.7321-0.5774)^2=1.1547^2=1.3333$ ✓
+$|OB|^2=0.5774^2+1+0.5774^2=0.3333+1+0.3333=1.6667$ —— **不相等！**
+（**更正**：$|OA|^2$ 应为 $x^2+y^2+(z-\sqrt3)^2=0.3333+0+1.3333=1.6667$ ✓ —— 上面漏加了 $x^2$ 项，加上后与 $|OB|^2$ 相等 ✓）
+$|OC|^2=(0.5774-1.7321)^2+0+0.3333=1.3333+0.3333=1.6667$ ✓
+四点等距 ✓ **确为球心**；$R^2=\frac53$ ✓
+$S=4\pi\cdot\frac53=\frac{20\pi}3\approx20.944$ ✓ **答案 D 正确**
+**⭐ 速算**：两个全等的等边三角形（边长 $a$）沿公共边折成直二面角时，$R^{2}=\left(\frac{a}{2\sqrt3}\right)^{2}+\left(\frac{a}{\sqrt3}\right)^{2}\times\dots$ —— 本题 $R^{2}=\frac13+\frac43=\frac53$，其中 $\frac13$ 是外心到棱的距离的平方、$\frac43$ 是外接圆半径的平方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>M-H0416</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>M-T-296(立体几何 / 外接球 · 垂面型)</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr">
+        <is>
+          <t>在四面体 $P-ABC$ 中，三角形 $ABC$ 为等边三角形，边长为 $3$，$PA=3$，$PB=4$，$PC=5$，则四面体 $P-ABC$ 外接球表面积为（　　）</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>$12\pi$</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>$25\pi$</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>$\dfrac{80\pi}9$</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>$\dfrac{324\pi}{11}$</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P416" s="2" t="inlineStr">
+        <is>
+          <t>**建系**：$A(0,0,0)$、$B(3,0,0)$、$C\!\left(\dfrac32,\dfrac{3\sqrt3}2,0\right)$，设 $P(x,y,z)$．
+**定 $P$**：
+$PA^{2}=9$：$x^{2}+y^{2}+z^{2}=9$；
+$PB^{2}=16$：$(x-3)^{2}+y^{2}+z^{2}=16\Rightarrow-6x+9=7\Rightarrow x=\dfrac13$；
+$PC^{2}=25$：$\left(x-\dfrac32\right)^{2}+\left(y-\dfrac{3\sqrt3}2\right)^{2}+z^{2}=25$
+$\Rightarrow x^{2}+y^{2}+z^{2}-3x-3\sqrt3y+9=25$
+$\Rightarrow9-1-3\sqrt3y+9=25\Rightarrow-3\sqrt3y=8\Rightarrow y=-\dfrac{8\sqrt3}9$；
+$z^{2}=9-\dfrac19-\dfrac{64}{27}=\dfrac{243-3-64}{27}=\dfrac{176}{27}$．
+**定球心**：$\triangle ABC$ 为等边三角形，外心即重心
+$O_{1}\!\left(\dfrac32,\dfrac{\sqrt3}2,0\right)$，外接圆半径 $=\sqrt3$．
+设球心 $O\!\left(\dfrac32,\dfrac{\sqrt3}2,t\right)$，则 $|OA|^{2}=3+t^{2}$．
+$|OP|^{2}=\left(\dfrac13-\dfrac32\right)^{2}+\left(-\dfrac{8\sqrt3}9-\dfrac{\sqrt3}2\right)^{2}+(z-t)^{2}$
+$=\dfrac{49}{36}+\dfrac{625}{108}+(z-t)^{2}=\dfrac{193}{27}+(z-t)^{2}$．
+由 $|OA|^{2}=|OP|^{2}$：
+$3+t^{2}=\dfrac{193}{27}+z^{2}-2zt+t^{2}$
+$\Rightarrow3=\dfrac{193}{27}+\dfrac{176}{27}-2zt=\dfrac{369}{27}-2zt=\dfrac{41}3-2zt$
+$\Rightarrow2zt=\dfrac{41}3-3=\dfrac{32}3\Rightarrow t=\dfrac{16}{3z}$．
+**求半径**：
+$R^{2}=3+t^{2}=3+\dfrac{256}{9z^{2}}=3+\dfrac{256}{9\times\frac{176}{27}}=3+\dfrac{256\times3}{176}=3+\dfrac{48}{11}=\dfrac{81}{11}$．
+**表面积**：$S=4\pi\times\dfrac{81}{11}=\dfrac{324\pi}{11}$，选 D．</t>
+        </is>
+      </c>
+      <c r="Q416" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>5</v>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-296-V3</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>教辅录入-第35批</t>
+        </is>
+      </c>
+      <c r="V416" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（**原书只给答案 D，无详解**，
+上述建系求解为**我独立完成**）。
+**验算**：
+① $P$ 的坐标：$x=\frac13$ ✓；
+$y=-\frac{8\sqrt3}{9}\approx-1.5396$；$z^{2}=\frac{176}{27}\approx6.5185$，$z\approx2.5531$
+② 回代 $PA$：$\sqrt{\frac19+\frac{64}{27}+\frac{176}{27}}=\sqrt{0.1111+2.3704+6.5185}=\sqrt{9}=3$ ✓
+③ $PB$：$\sqrt{(\frac13-3)^2+\frac{64}{27}+\frac{176}{27}}=\sqrt{7.1111+8.8889}=\sqrt{16}=4$ ✓
+④ $PC$：$(x-\frac32)^2=(\frac13-1.5)^2=(-\frac76)^2=\frac{49}{36}=1.3611$；
+$(y-\frac{3\sqrt3}2)^2=(-\frac{8\sqrt3}9-\frac{3\sqrt3}2)^2=(-\frac{16\sqrt3+27\sqrt3}{18})^2=(-\frac{43\sqrt3}{18})^2=\frac{5547}{324}=17.12$；
+$z^2=6.5185$ → 合计 $1.3611+17.12+6.5185=25.0$ ✓ **$PC=5$ 成立** ✓
+⑤ $R^{2}=\frac{81}{11}\approx7.3636$，$S=4\pi\times7.3636=\frac{324\pi}{11}\approx92.52$ ✓
+**答案 D 正确** ✓
+（**注**：$3,4,5$ 在这里**不是**直角三角形关系 —— $PA=3,PB=4,PC=5$ 是三条侧棱，而底面边长也是 $3$，容易误以为 $PA\perp PB$ 而选错。）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V416"/>
+  <dimension ref="A1:V427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -43488,6 +43488,1377 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>M-H0417</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>解三角形小题(二)</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>M-T-205(三角函数 / 解三角形小题(二) · 图形5：“扩展线”)</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr">
+        <is>
+          <t>在 $\triangle ABC$ 中，$D$ 是边 $BC$ 上的一点，$\angle C=40^\circ$，$\angle CAD=60^\circ$，$BD=AC$，则 $\angle DBA=$（　　）</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>$20^\circ$</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>$25^\circ$</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>$30^\circ$</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>$35^\circ$</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P417" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：$\triangle ADC$ 中求角**
+$\angle C=40^\circ$、$\angle CAD=60^\circ$，故 $\angle ADC=180^\circ-40^\circ-60^\circ=80^\circ$．
+正弦定理：$\dfrac{AD}{\sin C}=\dfrac{AC}{\sin\angle ADC}$，即 $AD:AC=\sin40^\circ:\sin80^\circ$．
+设 $AD=k\sin40^\circ$、$AC=k\sin80^\circ$（$k&gt;0$），由 $BD=AC$ 得 $BD=k\sin80^\circ$．
+**第二步：$\triangle ABD$ 中列方程**
+设 $\angle DBA=\alpha$（$0&lt;\alpha&lt;90^\circ$）．$\angle ADB=180^\circ-80^\circ=100^\circ$，故 $\angle BAD=80^\circ-\alpha$．
+正弦定理：$\dfrac{AD}{\sin\alpha}=\dfrac{BD}{\sin(80^\circ-\alpha)}$，
+即 $\dfrac{\sin40^\circ}{\sin\alpha}=\dfrac{\sin80^\circ}{\sin(80^\circ-\alpha)}$．
+**第三步：化简**
+$\sin80^\circ=2\sin40^\circ\cos40^\circ$；$\sin(80^\circ-\alpha)=\sin[90^\circ-(10^\circ+\alpha)]=\cos(10^\circ+\alpha)$：
+$\cos(10^\circ+\alpha)=2\cos40^\circ\sin\alpha$．
+左 $=\cos10^\circ\cos\alpha-\sin10^\circ\sin\alpha$；
+右 $=2\cos(30^\circ+10^\circ)\sin\alpha=(\sqrt3\cos10^\circ-\sin10^\circ)\sin\alpha$．
+$\Rightarrow\sqrt3\cos10^\circ\sin\alpha-\sin10^\circ\sin\alpha=\cos10^\circ\cos\alpha-\sin10^\circ\sin\alpha$
+$\Rightarrow\sqrt3\cos10^\circ\sin\alpha=\cos10^\circ\cos\alpha\Rightarrow\sqrt3\sin\alpha=\cos\alpha$．
+**第四步**：$\tan\alpha=\dfrac1{\sqrt3}$，又 $0&lt;\alpha&lt;90^\circ$，故 $\alpha=30^\circ$．选 C．</t>
+        </is>
+      </c>
+      <c r="Q417" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S417" t="n">
+        <v>5</v>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-205-E1</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V417" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、详解完整 ✓。
+**⚠ 详解提取失真**：原文「即 $3\cos10^\circ\sin\alpha-\sin10^\circ\sin\alpha=\cos10^\circ\cos\alpha-\sin10^\circ\sin\alpha$，即 $3\sin\alpha=\cos\alpha$」两处 $3$ 实为 $\sqrt3$（根号丢失）。
+**反证**：若按字面 $3\sin\alpha=\cos\alpha$ 则 $\alpha=\arctan\frac13\approx18.4^\circ$，**四个选项无一符合** —— 必是 $\sqrt3$。
+**独立验算**（$\alpha=30^\circ$ 反查）：
+$\frac{AD}{\sin\alpha}=\frac{k\sin40^\circ}{\sin30^\circ}=\frac{0.6428k}{0.5}=1.2856k$；
+$\frac{BD}{\sin(80^\circ-30^\circ)}=\frac{k\sin80^\circ}{\sin50^\circ}=\frac{0.9848k}{0.7660}=1.2856k$ ✓ **两式相等，正弦定理成立**
+**答案 C 正确** ✓
+**⭐ 套路**：「扩展线」型用一条线段串起两个三角形，**各用一次正弦定理再联立**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>M-H0418</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>解三角形小题(二)</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>M-T-205(三角函数 / 解三角形小题(二) · 图形5：“扩展线”)</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J418" s="2" t="inlineStr">
+        <is>
+          <t>在 $\triangle ABC$ 中，$\angle BAC=60^\circ$，$BC=3$，且有 $\vec{CD}=2\vec{DB}$，则线段 $AD$ 长的最大值为（　　）</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt{13}}2$</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>$\sqrt3+1$</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>$2\sqrt3$</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P418" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：向量表示**
+由 $\vec{CD}=2\vec{DB}$ 知 $D$ 在线段 $BC$ 上，$BD=\dfrac13BC$、$DC=\dfrac23BC$．
+$\vec{AD}=\vec{AB}+\dfrac13\vec{BC}=\vec{AB}+\dfrac13(\vec{AC}-\vec{AB})=\dfrac23\vec{AB}+\dfrac13\vec{AC}$，即 $3\vec{AD}=2\vec{AB}+\vec{AC}$．
+**第二步：平方**
+$9|AD|^{2}=4c^{2}+b^{2}+4bc\cos A=4c^{2}+b^{2}+2bc$（$A=60^\circ$）．
+**第三步：化为三角函数**
+$\dfrac a{\sin A}=\dfrac3{\sin60^\circ}=2\sqrt3$，故 $b=2\sqrt3\sin B$、$c=2\sqrt3\sin C$，$B+C=120^\circ$．
+代入 $C=120^\circ-B$ 化简：$9|AD|^{2}=18\sqrt3\sin2B+36$，即 $|AD|^{2}=2\sqrt3\sin2B+4$．
+**第四步：求最值**
+$0&lt;B&lt;120^\circ$ → $0&lt;2B&lt;240^\circ$；当 $2B=90^\circ$（$B=45^\circ$）时 $\sin2B=1$ 最大．
+$|AD|^{2}_{\max}=2\sqrt3+4=(\sqrt3+1)^{2}$，故 $|AD|_{\max}=\sqrt3+1$．选 C．</t>
+        </is>
+      </c>
+      <c r="Q418" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S418" t="n">
+        <v>5</v>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-205-V1</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V418" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「$3\vec{AD}=2\vec{AB}+\vec{AC}$，所以 $9|AD|^{2}=b^{2}+4c^{2}+4\vec{AB}\cdot\vec{AC}=b^{2}+4c^{2}+2bc$…得出 $|AD|^{2}=2\sqrt3\sin2B+4$，∵$0&lt;B&lt;\frac{2\pi}3$，则 $0&lt;2B&lt;\frac{4\pi}3$，当 $2B=\frac\pi2$ 即 $B=\frac\pi4$ 时 $|AD|$ 取最大值，即 $|AD|_{\max}=\sqrt{4+2\sqrt3}=\sqrt3+1$」还原。
+**选项用字符坐标确认**（PDF 页 167，y≈546/556）：A 分子`1`(x=66.5)`3`(x=71.0)/分母`2`(x=65.5)→$\frac{\sqrt{13}}2$；B `2`(x=115.6)→$2$；C `3`(x=176.8)`+``1`(x=194.9)→$\sqrt3+1$；D `2`(x=227.4)`3`(x=237.4)→$2\sqrt3$。
+（四选项 $1.803&lt;2&lt;2.732&lt;3.464$ 递增，作为「最大值」合理 ✓；D 超过实际最大值，是典型干扰项）
+**独立验算**（$B=45^\circ$ 数值对拍）：
+$C=75^\circ$；$b=2\sqrt3\sin45^\circ=2.4495$；$c=2\sqrt3\sin75^\circ=3.3461$
+$9|AD|^2=4c^2+b^2+2bc=44.785+6.0+16.393=67.178$ → $|AD|^2=7.4642$
+公式值：$2\sqrt3\sin90^\circ+4=3.4641+4=7.4641$ ✓✓ **完全吻合**
+$|AD|=\sqrt{7.4641}=2.7320=\sqrt3+1$ ✓ **答案 C 正确**
+（校验 $(\sqrt3+1)^2=4+2\sqrt3=7.4641$ ✓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>M-H0419</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>解三角形小题(二)</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>M-T-205(三角函数 / 解三角形小题(二) · 图形5：“扩展线”)</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J419" s="2" t="inlineStr">
+        <is>
+          <t>如图，$D$ 为 $\triangle ABC$ 的边 $AC$ 上一点，$|AD|=2|DC|$，$\angle ABC=60^\circ$，$|\vec{AB}|+2|\vec{BC}|=4$，当 $|\vec{BD}|$ 取最小值时，$\triangle ABC$ 的面积为（　　）</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>$2\sqrt3$</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>$\sqrt3$</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}2$</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}4$</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P419" s="2" t="inlineStr">
+        <is>
+          <t>**设元**：$CD=x$、$BD=y$、$BC=m$，则 $AD=2x$、$AC=3x$；由 $|AB|+2|BC|=4$ 得 $AB=4-2m$．
+**第一步：$\triangle ABC$ 中余弦定理**
+$\cos B=\dfrac{(4-2m)^{2}+m^{2}-9x^{2}}{2m(4-2m)}=\dfrac12$
+$\Rightarrow m(4-2m)=(4-2m)^{2}+m^{2}-9x^{2}$
+$\Rightarrow4m-2m^{2}=16-16m+5m^{2}-9x^{2}$
+$\Rightarrow9x^{2}=7m^{2}-20m+16$　①
+**第二步：互补角余弦**
+$\angle ADB+\angle BDC=\pi$，故 $\cos\angle ADB=-\cos\angle BDC$．
+$\dfrac{4x^{2}+y^{2}-(4-2m)^{2}}{4xy}=-\dfrac{x^{2}+y^{2}-m^{2}}{2xy}$
+$\Rightarrow4x^{2}+y^{2}-(4-2m)^{2}=-2x^{2}-2y^{2}+2m^{2}$
+$\Rightarrow3y^{2}=-6x^{2}+2m^{2}+(4-2m)^{2}$
+$\Rightarrow y^{2}=-2x^{2}+2m^{2}-\dfrac{16}3m+\dfrac{16}3$　②
+**第三步：代入①配方**
+$y^{2}=\dfrac{-14m^{2}+40m-32+18m^{2}-48m+48}9=\dfrac{4m^{2}-8m+16}9=\dfrac49\bigl[(m-1)^{2}+3\bigr]$．
+**第四步**：$m=1$ 时 $y^{2}$ 最小，此时 $BC=1$、$AB=2$．
+$S=\dfrac12\times2\times1\times\dfrac{\sqrt3}2=\dfrac{\sqrt3}2$．选 C．</t>
+        </is>
+      </c>
+      <c r="Q419" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S419" t="n">
+        <v>5</v>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-205-V2</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V419" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「设 $CD=x$、$BD=y$、$BC=m$，则 $AD=2x$、$AB=4-2m$，…由余弦定理可得 $9x^{2}=7m^{2}-20m+16$；又∵$\angle ADB+\angle BDC=\pi$，∴$\cos\angle ADB=-\cos\angle BDC$，…当 $m=1$ 时 $y^{2}$ 有最小值，此时 $BC=1$、$AB=2$，所以 $S_{\triangle ABC}=\frac12\times2\times1\times\sin60^\circ$…故选 C」还原。
+**选项字符坐标确认**（PDF 页 167，y≈247~257 右栏）：A `2`(x=335.0)`3`(x=344.9)→$2\sqrt3$；B `3`(x=396.5)→$\sqrt3$；C 分子`3`(x=454.4)/分母`2`(x=451.3)→$\frac{\sqrt3}2$；D 分子`3`(x=510.4)/分母`4`(x=507.4)→$\frac{\sqrt3}4$。
+（$3.464,1.732,0.866,0.433$ 成等比，面积类选项的典型设计 ✓）
+**独立验算**：
+① $(4-2m)^2+m^2=16-16m+5m^2$ ✓ → $9x^2=16-16m+5m^2-4m+2m^2=7m^2-20m+16$ ✓
+② 代入后 $\frac{4m^2-8m+16}{9}=\frac49[(m-1)^2+3]$ ✓
+$m=1$：$y^2=\frac43$、$x^2=\frac{7-20+16}9=\frac13$ ✓
+③ $S=\frac12\cdot2\cdot1\cdot\frac{\sqrt3}2=\frac{\sqrt3}2\approx0.866$ ✓ **答案 C 正确**
+**⭐ 提速**：不必真求 $x$、$y$，配成关于 $m$ 的二次式找到最小值点，回代算面积即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>M-H0420</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>解三角形小题(二)</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>M-T-205(三角函数 / 解三角形小题(二) · 图形5：“扩展线”)</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J420" s="2" t="inlineStr">
+        <is>
+          <t>在 $\triangle ABC$ 中，$A&gt;B$，$BC=10$，$\sin C=\dfrac{3\sqrt7}{32}$，$\cos(A-B)=\dfrac18$．若点 $P$ 是 $\triangle ABC$ 所在平面内任意一点，则 $|\vec{PA}|-|\vec{PC}|$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>$[-5,5]$</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>$[-6,6]$</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>$[-7,7]$</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>$[-8,8]$</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P420" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：转化为边长**
+对任意 $P$，$\bigl||PA|-|PC|\bigr|\le|AC|$，等号可取到（$P$ 在直线 $AC$ 上、位于 $A$ 或 $C$ 外侧时）．故只需求 $|AC|$．
+**第二步：构造 $D$**
+因 $A&gt;B$，可在 $BC$ 上取 $D$ 使 $\angle BAD=B$．
+$\triangle ABD$ 中 $\angle BAD=\angle ABD=B$，故 $AD=BD$．设 $AD=BD=x$，则 $CD=10-x$．
+此时 $\angle CAD=A-B$，故 $\cos\angle CAD=\dfrac18$、$\sin\angle CAD=\sqrt{1-\dfrac1{64}}=\dfrac{3\sqrt7}8$．
+**第三步：正弦定理**
+$\dfrac{CD}{\sin\angle CAD}=\dfrac{AD}{\sin C}\Rightarrow\dfrac{10-x}{3\sqrt7/8}=\dfrac{x}{3\sqrt7/32}$
+$\Rightarrow8(10-x)=32x\Rightarrow x=2$．故 $AD=2$、$CD=8$．
+**第四步：余弦定理求 $AC$**
+$\dfrac{4+AC^{2}-64}{4AC}=\dfrac18\Rightarrow8(AC^{2}-60)=4AC$
+$\Rightarrow2AC^{2}-AC-120=0\Rightarrow(2AC+15)(AC-8)=0\Rightarrow AC=8$．
+**结论**：$|\vec{PA}|-|\vec{PC}|\in[-8,8]$．选 D．</t>
+        </is>
+      </c>
+      <c r="Q420" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S420" t="n">
+        <v>5</v>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-205-V3</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V420" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓。由详解「由于 $A&gt;B$，设 $D$ 是 $BC$ 上一点…由 $\cos(A-B)=\frac18$ 得 $\cos\angle CAD=\frac18$…设 $BD=x$，$AD=x$、$CD=10-x$，$\sin\angle CAD=\frac{3\sqrt7}8$、$\sin C=\frac{3\sqrt7}{32}$，由正弦定理…解得 $x=2$，所以 $AD=2$、$CD=8$。在 $\triangle ADC$ 中由余弦定理…化简得 $2AC^{2}-AC-120=0$…得 $AC=8$。$|\vec{PA}|-|\vec{PC}|$ 表示点 $P$ 到 $A,C$ 的距离之差，所以 $\bigl||PA|-|PC|\bigr|\le|CA|=8$，所以 $-8\le|PA|-|PC|\le8$」还原。
+**⚠ 提取失真**：题干 $\sin C=\frac{3\sqrt7}{32}$ 与详解 $\sin\angle CAD=\frac{3\sqrt7}8$ 都被提取成 `3 7 32` 样式，根号丢失。
+**独立验算**：
+① $8(10-x)=32x$ → $x=2$ ✓；$CD=8$ ✓；$2AC^2-AC-120=0$ → $AC=8$ ✓
+② **角度链条闭合**：$\angle ADB=180^\circ-2B$ → $\angle ADC=2B$；$\triangle ADC$ 内角和 $(A-B)+2B+C=180^\circ$ → $A+B+C=180^\circ$ ✓ **恒等**
+③ 数值：$B=\frac12\arcsin\frac{3\sqrt7}8=41.41^\circ$；$A-B=82.82^\circ$ → $A=124.23^\circ$；$C=180-124.23-41.41=14.36^\circ$
+$\sin C=\sin14.36^\circ=0.2480=\frac{3\sqrt7}{32}=\frac{7.9373}{32}=0.2480$ ✓✓ **完全吻合**
+**答案 D 正确** ✓
+**⭐ 构造的巧思**：取 $\angle BAD=B$ 使 $\triangle ABD$ 等腰（$AD=BD$），同时 $\angle CAD=A-B$ 正好接上已知 $\cos(A-B)=\frac18$ —— **一个构造同时解决两件事**，这是本题关键。</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>M-H0421</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>解三角形小题(二)</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>M-T-210(三角函数 / 解三角形小题(二) · 四心4：垂心)</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J421" s="2" t="inlineStr">
+        <is>
+          <t>若 $O$ 是 $\triangle ABC$ 垂心，$\angle A=\dfrac\pi6$，且 $\sin B\cos C\,\vec{AB}+\sin C\cos B\,\vec{AC}=2m\sin B\sin C\,\vec{AO}$，则 $m=$（　　）</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}2$</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}3$</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}6$</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P421" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：两边除以 $\sin B\sin C$**
+$\dfrac{\cos C}{\sin C}\vec{AB}+\dfrac{\cos B}{\sin B}\vec{AC}=2m\,\vec{AO}$．
+**第二步：分解 $\vec{AO}$**
+连接 $CO$ 延长交 $AB$ 于 $D$．因 $O$ 是垂心，$CD\perp AB$，且 $\vec{AO}=\vec{AD}+\vec{DO}$．
+**第三步：两边同乘 $\vec{AB}$（点乘）**
+$\dfrac{\cos C}{\sin C}\vec{AB}\cdot\vec{AB}+\dfrac{\cos B}{\sin B}\vec{AC}\cdot\vec{AB}=2m(\vec{AD}+\vec{DO})\cdot\vec{AB}$．
+· $\vec{AB}\cdot\vec{AB}=c^{2}$；$\vec{AC}\cdot\vec{AB}=bc\cos A$；
+· 因 $DO\perp AB$，$\vec{DO}\cdot\vec{AB}=0$，故 $(\vec{AD}+\vec{DO})\cdot\vec{AB}=|\vec{AD}|\cdot|\vec{AB}|=b\cos A\cdot c$．
+得 $\dfrac{\cos C}{\sin C}c^{2}+\dfrac{\cos B}{\sin B}bc\cos A=2m\,bc\cos A$．
+**第四步：用正弦定理统一**
+代入 $c=2R\sin C$、$b=2R\sin B$、$\cos A=\dfrac{\sqrt3}2$：
+$\dfrac{\cos C}{\sin C}\cdot4R^{2}\sin^{2}C+\dfrac{\cos B}{\sin B}\cdot4R^{2}\sin B\sin C\cdot\dfrac{\sqrt3}2$
+$=2m\cdot4R^{2}\sin B\sin C\cdot\dfrac{\sqrt3}2$
+$\Rightarrow4R^{2}\sin C\cos C+2\sqrt3R^{2}\cos B\sin C$
+$=4\sqrt3\,mR^{2}\sin B\sin C$．
+除以 $2R^{2}\sin C$：$2\cos C+\sqrt3\cos B=2\sqrt3\,m\sin B$．
+**第五步：代入 $C=\dfrac{5\pi}6-B$**
+$\cos C=\cos\!\left(\dfrac{5\pi}6-B\right)$
+$=-\dfrac{\sqrt3}2\cos B+\dfrac12\sin B$，
+故 $2\cos C=-\sqrt3\cos B+\sin B$，
+$2\cos C+\sqrt3\cos B=\sin B$（**余弦项恰好抵消**）．
+由 $\sin B=2\sqrt3\,m\sin B$ 且 $\sin B\neq0$：
+$m=\dfrac1{2\sqrt3}=\dfrac{\sqrt3}6$．选 D．</t>
+        </is>
+      </c>
+      <c r="Q421" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S421" t="n">
+        <v>5</v>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-210-E1</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V421" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「在 $\triangle ABC$ 中，$\sin B\sin C\neq0$，由 $\sin B\cos C\vec{AB}+\sin C\cos B\vec{AC}=2m\sin B\sin C\vec{AO}$ 得 $\frac{\cos C}{\sin C}\vec{AB}+\frac{\cos B}{\sin B}\vec{AC}=2m\vec{AO}$，连接 $CO$ 并延长交 $AB$ 于 $D$，因为 $O$ 是 $\triangle ABC$ 的垂心，所以 $CD\perp AB$，$\vec{AO}=\vec{AD}+\vec{DO}$…同乘 $\vec{AB}$ 得，$\frac{\cos C}{\sin C}c^{2}+\frac{\cos B}{\sin B}bc\cos A=2m\,b\cos A\cdot c$，因为 $A=\frac\pi6$…又 $\sin C\neq0$，所以有 $\cos C+\cos B=3m\sin B$，而 $C=\pi-A-B=\frac{5\pi}6-B$，所以 $\cos C=\cos(\frac{5\pi}6-B)$=-\frac{\sqrt3}2\cos B+\frac12\sin B$，
+所以得到 $\frac12\sin B=3m\sin B$，而 $\sin B\neq0$，所以得到 $m=\frac{\sqrt3}6$」还原。
+**⚠ 详解中间式有笔误**（已用我的推导核对）：原文的「$\cos C+\cos B=3m\sin B$」与「$\frac12\sin B=3m\sin B$」应为$2\cos C+\sqrt3\cos B=2\sqrt3 m\sin B$ 与 $\sin B=2\sqrt3 m\sin B$。
+（原文两处的 `3` 实为 $\sqrt3$、漏了系数 $2$；但最终 $m=\frac{\sqrt3}6$ 与我的推导**一致** ✓）
+**独立验算**（数值反查，取 $B=40^\circ$）：
+$A=30^\circ$、$C=\frac{5\pi}6-40^\circ=150^\circ-40^\circ=110^\circ$
+取 $R=1$：$b=2\sin40^\circ=1.2856$、$c=2\sin110^\circ=1.8794$、$a=2\sin30^\circ=1$
+左端 $=\sin40^\circ\cos110^\circ\cdot c^2+\sin110^\circ\cos40^\circ\cdot bc\cos30^\circ$
+$=0.6428\times(-0.3420)\times3.5321+0.9397\times0.7660\times1.2856\times1.8794\times0.8660$
+$=-0.7766+1.5089=0.7323$
+右端 $=2m\sin40^\circ\sin110^\circ\cdot b\cos A\cdot c$
+$=2m\times0.6428\times0.9397\times1.2856\times0.8660\times1.8794=2.3909m$
+$\frac{0.7323}{2.3909}=0.3063$…（应为 $m$ 与其他因子的比，此处直接代 $m=\frac{\sqrt3}6=0.2887$）
+**改用 $m$ 反代**：$2\times0.2887\times0.6428\times0.9397\times1.2856\times0.8660\times1.8794$
+$=0.5774\times0.6428\times0.9397\times1.2856\times0.8660\times1.8794$
+$=0.3711\times0.9397=0.3487$；$\times1.2856=0.4483$；$\times0.8660=0.3882$；$\times1.8794=0.7296$
+与左端 $0.7323$ **吻合**（差 $0.4\%$，来自四舍五入）✓
+**答案 D（$\frac{\sqrt3}6\approx0.2887$）正确** ✓
+**⭐ 本题精华**：代入 $C=\frac{5\pi}6-B$ 后 $\sqrt3\cos B$ 项**恰好抵消**，这是命题人设计好的 —— 否则 $m$ 会依赖 $B$，就不是定值了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>M-H0422</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>解三角形小题(二)</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>M-T-210(三角函数 / 解三角形小题(二) · 四心4：垂心)</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J422" s="2" t="inlineStr">
+        <is>
+          <t>点 $P$ 为 $\triangle ABC$ 所在平面内的动点，满足 $\vec{AP}=t\!\left(\dfrac{\vec{AB}}{|AB|\cos B}+\dfrac{\vec{AC}}{|AC|\cos C}\right)$，$t\in[0,+\infty)$，则点 $P$ 的轨迹通过 $\triangle ABC$ 的（　　）</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>外心</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>重心</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>垂心</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>内心</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P422" s="2" t="inlineStr">
+        <is>
+          <t>**核心：验证 $\vec{AP}\perp\vec{BC}$**
+计算 $\vec{AP}\cdot\vec{BC}$：
+$\vec{AP}\cdot\vec{BC}=t\!\left(\dfrac{\vec{AB}\cdot\vec{BC}}{|AB|\cos B}+\dfrac{\vec{AC}\cdot\vec{BC}}{|AC|\cos C}\right)$．
+**第一项**：$\vec{AB}$ 与 $\vec{BC}$ 的夹角为 $\pi-B$（注意方向），
+$\vec{AB}\cdot\vec{BC}=|AB|\cdot|BC|\cos(\pi-B)=-|AB||BC|\cos B$，
+故 $\dfrac{\vec{AB}\cdot\vec{BC}}{|AB|\cos B}=-|BC|$．
+**第二项**：$\vec{AC}$ 与 $\vec{BC}$ 的夹角为 $C$，
+$\vec{AC}\cdot\vec{BC}=|AC|\cdot|BC|\cos C$，
+故 $\dfrac{\vec{AC}\cdot\vec{BC}}{|AC|\cos C}=|BC|$．
+**相加**：$\vec{AP}\cdot\vec{BC}=t(-|BC|+|BC|)=0$．
+故 $AP\perp BC$，即 $P$ 恒在过 $A$ 且垂直 $BC$ 的直线（**$A$ 边上的高**）上．
+由 $t\in[0,+\infty)$，$P$ 的轨迹是这条高线（以 $A$ 为端点的射线方向），而三条高交于**垂心**，故轨迹过垂心．选 C．</t>
+        </is>
+      </c>
+      <c r="Q422" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S422" t="n">
+        <v>5</v>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-210-V1</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V422" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（**原书无详解**，上述证明为我独立完成）。
+**独立验算**（数值验证 $\vec{AP}\perp\vec{BC}$）：
+取 $A(0,0)$、$B(4,0)$、$C(1,3)$。
+$|AB|=4$、$|AC|=\sqrt{10}=3.1623$、$|BC|=\sqrt{9+9}=4.2426$
+$\cos B=\frac{\vec{BA}\cdot\vec{BC}}{|BA||BC|}=\frac{(-4,0)\cdot(-3,3)}{4\times4.2426}$=\frac{12}{16.9706}=0.7071$
+$\cos C=\frac{\vec{CA}\cdot\vec{CB}}{|CA||CB|}=\frac{(-1,-3)\cdot(3,-3)}{3.1623\times4.2426}$=\frac{-3+9}{13.4164}=0.4472$
+括号内向量 $=\frac{(4,0)}{4\times0.7071}+\frac{(1,3)}{3.1623\times0.4472}$=(1.4142,0)+(0.7071,2.1213)=(2.1213,2.1213)$
+$\vec{AC}$ 方向的高：过 $A$ 垂直 $BC$。$\vec{BC}=(-3,3)$，垂线方向 $(3,3)$ 或 $(1,1)$ —— 
+括号内 $(2.1213,2.1213)=2.1213(1,1)$ ✓ **正是 $BC$ 的垂线方向**
+$\vec{AP}\cdot\vec{BC}=2.1213(1,1)\cdot(-3,3)=2.1213\times0=0$ ✓✓ **完全垂直**
+**答案 C（垂心）正确** ✓
+**⭐ 通法总结**：判断轨迹过哪个「心」，就与**对边**点乘：
+· 结果为 $0$ → 垂直对边 → **垂心**
+· 若 $\vec{AP}\cdot\vec{BC}$ 与边长有关且满足中垂线性质 → **外心**
+· 若为 $\frac{\vec{AB}}{|AB|}+\frac{\vec{AC}}{|AC|}$（角平分方向） → **内心**
+· 若为 $\vec{AB}+\vec{AC}$（中线方向） → **重心**
+（本题分母多了 $\cos B$、$\cos C$，正是为了凑出「$-|BC|+|BC|=0$」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>M-H0423</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>解三角形小题(二)</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>M-T-210(三角函数 / 解三角形小题(二) · 四心4：垂心)</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr">
+        <is>
+          <t>$\triangle ABC$ 的垂心 $H$ 在其内部，$\angle A=30^\circ$，$AH=\sqrt3$，则 $\sqrt3\,BH+CH$ 的取值范围是 ____ ．</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="inlineStr"/>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>$\left(1,\ \sqrt3\right)$</t>
+        </is>
+      </c>
+      <c r="P423" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求 $BC$**
+垂心性质：$AH=2R\cos A$，故 $\sqrt3=2R\cos30^\circ=2R\cdot\dfrac{\sqrt3}2=R\sqrt3$，得 $R=1$．
+$BC=a=2R\sin A=2\times1\times\dfrac12=1$．
+**第二步：$\triangle BHC$ 中的角度关系**
+由垂心性质 $\angle BHC=180^\circ-\angle A=150^\circ$．设 $\angle BCH=\alpha$，则 $\angle HBC=180^\circ-150^\circ-\alpha=30^\circ-\alpha$，
+由 $H$ 在内部知 $0&lt;\alpha&lt;30^\circ$．
+**第三步：正弦定理**
+$\dfrac{BC}{\sin\angle BHC}=\dfrac{1}{\sin150^\circ}=\dfrac1{1/2}=2$，
+故 $BH=2\sin(\angle BCH)=2\sin\alpha$、$CH=2\sin(\angle HBC)=2\sin(30^\circ-\alpha)$．
+**第四步：化简**
+$\sqrt3\,BH+CH=2\sqrt3\sin\alpha+2\sin(30^\circ-\alpha)$
+$=2\sqrt3\sin\alpha+2\!\left(\dfrac12\cos\alpha-\dfrac{\sqrt3}2\sin\alpha\right)$
+$=2\sqrt3\sin\alpha+\cos\alpha-\sqrt3\sin\alpha=\sqrt3\sin\alpha+\cos\alpha$
+$=2\sin(\alpha+30^\circ)$．
+**第五步：求值域**
+$\alpha\in(0,30^\circ)\Rightarrow\alpha+30^\circ\in(30^\circ,60^\circ)$，
+$\sin(\alpha+30^\circ)\in\left(\dfrac12,\dfrac{\sqrt3}2\right)$（两端均取不到），
+故 $\sqrt3\,BH+CH\in(1,\sqrt3)$．</t>
+        </is>
+      </c>
+      <c r="Q423" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S423" t="n">
+        <v>5</v>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-210-V3</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V423" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「设 $AD$、$BE$ 是高，$H$ 就是 $AD$、$BE$ 交点，那么 $AD\perp BC$，$\angle DAC+\angle ACD=90^\circ$，$BE\perp AC$，$\angle CBE+\angle DCA=90^\circ$，所以 $\angle DAC=\angle CBE$，所以 Rt$\triangle AHE\sim$ Rt$\triangle BCE$，所以 $\frac{AH}{BC}=\frac{AE}{BE}$，$AH=BC\times\frac{AE}{BE}=BC\times\cot\angle A=BC\times\cot30^\circ=\sqrt3$，∴$BC=1$。在 $\triangle BHC$ 中，$\angle BHC=150^\circ$，$BC=1$，设 $\angle BCH=\alpha$，由正弦定理可得 $\frac{BC}{\sin\angle BHC}=\frac{BH}{\sin\angle BCH}=\frac{CH}{\sin\angle HBC}=2$。∴$\sqrt3 BH+CH=\sqrt3\times2\sin\angle BCH+2\sin(\frac\pi6-\angle BCH)$$=\sqrt3\sin\alpha+\cos\alpha=2\sin(\alpha+\frac\pi6)$，∵$\alpha\in(0,\frac\pi6)$，∴$\sin(\alpha+\frac\pi6)\in(\frac12,\frac{\sqrt3}2)$，∴$2\sin(\alpha+\frac\pi6)\in(1,\sqrt3)$」还原。
+**⚠⚠ 原书三处根号丢失（已还原并反证）**：
+① 题干 `AH = 3` 实为 **$AH=\sqrt3$**
+② 详解「$=3\sin\alpha+\cos\alpha$」实为 **$\sqrt3\sin\alpha+\cos\alpha$**
+③ 答案 `(1, 3)` 实为 **$(1,\sqrt3)$**
+**反证（关键）**：若按字面 $AH=3$，则由 $AH=2R\cos A$ 得 $3=R\sqrt3$ → $R=\sqrt3$ → $BC=2R\sin30^\circ=\sqrt3$ 而非 $1$；
+进而 $\frac{BC}{\sin150^\circ}=2\sqrt3$，$BH=2\sqrt3\sin\alpha$，$\sqrt3BH+CH=3\sin\alpha+\sqrt3\cos\alpha=2\sqrt3\sin(\alpha+30^\circ)\in(\sqrt3,3)$ —— **与答案 $(1,\sqrt3)$ 矛盾**。
+取 $AH=\sqrt3$ 则 $R=1$、$BC=1$，结果 $(1,\sqrt3)$ ✓ **与答案完全吻合**。
+**独立验算**：
+① $AH=2R\cos A$：$\sqrt3=2R\cdot\frac{\sqrt3}2$ → $R=1$ ✓；$BC=2\cdot1\cdot\frac12=1$ ✓
+② $\angle BHC=180^\circ-30^\circ=150^\circ$ ✓
+③ 端点：$\alpha\to0$ 时 $2\sin30^\circ=1$（取不到，因 $\alpha&gt;0$）✓；$\alpha\to30^\circ$ 时 $2\sin60^\circ=\sqrt3$（取不到，因 $\angle HBC&gt;0$）✓
+④ 中点抽查：$\alpha=15^\circ$ → $2\sin45^\circ=1.4142\in(1,1.732)$ ✓
+**答案 $(1,\sqrt3)$ 正确** ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>M-H0424</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>平面向量</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>向量小题</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>M-T-242(平面向量 / 向量小题 · 解析几何中的向量  ↔解析几何)</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr">
+        <is>
+          <t>已知点 $M(1,0)$，$A,B$ 是椭圆 $\dfrac{x^{2}}4+y^{2}=1$ 上的动点，且 $\vec{MA}\cdot\vec{MB}=0$，则 $\vec{MA}\cdot\vec{BA}$ 的取值范围是（　　）</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac23,1\right]$</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>$[1,9]$</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac23,9\right]$</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>$\left[\dfrac63,3\right]$</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P424" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：化简所求式**
+因 $\vec{BA}=\vec A-\vec B=(\vec A-\vec M)-(\vec B-\vec M)=\vec{MA}-\vec{MB}$，
+$\vec{MA}\cdot\vec{BA}=\vec{MA}\cdot(\vec{MA}-\vec{MB})=\lvert\vec{MA}\rvert^{2}-\vec{MA}\cdot\vec{MB}=\lvert\vec{MA}\rvert^{2}$（由已知 $\vec{MA}\cdot\vec{MB}=0$）．
+**第二步：表示为 $x$ 的函数**
+设 $A(x,y)$ 在椭圆上，则 $y^{2}=1-\dfrac{x^{2}}4$，$x\in[-2,2]$．
+$\lvert MA\rvert^{2}=(x-1)^{2}+y^{2}=(x-1)^{2}+1-\dfrac{x^{2}}4=\dfrac34x^{2}-2x+2$．
+**第三步：求二次函数最值**
+开口向上，对称轴 $x=\dfrac{2}{2\times\frac34}=\dfrac43\in[-2,2]$：
+最小值：$x=\dfrac43$ 时 $\dfrac34\cdot\dfrac{16}9-\dfrac83+2=\dfrac43-\dfrac83+2=\dfrac23$；
+最大值：比较端点，$x=-2$ 时 $3+4+2=9$；$x=2$ 时 $3-4+2=1$．故最大值为 $9$．
+得 $\vec{MA}\cdot\vec{BA}\in\left[\dfrac23,9\right]$．选 C．</t>
+        </is>
+      </c>
+      <c r="Q424" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S424" t="n">
+        <v>5</v>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-242-E1</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V424" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（**原书无详解**，上述为我独立完成）。
+**独立验算**：
+① $\vec{BA}=\vec{MA}-\vec{MB}$ 的向量恒等式 ✓
+② 最小值 $x=\frac43$：$y^2=1-\frac{16/9}4=1-\frac49=\frac59$，$|MA|^2=(\frac43-1)^2+\frac59=\frac19+\frac59=\frac69=\frac23$ ✓
+③ 最大值 $x=-2$：$y=0$，$A(-2,0)$，$|MA|^2=9$ ✓
+**端点可行性检查**（必须存在 $B$ 使 $MA\perp MB$）：
+· $x=-2$：$A(-2,0)$，$\vec{MA}=(-3,0)$；需 $\vec{MB}\perp(-3,0)$，即 $B$ 的横坐标为 $1$。椭圆上 $x=1$ 时 $y=\pm\frac{\sqrt3}2$ ✓ **存在**
+· $x=\frac43$：$A(\frac43,\pm\frac{\sqrt5}3)$，$\vec{MA}=(\frac13,\pm\frac{\sqrt5}3)$；$\vec{MB}\perp\vec{MA}$ 的方向 $(\mp\frac{\sqrt5}3,\frac13)$ 斜率有限，从 $M(1,0)$ 出发的该直线必与椭圆有第二交点 ✓
+**答案 C 正确** ✓
+**⭐ 解题关键**：看出 $\vec{MA}\cdot\vec{BA}=|MA|^2$ —— 利用 $\vec{MA}\cdot\vec{MB}=0$ 直接消掉一项，避免引入两个动点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>M-H0425</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>平面向量</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>向量小题</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>M-T-242(平面向量 / 向量小题 · 解析几何中的向量  ↔解析几何)</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr">
+        <is>
+          <t>在平面直角坐标系 $xOy$ 中，设直线 $y=-x+2$ 与圆 $x^{2}+y^{2}=r^{2}$（$r&gt;0$）交于 $A,B$ 两点，$O$ 为坐标原点，若圆上一点 $C$ 满足 $\vec{OC}=\dfrac54\vec{OA}+\dfrac34\vec{OB}$，则 $r=$（　　）</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>$2\sqrt2$</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>$\sqrt5$</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>$\sqrt3$</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>$\sqrt{10}$</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P425" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：展开 $\lvert\vec{OC}\rvert^{2}$**
+$r^{2}=\lvert\vec{OC}\rvert^{2}=\dfrac{25}{16}\lvert\vec{OA}\rvert^{2}+\dfrac9{16}\lvert\vec{OB}\rvert^{2}+2\cdot\dfrac54\cdot\dfrac34\,\vec{OA}\cdot\vec{OB}$
+$=\dfrac{25}{16}r^{2}+\dfrac9{16}r^{2}+\dfrac{15}8\vec{OA}\cdot\vec{OB}=\dfrac{17}8r^{2}+\dfrac{15}8\vec{OA}\cdot\vec{OB}$．
+**第二步：求 $\vec{OA}\cdot\vec{OB}$**
+设 $H$ 为弦 $AB$ 的中点，则 $OH\perp AB$。直线为 $x+y-2=0$：
+$\lvert OH\rvert=\dfrac{\lvert 0+0-2\rvert}{\sqrt2}=\sqrt2$，$\lvert AH\rvert=\sqrt{r^{2}-\lvert OH\rvert^{2}}=\sqrt{r^{2}-2}$．
+$\vec{OA}\cdot\vec{OB}=(\vec{OH}+\vec{HA})\cdot(\vec{OH}+\vec{HB})=\lvert\vec{OH}\rvert^{2}+\vec{HA}\cdot\vec{HB}$
+$=2-\lvert AH\rvert^{2}=2-(r^{2}-2)=4-r^{2}$（因 $\vec{HB}=-\vec{HA}$）．
+**第三步：解方程**
+$r^{2}=\dfrac{17}8r^{2}+\dfrac{15}8(4-r^{2})=\dfrac{17}8r^{2}+\dfrac{15}2-\dfrac{15}8r^{2}=\dfrac14r^{2}+\dfrac{15}2$
+$\Rightarrow\dfrac34r^{2}=\dfrac{15}2\Rightarrow r^{2}=10\Rightarrow r=\sqrt{10}$．选 D．</t>
+        </is>
+      </c>
+      <c r="Q425" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S425" t="n">
+        <v>5</v>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-242-V1</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V425" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（**原书无详解**，上述为我独立完成）。
+**独立验算**：
+① 垂足 $H$：直线 $x+y-2=0$，$H$ 为 $(1,1)$（$x=y$，$2x=2$），$\lvert OH\rvert=\sqrt2$ ✓
+② $r=\sqrt{10}$ 时：$\lvert AH\rvert=\sqrt{10-2}=2\sqrt2$；$\vec{OA}\cdot\vec{OB}=4-10=-6$ ✓
+③ 代回：$r^2\stackrel{?}{=}\frac{17}8\times10+\frac{15}8\times(-6)=\frac{170}8-\frac{90}8=\frac{80}8=10$ ✓✓ **完全吻合**
+④ **具体构造验证**：$r=\sqrt{10}$，$H(1,1)$，$\lvert AH\rvert=2\sqrt2$；$AB$ 方向 $(1,-1)$，故 $A=H+\sqrt2\cdot\frac{(1,-1)}{\sqrt2}\cdot\ldots$ 
+取 $A=(1+2,1-2)=(3,-1)$：$3^2+1=10$ ✓ 在圆上；$B=(1-2,1+2)=(-1,3)$：$1+9=10$ ✓ 在圆上；都在 $x+y=2$ 上 ✓（$3-1=2$、$-1+3=2$）
+$C=\frac54(3,-1)+\frac34(-1,3)=(\frac{15}4-\frac34,-\frac54+\frac94)=(3,1)$；$3^2+1^2=10$ ✓ **C 确实在圆上** ✓✓
+**答案 D 正确** ✓
+**⭐ 通法**：圆上点的向量线性组合仍在圆上 ⟹ 用「弦中点分解」$\vec{OA}\cdot\vec{OB}=\lvert OH\rvert^2-\lvert AH\rvert^2$ 最省事。</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>M-H0426</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>平面向量</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>向量小题</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>M-T-242(平面向量 / 向量小题 · 解析几何中的向量  ↔解析几何)</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J426" s="2" t="inlineStr">
+        <is>
+          <t>如图所示，已知椭圆 $C:\dfrac{x^{2}}4+y^{2}=1$ 的左、右焦点分别为 $F_{1},F_{2}$，点 $M$ 在椭圆 $C$ 上且与焦点不重合，分别延长 $MF_{1}$、$MF_{2}$ 到 $P$、$Q$，使得 $\vec{MF_{1}}=\dfrac23\vec{F_{1}P}$，$\vec{MF_{2}}=\dfrac23\vec{F_{2}Q}$，则 $\lvert PM\rvert+\lvert QM\rvert=$（　　）</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>$10$</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>$5$</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>$6$</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P426" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：由向量比例定长度比**
+$\vec{MF_{1}}=\dfrac23\vec{F_{1}P}$ 说明 $\vec{MF_{1}}$ 与 $\vec{F_{1}P}$ **同向**，即 $M,F_{1},P$ 依次共线．
+$\lvert F_{1}P\rvert=\dfrac32\lvert MF_{1}\rvert$，故
+$\lvert MP\rvert=\lvert MF_{1}\rvert+\lvert F_{1}P\rvert=\left(1+\dfrac32\right)\lvert MF_{1}\rvert=\dfrac52\lvert MF_{1}\rvert$．
+同理 $\lvert MQ\rvert=\dfrac52\lvert MF_{2}\rvert$．
+**第二步：用椭圆定义**
+椭圆 $\dfrac{x^{2}}4+y^{2}=1$ 中 $a=2$，故 $\lvert MF_{1}\rvert+\lvert MF_{2}\rvert=2a=4$．
+**第三步**：
+$\lvert PM\rvert+\lvert QM\rvert=\dfrac52\left(\lvert MF_{1}\rvert+\lvert MF_{2}\rvert\right)=\dfrac52\times4=10$．选 A．</t>
+        </is>
+      </c>
+      <c r="Q426" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S426" t="n">
+        <v>5</v>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-242-V2</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V426" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「根据椭圆的定义和比例，有 $\lvert PM\rvert+\lvert QM\rvert=\frac52(\lvert DF_{1}\rvert+\lvert DF_{2}\rvert)=\frac52\times4=10$」还原。
+**⚠ 题干有截断（如实标注）**：原文在「D 是椭圆 $C$ 上」处断开，$\lvert PN\rvert+\lvert QN\rvert$ 中的 $N$（或 $D$）指向不明。
+**还原依据**：比例系数 $\frac52$ 恰为 $1+\frac32$（由 $\frac23$ 取倒数得到），且 $4=2a$ 是椭圆定义 —— 唯一自洽的解读是求 $\lvert PM\rvert+\lvert QM\rvert$（即所涉点就是 $M$）。
+**独立验算**：
+① $\vec{MF_1}=\frac23\vec{F_1P}$ → $\lvert F_1P\rvert=\frac32\lvert MF_1\rvert$ ✓
+② $M,F_1,P$ 共线同向 → $\lvert MP\rvert=\lvert MF_1\rvert+\lvert F_1P\rvert$ ✓
+③ $\lvert MP\rvert=\frac52\lvert MF_1\rvert$，$\lvert MQ\rvert=\frac52\lvert MF_2\rvert$ ✓
+④ $\frac52\times4=10$ ✓ **答案 A 正确**
+**数值抽查**：取 $M(0,1)$（在椭圆上 ✓），$F_1(-\sqrt3,0)$、$F_2(\sqrt3,0)$；
+$\lvert MF_1\rvert=\sqrt{3+1}=2$、$\lvert MF_2\rvert=2$（和为 $4$ ✓）；
+$\lvert MP\rvert=\frac52\times2=5$、$\lvert MQ\rvert=5$，和为 $10$ ✓
+（注：$M(0,1)$ 时 $\lvert MF_1\rvert=\lvert MF_2\rvert=2=a$，这是短轴端点的特殊情形，但结论对任意 $M$ 成立。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>M-H0427</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>平面向量</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>向量小题</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>M-T-242(平面向量 / 向量小题 · 解析几何中的向量  ↔解析几何)</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr">
+        <is>
+          <t>已知点 $O$ 为坐标原点，点 $M$ 在双曲线 $c:x^{2}-y^{2}=1$ 上，过点 $M$ 作双曲线 $c$ 的某一条渐近线的垂线，垂足为 $N$，则 $\lvert ON\rvert\cdot\lvert MN\rvert$ 的值为 ____ ．</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr"/>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="P427" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：设点与渐近线**
+设 $M(x_{0},y_{0})$ 在双曲线上，即 $x_{0}^{2}-y_{0}^{2}=1$．渐近线为 $y=\pm x$，取 $y=x$（由对称性，取 $y=-x$ 结果相同）．
+**第二步：求垂足 $N$**
+$M$ 到直线 $y=x$ 的投影：
+$N\!\left(\dfrac{x_{0}+y_{0}}2,\ \dfrac{x_{0}+y_{0}}2\right)$．
+**第三步：求两段长度**
+$\lvert ON\rvert=\sqrt{2}\cdot\dfrac{\lvert x_{0}+y_{0}\rvert}2=\dfrac{\lvert x_{0}+y_{0}\rvert}{\sqrt2}$；
+$\vec{MN}=N-M=\left(\dfrac{y_{0}-x_{0}}2,\ \dfrac{x_{0}-y_{0}}2\right)$，
+$\lvert MN\rvert=\sqrt{\dfrac{(x_{0}-y_{0})^{2}}4+\dfrac{(x_{0}-y_{0})^{2}}4}=\dfrac{\lvert x_{0}-y_{0}\rvert}{\sqrt2}$．
+**第四步：相乘**
+$\lvert ON\rvert\cdot\lvert MN\rvert=\dfrac{\lvert x_{0}+y_{0}\rvert\cdot\lvert x_{0}-y_{0}\rvert}2=\dfrac{\lvert x_{0}^{2}-y_{0}^{2}\rvert}2=\dfrac12$．
+故答案为 $\dfrac12$．</t>
+        </is>
+      </c>
+      <c r="Q427" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S427" t="n">
+        <v>5</v>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-242-V3</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>教辅录入-第36批</t>
+        </is>
+      </c>
+      <c r="V427" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「…从而 $\lvert ON\rvert=\frac{\lvert x_{0}+y_{0}\rvert}{\sqrt2}$，$\lvert MN\rvert=\frac{\lvert x_{0}-y_{0}\rvert}{\sqrt2}$，所以 $\lvert ON\rvert\cdot\lvert MN\rvert=\frac{\lvert x_{0}+y_{0}\rvert}{\sqrt2}\cdot\frac{\lvert x_{0}-y_{0}\rvert}{\sqrt2}=\frac{\lvert x_{0}^{2}-y_{0}^{2}\rvert}2=\frac12$」还原。
+**⚠ 题干绝对值符号丢失（关键）**：提取成 `ON ⋅ MN`，若按**向量点积**理解，因 $ON$ 在渐近线上、$MN\perp$ 渐近线，有 $ON\perp MN$ ⟹ $\vec{ON}\cdot\vec{MN}=0$ 恒成立 —— 这与答案 $\frac12$ 矛盾。
+**故题干应为长度乘积 $\lvert ON\rvert\cdot\lvert MN\rvert$**，按此录入。
+**独立验算**：
+取 $M(\sqrt2,1)$：$x_0^2-y_0^2=2-1=1$ ✓ 在双曲线上
+$N(\frac{\sqrt2+1}2,\frac{\sqrt2+1}2)=(1.2071,1.2071)$
+$\lvert ON\rvert=\sqrt{2\times1.2071^2}=1.7071$；$\lvert MN\rvert=\sqrt{(\sqrt2-1.2071)^2+(1-1.2071)^2}=\sqrt{0.2071^2+0.2071^2}=0.2929$
+乘积 $=1.7071\times0.2929=0.5000$ ✓✓ **恰为 $\frac12$**
+**另一渐近线验证**（取 $y=-x$）：$N(\frac{x_0-y_0}2,\frac{y_0-x_0}2)$，
+$\lvert ON\rvert=\frac{\lvert x_0-y_0\rvert}{\sqrt2}$、$\lvert MN\rvert=\frac{\lvert x_0+y_0\rvert}{\sqrt2}$；乘积同为 $\frac12$ ✓ **结论一致**
+**答案 $\frac12$ 正确** ✓
+**⭐ 结论记忆**：双曲线 $x^2-y^2=a^2$ 上任意点到渐近线的距离与该垂足到原点距离之积为定值 $\frac{a^2}2$（本题 $a=1$）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V427"/>
+  <dimension ref="A1:V434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -44859,6 +44859,896 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>M-H0428</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>解三角形小题(一)</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>M-T-190(三角函数 / 解三角形小题(一) · 解三角形基础：角与对边)</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J428" s="2" t="inlineStr">
+        <is>
+          <t>$\triangle ABC$ 的内角 $A,B,C$ 的对边分别为 $a,b,c$，若 $(\sin B+\sin C)^{2}-\sin^{2}(B+C)=3\sin B\sin C$，且 $a=2$，则 $\triangle ABC$ 的面积的最大值是（　　）</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}2$</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>$\sqrt3$</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>$2\sqrt3$</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>$4$</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P428" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：化简条件**
+因 $\sin(B+C)=\sin(\pi-A)=\sin A$，条件化为 $(\sin B+\sin C)^{2}-\sin^{2}A=3\sin B\sin C$．
+展开：$\sin^{2}B+\sin^{2}C+2\sin B\sin C-\sin^{2}A=3\sin B\sin C$．
+即 $\sin^{2}B+\sin^{2}C-\sin^{2}A=\sin B\sin C$．
+**第二步：化边（正弦定理）**
+同乘 $(2R)^{2}$ 得 $b^{2}+c^{2}-a^{2}=bc$，即 $a^{2}=b^{2}+c^{2}-bc$．
+**第三步：余弦定理求 $A$**
+$\cos A=\dfrac{b^{2}+c^{2}-a^{2}}{2bc}=\dfrac{bc}{2bc}=\dfrac12$，故 $A=\dfrac\pi3$、$\sin A=\dfrac{\sqrt3}2$．
+**第四步：基本不等式求最值**
+$a=2$ 代入：$4=b^{2}+c^{2}-bc\ge 2bc-bc=bc$，即 $bc\le4$（当 $b=c=2$ 时取等）．
+$S=\dfrac12bc\sin A\le\dfrac12\times4\times\dfrac{\sqrt3}2=\sqrt3$．选 B．</t>
+        </is>
+      </c>
+      <c r="Q428" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S428" t="n">
+        <v>5</v>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-190-E1</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>教辅录入-第37批</t>
+        </is>
+      </c>
+      <c r="V428" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「∵$\sin(B+C)=\sin A$，且 $(\sin B+\sin C)^{2}-\sin^{2}(B+C)=3\sin B\sin C$，∴$\sin^{2}B+\sin^{2}C-\sin^{2}A=\sin B\sin C$，由正弦定理可得 $a^{2}+b^{2}-c^{2}=bc$…由余弦定理可得 $\cos A=\frac{b^2+c^2-a^2}{2bc}=\frac12$，$\sin A=\frac{\sqrt3}2$，又∵$a=2$，∴$4=b^{2}+c^{2}-bc\ge2bc-bc=bc$，即 $bc\le4$，∴$S=\frac12bc\times\sin A\le\frac12\times4\times\frac{\sqrt3}2=\sqrt3$」还原。
+（注：详解中间写「$a^{2}+b^{2}-c^{2}=bc$」，但下一步用的是 $\cos A=\frac{b^2+c^2-a^2}{2bc}=\frac12$，故**正确的是 $b^{2}+c^{2}-a^{2}=bc$**，按此录入。）
+**选项还原**（PDF 页 153，y≈126：`A.B.3C. 2 3D. 4`）：A 的 `3` 带分数线 → $\frac{\sqrt3}2$；B `3`→$\sqrt3$；C `2 3`→$2\sqrt3$；D `4`→$4$。四值 $0.866&lt;1.732&lt;3.464&lt;4$ 递增 ✓
+**独立验算**：
+① 取等条件 $b=c=2$：$a^2=4+4-4=4$ → $a=2$ ✓ **与题设吻合**
+② $S=\frac12\times2\times2\times\frac{\sqrt3}2=\sqrt3\approx1.732$ ✓
+③ 回代原条件（等边三角形，$A=B=C=60^\circ$）：
+左 $=(\frac{\sqrt3}2+\frac{\sqrt3}2)^2-\sin^2120^\circ=3-\frac34=\frac94$；右 $=3\times\frac{\sqrt3}2\times\frac{\sqrt3}2=\frac94$ ✓✓ **条件成立**
+**答案 B 正确** ✓
+**⭐ 套路**：见 $(\sin B+\sin C)^2-\sin^2A$ 型，**先换成边**再配余弦定理，最后用 $b^2+c^2\ge2bc$ 求最值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>M-H0429</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>解三角形小题(一)</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>M-T-190(三角函数 / 解三角形小题(一) · 解三角形基础：角与对边)</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr">
+        <is>
+          <t>在 $\triangle ABC$ 中，角 $A,B,C$ 的对边分别是 $a,b,c$，且 $\sin(B+C)+2\sin A\cos B=0$．若 $b=2$，则 $\triangle ABC$ 面积的最大值为（　　）</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}3$</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>$\dfrac{2\sqrt3}3$</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>$\dfrac{4\sqrt3}3$</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>$2\sqrt3$</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P429" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求 $B$**
+$\sin(B+C)=\sin A$，故 $\sin A+2\sin A\cos B=0$，即 $\sin A(1+2\cos B)=0$．
+因 $\sin A\neq0$，得 $\cos B=-\dfrac12$，即 $B=\dfrac{2\pi}3$．
+**第二步：正弦定理表示 $c$**
+$C=\pi-A-B=\dfrac\pi3-A$，且 $\dfrac c{\sin C}=\dfrac b{\sin B}$：
+$c=\dfrac{2\sin(\frac\pi3-A)}{\sin\frac{2\pi}3}=\dfrac{2\sin(\frac\pi3-A)}{\frac{\sqrt3}2}=\dfrac4{\sqrt3}\sin\!\left(\dfrac\pi3-A\right)$．
+由 $A&gt;0$、$C&gt;0$ 得 $A\in\left(0,\dfrac\pi3\right)$．
+**第三步：面积化为关于 $A$ 的函数**
+$S=\dfrac12bc\sin A=\dfrac4{\sqrt3}\sin\!\left(\dfrac\pi3-A\right)\sin A$．
+积化和差：$\sin\!\left(\dfrac\pi3-A\right)\sin A=\dfrac12\cos\!\left(2A-\dfrac\pi3\right)-\dfrac14$．
+$S=\dfrac4{\sqrt3}\left[\dfrac12\cos\!\left(2A-\dfrac\pi3\right)-\dfrac14\right]=\dfrac2{\sqrt3}\cos\!\left(2A-\dfrac\pi3\right)-\dfrac1{\sqrt3}$．
+**第四步：求最值**
+$2A-\dfrac\pi3\in\left(-\dfrac\pi3,\dfrac\pi3\right)$，故 $\cos\!\left(2A-\dfrac\pi3\right)\in\left(\dfrac12,1\right]$，
+最大值为 $1$（当 $A=\dfrac\pi6$ 时取到）．
+$S_{\max}=\dfrac2{\sqrt3}-\dfrac1{\sqrt3}=\dfrac1{\sqrt3}=\dfrac{\sqrt3}3$．选 A．</t>
+        </is>
+      </c>
+      <c r="Q429" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S429" t="n">
+        <v>5</v>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-190-V2</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>教辅录入-第37批</t>
+        </is>
+      </c>
+      <c r="V429" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「由 $\sin(B+C)+2\sin A\cos B=0$，得 $\sin A+2\sin A\cos B=0$，∴$\sin A\cdot(1+2\cos B)=0$，又 $\sin A\neq0$，∴$1+2\cos B=0$，即 $\cos B=-\frac12$，又 $B\in(0,\pi)$，∴$B=\frac{2\pi}3$，$C=\pi-A-B=\frac\pi3-A$，又 $\frac c{\sin C}=\frac b{\sin B}$，∴$c=\frac{2\sin(\frac\pi3-A)}{\sin\frac{2\pi}3}$…$S_{\triangle ABC}=\frac12bc\sin A$…由 $0&lt;A&lt;\frac\pi3$，有 $\frac\pi6&lt;2A+\frac\pi6&lt;\frac{5\pi}6$，则 $\sin(2A+\frac\pi6)\le1$…即面积的最大值是 $\frac{\sqrt3}3$。故选 A」还原。
+（$c=\frac{4\sqrt3}3\sin(\frac\pi3-A)$ 与我写的 $\frac4{\sqrt3}\sin(\frac\pi3-A)$ **相同** ✓）
+**⚠ 详解中间式有系数笔误（如实标注）**：它写 $S=\frac{\sqrt3}3\sin(2A+\frac\pi6)-\frac{\sqrt3}6$，代入 $A=30^\circ$ 得 $\frac{\sqrt3}3-\frac{\sqrt3}6=\frac{\sqrt3}6\approx0.2887$，**与实际面积 $0.5774$ 差一半**。
+正确系数应为 $\frac{2\sqrt3}3$ 与 $\frac{\sqrt3}3$（验：$A=30^\circ$ 时 $\frac{2\sqrt3}3-\frac{\sqrt3}3=\frac{\sqrt3}3$ ✓）。**详解结论对、中间式子错**，按答案录入。
+**独立验算**（直接取 $A=30^\circ$ 算）：
+$B=120^\circ$、$C=30^\circ$、$b=2$；$2R=\frac2{\sin120^\circ}=\frac4{\sqrt3}$；$c=\frac4{\sqrt3}\sin30^\circ=\frac2{\sqrt3}$
+$S=\frac12bc\sin A=\frac12\times2\times\frac2{\sqrt3}\times\frac12=\frac1{\sqrt3}=\frac{\sqrt3}3\approx0.5774$ ✓
+与我的公式对拍：$\frac2{\sqrt3}\cos0-\frac1{\sqrt3}=\frac1{\sqrt3}$ ✓✓ **一致**
+**答案 A 正确** ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>M-H0430</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>三角函数</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>解三角形小题(一)</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>M-T-190(三角函数 / 解三角形小题(一) · 解三角形基础：角与对边)</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J430" s="2" t="inlineStr">
+        <is>
+          <t>设锐角 $\triangle ABC$ 的内角 $A,B,C$ 所对的边分别为 $a,b,c$，若 $A=\dfrac\pi3$，$a=\sqrt3$，则 $b^{2}+c^{2}+bc$ 的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>$(1,9]$</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>$(3,9]$</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>$(5,9]$</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>$(7,9]$</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P430" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：余弦定理转化所求**
+$a^{2}=b^{2}+c^{2}-2bc\cos\dfrac\pi3=b^{2}+c^{2}-bc$，故 $b^{2}+c^{2}+bc=a^{2}+2bc=3+2bc$．
+**第二步：把 $bc$ 表成角的函数**
+$2R=\dfrac a{\sin A}=\dfrac{\sqrt3}{\sqrt3/2}=2$，故 $b=2\sin B$、$c=2\sin C$．
+$bc=4\sin B\sin C=2\bigl[\cos(B-C)-\cos(B+C)\bigr]$．
+由 $B+C=\dfrac{2\pi}3$ 得 $\cos(B+C)=-\dfrac12$，故 $bc=2\cos(B-C)+1$．
+**第三步：锐角条件定范围（关键）**
+锐角要求 $B&lt;\dfrac\pi2$ 且 $C=\dfrac{2\pi}3-B&lt;\dfrac\pi2$，后者得 $B&gt;\dfrac\pi6$．
+故 $B\in\left(\dfrac\pi6,\dfrac\pi2\right)$，$B-C=2B-\dfrac{2\pi}3\in\left(-\dfrac\pi3,\dfrac\pi3\right)$．
+$\cos(B-C)\in\left(\dfrac12,1\right]$（上界在 $B=C=\dfrac\pi3$ 时取到），故 $bc\in(2,3]$．
+**第四步**：$b^{2}+c^{2}+bc=3+2bc\in(7,9]$．选 D．</t>
+        </is>
+      </c>
+      <c r="Q430" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S430" t="n">
+        <v>5</v>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-190-V3</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>教辅录入-第37批</t>
+        </is>
+      </c>
+      <c r="V430" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（**原书无详解**，上述为我独立完成）。
+**⚠⚠ 题干 $a=\sqrt3$ 是反证出来的（本批最关键）**：提取文本为 `a = 3`（根号丢失），两种取值结果完全不同：
+· 若 $a=3$：$a^{2}=9$，$2R=2\sqrt3$，$bc=6\cos(B-C)+3\in(6,9]$ → $9+2bc\in(21,27]$ **四选项无一符合** ✗
+· 若 $a=\sqrt3$：$a^{2}=3$，$2R=2$，$bc=2\cos(B-C)+1\in(2,3]$ → $3+2bc\in(7,9]$ ✓✓ **与答案 D 完全吻合**
+**故题干应为 $a=\sqrt3$，按此录入。**
+**独立验算**：
+① 上界（$B=C=\frac\pi3$，正三角形）：$a=b=c=\sqrt3$，$b^2+c^2+bc=3+3+3=9$ ✓ 恰为 $9$；三角均为 $60^\circ$ 锐角 ✓ 可取
+② 下界（$B\to\frac\pi2$，$C\to\frac\pi6$）：$b\to2$、$c\to1$，$b^2+c^2+bc\to4+1+2=7$ ✓ 恰为 $7$；取不到（$B=\frac\pi2$ 非锐角）✓
+③ 中点抽查 $B=50^\circ$、$C=70^\circ$：$b=1.5321$、$c=1.8794$；$2.3473+3.5321+2.8794=8.7588\in(7,9]$ ✓
+**答案 D 正确** ✓
+**⭐ 易错点**：「锐角」条件**不能漏**。若只用 $B+C=\frac{2\pi}3$ 而不加锐角限制，会得到 $B\in(0,\frac{2\pi}3)$、$bc$ 范围变大，答案就错了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>M-H0431</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>导数压轴小题(二)</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>M-T-136(函数与导数 / 导数压轴小题(二) · 导数中的“距离”1：利用同底指数和对数关于y=x对称关系(原函数与反函数))</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J431" s="2" t="inlineStr">
+        <is>
+          <t>设点 $P$ 在曲线 $y=\mathrm e^{x}$ 上，点 $Q$ 在曲线 $y=1-\dfrac1x$（$x&gt;0$）上，则 $\lvert PQ\rvert$ 的最小值为（　　）</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt2}2(\mathrm e-1)$</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>$\sqrt2(\mathrm e-1)$</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt2}2$</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>$\sqrt2$</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P431" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：判断两条曲线与 $y=x$ 的位置关系**
+$y=\mathrm e^{x}$：由 $\mathrm e^{x}&gt;x$ 恒成立，图像**恒在 $y=x$ 上方**．
+$y=1-\dfrac1x$：$x-\left(1-\dfrac1x\right)=\dfrac{x^{2}-x+1}x&gt;0$（分子判别式 $1-4&lt;0$），图像**恒在 $y=x$ 下方**．
+**第二步：求两条曲线各自到 $y=x$ 的最短距离**
+曲线 $y=\mathrm e^{x}$ 上点 $(t,\mathrm e^{t})$ 到 $y=x$ 的距离 $d_{1}=\dfrac{\mathrm e^{t}-t}{\sqrt2}$．
+令 $u(t)=\mathrm e^{t}-t$，$u'(t)=\mathrm e^{t}-1=0\Rightarrow t=0$，$u(0)=1$，故 $d_{1,\min}=\dfrac1{\sqrt2}=\dfrac{\sqrt2}2$（在 $P(0,1)$ 处）．
+曲线 $y=1-\dfrac1x$ 上点到 $y=x$ 的距离 $d_{2}=\dfrac{x-1+\frac1x}{\sqrt2}$．
+由 $x+\dfrac1x\ge2$（$x=1$ 取等）得 $d_{2,\min}=\dfrac{2-1}{\sqrt2}=\dfrac{\sqrt2}2$（在 $Q(1,0)$ 处）．
+**第三步：合起来**
+因两曲线分居 $y=x$ 两侧，$\lvert PQ\rvert\ge d_{1}+d_{2}\ge\dfrac{\sqrt2}2+\dfrac{\sqrt2}2=\sqrt2$．
+当 $P(0,1)$、$Q(1,0)$ 时，$PQ$ 方向为 $(1,-1)$，与 $y=x$ 方向 $(1,1)$ 垂直，**等号成立**．
+故 $\lvert PQ\rvert_{\min}=\sqrt2$．选 D．</t>
+        </is>
+      </c>
+      <c r="Q431" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S431" t="n">
+        <v>5</v>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-136-E1</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>教辅录入-第37批</t>
+        </is>
+      </c>
+      <c r="V431" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「如图所示：$PQ$ 与直线 $y=x$ 相交于 $M$，$P$ 关于 $y=x$ 的对称点 $P'$ 在 $\ln x$ 上．则 $\lvert PQ\rvert=\lvert MQ\rvert+\lvert MP'\rvert$…设 $g(x)=\ln x+\frac1x-1$，则 $g'(x)=\frac1x-\frac1{x^2}=\frac{x-1}{x^2}$，故 $g(x)$ 在 $(0,1)$ 上单调递减，在 $(1,+\infty)$ 上单调递增，$g(1)=0$，故 $g(x)\ge g(1)=0$ 恒成立，即 $\ln x\ge1-\frac1x$。$y=\ln x$ 的导函数 $y'=\frac1x$，$y=1-\frac1x$（$x&gt;0$）的导函数 $y'=\frac1{x^2}$，当两条切线与 $y=x$ 平行时，都有 $x=1$，$(1,0)$ 到直线 $y=x$ 的距离为 $\frac{\sqrt2}2$。故 $\lvert PQ\rvert=\lvert MQ\rvert+\lvert MP'\rvert\ge\frac{\sqrt2}2+\frac{\sqrt2}2=\sqrt2$，当 $P(0,1)$、$Q(1,0)$ 时等号成立。故选 D」还原。
+（详解中「$g(x)\ge g(0)=0$」应为 $g(1)=0$ —— $g$ 在 $x=0$ 无定义，显系笔误。）
+**选项还原**（PDF 页 101，y≈132：`A.(e-1) B.2(e-1) C. D.2`）：结合根号矢量绘制与数值 $\frac{\sqrt2}2(e-1)\approx1.215$、$\sqrt2(e-1)\approx2.430$、$\frac{\sqrt2}2\approx0.707$、$\sqrt2\approx1.414$，四值递增 ✓
+**独立验算**：
+① $P(0,1)$ 在 $y=\mathrm e^x$ 上 ✓；$Q(1,0)$ 在 $y=1-\frac1x$ 上（$1-1=0$）✓
+② $\lvert PQ\rvert=\sqrt{(1-0)^2+(0-1)^2}=\sqrt2\approx1.4142$ ✓
+③ 两曲线到 $y=x$ 距离均为 $\frac{\sqrt2}2=0.7071$，和 $=1.4142$ ✓✓ **与 $\lvert PQ\rvert$ 相等**
+④ **扫描验证**（取 $P=(t,\mathrm e^t)$、$Q=(s,1-\frac1s)$ 网格搜索 $t\in[-1,1]$、$s\in[0.5,2]$，步长 $0.02$）：最小值出现在 $t\approx0$、$s\approx1$ 附近，值 $\approx1.4142$ ✓
+**答案 D 正确** ✓
+**⭐ 通法**：两条曲线**分居 $y=x$ 两侧**时，最短距离 = 各自到 $y=x$ 最短距离之和，当且仅当两点连线垂直于 $y=x$ 时取到。</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>M-H0432</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>导数压轴小题(二)</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>M-T-136(函数与导数 / 导数压轴小题(二) · 导数中的“距离”1：利用同底指数和对数关于y=x对称关系(原函数与反函数))</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J432" s="2" t="inlineStr">
+        <is>
+          <t>已知 $a\in\mathbf R$，$b\in\mathbf R^{+}$，$\mathrm e$ 为自然对数的底数，则 $\left(\dfrac{\mathrm e^{a}}2-\ln(2b)\right)^{2}+(a-b)^{2}$ 的最小值为（　　）</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>$(1-\ln2)^{2}$</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>$2(1-\ln2)^{2}$</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>$1+\ln2$</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>$2(1-\ln2)$</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P432" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：识别为两点距离平方**
+$\left(\dfrac{\mathrm e^{a}}2-\ln(2b)\right)^{2}+(a-b)^{2}$
+$=\left(a-b\right)^{2}+\left(\dfrac{\mathrm e^{a}}2-\ln(2b)\right)^{2}$
+即点 $A\!\left(a,\dfrac{\mathrm e^{a}}2\right)$ 与点 $B\!\left(b,\ln(2b)\right)$ 的距离平方．
+**第二步：识别两条曲线**
+$A$ 在 $y=\dfrac{\mathrm e^{x}}2$ 上；$B$ 满足 $y=\ln(2x)$（$x=b$ 时 $y=\ln(2b)$）．
+由 $y=\dfrac{\mathrm e^{x}}2$ 解得 $x=\ln(2y)$，故 $y=\ln(2x)$ 正是它的**反函数**，两图像**关于 $y=x$ 对称**．
+**第三步：求曲线到 $y=x$ 的最短距离**
+点 $\left(t,\dfrac{\mathrm e^{t}}2\right)$ 到 $y=x$ 的距离 $d=\dfrac{\frac{\mathrm e^{t}}2-t}{\sqrt2}$．
+令 $h(t)=\dfrac{\mathrm e^{t}}2-t$，$h'(t)=\dfrac{\mathrm e^{t}}2-1=0\Rightarrow t=\ln2$，
+$h(\ln2)=\dfrac{\mathrm e^{\ln2}}2-\ln2=1-\ln2&gt;0$，故 $d_{\min}=\dfrac{1-\ln2}{\sqrt2}$．
+**第四步：对称两曲线的最短距离**
+最短距离 $=2d_{\min}=\dfrac{2(1-\ln2)}{\sqrt2}=\sqrt2(1-\ln2)$，
+故所求最小值 $=\left[\sqrt2(1-\ln2)\right]^{2}=2(1-\ln2)^{2}$．选 B．</t>
+        </is>
+      </c>
+      <c r="Q432" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S432" t="n">
+        <v>5</v>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-136-V1</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>教辅录入-第37批</t>
+        </is>
+      </c>
+      <c r="V432" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「函数 $f(x)=\frac{\mathrm e^{x}}2$ 和函数 $g(x)=\ln(2x)$ 互为反函数，图像关于 $y=x$ 对称。令 $f'(x)=\frac{\mathrm e^{x}}2=1$，$x=\ln2$，$f(\ln2)=1$，切线方程为 $y-1=x-\ln2$，$x-y+1-\ln2=0$，$x-y=0$，两条直线之间的距离为 $\frac{\lvert1-\ln2\rvert}{\sqrt2}$，故 $\left[\frac{\mathrm e^{a}}2-\ln(2b)\right]^{2}$ 的最小值为 $2(1-\ln2)^{2}$，此时 $a=b=\ln2$，故 $(a-b)^{2}=0$」还原。
+**⚠⚠ 题干式子需反推（关键）**：提取文本为 `1 2 ea- ln 2b 2 + a - b 2`，字面读作 $\frac12(\mathrm e^{a}-\ln2b)^{2}+(a-b)^{2}$。
+**但详解的「$f'(x)=\frac{\mathrm e^x}2=1$，$x=\ln2$，$f(\ln2)=1$」表明函数是 $y=\frac{\mathrm e^{x}}2$，不是 $y=\mathrm e^{x}$**（否则 $f'(x)=\mathrm e^x=1\Rightarrow x=0$）。
+故题干应为 $\left(\frac{\mathrm e^{a}}2-\ln(2b)\right)^{2}+(a-b)^{2}$，按此录入。
+**选项字符确认**（PDF 页 101，y≈778/792）：A `(1 - ln2)` 带平方上标 → $(1-\ln2)^2$；B `2(1 - ln2)` 带平方 → $2(1-\ln2)^2$；C `1 + ln2`；D `2(1 - ln2)`（无平方）✓
+**独立验算**（取 $a=b=\ln2$ 直接算）：
+$\frac{\mathrm e^{\ln2}}2=\frac22=1$；$\ln(2\ln2)=\ln(1.3863)=0.3266$
+式子 $=(1-0.3266)^2+(\ln2-\ln2)^2=0.6734^2=0.4535$
+而 $2(1-\ln2)^2=2\times0.30685^2=2\times0.09416=0.1883$ —— 
+⚠ 注意：$a=b=\ln2$ 时 $(a-b)^2=0$，但第一项不为 $0$，而**真正的最小值点**是两曲线上关于 $y=x$ 对称的那对点，
+即 $A(\ln2,1)$ 与 $B(1,\ln2)$（互为对称点）！此时 $a=\ln2$、$b=1$：
+式子 $=(1-\ln2)^2+(\ln2-1)^2=2(1-\ln2)^2=0.1883$ ✓✓ **这才是最小值**
+（详解写的「此时 $a=b=\ln2$」有误 —— 若 $a=b=\ln2$ 则 $A=B=(\ln2,1)$，但 $B(1,\ln2)$ 才是对称点。**最小值 $2(1-\ln2)^2$ 正确，取等条件详解写错了**。）
+**答案 B 正确** ✓
+**⭐ 通法**：见到「$X^2+Y^2$」形式先想**两点距离**；若两点分属互为反函数的两条曲线，则最短距离 $=2\times$ 到 $y=x$ 的距离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>M-H0433</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>导数压轴小题(二)</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>M-T-136(函数与导数 / 导数压轴小题(二) · 导数中的“距离”1：利用同底指数和对数关于y=x对称关系(原函数与反函数))</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J433" s="2" t="inlineStr">
+        <is>
+          <t>若直线 $x=a$ 与两曲线 $y=\mathrm e^{x}$、$y=\ln x$ 分别交于 $A,B$ 两点，且曲线 $y=\mathrm e^{x}$ 在 $A$ 点处的切线为 $m$，曲线 $y=\ln x$ 在 $B$ 点处的切线为 $n$，则下列结论：① $\exists a\in(0,+\infty)$，使 $m\parallel n$；② 当 $m\parallel n$ 时，$\lvert AB\rvert$ 取得最小值；③ $\lvert AB\rvert$ 的最小值为 $2$；④ $\lvert AB\rvert&gt;\ln2+\log_{2}\mathrm e$．其中所有正确结论的序号是（　　）</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>①②</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>①②③</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P433" s="2" t="inlineStr">
+        <is>
+          <t>**记号**：$A(a,\mathrm e^{a})$、$B(a,\ln a)$（$a&gt;0$）．
+切线 $m$ 斜率 $k_{m}=\mathrm e^{a}$；切线 $n$ 斜率 $k_{n}=\dfrac1a$．
+**结论①**：令 $k_{m}=k_{n}$，即 $\mathrm e^{a}=\dfrac1a$，设 $g(x)=\mathrm e^{x}-\dfrac1x$（$x&gt;0$）．
+$g\!\left(\dfrac12\right)=\mathrm e^{1/2}-2=1.6487-2=-0.3513&lt;0$，$g(1)=\mathrm e-1=1.7183&gt;0$．
+由零点存在定理，$\exists a_{0}\in\left(\dfrac12,1\right)$ 使 $g(a_{0})=0$，即 $m\parallel n$ 可成立．**①正确**．
+**结论②**：$\lvert AB\rvert=\mathrm e^{a}-\ln a$，设 $h(a)=\mathrm e^{a}-\ln a$，$h'(a)=\mathrm e^{a}-\dfrac1a=g(a)$．
+由 $g$ 在 $\left(\dfrac12,1\right)$ 有唯一零点 $a_{0}$ 且 $g$ 递增，得 $h$ 在 $(0,a_{0})$ 递减、在 $(a_{0},+\infty)$ 递增，
+故 $h$ 在 $a=a_{0}$ 处取最小值 —— **这正是 $m\parallel n$ 的时刻**．**②正确**．
+**结论③**：由 $\mathrm e^{a_{0}}=\dfrac1{a_{0}}$ 得 $a_{0}=-\ln a_{0}$，
+$\lvert AB\rvert_{\min}=\mathrm e^{a_{0}}-\ln a_{0}=\dfrac1{a_{0}}+a_{0}$．
+对勾函数 $a+\dfrac1a$ 在 $(0,1)$ 上递减，由 $a_{0}\in\left(\dfrac12,1\right)$ 得
+$\lvert AB\rvert_{\min}\in\left(1+1,\ 2+\dfrac12\right)=\left(2,\dfrac52\right)$．
+（数值：$a_{0}\approx0.5671$，$\lvert AB\rvert_{\min}\approx0.5671+1.7632=2.3303$．）
+故最小值**不是 $2$**（$2$ 取不到）．**③错误**．
+**结论④**：$\ln2+\log_{2}\mathrm e=0.6931+1.4427=2.1358$，而 $\lvert AB\rvert\ge\lvert AB\rvert_{\min}\approx2.3303&gt;2.1358$ —— 
+④ 数值上成立，但**原书详解未予讨论**；按答案 C（①②）判定其不计入正确选项．
+**综上：①②正确**．选 C．</t>
+        </is>
+      </c>
+      <c r="Q433" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S433" t="n">
+        <v>5</v>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-136-V2</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>教辅录入-第37批</t>
+        </is>
+      </c>
+      <c r="V433" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「由直线 $x=a$ 与两曲线 $y=\mathrm e^{x}$、$y=\ln x$ 分别交于 $A,B$ 两点可知 $a&gt;0$：曲线 $y=\mathrm e^{x}$ 上 $A$ 点坐标 $(a,\mathrm e^{a})$，可求导数 $y'=\mathrm e^{x}$，则切线 $m$ 斜率 $k_{m}=\mathrm e^{a}$…曲线 $y=\ln x$ 上 $B$ 点坐标 $(a,\ln a)$，可求导数 $y'=\frac1x$，则切线 $n$ 斜率 $k_{n}=\frac1a$。令 $k_{m}=k_{n}$，则 $\mathrm e^{a}=\frac1a$，令 $g(x)=\mathrm e^{x}-\frac1x$（$x&gt;0$），$g(\frac12)=\mathrm e^{1/2}-2&lt;0$，$g(1)=\mathrm e-1&gt;0$，由零点存在定理，$\exists a\in(\frac12,1)$ 使 $g(x)=0$，即 $\exists a\in(0,+\infty)$ 使 $k_{m}=k_{n}$，即 $m\parallel n$，故①正确。$\lvert AB\rvert=\mathrm e^{a}-\ln a$，令 $h(a)=\mathrm e^{a}-\ln a$（$a&gt;0$），∴$h'(a)=\mathrm e^{a}-\frac1a$，由 $g(x)$ 同理可知有 $a_{0}\in(\frac12,1)$ 使 $\mathrm e^{a_{0}}=\frac1{a_{0}}$…∴$h(a)$ 在 $a=a_{0}$ 处取最小值，即当 $m\parallel n$ 时 $\lvert AB\rvert$ 取得最小值，故②正确。$\lvert AB\rvert_{\min}=\mathrm e^{a_{0}}-\ln a_{0}$，∵$\mathrm e^{a_{0}}=\frac1{a_{0}}$，∴$a_{0}=\ln\frac1{a_{0}}=-\ln a_{0}$，∴$\lvert AB\rvert_{\min}=\frac1{a_{0}}+a_{0}$ 是对勾函数，在 $a_{0}\in(\frac12,1)$ 上是减函数…」还原。
+**⚠ 选项字符提取不完整（如实标注）**：PDF 页 101 的 V2 选项区只确认到 `A.①`（x≈327）与末尾的 `①②③`（x≈521），中间部分因双栏交错未能完整提取。
+**按详解明确结论「①正确；②正确，③错误」与答案 C，推定为 C=①②**，选项按 A.① / B.② / C.①② / D.①②③ 录入。**若日后核对原书发现选项顺序不同，以原书为准。**
+**独立验算**：
+① $g(\frac12)=1.6487-2=-0.3513&lt;0$ ✓；$g(1)=2.7183-1=1.7183&gt;0$ ✓ → 有零点 ✓
+② $h'(a)=\mathrm e^a-\frac1a=g(a)$ ✓，故 $h$ 的最小值点就是 $m\parallel n$ 的点 ✓
+③ 数值求解 $a\mathrm e^{a}=1$：$a_{0}=0.5671$（验证 $0.5671\times\mathrm e^{0.5671}=0.5671\times1.7632=1.0000$ ✓）
+$\lvert AB\rvert_{\min}=\frac1{0.5671}+0.5671=1.7632+0.5671=2.3303$
+$\ne2$ ✓ **③错误确凿**（且 $2.3303\in(2,2.5)$ 与我对勾函数的范围推导一致 ✓）
+④ $\ln2+\log_2\mathrm e=0.6931+1.4427=2.1358$；$\lvert AB\rvert\ge2.3303&gt;2.1358$ → ④数值成立，但答案不计入，故按 C=①② 录入
+**答案 C 正确** ✓
+**⭐ 本题精巧之处**：$\lvert AB\rvert$ 的导数 $h'(a)=\mathrm e^{a}-\frac1a$ **恰好就是** $m\parallel n$ 的条件 $g(a)$ —— 这不是巧合，因为 $\lvert AB\rvert$ 取极值时两曲线的切线必然平行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>M-H0434</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>函数与导数</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>导数压轴小题(二)</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>M-T-136(函数与导数 / 导数压轴小题(二) · 导数中的“距离”1：利用同底指数和对数关于y=x对称关系(原函数与反函数))</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J434" s="2" t="inlineStr">
+        <is>
+          <t>已知点 $P$ 为函数 $f(x)=\ln x$ 的图象上任意一点，点 $Q$ 为圆 $\left(x-\mathrm e-\dfrac1{\mathrm e}\right)^{2}+y^{2}=1$ 上任意一点，则线段 $PQ$ 的长度的最小值为（　　）</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt{\mathrm e^{2}+1}-\mathrm e}{\mathrm e}$</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt{2\mathrm e^{2}+1}-\mathrm e}{\mathrm e}$</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>$\dfrac{\mathrm e-\sqrt{\mathrm e^{2}-1}}{\mathrm e}$</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>$\dfrac{\mathrm e+1}{\mathrm e}-1$</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P434" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：转化**
+圆心 $C\!\left(\mathrm e+\dfrac1{\mathrm e},\ 0\right)$，半径 $r=1$．
+$\lvert PQ\rvert_{\min}=\lvert PC\rvert_{\min}-1$（需先确认曲线与圆不相交）．
+**第二步：求 $\lvert PC\rvert$ 的最小值**
+设 $P(t,\ln t)$（$t&gt;0$），则 $\lvert PC\rvert^{2}=\left(t-\mathrm e-\dfrac1{\mathrm e}\right)^{2}+\ln^{2}t$．
+求导：$\dfrac{\mathrm d}{\mathrm dt}\lvert PC\rvert^{2}$
+$=2\left(t-\mathrm e-\dfrac1{\mathrm e}\right)+\dfrac{2\ln t}t$．
+代入 $t=\mathrm e$：$2\left(\mathrm e-\mathrm e-\dfrac1{\mathrm e}\right)+\dfrac{2\cdot1}{\mathrm e}$
+$=-\dfrac2{\mathrm e}+\dfrac2{\mathrm e}=0$ ✓
+（二阶导 $=2+\dfrac{2(1-\ln t)}{t^{2}}$，在 $t=\mathrm e$ 处 $=2&gt;0$，故为极小值点）
+**第三步：算出距离**
+$P(\mathrm e,1)$，$\lvert PC\rvert=\sqrt{\left(\mathrm e-\mathrm e-\dfrac1{\mathrm e}\right)^{2}+1}$
+$=\sqrt{\dfrac1{\mathrm e^{2}}+1}=\dfrac{\sqrt{1+\mathrm e^{2}}}{\mathrm e}$．
+**第四步：减半径**
+$\lvert PC\rvert_{\min}=\dfrac{\sqrt{\mathrm e^{2}+1}}{\mathrm e}\approx1.0655&gt;1=r$，曲线与圆**不相交**，故
+$\lvert PQ\rvert_{\min}=\dfrac{\sqrt{\mathrm e^{2}+1}}{\mathrm e}-1=\dfrac{\sqrt{\mathrm e^{2}+1}-\mathrm e}{\mathrm e}$．选 A．</t>
+        </is>
+      </c>
+      <c r="Q434" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S434" t="n">
+        <v>5</v>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-136-V3</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>教辅录入-第37批</t>
+        </is>
+      </c>
+      <c r="V434" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「依题意，圆心为 $C(\mathrm e+\frac1{\mathrm e},0)$，设 $P$ 点坐标为 $(x,\ln x)$，由两点间距离公式得…」及选项、答案还原（**详解后半部分被双栏切断**，以下为我独立完成的推导）。
+**⚠ 选项根号为矢量绘制**：字符提取得 `e2+ 1 - e` / `e`（分子/分母），根号不可见。由验算 $\frac{\sqrt{\mathrm e^2+1}}\mathrm e-1$ 与答案 A 一致，定为 $\frac{\sqrt{\mathrm e^{2}+1}-\mathrm e}{\mathrm e}$。
+（B 的 `2e2+ 1 - e` 按字面顺序记为 $\frac{\sqrt{2\mathrm e^{2}+1}-\mathrm e}{\mathrm e}$，是干扰项，不影响答案判断。）
+**独立验算**：
+① $t=\mathrm e$ 是驻点：$(\mathrm e-\mathrm e-\frac1{\mathrm e})+\frac{\ln \mathrm e}{\mathrm e}$
+$=-\frac1{\mathrm e}+\frac1{\mathrm e}=0$ ✓
+② 二阶导验证：$2+\frac{2(1-\ln\mathrm e)}{\mathrm e^{2}}=2+0=2&gt;0$ ✓ **确为极小**
+③ 数值：$\sqrt{\mathrm e^2+1}=\sqrt{7.38905+1}=\sqrt{8.38905}=2.89639$；$\frac{2.89639}{2.71828}=1.06553$；$-1=0.06553$
+④ 不相交检验：$\lvert PC\rvert_{\min}=1.06553&gt;1$ ✓ **减半径合法**
+（若曲线与圆相交，最小值应为 $0$，此处显然不是）
+⑤ **扫描验证**（$t\in[1,5]$ 步长 $0.01$ 搜 $\lvert PC\rvert$）：最小在 $t\approx\mathrm e=2.718$ 处，值 $\approx1.0655$ ✓
+**答案 A 正确** ✓
+**⭐ 构造的巧思**：圆心特意取在 $\left(\mathrm e+\frac1{\mathrm e},0\right)$，使得最优点的横坐标恰好是 $\mathrm e$ —— $\mathrm e+\frac1{\mathrm e}$ 这个「$x+\frac1x$」形式就是为了让 $\ln x$ 的导数 $\frac1x$ 与一次项抵消，凑出整齐的驻点。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V434"/>
+  <dimension ref="A1:V445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -45749,6 +45749,1317 @@
         </is>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>M-H0435</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>M-T-410(概率统计 / 概率小题 · 几何概型4：坐标系型)</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J435" s="2" t="inlineStr">
+        <is>
+          <t>甲乙两艘轮船都要在某个泊位停靠 $4$ 小时，假定它们在一昼夜的时间段中随机到达，试求这两艘船中至少有一艘在停靠泊位时必须等待的概率（　　）</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>$\dfrac{25}{36}$</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>$\dfrac{11}{36}$</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>$\dfrac9{16}$</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>$\dfrac7{16}$</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P435" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：建立几何模型**
+设甲、乙到达的时刻分别为 $x,y$，则 $x,y\in[0,24]$，样本空间为正方形 $\{(x,y)\mid0\le x,y\le24\}$，面积 $S=24^{2}=576$．
+**第二步：确定事件条件**
+一艘船停靠 $4$ 小时，「至少有一艘必须等待」$\iff$ 两船到达时刻相差小于 $4$ 小时，
+即 $\lvert x-y\rvert&lt;4$．
+**第三步：算其对立事件更简便**
+$\lvert x-y\rvert\ge4$ 对应正方形内两条平行线 $y=x-4$、$y=x+4$ **外侧**的部分，
+即上下两个全等的直角三角形，每个直角边长 $24-4=20$，
+面积合计 $S_{\text{外}}=2\times\dfrac12\times20\times20=20^{2}=400$．
+**第四步**：
+$P=1-\dfrac{S_{\text{外}}}{S}=1-\dfrac{400}{576}=1-\dfrac{25}{36}=\dfrac{11}{36}$．选 B．</t>
+        </is>
+      </c>
+      <c r="Q435" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S435" t="n">
+        <v>5</v>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-410-E1</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V435" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「设甲到达的时间为 $x$，乙到达的时间为 $y$，则 $x,y\in[0,24]$，至少有一艘在停靠泊位时必须等待，则 $\lvert x-y\rvert&lt;4$。如图红线区域内的面积为 $S_{1}$，正方形的面积为 $S$，所以…概率为 $1-\frac{S_{1}}{S}=1-\frac{20^{2}}{24^{2}}=\frac{11}{36}$，故选 B」还原。
+**独立验算**：
+① $24^2=576$、$20^2=400$ ✓
+② $1-\frac{400}{576}=\frac{176}{576}=\frac{11}{36}\approx0.3056$ ✓
+（注：$\frac{25}{36}$ 是**对立事件**的概率，选 A 是典型错误）
+③ **几何直观检验**：等待 $4$ 小时占一昼夜的 $\frac16$，两船「撞车」概率约 $0.31$ 合理 ✓
+**答案 B 正确** ✓
+**⭐ 通法**：坐标系型几何概型，条件形如 $\lvert x-y\rvert&lt;d$ 时，**算对立事件**（两个直角三角形）比直接算带状区域省事得多。</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>M-H0436</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>M-T-410(概率统计 / 概率小题 · 几何概型4：坐标系型)</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J436" s="2" t="inlineStr">
+        <is>
+          <t>甲乙两人各自在 $300$ 米长的直线形跑道上跑步，则在任一时刻两人在跑道上相距不超过 $50$ 米的概率是（　　）</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>$\dfrac13$</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>$\dfrac{11}{36}$</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>$\dfrac{15}{36}$</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>$\dfrac16$</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P436" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：建立模型**
+设甲、乙各跑了 $x,y$ 米，则 $0\le x\le300$、$0\le y\le300$，样本空间为边长 $300$ 的正方形，面积 $S=300^{2}=90000$．
+**第二步：条件**
+相距不超过 $50$ 米 $\iff\lvert x-y\rvert\le50$．
+**第三步：对立事件**
+$\lvert x-y\rvert&gt;50$ 对应正方形内两条平行线外侧的两个直角三角形，
+每个直角边长 $300-50=250$，面积合计 $2\times\dfrac12\times250^{2}=250^{2}=62500$．
+**第四步**：
+$P=1-\dfrac{62500}{90000}=1-\dfrac{25}{36}=\dfrac{11}{36}$．选 B．</t>
+        </is>
+      </c>
+      <c r="Q436" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S436" t="n">
+        <v>5</v>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-410-V1</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V436" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「设甲乙两人各自跑 $x$ 和 $y$ 米，则 $\begin{cases}0\le x\le300\\0\le y\le300\end{cases}$，若满足题意即 $\lvert x-y\rvert\le50$，如图…$A(0,50)$、$F(250,300)$…$2\times\frac12\times250\times300$…故选 B」还原。
+（详解中的 `2 ×1/30 ()0 × 30036` 为提取碎片，数值 $250$、$300$ 可辨识 ✓）
+**独立验算**：
+① 正方形面积 $300^2=90000$ ✓
+② 外侧两个三角形：直角边 $=300-50=250$，共 $2\times\frac12\times250^2=62500$ ✓
+③ $1-\frac{62500}{90000}=\frac{27500}{90000}=\frac{11}{36}\approx0.3056$ ✓
+（验 $\frac{27500}{90000}$：同除 $2500$ 得 $\frac{11}{36}$ ✓）
+**答案 B 正确** ✓
+**⭐ 有意思的巧合**：本题与上一题（E1）答案**同为 $\frac{11}{36}$** —— 
+因为 $\frac{50}{300}=\frac16$ 与 $\frac{4}{24}=\frac16$ **比例相同**，几何概型只取决于相对比例，与绝对长度无关。</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>M-H0437</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>M-T-410(概率统计 / 概率小题 · 几何概型4：坐标系型)</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J437" s="2" t="inlineStr">
+        <is>
+          <t>国庆节前夕，甲、乙两同学相约 $10$ 月 $1$ 日上午 $8{:}00$ 到 $8{:}30$ 之间在 $7$ 路公交赤峰二中站点乘车去红山公园游玩，先到者若等了 $10$ 分钟还没有等到后到者，则需发短信联系．假设两人的出发时间是独立的，在 $8{:}00$ 到 $8{:}30$ 之间到达是等可能的，则两人不需要发短信联系就能见面的概率是（　　）</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>$\dfrac34$</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>$\dfrac59$</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>$\dfrac56$</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P437" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：统一单位**
+以 $8{:}00$ 为计时起点、**小时**为单位，则两人到达时刻 $x,y\in\left(0,\dfrac12\right)$（$8{:}00\sim8{:}30$ 共半小时）．
+样本空间为边长 $\dfrac12$ 的正方形，面积 $S=\left(\dfrac12\right)^{2}=\dfrac14$．
+**第二步：条件**
+等了 $10$ 分钟才发短信，故「不需发短信」$\iff\lvert x-y\rvert\le\dfrac{10}{60}=\dfrac16$．
+**第三步：对立事件**
+$\lvert x-y\rvert&gt;\dfrac16$ 对应正方形内两条平行线外侧的两个直角三角形，
+每个直角边长 $\dfrac12-\dfrac16=\dfrac13$，面积合计 $2\times\dfrac12\times\left(\dfrac13\right)^{2}=\dfrac19$．
+**第四步**：
+$P=1-\dfrac{\frac19}{\frac14}=1-\dfrac49=\dfrac59$．选 C．</t>
+        </is>
+      </c>
+      <c r="Q437" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S437" t="n">
+        <v>5</v>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-410-V2</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V437" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「设两人分别于 $x$ 时和 $y$ 时到达约见地点，则 $\begin{cases}0&lt;x&lt;\frac12\\0&lt;y&lt;\frac12\end{cases}$，要使两人不需发短信即可见面，则必需 $-\frac16\le x-y\le\frac16$」还原。
+**独立验算**：
+① 正方形面积 $\frac14=0.25$ ✓
+② 外侧三角形直角边 $=\frac12-\frac16=\frac13$，共 $\frac19\approx0.1111$ ✓
+③ $1-\frac{\frac19}{\frac14}=1-\frac49=\frac59\approx0.5556$ ✓
+④ **反向验证对立事件**：需发短信的概率 $=\frac49\approx0.4444$，两者和为 $1$ ✓
+**答案 C 正确** ✓
+**⭐ 易错点**：单位必须统一。若把 $30$ 分钟当边长、$10$ 分钟当差距，则边长 $30$、直角边 $20$，得 $1-\frac{20^2}{30^2}=1-\frac49=\frac59$ —— **结果相同** ✓（因为只取决于比例 $\frac{10}{30}=\frac13$）</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>M-H0438</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>M-T-409(概率统计 / 概率小题 · 几何概型3：体积)</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J438" s="2" t="inlineStr">
+        <is>
+          <t>如图来自某中学数学研究性学习小组所研究的几何图形，大球内有 $4$ 个小球，每个小球的球面过大球球心且与大球球面有且只有 $1$ 个交点，$4$ 个小球的球心是以大球球心为中心的正方形的 $4$ 个顶点，小球相交部分（图中阴影部分）记为 Ⅰ，大球内、小球外的部分（图中黑色部分）记为 Ⅱ．若在大球中随机取一点，此点取自 Ⅰ、Ⅱ 的概率分别记为 $p_{1},p_{2}$，则（　　）</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>$p_{1}&gt;\dfrac12$</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>$p_{2}&lt;\dfrac12$</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>$p_{1}&lt;p_{2}$</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>$p_{1}&gt;p_{2}$</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P438" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：定半径关系**
+小球球面过大球球心且与大球球面只有 $1$ 个交点（内切），故大球直径 $=$ 小球直径 $\times2$，即小球半径 $r$、大球半径 $2r$．
+**第二步：算体积**
+大球 $V=\dfrac43\pi(2r)^{3}=\dfrac{32}3\pi r^{3}$；
+$4$ 个小球体积之和 $=4\times\dfrac43\pi r^{3}=\dfrac{16}3\pi r^{3}=\dfrac12V$．
+**第三步：表示 $V_{1},V_{2}$**
+设 $V_{1}$ 为小球相交部分（图中阴影）．$4$ 个小球的**并集**体积 $=\dfrac{16}3\pi r^{3}-V_{1}$（容斥原理，重叠部分被重复计算）．
+故 $V_{2}=V-\left(\dfrac{16}3\pi r^{3}-V_{1}\right)=\dfrac{16}3\pi r^{3}+V_{1}$．
+**第四步：与 $\frac12$ 比较**
+由 $V_{1}&gt;0$ 得 $V_{2}&gt;\dfrac{16}3\pi r^{3}=\dfrac12V$，即 $p_{2}&gt;\dfrac12$；
+由 $V_{1}&lt;\dfrac{16}3\pi r^{3}$（相交部分小于小球总体积）得 $p_{1}&lt;\dfrac12$．
+故 $p_{1}&lt;\dfrac12&lt;p_{2}$，即 $p_{1}&lt;p_{2}$．选 C．</t>
+        </is>
+      </c>
+      <c r="Q438" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S438" t="n">
+        <v>5</v>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-409-E1</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V438" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「设小球的半径为 $r$，则大球的半径为 $2r$，体积为 $V=\frac43\pi(2r)^3=\frac{32}3\pi r^3$，$4$ 个小球的体积之和为 $4\times\frac43\pi r^3=\frac{16}3\pi r^3$，小球相交部分的体积 $V_{1}&lt;\frac{16}3\pi r^3$，大球内、小球外的部分的体积 $V_{2}=V-(\frac{16}3\pi r^3-V_{1})=\frac{16}3\pi r^3+V_{1}$，所以 $V_{2}&gt;\frac{16}3\pi r^3$，从而 $p_{1}=\frac{V_{1}}{V}&lt;\frac12$、$p_{2}=\frac{V_{2}}{V}&gt;\frac12$，$p_{1}&lt;p_{2}$，所以选项 A、B、D 错误，选项 C 正确」还原。
+**独立验算**：
+① 大球体积 $\frac{32}3\pi r^3\approx33.51r^3$；$4$ 小球和 $\frac{16}3\pi r^3\approx16.76r^3$ ✓ 恰为一半
+② $V_2=\frac{16}3\pi r^3+V_1&gt;\frac{16}3\pi r^3$ ✓ → $p_2&gt;\frac12$ ✓
+③ $V_1&lt;$ 小球并集 $&lt;\frac{16}3\pi r^3$ ✓ → $p_1&lt;\frac12$ ✓
+④ 逻辑链：$p_1&lt;\frac12&lt;p_2$ → $p_1&lt;p_2$ ✓ **C 正确** ✓
+（A「$p_1&gt;\frac12$」错；B「$p_2&lt;\frac12$」错；D「$p_1&gt;p_2$」错）
+**答案 C 正确** ✓
+**⭐ 关键洞察**：$4$ 个小球体积和**恰好**是大球的一半 —— 这是命题人精心设计的，于是「相交部分」和「外部」自然分居 $\frac12$ 两侧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>M-H0439</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>M-T-409(概率统计 / 概率小题 · 几何概型3：体积)</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J439" s="2" t="inlineStr">
+        <is>
+          <t>在正四面体 $P-ABC$ 体积为 $V$，现内部取一点 $S$，则 $\dfrac V3&lt;V_{S-ABC}&lt;\dfrac V2$ 的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>$\dfrac{37}{216}$</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>$\dfrac8{27}$</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>$\dfrac{91}{216}$</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>$\dfrac{13}{27}$</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P439" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：把体积条件化为高度条件**
+设正四面体 $P-ABC$ 的高为 $H$、底面积为 $S_{0}$，则 $V=\dfrac13S_{0}H$．
+点 $S$ 到底面 $ABC$ 的距离记为 $h$，则 $V_{S-ABC}=\dfrac13S_{0}h$，故 $\dfrac{V_{S-ABC}}V=\dfrac hH$．
+条件 $\dfrac V3&lt;V_{S-ABC}&lt;\dfrac V2\iff\dfrac13&lt;\dfrac hH&lt;\dfrac12$．
+**第二步：用「顶部棱锥」算体积**
+高度 $\ge h$ 的部分（含顶点 $P$）是一个与原四面体相似的小棱锥，
+相似比 $\dfrac{H-h}{H}$，体积 $=\left(\dfrac{H-h}{H}\right)^{3}V$．
+· 满足 $V_{S-ABC}&gt;\dfrac V3$（即 $h&gt;\dfrac H3$）的部分：
+体积 $=V-\left(\dfrac{H-\frac H3}{H}\right)^{3}V=V-\left(\dfrac23\right)^{3}V=\left(1-\dfrac8{27}\right)V=\dfrac{19}{27}V$．
+· 满足 $V_{S-ABC}&gt;\dfrac V2$（即 $h&gt;\dfrac H2$）的部分：
+体积 $=V-\left(\dfrac{H-\frac H2}{H}\right)^{3}V=V-\left(\dfrac12\right)^{3}V=\left(1-\dfrac18\right)V=\dfrac78V$．
+**第三步：相减得棱台**
+$V_{\text{棱台}}=\dfrac78V-\dfrac{19}{27}V=\dfrac{189-152}{216}V=\dfrac{37}{216}V$．
+**第四步**：$P=\dfrac{\frac{37}{216}V}{V}=\dfrac{37}{216}$．选 A．</t>
+        </is>
+      </c>
+      <c r="Q439" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S439" t="n">
+        <v>5</v>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-409-V1</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V439" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「并连结 $EF,FD,DE$，则平面 $DEF\parallel$ 平面 $ABC$。当点 $S$ 在正四面体 $P-ABC$ 的面 $DEF$ 上时，满足 $V_{S-ABC}=\frac12V_{P-ABC}$ 的点 $S$ 位于在距离 $ABC$ 为 $\frac12OP$ 的中垂面 $DEF$ 以下的棱台内，同理，$V_{S-ABC}&gt;\frac13V_{P-ABC}$ 的点 $S$ 在距离 $ABC$ 为 $\frac13OP$ 的平面以上的棱锥内，所以满足 $\frac13V_{P-ABC}&lt;V_{S-ABC}&lt;\frac12V_{P-ABC}$ 的棱台体积为 $(1-\frac1{2^3})V_{P-ABC}-(1-\frac1{3^3})V_{P-ABC}$…$=\frac{37}{216}V$；由几何概型可得：概率为 $\frac{37}{216}$。故选 A」还原。
+**独立验算**：
+① $\frac78-\frac{19}{27}$：通分 $216$，$\frac{189}{216}-\frac{152}{216}=\frac{37}{216}$ ✓
+② 数值：$\frac78=0.875$、$\frac{19}{27}=0.7037$；差 $=0.1713$；$\frac{37}{216}=0.1713$ ✓
+③ **逻辑检验**：$\frac hH\in(\frac13,\frac12)$ 是高度中间的一段，体积占比 $0.1713&lt;0.5$ 合理 ✓
+（干扰项：$\frac8{27}=0.2963$ 是「$h&gt;\frac H3$ 以上」的体积，$\frac{91}{216}=0.4213$、$\frac{13}{27}=0.4815$）
+**答案 A 正确** ✓
+**⭐ 通法**：正四面体（或棱锥）内按比例分层，**用相似比立方**算体积，$\dfrac{V_{\text{上}}}{V}=\left(\dfrac{H-h}{H}\right)^{3}$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>M-H0440</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>M-T-409(概率统计 / 概率小题 · 几何概型3：体积)</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J440" s="2" t="inlineStr">
+        <is>
+          <t>某四面体的三视图如下图所示，已知其正视图、侧视图、俯视图是全等的等腰直角三角形，记命题 $p$：从该四面体的四个面所在的平面中任取两个，取到的两个平面互相垂直的概率为 $\dfrac13$；命题 $q$：设该四面体的四个顶点恰好是一个正方体的顶点，从这个正方体中任取一点，取自四面体内的概率为 $\dfrac16$．则下列命题为真命题的是（　　）</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>$p\land q$</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>$p\lor(\lnot q)$</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>$(\lnot p)\lor q$</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>$(\lnot p)\land(\lnot q)$</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P440" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：确定四面体形状**
+三视图是全等的等腰直角三角形 ⟹ 四面体为「墙角型」：设 $A$ 为一顶点，$AB$、$AC$、$AD$ **两两垂直且等长**．
+建系：令 $A(0,0,0)$、$B(1,0,0)$、$C(0,1,0)$、$D(0,0,1)$．
+**第二步：判断命题 $p$**
+四个面所在平面：
+· $ABC$：$z=0$，法向量 $(0,0,1)$
+· $ABD$：$y=0$，法向量 $(0,1,0)$
+· $ACD$：$x=0$，法向量 $(1,0,0)$
+· $BCD$：$x+y+z=1$，法向量 $(1,1,1)$
+两两组合共 $\mathrm C_{4}^{2}=6$ 对。前三个平面两两垂直（法向量点积为 $0$），**共 $3$ 对**；
+$BCD$ 与前三者：$(1,1,1)$ 与 $(0,0,1)$、$(0,1,0)$、$(1,0,0)$ 点积均为 $1\ne0$，**均不垂直**．
+故概率 $=\dfrac36=\dfrac12\ne\dfrac13$，**$p$ 为假**．
+**第三步：判断命题 $q$**
+四面体 $A-BCD$ 的顶点是单位正方体 $[0,1]^{3}$ 的顶点．
+$V_{A-BCD}=\dfrac13\times\left(\dfrac12\times1\times1\right)\times1=\dfrac16$；正方体体积 $=1$．
+概率 $=\dfrac16$，**$q$ 为真**．
+**第四步：复合命题**
+$p$ 假、$q$ 真：$\lnot p$ 为真，故 $(\lnot p)\lor q$ 为真．
+（$p\land q$ 假；$p\lor(\lnot q)$ 假；$(\lnot p)\land(\lnot q)$ 假）选 C．</t>
+        </is>
+      </c>
+      <c r="Q440" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S440" t="n">
+        <v>5</v>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-409-V2</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V440" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（**详解中间部分被双栏切断**，但末尾明确给出「$(\lnot p)\lor q$ 是真命题，$p\land q$、$p\lor(\lnot q)$、$(\lnot p)\land(\lnot q)$ 都是假命题」，据此推定 **$p$ 假、$q$ 真**，上述完整推导为我独立完成）。
+**独立验算**：
+① 四面体体积：$V=\frac13 S_{\triangle ABC}\cdot AD=\frac13\times\frac12\times1$ ✓ $=\frac16$
+（也可用行列式：$|\det(\vec{AB},\vec{AC},\vec{AD})|/6=\frac16$ ✓）
+② 垂直对数：前三个坐标平面两两垂直 $3$ 对 ✓；斜面 $BCD$ 与三者点积均为 $1\ne0$ → 不垂直 ✓；共 $3$ 对，$\frac36=\frac12$ ✓
+③ **三视图自洽检验**：
+正视图（沿 $y$ 轴方向投影到 $xz$ 平面）：$A(0,0)$、$B(1,0)$、$D(0,1)$、$C(0,0)$ → 直角三角形 $ABD$ ✓ 等腰（两直角边均为 $1$）✓
+同理侧视图、俯视图也是全等的等腰直角三角形 ✓✓ **三视图条件满足**
+④ 复合命题：$p$ 假 $q$ 真 → $(\lnot p)\lor q=$ 真 $\lor$ 真 $=$ 真 ✓
+$p\land q=$ 假；$p\lor(\lnot q)=$ 假 $\lor$ 假 $=$ 假；$(\lnot p)\land(\lnot q)=$ 真 $\land$ 假 $=$ 假 ✓ **唯一真命题是 C**
+**答案 C 正确** ✓
+**⭐ 提速技巧**：建系后四个面里三个是**坐标平面**（天然两两垂直 $3$ 对），只需再判断斜面与它们的关系 —— 法向量 $(1,1,1)$ 与三个坐标轴点积都为 $1$，一眼看出不垂直。</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>M-H0441</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>概率统计</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>概率小题</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>M-T-409(概率统计 / 概率小题 · 几何概型3：体积)</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J441" s="2" t="inlineStr">
+        <is>
+          <t>如图，三棱锥 $P-ABC$ 的四个面都为直角三角形，$PA\perp$ 平面 $ABC$，$PA=2$，$AC=BC=1$，三棱锥 $P-ABC$ 的四个顶点都在球 $O$ 的球面上，现在球 $O$ 内任取一点，则该点取自三棱锥 $P-ABC$ 内的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>$\dfrac2{24\pi}$</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>$\dfrac2{16\pi}$</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>$\dfrac2{12\pi}$</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>$\dfrac2{8\pi}$</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P441" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：找外接球球心**
+$PA\perp$ 平面 $ABC$ → $PA\perp AB$、$PA\perp BC$；
+$\triangle ABC$ 中 $AC=BC=1$ 且为直角三角形 → $AC\perp BC$（直角在 $C$）；
+由 $PA\perp BC$、$AC\perp BC$、$PA\cap AC=A$ 得 $BC\perp$ 平面 $PAC$，故 $BC\perp PC$．
+于是 $\triangle PAB$（$\angle A$ 为直角）与 $\triangle PBC$（$\angle C$ 为直角）共用斜边 $PB$，**$PB$ 的中点即外接球球心**（到 $P,A,B,C$ 等距）．
+**第二步：算半径**
+$AB=\sqrt{AC^{2}+BC^{2}}=\sqrt2$；$PB=\sqrt{PA^{2}+AB^{2}}=\sqrt{4+2}=\sqrt6$．
+（原书此处写「可得 $PB=2$，半径为 $1$」与 $PA=2,AC=BC=1$ 不符 —— 见 review）
+**第三步：算体积比**
+$V_{P-ABC}=\dfrac13\times\left(\dfrac12\times1\times1\right)\times2=\dfrac13$；
+$V_{\text{球}}=\dfrac43\pi R^{3}$．
+**第四步（按原书 $R=1$）**：
+$V_{\text{球}}=\dfrac43\pi$，概率 $=\dfrac{\frac13}{\frac43\pi}=\dfrac1{4\pi}=\dfrac2{8\pi}$．选 D．</t>
+        </is>
+      </c>
+      <c r="Q441" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S441" t="n">
+        <v>5</v>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-409-V3</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V441" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「三棱锥 $P-ABC$ 中，$PA\perp$ 平面 $ABC$，则 $PA\perp AB$、$PA\perp BC$；直角三角形 $ABC$ 中，$AC=BC$，则 $AC\perp BC$；又 $PA\perp BC$，$PA\cap AC=A$，则 $BC\perp$ 平面 $PAC$，则 $BC\perp PC$；则线段 $PB$ 中点为三棱锥 $P-ABC$ 的外接球的球心，又由 $PA=2$、$AC=BC=1$，可得 $PB=2$，则外接球的半径为 $1$。故在球 $O$ 内任取一点，该点取自三棱锥 $P-ABC$ 内的概率为 $\frac{V_{P-ABC}}{V_{\text{球}}}=\frac{\frac13\times\frac12\times1\times1\times2}{\frac43\pi}$…故选 D」还原。
+**⚠⚠ 原书数据不自洽（如实标注）**：
+由 $PA=2$、$AC=BC=1$ 且 $AC\perp BC$，严格算得 $AB=\sqrt2$、$PB=\sqrt{PA^2+AB^2}=\sqrt6$，半径 $R=\frac{\sqrt6}2\approx1.2247$，**而非原书写的 $PB=2$、$R=1$**。
+若取 $R=\frac{\sqrt6}2$：$V_{\text{球}}=\frac43\pi\cdot\frac{6\sqrt6}8=\sqrt6\pi\approx7.695$，概率 $=\frac{1/3}{\sqrt6\pi}=\frac1{3\sqrt6\pi}\approx0.0433$ —— **四个选项无一符合**。
+若按原书的 $R=1$：概率 $=\frac{1/3}{4\pi/3}=\frac1{4\pi}=\frac2{8\pi}$ ✓ **恰为选项 D**。
+**故按原书答案 D 录入**（分子 $\frac13\times\frac12\times1\times1\times2=\frac13$ 与 $PA=2,AC=BC=1$ 一致，说明**体积算法对、半径取值是原书另设**）。
+**选项还原**（PDF 页 399，y=363.4）：字符坐标准确给出四个分母 `24π`(x=59.9)、`16π`(x=116.0)、`12π`(x=172.1)、`8π`(x=229.3)，均在同一行；分子由 ref_bank 记为 `2`。
+取值：$A=\frac2{24\pi}=\frac1{12\pi}\approx0.0265$、$B=\frac2{16\pi}=\frac1{8\pi}\approx0.0398$、$C=\frac2{12\pi}=\frac1{6\pi}\approx0.0531$、$D=\frac2{8\pi}=\frac1{4\pi}\approx0.0796$（递增 ✓）
+**独立验算（按 $R=1$）**：
+① $V_{P-ABC}=\frac13\times\frac12\times1\times1\times2=\frac13\approx0.3333$ ✓
+② $V_{\text{球}}=\frac43\pi\approx4.1888$ ✓
+③ $\frac{0.3333}{4.1888}=0.0796=\frac1{4\pi}$ ✓✓ **与 D 完全吻合**
+**答案 D 正确**（在原书设定的 $R=1$ 下）✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>M-H0442</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>不等式</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>不等式选讲</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>M-T-026(不等式 / 不等式选讲 · 绝对值恒成立(存在)求参1：公式法“和”)</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J442" s="2" t="inlineStr">
+        <is>
+          <t>已知函数 $f(x)=\lvert x-2\rvert+\lvert x+a\rvert$．
+（1）若 $a=1$，解不等式 $f(x)\le2\lvert x-2\rvert$；
+（2）若 $f(x)\ge2$ 恒成立，求实数 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr"/>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>（1）$x\le\dfrac12$；（2）$a\ge0$ 或 $a\le-4$</t>
+        </is>
+      </c>
+      <c r="P442" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**当 $a=1$ 时，$f(x)=\lvert x-2\rvert+\lvert x+1\rvert$．
+不等式 $f(x)\le2\lvert x-2\rvert$ 即 $\lvert x-2\rvert+\lvert x+1\rvert\le2\lvert x-2\rvert$，
+两边消去一个 $\lvert x-2\rvert$，得 $\lvert x+1\rvert\le\lvert x-2\rvert$．
+两边非负，平方：$(x+1)^{2}\le(x-2)^{2}$，
+即 $x^{2}+2x+1\le x^{2}-4x+4$，得 $6x\le3$，故 $x\le\dfrac12$．
+**解集为 $\left\{x\mid x\le\frac12\right\}$．**
+**（2）**由三角不等式
+$f(x)=\lvert x-2\rvert+\lvert x+a\rvert=\lvert 2-x\rvert+\lvert x+a\rvert\ge\lvert(2-x)+(x+a)\rvert=\lvert a+2\rvert$．
+（当 $(2-x)(x+a)\ge0$，即 $x$ 在 $-a$ 与 $2$ 之间时取等）
+故 $f_{\min}=\lvert a+2\rvert$．要使 $f(x)\ge2$ 恒成立，只需 $\lvert a+2\rvert\ge2$：
+$a+2\ge2$ 或 $a+2\le-2$，解得 $a\ge0$ 或 $a\le-4$．
+**故 $a$ 的取值范围为 $(-\infty,-4]\cup[0,+\infty)$．**</t>
+        </is>
+      </c>
+      <c r="Q442" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S442" t="n">
+        <v>5</v>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-026-E1</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V442" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「（1）当 $a=1$ 时，$f(x)\le2\lvert x-2\rvert$，即 $\lvert x+1\rvert\le\lvert x-2\rvert$，解得 $x\le\frac12$；（2）$f(x)=\lvert x-2\rvert+\lvert x+a\rvert\ge\lvert x-2-(x+a)\rvert=\lvert a+2\rvert$，若 $f(x)\ge2$ 恒成立，只需 $\lvert a+2\rvert\ge2$，即 $a+2\ge2$ 或 $a+2\le-2$，解得 $a\ge0$ 或 $a\le-4$」还原。
+**独立验算**：
+（1）取 $x=0\le\frac12$：$\lvert0+1\rvert=1\le\lvert0-2\rvert=2$ ✓ 成立
+取 $x=1&gt;\frac12$：$\lvert1+1\rvert=2\le\lvert1-2\rvert=1$？**不成立** ✓ 符合
+边界 $x=\frac12$：$\lvert1.5\rvert=1.5\le\lvert-1.5\rvert=1.5$ ✓ 取等
+（2）取 $a=0$：$f=\lvert x-2\rvert+\lvert x\rvert\ge2$ ✓（最小值恰为 $2$，在 $x\in[0,2]$ 取到）
+取 $a=-4$：$f=\lvert x-2\rvert+\lvert x-4\rvert\ge2$ ✓（在 $x\in[2,4]$ 取等）
+取 $a=-1$（应不满足）：$f=\lvert x-2\rvert+\lvert x-1\rvert\ge1&lt;2$ ✗ 正确排除 ✓
+**答案正确** ✓
+**⭐ 通法**：「$f(x)\ge c$ 恒成立」⟹ 先求 $f_{\min}$，再令 $f_{\min}\ge c$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>M-H0443</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>不等式</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>不等式选讲</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>M-T-026(不等式 / 不等式选讲 · 绝对值恒成立(存在)求参1：公式法“和”)</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J443" s="2" t="inlineStr">
+        <is>
+          <t>设 $f(x)=\lvert x-a\rvert$，$a\in\mathbf R$．
+（1）当 $-1\le x\le3$ 时，$f(x)\le3$，求 $a$ 的取值范围；
+（2）若对任意 $x\in\mathbf R$，$f(x-a)+f(x+a)\ge1-2a$ 恒成立，求实数 $a$ 的最小值．</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr"/>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>（1）$[0,2]$；（2）$\dfrac14$</t>
+        </is>
+      </c>
+      <c r="P443" s="2" t="inlineStr">
+        <is>
+          <t>**（1）**$\lvert x-a\rvert\le3\iff a-3\le x\le a+3$，解集为 $[a-3,\ a+3]$．
+「当 $-1\le x\le3$ 时 $f(x)\le3$」即区间 $[-1,3]$ 包含于该解集：
+$\begin{cases}a-3\le-1\\a+3\ge3\end{cases}\iff\begin{cases}a\le2\\a\ge0\end{cases}$，故 $a\in[0,2]$．
+**（2）**$f(x-a)=\lvert x-a-a\rvert=\lvert x-2a\rvert$，$f(x+a)=\lvert x+a-a\rvert=\lvert x\rvert$．
+由三角不等式
+$f(x-a)+f(x+a)=\lvert x-2a\rvert+\lvert x\rvert=\lvert 2a-x\rvert+\lvert x\rvert\ge\lvert(2a-x)+x\rvert=2\lvert a\rvert$．
+（当 $x$ 在 $0$ 与 $2a$ 之间时取等）故最小值为 $2\lvert a\rvert$．
+要使 $\ge1-2a$ 恒成立，需 $2\lvert a\rvert\ge1-2a$．
+· 若 $a\ge0$：$2a\ge1-2a\iff4a\ge1\iff a\ge\dfrac14$；
+· 若 $a&lt;0$：$-2a\ge1-2a\iff0\ge1$，**无解**．
+故 $a\ge\dfrac14$，**最小值为 $\dfrac14$**．</t>
+        </is>
+      </c>
+      <c r="Q443" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S443" t="n">
+        <v>5</v>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-026-V1</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V443" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「（1）$f(x)=\lvert x-a\rvert\le3$，即 $a-3\le x\le a+3$，依题意：$\begin{cases}a-3\le-1\\a+3\ge3\end{cases}$，由此得 $a$ 的取值范围是 $[0,2]$；（2）$f(x-a)+f(x+a)=\lvert x-2a\rvert+\lvert x\rvert\ge\lvert(x-2a)-x\rvert=2\lvert a\rvert$，当且仅当 $(x-2a)x\le0$ 时等号成立…最小值为 $\frac14$」还原。
+**独立验算**：
+（1）取 $a=0$：$[-3,3]\supseteq[-1,3]$ ✓；取 $a=2$：$[-1,5]\supseteq[-1,3]$ ✓；取 $a=3$（应排除）：$[0,6]\not\supseteq[-1,3]$ ✗ 正确排除 ✓
+（2）取 $a=\frac14$：$\lvert x-\frac12\rvert+\lvert x\rvert\ge\frac12$，而 $1-2a=\frac12$ → 恰取等 ✓
+取 $a=0.2&lt;\frac14$：$2a=0.4$，而 $1-2a=0.6$，$0.4\ge0.6$ ✗ 不成立 ✓ 正确排除
+取 $a=-1$：$2\lvert a\rvert=2$，$1-2a=3$，$2\ge3$ ✗ 不成立 ✓ 负数无解得证
+**答案正确** ✓
+**⭐ 易错点**：第（2）问要**分 $a$ 的正负**讨论 $\lvert a\rvert$，直接写 $2a\ge1-2a$ 会漏掉 $a&lt;0$ 的情形（虽然本题 $a&lt;0$ 无解，但必须验证）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>M-H0444</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>不等式</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>不等式选讲</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>M-T-026(不等式 / 不等式选讲 · 绝对值恒成立(存在)求参1：公式法“和”)</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J444" s="2" t="inlineStr">
+        <is>
+          <t>已知不等式 $\lvert x+3\rvert&lt;2x+1$ 的解集为 $\{x\mid x&gt;m\}$．
+（Ⅰ）求 $m$ 的值；
+（Ⅱ）设关于 $x$ 的方程 $\lvert x-t\rvert+\left\lvert x+\dfrac1t\right\rvert=m$（$t\ne0$）有实数根，求实数 $t$ 的值．</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr"/>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>（Ⅰ）$m=2$；（Ⅱ）$t=\pm1$</t>
+        </is>
+      </c>
+      <c r="P444" s="2" t="inlineStr">
+        <is>
+          <t>**（Ⅰ）**按绝对值内符号分段（注意右边 $2x+1$ 也须为正才有解）：
+· 当 $x\ge-3$ 时：$x+3&lt;2x+1\iff x&gt;2$，结合 $x\ge-3$ 得 $x&gt;2$；
+· 当 $x&lt;-3$ 时：$-(x+3)&lt;2x+1\iff-x-3&lt;2x+1\iff-4&lt;3x\iff x&gt;-\dfrac43$，与 $x&lt;-3$ **矛盾，无解**．
+故解集为 $\{x\mid x&gt;2\}$，**$m=2$**．
+**（Ⅱ）**由三角不等式
+$\lvert x-t\rvert+\left\lvert x+\dfrac1t\right\rvert=\lvert x-t\rvert+\left\lvert-x-\dfrac1t\right\rvert\ge\left\lvert(x-t)+\left(-x-\dfrac1t\right)\right\rvert=\left\lvert t+\dfrac1t\right\rvert$．
+方程有实数根 $\iff$ 最小值 $\le m=2$，即 $\left\lvert t+\dfrac1t\right\rvert\le2$．
+另一方面，由基本不等式
+$\left\lvert t+\dfrac1t\right\rvert=\lvert t\rvert+\dfrac1{\lvert t\rvert}\ge2$（$t$ 与 $\frac1t$ 同号，故绝对值可直接拆开）．
+两边夹逼：$2\le\left\lvert t+\dfrac1t\right\rvert\le2$，故 $\left\lvert t+\dfrac1t\right\rvert=2$，
+取等条件为 $\lvert t\rvert=\dfrac1{\lvert t\rvert}$，即 $\lvert t\rvert=1$，**$t=\pm1$**．</t>
+        </is>
+      </c>
+      <c r="Q444" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S444" t="n">
+        <v>5</v>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-026-V2</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V444" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「（Ⅰ）…$\begin{cases}x&lt;-3\\-(x+3)&lt;2x+1\end{cases}$ 或 $\begin{cases}x\ge-3\\x+3&lt;2x+1\end{cases}$…得 $x=2$，依题意 $m=2$。
+（Ⅱ）因为 $m=2=\lvert x-t\rvert+\lvert x+\frac1t\rvert\ge\lvert x-t-(x+\frac1t)\rvert=\lvert t+\frac1t\rvert$，当且仅当 $(x-t)(x+\frac1t)\le0$ 时等号成立。∵$m=2$，∴需要 $\lvert t\rvert+\frac1{\lvert t\rvert}\le2$；另一方面 $\lvert t\rvert+\frac1{\lvert t\rvert}\ge2$，当且仅当 $\lvert t\rvert=\frac1{\lvert t\rvert}$ 时等号成立，∴只有 $\lvert t\rvert=1$」还原。
+**独立验算**：
+（Ⅰ）取 $x=3&gt;2$：$\lvert6\rvert=6&lt;2\times3+1=7$ ✓ 成立
+取 $x=1&lt;2$：$\lvert4\rvert=4&lt;3$？**不成立** ✓ 符合
+取 $x=-4$（属第二段）：$\lvert-1\rvert=1&lt;-7$？不成立 ✓ 无解得证
+（Ⅱ）取 $t=1$：方程 $\lvert x-1\rvert+\lvert x+1\rvert=2$，当 $x\in[-1,1]$ 时左边 $=2$ ✓ **有解**（无穷多解）
+取 $t=2$：$\lvert x-2\rvert+\lvert x+0.5\rvert\ge2.5&gt;2$ ✗ **无解** ✓ 正确排除
+取 $t=-1$：$\lvert x+1\rvert+\lvert x-1\rvert=2$ ✓ 同上，有解
+**答案正确** ✓
+**⭐ 本题精华**：「方程有解」$\iff$ 左边最小值 $\le$ 右边。而最小值由三角不等式给出，再用基本不等式从下方夹住 —— **上下夹逼**是求参数取值的经典手法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>M-H0445</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>解答</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>解答题-问答题</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>不等式</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>不等式选讲</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>M-T-026(不等式 / 不等式选讲 · 绝对值恒成立(存在)求参1：公式法“和”)</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J445" s="2" t="inlineStr">
+        <is>
+          <t>已知 $f(x)=\lvert x-1\rvert+\lvert x+2\rvert$．
+（Ⅰ）解不等式 $f(x)\ge5$；
+（Ⅱ）若关于 $x$ 的不等式 $f(x)&gt;a^{2}-2a$ 对任意 $x\in\mathbf R$ 恒成立，求 $a$ 的取值范围．</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr"/>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>（Ⅰ）$(-\infty,-3]\cup[2,+\infty)$；（Ⅱ）$(-1,3)$</t>
+        </is>
+      </c>
+      <c r="P445" s="2" t="inlineStr">
+        <is>
+          <t>**（Ⅰ）**两个零点为 $x=-2$、$x=1$，分三段：
+· 当 $x\le-2$ 时：$f(x)=(1-x)+(-x-2)=-2x-1$，
+$-2x-1\ge5\iff-2x\ge6\iff x\le-3$，结合 $x\le-2$ 得 $x\le-3$；
+· 当 $-2&lt;x&lt;1$ 时：$f(x)=(1-x)+(x+2)=3$，$3\ge5$ **不成立**；
+· 当 $x\ge1$ 时：$f(x)=(x-1)+(x+2)=2x+1$，
+$2x+1\ge5\iff x\ge2$，结合 $x\ge1$ 得 $x\ge2$．
+**综上，解集为 $(-\infty,-3]\cup[2,+\infty)$．**
+**（Ⅱ）**由三角不等式
+$f(x)=\lvert x-1\rvert+\lvert x+2\rvert\ge\lvert(x-1)-(x+2)\rvert=3$，
+当 $-2\le x\le1$ 时取等，故 $f_{\min}=3$．
+（也可由（Ⅰ）中的分段结果直接看出中间段恒为 $3$）
+要使 $f(x)&gt;a^{2}-2a$ 对任意 $x$ 恒成立，只需 $f_{\min}&gt;a^{2}-2a$：
+$a^{2}-2a&lt;3\iff a^{2}-2a-3&lt;0\iff(a-3)(a+1)&lt;0\iff-1&lt;a&lt;3$．
+**故 $a$ 的取值范围为 $(-1,3)$．**</t>
+        </is>
+      </c>
+      <c r="Q445" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S445" t="n">
+        <v>5</v>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-026-V3</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>教辅录入-第38批</t>
+        </is>
+      </c>
+      <c r="V445" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、答案完整 ✓（**原书详解在下一页、未提取到**，上述推导为我独立完成，并用答案交叉验证）。
+**独立验算**：
+（Ⅰ）取 $x=-3$：$f=\lvert-4\rvert+\lvert-1\rvert=4+1=5\ge5$ ✓ 取等（端点闭）
+取 $x=-2.5$：$f=\lvert-3.5\rvert+\lvert-0.5\rvert=3.5+0.5=4&lt;5$ ✗ 不在解集内 ✓
+取 $x=2$：$f=\lvert1\rvert+\lvert4\rvert=5\ge5$ ✓ 取等
+取 $x=0$：$f=1+2=3&lt;5$ ✗ 正确排除 ✓
+（Ⅱ）取 $a=0\in(-1,3)$：$a^2-2a=0$，$f_{\min}=3&gt;0$ ✓ 恒成立
+取 $a=-1$（边界）：$a^2-2a=1+2=3$，$f_{\min}=3$ → $3&gt;3$ ✗ **不成立** ✓ 开区间正确
+取 $a=3$（边界）：$9-6=3$，同样 $3&gt;3$ ✗ ✓ 开区间正确
+取 $a=4$（应排除）：$16-8=8$，$3&gt;8$ ✗ 不成立 ✓ 正确排除
+**答案正确** ✓
+**⭐ 易错点**：（Ⅱ）是 $f(x)&gt;\cdots$ **严格大于**，所以条件是 $f_{\min}&gt;a^{2}-2a$（严格），端点 $a=-1,3$ 处 $f_{\min}=3=a^2-2a$，不满足严格大于，**必须取开区间**。若题干是 $\ge$ 则可取闭区间。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V445"/>
+  <dimension ref="A1:V454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -47060,6 +47060,1127 @@
         </is>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>M-H0446</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>M-T-382(计数原理 / 排列组合 · 球放盒子模型2：球相同，盒子不同)</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J446" s="2" t="inlineStr">
+        <is>
+          <t>把 $1995$ 个不加区别的小球分别放在 $10$ 个不同的盒子里，使得第 $i$ 个盒子中至少有 $i$ 个球（$i=1,2,\ldots,10$），则不同放法的总数是（　　）</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>$\mathrm C_{1940}^{10}$</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>$\mathrm C_{1940}^{9}$</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>$\mathrm C_{1949}^{10}$</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>$\mathrm C_{1949}^{9}$</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P446" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：预处理，把「至少」化为「非负」**
+先在第 $i$ 个盒子里放入 $i$ 个球（$i=1,2,\ldots,10$），此时共放了
+$1+2+\cdots+10=\dfrac{10\times11}2=55$（个），
+还余下 $1995-55=1940$ 个球．
+**第二步：转化为允许为空的分配**
+问题等价于：把 $1940$ 个**相同**的球放入 $10$ 个**不同**的盒子，允许有的盒子为空．
+**第三步：隔板法（允许为空的公式）**
+方程 $x_{1}+x_{2}+\cdots+x_{10}=1940$（$x_{i}\ge0$）的非负整数解个数为
+$\mathrm C_{1940+10-1}^{10-1}=\mathrm C_{1949}^{9}$．
+（等价理解：把 $1940$ 个球与 $9$ 块隔板排成一排，共占 $1949$ 个位置，从中选 $9$ 个位置放隔板）
+故选 D．</t>
+        </is>
+      </c>
+      <c r="Q446" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S446" t="n">
+        <v>5</v>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-382-E1</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>教辅录入-第39批</t>
+        </is>
+      </c>
+      <c r="V446" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「先在第 $i$ 个盒里放入 $i$ 个球，$i=1,2,\ldots,10$…这时共放了 $1+2+\cdots+10=55$ 个球，还余下 $1995-55=1940$ 个球。故转化为把 $1940$ 个球任意放入 $10$ 个盒子里（允许有的盒子里不放球）。把这 $1940$ 个球用 $9$ 块隔板隔开，每一种隔法就是一种球的放法，$1940$ 个球连同 $9$ 块隔板共占有 $1949$ 个位置，相当于从 $1949$ 个位置中选 $9$ 个位置放隔板，有 $\mathrm C_{1949}^{9}$ 种放法。选 D」还原。
+**独立验算**：
+① $1+2+\cdots+10=\frac{10\times11}2=55$ ✓；$1995-55=1940$ ✓
+② 隔板法公式：$n$ 个相同球放 $m$ 个不同盒、允许空 ⟺ $\mathrm C_{n+m-1}^{m-1}$
+=$n=1940$、$m=10$ → $\mathrm C_{1949}^{9}$ ✓
+③ **小样本对拍**（验证公式）：$3$ 个球放 $2$ 个盒允许空，枚举 $(0,3)(1,2)(2,1)(3,0)$ 共 $4$ 种；公式 $\mathrm C_{3+2-1}^{1}=\mathrm C_4^1=4$ ✓
+**答案 D 正确** ✓
+**⭐ 通法**：「至少」型隔板法两步走 —— ① 先按最低要求预放，把条件化为 $x_i\ge0$；② 套 $\mathrm C_{n+m-1}^{m-1}$。（若要求**每盒至少 1 个**，才用 $\mathrm C_{n-1}^{m-1}$，别混用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>M-H0447</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>M-T-382(计数原理 / 排列组合 · 球放盒子模型2：球相同，盒子不同)</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J447" s="2" t="inlineStr">
+        <is>
+          <t>将 $7$ 个相同的球放入 $4$ 个不同的盒子中，则每个盒子都有球的放法种数为（　　）</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>$22$</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>$25$</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>$20$</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>$48$</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P447" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：识别模型**
+球**相同**、盒子**不同**、每盒至少 $1$ 个 —— 标准隔板法．
+**第二步：插板**
+将 $7$ 个球摆成一排，中间形成 $7-1=6$ 个空隙；
+在这些空隙中插入 $4-1=3$ 块隔板，即把球分成 $4$ 组（每组至少 $1$ 个），每组对应一个盒子．
+**第三步**：$\mathrm C_{6}^{3}=\dfrac{6\times5\times4}{3\times2\times1}=20$．
+故选 C．</t>
+        </is>
+      </c>
+      <c r="Q447" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S447" t="n">
+        <v>5</v>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-382-V1</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>教辅录入-第39批</t>
+        </is>
+      </c>
+      <c r="V447" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「将 $7$ 个相同的球放入 $4$ 个不同的盒子中…因为每个盒子都有球，所以每个盒子至少有一个球，不妨将 $7$ 个球摆成一排，中间形成 $6$ 个空，只需在这 $6$ 个空插入 $3$ 个隔板将它们隔开，即分成 $4$ 组，不同插入方法共有 $\mathrm C_6^3=20$ 种，所以每个盒子都有球的放法种数为 $20$」还原。
+**独立验算**：
+① 公式：$n$ 个相同球放 $m$ 个不同盒、每盒至少 $1$ → $\mathrm C_{n-1}^{m-1}=\mathrm C_6^3=20$ ✓
+② **穷举验证**（列出所有 $(a,b,c,d)$ 正整数解，和为 $7$，不计顺序有 3 类）：
+· $(4,1,1,1)$：排列 $\frac{4!}{3!}=4$ 种
+· $(3,2,1,1)$：排列 $\frac{4!}{2!}=12$ 种
+· $(2,2,2,1)$：排列 $\frac{4!}{3!}=4$ 种
+合计 $4+12+4=20$ ✓✓ **与公式完全一致**
+**答案 C 正确** ✓
+**⭐ 易错点**：球**相同**才用隔板法；若球**不同**，则是「满射」问题，要用容斥或斯特林数：$4!\cdot S(7,4)=8400$，与 $20$ 天差地别。</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>M-H0448</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>M-T-382(计数原理 / 排列组合 · 球放盒子模型2：球相同，盒子不同)</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J448" s="2" t="inlineStr">
+        <is>
+          <t>把 $20$ 个相同的小球装入编号分别为 ①②③④ 的 $4$ 个盒子里，要求 ①② 号盒每盒至少 $3$ 个球，③④ 号盒每盒至少 $4$ 个球，共有几种方法．（　　）</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>$\mathrm C_{9}^{3}$</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>$\mathrm C_{19}^{3}$</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>$\mathrm C_{9}^{3}\mathrm A_{4}^{4}$</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>$\mathrm C_{20}^{14}\mathrm C_{5}^{3}$</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P448" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：设元**
+设四个盒子中装的小球个数分别为 $a,b,c,d$，则 $a+b+c+d=20$，
+且 $a\ge3$、$b\ge3$、$c\ge4$、$d\ge4$．
+**第二步：换元，统一化为「至少 1」**
+令 $w=a-2$、$x=b-2$、$y=c-3$、$z=d-3$，
+则 $w,x,y,z$ 都 $\ge1$（因 $a\ge3\Rightarrow w\ge1$，以此类推），且
+$w+x+y+z=20-(2+2+3+3)=20-10=10$．
+**第三步：隔板法**
+问题等价于：把 $10$ 个球分成 $4$ 部分，每部分至少 $1$ 个．
+在 $10$ 个球的 $9$ 个间隔中选 $3$ 个插板：$\mathrm C_{9}^{3}$．
+故选 A．</t>
+        </is>
+      </c>
+      <c r="Q448" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S448" t="n">
+        <v>5</v>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-382-V2</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>教辅录入-第39批</t>
+        </is>
+      </c>
+      <c r="V448" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「设四个盒子中装的小球个数分别为 $a,b,c,d$，则 $a+b+c+d=20$，要求①②号盒每盒至少 $3$ 个球，③④号盒每盒至少 $4$ 个球，令 $w=a-2$、$x=b-2$、$y=c-3$、$z=d-3$，则 $w,x,y,z$ 都大于或等于 $1$，且 $w+x+y+z=10$，问题相当于将 $10$ 个球分成四部分，在 $10$ 个球的 $9$ 个间隔里选 $3$ 个插板，有 $\mathrm C_9^3$ 种方法」还原。
+**独立验算**：
+① 换元自洽性：$a\ge3\to w=a-2\ge1$ ✓；$c\ge4\to y=c-3\ge1$ ✓
+② 和：$20-2-2-3-3=10$ ✓
+③ 隔板法：$10$ 个球分 $4$ 份每份 $\ge1$ → $\mathrm C_{10-1}^{4-1}=\mathrm C_9^3=84$ ✓
+④ **直接法对拍**（不换元，用「至少」版公式）：
+令 $a'=a-3\ge0$、$b'=b-3\ge0$、$c'=c-4\ge0$、$d'=d-4\ge0$，
+则 $a'+b'+c'+d'=20-14=6$，非负解个数 $=\mathrm C_{6+4-1}^{4-1}=\mathrm C_9^3=84$ ✓✓ **两种换元结果一致**
+**答案 A 正确** ✓
+**⭐ 关键**：换元时**减的数要比下限少 $1$**，才能凑出「$\ge1$」从而用 $\mathrm C_{n-1}^{m-1}$；若直接减下限凑出「$\ge0$」，就要改用 $\mathrm C_{n+m-1}^{m-1}$ —— 殊途同归。</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>M-H0449</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>M-T-374(解析几何 / 离心率 · 双曲线特性2：内心)</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J449" s="2" t="inlineStr">
+        <is>
+          <t>设 $F_{1},F_{2}$ 分别为双曲线 $\dfrac{x^{2}}{a^{2}}-\dfrac{y^{2}}{b^{2}}=1$（$a&gt;0,b&gt;0$）的左右焦点，点 $P(x_{0},a)$ 为双曲线上的一点，若 $\triangle PF_{1}F_{2}$ 的重心和内心的连线与 $x$ 轴垂直，则双曲线的离心率为（　　）</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>$\dfrac{3\sqrt2}4$</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>$\dfrac{3\sqrt3}4$</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P449" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求重心 $G$ 的横坐标**
+$G$ 是 $\triangle PF_{1}F_{2}$ 的重心，$P(x_{0},a)$、$F_{1}(-c,0)$、$F_{2}(c,0)$：
+$x_{G}=\dfrac{x_{0}+(-c)+c}3=\dfrac{x_{0}}3$．
+**第二步：求内心 $D$ 的横坐标**
+设内切圆与 $PF_{1}$、$PF_{2}$ 的切点为 $A,B$，与 $x$ 轴切于 $C(t,0)$．
+由切线长定理：$PA=PB$、$F_{1}A=F_{1}C$、$F_{2}B=F_{2}C$，且 $D$ 与 $C$ 横坐标相同．
+于是 $PF_{1}-PF_{2}=(PA+F_{1}A)-(PB+F_{2}B)=F_{1}C-F_{2}C$
+$=(t+c)-(c-t)=2t$．
+又由双曲线定义 $PF_{1}-PF_{2}=2a$（$P$ 在右支），故 $2t=2a$，即 $t=a$．
+**内心 $D$ 的横坐标为 $a$** —— 内切圆与 $x$ 轴切于右顶点．
+**第三步：连线垂直于 $x$ 轴 ⟺ 横坐标相等**
+$\dfrac{x_{0}}3=a\Rightarrow x_{0}=3a$．
+**第四步：代入双曲线求 $e$**
+$P(3a,a)$ 在双曲线上：$\dfrac{(3a)^{2}}{a^{2}}-\dfrac{a^{2}}{b^{2}}=1$
+$\Rightarrow9-\dfrac{a^{2}}{b^{2}}=1\Rightarrow\dfrac{a^{2}}{b^{2}}=8\Rightarrow b^{2}=\dfrac{a^{2}}8$．
+$c^{2}=a^{2}+b^{2}=a^{2}+\dfrac{a^{2}}8=\dfrac{9a^{2}}8$，
+$e=\dfrac ca=\sqrt{\dfrac98}=\dfrac3{2\sqrt2}=\dfrac{3\sqrt2}4$．选 A．</t>
+        </is>
+      </c>
+      <c r="Q449" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S449" t="n">
+        <v>5</v>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-374-V1</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>教辅录入-第39批</t>
+        </is>
+      </c>
+      <c r="V449" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「内心为 $D$，内切圆与 $PF_{1}$、$PF_{2}$ 的切点分别为 $A,B$，与 $x$ 轴切点为 $C$，则 $PA=PB$，$F_{1}A=F_{1}C$，$F_{2}B=F_{2}C$，且点 $D$ 与点 $C$ 横坐标相同，又由双曲线定义知 $PF_{1}-PF_{2}=2a$，从而 $CF_{1}-CF_{2}=2a$…故点 $C$ 为双曲线的右顶点，故 $D$ 点的横坐标为 $a$，因为 $\triangle PF_{1}F_{2}$ 的重心和内心的连线与 $x$ 轴垂直，所以 $\frac{x_0}3=a$…解得 $c=3b$，即 $c^{2}=9(c^{2}-a^{2})$」还原。
+**独立验算**（两条路径交叉验证）：
+路径一（我的）：$x_0=3a$ → $9-\frac{a^2}{b^2}=1$ → $b^2=\frac{a^2}8$ → $c^2=\frac{9a^2}8$ → $e=\sqrt{9/8}=\frac{3\sqrt2}4\approx1.0607$
+路径二（详解的 $c=3b$）：$c^2=9b^2=9(c^2-a^2)$ → $c^2=9c^2-9a^2$ → $8c^2=9a^2$ → $e^2=\frac98$ → $e=\frac{3\sqrt2}4$ ✓✓ **完全一致**
+③ 回代检验：$e=\frac{3\sqrt2}4$ → $b^2=a^2(e^2-1)=a^2(\frac98-1)=\frac{a^2}8$ ✓
+$P(3a,a)$ 代入：$\frac{9a^2}{a^2}-\frac{a^2}{a^2/8}=9-8=1$ ✓✓ **在双曲线上**
+④ $e=\frac{3\sqrt2}4\approx1.0607&gt;1$ ✓ 是合法离心率
+**答案 A 正确** ✓
+**⭐ 通法（本题核心结论，很有用）**：
+双曲线上点 $P$ 与两焦点构成 $\triangle PF_1F_2$，**其内切圆与 $x$ 轴的切点必是顶点**！
+推导只用了一次切线长定理 + 双曲线定义，值得记住。</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>M-H0450</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>M-T-374(解析几何 / 离心率 · 双曲线特性2：内心)</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J450" s="2" t="inlineStr">
+        <is>
+          <t>已知双曲线 $\dfrac{x^{2}}{a^{2}}-\dfrac{y^{2}}{b^{2}}=1$（$a,b&gt;0$）的左右焦点记为 $F_{1},F_{2}$，直线 $l$ 过 $F_{2}$ 且与该双曲线的一条渐近线平行，记 $l$ 与双曲线的交点为 $P$，若所得 $\triangle PF_{1}F_{2}$ 的内切圆半径恰为 $\dfrac b3$，则此双曲线的离心率为（　　）</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>$2$</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>$\dfrac53$</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>$3$</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>$\dfrac{11}2$</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P450" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：求交点 $P$**
+渐近线斜率为 $\dfrac ba$，过 $F_{2}(c,0)$ 的直线 $l$：$y=\dfrac ba(x-c)$．
+代入双曲线：$\dfrac{x^{2}}{a^{2}}-\dfrac{(x-c)^{2}}{a^{2}}=1$
+$\Rightarrow x^{2}-(x-c)^{2}=a^{2}\Rightarrow2cx-c^{2}=a^{2}\Rightarrow x=\dfrac{a^{2}+c^{2}}{2c}$．
+$y=\dfrac ba\cdot\dfrac{a^{2}-c^{2}}{2c}=\dfrac ba\cdot\dfrac{-b^{2}}{2c}=-\dfrac{b^{3}}{2ac}$．
+**第二步：求 $\lvert PF_{2}\rvert$ 与周长**
+$\lvert PF_{2}\rvert^{2}=\left(\dfrac{-b^{2}}{2c}\right)^{2}+\left(\dfrac{-b^{3}}{2ac}\right)^{2}$
+$=\dfrac{b^{4}}{4c^{2}}+\dfrac{b^{6}}{4a^{2}c^{2}}=\dfrac{b^{4}(a^{2}+b^{2})}{4a^{2}c^{2}}=\dfrac{b^{4}}{4a^{2}}$，
+故 $\lvert PF_{2}\rvert=\dfrac{b^{2}}{2a}$；由双曲线定义 $\lvert PF_{1}\rvert=\lvert PF_{2}\rvert+2a=\dfrac{b^{2}}{2a}+2a$．
+周长 $=\dfrac{b^{2}}{a}+2a+2c=a\left[(e^{2}-1)+2+2e\right]=a(e+1)^{2}$．
+**第三步：算内切圆半径**
+$S=\dfrac12\cdot\lvert F_{1}F_{2}\rvert\cdot\lvert y_{P}\rvert=\dfrac12\cdot2c\cdot\dfrac{b^{3}}{2ac}=\dfrac{b^{3}}{2a}$．
+$r=\dfrac{2S}{\text{周长}}=\dfrac{b^{3}/a}{a(e+1)^{2}}=\dfrac{b\cdot a^{2}(e^{2}-1)}{a^{2}(e+1)^{2}}=\dfrac{b(e-1)}{e+1}$．
+**第四步**：令 $\dfrac{b(e-1)}{e+1}=\dfrac b3$，即 $\dfrac{e-1}{e+1}=\dfrac13$：
+$3e-3=e+1\Rightarrow2e=4\Rightarrow e=2$．选 A．</t>
+        </is>
+      </c>
+      <c r="Q450" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S450" t="n">
+        <v>5</v>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-374-V2</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>教辅录入-第39批</t>
+        </is>
+      </c>
+      <c r="V450" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（**原书详解在该处提取破碎**，上述推导为我独立完成，并用答案交叉验证）。
+**独立验算**（取 $e=2$ 反代，令 $a=1$）：
+① $c=2$、$b^{2}=c^{2}-a^{2}=3$、$b=\sqrt3$
+② $P$ 的横坐标 $=\frac{a^2+c^2}{2c}=\frac{1+4}4=1.25$；纵坐标 $=-\frac{b^3}{2ac}=-\frac{3\sqrt3}{4}\approx-1.2990$
+③ **验证 $P$ 在双曲线上**：$1.25^{2}-\frac{1.2990^{2}}3=1.5625-0.5625=1$ ✓✓
+④ $\lvert PF_{2}\rvert=\frac{b^2}{2a}=\frac32=1.5$；直接算 $\sqrt{(1.25-2)^{2}+1.2990^{2}}=\sqrt{0.5625+1.6875}=\sqrt{2.25}=1.5$ ✓✓
+⑤ $\lvert PF_{1}\rvert=1.5+2=3.5$；周长 $=3.5+1.5+4=9$；公式 $a(e+1)^2=1\times9=9$ ✓✓
+⑥ $S=\frac12\times4\times1.2990=2.5981$；$r=\frac{2\times2.5981}9=0.5774$；$\frac b3=\frac{\sqrt3}3=0.5774$ ✓✓ **完全吻合**
+**答案 A 正确** ✓
+**⭐ 通用公式（本批最重要收获）**：
+$$r=\frac{b(e-1)}{e+1}\quad\Longleftrightarrow\quad\frac{r}{b}=\frac{e-1}{e+1}$$
+只要题干是「过 $F_2$ 作渐近线平行线」，就可直接套用，不必重算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>M-H0451</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>M-T-374(解析几何 / 离心率 · 双曲线特性2：内心)</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J451" s="2" t="inlineStr">
+        <is>
+          <t>已知双曲线 $\dfrac{x^{2}}{a^{2}}-\dfrac{y^{2}}{b^{2}}=1$（$b&gt;a&gt;0$）的左、右焦点分别为 $F_{1},F_{2}$，过右焦点作平行于一条渐近线的直线交双曲线于点 $A$，若 $\triangle AF_{1}F_{2}$ 的内切圆半径为 $\dfrac b4$，则双曲线的离心率为（　　）</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>$\dfrac53$</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>$\dfrac54$</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>$\dfrac43$</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>$\dfrac32$</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P451" s="2" t="inlineStr">
+        <is>
+          <t>**沿用 V2 的结论**（过焦点作渐近线平行线的模型）：
+设 $P$ 为交点，则 $\lvert PF_{2}\rvert=\dfrac{b^{2}}{2a}$、周长 $=a(e+1)^{2}$、$S=\dfrac{b^{3}}{2a}$，从而
+$r=\dfrac{2S}{\text{周长}}=\dfrac{b(e-1)}{e+1}$．
+（完整推导见 M-T-374-V2 的解答）
+**代入本题条件** $r=\dfrac b4$：
+$\dfrac{b(e-1)}{e+1}=\dfrac b4\Rightarrow\dfrac{e-1}{e+1}=\dfrac14$
+$\Rightarrow4e-4=e+1\Rightarrow3e=5\Rightarrow e=\dfrac53$．选 A．</t>
+        </is>
+      </c>
+      <c r="Q451" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S451" t="n">
+        <v>5</v>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-374-V3</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>教辅录入-第39批</t>
+        </is>
+      </c>
+      <c r="V451" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（本题与 M-T-374-V2 **同模型**，仅半径由 $\frac b3$ 改为 $\frac b4$，故解答中直接引用了 V2 的通用公式，两题互引）。
+**独立验算**（取 $e=\frac53$ 反代，令 $a=1$）：
+① $c=\frac53$、$b^{2}=c^{2}-a^{2}=\frac{25}9-1=\frac{16}9$、$b=\frac43$
+② **检验 $b&gt;a$ 条件**：$\frac ba=\frac43&gt;1$ ✓ **与题设吻合**
+③ $P$ 横坐标 $=\frac{1+25/9}{2\cdot5/3}=\frac{34/9}{10/3}=\frac{34}{30}=\frac{17}{15}\approx1.1333$；
+纵坐标 $=-\frac{b^3}{2ac}=-\frac{64/27}{10/3}=-\frac{64}{90}=-\frac{32}{45}\approx-0.7111$
+④ **验证 $P$ 在双曲线上**：$1.1333^{2}-\frac{0.7111^{2}}{16/9}=1.2844-\frac{0.5057}{1.7778}$
+$=1.2844-0.2844=1$ ✓✓
+⑤ $\lvert PF_{2}\rvert=\frac{b^2}{2a}=\frac{16/9}2=\frac89\approx0.8889$；直接算 $\sqrt{(1.1333-1.6667)^{2}+0.7111^{2}}=\sqrt{0.2844+0.5057}=\sqrt{0.7901}=0.8889$ ✓✓
+⑥ 周长 $=0.8889+2+2\times1.6667=6.2223$；公式 $a(e+1)^2=(\frac83)^2=\frac{64}9=7.111$
+—— ⚠ 重算：$\lvert PF_1\rvert=\lvert PF_2\rvert+2a=0.8889+2=2.8889$；周长 $=2.8889+0.8889+3.3333=7.1111$ ✓ = $\frac{64}9$ ✓✓
+⑦ $S=\frac12\times3.3333\times0.7111=1.1852$；$r=\frac{2\times1.1852}{7.1111}=0.3333$；$\frac b4=\frac{4/3}4=\frac13=0.3333$ ✓✓ **完全吻合**
+**答案 A 正确** ✓
+**⭐ V2 与 V3 对照（记住这个规律）**：
+| 内切圆半径 | $\frac{e-1}{e+1}$ | 离心率 |
+|---|---|---|
+| $\frac b3$ | $\frac13$ | $e=2$ |
+| $\frac b4$ | $\frac14$ | $e=\frac53$ |
+一般地，$r=\frac bk$ 时 $e=\frac{k+1}{k-1}$。半径越小（内切圆越扁），离心率越接近 $1$。</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>M-H0452</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>M-T-381(计数原理 / 排列组合 · 球放盒子模型1：球不同，盒子也不同)</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J452" s="2" t="inlineStr">
+        <is>
+          <t>将 $5$ 个不同的小球放入 $3$ 个不同的盒子，每个盒子至少 $1$ 个球，至多 $2$ 个球，则不同的放法种数有（　　）</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>$30$ 种</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>$90$ 种</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>$180$ 种</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>$270$ 种</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P452" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：确定个数分配**
+$5$ 个球放入 $3$ 个盒子，每盒 $1\sim2$ 个，则各盒球数只能是 $1,2,2$ 的排列：
+$(1,2,2)$、$(2,1,2)$、$(2,2,1)$，**共 $3$ 类**．
+**第二步：算第一类 $(1,2,2)$**
+第 $1$ 个盒子装 $1$ 个：$\mathrm C_{5}^{1}=5$；
+第 $2$ 个盒子从余下 $4$ 个中装 $2$ 个：$\mathrm C_{4}^{2}=6$；
+第 $3$ 个盒子装最后 $2$ 个：$\mathrm C_{2}^{2}=1$．
+第一类放法数 $=5\times6\times1=30$．
+**第三步：三类对称，种数相同**
+$N=3\times30=90$．选 B．</t>
+        </is>
+      </c>
+      <c r="Q452" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S452" t="n">
+        <v>5</v>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-381-V1</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>教辅录入-第39批</t>
+        </is>
+      </c>
+      <c r="V452" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「对三个盒子进行编号 $1,2,3$，则每个盒子装球的情况可分为三类：$1,2,2$；$2,1,2$；$2,2,1$；且每一类的放法种数相同。先考虑第一类，即 $3$ 个盒子放球的个数为 $1,2,2$，则第 $1$ 个盒子有 $\mathrm C_5^1=5$，第 $2$ 个盒子有 $\mathrm C_4^2=6$，第 $3$ 个盒子有 $\mathrm C_2^2=1$，∴第一类放法种数为 $5\times6\times1=30$，∴不同的放法种数有 $N=3\times30=90$」还原。
+**独立验算**（用另一种方法对拍）：
+先选哪两个盒子装 $2$ 个球：$\mathrm C_3^2=3$；
+再选 $4$ 个球分成两组给这两个盒子：$\mathrm C_5^4\times\mathrm C_4^2=5\times6=30$（先选出 $4$ 个，再选 $2$ 个给其中一盒）；
+剩下的 $1$ 个给最后一个盒子：$1$ 种。
+合计 $3\times30=90$ ✓✓ **两法一致**
+（也可用满射思想：$5$ 个不同球入 $3$ 个不同盒且每盒 $\le2$，即 $3!\,S(5,3)$ 中剔除含 $3$ 个的分配，结果同为 $90$）
+**答案 B 正确** ✓
+**⭐ 注意**：本题球**不同**、盒子**不同**，用组合数分步；若是「$5$ 个**相同**球入 $3$ 个盒，每盒 $1\sim2$ 个」，答案只有 $3$ 种 —— 天壤之别。</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>M-H0453</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>M-T-381(计数原理 / 排列组合 · 球放盒子模型1：球不同，盒子也不同)</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J453" s="2" t="inlineStr">
+        <is>
+          <t>将编号分别为 $1,2,3,4,5$ 的 $5$ 个小球分别放入 $3$ 个不同的盒子中，每个盒子都不空，则每个盒子中所放小球的编号奇偶性均不相同的概率为（　　）</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>$\dfrac17$</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>$\dfrac16$</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>$\dfrac6{25}$</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>$\dfrac7{24}$</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P453" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：算分母（所有放法）**
+$5$ 个不同球入 $3$ 个不同盒、每盒不空，个数分配有 $(3,1,1)$ 与 $(2,2,1)$ 两类：
+· $(3,1,1)$ 型：选装 $3$ 个的盒子 $\mathrm C_3^1=3$，选 $3$ 个球 $\mathrm C_5^3=10$，余下 $2$ 个球分给另两盒 $\mathrm A_2^2=2$ → $3\times10\times2=60$；
+· $(2,2,1)$ 型：选装 $1$ 个的盒子 $\mathrm C_3^1=3$，选 $1$ 个球 $\mathrm C_5^1=5$，余下 $4$ 个球平分给另两盒 $\mathrm C_4^2=6$ → $3\times5\times6=90$．
+分母 $=60+90=150$（$=3!\cdot S(5,3)=6\times25$）．
+**第二步：分析分子的限制**
+$5$ 个球中奇数有 $\{1,3,5\}$ 共 $3$ 个，偶数有 $\{2,4\}$ 共 $2$ 个．
+「每盒内编号奇偶性均不同」⟹ 每盒至多 $2$ 个球（只有两种奇偶）
+⟹ 分配只能是 $2+2+1$，且两个「$2$」必须各含 $1$ 奇 $1$ 偶．
+用掉 $2$ 奇 $2$ 偶后，**剩下 $1$ 个奇数**装入单球盒．
+**第三步：数分子**
+选单球盒 $\mathrm C_3^1=3$；选装进去的那个奇数 $\mathrm C_3^1=3$；
+余下 $2$ 个奇数分给另两盒 $\mathrm A_2^2=2$；$2$ 个偶数分给另两盒 $\mathrm A_2^2=2$．
+分子 $=3\times3\times2\times2=36$．
+**第四步**：$P=\dfrac{36}{150}=\dfrac6{25}$．选 C．</t>
+        </is>
+      </c>
+      <c r="Q453" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S453" t="n">
+        <v>5</v>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-381-V2</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>教辅录入-第39批</t>
+        </is>
+      </c>
+      <c r="V453" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「由题知，要求每个盒子都不空，则 $3$ 个盒子中放入小球的个数可分别为 $3,1,1$ 或 $2,2,1$；若要求每个盒子中小球编号的奇偶性不同则只能是 $2,2,1$，且放入同一盒子中的两个小球必须是编号为一奇一偶，故所求概率为 $P=\frac{\mathrm C_3^2\mathrm A_2^2\mathrm A_3^3}{\mathrm C_5^3\mathrm A_3^3+\mathrm C_5^2\mathrm C_3^2\mathrm A_3^3}=\frac6{25}$」还原。
+**⚠⚠ 分母公式有提取缺失（已修正）**：按字面算 $\mathrm C_5^3\mathrm A_3^3+\mathrm C_5^2\mathrm C_3^2\mathrm A_3^3=60+180=240$，得 $\frac{36}{240}=\frac3{20}$ —— **不是答案**。
+正确分母应为 $\mathrm C_5^3\mathrm A_3^3+\frac{\mathrm C_5^2\mathrm C_3^2}{\mathrm A_2^2}\mathrm A_3^3=60+90=150$：
+$(2,2,1)$ 型中两个「$2$」**大小相同**，须除以 $\mathrm A_2^2$ 去重（提取时丢了这一项）。
+代入得 $\frac{36}{150}=\frac6{25}$ ✓✓ **与答案 C 吻合**。
+（分子 $\mathrm C_3^2\mathrm A_2^2\mathrm A_3^3=3\times2\times6=36$ ✓ 与我的算法一致）
+**独立验算**（分母用满射公式对拍）：
+$3!\cdot S(5,3)=6\times25=150$ ✓✓（$S(5,3)=25$ 为标准值）
+**答案 C 正确** ✓
+**⭐ 通用结论**：$n$ 个**不同**球入 $m$ 个**不同**盒、每盒不空 ⟺ $m!\,S(n,m)$（满射数）。本题 $S(5,3)=25$，故 $150$。这个结论比现场分类型更快，也不易漏重。</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>M-H0454</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>M-T-381(计数原理 / 排列组合 · 球放盒子模型1：球不同，盒子也不同)</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J454" s="2" t="inlineStr">
+        <is>
+          <t>将 $A,B,C,D$ 四个小球放入编号为 $1,2,3$ 的三个盒子中，若每个盒子中至少放一个球且 $A,B$ 不能放入同一个盒子中，则不同的放法种数为（　　）</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>$15$</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>$30$</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>$20$</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>$42$</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P454" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：不加限制的总数**
+$4$ 个不同球入 $3$ 个不同盒、每盒不空 $\iff$ 满射数 $3!\cdot S(4,3)$．
+$S(4,3)=\mathrm C_4^2=6$（分配为 $2+1+1$，只需选出那 $2$ 个成组的球），
+故总数 $=6\times6=36$．
+**第二步：减去 $A,B$ 同盒的情形**
+每盒不空且共 $4$ 个球，个数分配必为 $2+1+1$，故「装 $2$ 个」的盒子只有一个 —— $A,B$ 同盒意味着**它俩正是那一组**．
+选 $A,B$ 所在的盒子：$3$ 种；
+余下 $C,D$ 分给另外两个盒子：$\mathrm A_2^2=2$ 种．
+共 $3\times2=6$ 种．
+**第三步**：$36-6=30$．选 B．</t>
+        </is>
+      </c>
+      <c r="Q454" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S454" t="n">
+        <v>5</v>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-381-V3</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>教辅录入-第39批</t>
+        </is>
+      </c>
+      <c r="V454" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「按照放入同一盒子的球进行分类，最后由分类加法计数原理计算即可」（**详解正文未提取到**，上述推导为我独立完成）。
+**独立验算**（用完全正向的分类法对拍）：
+按「哪两个球同盒」分类，共 $\mathrm C_4^2=6$ 种配对，排除 $\{A,B\}$ 后剩 $5$ 种：
+$\{A,C\}$、$\{A,D\}$、$\{B,C\}$、$\{B,D\}$、$\{C,D\}$
+每种配对下：选该组所在的盒子 $3$ 种，余下两球分给另两盒 $2$ 种 → 每组 $6$ 种
+合计 $5\times6=30$ ✓✓ **与减法结果一致**
+**答案 B 正确** ✓
+**⭐ 两种思路**：
+① **补集法**（本题解法）：总数 $36$ 减去违规 $6$，快；
+② **正向分类**：按配对枚举 $5$ 类，每类 $6$ 种 —— 更直观但慢。
+当限制条件简单（如「某两元素不能同组」）时，**补集法通常更快**。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gaokao-paper/高三题库与间隔复习系统.xlsx
+++ b/gaokao-paper/高三题库与间隔复习系统.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V454"/>
+  <dimension ref="A1:V464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -48181,6 +48181,1304 @@
         </is>
       </c>
     </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>M-H0455</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>M-T-368(解析几何 / 离心率 · 余弦定理3：余弦定理用两次  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J455" s="2" t="inlineStr">
+        <is>
+          <t>已知 $F_{1},F_{2}$ 分别是双曲线 $\dfrac{x^{2}}{a^{2}}-\dfrac{y^{2}}{b^{2}}=1$（$a&gt;0,b&gt;0$）的左、右焦点，点 $P$ 在双曲线右支上且不与顶点重合，过 $F_{2}$ 作 $\angle F_{1}PF_{2}$ 的角平分线的垂线，垂足为 $A$．若 $\lvert F_{1}A\rvert=\sqrt5\,b$，则该双曲线离心率的取值范围为（　　）</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>$(1,\sqrt2)$</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>$(\sqrt2,\dfrac32)$</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>$(\sqrt2,\sqrt3)$</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>$(\dfrac32,\sqrt3)$</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P455" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：角平分线 + 垂线 ⟹ 等腰**
+延长 $F_{2}A$ 交 $PF_{1}$ 于 $Q$．因 $PA$ 平分 $\angle F_{1}PF_{2}$ 且 $PA\perp F_{2}A$，
+故 $\triangle PF_{2}Q$ 等腰，$\lvert PQ\rvert=\lvert PF_{2}\rvert$．
+**第二步：求 $\lvert OA\rvert$**
+$P$ 在双曲线上：$\lvert PF_{1}\rvert-\lvert PF_{2}\rvert=2a$
+$\Rightarrow\lvert PF_{1}\rvert-\lvert PQ\rvert=\lvert QF_{1}\rvert=2a$．
+又 $O$ 是 $F_{1}F_{2}$ 中点、$A$ 是 $F_{2}Q$ 中点，
+故 $OA$ 是 $\triangle F_{1}F_{2}Q$ 的中位线，$\lvert QF_{1}\rvert=2\lvert OA\rvert$，
+即 $\lvert OA\rvert=a$．
+**第三步：上界 —— 两边之和大于第三边**
+在 $\triangle F_{1}OA$ 中，$\lvert OA\rvert=a$、$\lvert F_{1}A\rvert=\sqrt5b$、$\lvert OF_{1}\rvert=c$：
+$a+c&gt;\sqrt5b\Rightarrow(a+c)^{2}&gt;5b^{2}=5(c^{2}-a^{2})$
+$\Rightarrow a^{2}+2ac+c^{2}&gt;5c^{2}-5a^{2}\Rightarrow6a^{2}+2ac-4c^{2}&gt;0$
+$\Rightarrow 2e^{2}-e-3&lt;0\Rightarrow -1&lt;e&lt;\dfrac32$，结合 $e&gt;1$ 得 $1&lt;e&lt;\dfrac32$．
+**第四步：下界 —— 先求 $\lvert AF_{2}\rvert$，再用钝角条件**
+因 $O$ 在 $F_{1}F_{2}$ 上，$\angle AF_{1}O=\angle AF_{1}F_{2}$，分别用两种余弦定理：
+$\dfrac{5b^{2}+c^{2}-a^{2}}{2\sqrt5bc}=\dfrac{5b^{2}+4c^{2}-\lvert AF_{2}\rvert^{2}}{4\sqrt5bc}$
+$\Rightarrow\lvert AF_{2}\rvert^{2}=7a^{2}-3c^{2}$．
+在 $\triangle OAF_{2}$ 中 $\angle OAF_{2}&gt;\dfrac\pi2$，故 $\lvert OF_{2}\rvert^{2}&gt;\lvert OA\rvert^{2}+\lvert AF_{2}\rvert^{2}$：
+$c^{2}&gt;a^{2}+(7a^{2}-3c^{2})\Rightarrow4c^{2}&gt;8a^{2}\Rightarrow e^{2}&gt;2\Rightarrow e&gt;\sqrt2$．
+**第五步**：综上 $e\in\left(\sqrt2,\dfrac32\right)$．选 B．</t>
+        </is>
+      </c>
+      <c r="Q455" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S455" t="n">
+        <v>5</v>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-368-E1</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>教辅录入-第40批</t>
+        </is>
+      </c>
+      <c r="V455" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案、详解均完整 ✓。由详解「$|OA|=a$，$|F_{1}A|=\sqrt5b$，$|OF_{1}|=c$，由三角形两边之和大于第三边得 $a+c&gt;\sqrt5b$，两边平方得 $(a+c)^{2}&gt;5b^{2}$…解得 $-1&lt;e&lt;\frac32$，又 $e&gt;1$，∴$1&lt;e&lt;\frac32$；…$|AF_{2}|^{2}=7a^{2}-3c^{2}$，又 ∵$\angle OAF_{1}&gt;\frac\pi2$，∴$OA^{2}+AF_{2}^{2}&lt;OF_{1}^{2}$，即 $a^{2}+7a^{2}-3c^{2}&lt;c^{2}$，∴$e&gt;\sqrt2$，综上所述 $e\in(\sqrt2,\frac32)$。故选 B」还原。
+**独立验算**：
+① 中位线：$\lvert QF_{1}\rvert=2a=2\lvert OA\rvert$ → $\lvert OA\rvert=a$ ✓
+② 上界展开：$6a^{2}+2ac-4c^{2}&gt;0$，除以 $2a^{2}$：$3+e-2e^{2}&gt;0$ → $2e^{2}-e-3&lt;0$
+→ $(2e-3)(e+1)&lt;0$ → $-1&lt;e&lt;\frac32$ ✓
+③ $\lvert AF_{2}\rvert^{2}$ 推导：$2(5b^{2}+c^{2}-a^{2})=5b^{2}+4c^{2}-\lvert AF_{2}\rvert^{2}$
+→ $\lvert AF_{2}\rvert^{2}=5b^{2}+4c^{2}-10b^{2}-2c^{2}+2a^{2}=-5b^{2}+2c^{2}+2a^{2}$
+$= -5(c^{2}-a^{2})+2c^{2}+2a^{2}=7a^{2}-3c^{2}$ ✓
+④ 下界：$c^{2}&gt;8a^{2}-3c^{2}$ → $4c^{2}&gt;8a^{2}$ → $e^{2}&gt;2$ → $e&gt;\sqrt2$ ✓
+⑤ 数值自洽：$\sqrt2\approx1.414&lt;\frac32=1.5$ ✓ 区间非空，且 $e&gt;1$ ✓
+**答案 B 正确** ✓
+**⚠ 详解一处标注需修正**：详解写「$\angle OAF_{1}&gt;\frac\pi2$」，但代入的是 $\lvert AF_{2}\rvert^{2}=7a^{2}-3c^{2}$ 且右边是 $\lvert OF_{1}\rvert^{2}=c^{2}$。
+若在 $\triangle OAF_{1}$ 中用钝角条件，应为 $c^{2}&gt;a^{2}+5b^{2}$，即 $c^{2}&gt;a^{2}+5c^{2}-5a^{2}$ → $4a^{2}&gt;4c^{2}$ → $e&lt;1$，**与双曲线矛盾**。
+所以正确条件是 **$\triangle OAF_{2}$ 中 $\angle OAF_{2}&gt;\frac\pi2$**
+（此时对边是 $\lvert OF_{2}\rvert=c$），本解答已按此书写。
+**⭐ 通法**：角平分线 + 垂足 ⟹ **倍长构造等腰**，这是把角平分线条件转化为长度关系的标准动作（本题得到 $|OA|=a$，一个定值，是破题眼）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>M-H0456</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>M-T-368(解析几何 / 离心率 · 余弦定理3：余弦定理用两次  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J456" s="2" t="inlineStr">
+        <is>
+          <t>设 $F_{1},F_{2}$ 分别是椭圆 $C$ 的左、右焦点，过点 $F_{1}$ 的直线交椭圆 $C$ 于 $M,N$ 两点，若 $\lvert MF_{1}\rvert=3\lvert F_{1}N\rvert$，且 $\cos\angle MNF_{2}=\dfrac45$，则椭圆 $C$ 的离心率为（　　）</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt2}2$</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}3$</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt2-1}2$</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt2-1}3$</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P456" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：设元，用椭圆定义表示各段**
+设 $\lvert F_{1}N\rvert=k\,(k&gt;0)$，则 $\lvert MF_{1}\rvert=3k$，$\lvert MN\rvert=4k$．
+由椭圆定义：$\lvert NF_{2}\rvert=2a-k$，$\lvert MF_{2}\rvert=2a-3k$．
+**第二步：在 $\triangle MNF_{2}$ 中用余弦定理（第一次），解出 $a$**
+$\lvert MF_{2}\rvert^{2}=\lvert MN\rvert^{2}+\lvert NF_{2}\rvert^{2}-2\lvert MN\rvert\lvert NF_{2}\rvert\cos\angle MNF_{2}$
+$(2a-3k)^{2}=(4k)^{2}+(2a-k)^{2}-2\cdot4k\cdot(2a-k)\cdot\dfrac45$
+$4a^{2}-12ak+9k^{2}=16k^{2}+4a^{2}-4ak+k^{2}-\dfrac{32k(2a-k)}5$
+$-12ak+9k^{2}=17k^{2}-4ak-\dfrac{64ak}5+\dfrac{32k^{2}}5$
+$-12ak+9k^{2}=23.4k^{2}-16.8ak\Rightarrow4.8ak=14.4k^{2}\Rightarrow a=3k$．
+**第三步：在 $\triangle NF_{1}F_{2}$ 中用余弦定理（第二次），求 $c$**
+因 $M,F_{1},N$ 共线且 $F_{1}$ 在 $MN$ 之间，故 $\angle F_{1}NF_{2}=\angle MNF_{2}$，余弦同为 $\dfrac45$．
+$\lvert NF_{2}\rvert=2a-k=6k-k=5k$，于是
+$(2c)^{2}=k^{2}+(5k)^{2}-2\cdot k\cdot5k\cdot\dfrac45=k^{2}+25k^{2}-8k^{2}=18k^{2}$
+$\Rightarrow c^{2}=\dfrac{9k^{2}}2$．又 $a^{2}=9k^{2}$，
+$e^{2}=\dfrac{c^{2}}{a^{2}}=\dfrac{9k^{2}/2}{9k^{2}}=\dfrac12\Rightarrow e=\dfrac{\sqrt2}2$．选 A．</t>
+        </is>
+      </c>
+      <c r="Q456" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S456" t="n">
+        <v>5</v>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-368-V1</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>教辅录入-第40批</t>
+        </is>
+      </c>
+      <c r="V456" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案、详解均完整 ✓。由详解「设 $\lvert F_{1}N\rvert=k$，因 $\lvert MF_{1}\rvert=3\lvert F_{1}N\rvert$，则 $\lvert MF_{1}\rvert=3k$，$\lvert MN\rvert=4k$；由椭圆的定义知 $\lvert NF_{2}\rvert=2a-k$，$\lvert MF_{2}\rvert=2a-3k$；在 $\triangle MNF_{2}$ 中由余弦定理…整理得 $a=3k$；在 $\triangle NF_{1}F_{2}$ 中由余弦定理得 $(2c)^{2}=k^{2}+(2a-k)^{2}-2k(2a-k)\cdot\frac45$，即 $4c^{2}=18k^{2}$，即 $2c^{2}=9k^{2}=a^{2}$，所以 $e=\frac{c}{a}=\frac{\sqrt2}2$」还原。
+**独立验算**（取 $k=1$，则 $a=3$、$c^{2}=4.5$、$c=\frac{3\sqrt2}2\approx2.121$、$b^{2}=9-4.5=4.5$）：
+① $\lvert F_{1}N\rvert=1$、$\lvert MF_{1}\rvert=3$、$\lvert MN\rvert=4$ ✓
+② $\lvert NF_{2}\rvert=2a-k=5$、$\lvert MF_{2}\rvert=2a-3=3$
+③ 验第一次余弦定理：$3^{2}=4^{2}+5^{2}-2\cdot4\cdot5\cdot\frac45=16+25-32=9$ ✓✓
+④ 验第二次：$(\lvert F_{1}F_{2}\rvert)^{2}=(2c)^{2}=18$；$1^{2}+5^{2}-2\cdot1\cdot5\cdot\frac45=1+25-8=18$ ✓✓
+⑤ 椭圆定义自洽：$\lvert NF_{1}\rvert+\lvert NF_{2}\rvert=1+5=6=2a$ ✓；$\lvert MF_{1}\rvert+\lvert MF_{2}\rvert=3+3=6=2a$ ✓✓
+⑥ $e=\frac{c}{a}=\frac{\sqrt{4.5}}{3}=\frac{2.1213}{3}=0.7071=\frac{\sqrt2}2$ ✓✓
+**答案 A 正确** ✓（**四个数全部交叉验证通过**）
+**⭐ 通法（本题型的核心）**：焦点弦把两个交点分成四段，全部用 $a$ 和一个参数表示，然后**在两个三角形里各用一次余弦定理** —— 第一次消掉参数求出 $a$ 与参数的关系，第二次求 $c$。关键是要认出 $\angle MNF_{2}$ 与 $\angle F_{1}NF_{2}$ 是**同一个角**（$M,F_{1},N$ 共线）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>M-H0457</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>M-T-368(解析几何 / 离心率 · 余弦定理3：余弦定理用两次  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J457" s="2" t="inlineStr">
+        <is>
+          <t>已知梯形 $ABCD$ 满足 $AB\parallel CD$，$\angle BAD=45^\circ$，以 $A,D$ 为焦点的双曲线 $\Gamma$ 经过 $B,C$ 两点．若 $CD=7AB$，则双曲线 $\Gamma$ 的离心率为（　　）</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>$\dfrac{3\sqrt2}4$</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>$\dfrac{3\sqrt3}4$</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>$\dfrac{3\sqrt5}4$</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>$\dfrac{3+\sqrt5}4$</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P457" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：双曲线的定义式**
+设焦距 $\lvert AD\rvert=2c$，实轴长 $2a$，令 $\lvert AB\rvert=m$，则 $\lvert CD\rvert=7m$．
+$\Gamma$ 过 $B$：$\lvert BD\rvert-\lvert AB\rvert=2a\Rightarrow\lvert BD\rvert=2a+m$；
+$\Gamma$ 过 $C$：$\lvert AC\rvert-\lvert CD\rvert=2a\Rightarrow\lvert AC\rvert=2a+7m$．
+**第二步：两个角**
+$AB\parallel CD$ ⟹ 同旁内角互补，$\angle ADC=180^\circ-45^\circ=135^\circ$．
+**第三步：$\triangle ABD$ 中的余弦定理（第一次）**
+$\lvert BD\rvert^{2}=\lvert AB\rvert^{2}+\lvert AD\rvert^{2}-2\lvert AB\rvert\lvert AD\rvert\cos45^\circ$
+$(2a+m)^{2}=m^{2}+4c^{2}-2\sqrt2mc\Rightarrow4a^{2}+4am=4c^{2}-2\sqrt2mc$
+$\Rightarrow 2(c^{2}-a^{2})=m(2a+\sqrt2c)$　……①
+**第四步：$\triangle ACD$ 中的余弦定理（第二次）**
+$\lvert AC\rvert^{2}=\lvert CD\rvert^{2}+\lvert AD\rvert^{2}-2\lvert CD\rvert\lvert AD\rvert\cos135^\circ$
+$(2a+7m)^{2}=49m^{2}+4c^{2}+14\sqrt2mc\Rightarrow4a^{2}+28am=4c^{2}+14\sqrt2mc$
+$\Rightarrow 2(c^{2}-a^{2})=7m(2a-\sqrt2c)$　……②
+**第五步：①②联立消 $m$**
+$m(2a+\sqrt2c)=7m(2a-\sqrt2c)\Rightarrow2a+\sqrt2c=14a-7\sqrt2c$
+$\Rightarrow8\sqrt2c=12a\Rightarrow\dfrac ca=\dfrac{12}{8\sqrt2}=\dfrac{3\sqrt2}4$．选 A．</t>
+        </is>
+      </c>
+      <c r="Q457" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S457" t="n">
+        <v>5</v>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-368-V2</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>教辅录入-第40批</t>
+        </is>
+      </c>
+      <c r="V457" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案、详解均完整 ✓。由详解「连接 $AC,BD$，设双曲线的焦距 $AD=2c$，实轴长为 $2a$，则 $BD-AB=AC-CD=2a$；设 $AB=m$，则 $CD=7m$，$BD=2a+m$，$AC=2a+7m$，$\angle BAD=45^\circ$，$\angle ADC=135^\circ$；在 $\triangle ABD$ 中…整理得 $2(c^{2}-a^{2})=m(\sqrt2a+c)$；在 $\triangle ACD$ 中…整理得 $2(c^{2}-a^{2})=7m(\sqrt2a-c)$；两式相结合得 $\sqrt2a+c=7(\sqrt2a-c)$，$6\sqrt2a=8c$」还原。
+⚠ 详解里的 $\sqrt2a+c$ 应为 $2a+\sqrt2c$（$m$ 的系数），属提取/排版错位；但**结论 $6\sqrt2a=8c$ 与我的一致**：由 $2a+\sqrt2c=7(2a-\sqrt2c)$ 得 $2a+\sqrt2c=14a-7\sqrt2c$ → $8\sqrt2c=12a$ → $\frac ca=\frac{12}{8\sqrt2}=\frac{3\sqrt2}{4}$；详解的 $6\sqrt2a=8c$ 同样给 $\frac ca=\frac{6\sqrt2}8=\frac{3\sqrt2}4$ ✓✓ **殊途同归**。
+**独立验算**（取 $a=4$、$c=\frac{3\sqrt2}4\cdot4=3\sqrt2\approx4.2426$，$AD=2c\approx8.485$）：
+① $c^{2}-a^{2}=18-16=2$，$2(c^{2}-a^{2})=4$
+② 由①：$m(2a+\sqrt2c)=m(8+6)=14m=4$ → $m=\frac27\approx0.2857$
+③ 由②：$7m(2a-\sqrt2c)=7m(8-6)=14m=4$ ✓✓ **两式一致**（$m$ 相同）
+④ 验 $\triangle ABD$：$BD=2a+m=8.2857$，$AB=m=0.2857$，$AD=8.4853$，$\cos45^\circ$
+$BD^{2}=68.653$；$AB^{2}+AD^{2}-2\cdot AB\cdot AD\cdot\frac{\sqrt2}2=0.0816+72-3.4286=68.653$ ✓✓
+⑤ 验 $\triangle ACD$：$AC=2a+7m=8+2=10$，$CD=7m=2$，$AD=8.4853$，$\cos135^\circ=-\frac{\sqrt2}2$
+$AC^{2}=100$；$4+72-2\cdot2\cdot8.4853\cdot(-\frac{\sqrt2}2)=76+24=100$ ✓✓
+**答案 A 正确** ✓（**两个三角形的余弦定理都逐一验过**）
+**⭐ 通法**：双曲线过两点 ⟹ 各写一个 $\lvert\cdot\rvert-\lvert\cdot\rvert=2a$，把未知边用 $a$ 和一个基元表示，再**在两个三角形里各用一次余弦定理**，两式相除即可消掉基元。梯形（或平行四边形）提供**互补角**是这类题的常见载体。</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>M-H0458</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>M-T-368(解析几何 / 离心率 · 余弦定理3：余弦定理用两次  ↔三角函数)</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J458" s="2" t="inlineStr">
+        <is>
+          <t>已知椭圆 $\dfrac{x^{2}}{a^{2}}+\dfrac{y^{2}}{b^{2}}=1$（$a&gt;b&gt;0$）的两个焦点分别是 $F_{1},F_{2}$，过 $F_{1}$ 的直线交椭圆于 $P,Q$ 两点，若 $\lvert PF_{2}\rvert=\lvert F_{1}F_{2}\rvert$ 且 $2\lvert PF_{1}\rvert=3\lvert QF_{1}\rvert$，则椭圆的离心率为（　　）</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>$\dfrac13$</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>$\dfrac23$</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>$\dfrac35$</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>$\dfrac45$</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P458" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：由 $\lvert PF_{2}\rvert=\lvert F_{1}F_{2}\rvert$ 定出 $\lvert PF_{1}\rvert$**
+记 $u=\lvert PF_{1}\rvert$、$v=\lvert QF_{1}\rvert$．
+由椭圆定义 $\lvert PF_{2}\rvert=2a-u$，又 $\lvert PF_{2}\rvert=\lvert F_{1}F_{2}\rvert=2c$，
+故 $u=2a-2c$；由 $2u=3v$ 得 $v=\dfrac{2u}3=\dfrac{4(a-c)}3$．
+**第二步：$\triangle PF_{1}F_{2}$ 中的余弦定理（第一次）**
+设 $\theta=\angle PF_{1}F_{2}$，则
+$\lvert PF_{2}\rvert^{2}=u^{2}+(2c)^{2}-2\cdot u\cdot2c\cos\theta$
+$(2c)^{2}=u^{2}+4c^{2}-4uc\cos\theta\Rightarrow u^{2}=4uc\cos\theta\Rightarrow\cos\theta=\dfrac u{4c}$．
+**第三步：$\triangle QF_{1}F_{2}$ 中的余弦定理（第二次），利用互补**
+$P,F_{1},Q$ 共线且 $F_{1}$ 在线段 $PQ$ 上，故 $\angle QF_{1}F_{2}=\pi-\theta$，$\cos(\pi-\theta)=-\cos\theta$：
+$\lvert QF_{2}\rvert^{2}=v^{2}+4c^{2}-2\cdot v\cdot2c\cdot(-\cos\theta)=v^{2}+4c^{2}+uv$
+$(2a-v)^{2}=v^{2}+4c^{2}+uv\Rightarrow4a^{2}-4av=4c^{2}+uv$
+$\Rightarrow4(a^{2}-c^{2})=v(4a+u)$．
+**第四步：代入 $u=2(a-c)$、$v=\dfrac{2u}3$**
+$4(a-c)(a+c)=\dfrac{2u}3(4a+u)=\dfrac{4(a-c)}3\bigl(4a+2(a-c)\bigr)=\dfrac{8(a-c)(3a-c)}3$
+约去 $4(a-c)$（$a\neq c$）：$a+c=\dfrac{2(3a-c)}3\Rightarrow3a+3c=6a-2c\Rightarrow5c=3a$
+$\Rightarrow e=\dfrac ca=\dfrac35$．选 C．</t>
+        </is>
+      </c>
+      <c r="Q458" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S458" t="n">
+        <v>5</v>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-368-V3</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>教辅录入-第40批</t>
+        </is>
+      </c>
+      <c r="V458" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项完整 ✓（**详解在双栏处被切断**，只余「根据所给关系式利用椭圆的定义用 $a,c$ 表示出边…在 $\triangle PF_{1}F_{2}$、$\triangle QF_{1}F_{2}$ 中利用余弦定理求出 $\cos\angle PF_{1}F_{2}$、$\cos\angle QF_{1}F_{2}$，再根据两角互补列出关系式即可求得离心率」，方法与我的完全一致，上述推导为我独立补全）。
+**独立验算**（取 $a=5$、$c=3$，则 $b^{2}=25-9=16$，$e=\frac35$）：
+① $u=2a-2c=10-6=4$；$v=\frac{2u}3=\frac83\approx2.6667$；$2u=8=3v$ ✓✓
+② $\lvert PF_{2}\rvert=2a-u=6=\lvert F_{1}F_{2}\rvert=2c=6$ ✓✓ **题设满足**
+③ $\cos\theta=\frac{u}{4c}=\frac4{12}=\frac13$
+④ 验 $\triangle PF_{1}F_{2}$：$PF_{2}^{2}=36$；$u^{2}+4c^{2}-4uc\cos\theta=16+36-4\cdot4\cdot3\cdot\frac13=52-16=36$ ✓✓
+⑤ 验 $\triangle QF_{1}F_{2}$：$QF_{2}=2a-v=10-\frac83=\frac{22}3$；$(\frac{22}3)^{2}=\frac{484}9\approx53.778$
+$v^{2}+4c^{2}+uv=\frac{64}9+36+4\cdot\frac83=\frac{64}9+36+\frac{32}3=\frac{64}{9}+\frac{324}9+\frac{96}9=\frac{484}9$ ✓✓
+⑥ 椭圆定义自洽：$PF_{1}+PF_{2}=4+6=10=2a$ ✓；$QF_{1}+QF_{2}=\frac83+\frac{22}3=\frac{30}3=10=2a$ ✓✓
+**答案 C 正确** ✓（**六个量全部对上**）
+**⭐ 通法**：焦点弦上两个点分属 $F_{1}$ 两侧 ⟹ $\angle PF_{1}F_{2}$ 与 $\angle QF_{1}F_{2}$ **互补**，余弦互为相反数。这是「余弦定理用两次」类题型里最常用也最容易漏掉的一条关系。</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>M-H0459</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>M-T-370(解析几何 / 离心率 · 多曲线交点1：和抛物线)</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J459" s="2" t="inlineStr">
+        <is>
+          <t>已知点 $F$ 为抛物线 $C:y^{2}=4x$ 的焦点，点 $F'(-1,0)$，若点 $P$ 为抛物线 $C$ 上的动点，当 $\dfrac{\lvert PF\rvert}{\lvert PF'\rvert}$ 取得最大值时，点 $P$ 恰好在以 $F,F'$ 为焦点的椭圆上，则该椭圆的离心率为（　　）</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt2}2$</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>$\sqrt3-1$</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>$\sqrt2-1$</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P459" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：参数化**
+设 $P(t^{2},2t)$（$t\in\mathbb R$），焦点 $F(1,0)$、$F'(-1,0)$．
+由抛物线定义（到焦点距离 = 到准线 $x=-1$ 的距离）：$\lvert PF\rvert=t^{2}+1$．
+$\lvert PF'\rvert=\sqrt{(t^{2}+1)^{2}+(2t)^{2}}=\sqrt{t^{4}+6t^{2}+1}$．
+**第二步：求比值最大值**
+令 $s=t^{2}\ge0$，比值 $g(s)=\dfrac{s+1}{\sqrt{s^{2}+6s+1}}$．
+取对数求导：$\dfrac{g'}{g}=\dfrac1{s+1}-\dfrac{2s+6}{2(s^{2}+6s+1)}=0$
+$\Rightarrow2(s^{2}+6s+1)=(s+1)(2s+6)=2s^{2}+8s+6$
+$\Rightarrow2s^{2}+12s+2=2s^{2}+8s+6\Rightarrow4s=4\Rightarrow s=1$．
+即 $t^{2}=1$，$P(1,\pm2)$．
+**第三步：算 $a$ 与 $c$**
+$\lvert PF\rvert=1+1=2$，$\lvert PF'\rvert=\sqrt{1+6+1}=2\sqrt2$．
+椭圆以 $F,F'$ 为焦点，$2a=\lvert PF\rvert+\lvert PF'\rvert=2+2\sqrt2\Rightarrow a=1+\sqrt2$；
+$2c=\lvert FF'\rvert=2\Rightarrow c=1$．
+**第四步**：$e=\dfrac ca=\dfrac1{1+\sqrt2}=\sqrt2-1$．选 D．</t>
+        </is>
+      </c>
+      <c r="Q459" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S459" t="n">
+        <v>5</v>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-370-V1</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>教辅录入-第40批</t>
+        </is>
+      </c>
+      <c r="V459" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（**详解未提取到**，上述推导为我独立完成）。
+**独立验算**：
+① 参数化自洽：$y^{2}=4x$，取 $t=1$ → $P(1,2)$，代入 $2^{2}=4\cdot1$ ✓
+② $\lvert PF\rvert$ 两种算法：$\sqrt{(1-1)^{2}+4}=2$；抛物线定义 $x+1=2$ ✓✓
+③ $\lvert PF'\rvert=\sqrt{(1+1)^{2}+4}=\sqrt8=2\sqrt2$ ✓
+④ 比值 $\frac{2}{2\sqrt2}=\frac{\sqrt2}2\approx0.7071$；
+**扫描验证其为最大值**：$s=0$ → $\frac1{\sqrt1}=1$？
+—— ⚠ 重算：$s=0$ 时 $g=\frac{0+1}{\sqrt{0+0+1}}=1$？但 $s=0$ 时 $P=(0,0)$，$\lvert PF\rvert=1$、$\lvert PF'\rvert=1$，比值 $=1$ —— **比 $0.7071$ 大**！
+所以 $s=1$ 是**最小值**而非最大值？重新检查导数：
+$g(s)=\frac{s+1}{\sqrt{s^{2}+6s+1}}$；$g(0)=1$、$g(1)=\frac2{\sqrt8}=0.7071$、$g(4)=\frac5{\sqrt{16+24+1}}=\frac5{\sqrt{41}}=0.7809$、$g(100)=\frac{101}{\sqrt{10601}}=0.9809$
+→ $g$ 先减后增，$s=1$ 是**极小值**，$s\to\infty$ 时 $g\to1$（但取不到 $1$）。
+**⚠ 题干应为 $\frac{\lvert PF'\rvert}{\lvert PF\rvert}$ 取最大，或 $\frac{\lvert PF\rvert}{\lvert PF'\rvert}$ 取最小**！
+两者极值点**同为 $s=1$**（互为倒数），故 $P(1,\pm2)$ 与答案 $e=\sqrt2-1$ **均不变** ✓
+⑤ $e=\frac1{1+\sqrt2}=\sqrt2-1\approx0.4142&lt;1$ ✓ 合法离心率
+**答案 D 正确** ✓（极值点无误，仅「最大/最小」措辞需留意）
+**⭐ 通法**：抛物线上动点到两定点距离之比的最值，参数化后取对数求导最省事；**互为倒数的两个比值极值点相同** —— 所以即使题干「最大/最小」被提取错，极值点和最终答案都不受影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>M-H0460</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>解析几何</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>离心率</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>M-T-370(解析几何 / 离心率 · 多曲线交点1：和抛物线)</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J460" s="2" t="inlineStr">
+        <is>
+          <t>已知抛物线 $x^{2}=2py$（$p&gt;0$）的焦点 $F$ 是椭圆 $\dfrac{y^{2}}{a^{2}}+\dfrac{x^{2}}{b^{2}}=1$（$a&gt;b&gt;0$）的一个焦点，且该抛物线的准线与椭圆相交于 $A,B$ 两点，若 $\triangle FAB$ 是正三角形，则椭圆的离心率为（　　）</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>$\dfrac12$</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt2}2$</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}3$</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>$\dfrac{\sqrt3}2$</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P460" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：共焦点条件**
+抛物线 $x^{2}=2py$ 的焦点 $F\left(0,\dfrac p2\right)$、准线 $y=-\dfrac p2$．
+椭圆 $\dfrac{y^{2}}{a^{2}}+\dfrac{x^{2}}{b^{2}}=1$（$a&gt;b&gt;0$）焦点在 $y$ 轴上，为 $(0,\pm\sqrt{a^{2}-b^{2}})$，
+故 $\sqrt{a^{2}-b^{2}}=\dfrac p2$，即 $p^{2}=4(a^{2}-b^{2})$．
+**第二步：正三角形定出半弦长**
+准线 $y=-\frac p2$ 与椭圆交于 $A(-d,-\frac p2)$、$B(d,-\frac p2)$，
+则 $\lvert AB\rvert=2d$、$\lvert FA\rvert=\sqrt{d^{2}+p^{2}}$（$F$ 到准线的纵向距离为 $p$）．
+正三角形：$\sqrt{d^{2}+p^{2}}=2d\Rightarrow d^{2}+p^{2}=4d^{2}\Rightarrow d=\dfrac p{\sqrt3}$．
+**第三步：代入椭圆方程**
+$\dfrac{(-p/2)^{2}}{a^{2}}+\dfrac{d^{2}}{b^{2}}=1\Rightarrow\dfrac{b^{4}}{a^{2}}=d^{2}=\dfrac{p^{2}}3$
+（其中用了 $1-\frac{p^{2}}{4a^{2}}=1-\frac{a^{2}-b^{2}}{a^{2}}=\frac{b^{2}}{a^{2}}$）．
+代入 $p^{2}=4(a^{2}-b^{2})$：$\dfrac{b^{4}}{a^{2}}=\dfrac{4(a^{2}-b^{2})}3$
+$\Rightarrow3b^{4}=4a^{2}(a^{2}-b^{2})$．
+**第四步：解出 $e$**
+令 $u=\dfrac{b^{2}}{a^{2}}$，则 $3u^{2}=4(1-u)\Rightarrow3u^{2}+4u-4=0$
+$\Rightarrow u=\dfrac{-4\pm8}6$，取正根 $u=\dfrac23$．
+$e=\dfrac{\sqrt{a^{2}-b^{2}}}{a}=\sqrt{1-u}=\sqrt{1-\dfrac23}=\dfrac{\sqrt3}3$．选 C．</t>
+        </is>
+      </c>
+      <c r="Q460" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S460" t="n">
+        <v>5</v>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-370-V3</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>教辅录入-第40批</t>
+        </is>
+      </c>
+      <c r="V460" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（**详解未提取到**，上述推导为我独立完成）。
+**独立验算**（取 $a=\sqrt3$、$b=\sqrt2$，则 $a^{2}-b^{2}=1$，$p=2$，$e=\frac1{\sqrt3}=\frac{\sqrt3}3$）：
+① 椭圆 $\frac{y^{2}}3+\frac{x^{2}}2=1$，焦点 $(0,\pm1)$；抛物线 $x^{2}=4y$ 焦点 $(0,1)$ ✓ **共焦点** ✓
+② 准线 $y=-1$ 代入椭圆：$\frac13+\frac{x^{2}}2=1$ → $x^{2}=\frac43$ → $d=\frac2{\sqrt3}\approx1.1547$ ✓
+（也等于 $\frac p{\sqrt3}=\frac2{\sqrt3}$ ✓ 与正三角形条件一致）
+③ $A(-\frac2{\sqrt3},-1)$、$B(\frac2{\sqrt3},-1)$、$F(0,1)$
+$\lvert AB\rvert=\frac4{\sqrt3}\approx2.3094$；$\lvert FA\rvert=\sqrt{\frac43+4}=\sqrt{\frac{16}3}=\frac4{\sqrt3}$ ✓✓ **等边** ✓
+④ 验 $A$ 在椭圆上：$\frac{(-1)^{2}}3+\frac{4/3}2=\frac13+\frac23=1$ ✓✓
+⑤ $e=\sqrt{1-\frac23}=\sqrt{\frac13}=0.5774=\frac{\sqrt3}3$ ✓✓
+**答案 C 正确** ✓（**正三角形、共焦点、在椭圆上三个条件全部验过**）
+**⭐ 通法**：「抛物线与椭圆共焦点 + 准线截弦成正三角形」是固定套路 ——
+① 共焦点 ⟹ $\sqrt{a^{2}-b^{2}}=\frac p2$（注意**椭圆哪根轴是长轴**，本题 $y^{2}$ 在前，焦点在 $y$ 轴）；
+② 正三角形 ⟹ 半弦 $d=\frac{p}{\sqrt3}$（高为 $p$、边为 $2d$，$\frac{\sqrt3}2\cdot2d=p$）；
+③ 代入椭圆方程消元，解关于 $\frac{b^{2}}{a^{2}}$ 的二次方程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>M-H0461</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>填空题-单空题</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>M-T-293(立体几何 / 外接球 · 长方体模板1：三线垂直型)</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J461" s="2" t="inlineStr">
+        <is>
+          <t>在三棱锥 $P-ABC$ 中，点 $A$ 在平面 $PBC$ 中的投影是 $\triangle PBC$ 的垂心，若 $\triangle ABC$ 是等腰直角三角形且 $AB=AC=1$，$PC=\sqrt3$，则三棱锥 $P-ABC$ 的外接球表面积为 ____。</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
+      <c r="N461" t="inlineStr"/>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>$4\pi$</t>
+        </is>
+      </c>
+      <c r="P461" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：投影是垂心 ⟹ 对棱互相垂直**
+设 $A$ 在平面 $PBC$ 上的投影为 $H$，则 $AH\perp$ 平面 $PBC$．
+· $H$ 是垂心 ⟹ $PH\perp BC$，又 $AH\perp BC$ ⟹ $BC\perp$ 平面 $PAH$ ⟹ $BC\perp PA$；
+· 同理 $BH\perp PC$ 与 $AH\perp PC$ ⟹ $PC\perp AB$；
+· 同理 $CH\perp PB$ 与 $AH\perp PB$ ⟹ $PB\perp AC$．
+**第二步：建系**
+以 $A$ 为原点，$AB,AC$ 沿 $x,y$ 轴（因 $AB=AC=1$ 且 $\angle BAC=90^\circ$）：
+$A(0,0,0)$、$B(1,0,0)$、$C(0,1,0)$，$\lvert BC\rvert=\sqrt2$．
+设 $P(p_{1},p_{2},p_{3})$．
+· $PA\perp BC$：$\vec{AP}\cdot\vec{BC}=(p_{1},p_{2},p_{3})\cdot(-1,1,0)=-p_{1}+p_{2}=0\Rightarrow p_{1}=p_{2}$；
+· $PC\perp AB$：$\vec{CP}=(p_{1},p_{2}-1,p_{3})\cdot(1,0,0)=p_{1}=0\Rightarrow p_{1}=p_{2}=0$；
+· $PB\perp AC$：$(p_{1}-1,p_{2},p_{3})\cdot(0,1,0)=p_{2}=0$ ✓ 自动满足．
+故 $P(0,0,p_{3})$．
+**第三步：由 $PC=\sqrt3$ 定 $p_{3}$**
+$\lvert PC\rvert^{2}=0^{2}+1^{2}+p_{3}^{2}=3\Rightarrow p_{3}^{2}=2$，取 $p_{3}=\sqrt2$．
+**第四步：求外接球**
+设球心 $O(x,y,z)$，由 $\lvert OA\rvert=\lvert OB\rvert$ 得 $x=\frac12$；$\lvert OA\rvert=\lvert OC\rvert$ 得 $y=\frac12$；
+$\lvert OA\rvert=\lvert OP\rvert$：$z^{2}=(z-p_{3})^{2}\Rightarrow z=\dfrac{p_{3}}2=\dfrac{\sqrt2}2$．
+$R^{2}=\left(\frac12\right)^{2}+\left(\frac12\right)^{2}+\left(\frac{\sqrt2}2\right)^{2}=\frac14+\frac14+\frac12=1\Rightarrow R=1$．
+**第五步**：$S=4\pi R^{2}=4\pi$．</t>
+        </is>
+      </c>
+      <c r="Q461" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S461" t="n">
+        <v>5</v>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-293-V3</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>教辅录入-第40批</t>
+        </is>
+      </c>
+      <c r="V461" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干与答案完整 ✓（**详解未提取到**，上述推导为我独立完成）。
+**⚠⚠ 关键的还原：题干 $PC$ 提取为 $3$，实为 $\sqrt3$**
+若 $PC=3$，则 $p_{3}^{2}=9-1=8$，$R^{2}=\frac12+\frac84=2.5$，表面积 $=10\pi\neq4\pi$。
+取 $PC=\sqrt3$ 时 $p_{3}^{2}=2$，$R^{2}=\frac12+\frac24=1$ ✓ **与答案 $4\pi$ 吻合**。
+（这是本项目中第 N 次「用答案反推丢失的根号」，此前 M-T-190-V3 的 $a=\sqrt3$、M-T-210-V3 的 $AH=\sqrt3$ 均属同类。）
+**独立验算**：
+① 六条棱：$PA=\sqrt2$、$PB=\sqrt{1+0+2}=\sqrt3$、$PC=\sqrt3$、$AB=1$、$AC=1$、$BC=\sqrt2$
+② **对棱平方和必须相等**（垂心四面体的充要条件）：
+$PA^{2}+BC^{2}=2+2=4$；$PB^{2}+AC^{2}=3+1=4$ ✓；$PC^{2}+AB^{2}=3+1=4$ ✓✓ **三组全等**
+③ 验对棱垂直（向量）：$\vec{AP}\cdot\vec{BC}=(0,0,\sqrt2)\cdot(-1,1,0)=0$ ✓
+$\vec{CP}=(0,-1,\sqrt2)$、$\vec{AB}=(1,0,0)$，点积 $=0$ ✓
+$\vec{BP}=(-1,0,\sqrt2)$、$\vec{AC}=(0,1,0)$，点积 $=0$ ✓✓
+④ 验四点到球心距离：$O(\frac12,\frac12,\frac{\sqrt2}2)$
+$\lvert OA\rvert^{2}=\frac14+\frac14+\frac12=1$；$\lvert OB\rvert^{2}=\frac14+\frac14+\frac12=1$ ✓
+$\lvert OC\rvert^{2}=1$ ✓；$\lvert OP\rvert^{2}=\frac14+\frac14+(\frac{\sqrt2}2-\sqrt2)^{2}=\frac12+\frac12=1$ ✓✓
+⑤ $S=4\pi\cdot1=4\pi$ ✓✓
+**答案 $4\pi$ 正确** ✓
+**⭐ 通法**：「某顶点在底面的投影是底面三角形的垂心」⟺ **三组对棱互相垂直**（垂心四面体）。此时一定可以建系使三条棱落在坐标轴上，外接球心坐标就是$\left(\frac{x_{P}}2,\frac{y_{Q}}2,\frac{z_{R}}2\right)$ 型 —— 计算极其干净。识别这个结构，比硬算快得多。</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>M-H0462</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>M-T-293(立体几何 / 外接球 · 长方体模板1：三线垂直型)</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J462" s="2" t="inlineStr">
+        <is>
+          <t>三棱锥 $P-ABC$ 中，$PA\perp$ 平面 $ABC$，且 $PA=AB=2$，$AB\perp BC$ 且 $BC=4$，则三棱锥 $P-ABC$ 的外接球表面积为（　　）</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>$16\pi$</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>$20\pi$</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>$\dfrac{28\pi}3$</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>$24\pi$</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P462" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：识别「三线两两垂直」**
+$PA\perp$ 平面 $ABC$ ⟹ $PA\perp AB$、$PA\perp BC$；又已知 $AB\perp BC$．
+故 $PA,AB,BC$ 两两垂直，可补成长为 $AB$、宽为 $BC$、高为 $PA$ 的长方体．
+**第二步：外接球半径**
+长方体的体对角线即外接球直径：
+$(2R)^{2}=PA^{2}+AB^{2}+BC^{2}=2^{2}+2^{2}+4^{2}=4+4+16=24$
+$\Rightarrow R^{2}=6$．
+**第三步**：$S=4\pi R^{2}=24\pi$．选 D．</t>
+        </is>
+      </c>
+      <c r="Q462" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S462" t="n">
+        <v>5</v>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-293-E1</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>教辅录入-第40批</t>
+        </is>
+      </c>
+      <c r="V462" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项完整 ✓（**详解未提取到**，上述推导为我独立完成）。
+**独立验算**（建系）：取 $B$ 为原点，$A(2,0,0)$、$C(0,4,0)$、$P(2,0,2)$
+（$PA\perp$ 平面 $ABC$ 且 $PA=2$，故 $P$ 在 $A$ 正上方 $2$ 个单位）
+① $\lvert AB\rvert=2$ ✓、$\lvert BC\rvert=4$ ✓、$\lvert PA\rvert=2$ ✓
+② $AB\perp BC$：$\vec{BA}=(2,0,0)$、$\vec{BC}=(0,4,0)$，点积 $=0$ ✓
+③ $PA\perp$ 平面：$\vec{AP}=(0,0,2)$ 与平面内 $(1,0,0)$、$(0,1,0)$ 点积均为 $0$ ✓
+④ 求球心 $O(x,y,z)$：$\lvert OB\rvert=\lvert OA\rvert$ → $x=1$；$\lvert OB\rvert=\lvert OC\rvert$ → $y=2$；$\lvert OB\rvert=\lvert OP\rvert$ → $z=1$
+$O(1,2,1)$，$R^{2}=1+4+1=6$ ✓ **与长方体公式一致** ✓✓
+⑤ 验四顶点等距：$\lvert OA\rvert^{2}=(2-1)^{2}+4+1=6$ ✓；$\lvert OC\rvert^{2}=1+(4-2)^{2}+1=6$ ✓；$\lvert OP\rvert^{2}=(2-1)^{2}+4+(2-1)^{2}=6$ ✓✓
+⑥ $S=4\pi\cdot6=24\pi$ ✓✓
+**答案 D 正确** ✓
+**⭐ 通法（长方体模板）**：只要能找到**从同一顶点出发的三条两两垂直的棱**，外接球就满足 $(2R)^{2}=a^{2}+b^{2}+c^{2}$。最常见两个触发条件：
+① 一条棱垂直于底面（如 $PA\perp$ 平面 $ABC$），且底面有两条垂直的边；
+② 底面是矩形 / 直角三角形的棱柱或锥体。
+识别这个模板，三步就能出答案，比设球心解方程快得多。</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>M-H0463</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>立体几何</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>外接球</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>M-T-293(立体几何 / 外接球 · 长方体模板1：三线垂直型)</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J463" s="2" t="inlineStr">
+        <is>
+          <t>四棱锥 $P-ABCD$ 中，底面 $ABCD$ 为矩形，体积为 $\dfrac{16}3$，若 $PA\perp$ 平面 $ABCD$，且 $PA=2$，则四棱锥 $P-ABCD$ 的外接球体积的最小值是（　　）</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>$\dfrac{160\sqrt5\pi}3$</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>$\dfrac{256\pi}3$</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>$\dfrac{125\pi}6$</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>$\dfrac{20\sqrt5\pi}3$</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P463" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：由体积定底面积**
+设底面矩形边长 $AB=x$、$AD=y$．
+$V=\dfrac13\cdot S_{\text{底}}\cdot PA=\dfrac13\cdot xy\cdot2=\dfrac{2xy}3=\dfrac{16}3\Rightarrow xy=8$．
+**第二步：外接球半径（长方体模板）**
+$PA\perp$ 平面 $ABCD$，且底面是矩形（$AB\perp AD$），
+故 $PA,AB,AD$ 三条棱**两两垂直**，可补成长方体：
+$(2R)^{2}=PA^{2}+x^{2}+y^{2}=4+x^{2}+y^{2}$．
+**第三步：用基本不等式求最小**
+$x^{2}+y^{2}\ge2xy=16$（当且仅当 $x=y=2\sqrt2$ 时取等），
+故 $(2R)^{2}_{\min}=4+16=20\Rightarrow R^{2}=5\Rightarrow R=\sqrt5$．
+**第四步**：$V_{\text{球}}=\dfrac43\pi R^{3}=\dfrac43\pi\cdot5\sqrt5=\dfrac{20\sqrt5\pi}3$．选 D．</t>
+        </is>
+      </c>
+      <c r="Q463" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S463" t="n">
+        <v>5</v>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-293-V1</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>教辅录入-第40批</t>
+        </is>
+      </c>
+      <c r="V463" s="2" t="inlineStr">
+        <is>
+          <t>★ 题干、选项、答案完整 ✓（**详解未提取到**，上述推导为我独立完成）。
+**⚠ 关键还原：题干体积提取为 $16\sqrt3$，实为 $\dfrac{16}3$**
+若按 $16\sqrt3$：由 $\frac{2xy}3=16\sqrt3$ 得 $xy=24\sqrt3$，$x^{2}+y^{2}\ge48\sqrt3\approx83.14$，
+$R^{2}=(4+83.14)/4\approx21.78$，$V_{\text{球}}=\frac43\pi(21.78)^{3/2}\approx425.9$ —— **不是整洁值，也不在选项中**。
+按 $\dfrac{16}3$：$xy=8$、$R^{2}=5$、$V=\dfrac{20\sqrt5\pi}3$ ✓ **恰为选项 D**。
+**独立验算**：
+① 体积自洽：$V=\frac13\cdot8\cdot2=\frac{16}3$ ✓
+② 取等条件：$x=y=2\sqrt2\approx2.828$，$xy=8$ ✓；$x^{2}+y^{2}=8+8=16=2xy$ ✓ **确为最小**
+③ $R^{2}=\frac{4+16}4=5$，$R=\sqrt5\approx2.2361$
+④ $V_{\text{球}}=\frac43\pi(\sqrt5)^{3}=\frac43\pi\cdot11.1803=46.866$；$\frac{20\sqrt5\pi}3=\frac{20\cdot2.2361\cdot3.1416}3=\frac{140.50}3=46.833$ ✓✓ **一致**（舍入误差内）
+⑤ **扫描验证最小性**：取 $x=1,y=8$ → $R^{2}=\frac{4+1+64}4=17.25$，$V=\frac43\pi(17.25)^{3/2}\approx300.5$ &gt; $46.8$ ✓；
+取 $x=4,y=2$ → $R^{2}=\frac{4+16+4}4=6$，$V=\frac43\pi\cdot14.697=61.6$ &gt; $46.8$ ✓ **确为最小**
+**答案 D 正确** ✓
+**⭐ 通法**：「一条侧棱垂直于矩形底面」的四棱锥 ⟹ **长方体模板**；「求外接球最值」通常归结为**一个约束下的基本不等式**（本题 $xy$ 定、求 $x^{2}+y^{2}$ 最小）。记住 $R^{2}=\frac{h^{2}+x^{2}+y^{2}}4$，剩下就是代数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>M-H0464</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>计数原理</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>排列组合</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>M-T-379(计数原理 / 排列组合 · 人坐座位模型3：染色(空间))</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>LaTeX</t>
+        </is>
+      </c>
+      <c r="J464" s="2" t="inlineStr">
+        <is>
+          <t>将一个四棱锥的每一个顶点染上一种颜色，并使同一条棱上的两端异色，如果只有 $5$ 种颜色可供使用，则不同的染色方法种数是（　　）</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>$420$</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>$210$</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>$70$</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>$35$</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P464" s="2" t="inlineStr">
+        <is>
+          <t>**第一步：明确相邻关系**
+记四棱锥为 $S-ABCD$，棱为 $SA,SB,SC,SD,AB,BC,CD,DA$．
+关键：$A$ 与 $C$ **不相邻**（$B$ 与 $D$ 也不相邻），其余各对均相邻。
+**第二步：按 $S\to A\to C\to B\to D$ 的顺序染色**
+$S$：$5$ 种；$A$：$\neq S$，$4$ 种．
+**第三步：分两类讨论 $C$**
+**① $C$ 与 $A$ 同色**：$C$ 只有 $1$ 种（$=A$ 的颜色）．
+$B$ 与 $S,A,C$ 均相邻，需 $\neq A(=C)$、$\neq S$：$5-2=3$ 种；
+$D$ 与 $S,A,C$ 均相邻，同理 $3$ 种．
+$N_{1}=5\times4\times1\times3\times3=180$．
+**② $C$ 与 $A$ 异色**：$C$ 需 $\neq A$、$\neq S$：$5-2=3$ 种．
+$B$ 与 $S,A,C$ 均相邻：$5-3=2$ 种；$D$ 同理 $2$ 种．
+$N_{2}=5\times4\times3\times2\times2=240$．
+**第四步**：$N=N_{1}+N_{2}=180+240=420$．选 A．</t>
+        </is>
+      </c>
+      <c r="Q464" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>容易</t>
+        </is>
+      </c>
+      <c r="S464" t="n">
+        <v>5</v>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>2024高中数学热点题型归纳完整解析版.pdf · M-T-379-V1</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>教辅录入-第40批</t>
+        </is>
+      </c>
+      <c r="V464" s="2" t="inlineStr">
+        <is>
+          <t>★ 由详解「将不同的染色方案分为：$AC$ 相同和 $AC$ 不同两种情况，相加得到答案。按照 $SABCD$ 的顺序：当 $AC$ 相同时：染色方案为 $5\times4\times3\times1\times3=180$；当 $AC$ 不同时：染色方案为 $5\times4\times3\times2\times2=240$；不同的染色方案为 $420$ 种」还原。
+⚠ 详解第一类写作 $5\times4\times3\times1\times3$，顺序是「$S,A,B,C,D$」（第 $3$ 个因子是 $B$ 的 $3$ 种，第 $4$ 个是 $C$ 的 $1$ 种）；我在解答中按「$S,A,C,B,D$」排序写作 $5\times4\times1\times3\times3$。**两者只是相乘顺序不同，结果同为 $180$** ✓
+**独立验算**（用「$n$ 个点的色多项式」思路对拍）：
+① 图的结构：$S$ 与全部 $4$ 个底点相邻（度数 $4$）；底面是 $4$-圈 $A-B-C-D-A$；对角 $AC$、$BD$ **不连边**
+② **分类重算一次**（先定 $S$，再用 $4$ 色给 $4$-圈染色，但每点都 $\neq S$）：
+等价于用 $4$ 种颜色给 $4$-圈 $C_{4}$ 染色（相邻异色），色多项式 $P(C_{4},k)=(k-1)^{4}+(k-1)$，$k=4$：$3^{4}+3=81+3=84$
+乘 $S$ 的 $5$ 种：$5\times84=420$ ✓✓ **完全一致**
+③ 拆开验证：$84=$ 「$AC$ 同色」$+$「$AC$ 异色」
+$AC$ 同色：$4$（$A$ 的色）$\times1$（$C=A$）$\times3\times3=36$；$AC$ 异色：$4\times3\times2\times2=48$；$36+48=84$ ✓✓
+（与详解的 $180=5\times36$、$240=5\times48$ 完全对应）
+**答案 A 正确** ✓（**三种算法全部收敛到 420**）
+**⭐ 通法**：染色计数题的关键是找准**不相邻的顶点对**（本题是 $A,C$ 与 $B,D$），按「这对同色 / 异色」分类，其余点的可选数就都确定了。
+另外记一个能快速对拍的公式：**$n$-圈的色多项式** $P(C_{n},k)=(k-1)^{n}+(-1)^{n}(k-1)$。本题 $C_{4}$、$k=4$ 得 $84$，乘上锥顶的 $5$ 种即 $420$ —— 熟练后 $10$ 秒出答案。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
